--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -6549,25 +6549,25 @@
         <v>481</v>
       </c>
       <c r="G68" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="H68" t="n">
         <v>3.4</v>
       </c>
       <c r="I68" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
-        <v>0.3938223938223938</v>
+        <v>0.3852691218130311</v>
       </c>
       <c r="K68" t="n">
-        <v>0.277992277992278</v>
+        <v>0.2776203966005666</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3281853281853282</v>
+        <v>0.3371104815864023</v>
       </c>
       <c r="M68" t="n">
-        <v>0.05800653594771243</v>
+        <v>0.05942376950780304</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
@@ -6585,13 +6585,13 @@
         <v>1</v>
       </c>
       <c r="S68" t="n">
-        <v>0.1062129221359085</v>
+        <v>0.10658480352762</v>
       </c>
       <c r="T68" t="n">
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>0.1062129221359085</v>
+        <v>0.10658480352762</v>
       </c>
       <c r="V68" t="n">
         <v>0.3842052001281865</v>
@@ -7099,7 +7099,7 @@
         <v>484</v>
       </c>
       <c r="G74" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="H74" t="n">
         <v>3.4</v>
@@ -7108,16 +7108,16 @@
         <v>2.5</v>
       </c>
       <c r="J74" t="n">
-        <v>0.3479328694228407</v>
+        <v>0.3437815975733064</v>
       </c>
       <c r="K74" t="n">
-        <v>0.2762996316004912</v>
+        <v>0.2780586450960567</v>
       </c>
       <c r="L74" t="n">
-        <v>0.375767498976668</v>
+        <v>0.3781597573306371</v>
       </c>
       <c r="M74" t="n">
-        <v>0.06448801742919397</v>
+        <v>0.05775401069518704</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="n">
-        <v>1.298076923076923</v>
+        <v>1.30952380952381</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -12637,25 +12637,25 @@
         <v>594</v>
       </c>
       <c r="G146" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="H146" t="n">
         <v>3.5</v>
       </c>
       <c r="I146" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J146" t="n">
-        <v>0.4926019487549621</v>
+        <v>0.5022421524663677</v>
       </c>
       <c r="K146" t="n">
-        <v>0.2674124864669794</v>
+        <v>0.2654708520179372</v>
       </c>
       <c r="L146" t="n">
-        <v>0.2399855647780585</v>
+        <v>0.2322869955156951</v>
       </c>
       <c r="M146" t="n">
-        <v>0.06844033159822627</v>
+        <v>0.07625482625482616</v>
       </c>
       <c r="N146" t="n">
         <v>1</v>
@@ -12673,19 +12673,19 @@
         <v>1</v>
       </c>
       <c r="S146" t="n">
-        <v>0.2904844870607921</v>
+        <v>0.2808442833493865</v>
       </c>
       <c r="T146" t="n">
         <v>1</v>
       </c>
       <c r="U146" t="n">
-        <v>0.2904844870607921</v>
+        <v>0.2808442833493865</v>
       </c>
       <c r="V146" t="n">
         <v>0.7830864358157542</v>
       </c>
       <c r="W146" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
@@ -12735,25 +12735,25 @@
         <v>771</v>
       </c>
       <c r="G147" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="H147" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I147" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
-        <v>0.1649473486776882</v>
+        <v>0.1590214067278287</v>
       </c>
       <c r="K147" t="n">
-        <v>0.2495913828675545</v>
+        <v>0.2446483180428135</v>
       </c>
       <c r="L147" t="n">
-        <v>0.5854612684547574</v>
+        <v>0.5963302752293578</v>
       </c>
       <c r="M147" t="n">
-        <v>0.05435488883238682</v>
+        <v>0.04807692307692313</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
@@ -12771,19 +12771,19 @@
         <v>1</v>
       </c>
       <c r="S147" t="n">
-        <v>0.286323316151555</v>
+        <v>0.291266380976296</v>
       </c>
       <c r="T147" t="n">
         <v>0</v>
       </c>
       <c r="U147" t="n">
-        <v>0.286323316151555</v>
+        <v>0.291266380976296</v>
       </c>
       <c r="V147" t="n">
         <v>0.5359146990191095</v>
       </c>
       <c r="W147" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
@@ -13715,25 +13715,25 @@
         <v>773</v>
       </c>
       <c r="G157" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="H157" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I157" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="J157" t="n">
-        <v>0.5010684547933092</v>
+        <v>0.5826050769870995</v>
       </c>
       <c r="K157" t="n">
-        <v>0.2696927271387518</v>
+        <v>0.2476071577195173</v>
       </c>
       <c r="L157" t="n">
-        <v>0.229238818067939</v>
+        <v>0.1697877652933833</v>
       </c>
       <c r="M157" t="n">
-        <v>0.09056573449051752</v>
+        <v>0.1218487394957983</v>
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
@@ -13747,7 +13747,7 @@
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
       <c r="W157" t="n">
-        <v>1.25557461406518</v>
+        <v>1.184734513274336</v>
       </c>
       <c r="X157" t="inlineStr">
         <is>
@@ -13793,25 +13793,25 @@
         <v>773</v>
       </c>
       <c r="G158" t="n">
-        <v>4.14</v>
+        <v>3.25</v>
       </c>
       <c r="H158" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="I158" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="J158" t="n">
-        <v>0.2216320651496475</v>
+        <v>0.2734143106751153</v>
       </c>
       <c r="K158" t="n">
-        <v>0.247988310735011</v>
+        <v>0.261351914615919</v>
       </c>
       <c r="L158" t="n">
-        <v>0.5303796241153415</v>
+        <v>0.4652337747089658</v>
       </c>
       <c r="M158" t="n">
-        <v>0.08985084607100191</v>
+        <v>0.125370164175215</v>
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
@@ -13825,7 +13825,7 @@
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
       <c r="W158" t="n">
-        <v>1.220136286201022</v>
+        <v>1.203003875968992</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
@@ -13871,25 +13871,25 @@
         <v>773</v>
       </c>
       <c r="G159" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="H159" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I159" t="n">
-        <v>6.17</v>
+        <v>5</v>
       </c>
       <c r="J159" t="n">
-        <v>0.6227621063893677</v>
+        <v>0.5713922925528538</v>
       </c>
       <c r="K159" t="n">
-        <v>0.2288650740980926</v>
+        <v>0.2491905275855502</v>
       </c>
       <c r="L159" t="n">
-        <v>0.1483728195125398</v>
+        <v>0.1794171798615961</v>
       </c>
       <c r="M159" t="n">
-        <v>0.09234666313851303</v>
+        <v>0.1147204529370134</v>
       </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
@@ -13903,7 +13903,7 @@
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
       <c r="W159" t="n">
-        <v>1.187159685863874</v>
+        <v>1.19482496194825</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
@@ -13949,25 +13949,25 @@
         <v>773</v>
       </c>
       <c r="G160" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="H160" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I160" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="J160" t="n">
-        <v>0.2902468687989416</v>
+        <v>0.3457292271934921</v>
       </c>
       <c r="K160" t="n">
-        <v>0.2997631595792349</v>
+        <v>0.2765833817547937</v>
       </c>
       <c r="L160" t="n">
-        <v>0.4099899716218234</v>
+        <v>0.3776873910517141</v>
       </c>
       <c r="M160" t="n">
-        <v>0.09375966319287654</v>
+        <v>0.1124757595345831</v>
       </c>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
@@ -13981,7 +13981,7 @@
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
       <c r="W160" t="n">
-        <v>1.305669144981413</v>
+        <v>1.242570281124498</v>
       </c>
       <c r="X160" t="inlineStr">
         <is>
@@ -16401,28 +16401,28 @@
         <v>2</v>
       </c>
       <c r="O188" t="n">
-        <v>0.08782328920802665</v>
+        <v>0.0872820175588496</v>
       </c>
       <c r="P188" t="n">
-        <v>0.3046577231035404</v>
+        <v>0.3035668257168786</v>
       </c>
       <c r="Q188" t="n">
-        <v>0.6075189876884329</v>
+        <v>0.6091511567242718</v>
       </c>
       <c r="R188" t="n">
         <v>1</v>
       </c>
       <c r="S188" t="n">
-        <v>0.06680752523784006</v>
+        <v>0.06843969427367891</v>
       </c>
       <c r="T188" t="n">
         <v>2</v>
       </c>
       <c r="U188" t="n">
-        <v>0.06680752523784006</v>
+        <v>0.06843969427367891</v>
       </c>
       <c r="V188" t="n">
-        <v>0.6075189876884329</v>
+        <v>0.6091511567242718</v>
       </c>
       <c r="W188" t="n">
         <v>1.75</v>
@@ -16433,10 +16433,10 @@
         </is>
       </c>
       <c r="Y188" t="n">
-        <v>9.301357700623464</v>
+        <v>9.32634685872037</v>
       </c>
       <c r="Z188" t="n">
-        <v>9.301357700623464</v>
+        <v>9.32634685872037</v>
       </c>
       <c r="AA188" t="inlineStr">
         <is>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -9756,902 +9756,610 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>hallescher</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F107" t="n">
-        <v>551</v>
-      </c>
-      <c r="G107" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="H107" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I107" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0.1789903110657828</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0.2409484956654768</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0.5800611932687404</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0.06417039750373088</v>
-      </c>
-      <c r="N107" t="n">
-        <v>2</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0.1664549248772655</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0.1487827602374613</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0.6847623148852729</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
       <c r="R107" t="n">
         <v>1</v>
       </c>
-      <c r="S107" t="n">
-        <v>0.1047011216165326</v>
-      </c>
+      <c r="S107" t="inlineStr"/>
       <c r="T107" t="n">
-        <v>2</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0.1047011216165326</v>
-      </c>
-      <c r="V107" t="n">
-        <v>0.6847623148852729</v>
-      </c>
-      <c r="W107" t="n">
-        <v>1.62</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y107" t="n">
-        <v>12.13230199941425</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>12.13230199941425</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>dfb pokal</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>wehen</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F108" t="n">
-        <v>551</v>
-      </c>
-      <c r="G108" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H108" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I108" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0.2912772585669782</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0.2784267912772586</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0.4302959501557632</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0.05635540929658589</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="n">
         <v>2</v>
       </c>
       <c r="O108" t="n">
-        <v>0.2371626881820494</v>
+        <v>0.0971796147990323</v>
       </c>
       <c r="P108" t="n">
-        <v>0.1955269582216931</v>
+        <v>0.1193467756926307</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.5673103535962573</v>
+        <v>0.7834736095083371</v>
       </c>
       <c r="R108" t="n">
         <v>1</v>
       </c>
-      <c r="S108" t="n">
-        <v>0.1370144034404941</v>
-      </c>
+      <c r="S108" t="inlineStr"/>
       <c r="T108" t="n">
-        <v>2</v>
-      </c>
-      <c r="U108" t="n">
-        <v>0.1370144034404941</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U108" t="inlineStr"/>
       <c r="V108" t="n">
-        <v>0.5673103535962573</v>
-      </c>
-      <c r="W108" t="n">
-        <v>2.2</v>
-      </c>
+        <v>0.2165263904916629</v>
+      </c>
+      <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="Y108" t="n">
-        <v>10.05134246965305</v>
+        <v>1.450043520282718</v>
       </c>
       <c r="Z108" t="n">
-        <v>10.05134246965305</v>
+        <v>1.450043520282718</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>dfb pokal</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>wurzburger kickers</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F109" t="n">
-        <v>551</v>
-      </c>
-      <c r="G109" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="H109" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I109" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0.3677036001398113</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0.2757777001048585</v>
-      </c>
-      <c r="L109" t="n">
-        <v>0.3565186997553303</v>
-      </c>
-      <c r="M109" t="n">
-        <v>0.06650264668605077</v>
-      </c>
-      <c r="N109" t="n">
-        <v>2</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0.354926915744822</v>
-      </c>
-      <c r="P109" t="n">
-        <v>0.2495066794755585</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0.3955664047796192</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
       <c r="R109" t="n">
         <v>1</v>
       </c>
-      <c r="S109" t="n">
-        <v>0.03904770502428889</v>
-      </c>
+      <c r="S109" t="inlineStr"/>
       <c r="T109" t="n">
-        <v>2</v>
-      </c>
-      <c r="U109" t="n">
-        <v>0.03904770502428889</v>
-      </c>
-      <c r="V109" t="n">
-        <v>0.3955664047796192</v>
-      </c>
-      <c r="W109" t="n">
-        <v>2.63</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y109" t="n">
-        <v>7.008462614378747</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>7.008462614378747</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr"/>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>dfb pokal</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>ulm</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F110" t="n">
-        <v>551</v>
-      </c>
-      <c r="G110" t="n">
-        <v>7</v>
-      </c>
-      <c r="H110" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I110" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J110" t="n">
-        <v>0.1354436948624805</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0.210690192008303</v>
-      </c>
-      <c r="L110" t="n">
-        <v>0.6538661131292164</v>
-      </c>
-      <c r="M110" t="n">
-        <v>0.05473453749315826</v>
-      </c>
-      <c r="N110" t="n">
-        <v>2</v>
-      </c>
-      <c r="O110" t="n">
-        <v>0.1427096599821709</v>
-      </c>
-      <c r="P110" t="n">
-        <v>0.1812842175949421</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0.676006122422887</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
       <c r="R110" t="n">
         <v>1</v>
       </c>
-      <c r="S110" t="n">
-        <v>0.02214000929367066</v>
-      </c>
+      <c r="S110" t="inlineStr"/>
       <c r="T110" t="n">
-        <v>2</v>
-      </c>
-      <c r="U110" t="n">
-        <v>0.02214000929367066</v>
-      </c>
-      <c r="V110" t="n">
-        <v>0.676006122422887</v>
-      </c>
-      <c r="W110" t="n">
-        <v>1.45</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y110" t="n">
-        <v>11.97716383101715</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>11.97716383101715</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr"/>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>dfb pokal</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>aue</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F111" t="n">
-        <v>551</v>
-      </c>
-      <c r="G111" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H111" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I111" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J111" t="n">
-        <v>0.6297577854671281</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0.2249134948096886</v>
-      </c>
-      <c r="L111" t="n">
-        <v>0.1453287197231834</v>
-      </c>
-      <c r="M111" t="n">
-        <v>0.0586080586080584</v>
-      </c>
-      <c r="N111" t="n">
-        <v>1</v>
-      </c>
-      <c r="O111" t="n">
-        <v>0.5735556639085384</v>
-      </c>
-      <c r="P111" t="n">
-        <v>0.275418703280472</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>0.1510256328109897</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
       <c r="R111" t="n">
         <v>1</v>
       </c>
-      <c r="S111" t="n">
-        <v>-0.05620212155858972</v>
-      </c>
+      <c r="S111" t="inlineStr"/>
       <c r="T111" t="n">
-        <v>1</v>
-      </c>
-      <c r="U111" t="n">
-        <v>-0.05620212155858972</v>
-      </c>
-      <c r="V111" t="n">
-        <v>0.5735556639085384</v>
-      </c>
-      <c r="W111" t="n">
-        <v>1.5</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y111" t="n">
-        <v>10.16199398937248</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>10.16199398937248</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr"/>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>dfb pokal</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>schott mainz</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>greuther furth</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F112" t="n">
-        <v>551</v>
-      </c>
-      <c r="G112" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H112" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I112" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0.4603234298608499</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0.2775479503572771</v>
-      </c>
-      <c r="L112" t="n">
-        <v>0.2621286197818729</v>
-      </c>
-      <c r="M112" t="n">
-        <v>0.05970030288538197</v>
-      </c>
-      <c r="N112" t="n">
-        <v>1</v>
-      </c>
-      <c r="O112" t="n">
-        <v>0.4547109040248056</v>
-      </c>
-      <c r="P112" t="n">
-        <v>0.260593877861823</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0.2846952181133715</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
       <c r="R112" t="n">
         <v>1</v>
       </c>
-      <c r="S112" t="n">
-        <v>-0.005612525836044324</v>
-      </c>
+      <c r="S112" t="inlineStr"/>
       <c r="T112" t="n">
-        <v>1</v>
-      </c>
-      <c r="U112" t="n">
-        <v>-0.005612525836044324</v>
-      </c>
-      <c r="V112" t="n">
-        <v>0.4547109040248056</v>
-      </c>
-      <c r="W112" t="n">
-        <v>2.05</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y112" t="n">
-        <v>8.056357498265502</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>8.056357498265502</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>dfb pokal</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.4375</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>aalen</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>schalke</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F113" t="n">
-        <v>551</v>
-      </c>
-      <c r="G113" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H113" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I113" t="n">
-        <v>2</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0.2705667276051188</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0.2559414990859232</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0.473491773308958</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0.05598455598455598</v>
-      </c>
-      <c r="N113" t="n">
-        <v>2</v>
-      </c>
-      <c r="O113" t="n">
-        <v>0.3483132254346947</v>
-      </c>
-      <c r="P113" t="n">
-        <v>0.2281432612817216</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0.4235435132835836</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
       <c r="R113" t="n">
         <v>1</v>
       </c>
-      <c r="S113" t="n">
-        <v>-0.04994826002537434</v>
-      </c>
+      <c r="S113" t="inlineStr"/>
       <c r="T113" t="n">
-        <v>2</v>
-      </c>
-      <c r="U113" t="n">
-        <v>-0.04994826002537434</v>
-      </c>
-      <c r="V113" t="n">
-        <v>0.4235435132835836</v>
-      </c>
-      <c r="W113" t="n">
-        <v>2</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y113" t="n">
-        <v>7.504148083719076</v>
-      </c>
-      <c r="Z113" t="n">
-        <v>7.504148083719076</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr"/>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>dfb pokal</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.4375</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>greifswald</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F114" t="n">
-        <v>551</v>
-      </c>
-      <c r="G114" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H114" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I114" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0.4228527011270889</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0.2798289933929266</v>
-      </c>
-      <c r="L114" t="n">
-        <v>0.2973183054799844</v>
-      </c>
-      <c r="M114" t="n">
-        <v>0.05106209150326801</v>
-      </c>
-      <c r="N114" t="n">
-        <v>1</v>
-      </c>
-      <c r="O114" t="n">
-        <v>0.3836468384032026</v>
-      </c>
-      <c r="P114" t="n">
-        <v>0.2369855400499945</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>0.3793676215468028</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
       <c r="R114" t="n">
         <v>1</v>
       </c>
-      <c r="S114" t="n">
-        <v>-0.03920586272388638</v>
-      </c>
+      <c r="S114" t="inlineStr"/>
       <c r="T114" t="n">
-        <v>1</v>
-      </c>
-      <c r="U114" t="n">
-        <v>-0.03920586272388638</v>
-      </c>
-      <c r="V114" t="n">
-        <v>0.3836468384032026</v>
-      </c>
-      <c r="W114" t="n">
-        <v>2.25</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y114" t="n">
-        <v>6.79727725000165</v>
-      </c>
-      <c r="Z114" t="n">
-        <v>6.79727725000165</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr"/>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>dfb pokal</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.4375</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>ingolstadt</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>kaiserslautern</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F115" t="n">
-        <v>551</v>
-      </c>
-      <c r="G115" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H115" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I115" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0.4603234298608499</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0.2775479503572771</v>
-      </c>
-      <c r="L115" t="n">
-        <v>0.2621286197818729</v>
-      </c>
-      <c r="M115" t="n">
-        <v>0.05970030288538197</v>
-      </c>
-      <c r="N115" t="n">
-        <v>1</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0.4366857274476634</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0.2827917961495244</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0.2805224764028122</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
       <c r="R115" t="n">
         <v>1</v>
       </c>
-      <c r="S115" t="n">
-        <v>-0.02363770241318652</v>
-      </c>
+      <c r="S115" t="inlineStr"/>
       <c r="T115" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" t="n">
-        <v>-0.02363770241318652</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0.4366857274476634</v>
-      </c>
-      <c r="W115" t="n">
-        <v>2.05</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y115" t="n">
-        <v>7.736995756135612</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>7.736995756135612</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>dfb pokal</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>hallescher</t>
+          <t>rw essen</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -10702,20 +10410,20 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>wehen</t>
+          <t>vfl osnabruck</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -10735,13 +10443,13 @@
         <v>2</v>
       </c>
       <c r="O117" t="n">
-        <v>0.0971796147990323</v>
+        <v>0.05890705866981628</v>
       </c>
       <c r="P117" t="n">
-        <v>0.1193467756926307</v>
+        <v>0.0850825161689492</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.7834736095083371</v>
+        <v>0.8560104251612345</v>
       </c>
       <c r="R117" t="n">
         <v>1</v>
@@ -10752,7 +10460,7 @@
       </c>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="n">
-        <v>0.2165263904916629</v>
+        <v>0.1439895748387655</v>
       </c>
       <c r="W117" t="inlineStr"/>
       <c r="X117" t="inlineStr">
@@ -10761,10 +10469,10 @@
         </is>
       </c>
       <c r="Y117" t="n">
-        <v>1.450043520282718</v>
+        <v>0.9642757610705874</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.450043520282718</v>
+        <v>0.9642757610705874</v>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
@@ -10780,20 +10488,20 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>wurzburger kickers</t>
+          <t>villingen</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -10844,20 +10552,20 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ulm</t>
+          <t>alemannia aachen</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -10908,20 +10616,20 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>aue</t>
+          <t>arminia bielefeld</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>hannover</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -10972,20 +10680,20 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>schott mainz</t>
+          <t>I1Vk6k3R</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>greuther furth</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -11036,20 +10744,20 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>aalen</t>
+          <t>saarbrucken</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>schalke</t>
+          <t>nurnberg</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -11100,20 +10808,20 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>greifswald</t>
+          <t>viktoria berlin</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -11164,20 +10872,20 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ingolstadt</t>
+          <t>bremer</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>kaiserslautern</t>
+          <t>paderborn</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -11228,20 +10936,20 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>rw essen</t>
+          <t>hansa rostock</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>hertha berlin</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -11257,27 +10965,41 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
+      <c r="N125" t="n">
+        <v>2</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.1794567954919975</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.1125722033075784</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.7079710012004241</v>
+      </c>
       <c r="R125" t="n">
         <v>1</v>
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="n">
-        <v>-100</v>
+        <v>-2</v>
       </c>
       <c r="U125" t="inlineStr"/>
-      <c r="V125" t="inlineStr"/>
+      <c r="V125" t="n">
+        <v>0.2920289987995759</v>
+      </c>
       <c r="W125" t="inlineStr"/>
       <c r="X125" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr"/>
-      <c r="Z125" t="inlineStr"/>
+      <c r="Y125" t="n">
+        <v>1.955672731081154</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>1.955672731081154</v>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>germany</t>
@@ -11292,20 +11014,20 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>vfl osnabruck</t>
+          <t>E3xs5mIe</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>elversberg</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -11321,41 +11043,27 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="n">
-        <v>2</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0.05890705866981628</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0.0850825161689492</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0.8560104251612345</v>
-      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
       <c r="R126" t="n">
         <v>1</v>
       </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="n">
-        <v>-2</v>
+        <v>-100</v>
       </c>
       <c r="U126" t="inlineStr"/>
-      <c r="V126" t="n">
-        <v>0.1439895748387655</v>
-      </c>
+      <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr"/>
       <c r="X126" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="Y126" t="n">
-        <v>0.9642757610705874</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>0.9642757610705874</v>
-      </c>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr"/>
       <c r="AA126" t="inlineStr">
         <is>
           <t>germany</t>
@@ -11370,20 +11078,20 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>villingen</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -11434,20 +11142,20 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>alemannia aachen</t>
+          <t>sandhausen</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>fc koln</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -11498,20 +11206,20 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>arminia bielefeld</t>
+          <t>teutonia ottensen</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>hannover</t>
+          <t>darmstadt</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -11562,20 +11270,20 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>I1Vk6k3R</t>
+          <t>lotte</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>karlsruher sc</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -11626,20 +11334,20 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>saarbrucken</t>
+          <t>meppen</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>nurnberg</t>
+          <t>hamburger sv</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -11690,20 +11398,20 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>viktoria berlin</t>
+          <t>sg dynamo dresden</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>dusseldorf</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -11754,20 +11462,20 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>bremer</t>
+          <t>cottbus</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>paderborn</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -11818,20 +11526,20 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>hansa rostock</t>
+          <t>offenbach</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>hertha berlin</t>
+          <t>magdeburg</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -11847,41 +11555,27 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" t="n">
-        <v>2</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0.1794567954919975</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0.1125722033075784</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0.7079710012004241</v>
-      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
       <c r="R134" t="n">
         <v>1</v>
       </c>
       <c r="S134" t="inlineStr"/>
       <c r="T134" t="n">
-        <v>-2</v>
+        <v>-100</v>
       </c>
       <c r="U134" t="inlineStr"/>
-      <c r="V134" t="n">
-        <v>0.2920289987995759</v>
-      </c>
+      <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr"/>
       <c r="X134" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="Y134" t="n">
-        <v>1.955672731081154</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>1.955672731081154</v>
-      </c>
+      <c r="Y134" t="inlineStr"/>
+      <c r="Z134" t="inlineStr"/>
       <c r="AA134" t="inlineStr">
         <is>
           <t>germany</t>
@@ -11896,20 +11590,20 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>E3xs5mIe</t>
+          <t>tus koblenz</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>elversberg</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -11960,20 +11654,20 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.65625</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>braunschweig</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -11989,27 +11683,41 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
+      <c r="N136" t="n">
+        <v>2</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.03866522508709244</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.0701925108605358</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.8911422640523718</v>
+      </c>
       <c r="R136" t="n">
         <v>1</v>
       </c>
       <c r="S136" t="inlineStr"/>
       <c r="T136" t="n">
-        <v>-100</v>
+        <v>-2</v>
       </c>
       <c r="U136" t="inlineStr"/>
-      <c r="V136" t="inlineStr"/>
+      <c r="V136" t="n">
+        <v>0.1088577359476282</v>
+      </c>
       <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="Y136" t="inlineStr"/>
-      <c r="Z136" t="inlineStr"/>
+      <c r="Y136" t="n">
+        <v>0.7290033066411972</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.7290033066411972</v>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>germany</t>
@@ -12024,56 +11732,90 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>sandhausen</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>fc koln</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="E137" t="n">
         <v>59</v>
       </c>
       <c r="F137" t="n">
-        <v>593</v>
-      </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
+        <v>594</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H137" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I137" t="n">
+        <v>4</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.5022421524663677</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.2654708520179372</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2322869955156951</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.07625482625482616</v>
+      </c>
+      <c r="N137" t="n">
+        <v>1</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.7830864358157542</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.04088231273115332</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.1760312514530925</v>
+      </c>
       <c r="R137" t="n">
         <v>1</v>
       </c>
-      <c r="S137" t="inlineStr"/>
+      <c r="S137" t="n">
+        <v>0.2808442833493865</v>
+      </c>
       <c r="T137" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U137" t="inlineStr"/>
-      <c r="V137" t="inlineStr"/>
-      <c r="W137" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.2808442833493865</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.7830864358157542</v>
+      </c>
+      <c r="W137" t="n">
+        <v>1.85</v>
+      </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr"/>
-      <c r="Z137" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y137" t="n">
+        <v>5.24420792078758</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>5.24420792078758</v>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>germany</t>
@@ -12081,651 +11823,909 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>super cup</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>O2Fteteo</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.5625</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>teutonia ottensen</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>darmstadt</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F138" t="n">
-        <v>593</v>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G138" t="n">
+        <v>6</v>
+      </c>
+      <c r="H138" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.1590214067278287</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.2446483180428135</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.5963302752293578</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.04807692307692313</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.2287387667007373</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.5359146990191095</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.2353465342801532</v>
+      </c>
       <c r="R138" t="n">
         <v>1</v>
       </c>
-      <c r="S138" t="inlineStr"/>
+      <c r="S138" t="n">
+        <v>0.291266380976296</v>
+      </c>
       <c r="T138" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U138" t="inlineStr"/>
-      <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.291266380976296</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.5359146990191095</v>
+      </c>
+      <c r="W138" t="n">
+        <v>3.9</v>
+      </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr"/>
-      <c r="Z138" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y138" t="n">
+        <v>6.408519536582851</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>6.408519536582851</v>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>serie a</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>Sf88FVcc</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45521.5625</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>lotte</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>karlsruher sc</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F139" t="n">
-        <v>593</v>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H139" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.2858844550327576</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.2948183442525313</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.4192972007147112</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.0599747474747474</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.2725231151948335</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3956846156670256</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3317922691381407</v>
+      </c>
       <c r="R139" t="n">
         <v>1</v>
       </c>
-      <c r="S139" t="inlineStr"/>
+      <c r="S139" t="n">
+        <v>0.1008662714144943</v>
+      </c>
       <c r="T139" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U139" t="inlineStr"/>
-      <c r="V139" t="inlineStr"/>
-      <c r="W139" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.1008662714144943</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3956846156670256</v>
+      </c>
+      <c r="W139" t="n">
+        <v>3.2</v>
+      </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr"/>
-      <c r="Z139" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y139" t="n">
+        <v>4.731634706920012</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>4.731634706920012</v>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>serie a</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>0lGMiS5j</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45521.65625</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>meppen</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>hamburger sv</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F140" t="n">
-        <v>593</v>
-      </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H140" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I140" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.5439668439257036</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.2767831294092551</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.1792500266650414</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.06262851961593885</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.4400086634656995</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.4942897790766149</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.06570155745768574</v>
+      </c>
       <c r="R140" t="n">
         <v>1</v>
       </c>
-      <c r="S140" t="inlineStr"/>
+      <c r="S140" t="n">
+        <v>0.2175066496673598</v>
+      </c>
       <c r="T140" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U140" t="inlineStr"/>
-      <c r="V140" t="inlineStr"/>
-      <c r="W140" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.2175066496673598</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.4942897790766149</v>
+      </c>
+      <c r="W140" t="n">
+        <v>3.4</v>
+      </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr"/>
-      <c r="Z140" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y140" t="n">
+        <v>5.910764738760704</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>5.910764738760704</v>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>serie a</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>hKOA02XN</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45521.65625</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>sg dynamo dresden</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>dusseldorf</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F141" t="n">
-        <v>593</v>
-      </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H141" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I141" t="n">
+        <v>3</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.392156862745098</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3137254901960784</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3447548041594359</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3527536688143402</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3024915270262238</v>
+      </c>
       <c r="R141" t="n">
         <v>1</v>
       </c>
-      <c r="S141" t="inlineStr"/>
+      <c r="S141" t="n">
+        <v>0.05863602175551663</v>
+      </c>
       <c r="T141" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U141" t="inlineStr"/>
-      <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.05863602175551663</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3527536688143402</v>
+      </c>
+      <c r="W141" t="n">
+        <v>3.2</v>
+      </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr"/>
-      <c r="Z141" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y141" t="n">
+        <v>4.218262313639893</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>4.218262313639893</v>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>serie a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>4xHh663n</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.5625</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>cottbus</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F142" t="n">
-        <v>593</v>
-      </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H142" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I142" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.511293669135136</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.2702552251142862</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.2184511057505777</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.0572017084719163</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.4272144406220799</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3766028498451762</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.1961827095327438</v>
+      </c>
       <c r="R142" t="n">
         <v>1</v>
       </c>
-      <c r="S142" t="inlineStr"/>
+      <c r="S142" t="n">
+        <v>-0.0840792285130561</v>
+      </c>
       <c r="T142" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U142" t="inlineStr"/>
-      <c r="V142" t="inlineStr"/>
-      <c r="W142" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U142" t="n">
+        <v>-0.0840792285130561</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.4272144406220799</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1.85</v>
+      </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr"/>
-      <c r="Z142" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y142" t="n">
+        <v>5.108671387532308</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>5.108671387532308</v>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>serie a</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>6RvR2hEi</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.5625</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>offenbach</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>magdeburg</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F143" t="n">
-        <v>593</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G143" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H143" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.2259083728278041</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.287519747235387</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.4865718799368088</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.05394605394605412</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.2314049743946865</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.5173633450324683</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.2512316805728451</v>
+      </c>
       <c r="R143" t="n">
         <v>1</v>
       </c>
-      <c r="S143" t="inlineStr"/>
+      <c r="S143" t="n">
+        <v>0.2298435977970813</v>
+      </c>
       <c r="T143" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U143" t="inlineStr"/>
-      <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.2298435977970813</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.5173633450324683</v>
+      </c>
+      <c r="W143" t="n">
+        <v>3.3</v>
+      </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr"/>
-      <c r="Z143" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y143" t="n">
+        <v>6.186680660599315</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>6.186680660599315</v>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>serie a</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>YH892O2B</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.65625</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>tus koblenz</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F144" t="n">
-        <v>593</v>
-      </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H144" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0.2411347517730496</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0.276595744680851</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.4822695035460993</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.06334841628959298</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0.243982251206936</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0.4947117110728264</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0.2613060377202377</v>
+      </c>
       <c r="R144" t="n">
         <v>1</v>
       </c>
-      <c r="S144" t="inlineStr"/>
+      <c r="S144" t="n">
+        <v>0.2181159663919753</v>
+      </c>
       <c r="T144" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U144" t="inlineStr"/>
-      <c r="V144" t="inlineStr"/>
-      <c r="W144" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0.2181159663919753</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0.4947117110728264</v>
+      </c>
+      <c r="W144" t="n">
+        <v>3.4</v>
+      </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr"/>
-      <c r="Z144" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y144" t="n">
+        <v>5.915810242169697</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>5.915810242169697</v>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>serie a</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>8jyraADG</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45522.65625</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>braunschweig</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F145" t="n">
-        <v>593</v>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H145" t="n">
+        <v>4</v>
+      </c>
+      <c r="I145" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.6380263717566993</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0.2360697575499787</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.125903870693322</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.05900900900900896</v>
+      </c>
       <c r="N145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O145" t="n">
-        <v>0.03866522508709244</v>
+        <v>0.4688481526967667</v>
       </c>
       <c r="P145" t="n">
-        <v>0.0701925108605358</v>
+        <v>0.4645031770758087</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.8911422640523718</v>
+        <v>0.06664867022742459</v>
       </c>
       <c r="R145" t="n">
         <v>1</v>
       </c>
-      <c r="S145" t="inlineStr"/>
+      <c r="S145" t="n">
+        <v>-0.1691782190599326</v>
+      </c>
       <c r="T145" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U145" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U145" t="n">
+        <v>-0.1691782190599326</v>
+      </c>
       <c r="V145" t="n">
-        <v>0.1088577359476282</v>
-      </c>
-      <c r="W145" t="inlineStr"/>
+        <v>0.4688481526967667</v>
+      </c>
+      <c r="W145" t="n">
+        <v>1.48</v>
+      </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y145" t="n">
-        <v>0.7290033066411972</v>
+        <v>5.606531322517188</v>
       </c>
       <c r="Z145" t="n">
-        <v>0.7290033066411972</v>
+        <v>5.606531322517188</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>serie a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>fcxqFy2l</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45523.5625</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F146" t="n">
-        <v>594</v>
+        <v>771</v>
       </c>
       <c r="G146" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H146" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I146" t="n">
         <v>1.85</v>
       </c>
-      <c r="H146" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I146" t="n">
-        <v>4</v>
-      </c>
       <c r="J146" t="n">
-        <v>0.5022421524663677</v>
+        <v>0.23125</v>
       </c>
       <c r="K146" t="n">
-        <v>0.2654708520179372</v>
+        <v>0.25625</v>
       </c>
       <c r="L146" t="n">
-        <v>0.2322869955156951</v>
+        <v>0.5125</v>
       </c>
       <c r="M146" t="n">
-        <v>0.07625482625482616</v>
+        <v>0.05471324983520098</v>
       </c>
       <c r="N146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>0.7830864358157542</v>
+        <v>0.2651006284586224</v>
       </c>
       <c r="P146" t="n">
-        <v>0.04088231273115332</v>
+        <v>0.406726162603766</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.1760312514530925</v>
+        <v>0.3281732089376114</v>
       </c>
       <c r="R146" t="n">
         <v>1</v>
       </c>
       <c r="S146" t="n">
-        <v>0.2808442833493865</v>
+        <v>0.1504761626037661</v>
       </c>
       <c r="T146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>0.2808442833493865</v>
+        <v>0.1504761626037661</v>
       </c>
       <c r="V146" t="n">
-        <v>0.7830864358157542</v>
+        <v>0.406726162603766</v>
       </c>
       <c r="W146" t="n">
-        <v>1.85</v>
+        <v>3.7</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y146" t="n">
-        <v>5.24420792078758</v>
+        <v>4.8636705876072</v>
       </c>
       <c r="Z146" t="n">
-        <v>5.24420792078758</v>
+        <v>4.8636705876072</v>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>super cup</t>
+          <t>serie a</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45523.65625</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -12735,55 +12735,55 @@
         <v>771</v>
       </c>
       <c r="G147" t="n">
-        <v>6</v>
+        <v>1.33</v>
       </c>
       <c r="H147" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="J147" t="n">
-        <v>0.1590214067278287</v>
+        <v>0.7112375533428166</v>
       </c>
       <c r="K147" t="n">
-        <v>0.2446483180428135</v>
+        <v>0.1891891891891892</v>
       </c>
       <c r="L147" t="n">
-        <v>0.5963302752293578</v>
+        <v>0.09957325746799432</v>
       </c>
       <c r="M147" t="n">
-        <v>0.04807692307692313</v>
+        <v>0.05714285714285694</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O147" t="n">
-        <v>0.2287387667007373</v>
+        <v>0.4889679156451812</v>
       </c>
       <c r="P147" t="n">
-        <v>0.5359146990191095</v>
+        <v>0.4566736230579956</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.2353465342801532</v>
+        <v>0.05435846129682308</v>
       </c>
       <c r="R147" t="n">
         <v>1</v>
       </c>
       <c r="S147" t="n">
-        <v>0.291266380976296</v>
+        <v>-0.2222696376976354</v>
       </c>
       <c r="T147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U147" t="n">
-        <v>0.291266380976296</v>
+        <v>-0.2222696376976354</v>
       </c>
       <c r="V147" t="n">
-        <v>0.5359146990191095</v>
+        <v>0.4889679156451812</v>
       </c>
       <c r="W147" t="n">
-        <v>3.9</v>
+        <v>1.33</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Y147" t="n">
-        <v>6.408519536582851</v>
+        <v>5.847125383777921</v>
       </c>
       <c r="Z147" t="n">
-        <v>6.408519536582851</v>
+        <v>5.847125383777921</v>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
@@ -12810,90 +12810,70 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>f9bfyqFM</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45507.54166666666</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>carrarese</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>catania</t>
         </is>
       </c>
       <c r="E148" t="n">
         <v>77</v>
       </c>
       <c r="F148" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G148" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="H148" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="I148" t="n">
-        <v>2.25</v>
+        <v>5.25</v>
       </c>
       <c r="J148" t="n">
-        <v>0.2858844550327576</v>
+        <v>0.5826050769870995</v>
       </c>
       <c r="K148" t="n">
-        <v>0.2948183442525313</v>
+        <v>0.2476071577195173</v>
       </c>
       <c r="L148" t="n">
-        <v>0.4192972007147112</v>
+        <v>0.1697877652933833</v>
       </c>
       <c r="M148" t="n">
-        <v>0.0599747474747474</v>
-      </c>
-      <c r="N148" t="n">
-        <v>0</v>
-      </c>
-      <c r="O148" t="n">
-        <v>0.2725231151948335</v>
-      </c>
-      <c r="P148" t="n">
-        <v>0.3956846156670256</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>0.3317922691381407</v>
-      </c>
-      <c r="R148" t="n">
-        <v>1</v>
-      </c>
-      <c r="S148" t="n">
-        <v>0.1008662714144943</v>
-      </c>
+        <v>0.1218487394957983</v>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr"/>
       <c r="T148" t="n">
-        <v>0</v>
-      </c>
-      <c r="U148" t="n">
-        <v>0.1008662714144943</v>
-      </c>
-      <c r="V148" t="n">
-        <v>0.3956846156670256</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
       <c r="W148" t="n">
-        <v>3.2</v>
+        <v>1.184734513274336</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y148" t="n">
-        <v>4.731634706920012</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>4.731634706920012</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr"/>
+      <c r="Z148" t="inlineStr"/>
       <c r="AA148" t="inlineStr">
         <is>
           <t>italy</t>
@@ -12901,97 +12881,77 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>coppa italia</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>bHLf4sq9</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45507.64583333334</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>UiGfvfvT</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>mantova</t>
         </is>
       </c>
       <c r="E149" t="n">
         <v>77</v>
       </c>
       <c r="F149" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G149" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="H149" t="n">
         <v>3.4</v>
       </c>
       <c r="I149" t="n">
-        <v>5.25</v>
+        <v>1.91</v>
       </c>
       <c r="J149" t="n">
-        <v>0.5439668439257036</v>
+        <v>0.2734143106751153</v>
       </c>
       <c r="K149" t="n">
-        <v>0.2767831294092551</v>
+        <v>0.261351914615919</v>
       </c>
       <c r="L149" t="n">
-        <v>0.1792500266650414</v>
+        <v>0.4652337747089658</v>
       </c>
       <c r="M149" t="n">
-        <v>0.06262851961593885</v>
-      </c>
-      <c r="N149" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" t="n">
-        <v>0.4400086634656995</v>
-      </c>
-      <c r="P149" t="n">
-        <v>0.4942897790766149</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>0.06570155745768574</v>
-      </c>
-      <c r="R149" t="n">
-        <v>1</v>
-      </c>
-      <c r="S149" t="n">
-        <v>0.2175066496673598</v>
-      </c>
+        <v>0.125370164175215</v>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr"/>
       <c r="T149" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" t="n">
-        <v>0.2175066496673598</v>
-      </c>
-      <c r="V149" t="n">
-        <v>0.4942897790766149</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
       <c r="W149" t="n">
-        <v>3.4</v>
+        <v>1.203003875968992</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y149" t="n">
-        <v>5.910764738760704</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>5.910764738760704</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr"/>
+      <c r="Z149" t="inlineStr"/>
       <c r="AA149" t="inlineStr">
         <is>
           <t>italy</t>
@@ -12999,97 +12959,77 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>coppa italia</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45508.64583333334</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>cesena</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>padova</t>
         </is>
       </c>
       <c r="E150" t="n">
         <v>77</v>
       </c>
       <c r="F150" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G150" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="H150" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="I150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J150" t="n">
-        <v>0.392156862745098</v>
+        <v>0.5713922925528538</v>
       </c>
       <c r="K150" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2491905275855502</v>
       </c>
       <c r="L150" t="n">
-        <v>0.3137254901960784</v>
+        <v>0.1794171798615961</v>
       </c>
       <c r="M150" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0.3447548041594359</v>
-      </c>
-      <c r="P150" t="n">
-        <v>0.3527536688143402</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>0.3024915270262238</v>
-      </c>
-      <c r="R150" t="n">
-        <v>1</v>
-      </c>
-      <c r="S150" t="n">
-        <v>0.05863602175551663</v>
-      </c>
+        <v>0.1147204529370134</v>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr"/>
       <c r="T150" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" t="n">
-        <v>0.05863602175551663</v>
-      </c>
-      <c r="V150" t="n">
-        <v>0.3527536688143402</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
       <c r="W150" t="n">
-        <v>3.2</v>
+        <v>1.19482496194825</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y150" t="n">
-        <v>4.218262313639893</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>4.218262313639893</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="inlineStr"/>
       <c r="AA150" t="inlineStr">
         <is>
           <t>italy</t>
@@ -13097,97 +13037,77 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>coppa italia</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45508.65625</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>avellino</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>juve stabia</t>
         </is>
       </c>
       <c r="E151" t="n">
         <v>77</v>
       </c>
       <c r="F151" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G151" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="H151" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="I151" t="n">
-        <v>4.33</v>
+        <v>2.38</v>
       </c>
       <c r="J151" t="n">
-        <v>0.511293669135136</v>
+        <v>0.3457292271934921</v>
       </c>
       <c r="K151" t="n">
-        <v>0.2702552251142862</v>
+        <v>0.2765833817547937</v>
       </c>
       <c r="L151" t="n">
-        <v>0.2184511057505777</v>
+        <v>0.3776873910517141</v>
       </c>
       <c r="M151" t="n">
-        <v>0.0572017084719163</v>
-      </c>
-      <c r="N151" t="n">
-        <v>1</v>
-      </c>
-      <c r="O151" t="n">
-        <v>0.4272144406220799</v>
-      </c>
-      <c r="P151" t="n">
-        <v>0.3766028498451762</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>0.1961827095327438</v>
-      </c>
-      <c r="R151" t="n">
-        <v>1</v>
-      </c>
-      <c r="S151" t="n">
-        <v>-0.0840792285130561</v>
-      </c>
+        <v>0.1124757595345831</v>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr"/>
       <c r="T151" t="n">
-        <v>1</v>
-      </c>
-      <c r="U151" t="n">
-        <v>-0.0840792285130561</v>
-      </c>
-      <c r="V151" t="n">
-        <v>0.4272144406220799</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
       <c r="W151" t="n">
-        <v>1.85</v>
+        <v>1.242570281124498</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y151" t="n">
-        <v>5.108671387532308</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>5.108671387532308</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr"/>
       <c r="AA151" t="inlineStr">
         <is>
           <t>italy</t>
@@ -13195,96 +13115,76 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>coppa italia</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45513.54166666666</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>sassuolo</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>cittadella</t>
         </is>
       </c>
       <c r="E152" t="n">
         <v>77</v>
       </c>
       <c r="F152" t="n">
-        <v>771</v>
-      </c>
-      <c r="G152" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H152" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I152" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J152" t="n">
-        <v>0.2259083728278041</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0.287519747235387</v>
-      </c>
-      <c r="L152" t="n">
-        <v>0.4865718799368088</v>
-      </c>
-      <c r="M152" t="n">
-        <v>0.05394605394605412</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O152" t="n">
-        <v>0.2314049743946865</v>
+        <v>0.4694967552742121</v>
       </c>
       <c r="P152" t="n">
-        <v>0.5173633450324683</v>
+        <v>0.4042830898537844</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.2512316805728451</v>
+        <v>0.1262201548720035</v>
       </c>
       <c r="R152" t="n">
         <v>1</v>
       </c>
-      <c r="S152" t="n">
-        <v>0.2298435977970813</v>
-      </c>
+      <c r="S152" t="inlineStr"/>
       <c r="T152" t="n">
-        <v>0</v>
-      </c>
-      <c r="U152" t="n">
-        <v>0.2298435977970813</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U152" t="inlineStr"/>
       <c r="V152" t="n">
-        <v>0.5173633450324683</v>
-      </c>
-      <c r="W152" t="n">
-        <v>3.3</v>
-      </c>
+        <v>0.5305032447257878</v>
+      </c>
+      <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y152" t="n">
-        <v>6.186680660599315</v>
+        <v>6.343808845453178</v>
       </c>
       <c r="Z152" t="n">
-        <v>6.186680660599315</v>
+        <v>6.343808845453178</v>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
@@ -13293,96 +13193,76 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>coppa italia</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45513.65625</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>reggiana</t>
         </is>
       </c>
       <c r="E153" t="n">
         <v>77</v>
       </c>
       <c r="F153" t="n">
-        <v>771</v>
-      </c>
-      <c r="G153" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H153" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I153" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J153" t="n">
-        <v>0.2411347517730496</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0.276595744680851</v>
-      </c>
-      <c r="L153" t="n">
-        <v>0.4822695035460993</v>
-      </c>
-      <c r="M153" t="n">
-        <v>0.06334841628959298</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O153" t="n">
-        <v>0.243982251206936</v>
+        <v>0.4727240812949189</v>
       </c>
       <c r="P153" t="n">
-        <v>0.4947117110728264</v>
+        <v>0.4071627836349588</v>
       </c>
       <c r="Q153" t="n">
-        <v>0.2613060377202377</v>
+        <v>0.1201131350701222</v>
       </c>
       <c r="R153" t="n">
         <v>1</v>
       </c>
-      <c r="S153" t="n">
-        <v>0.2181159663919753</v>
-      </c>
+      <c r="S153" t="inlineStr"/>
       <c r="T153" t="n">
-        <v>0</v>
-      </c>
-      <c r="U153" t="n">
-        <v>0.2181159663919753</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U153" t="inlineStr"/>
       <c r="V153" t="n">
-        <v>0.4947117110728264</v>
-      </c>
-      <c r="W153" t="n">
-        <v>3.4</v>
-      </c>
+        <v>0.5272759187050811</v>
+      </c>
+      <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y153" t="n">
-        <v>5.915810242169697</v>
+        <v>6.305216170364257</v>
       </c>
       <c r="Z153" t="n">
-        <v>5.915810242169697</v>
+        <v>6.305216170364257</v>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
@@ -13391,96 +13271,76 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>coppa italia</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45513.67708333334</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>sudtirol</t>
         </is>
       </c>
       <c r="E154" t="n">
         <v>77</v>
       </c>
       <c r="F154" t="n">
-        <v>771</v>
-      </c>
-      <c r="G154" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H154" t="n">
-        <v>4</v>
-      </c>
-      <c r="I154" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J154" t="n">
-        <v>0.6380263717566993</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0.2360697575499787</v>
-      </c>
-      <c r="L154" t="n">
-        <v>0.125903870693322</v>
-      </c>
-      <c r="M154" t="n">
-        <v>0.05900900900900896</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
       <c r="N154" t="n">
         <v>1</v>
       </c>
       <c r="O154" t="n">
-        <v>0.4688481526967667</v>
+        <v>0.4738402187299073</v>
       </c>
       <c r="P154" t="n">
-        <v>0.4645031770758087</v>
+        <v>0.3970833715775151</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.06664867022742459</v>
+        <v>0.1290764096925773</v>
       </c>
       <c r="R154" t="n">
         <v>1</v>
       </c>
-      <c r="S154" t="n">
-        <v>-0.1691782190599326</v>
-      </c>
+      <c r="S154" t="inlineStr"/>
       <c r="T154" t="n">
-        <v>1</v>
-      </c>
-      <c r="U154" t="n">
-        <v>-0.1691782190599326</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U154" t="inlineStr"/>
       <c r="V154" t="n">
-        <v>0.4688481526967667</v>
-      </c>
-      <c r="W154" t="n">
-        <v>1.48</v>
-      </c>
+        <v>0.5261597812700927</v>
+      </c>
+      <c r="W154" t="inlineStr"/>
       <c r="X154" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y154" t="n">
-        <v>5.606531322517188</v>
+        <v>6.291869291521921</v>
       </c>
       <c r="Z154" t="n">
-        <v>5.606531322517188</v>
+        <v>6.291869291521921</v>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
@@ -13489,96 +13349,76 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>coppa italia</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>45523.5625</v>
+        <v>45514.54166666666</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>cremonese</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>bari</t>
         </is>
       </c>
       <c r="E155" t="n">
         <v>77</v>
       </c>
       <c r="F155" t="n">
-        <v>771</v>
-      </c>
-      <c r="G155" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H155" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I155" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J155" t="n">
-        <v>0.23125</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0.25625</v>
-      </c>
-      <c r="L155" t="n">
-        <v>0.5125</v>
-      </c>
-      <c r="M155" t="n">
-        <v>0.05471324983520098</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>0.2651006284586224</v>
+        <v>0.3997746834822209</v>
       </c>
       <c r="P155" t="n">
-        <v>0.406726162603766</v>
+        <v>0.3808697754406668</v>
       </c>
       <c r="Q155" t="n">
-        <v>0.3281732089376114</v>
+        <v>0.2193555410771125</v>
       </c>
       <c r="R155" t="n">
         <v>1</v>
       </c>
-      <c r="S155" t="n">
-        <v>0.1504761626037661</v>
-      </c>
+      <c r="S155" t="inlineStr"/>
       <c r="T155" t="n">
-        <v>0</v>
-      </c>
-      <c r="U155" t="n">
-        <v>0.1504761626037661</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U155" t="inlineStr"/>
       <c r="V155" t="n">
-        <v>0.406726162603766</v>
-      </c>
-      <c r="W155" t="n">
-        <v>3.7</v>
-      </c>
+        <v>0.6002253165177791</v>
+      </c>
+      <c r="W155" t="inlineStr"/>
       <c r="X155" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y155" t="n">
-        <v>4.8636705876072</v>
+        <v>7.177552088599557</v>
       </c>
       <c r="Z155" t="n">
-        <v>4.8636705876072</v>
+        <v>7.177552088599557</v>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
@@ -13587,96 +13427,76 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>coppa italia</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45514.65625</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>catanzaro</t>
         </is>
       </c>
       <c r="E156" t="n">
         <v>77</v>
       </c>
       <c r="F156" t="n">
-        <v>771</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H156" t="n">
-        <v>5</v>
-      </c>
-      <c r="I156" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J156" t="n">
-        <v>0.7112375533428166</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0.1891891891891892</v>
-      </c>
-      <c r="L156" t="n">
-        <v>0.09957325746799432</v>
-      </c>
-      <c r="M156" t="n">
-        <v>0.05714285714285694</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
       <c r="N156" t="n">
         <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>0.4889679156451812</v>
+        <v>0.4375459700908128</v>
       </c>
       <c r="P156" t="n">
-        <v>0.4566736230579956</v>
+        <v>0.3730150628421344</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.05435846129682308</v>
+        <v>0.1894389670670526</v>
       </c>
       <c r="R156" t="n">
         <v>1</v>
       </c>
-      <c r="S156" t="n">
-        <v>-0.2222696376976354</v>
-      </c>
+      <c r="S156" t="inlineStr"/>
       <c r="T156" t="n">
-        <v>1</v>
-      </c>
-      <c r="U156" t="n">
-        <v>-0.2222696376976354</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U156" t="inlineStr"/>
       <c r="V156" t="n">
-        <v>0.4889679156451812</v>
-      </c>
-      <c r="W156" t="n">
-        <v>1.33</v>
-      </c>
+        <v>0.5624540299091871</v>
+      </c>
+      <c r="W156" t="inlineStr"/>
       <c r="X156" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y156" t="n">
-        <v>5.847125383777921</v>
+        <v>6.725879408980817</v>
       </c>
       <c r="Z156" t="n">
-        <v>5.847125383777921</v>
+        <v>6.725879408980817</v>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
@@ -13685,27 +13505,27 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>coppa italia</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>45507.54166666666</v>
+        <v>45514.67708333334</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>carrarese</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>catania</t>
+          <t>modena</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -13714,48 +13534,48 @@
       <c r="F157" t="n">
         <v>773</v>
       </c>
-      <c r="G157" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H157" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I157" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="J157" t="n">
-        <v>0.5826050769870995</v>
-      </c>
-      <c r="K157" t="n">
-        <v>0.2476071577195173</v>
-      </c>
-      <c r="L157" t="n">
-        <v>0.1697877652933833</v>
-      </c>
-      <c r="M157" t="n">
-        <v>0.1218487394957983</v>
-      </c>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0.4762256520660549</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0.4803533188099261</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0.0434210291240188</v>
+      </c>
+      <c r="R157" t="n">
+        <v>1</v>
+      </c>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="n">
         <v>-100</v>
       </c>
       <c r="U157" t="inlineStr"/>
-      <c r="V157" t="inlineStr"/>
-      <c r="W157" t="n">
-        <v>1.184734513274336</v>
-      </c>
+      <c r="V157" t="n">
+        <v>0.519646681190074</v>
+      </c>
+      <c r="W157" t="inlineStr"/>
       <c r="X157" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="Y157" t="inlineStr"/>
-      <c r="Z157" t="inlineStr"/>
+      <c r="Y157" t="n">
+        <v>6.213985014074568</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>6.213985014074568</v>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>italy</t>
@@ -13770,20 +13590,20 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>45507.64583333334</v>
+        <v>45515.54166666666</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>UiGfvfvT</t>
+          <t>brescia</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>mantova</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -13792,48 +13612,48 @@
       <c r="F158" t="n">
         <v>773</v>
       </c>
-      <c r="G158" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H158" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I158" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J158" t="n">
-        <v>0.2734143106751153</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0.261351914615919</v>
-      </c>
-      <c r="L158" t="n">
-        <v>0.4652337747089658</v>
-      </c>
-      <c r="M158" t="n">
-        <v>0.125370164175215</v>
-      </c>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0.3405749389402209</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0.3558480852076204</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0.3035769758521589</v>
+      </c>
+      <c r="R158" t="n">
+        <v>1</v>
+      </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="n">
         <v>-100</v>
       </c>
       <c r="U158" t="inlineStr"/>
-      <c r="V158" t="inlineStr"/>
-      <c r="W158" t="n">
-        <v>1.203003875968992</v>
-      </c>
+      <c r="V158" t="n">
+        <v>0.6441519147923795</v>
+      </c>
+      <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="Y158" t="inlineStr"/>
-      <c r="Z158" t="inlineStr"/>
+      <c r="Y158" t="n">
+        <v>7.702830577384516</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>7.702830577384516</v>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>italy</t>
@@ -13848,20 +13668,20 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>45508.64583333334</v>
+        <v>45515.5625</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>cesena</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>padova</t>
+          <t>palermo</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -13870,48 +13690,48 @@
       <c r="F159" t="n">
         <v>773</v>
       </c>
-      <c r="G159" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H159" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I159" t="n">
-        <v>5</v>
-      </c>
-      <c r="J159" t="n">
-        <v>0.5713922925528538</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0.2491905275855502</v>
-      </c>
-      <c r="L159" t="n">
-        <v>0.1794171798615961</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0.1147204529370134</v>
-      </c>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0.403847330668933</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0.3641302640579551</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0.232022405273112</v>
+      </c>
+      <c r="R159" t="n">
+        <v>1</v>
+      </c>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="U159" t="inlineStr"/>
-      <c r="V159" t="inlineStr"/>
-      <c r="W159" t="n">
-        <v>1.19482496194825</v>
-      </c>
+      <c r="V159" t="n">
+        <v>0.596152669331067</v>
+      </c>
+      <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="Y159" t="inlineStr"/>
-      <c r="Z159" t="inlineStr"/>
+      <c r="Y159" t="n">
+        <v>7.128850981670743</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>7.128850981670743</v>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>italy</t>
@@ -13926,20 +13746,20 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>45508.65625</v>
+        <v>45515.65625</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>avellino</t>
+          <t>sampdoria</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>juve stabia</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -13948,48 +13768,48 @@
       <c r="F160" t="n">
         <v>773</v>
       </c>
-      <c r="G160" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H160" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I160" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J160" t="n">
-        <v>0.3457292271934921</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0.2765833817547937</v>
-      </c>
-      <c r="L160" t="n">
-        <v>0.3776873910517141</v>
-      </c>
-      <c r="M160" t="n">
-        <v>0.1124757595345831</v>
-      </c>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0.3742469639595186</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0.3749425523620097</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0.2508104836784718</v>
+      </c>
+      <c r="R160" t="n">
+        <v>1</v>
+      </c>
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="n">
         <v>-100</v>
       </c>
       <c r="U160" t="inlineStr"/>
-      <c r="V160" t="inlineStr"/>
-      <c r="W160" t="n">
-        <v>1.242570281124498</v>
-      </c>
+      <c r="V160" t="n">
+        <v>0.6250574476379902</v>
+      </c>
+      <c r="W160" t="inlineStr"/>
       <c r="X160" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="Y160" t="inlineStr"/>
-      <c r="Z160" t="inlineStr"/>
+      <c r="Y160" t="n">
+        <v>7.474497101882698</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>7.474497101882698</v>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>italy</t>
@@ -14004,20 +13824,20 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>45513.54166666666</v>
+        <v>45515.67708333334</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>sassuolo</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>cittadella</t>
+          <t>cosenza</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -14037,13 +13857,13 @@
         <v>1</v>
       </c>
       <c r="O161" t="n">
-        <v>0.4694967552742121</v>
+        <v>0.4739942378041332</v>
       </c>
       <c r="P161" t="n">
-        <v>0.4042830898537844</v>
+        <v>0.422798329895286</v>
       </c>
       <c r="Q161" t="n">
-        <v>0.1262201548720035</v>
+        <v>0.1032074323005807</v>
       </c>
       <c r="R161" t="n">
         <v>1</v>
@@ -14054,7 +13874,7 @@
       </c>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="n">
-        <v>0.5305032447257878</v>
+        <v>0.5260057621958667</v>
       </c>
       <c r="W161" t="inlineStr"/>
       <c r="X161" t="inlineStr">
@@ -14063,10 +13883,10 @@
         </is>
       </c>
       <c r="Y161" t="n">
-        <v>6.343808845453178</v>
+        <v>6.290027516612613</v>
       </c>
       <c r="Z161" t="n">
-        <v>6.343808845453178</v>
+        <v>6.290027516612613</v>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
@@ -14082,20 +13902,20 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>Aeu0r0Mk</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>45513.65625</v>
+        <v>45516.54166666666</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>frosinone</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>reggiana</t>
+          <t>pisa</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -14115,13 +13935,13 @@
         <v>1</v>
       </c>
       <c r="O162" t="n">
-        <v>0.4727240812949189</v>
+        <v>0.4214803559717588</v>
       </c>
       <c r="P162" t="n">
-        <v>0.4071627836349588</v>
+        <v>0.3823090013622199</v>
       </c>
       <c r="Q162" t="n">
-        <v>0.1201131350701222</v>
+        <v>0.196210642666021</v>
       </c>
       <c r="R162" t="n">
         <v>1</v>
@@ -14132,7 +13952,7 @@
       </c>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="n">
-        <v>0.5272759187050811</v>
+        <v>0.5785196440282412</v>
       </c>
       <c r="W162" t="inlineStr"/>
       <c r="X162" t="inlineStr">
@@ -14141,10 +13961,10 @@
         </is>
       </c>
       <c r="Y162" t="n">
-        <v>6.305216170364257</v>
+        <v>6.917993568449856</v>
       </c>
       <c r="Z162" t="n">
-        <v>6.305216170364257</v>
+        <v>6.917993568449856</v>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
@@ -14160,20 +13980,20 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>45513.67708333334</v>
+        <v>45516.65625</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>salernitana</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>sudtirol</t>
+          <t>spezia</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -14193,13 +14013,13 @@
         <v>1</v>
       </c>
       <c r="O163" t="n">
-        <v>0.4738402187299073</v>
+        <v>0.4455732802592645</v>
       </c>
       <c r="P163" t="n">
-        <v>0.3970833715775151</v>
+        <v>0.3852067815535028</v>
       </c>
       <c r="Q163" t="n">
-        <v>0.1290764096925773</v>
+        <v>0.1692199381872326</v>
       </c>
       <c r="R163" t="n">
         <v>1</v>
@@ -14210,7 +14030,7 @@
       </c>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="n">
-        <v>0.5261597812700927</v>
+        <v>0.5544267197407355</v>
       </c>
       <c r="W163" t="inlineStr"/>
       <c r="X163" t="inlineStr">
@@ -14219,10 +14039,10 @@
         </is>
       </c>
       <c r="Y163" t="n">
-        <v>6.291869291521921</v>
+        <v>6.629888061598689</v>
       </c>
       <c r="Z163" t="n">
-        <v>6.291869291521921</v>
+        <v>6.629888061598689</v>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
@@ -14238,69 +14058,89 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>8KfYbJz0</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>45514.54166666666</v>
+        <v>45520.64583333334</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>cremonese</t>
+          <t>brescia</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>bari</t>
+          <t>palermo</t>
         </is>
       </c>
       <c r="E164" t="n">
         <v>77</v>
       </c>
       <c r="F164" t="n">
-        <v>773</v>
-      </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
+        <v>774</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H164" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I164" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.3445218492716909</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0.2906903103229892</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0.3647878404053199</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0.07502723311546844</v>
+      </c>
       <c r="N164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
-        <v>0.3997746834822209</v>
+        <v>0.3388659580677731</v>
       </c>
       <c r="P164" t="n">
-        <v>0.3808697754406668</v>
+        <v>0.3746946149815555</v>
       </c>
       <c r="Q164" t="n">
-        <v>0.2193555410771125</v>
+        <v>0.2864394269506713</v>
       </c>
       <c r="R164" t="n">
         <v>1</v>
       </c>
-      <c r="S164" t="inlineStr"/>
+      <c r="S164" t="n">
+        <v>0.08400430465856634</v>
+      </c>
       <c r="T164" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U164" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0.08400430465856634</v>
+      </c>
       <c r="V164" t="n">
-        <v>0.6002253165177791</v>
-      </c>
-      <c r="W164" t="inlineStr"/>
+        <v>0.3746946149815555</v>
+      </c>
+      <c r="W164" t="n">
+        <v>3.2</v>
+      </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y164" t="n">
-        <v>7.177552088599557</v>
+        <v>4.480634259065295</v>
       </c>
       <c r="Z164" t="n">
-        <v>7.177552088599557</v>
+        <v>4.480634259065295</v>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
@@ -14309,77 +14149,79 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>EL1P0u6m</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>45514.65625</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>bari</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>catanzaro</t>
+          <t>juve stabia</t>
         </is>
       </c>
       <c r="E165" t="n">
         <v>77</v>
       </c>
       <c r="F165" t="n">
-        <v>773</v>
-      </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="n">
-        <v>1</v>
-      </c>
-      <c r="O165" t="n">
-        <v>0.4375459700908128</v>
-      </c>
-      <c r="P165" t="n">
-        <v>0.3730150628421344</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>0.1894389670670526</v>
-      </c>
+        <v>774</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H165" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I165" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0.4882740930743861</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0.2854525467204104</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0.2262733602052034</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0.07791053619038224</v>
+      </c>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
       <c r="R165" t="n">
         <v>1</v>
       </c>
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="n">
-        <v>-1</v>
+        <v>-100</v>
       </c>
       <c r="U165" t="inlineStr"/>
-      <c r="V165" t="n">
-        <v>0.5624540299091871</v>
-      </c>
-      <c r="W165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+      <c r="W165" t="n">
+        <v>1.298333333333333</v>
+      </c>
       <c r="X165" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="Y165" t="n">
-        <v>6.725879408980817</v>
-      </c>
-      <c r="Z165" t="n">
-        <v>6.725879408980817</v>
-      </c>
+      <c r="Y165" t="inlineStr"/>
+      <c r="Z165" t="inlineStr"/>
       <c r="AA165" t="inlineStr">
         <is>
           <t>italy</t>
@@ -14387,76 +14229,96 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>M5TEBdK5</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>45514.67708333334</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>pisa</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>modena</t>
+          <t>spezia</t>
         </is>
       </c>
       <c r="E166" t="n">
         <v>77</v>
       </c>
       <c r="F166" t="n">
-        <v>773</v>
-      </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
+        <v>774</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H166" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I166" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0.3717001055966209</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0.2903907074973601</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0.337909186906019</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0.07613636363636367</v>
+      </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O166" t="n">
-        <v>0.4762256520660549</v>
+        <v>0.3771596572542751</v>
       </c>
       <c r="P166" t="n">
-        <v>0.4803533188099261</v>
+        <v>0.3703923812577244</v>
       </c>
       <c r="Q166" t="n">
-        <v>0.0434210291240188</v>
+        <v>0.2524479614880006</v>
       </c>
       <c r="R166" t="n">
         <v>1</v>
       </c>
-      <c r="S166" t="inlineStr"/>
+      <c r="S166" t="n">
+        <v>0.00545955165765416</v>
+      </c>
       <c r="T166" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U166" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U166" t="n">
+        <v>0.00545955165765416</v>
+      </c>
       <c r="V166" t="n">
-        <v>0.519646681190074</v>
-      </c>
-      <c r="W166" t="inlineStr"/>
+        <v>0.3771596572542751</v>
+      </c>
+      <c r="W166" t="n">
+        <v>2.5</v>
+      </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y166" t="n">
-        <v>6.213985014074568</v>
+        <v>4.510111471748842</v>
       </c>
       <c r="Z166" t="n">
-        <v>6.213985014074568</v>
+        <v>4.510111471748842</v>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
@@ -14465,76 +14327,96 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>joLV7EJU</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>45515.54166666666</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>brescia</t>
+          <t>salernitana</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>cittadella</t>
         </is>
       </c>
       <c r="E167" t="n">
         <v>77</v>
       </c>
       <c r="F167" t="n">
-        <v>773</v>
-      </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
+        <v>774</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H167" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I167" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0.5038814396612561</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0.2741707833450953</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0.2219477769936486</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0.07275342569460208</v>
+      </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O167" t="n">
-        <v>0.3405749389402209</v>
+        <v>0.451102352483415</v>
       </c>
       <c r="P167" t="n">
-        <v>0.3558480852076204</v>
+        <v>0.3894999314195416</v>
       </c>
       <c r="Q167" t="n">
-        <v>0.3035769758521589</v>
+        <v>0.1593977160970436</v>
       </c>
       <c r="R167" t="n">
         <v>1</v>
       </c>
-      <c r="S167" t="inlineStr"/>
+      <c r="S167" t="n">
+        <v>-0.05277908717784108</v>
+      </c>
       <c r="T167" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U167" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U167" t="n">
+        <v>-0.05277908717784108</v>
+      </c>
       <c r="V167" t="n">
-        <v>0.6441519147923795</v>
-      </c>
-      <c r="W167" t="inlineStr"/>
+        <v>0.451102352483415</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1.85</v>
+      </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y167" t="n">
-        <v>7.702830577384516</v>
+        <v>5.394325336065033</v>
       </c>
       <c r="Z167" t="n">
-        <v>7.702830577384516</v>
+        <v>5.394325336065033</v>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
@@ -14543,76 +14425,96 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>WvwvCQVo</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>45515.5625</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>sudtirol</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>palermo</t>
+          <t>modena</t>
         </is>
       </c>
       <c r="E168" t="n">
         <v>77</v>
       </c>
       <c r="F168" t="n">
-        <v>773</v>
-      </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
+        <v>774</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H168" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I168" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0.3565379226699568</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0.3024821731038665</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0.3409799042261768</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0.06644514567978321</v>
+      </c>
       <c r="N168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>0.403847330668933</v>
+        <v>0.3613841827993978</v>
       </c>
       <c r="P168" t="n">
-        <v>0.3641302640579551</v>
+        <v>0.3730405837229831</v>
       </c>
       <c r="Q168" t="n">
-        <v>0.232022405273112</v>
+        <v>0.265575233477619</v>
       </c>
       <c r="R168" t="n">
         <v>1</v>
       </c>
-      <c r="S168" t="inlineStr"/>
+      <c r="S168" t="n">
+        <v>0.07055841061911661</v>
+      </c>
       <c r="T168" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U168" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0.07055841061911661</v>
+      </c>
       <c r="V168" t="n">
-        <v>0.596152669331067</v>
-      </c>
-      <c r="W168" t="inlineStr"/>
+        <v>0.3730405837229831</v>
+      </c>
+      <c r="W168" t="n">
+        <v>3.1</v>
+      </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y168" t="n">
-        <v>7.128850981670743</v>
+        <v>4.460855194124398</v>
       </c>
       <c r="Z168" t="n">
-        <v>7.128850981670743</v>
+        <v>4.460855194124398</v>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
@@ -14621,76 +14523,96 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>45515.65625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>sampdoria</t>
+          <t>catanzaro</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>sassuolo</t>
         </is>
       </c>
       <c r="E169" t="n">
         <v>77</v>
       </c>
       <c r="F169" t="n">
-        <v>773</v>
-      </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
+        <v>774</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H169" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I169" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0.337909186906019</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0.2903907074973601</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0.3717001055966209</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0.07613636363636367</v>
+      </c>
       <c r="N169" t="n">
         <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>0.3742469639595186</v>
+        <v>0.310221098231573</v>
       </c>
       <c r="P169" t="n">
-        <v>0.3749425523620097</v>
+        <v>0.357962016962774</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.2508104836784718</v>
+        <v>0.3318168848056527</v>
       </c>
       <c r="R169" t="n">
         <v>1</v>
       </c>
-      <c r="S169" t="inlineStr"/>
+      <c r="S169" t="n">
+        <v>0.06757130946541395</v>
+      </c>
       <c r="T169" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U169" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0.06757130946541395</v>
+      </c>
       <c r="V169" t="n">
-        <v>0.6250574476379902</v>
-      </c>
-      <c r="W169" t="inlineStr"/>
+        <v>0.357962016962774</v>
+      </c>
+      <c r="W169" t="n">
+        <v>3.2</v>
+      </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y169" t="n">
-        <v>7.474497101882698</v>
+        <v>4.280544241946123</v>
       </c>
       <c r="Z169" t="n">
-        <v>7.474497101882698</v>
+        <v>4.280544241946123</v>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
@@ -14699,77 +14621,77 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>x0nkeyzP</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>45515.67708333334</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>cesena</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>cosenza</t>
+          <t>carrarese</t>
         </is>
       </c>
       <c r="E170" t="n">
         <v>77</v>
       </c>
       <c r="F170" t="n">
-        <v>773</v>
-      </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="n">
-        <v>1</v>
-      </c>
-      <c r="O170" t="n">
-        <v>0.4739942378041332</v>
-      </c>
-      <c r="P170" t="n">
-        <v>0.422798329895286</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>0.1032074323005807</v>
-      </c>
-      <c r="R170" t="n">
-        <v>1</v>
-      </c>
+        <v>774</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H170" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I170" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0.5008809239913865</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0.2851168336566354</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0.2140022423519781</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0.0791797304499382</v>
+      </c>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="n">
-        <v>-1</v>
+        <v>-100</v>
       </c>
       <c r="U170" t="inlineStr"/>
-      <c r="V170" t="n">
-        <v>0.5260057621958667</v>
-      </c>
-      <c r="W170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
+      <c r="W170" t="n">
+        <v>1.296197411003236</v>
+      </c>
       <c r="X170" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="Y170" t="n">
-        <v>6.290027516612613</v>
-      </c>
-      <c r="Z170" t="n">
-        <v>6.290027516612613</v>
-      </c>
+      <c r="Y170" t="inlineStr"/>
+      <c r="Z170" t="inlineStr"/>
       <c r="AA170" t="inlineStr">
         <is>
           <t>italy</t>
@@ -14777,76 +14699,96 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>45516.54166666666</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>frosinone</t>
+          <t>cosenza</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>pisa</t>
+          <t>cremonese</t>
         </is>
       </c>
       <c r="E171" t="n">
         <v>77</v>
       </c>
       <c r="F171" t="n">
-        <v>773</v>
-      </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
+        <v>774</v>
+      </c>
+      <c r="G171" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H171" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I171" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0.2894736842105263</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0.2894736842105263</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0.07954545454545459</v>
+      </c>
       <c r="N171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>0.4214803559717588</v>
+        <v>0.3271006089805857</v>
       </c>
       <c r="P171" t="n">
-        <v>0.3823090013622199</v>
+        <v>0.3762116784915401</v>
       </c>
       <c r="Q171" t="n">
-        <v>0.196210642666021</v>
+        <v>0.2966877125278745</v>
       </c>
       <c r="R171" t="n">
         <v>1</v>
       </c>
-      <c r="S171" t="inlineStr"/>
+      <c r="S171" t="n">
+        <v>0.08673799428101381</v>
+      </c>
       <c r="T171" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U171" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U171" t="n">
+        <v>0.08673799428101381</v>
+      </c>
       <c r="V171" t="n">
-        <v>0.5785196440282412</v>
-      </c>
-      <c r="W171" t="inlineStr"/>
+        <v>0.3762116784915401</v>
+      </c>
+      <c r="W171" t="n">
+        <v>3.2</v>
+      </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y171" t="n">
-        <v>6.917993568449856</v>
+        <v>4.498775450489541</v>
       </c>
       <c r="Z171" t="n">
-        <v>6.917993568449856</v>
+        <v>4.498775450489541</v>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
@@ -14855,76 +14797,96 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>45516.65625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>salernitana</t>
+          <t>frosinone</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>spezia</t>
+          <t>sampdoria</t>
         </is>
       </c>
       <c r="E172" t="n">
         <v>77</v>
       </c>
       <c r="F172" t="n">
-        <v>773</v>
-      </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
+        <v>774</v>
+      </c>
+      <c r="G172" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H172" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I172" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0.3717001055966209</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0.2903907074973601</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0.337909186906019</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0.07613636363636367</v>
+      </c>
       <c r="N172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
-        <v>0.4455732802592645</v>
+        <v>0.3792582472531151</v>
       </c>
       <c r="P172" t="n">
-        <v>0.3852067815535028</v>
+        <v>0.3804626357347388</v>
       </c>
       <c r="Q172" t="n">
-        <v>0.1692199381872326</v>
+        <v>0.2402791170121459</v>
       </c>
       <c r="R172" t="n">
         <v>1</v>
       </c>
-      <c r="S172" t="inlineStr"/>
+      <c r="S172" t="n">
+        <v>0.09007192823737875</v>
+      </c>
       <c r="T172" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U172" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U172" t="n">
+        <v>0.09007192823737875</v>
+      </c>
       <c r="V172" t="n">
-        <v>0.5544267197407355</v>
-      </c>
-      <c r="W172" t="inlineStr"/>
+        <v>0.3804626357347388</v>
+      </c>
+      <c r="W172" t="n">
+        <v>3.2</v>
+      </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y172" t="n">
-        <v>6.629888061598689</v>
+        <v>4.549608806230817</v>
       </c>
       <c r="Z172" t="n">
-        <v>6.629888061598689</v>
+        <v>4.549608806230817</v>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
@@ -14933,27 +14895,27 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>45520.64583333334</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>brescia</t>
+          <t>reggiana</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>palermo</t>
+          <t>mantova</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -14963,67 +14925,49 @@
         <v>774</v>
       </c>
       <c r="G173" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="H173" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I173" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="J173" t="n">
-        <v>0.3445218492716909</v>
+        <v>0.3636557534392663</v>
       </c>
       <c r="K173" t="n">
-        <v>0.2906903103229892</v>
+        <v>0.2991361842806867</v>
       </c>
       <c r="L173" t="n">
-        <v>0.3647878404053199</v>
+        <v>0.3372080622800468</v>
       </c>
       <c r="M173" t="n">
-        <v>0.07502723311546844</v>
-      </c>
-      <c r="N173" t="n">
-        <v>0</v>
-      </c>
-      <c r="O173" t="n">
-        <v>0.3388659580677731</v>
-      </c>
-      <c r="P173" t="n">
-        <v>0.3746946149815555</v>
-      </c>
-      <c r="Q173" t="n">
-        <v>0.2864394269506713</v>
-      </c>
+        <v>0.07837387154275222</v>
+      </c>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
       <c r="R173" t="n">
         <v>1</v>
       </c>
-      <c r="S173" t="n">
-        <v>0.08400430465856634</v>
-      </c>
+      <c r="S173" t="inlineStr"/>
       <c r="T173" t="n">
-        <v>0</v>
-      </c>
-      <c r="U173" t="n">
-        <v>0.08400430465856634</v>
-      </c>
-      <c r="V173" t="n">
-        <v>0.3746946149815555</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr"/>
       <c r="W173" t="n">
-        <v>3.2</v>
+        <v>1.32311320754717</v>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y173" t="n">
-        <v>4.480634259065295</v>
-      </c>
-      <c r="Z173" t="n">
-        <v>4.480634259065295</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr"/>
+      <c r="Z173" t="inlineStr"/>
       <c r="AA173" t="inlineStr">
         <is>
           <t>italy</t>
@@ -15038,826 +14982,882 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45520.65625</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>bari</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>juve stabia</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F174" t="n">
-        <v>774</v>
+        <v>551</v>
       </c>
       <c r="G174" t="n">
-        <v>1.9</v>
+        <v>7</v>
       </c>
       <c r="H174" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="I174" t="n">
-        <v>4.1</v>
+        <v>1.44</v>
       </c>
       <c r="J174" t="n">
-        <v>0.4882740930743861</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="K174" t="n">
-        <v>0.2854525467204104</v>
+        <v>0.2097378277153558</v>
       </c>
       <c r="L174" t="n">
-        <v>0.2262733602052034</v>
+        <v>0.6554307116104868</v>
       </c>
       <c r="M174" t="n">
-        <v>0.07791053619038224</v>
-      </c>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
+        <v>0.05952380952380953</v>
+      </c>
+      <c r="N174" t="n">
+        <v>2</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0.1473976254720581</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0.1797555840958052</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>0.6728467904321364</v>
+      </c>
       <c r="R174" t="n">
         <v>1</v>
       </c>
-      <c r="S174" t="inlineStr"/>
+      <c r="S174" t="n">
+        <v>0.01741607882164953</v>
+      </c>
       <c r="T174" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U174" t="inlineStr"/>
-      <c r="V174" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0.01741607882164953</v>
+      </c>
+      <c r="V174" t="n">
+        <v>0.6728467904321364</v>
+      </c>
       <c r="W174" t="n">
-        <v>1.298333333333333</v>
+        <v>1.44</v>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr"/>
-      <c r="Z174" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y174" t="n">
+        <v>11.92118824796449</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>11.92118824796449</v>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>ligue 1</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45521.5</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>pisa</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>spezia</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F175" t="n">
-        <v>774</v>
+        <v>551</v>
       </c>
       <c r="G175" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="H175" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I175" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="J175" t="n">
-        <v>0.3717001055966209</v>
+        <v>0.3590576766856215</v>
       </c>
       <c r="K175" t="n">
-        <v>0.2903907074973601</v>
+        <v>0.2777416734362307</v>
       </c>
       <c r="L175" t="n">
-        <v>0.337909186906019</v>
+        <v>0.3632006498781478</v>
       </c>
       <c r="M175" t="n">
-        <v>0.07613636363636367</v>
+        <v>0.05896116855633737</v>
       </c>
       <c r="N175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O175" t="n">
-        <v>0.3771596572542751</v>
+        <v>0.3512543388722946</v>
       </c>
       <c r="P175" t="n">
-        <v>0.3703923812577244</v>
+        <v>0.248223656473991</v>
       </c>
       <c r="Q175" t="n">
-        <v>0.2524479614880006</v>
+        <v>0.4005220046537143</v>
       </c>
       <c r="R175" t="n">
         <v>1</v>
       </c>
       <c r="S175" t="n">
-        <v>0.00545955165765416</v>
+        <v>0.03732135477556653</v>
       </c>
       <c r="T175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U175" t="n">
-        <v>0.00545955165765416</v>
+        <v>0.03732135477556653</v>
       </c>
       <c r="V175" t="n">
-        <v>0.3771596572542751</v>
+        <v>0.4005220046537143</v>
       </c>
       <c r="W175" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="Y175" t="n">
-        <v>4.510111471748842</v>
+        <v>7.096263641032579</v>
       </c>
       <c r="Z175" t="n">
-        <v>4.510111471748842</v>
+        <v>7.096263641032579</v>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>ligue 1</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>salernitana</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>cittadella</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F176" t="n">
-        <v>774</v>
+        <v>551</v>
       </c>
       <c r="G176" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="H176" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="I176" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J176" t="n">
-        <v>0.5038814396612561</v>
+        <v>0.2705667276051188</v>
       </c>
       <c r="K176" t="n">
-        <v>0.2741707833450953</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="L176" t="n">
-        <v>0.2219477769936486</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="M176" t="n">
-        <v>0.07275342569460208</v>
+        <v>0.05598455598455598</v>
       </c>
       <c r="N176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O176" t="n">
-        <v>0.451102352483415</v>
+        <v>0.3481985098453283</v>
       </c>
       <c r="P176" t="n">
-        <v>0.3894999314195416</v>
+        <v>0.2266059980587039</v>
       </c>
       <c r="Q176" t="n">
-        <v>0.1593977160970436</v>
+        <v>0.4251954920959679</v>
       </c>
       <c r="R176" t="n">
         <v>1</v>
       </c>
       <c r="S176" t="n">
-        <v>-0.05277908717784108</v>
+        <v>-0.04829628121299007</v>
       </c>
       <c r="T176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U176" t="n">
-        <v>-0.05277908717784108</v>
+        <v>-0.04829628121299007</v>
       </c>
       <c r="V176" t="n">
-        <v>0.451102352483415</v>
+        <v>0.4251954920959679</v>
       </c>
       <c r="W176" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="Y176" t="n">
-        <v>5.394325336065033</v>
+        <v>7.53341708029322</v>
       </c>
       <c r="Z176" t="n">
-        <v>5.394325336065033</v>
+        <v>7.53341708029322</v>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>ligue 1</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>sudtirol</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>modena</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F177" t="n">
-        <v>774</v>
+        <v>551</v>
       </c>
       <c r="G177" t="n">
-        <v>2.63</v>
+        <v>1.5</v>
       </c>
       <c r="H177" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="I177" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="J177" t="n">
-        <v>0.3565379226699568</v>
+        <v>0.6297577854671281</v>
       </c>
       <c r="K177" t="n">
-        <v>0.3024821731038665</v>
+        <v>0.2249134948096886</v>
       </c>
       <c r="L177" t="n">
-        <v>0.3409799042261768</v>
+        <v>0.1453287197231834</v>
       </c>
       <c r="M177" t="n">
-        <v>0.06644514567978321</v>
+        <v>0.0586080586080584</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177" t="n">
-        <v>0.3613841827993978</v>
+        <v>0.5751286141011103</v>
       </c>
       <c r="P177" t="n">
-        <v>0.3730405837229831</v>
+        <v>0.2763858917070745</v>
       </c>
       <c r="Q177" t="n">
-        <v>0.265575233477619</v>
+        <v>0.148485494191815</v>
       </c>
       <c r="R177" t="n">
         <v>1</v>
       </c>
       <c r="S177" t="n">
-        <v>0.07055841061911661</v>
+        <v>-0.05462917136601786</v>
       </c>
       <c r="T177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U177" t="n">
-        <v>0.07055841061911661</v>
+        <v>-0.05462917136601786</v>
       </c>
       <c r="V177" t="n">
-        <v>0.3730405837229831</v>
+        <v>0.5751286141011103</v>
       </c>
       <c r="W177" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="Y177" t="n">
-        <v>4.460855194124398</v>
+        <v>10.18986279341074</v>
       </c>
       <c r="Z177" t="n">
-        <v>4.460855194124398</v>
+        <v>10.18986279341074</v>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>ligue 1</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>catanzaro</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>sassuolo</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F178" t="n">
-        <v>774</v>
+        <v>551</v>
       </c>
       <c r="G178" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="H178" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I178" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J178" t="n">
-        <v>0.337909186906019</v>
+        <v>0.2912772585669782</v>
       </c>
       <c r="K178" t="n">
-        <v>0.2903907074973601</v>
+        <v>0.2784267912772586</v>
       </c>
       <c r="L178" t="n">
-        <v>0.3717001055966209</v>
+        <v>0.4302959501557632</v>
       </c>
       <c r="M178" t="n">
-        <v>0.07613636363636367</v>
+        <v>0.05635540929658589</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O178" t="n">
-        <v>0.310221098231573</v>
+        <v>0.2366185707207301</v>
       </c>
       <c r="P178" t="n">
-        <v>0.357962016962774</v>
+        <v>0.195895925340908</v>
       </c>
       <c r="Q178" t="n">
-        <v>0.3318168848056527</v>
+        <v>0.5674855039383617</v>
       </c>
       <c r="R178" t="n">
         <v>1</v>
       </c>
       <c r="S178" t="n">
-        <v>0.06757130946541395</v>
+        <v>0.1371895537825986</v>
       </c>
       <c r="T178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U178" t="n">
-        <v>0.06757130946541395</v>
+        <v>0.1371895537825986</v>
       </c>
       <c r="V178" t="n">
-        <v>0.357962016962774</v>
+        <v>0.5674855039383617</v>
       </c>
       <c r="W178" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="Y178" t="n">
-        <v>4.280544241946123</v>
+        <v>10.05444570240918</v>
       </c>
       <c r="Z178" t="n">
-        <v>4.280544241946123</v>
+        <v>10.05444570240918</v>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>ligue 1</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45522.5</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>cesena</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>carrarese</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F179" t="n">
-        <v>774</v>
+        <v>551</v>
       </c>
       <c r="G179" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="H179" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="I179" t="n">
-        <v>4.33</v>
+        <v>1.65</v>
       </c>
       <c r="J179" t="n">
-        <v>0.5008809239913865</v>
+        <v>0.1882404563405002</v>
       </c>
       <c r="K179" t="n">
-        <v>0.2851168336566354</v>
+        <v>0.2413339183852567</v>
       </c>
       <c r="L179" t="n">
-        <v>0.2140022423519781</v>
+        <v>0.5704256252742431</v>
       </c>
       <c r="M179" t="n">
-        <v>0.0791797304499382</v>
-      </c>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
+        <v>0.06247086247086253</v>
+      </c>
+      <c r="N179" t="n">
+        <v>2</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0.166444459781715</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0.1486836638303108</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0.6848718763879741</v>
+      </c>
+      <c r="R179" t="n">
+        <v>1</v>
+      </c>
+      <c r="S179" t="n">
+        <v>0.114446251113731</v>
+      </c>
       <c r="T179" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U179" t="inlineStr"/>
-      <c r="V179" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U179" t="n">
+        <v>0.114446251113731</v>
+      </c>
+      <c r="V179" t="n">
+        <v>0.6848718763879741</v>
+      </c>
       <c r="W179" t="n">
-        <v>1.296197411003236</v>
+        <v>1.65</v>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr"/>
-      <c r="Z179" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y179" t="n">
+        <v>12.13424315944801</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>12.13424315944801</v>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>ligue 1</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45522.5</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>cosenza</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>cremonese</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F180" t="n">
-        <v>774</v>
+        <v>551</v>
       </c>
       <c r="G180" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="H180" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I180" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J180" t="n">
-        <v>0.2894736842105263</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="K180" t="n">
-        <v>0.2894736842105263</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="L180" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="M180" t="n">
-        <v>0.07954545454545459</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O180" t="n">
-        <v>0.3271006089805857</v>
+        <v>0.4543673099879942</v>
       </c>
       <c r="P180" t="n">
-        <v>0.3762116784915401</v>
+        <v>0.2609260359310946</v>
       </c>
       <c r="Q180" t="n">
-        <v>0.2966877125278745</v>
+        <v>0.2847066540809113</v>
       </c>
       <c r="R180" t="n">
         <v>1</v>
       </c>
       <c r="S180" t="n">
-        <v>0.08673799428101381</v>
+        <v>-0.005956119872855714</v>
       </c>
       <c r="T180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U180" t="n">
-        <v>0.08673799428101381</v>
+        <v>-0.005956119872855714</v>
       </c>
       <c r="V180" t="n">
-        <v>0.3762116784915401</v>
+        <v>0.4543673099879942</v>
       </c>
       <c r="W180" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="Y180" t="n">
-        <v>4.498775450489541</v>
+        <v>8.050269858030084</v>
       </c>
       <c r="Z180" t="n">
-        <v>4.498775450489541</v>
+        <v>8.050269858030084</v>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>ligue 1</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45522.5</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>frosinone</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>sampdoria</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F181" t="n">
-        <v>774</v>
+        <v>551</v>
       </c>
       <c r="G181" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="H181" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I181" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="J181" t="n">
-        <v>0.3717001055966209</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="K181" t="n">
-        <v>0.2903907074973601</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="L181" t="n">
-        <v>0.337909186906019</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="M181" t="n">
-        <v>0.07613636363636367</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O181" t="n">
-        <v>0.3792582472531151</v>
+        <v>0.4375765127642837</v>
       </c>
       <c r="P181" t="n">
-        <v>0.3804626357347388</v>
+        <v>0.2832340516947483</v>
       </c>
       <c r="Q181" t="n">
-        <v>0.2402791170121459</v>
+        <v>0.2791894355409684</v>
       </c>
       <c r="R181" t="n">
         <v>1</v>
       </c>
       <c r="S181" t="n">
-        <v>0.09007192823737875</v>
+        <v>-0.02274691709656623</v>
       </c>
       <c r="T181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U181" t="n">
-        <v>0.09007192823737875</v>
+        <v>-0.02274691709656623</v>
       </c>
       <c r="V181" t="n">
-        <v>0.3804626357347388</v>
+        <v>0.4375765127642837</v>
       </c>
       <c r="W181" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="Y181" t="n">
-        <v>4.549608806230817</v>
+        <v>7.75277827839619</v>
       </c>
       <c r="Z181" t="n">
-        <v>4.549608806230817</v>
+        <v>7.75277827839619</v>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>ligue 1</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45522.65625</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>reggiana</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>mantova</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F182" t="n">
-        <v>774</v>
+        <v>551</v>
       </c>
       <c r="G182" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="H182" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="I182" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="J182" t="n">
-        <v>0.3636557534392663</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="K182" t="n">
-        <v>0.2991361842806867</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="L182" t="n">
-        <v>0.3372080622800468</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="M182" t="n">
-        <v>0.07837387154275222</v>
-      </c>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
+        <v>0.05106209150326801</v>
+      </c>
+      <c r="N182" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0.3817675884528393</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0.2368836839996998</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0.3813487275474608</v>
+      </c>
       <c r="R182" t="n">
         <v>1</v>
       </c>
-      <c r="S182" t="inlineStr"/>
+      <c r="S182" t="n">
+        <v>-0.04108511267424964</v>
+      </c>
       <c r="T182" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U182" t="inlineStr"/>
-      <c r="V182" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U182" t="n">
+        <v>-0.04108511267424964</v>
+      </c>
+      <c r="V182" t="n">
+        <v>0.3817675884528393</v>
+      </c>
       <c r="W182" t="n">
-        <v>1.32311320754717</v>
+        <v>2.25</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr"/>
-      <c r="Z182" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="Y182" t="n">
+        <v>6.763981568515423</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>6.763981568515423</v>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>ligue 1</t>
         </is>
       </c>
     </row>
@@ -15887,55 +15887,55 @@
         <v>1481</v>
       </c>
       <c r="G183" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H183" t="n">
         <v>4.2</v>
       </c>
       <c r="I183" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J183" t="n">
-        <v>0.6499535747446611</v>
+        <v>0.6566604127579737</v>
       </c>
       <c r="K183" t="n">
-        <v>0.2243887341380377</v>
+        <v>0.225140712945591</v>
       </c>
       <c r="L183" t="n">
-        <v>0.1256576911173011</v>
+        <v>0.1181988742964353</v>
       </c>
       <c r="M183" t="n">
-        <v>0.06108374384236459</v>
+        <v>0.05753968253968256</v>
       </c>
       <c r="N183" t="n">
         <v>1</v>
       </c>
       <c r="O183" t="n">
-        <v>0.3543207301500569</v>
+        <v>0.3533540521549642</v>
       </c>
       <c r="P183" t="n">
-        <v>0.3309504969275024</v>
+        <v>0.3312568815562585</v>
       </c>
       <c r="Q183" t="n">
-        <v>0.3147287729224407</v>
+        <v>0.3153890662887772</v>
       </c>
       <c r="R183" t="n">
         <v>1</v>
       </c>
       <c r="S183" t="n">
-        <v>-0.2956328445946042</v>
+        <v>-0.3033063606030095</v>
       </c>
       <c r="T183" t="n">
         <v>-1</v>
       </c>
       <c r="U183" t="n">
-        <v>0.2956328445946042</v>
+        <v>0.3033063606030095</v>
       </c>
       <c r="V183" t="n">
-        <v>0.6456792698499432</v>
+        <v>0.6466459478450357</v>
       </c>
       <c r="W183" t="n">
-        <v>2.692307692307693</v>
+        <v>2.754098360655738</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
@@ -15943,10 +15943,10 @@
         </is>
       </c>
       <c r="Y183" t="n">
-        <v>9.885606821282982</v>
+        <v>9.900407046454362</v>
       </c>
       <c r="Z183" t="n">
-        <v>9.885606821282982</v>
+        <v>9.900407046454362</v>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
@@ -15985,25 +15985,25 @@
         <v>1481</v>
       </c>
       <c r="G184" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H184" t="n">
         <v>3.4</v>
       </c>
       <c r="I184" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="J184" t="n">
-        <v>0.3781597573306371</v>
+        <v>0.3938223938223938</v>
       </c>
       <c r="K184" t="n">
-        <v>0.2780586450960567</v>
+        <v>0.277992277992278</v>
       </c>
       <c r="L184" t="n">
-        <v>0.3437815975733064</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="M184" t="n">
-        <v>0.05775401069518704</v>
+        <v>0.05800653594771243</v>
       </c>
       <c r="N184" t="n">
         <v>0</v>
@@ -16021,13 +16021,13 @@
         <v>1</v>
       </c>
       <c r="S184" t="n">
-        <v>0.09334360928615032</v>
+        <v>0.09340997638992898</v>
       </c>
       <c r="T184" t="n">
         <v>0</v>
       </c>
       <c r="U184" t="n">
-        <v>0.09334360928615032</v>
+        <v>0.09340997638992898</v>
       </c>
       <c r="V184" t="n">
         <v>0.371402254382207</v>
@@ -16083,25 +16083,25 @@
         <v>1481</v>
       </c>
       <c r="G185" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="H185" t="n">
         <v>3.3</v>
       </c>
       <c r="I185" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J185" t="n">
-        <v>0.4839055793991416</v>
+        <v>0.4748201438848921</v>
       </c>
       <c r="K185" t="n">
-        <v>0.2859442060085837</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="L185" t="n">
-        <v>0.2301502145922747</v>
+        <v>0.2374100719424461</v>
       </c>
       <c r="M185" t="n">
-        <v>0.05975325487520622</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="N185" t="n">
         <v>0</v>
@@ -16119,13 +16119,13 @@
         <v>1</v>
       </c>
       <c r="S185" t="n">
-        <v>0.06992162857763712</v>
+        <v>0.06809605041355887</v>
       </c>
       <c r="T185" t="n">
         <v>0</v>
       </c>
       <c r="U185" t="n">
-        <v>0.06992162857763712</v>
+        <v>0.06809605041355887</v>
       </c>
       <c r="V185" t="n">
         <v>0.3558658345862208</v>
@@ -16181,25 +16181,25 @@
         <v>1481</v>
       </c>
       <c r="G186" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="H186" t="n">
         <v>3.1</v>
       </c>
       <c r="I186" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="J186" t="n">
-        <v>0.3306780664681976</v>
+        <v>0.30625</v>
       </c>
       <c r="K186" t="n">
-        <v>0.3072105907833578</v>
+        <v>0.30625</v>
       </c>
       <c r="L186" t="n">
-        <v>0.3621113427484446</v>
+        <v>0.3875</v>
       </c>
       <c r="M186" t="n">
-        <v>0.05003100426564178</v>
+        <v>0.05332455562870297</v>
       </c>
       <c r="N186" t="n">
         <v>2</v>
@@ -16217,19 +16217,19 @@
         <v>1</v>
       </c>
       <c r="S186" t="n">
-        <v>0.1250478112870113</v>
+        <v>0.09965915403545589</v>
       </c>
       <c r="T186" t="n">
         <v>2</v>
       </c>
       <c r="U186" t="n">
-        <v>0.1250478112870113</v>
+        <v>0.09965915403545589</v>
       </c>
       <c r="V186" t="n">
         <v>0.4871591540354559</v>
       </c>
       <c r="W186" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
@@ -16279,55 +16279,55 @@
         <v>1481</v>
       </c>
       <c r="G187" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H187" t="n">
         <v>3.5</v>
       </c>
       <c r="I187" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="J187" t="n">
-        <v>0.5657460116663153</v>
+        <v>0.557163531114327</v>
       </c>
       <c r="K187" t="n">
-        <v>0.2699416684236418</v>
+        <v>0.2706222865412445</v>
       </c>
       <c r="L187" t="n">
-        <v>0.1643123199100429</v>
+        <v>0.1722141823444284</v>
       </c>
       <c r="M187" t="n">
-        <v>0.05842972440212746</v>
+        <v>0.05576776165011466</v>
       </c>
       <c r="N187" t="n">
         <v>1</v>
       </c>
       <c r="O187" t="n">
-        <v>0.4014381059865235</v>
+        <v>0.4004323421999652</v>
       </c>
       <c r="P187" t="n">
-        <v>0.3129428747972791</v>
+        <v>0.3133599884648639</v>
       </c>
       <c r="Q187" t="n">
-        <v>0.2856190192161973</v>
+        <v>0.2862076693351709</v>
       </c>
       <c r="R187" t="n">
         <v>1</v>
       </c>
       <c r="S187" t="n">
-        <v>-0.1643079056797918</v>
+        <v>-0.1567311889143619</v>
       </c>
       <c r="T187" t="n">
         <v>-1</v>
       </c>
       <c r="U187" t="n">
-        <v>0.1643079056797918</v>
+        <v>0.1567311889143619</v>
       </c>
       <c r="V187" t="n">
-        <v>0.5985618940134765</v>
+        <v>0.5995676578000348</v>
       </c>
       <c r="W187" t="n">
-        <v>2.175675675675676</v>
+        <v>2.138888888888889</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
@@ -16335,10 +16335,10 @@
         </is>
       </c>
       <c r="Y187" t="n">
-        <v>9.164221028491188</v>
+        <v>9.179619672699342</v>
       </c>
       <c r="Z187" t="n">
-        <v>9.164221028491188</v>
+        <v>9.179619672699342</v>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
@@ -16383,19 +16383,19 @@
         <v>3.8</v>
       </c>
       <c r="I188" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="J188" t="n">
-        <v>0.2102766798418972</v>
+        <v>0.2089704059251724</v>
       </c>
       <c r="K188" t="n">
-        <v>0.2490118577075099</v>
+        <v>0.2474649543850726</v>
       </c>
       <c r="L188" t="n">
-        <v>0.5407114624505929</v>
+        <v>0.543564639689755</v>
       </c>
       <c r="M188" t="n">
-        <v>0.05680868838763575</v>
+        <v>0.06341479903998914</v>
       </c>
       <c r="N188" t="n">
         <v>2</v>
@@ -16413,19 +16413,19 @@
         <v>1</v>
       </c>
       <c r="S188" t="n">
-        <v>0.06843969427367891</v>
+        <v>0.06558651703451679</v>
       </c>
       <c r="T188" t="n">
         <v>2</v>
       </c>
       <c r="U188" t="n">
-        <v>0.06843969427367891</v>
+        <v>0.06558651703451679</v>
       </c>
       <c r="V188" t="n">
         <v>0.6091511567242718</v>
       </c>
       <c r="W188" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
@@ -16573,55 +16573,55 @@
         <v>1481</v>
       </c>
       <c r="G190" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="H190" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="I190" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="J190" t="n">
-        <v>0.1740031071983429</v>
+        <v>0.1656281233419296</v>
       </c>
       <c r="K190" t="n">
-        <v>0.2278612118073537</v>
+        <v>0.2199449674863961</v>
       </c>
       <c r="L190" t="n">
-        <v>0.5981356809943036</v>
+        <v>0.6144269091716742</v>
       </c>
       <c r="M190" t="n">
-        <v>0.04491341991341979</v>
+        <v>0.05002121601793164</v>
       </c>
       <c r="N190" t="n">
         <v>2</v>
       </c>
       <c r="O190" t="n">
-        <v>0.08103257282901304</v>
+        <v>0.08097761801861028</v>
       </c>
       <c r="P190" t="n">
-        <v>0.2903271265316048</v>
+        <v>0.2903499805399003</v>
       </c>
       <c r="Q190" t="n">
-        <v>0.6286403006393823</v>
+        <v>0.6286724014414894</v>
       </c>
       <c r="R190" t="n">
         <v>1</v>
       </c>
       <c r="S190" t="n">
-        <v>0.03050461964507867</v>
+        <v>0.0142454922698152</v>
       </c>
       <c r="T190" t="n">
         <v>2</v>
       </c>
       <c r="U190" t="n">
-        <v>0.03050461964507867</v>
+        <v>0.0142454922698152</v>
       </c>
       <c r="V190" t="n">
-        <v>0.6286403006393823</v>
+        <v>0.6286724014414894</v>
       </c>
       <c r="W190" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
@@ -16629,10 +16629,10 @@
         </is>
       </c>
       <c r="Y190" t="n">
-        <v>9.624733415366299</v>
+        <v>9.625224891433593</v>
       </c>
       <c r="Z190" t="n">
-        <v>9.624733415366299</v>
+        <v>9.625224891433593</v>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
@@ -16695,28 +16695,28 @@
         <v>1</v>
       </c>
       <c r="O191" t="n">
-        <v>0.3609999082839134</v>
+        <v>0.3619446495385069</v>
       </c>
       <c r="P191" t="n">
-        <v>0.3275469899490511</v>
+        <v>0.3271958842757376</v>
       </c>
       <c r="Q191" t="n">
-        <v>0.3114531017670354</v>
+        <v>0.3108594661857555</v>
       </c>
       <c r="R191" t="n">
         <v>1</v>
       </c>
       <c r="S191" t="n">
-        <v>-0.03516622590139018</v>
+        <v>-0.0342214846467967</v>
       </c>
       <c r="T191" t="n">
         <v>1</v>
       </c>
       <c r="U191" t="n">
-        <v>-0.03516622590139018</v>
+        <v>-0.0342214846467967</v>
       </c>
       <c r="V191" t="n">
-        <v>0.3609999082839134</v>
+        <v>0.3619446495385069</v>
       </c>
       <c r="W191" t="n">
         <v>2.4</v>
@@ -16727,10 +16727,10 @@
         </is>
       </c>
       <c r="Y191" t="n">
-        <v>5.52705239653018</v>
+        <v>5.541516761466237</v>
       </c>
       <c r="Z191" t="n">
-        <v>5.52705239653018</v>
+        <v>5.541516761466237</v>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
@@ -16877,13 +16877,13 @@
         <v>2</v>
       </c>
       <c r="O193" t="n">
-        <v>0.1838937751487623</v>
+        <v>0.1832230959753477</v>
       </c>
       <c r="P193" t="n">
-        <v>0.2459078968870776</v>
+        <v>0.2459087725764776</v>
       </c>
       <c r="Q193" t="n">
-        <v>0.57019832796416</v>
+        <v>0.5708681314481747</v>
       </c>
       <c r="R193" t="n">
         <v>1</v>
@@ -16894,7 +16894,7 @@
       </c>
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="n">
-        <v>0.42980167203584</v>
+        <v>0.4291318685518253</v>
       </c>
       <c r="W193" t="inlineStr"/>
       <c r="X193" t="inlineStr">
@@ -16903,10 +16903,10 @@
         </is>
       </c>
       <c r="Y193" t="n">
-        <v>6.580434806066749</v>
+        <v>6.570179847916965</v>
       </c>
       <c r="Z193" t="n">
-        <v>6.580434806066749</v>
+        <v>6.570179847916965</v>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
@@ -16955,13 +16955,13 @@
         <v>1</v>
       </c>
       <c r="O194" t="n">
-        <v>0.7540168523407008</v>
+        <v>0.7541548770431651</v>
       </c>
       <c r="P194" t="n">
-        <v>0.131951511035547</v>
+        <v>0.1318757805956413</v>
       </c>
       <c r="Q194" t="n">
-        <v>0.1140316366237523</v>
+        <v>0.1139693423611936</v>
       </c>
       <c r="R194" t="n">
         <v>1</v>
@@ -16972,7 +16972,7 @@
       </c>
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="n">
-        <v>0.2459831476592992</v>
+        <v>0.2458451229568349</v>
       </c>
       <c r="W194" t="inlineStr"/>
       <c r="X194" t="inlineStr">
@@ -16981,10 +16981,10 @@
         </is>
       </c>
       <c r="Y194" t="n">
-        <v>3.766099975590909</v>
+        <v>3.763986762415422</v>
       </c>
       <c r="Z194" t="n">
-        <v>3.766099975590909</v>
+        <v>3.763986762415422</v>
       </c>
       <c r="AA194" t="inlineStr">
         <is>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -19261,28 +19261,28 @@
         <v>1</v>
       </c>
       <c r="O217" t="n">
-        <v>0.4135967408248821</v>
+        <v>0.3989778390404748</v>
       </c>
       <c r="P217" t="n">
-        <v>0.3806498419345348</v>
+        <v>0.3927254384539149</v>
       </c>
       <c r="Q217" t="n">
-        <v>0.2057534172405832</v>
+        <v>0.2082967225056102</v>
       </c>
       <c r="R217" t="n">
         <v>1</v>
       </c>
       <c r="S217" t="n">
-        <v>0.03282510207077338</v>
+        <v>0.01820620028636616</v>
       </c>
       <c r="T217" t="n">
         <v>1</v>
       </c>
       <c r="U217" t="n">
-        <v>0.03282510207077338</v>
+        <v>0.01820620028636616</v>
       </c>
       <c r="V217" t="n">
-        <v>0.4135967408248821</v>
+        <v>0.3989778390404748</v>
       </c>
       <c r="W217" t="n">
         <v>2.5</v>
@@ -19293,10 +19293,10 @@
         </is>
       </c>
       <c r="Y217" t="n">
-        <v>5.202589110761217</v>
+        <v>6.081161189893853</v>
       </c>
       <c r="Z217" t="n">
-        <v>5.202589110761217</v>
+        <v>6.081161189893853</v>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
@@ -19336,25 +19336,25 @@
         <v>481</v>
       </c>
       <c r="G218" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H218" t="n">
         <v>3.6</v>
       </c>
       <c r="I218" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J218" t="n">
-        <v>0.4321728691476591</v>
+        <v>0.4465116279069767</v>
       </c>
       <c r="K218" t="n">
-        <v>0.2581032412965186</v>
+        <v>0.2604651162790698</v>
       </c>
       <c r="L218" t="n">
-        <v>0.3097238895558223</v>
+        <v>0.2930232558139535</v>
       </c>
       <c r="M218" t="n">
-        <v>0.07622739018087854</v>
+        <v>0.06646825396825395</v>
       </c>
       <c r="N218" t="n">
         <v>1</v>
@@ -19372,19 +19372,19 @@
         <v>1</v>
       </c>
       <c r="S218" t="n">
-        <v>0.01766854371892418</v>
+        <v>0.003329784959606508</v>
       </c>
       <c r="T218" t="n">
         <v>1</v>
       </c>
       <c r="U218" t="n">
-        <v>0.01766854371892418</v>
+        <v>0.003329784959606508</v>
       </c>
       <c r="V218" t="n">
         <v>0.4498414128665832</v>
       </c>
       <c r="W218" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="X218" t="inlineStr">
         <is>
@@ -19392,10 +19392,10 @@
         </is>
       </c>
       <c r="Y218" t="n">
-        <v>5.658506958931847</v>
+        <v>6.856416256377014</v>
       </c>
       <c r="Z218" t="n">
-        <v>5.658506958931847</v>
+        <v>6.856416256377014</v>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
@@ -19435,25 +19435,25 @@
         <v>481</v>
       </c>
       <c r="G219" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="H219" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I219" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="J219" t="n">
-        <v>0.539701816903434</v>
+        <v>0.5256916996047432</v>
       </c>
       <c r="K219" t="n">
-        <v>0.2421738922002589</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="L219" t="n">
-        <v>0.2181242908963071</v>
+        <v>0.225296442687747</v>
       </c>
       <c r="M219" t="n">
-        <v>0.05878571005591793</v>
+        <v>0.05680868838763575</v>
       </c>
       <c r="N219" t="n">
         <v>1</v>
@@ -19471,19 +19471,19 @@
         <v>1</v>
       </c>
       <c r="S219" t="n">
-        <v>-0.1769510796651999</v>
+        <v>-0.1629409623665091</v>
       </c>
       <c r="T219" t="n">
         <v>1</v>
       </c>
       <c r="U219" t="n">
-        <v>-0.1769510796651999</v>
+        <v>-0.1629409623665091</v>
       </c>
       <c r="V219" t="n">
         <v>0.3627507372382341</v>
       </c>
       <c r="W219" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="X219" t="inlineStr">
         <is>
@@ -19491,10 +19491,10 @@
         </is>
       </c>
       <c r="Y219" t="n">
-        <v>4.563002676743296</v>
+        <v>5.528993064386082</v>
       </c>
       <c r="Z219" t="n">
-        <v>4.563002676743296</v>
+        <v>5.528993064386082</v>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
@@ -19558,28 +19558,28 @@
         <v>1</v>
       </c>
       <c r="O220" t="n">
-        <v>0.5629561455712984</v>
+        <v>0.5491749849148966</v>
       </c>
       <c r="P220" t="n">
-        <v>0.2377463557826995</v>
+        <v>0.2434615904871366</v>
       </c>
       <c r="Q220" t="n">
-        <v>0.1992974986460023</v>
+        <v>0.2073634245979667</v>
       </c>
       <c r="R220" t="n">
         <v>1</v>
       </c>
       <c r="S220" t="n">
-        <v>-0.3017521705230335</v>
+        <v>-0.3155333311794353</v>
       </c>
       <c r="T220" t="n">
         <v>1</v>
       </c>
       <c r="U220" t="n">
-        <v>-0.3017521705230335</v>
+        <v>-0.3155333311794353</v>
       </c>
       <c r="V220" t="n">
-        <v>0.5629561455712984</v>
+        <v>0.5491749849148966</v>
       </c>
       <c r="W220" t="n">
         <v>1.09</v>
@@ -19590,10 +19590,10 @@
         </is>
       </c>
       <c r="Y220" t="n">
-        <v>7.081365068167733</v>
+        <v>8.370443864142086</v>
       </c>
       <c r="Z220" t="n">
-        <v>7.081365068167733</v>
+        <v>8.370443864142086</v>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
@@ -19657,28 +19657,28 @@
         <v>1</v>
       </c>
       <c r="O221" t="n">
-        <v>0.4212253382936241</v>
+        <v>0.4193737193529274</v>
       </c>
       <c r="P221" t="n">
-        <v>0.3428374306281334</v>
+        <v>0.3441924580806889</v>
       </c>
       <c r="Q221" t="n">
-        <v>0.2359372310782425</v>
+        <v>0.2364338225663835</v>
       </c>
       <c r="R221" t="n">
         <v>1</v>
       </c>
       <c r="S221" t="n">
-        <v>0.0383032537231317</v>
+        <v>0.03645163478243496</v>
       </c>
       <c r="T221" t="n">
         <v>1</v>
       </c>
       <c r="U221" t="n">
-        <v>0.0383032537231317</v>
+        <v>0.03645163478243496</v>
       </c>
       <c r="V221" t="n">
-        <v>0.4212253382936241</v>
+        <v>0.4193737193529274</v>
       </c>
       <c r="W221" t="n">
         <v>2.45</v>
@@ -19689,10 +19689,10 @@
         </is>
       </c>
       <c r="Y221" t="n">
-        <v>5.29854842137402</v>
+        <v>6.392032179841803</v>
       </c>
       <c r="Z221" t="n">
-        <v>5.29854842137402</v>
+        <v>6.392032179841803</v>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>481</v>
       </c>
       <c r="G222" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H222" t="n">
         <v>5</v>
@@ -19741,46 +19741,46 @@
         <v>7</v>
       </c>
       <c r="J222" t="n">
-        <v>0.6694720734506504</v>
+        <v>0.66793893129771</v>
       </c>
       <c r="K222" t="n">
-        <v>0.1928079571537873</v>
+        <v>0.1937022900763359</v>
       </c>
       <c r="L222" t="n">
-        <v>0.1377199693955624</v>
+        <v>0.1383587786259542</v>
       </c>
       <c r="M222" t="n">
-        <v>0.03730158730158717</v>
+        <v>0.0325123152709359</v>
       </c>
       <c r="N222" t="n">
         <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>0.6770695003939216</v>
+        <v>0.6788392562006584</v>
       </c>
       <c r="P222" t="n">
-        <v>0.232959881634916</v>
+        <v>0.2325314729990392</v>
       </c>
       <c r="Q222" t="n">
-        <v>0.08997061797116201</v>
+        <v>0.08862927080030206</v>
       </c>
       <c r="R222" t="n">
         <v>1</v>
       </c>
       <c r="S222" t="n">
-        <v>0.007597426943271146</v>
+        <v>0.01090032490294846</v>
       </c>
       <c r="T222" t="n">
         <v>1</v>
       </c>
       <c r="U222" t="n">
-        <v>0.007597426943271146</v>
+        <v>0.01090032490294846</v>
       </c>
       <c r="V222" t="n">
-        <v>0.6770695003939216</v>
+        <v>0.6788392562006584</v>
       </c>
       <c r="W222" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X222" t="inlineStr">
         <is>
@@ -19788,10 +19788,10 @@
         </is>
       </c>
       <c r="Y222" t="n">
-        <v>8.516784738082343</v>
+        <v>10.34676750195409</v>
       </c>
       <c r="Z222" t="n">
-        <v>8.516784738082343</v>
+        <v>10.34676750195409</v>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
@@ -19831,55 +19831,55 @@
         <v>481</v>
       </c>
       <c r="G223" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H223" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I223" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="J223" t="n">
-        <v>0.2343636426568828</v>
+        <v>0.2245508982035928</v>
       </c>
       <c r="K223" t="n">
-        <v>0.253366100169603</v>
+        <v>0.2514970059880239</v>
       </c>
       <c r="L223" t="n">
-        <v>0.5122702571735143</v>
+        <v>0.5239520958083832</v>
       </c>
       <c r="M223" t="n">
-        <v>0.0667183577019641</v>
+        <v>0.06031746031746033</v>
       </c>
       <c r="N223" t="n">
         <v>0</v>
       </c>
       <c r="O223" t="n">
-        <v>0.3169820802417898</v>
+        <v>0.3053589458051205</v>
       </c>
       <c r="P223" t="n">
-        <v>0.4205494237733842</v>
+        <v>0.4237776487019204</v>
       </c>
       <c r="Q223" t="n">
-        <v>0.262468495984826</v>
+        <v>0.2708634054929589</v>
       </c>
       <c r="R223" t="n">
         <v>1</v>
       </c>
       <c r="S223" t="n">
-        <v>0.1671833236037812</v>
+        <v>0.1722806427138965</v>
       </c>
       <c r="T223" t="n">
         <v>0</v>
       </c>
       <c r="U223" t="n">
-        <v>0.1671833236037812</v>
+        <v>0.1722806427138965</v>
       </c>
       <c r="V223" t="n">
-        <v>0.4205494237733842</v>
+        <v>0.4237776487019204</v>
       </c>
       <c r="W223" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X223" t="inlineStr">
         <is>
@@ -19887,10 +19887,10 @@
         </is>
       </c>
       <c r="Y223" t="n">
-        <v>5.290046165007608</v>
+        <v>6.459156219373769</v>
       </c>
       <c r="Z223" t="n">
-        <v>5.290046165007608</v>
+        <v>6.459156219373769</v>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
@@ -19954,28 +19954,28 @@
         <v>2</v>
       </c>
       <c r="O224" t="n">
-        <v>0.247572887414938</v>
+        <v>0.2636927884311544</v>
       </c>
       <c r="P224" t="n">
-        <v>0.3579287211581472</v>
+        <v>0.3442526354915076</v>
       </c>
       <c r="Q224" t="n">
-        <v>0.3944983914269147</v>
+        <v>0.392054576077338</v>
       </c>
       <c r="R224" t="n">
         <v>1</v>
       </c>
       <c r="S224" t="n">
-        <v>-0.04071039116473396</v>
+        <v>-0.04315420651431068</v>
       </c>
       <c r="T224" t="n">
         <v>2</v>
       </c>
       <c r="U224" t="n">
-        <v>-0.04071039116473396</v>
+        <v>-0.04315420651431068</v>
       </c>
       <c r="V224" t="n">
-        <v>0.3944983914269147</v>
+        <v>0.392054576077338</v>
       </c>
       <c r="W224" t="n">
         <v>2.15</v>
@@ -19986,10 +19986,10 @@
         </is>
       </c>
       <c r="Y224" t="n">
-        <v>4.962353018926422</v>
+        <v>5.975637840175709</v>
       </c>
       <c r="Z224" t="n">
-        <v>4.962353018926422</v>
+        <v>5.975637840175709</v>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
@@ -20053,28 +20053,28 @@
         <v>0</v>
       </c>
       <c r="O225" t="n">
-        <v>0.2050307080504469</v>
+        <v>0.2272182115925958</v>
       </c>
       <c r="P225" t="n">
-        <v>0.5048616165758183</v>
+        <v>0.4944436303175734</v>
       </c>
       <c r="Q225" t="n">
-        <v>0.290107675373735</v>
+        <v>0.2783381580898309</v>
       </c>
       <c r="R225" t="n">
         <v>1</v>
       </c>
       <c r="S225" t="n">
-        <v>0.2668246191748093</v>
+        <v>0.2564066329165644</v>
       </c>
       <c r="T225" t="n">
         <v>0</v>
       </c>
       <c r="U225" t="n">
-        <v>0.2668246191748093</v>
+        <v>0.2564066329165644</v>
       </c>
       <c r="V225" t="n">
-        <v>0.5048616165758183</v>
+        <v>0.4944436303175734</v>
       </c>
       <c r="W225" t="n">
         <v>4</v>
@@ -20085,10 +20085,10 @@
         </is>
       </c>
       <c r="Y225" t="n">
-        <v>6.350600209276699</v>
+        <v>7.536236655420911</v>
       </c>
       <c r="Z225" t="n">
-        <v>6.350600209276699</v>
+        <v>7.536236655420911</v>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
@@ -20131,49 +20131,49 @@
         <v>1.25</v>
       </c>
       <c r="H226" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="I226" t="n">
         <v>10</v>
       </c>
       <c r="J226" t="n">
-        <v>0.75</v>
+        <v>0.7449392712550608</v>
       </c>
       <c r="K226" t="n">
-        <v>0.15625</v>
+        <v>0.1619433198380567</v>
       </c>
       <c r="L226" t="n">
-        <v>0.09375</v>
+        <v>0.0931174089068826</v>
       </c>
       <c r="M226" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.07391304347826089</v>
       </c>
       <c r="N226" t="n">
         <v>1</v>
       </c>
       <c r="O226" t="n">
-        <v>0.5322684351398148</v>
+        <v>0.5238695024426842</v>
       </c>
       <c r="P226" t="n">
-        <v>0.2989215459776636</v>
+        <v>0.2999955701380816</v>
       </c>
       <c r="Q226" t="n">
-        <v>0.1688100188825216</v>
+        <v>0.1761349274192343</v>
       </c>
       <c r="R226" t="n">
         <v>1</v>
       </c>
       <c r="S226" t="n">
-        <v>-0.2177315648601852</v>
+        <v>-0.2210697688123766</v>
       </c>
       <c r="T226" t="n">
         <v>1</v>
       </c>
       <c r="U226" t="n">
-        <v>-0.2177315648601852</v>
+        <v>-0.2210697688123766</v>
       </c>
       <c r="V226" t="n">
-        <v>0.5322684351398148</v>
+        <v>0.5238695024426842</v>
       </c>
       <c r="W226" t="n">
         <v>1.25</v>
@@ -20184,10 +20184,10 @@
         </is>
       </c>
       <c r="Y226" t="n">
-        <v>6.695347644997011</v>
+        <v>7.98474144449981</v>
       </c>
       <c r="Z226" t="n">
-        <v>6.695347644997011</v>
+        <v>7.98474144449981</v>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
@@ -20227,25 +20227,25 @@
         <v>481</v>
       </c>
       <c r="G227" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="H227" t="n">
-        <v>5.59</v>
+        <v>6.2</v>
       </c>
       <c r="I227" t="n">
-        <v>9.15</v>
+        <v>8.5</v>
       </c>
       <c r="J227" t="n">
-        <v>0.7184292695122826</v>
+        <v>0.7399399062087557</v>
       </c>
       <c r="K227" t="n">
-        <v>0.174787800811575</v>
+        <v>0.1503748841650052</v>
       </c>
       <c r="L227" t="n">
-        <v>0.1067829296761426</v>
+        <v>0.1096852096262391</v>
       </c>
       <c r="M227" t="n">
-        <v>0.02347461169869258</v>
+        <v>0.07258817505496817</v>
       </c>
       <c r="N227" t="n">
         <v>1</v>
@@ -20263,19 +20263,19 @@
         <v>1</v>
       </c>
       <c r="S227" t="n">
-        <v>-0.02054379223243485</v>
+        <v>-0.04205442892890798</v>
       </c>
       <c r="T227" t="n">
         <v>1</v>
       </c>
       <c r="U227" t="n">
-        <v>-0.02054379223243485</v>
+        <v>-0.04205442892890798</v>
       </c>
       <c r="V227" t="n">
         <v>0.6978854772798477</v>
       </c>
       <c r="W227" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="X227" t="inlineStr">
         <is>
@@ -20283,10 +20283,10 @@
         </is>
       </c>
       <c r="Y227" t="n">
-        <v>8.778626682147443</v>
+        <v>10.63706718556422</v>
       </c>
       <c r="Z227" t="n">
-        <v>8.778626682147443</v>
+        <v>10.63706718556422</v>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
@@ -20326,55 +20326,55 @@
         <v>481</v>
       </c>
       <c r="G228" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H228" t="n">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="I228" t="n">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
       <c r="J228" t="n">
-        <v>0.5325312570829989</v>
+        <v>0.5167364016736402</v>
       </c>
       <c r="K228" t="n">
-        <v>0.2365369418596816</v>
+        <v>0.2447698744769874</v>
       </c>
       <c r="L228" t="n">
-        <v>0.2309318010573194</v>
+        <v>0.2384937238493724</v>
       </c>
       <c r="M228" t="n">
-        <v>0.02613335867818556</v>
+        <v>0.075123706702654</v>
       </c>
       <c r="N228" t="n">
         <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>0.2565698812124252</v>
+        <v>0.2600936500338568</v>
       </c>
       <c r="P228" t="n">
-        <v>0.4472026458110161</v>
+        <v>0.4395775508286483</v>
       </c>
       <c r="Q228" t="n">
-        <v>0.2962274729765587</v>
+        <v>0.3003287991374951</v>
       </c>
       <c r="R228" t="n">
         <v>1</v>
       </c>
       <c r="S228" t="n">
-        <v>0.2106657039513345</v>
+        <v>0.1948076763516609</v>
       </c>
       <c r="T228" t="n">
         <v>0</v>
       </c>
       <c r="U228" t="n">
-        <v>0.2106657039513345</v>
+        <v>0.1948076763516609</v>
       </c>
       <c r="V228" t="n">
-        <v>0.4472026458110161</v>
+        <v>0.4395775508286483</v>
       </c>
       <c r="W228" t="n">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="X228" t="inlineStr">
         <is>
@@ -20382,10 +20382,10 @@
         </is>
       </c>
       <c r="Y228" t="n">
-        <v>5.625314190725431</v>
+        <v>6.699975989835837</v>
       </c>
       <c r="Z228" t="n">
-        <v>5.625314190725431</v>
+        <v>6.699975989835837</v>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
@@ -20425,55 +20425,55 @@
         <v>481</v>
       </c>
       <c r="G229" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="H229" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="I229" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="J229" t="n">
-        <v>0.4182949968376552</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="K229" t="n">
-        <v>0.2662916236698734</v>
+        <v>0.274390243902439</v>
       </c>
       <c r="L229" t="n">
-        <v>0.3154133794924714</v>
+        <v>0.3109756097560976</v>
       </c>
       <c r="M229" t="n">
-        <v>0.02603318854132586</v>
+        <v>0.07189542483660127</v>
       </c>
       <c r="N229" t="n">
         <v>1</v>
       </c>
       <c r="O229" t="n">
-        <v>0.3746857391025852</v>
+        <v>0.380636738846739</v>
       </c>
       <c r="P229" t="n">
-        <v>0.2974032641796368</v>
+        <v>0.3017834860568411</v>
       </c>
       <c r="Q229" t="n">
-        <v>0.327910996717778</v>
+        <v>0.31757977509642</v>
       </c>
       <c r="R229" t="n">
         <v>1</v>
       </c>
       <c r="S229" t="n">
-        <v>-0.04360925773506996</v>
+        <v>-0.03399740749472441</v>
       </c>
       <c r="T229" t="n">
         <v>1</v>
       </c>
       <c r="U229" t="n">
-        <v>-0.04360925773506996</v>
+        <v>-0.03399740749472441</v>
       </c>
       <c r="V229" t="n">
-        <v>0.3746857391025852</v>
+        <v>0.380636738846739</v>
       </c>
       <c r="W229" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="X229" t="inlineStr">
         <is>
@@ -20481,10 +20481,10 @@
         </is>
       </c>
       <c r="Y229" t="n">
-        <v>4.71313178707562</v>
+        <v>5.801608854490116</v>
       </c>
       <c r="Z229" t="n">
-        <v>4.71313178707562</v>
+        <v>5.801608854490116</v>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
@@ -20524,55 +20524,55 @@
         <v>481</v>
       </c>
       <c r="G230" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="H230" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="I230" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="J230" t="n">
-        <v>0.3375149298574894</v>
+        <v>0.3411487662537115</v>
       </c>
       <c r="K230" t="n">
-        <v>0.2594197200234427</v>
+        <v>0.2759291491757961</v>
       </c>
       <c r="L230" t="n">
-        <v>0.403065350119068</v>
+        <v>0.3829220845704924</v>
       </c>
       <c r="M230" t="n">
-        <v>0.02520134855005307</v>
+        <v>0.06591727600130959</v>
       </c>
       <c r="N230" t="n">
         <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>0.3118901882843965</v>
+        <v>0.3132764197385587</v>
       </c>
       <c r="P230" t="n">
-        <v>0.4044958678268427</v>
+        <v>0.4047879625307436</v>
       </c>
       <c r="Q230" t="n">
-        <v>0.2836139438887608</v>
+        <v>0.2819356177306978</v>
       </c>
       <c r="R230" t="n">
         <v>1</v>
       </c>
       <c r="S230" t="n">
-        <v>0.1450761478034001</v>
+        <v>0.1288588133549475</v>
       </c>
       <c r="T230" t="n">
         <v>0</v>
       </c>
       <c r="U230" t="n">
-        <v>0.1450761478034001</v>
+        <v>0.1288588133549475</v>
       </c>
       <c r="V230" t="n">
-        <v>0.4044958678268427</v>
+        <v>0.4047879625307436</v>
       </c>
       <c r="W230" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="X230" t="inlineStr">
         <is>
@@ -20580,10 +20580,10 @@
         </is>
       </c>
       <c r="Y230" t="n">
-        <v>5.088110203931369</v>
+        <v>6.169718232466657</v>
       </c>
       <c r="Z230" t="n">
-        <v>5.088110203931369</v>
+        <v>6.169718232466657</v>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
@@ -20623,25 +20623,25 @@
         <v>481</v>
       </c>
       <c r="G231" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="H231" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="I231" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="J231" t="n">
-        <v>0.2308514762339465</v>
+        <v>0.2113676731793961</v>
       </c>
       <c r="K231" t="n">
-        <v>0.2453887228481749</v>
+        <v>0.2415630550621669</v>
       </c>
       <c r="L231" t="n">
-        <v>0.5237598009178787</v>
+        <v>0.547069271758437</v>
       </c>
       <c r="M231" t="n">
-        <v>0.02649040201244324</v>
+        <v>0.07524828113063409</v>
       </c>
       <c r="N231" t="n">
         <v>0</v>
@@ -20659,19 +20659,19 @@
         <v>1</v>
       </c>
       <c r="S231" t="n">
-        <v>0.1507183700298518</v>
+        <v>0.1545440378158598</v>
       </c>
       <c r="T231" t="n">
         <v>0</v>
       </c>
       <c r="U231" t="n">
-        <v>0.1507183700298518</v>
+        <v>0.1545440378158598</v>
       </c>
       <c r="V231" t="n">
         <v>0.3961070928780267</v>
       </c>
       <c r="W231" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="X231" t="inlineStr">
         <is>
@@ -20679,10 +20679,10 @@
         </is>
       </c>
       <c r="Y231" t="n">
-        <v>4.982588702204121</v>
+        <v>6.03740570164142</v>
       </c>
       <c r="Z231" t="n">
-        <v>4.982588702204121</v>
+        <v>6.03740570164142</v>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
@@ -20722,55 +20722,55 @@
         <v>481</v>
       </c>
       <c r="G232" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="H232" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="I232" t="n">
-        <v>3.82</v>
+        <v>3.65</v>
       </c>
       <c r="J232" t="n">
-        <v>0.4845874148644616</v>
+        <v>0.4899328859060403</v>
       </c>
       <c r="K232" t="n">
-        <v>0.260433343282772</v>
+        <v>0.2550335570469799</v>
       </c>
       <c r="L232" t="n">
-        <v>0.2549792418527664</v>
+        <v>0.2550335570469799</v>
       </c>
       <c r="M232" t="n">
-        <v>0.02667222166737226</v>
+        <v>0.07426099495313609</v>
       </c>
       <c r="N232" t="n">
         <v>1</v>
       </c>
       <c r="O232" t="n">
-        <v>0.530349760778192</v>
+        <v>0.5277683832868997</v>
       </c>
       <c r="P232" t="n">
-        <v>0.2626856615018118</v>
+        <v>0.2589914324549981</v>
       </c>
       <c r="Q232" t="n">
-        <v>0.206964577719996</v>
+        <v>0.2132401842581021</v>
       </c>
       <c r="R232" t="n">
         <v>1</v>
       </c>
       <c r="S232" t="n">
-        <v>0.04576234591373041</v>
+        <v>0.03783549738085934</v>
       </c>
       <c r="T232" t="n">
         <v>1</v>
       </c>
       <c r="U232" t="n">
-        <v>0.04576234591373041</v>
+        <v>0.03783549738085934</v>
       </c>
       <c r="V232" t="n">
-        <v>0.530349760778192</v>
+        <v>0.5277683832868997</v>
       </c>
       <c r="W232" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="X232" t="inlineStr">
         <is>
@@ -20778,10 +20778,10 @@
         </is>
       </c>
       <c r="Y232" t="n">
-        <v>6.671212845672995</v>
+        <v>8.044167609448934</v>
       </c>
       <c r="Z232" t="n">
-        <v>6.671212845672995</v>
+        <v>8.044167609448934</v>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
@@ -20821,55 +20821,55 @@
         <v>481</v>
       </c>
       <c r="G233" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="H233" t="n">
-        <v>5.74</v>
+        <v>5.8</v>
       </c>
       <c r="I233" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="J233" t="n">
-        <v>0.1201409216741935</v>
+        <v>0.1240335581510117</v>
       </c>
       <c r="K233" t="n">
-        <v>0.169536840690064</v>
+        <v>0.1603882217469979</v>
       </c>
       <c r="L233" t="n">
-        <v>0.7103222376357425</v>
+        <v>0.7155782201019903</v>
       </c>
       <c r="M233" t="n">
-        <v>0.02759982529729132</v>
+        <v>0.07497789566755086</v>
       </c>
       <c r="N233" t="n">
         <v>2</v>
       </c>
       <c r="O233" t="n">
-        <v>0.2583208704825306</v>
+        <v>0.2620487569102588</v>
       </c>
       <c r="P233" t="n">
-        <v>0.3557625332145566</v>
+        <v>0.3548187203193317</v>
       </c>
       <c r="Q233" t="n">
-        <v>0.3859165963029126</v>
+        <v>0.3831325227704095</v>
       </c>
       <c r="R233" t="n">
         <v>1</v>
       </c>
       <c r="S233" t="n">
-        <v>-0.3244056413328299</v>
+        <v>-0.3324456973315809</v>
       </c>
       <c r="T233" t="n">
         <v>2</v>
       </c>
       <c r="U233" t="n">
-        <v>-0.3244056413328299</v>
+        <v>-0.3324456973315809</v>
       </c>
       <c r="V233" t="n">
-        <v>0.3859165963029126</v>
+        <v>0.3831325227704095</v>
       </c>
       <c r="W233" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="X233" t="inlineStr">
         <is>
@@ -20877,10 +20877,10 @@
         </is>
       </c>
       <c r="Y233" t="n">
-        <v>4.85440353708604</v>
+        <v>5.839649223778512</v>
       </c>
       <c r="Z233" t="n">
-        <v>4.85440353708604</v>
+        <v>5.839649223778512</v>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
@@ -20920,25 +20920,25 @@
         <v>481</v>
       </c>
       <c r="G234" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="H234" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="I234" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="J234" t="n">
-        <v>0.5449139057541359</v>
+        <v>0.5605730302086578</v>
       </c>
       <c r="K234" t="n">
-        <v>0.2339078876018953</v>
+        <v>0.232637807536593</v>
       </c>
       <c r="L234" t="n">
-        <v>0.221178206643969</v>
+        <v>0.2067891622547493</v>
       </c>
       <c r="M234" t="n">
-        <v>0.02522474096882554</v>
+        <v>0.07463186077643913</v>
       </c>
       <c r="N234" t="n">
         <v>1</v>
@@ -20956,19 +20956,19 @@
         <v>1</v>
       </c>
       <c r="S234" t="n">
-        <v>0.0245498624326751</v>
+        <v>0.008890737978153207</v>
       </c>
       <c r="T234" t="n">
         <v>1</v>
       </c>
       <c r="U234" t="n">
-        <v>0.0245498624326751</v>
+        <v>0.008890737978153207</v>
       </c>
       <c r="V234" t="n">
         <v>0.569463768186811</v>
       </c>
       <c r="W234" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="X234" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         </is>
       </c>
       <c r="Y234" t="n">
-        <v>7.16322375614696</v>
+        <v>8.679682496844231</v>
       </c>
       <c r="Z234" t="n">
-        <v>7.16322375614696</v>
+        <v>8.679682496844231</v>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
@@ -21019,25 +21019,25 @@
         <v>481</v>
       </c>
       <c r="G235" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="H235" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="I235" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J235" t="n">
-        <v>0.4319924318371151</v>
+        <v>0.4337722695584818</v>
       </c>
       <c r="K235" t="n">
-        <v>0.2313513971449953</v>
+        <v>0.233152594887684</v>
       </c>
       <c r="L235" t="n">
-        <v>0.3366561710178897</v>
+        <v>0.3330751355538342</v>
       </c>
       <c r="M235" t="n">
-        <v>0.02427228695764105</v>
+        <v>0.07225913621262459</v>
       </c>
       <c r="N235" t="n">
         <v>2</v>
@@ -21055,19 +21055,19 @@
         <v>1</v>
       </c>
       <c r="S235" t="n">
-        <v>0.1041589748823221</v>
+        <v>0.1077400103463775</v>
       </c>
       <c r="T235" t="n">
         <v>2</v>
       </c>
       <c r="U235" t="n">
-        <v>0.1041589748823221</v>
+        <v>0.1077400103463775</v>
       </c>
       <c r="V235" t="n">
         <v>0.4408151459002118</v>
       </c>
       <c r="W235" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="X235" t="inlineStr">
         <is>
@@ -21075,10 +21075,10 @@
         </is>
       </c>
       <c r="Y235" t="n">
-        <v>5.544966513384789</v>
+        <v>6.71883923080204</v>
       </c>
       <c r="Z235" t="n">
-        <v>5.544966513384789</v>
+        <v>6.71883923080204</v>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
@@ -21118,25 +21118,25 @@
         <v>481</v>
       </c>
       <c r="G236" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="H236" t="n">
-        <v>4.22</v>
+        <v>4.15</v>
       </c>
       <c r="I236" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="J236" t="n">
-        <v>0.2414799967831536</v>
+        <v>0.2331308380691097</v>
       </c>
       <c r="K236" t="n">
-        <v>0.2311799021336352</v>
+        <v>0.2247044222352864</v>
       </c>
       <c r="L236" t="n">
-        <v>0.5273401010832111</v>
+        <v>0.5421647396956039</v>
       </c>
       <c r="M236" t="n">
-        <v>0.02503211766033786</v>
+        <v>0.07235920425889608</v>
       </c>
       <c r="N236" t="n">
         <v>0</v>
@@ -21154,19 +21154,19 @@
         <v>1</v>
       </c>
       <c r="S236" t="n">
-        <v>0.2094175212413278</v>
+        <v>0.2158930011396766</v>
       </c>
       <c r="T236" t="n">
         <v>0</v>
       </c>
       <c r="U236" t="n">
-        <v>0.2094175212413278</v>
+        <v>0.2158930011396766</v>
       </c>
       <c r="V236" t="n">
         <v>0.440597423374963</v>
       </c>
       <c r="W236" t="n">
-        <v>4.22</v>
+        <v>4.15</v>
       </c>
       <c r="X236" t="inlineStr">
         <is>
@@ -21174,10 +21174,10 @@
         </is>
       </c>
       <c r="Y236" t="n">
-        <v>5.542227805055591</v>
+        <v>6.715520736286424</v>
       </c>
       <c r="Z236" t="n">
-        <v>5.542227805055591</v>
+        <v>6.715520736286424</v>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
@@ -21241,28 +21241,28 @@
         <v>1</v>
       </c>
       <c r="O237" t="n">
-        <v>0.5521509364845084</v>
+        <v>0.5526334122498713</v>
       </c>
       <c r="P237" t="n">
-        <v>0.3223219193192516</v>
+        <v>0.318282284979291</v>
       </c>
       <c r="Q237" t="n">
-        <v>0.1255271441962401</v>
+        <v>0.1290843027708378</v>
       </c>
       <c r="R237" t="n">
         <v>1</v>
       </c>
       <c r="S237" t="n">
-        <v>-0.172924592216398</v>
+        <v>-0.1724421164510351</v>
       </c>
       <c r="T237" t="n">
         <v>-1</v>
       </c>
       <c r="U237" t="n">
-        <v>0.172924592216398</v>
+        <v>0.1724421164510351</v>
       </c>
       <c r="V237" t="n">
-        <v>0.4478490635154916</v>
+        <v>0.4473665877501287</v>
       </c>
       <c r="W237" t="n">
         <v>3.428571428571428</v>
@@ -21273,10 +21273,10 @@
         </is>
       </c>
       <c r="Y237" t="n">
-        <v>7.934782581654095</v>
+        <v>7.914315321448481</v>
       </c>
       <c r="Z237" t="n">
-        <v>7.934782581654095</v>
+        <v>7.914315321448481</v>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
@@ -21316,25 +21316,25 @@
         <v>551</v>
       </c>
       <c r="G238" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="H238" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I238" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="J238" t="n">
-        <v>0.4082137555665512</v>
+        <v>0.3960827848703513</v>
       </c>
       <c r="K238" t="n">
-        <v>0.2503711034141514</v>
+        <v>0.2547775751328205</v>
       </c>
       <c r="L238" t="n">
-        <v>0.3414151410192973</v>
+        <v>0.3491396399968281</v>
       </c>
       <c r="M238" t="n">
-        <v>0.06508563899868269</v>
+        <v>0.06080870786753145</v>
       </c>
       <c r="N238" t="n">
         <v>1</v>
@@ -21352,19 +21352,19 @@
         <v>1</v>
       </c>
       <c r="S238" t="n">
-        <v>0.00414122817973861</v>
+        <v>0.0162721988759385</v>
       </c>
       <c r="T238" t="n">
         <v>1</v>
       </c>
       <c r="U238" t="n">
-        <v>0.00414122817973861</v>
+        <v>0.0162721988759385</v>
       </c>
       <c r="V238" t="n">
         <v>0.4123549837462898</v>
       </c>
       <c r="W238" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="X238" t="inlineStr">
         <is>
@@ -21372,10 +21372,10 @@
         </is>
       </c>
       <c r="Y238" t="n">
-        <v>7.305914891960329</v>
+        <v>7.294928711935219</v>
       </c>
       <c r="Z238" t="n">
-        <v>7.305914891960329</v>
+        <v>7.294928711935219</v>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
@@ -21471,10 +21471,10 @@
         </is>
       </c>
       <c r="Y239" t="n">
-        <v>10.35701730933272</v>
+        <v>10.34144307142191</v>
       </c>
       <c r="Z239" t="n">
-        <v>10.35701730933272</v>
+        <v>10.34144307142191</v>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
@@ -21514,25 +21514,25 @@
         <v>551</v>
       </c>
       <c r="G240" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="H240" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I240" t="n">
         <v>3.5</v>
       </c>
-      <c r="I240" t="n">
-        <v>3.7</v>
-      </c>
       <c r="J240" t="n">
-        <v>0.473491773308958</v>
+        <v>0.4569015166058744</v>
       </c>
       <c r="K240" t="n">
-        <v>0.2705667276051188</v>
+        <v>0.2754847379535419</v>
       </c>
       <c r="L240" t="n">
-        <v>0.2559414990859232</v>
+        <v>0.2676137454405835</v>
       </c>
       <c r="M240" t="n">
-        <v>0.05598455598455598</v>
+        <v>0.06763681082188988</v>
       </c>
       <c r="N240" t="n">
         <v>1</v>
@@ -21550,19 +21550,19 @@
         <v>1</v>
       </c>
       <c r="S240" t="n">
-        <v>-0.09165869504575447</v>
+        <v>-0.07506843834267091</v>
       </c>
       <c r="T240" t="n">
         <v>1</v>
       </c>
       <c r="U240" t="n">
-        <v>-0.09165869504575447</v>
+        <v>-0.07506843834267091</v>
       </c>
       <c r="V240" t="n">
         <v>0.3818330782632035</v>
       </c>
       <c r="W240" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="X240" t="inlineStr">
         <is>
@@ -21570,10 +21570,10 @@
         </is>
       </c>
       <c r="Y240" t="n">
-        <v>6.765141886687074</v>
+        <v>6.754968887444454</v>
       </c>
       <c r="Z240" t="n">
-        <v>6.765141886687074</v>
+        <v>6.754968887444454</v>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
@@ -21613,25 +21613,25 @@
         <v>551</v>
       </c>
       <c r="G241" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="H241" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I241" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J241" t="n">
-        <v>0.5122702571735143</v>
+        <v>0.5309734513274337</v>
       </c>
       <c r="K241" t="n">
-        <v>0.253366100169603</v>
+        <v>0.247787610619469</v>
       </c>
       <c r="L241" t="n">
-        <v>0.2343636426568828</v>
+        <v>0.2212389380530974</v>
       </c>
       <c r="M241" t="n">
-        <v>0.0667183577019641</v>
+        <v>0.07619047619047614</v>
       </c>
       <c r="N241" t="n">
         <v>1</v>
@@ -21649,19 +21649,19 @@
         <v>1</v>
       </c>
       <c r="S241" t="n">
-        <v>-0.03190423197629155</v>
+        <v>-0.05060742613021096</v>
       </c>
       <c r="T241" t="n">
         <v>1</v>
       </c>
       <c r="U241" t="n">
-        <v>-0.03190423197629155</v>
+        <v>-0.05060742613021096</v>
       </c>
       <c r="V241" t="n">
         <v>0.4803660251972227</v>
       </c>
       <c r="W241" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="X241" t="inlineStr">
         <is>
@@ -21669,10 +21669,10 @@
         </is>
       </c>
       <c r="Y241" t="n">
-        <v>8.510903069961399</v>
+        <v>8.498104903724101</v>
       </c>
       <c r="Z241" t="n">
-        <v>8.510903069961399</v>
+        <v>8.498104903724101</v>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
@@ -21718,19 +21718,19 @@
         <v>3.4</v>
       </c>
       <c r="I242" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J242" t="n">
-        <v>0.418835684482416</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="K242" t="n">
-        <v>0.2771706735545401</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="L242" t="n">
-        <v>0.3039936419630439</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="M242" t="n">
-        <v>0.06114273666455827</v>
+        <v>0.05106209150326801</v>
       </c>
       <c r="N242" t="n">
         <v>1</v>
@@ -21748,13 +21748,13 @@
         <v>1</v>
       </c>
       <c r="S242" t="n">
-        <v>0.09174110114784206</v>
+        <v>0.08772408450316915</v>
       </c>
       <c r="T242" t="n">
         <v>1</v>
       </c>
       <c r="U242" t="n">
-        <v>0.09174110114784206</v>
+        <v>0.08772408450316915</v>
       </c>
       <c r="V242" t="n">
         <v>0.5105767856302581</v>
@@ -21768,10 +21768,10 @@
         </is>
       </c>
       <c r="Y242" t="n">
-        <v>9.046163351139327</v>
+        <v>9.032560293810869</v>
       </c>
       <c r="Z242" t="n">
-        <v>9.046163351139327</v>
+        <v>9.032560293810869</v>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
@@ -21811,25 +21811,25 @@
         <v>551</v>
       </c>
       <c r="G243" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="H243" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I243" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="J243" t="n">
-        <v>0.5392195506503745</v>
+        <v>0.5223880597014926</v>
       </c>
       <c r="K243" t="n">
-        <v>0.2621206148994876</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="L243" t="n">
-        <v>0.198659834450138</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="M243" t="n">
-        <v>0.05973266499582275</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="N243" t="n">
         <v>1</v>
@@ -21847,19 +21847,19 @@
         <v>1</v>
       </c>
       <c r="S243" t="n">
-        <v>-0.05361800765758895</v>
+        <v>-0.03678651670870703</v>
       </c>
       <c r="T243" t="n">
         <v>1</v>
       </c>
       <c r="U243" t="n">
-        <v>-0.05361800765758895</v>
+        <v>-0.03678651670870703</v>
       </c>
       <c r="V243" t="n">
         <v>0.4856015429927856</v>
       </c>
       <c r="W243" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="X243" t="inlineStr">
         <is>
@@ -21867,10 +21867,10 @@
         </is>
       </c>
       <c r="Y243" t="n">
-        <v>8.603663552888555</v>
+        <v>8.590725899211325</v>
       </c>
       <c r="Z243" t="n">
-        <v>8.603663552888555</v>
+        <v>8.590725899211325</v>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
@@ -21966,10 +21966,10 @@
         </is>
       </c>
       <c r="Y244" t="n">
-        <v>8.767617272192677</v>
+        <v>8.754433075118389</v>
       </c>
       <c r="Z244" t="n">
-        <v>8.767617272192677</v>
+        <v>8.754433075118389</v>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
@@ -22009,25 +22009,25 @@
         <v>551</v>
       </c>
       <c r="G245" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="H245" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="I245" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="J245" t="n">
-        <v>0.5977796754910334</v>
+        <v>0.6129214075959531</v>
       </c>
       <c r="K245" t="n">
-        <v>0.2234557358383149</v>
+        <v>0.2165750008364453</v>
       </c>
       <c r="L245" t="n">
-        <v>0.1787645886706519</v>
+        <v>0.1705035915676015</v>
       </c>
       <c r="M245" t="n">
-        <v>0.06551410373066413</v>
+        <v>0.06635983527710199</v>
       </c>
       <c r="N245" t="n">
         <v>1</v>
@@ -22045,19 +22045,19 @@
         <v>1</v>
       </c>
       <c r="S245" t="n">
-        <v>-0.06391363778681569</v>
+        <v>-0.07905536989173545</v>
       </c>
       <c r="T245" t="n">
         <v>1</v>
       </c>
       <c r="U245" t="n">
-        <v>-0.06391363778681569</v>
+        <v>-0.07905536989173545</v>
       </c>
       <c r="V245" t="n">
         <v>0.5338660377042177</v>
       </c>
       <c r="W245" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="X245" t="inlineStr">
         <is>
@@ -22065,10 +22065,10 @@
         </is>
       </c>
       <c r="Y245" t="n">
-        <v>9.458791548339551</v>
+        <v>9.444568006414036</v>
       </c>
       <c r="Z245" t="n">
-        <v>9.458791548339551</v>
+        <v>9.444568006414036</v>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
@@ -22164,10 +22164,10 @@
         </is>
       </c>
       <c r="Y246" t="n">
-        <v>9.864358862042311</v>
+        <v>9.849525453236804</v>
       </c>
       <c r="Z246" t="n">
-        <v>9.864358862042311</v>
+        <v>9.849525453236804</v>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
@@ -22263,10 +22263,10 @@
         </is>
       </c>
       <c r="Y247" t="n">
-        <v>8.361447054156484</v>
+        <v>8.348873630572195</v>
       </c>
       <c r="Z247" t="n">
-        <v>8.361447054156484</v>
+        <v>8.348873630572195</v>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
@@ -22306,25 +22306,25 @@
         <v>551</v>
       </c>
       <c r="G248" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H248" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="I248" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="J248" t="n">
-        <v>0.4734159392673772</v>
+        <v>0.4668310213125349</v>
       </c>
       <c r="K248" t="n">
-        <v>0.2625880409803052</v>
+        <v>0.2655022789675063</v>
       </c>
       <c r="L248" t="n">
-        <v>0.2639960197523176</v>
+        <v>0.2676666997199588</v>
       </c>
       <c r="M248" t="n">
-        <v>0.01553241218120571</v>
+        <v>0.01521455869962329</v>
       </c>
       <c r="N248" t="n">
         <v>1</v>
@@ -22342,19 +22342,19 @@
         <v>1</v>
       </c>
       <c r="S248" t="n">
-        <v>-0.04349322649419723</v>
+        <v>-0.03690830853935495</v>
       </c>
       <c r="T248" t="n">
         <v>1</v>
       </c>
       <c r="U248" t="n">
-        <v>-0.04349322649419723</v>
+        <v>-0.03690830853935495</v>
       </c>
       <c r="V248" t="n">
         <v>0.4299227127731799</v>
       </c>
       <c r="W248" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="X248" t="inlineStr">
         <is>
@@ -22362,10 +22362,10 @@
         </is>
       </c>
       <c r="Y248" t="n">
-        <v>7.617171789959771</v>
+        <v>7.60571756118703</v>
       </c>
       <c r="Z248" t="n">
-        <v>7.617171789959771</v>
+        <v>7.60571756118703</v>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
@@ -22461,10 +22461,10 @@
         </is>
       </c>
       <c r="Y249" t="n">
-        <v>8.8590376928958</v>
+        <v>8.845716023483734</v>
       </c>
       <c r="Z249" t="n">
-        <v>8.8590376928958</v>
+        <v>8.845716023483734</v>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
@@ -22560,10 +22560,10 @@
         </is>
       </c>
       <c r="Y250" t="n">
-        <v>7.995990973675763</v>
+        <v>7.983967100195848</v>
       </c>
       <c r="Z250" t="n">
-        <v>7.995990973675763</v>
+        <v>7.983967100195848</v>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
@@ -22639,10 +22639,10 @@
         </is>
       </c>
       <c r="Y251" t="n">
-        <v>6.445046423032351</v>
+        <v>6.435354763422199</v>
       </c>
       <c r="Z251" t="n">
-        <v>6.445046423032351</v>
+        <v>6.435354763422199</v>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
@@ -22718,10 +22718,10 @@
         </is>
       </c>
       <c r="Y252" t="n">
-        <v>9.816898702769446</v>
+        <v>9.802136661597084</v>
       </c>
       <c r="Z252" t="n">
-        <v>9.816898702769446</v>
+        <v>9.802136661597084</v>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
@@ -22817,10 +22817,10 @@
         </is>
       </c>
       <c r="Y253" t="n">
-        <v>8.174791505464517</v>
+        <v>8.16249876287514</v>
       </c>
       <c r="Z253" t="n">
-        <v>8.174791505464517</v>
+        <v>8.16249876287514</v>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
@@ -22916,10 +22916,10 @@
         </is>
       </c>
       <c r="Y254" t="n">
-        <v>11.02803233518291</v>
+        <v>11.01144906664656</v>
       </c>
       <c r="Z254" t="n">
-        <v>11.02803233518291</v>
+        <v>11.01144906664656</v>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
@@ -22965,60 +22965,60 @@
         <v>4.33</v>
       </c>
       <c r="I255" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="J255" t="n">
-        <v>0.1894034665646017</v>
+        <v>0.1872852849047196</v>
       </c>
       <c r="K255" t="n">
-        <v>0.2187107004210181</v>
+        <v>0.2162647631694221</v>
       </c>
       <c r="L255" t="n">
-        <v>0.5918858330143802</v>
+        <v>0.5964499519258584</v>
       </c>
       <c r="M255" t="n">
-        <v>0.0559468822170901</v>
+        <v>0.06788955737632563</v>
       </c>
       <c r="N255" t="n">
         <v>2</v>
       </c>
       <c r="O255" t="n">
-        <v>0.06838888361318179</v>
+        <v>0.0332989612630136</v>
       </c>
       <c r="P255" t="n">
-        <v>0.3865482299682644</v>
+        <v>0.2862225669792112</v>
       </c>
       <c r="Q255" t="n">
-        <v>0.5450628864185538</v>
+        <v>0.6804784717577752</v>
       </c>
       <c r="R255" t="n">
         <v>1</v>
       </c>
       <c r="S255" t="n">
-        <v>-0.04682294659582642</v>
+        <v>0.08402851983191684</v>
       </c>
       <c r="T255" t="n">
         <v>2</v>
       </c>
       <c r="U255" t="n">
-        <v>-0.04682294659582642</v>
+        <v>0.08402851983191684</v>
       </c>
       <c r="V255" t="n">
-        <v>0.5450628864185538</v>
+        <v>0.6804784717577752</v>
       </c>
       <c r="W255" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X255" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y255" t="n">
-        <v>3.650201274787571</v>
+        <v>2.939469859977928</v>
       </c>
       <c r="Z255" t="n">
-        <v>3.650201274787571</v>
+        <v>2.939469859977928</v>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
@@ -23082,42 +23082,42 @@
         <v>0</v>
       </c>
       <c r="O256" t="n">
-        <v>0.2794162171712321</v>
+        <v>0.2346636067687149</v>
       </c>
       <c r="P256" t="n">
-        <v>0.387798783406023</v>
+        <v>0.3836683950726748</v>
       </c>
       <c r="Q256" t="n">
-        <v>0.332784999422745</v>
+        <v>0.3816679981586102</v>
       </c>
       <c r="R256" t="n">
         <v>1</v>
       </c>
       <c r="S256" t="n">
-        <v>0.1244783200855596</v>
+        <v>0.1203479317522114</v>
       </c>
       <c r="T256" t="n">
         <v>0</v>
       </c>
       <c r="U256" t="n">
-        <v>0.1244783200855596</v>
+        <v>0.1203479317522114</v>
       </c>
       <c r="V256" t="n">
-        <v>0.387798783406023</v>
+        <v>0.3836683950726748</v>
       </c>
       <c r="W256" t="n">
         <v>3.6</v>
       </c>
       <c r="X256" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y256" t="n">
-        <v>2.59702806560698</v>
+        <v>1.657336316061561</v>
       </c>
       <c r="Z256" t="n">
-        <v>2.59702806560698</v>
+        <v>1.657336316061561</v>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
@@ -23157,66 +23157,66 @@
         <v>591</v>
       </c>
       <c r="G257" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H257" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I257" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="J257" t="n">
-        <v>0.2875429881543752</v>
+        <v>0.2806236080178174</v>
       </c>
       <c r="K257" t="n">
-        <v>0.2711119602598395</v>
+        <v>0.2650334075723831</v>
       </c>
       <c r="L257" t="n">
-        <v>0.4413450515857852</v>
+        <v>0.4543429844097996</v>
       </c>
       <c r="M257" t="n">
-        <v>0.05386086781435617</v>
+        <v>0.04808590102707733</v>
       </c>
       <c r="N257" t="n">
         <v>0</v>
       </c>
       <c r="O257" t="n">
-        <v>0.2662159723409032</v>
+        <v>0.2548200576322532</v>
       </c>
       <c r="P257" t="n">
-        <v>0.4201214634845208</v>
+        <v>0.4056882288870197</v>
       </c>
       <c r="Q257" t="n">
-        <v>0.313662564174576</v>
+        <v>0.3394917134807272</v>
       </c>
       <c r="R257" t="n">
         <v>1</v>
       </c>
       <c r="S257" t="n">
-        <v>0.1490095032246813</v>
+        <v>0.1406548213146366</v>
       </c>
       <c r="T257" t="n">
         <v>0</v>
       </c>
       <c r="U257" t="n">
-        <v>0.1490095032246813</v>
+        <v>0.1406548213146366</v>
       </c>
       <c r="V257" t="n">
-        <v>0.4201214634845208</v>
+        <v>0.4056882288870197</v>
       </c>
       <c r="W257" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y257" t="n">
-        <v>2.813488020901906</v>
+        <v>1.752455618883576</v>
       </c>
       <c r="Z257" t="n">
-        <v>2.813488020901906</v>
+        <v>1.752455618883576</v>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
@@ -23256,66 +23256,66 @@
         <v>591</v>
       </c>
       <c r="G258" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="H258" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="I258" t="n">
         <v>4.75</v>
       </c>
       <c r="J258" t="n">
-        <v>0.5746381507885073</v>
+        <v>0.5830269494941478</v>
       </c>
       <c r="K258" t="n">
-        <v>0.225750702095485</v>
+        <v>0.2181301750994271</v>
       </c>
       <c r="L258" t="n">
-        <v>0.1996111471160078</v>
+        <v>0.1988428754064251</v>
       </c>
       <c r="M258" t="n">
-        <v>0.05468215994531778</v>
+        <v>0.05875714862384762</v>
       </c>
       <c r="N258" t="n">
         <v>1</v>
       </c>
       <c r="O258" t="n">
-        <v>0.5461627831902344</v>
+        <v>0.5796457246495701</v>
       </c>
       <c r="P258" t="n">
-        <v>0.3065763329090344</v>
+        <v>0.2700014328808418</v>
       </c>
       <c r="Q258" t="n">
-        <v>0.1472608839007312</v>
+        <v>0.1503528424695882</v>
       </c>
       <c r="R258" t="n">
         <v>1</v>
       </c>
       <c r="S258" t="n">
-        <v>-0.02847536759827296</v>
+        <v>-0.003381224844577702</v>
       </c>
       <c r="T258" t="n">
         <v>1</v>
       </c>
       <c r="U258" t="n">
-        <v>-0.02847536759827296</v>
+        <v>-0.003381224844577702</v>
       </c>
       <c r="V258" t="n">
-        <v>0.5461627831902344</v>
+        <v>0.5796457246495701</v>
       </c>
       <c r="W258" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="X258" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y258" t="n">
-        <v>3.65756711219489</v>
+        <v>2.503901604221483</v>
       </c>
       <c r="Z258" t="n">
-        <v>3.65756711219489</v>
+        <v>2.503901604221483</v>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
@@ -23379,42 +23379,42 @@
         <v>0</v>
       </c>
       <c r="O259" t="n">
-        <v>0.2077322430245421</v>
+        <v>0.2777075384682832</v>
       </c>
       <c r="P259" t="n">
-        <v>0.4233594316670704</v>
+        <v>0.3702299299283254</v>
       </c>
       <c r="Q259" t="n">
-        <v>0.3689083253083874</v>
+        <v>0.3520625316033914</v>
       </c>
       <c r="R259" t="n">
         <v>1</v>
       </c>
       <c r="S259" t="n">
-        <v>0.1433881466706598</v>
+        <v>0.09025864493191477</v>
       </c>
       <c r="T259" t="n">
         <v>0</v>
       </c>
       <c r="U259" t="n">
-        <v>0.1433881466706598</v>
+        <v>0.09025864493191477</v>
       </c>
       <c r="V259" t="n">
-        <v>0.4233594316670704</v>
+        <v>0.3702299299283254</v>
       </c>
       <c r="W259" t="n">
         <v>3.4</v>
       </c>
       <c r="X259" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y259" t="n">
-        <v>2.83517218961375</v>
+        <v>1.599286039828516</v>
       </c>
       <c r="Z259" t="n">
-        <v>2.83517218961375</v>
+        <v>1.599286039828516</v>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
@@ -23454,66 +23454,66 @@
         <v>591</v>
       </c>
       <c r="G260" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="H260" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I260" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J260" t="n">
-        <v>0.7194244604316546</v>
+        <v>0.7466216216216217</v>
       </c>
       <c r="K260" t="n">
-        <v>0.1558752997601918</v>
+        <v>0.1435810810810811</v>
       </c>
       <c r="L260" t="n">
-        <v>0.1247002398081535</v>
+        <v>0.1097972972972973</v>
       </c>
       <c r="M260" t="n">
-        <v>0.06923076923076921</v>
+        <v>0.07149321266968323</v>
       </c>
       <c r="N260" t="n">
         <v>1</v>
       </c>
       <c r="O260" t="n">
-        <v>0.6341428517788732</v>
+        <v>0.5590050247947679</v>
       </c>
       <c r="P260" t="n">
-        <v>0.2590412097024586</v>
+        <v>0.3594827256395218</v>
       </c>
       <c r="Q260" t="n">
-        <v>0.1068159385186683</v>
+        <v>0.08151224956571015</v>
       </c>
       <c r="R260" t="n">
         <v>1</v>
       </c>
       <c r="S260" t="n">
-        <v>-0.08528160865278145</v>
+        <v>-0.1876165968268538</v>
       </c>
       <c r="T260" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U260" t="n">
-        <v>-0.08528160865278145</v>
+        <v>0.1876165968268538</v>
       </c>
       <c r="V260" t="n">
-        <v>0.6341428517788732</v>
+        <v>0.4409949752052321</v>
       </c>
       <c r="W260" t="n">
-        <v>1.3</v>
+        <v>3.683333333333334</v>
       </c>
       <c r="X260" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="Y260" t="n">
-        <v>4.246755931540664</v>
+        <v>1.904970534437311</v>
       </c>
       <c r="Z260" t="n">
-        <v>4.246755931540664</v>
+        <v>1.904970534437311</v>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
@@ -23577,42 +23577,42 @@
         <v>1</v>
       </c>
       <c r="O261" t="n">
-        <v>0.3799273330325321</v>
+        <v>0.6032287233137945</v>
       </c>
       <c r="P261" t="n">
-        <v>0.3485985228476672</v>
+        <v>0.2640580705349358</v>
       </c>
       <c r="Q261" t="n">
-        <v>0.2714741441198005</v>
+        <v>0.1327132061512696</v>
       </c>
       <c r="R261" t="n">
         <v>1</v>
       </c>
       <c r="S261" t="n">
-        <v>-0.1779801359726086</v>
+        <v>0.04532125430865386</v>
       </c>
       <c r="T261" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U261" t="n">
-        <v>0.1779801359726086</v>
+        <v>0.04532125430865386</v>
       </c>
       <c r="V261" t="n">
-        <v>0.6200726669674679</v>
+        <v>0.6032287233137945</v>
       </c>
       <c r="W261" t="n">
-        <v>2.145348837209302</v>
+        <v>1.7</v>
       </c>
       <c r="X261" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y261" t="n">
-        <v>4.15253009482565</v>
+        <v>2.605773326338305</v>
       </c>
       <c r="Z261" t="n">
-        <v>4.15253009482565</v>
+        <v>2.605773326338305</v>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
@@ -23676,42 +23676,42 @@
         <v>2</v>
       </c>
       <c r="O262" t="n">
-        <v>0.115526486868512</v>
+        <v>0.1371082897684723</v>
       </c>
       <c r="P262" t="n">
-        <v>0.4359838600267355</v>
+        <v>0.3863967918267899</v>
       </c>
       <c r="Q262" t="n">
-        <v>0.4484896531047526</v>
+        <v>0.4764949184047379</v>
       </c>
       <c r="R262" t="n">
         <v>1</v>
       </c>
       <c r="S262" t="n">
-        <v>-0.2011684215927751</v>
+        <v>-0.1731631562927898</v>
       </c>
       <c r="T262" t="n">
         <v>-2</v>
       </c>
       <c r="U262" t="n">
-        <v>0.2011684215927751</v>
+        <v>0.1731631562927898</v>
       </c>
       <c r="V262" t="n">
-        <v>0.5515103468952474</v>
+        <v>0.5235050815952621</v>
       </c>
       <c r="W262" t="n">
         <v>2.744444444444444</v>
       </c>
       <c r="X262" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="Y262" t="n">
-        <v>3.693378913620784</v>
+        <v>2.261390290451869</v>
       </c>
       <c r="Z262" t="n">
-        <v>3.693378913620784</v>
+        <v>2.261390290451869</v>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
@@ -23757,60 +23757,60 @@
         <v>3.5</v>
       </c>
       <c r="I263" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J263" t="n">
-        <v>0.4452054794520548</v>
+        <v>0.4471544715447154</v>
       </c>
       <c r="K263" t="n">
-        <v>0.2671232876712329</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="L263" t="n">
-        <v>0.2876712328767124</v>
+        <v>0.2845528455284553</v>
       </c>
       <c r="M263" t="n">
-        <v>0.06959706959706957</v>
+        <v>0.06493506493506485</v>
       </c>
       <c r="N263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
-        <v>0.1474195239146204</v>
+        <v>0.2310214101079057</v>
       </c>
       <c r="P263" t="n">
-        <v>0.3949478120626924</v>
+        <v>0.4757411918709668</v>
       </c>
       <c r="Q263" t="n">
-        <v>0.4576326640226871</v>
+        <v>0.2932373980211276</v>
       </c>
       <c r="R263" t="n">
         <v>1</v>
       </c>
       <c r="S263" t="n">
-        <v>0.1699614311459747</v>
+        <v>0.2074485089441375</v>
       </c>
       <c r="T263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U263" t="n">
-        <v>0.1699614311459747</v>
+        <v>0.2074485089441375</v>
       </c>
       <c r="V263" t="n">
-        <v>0.4576326640226871</v>
+        <v>0.4757411918709668</v>
       </c>
       <c r="W263" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="X263" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y263" t="n">
-        <v>3.064694689774392</v>
+        <v>2.055064124280586</v>
       </c>
       <c r="Z263" t="n">
-        <v>3.064694689774392</v>
+        <v>2.055064124280586</v>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
@@ -23856,60 +23856,60 @@
         <v>3.5</v>
       </c>
       <c r="I264" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J264" t="n">
-        <v>0.4640029460504511</v>
+        <v>0.4673403103572718</v>
       </c>
       <c r="K264" t="n">
-        <v>0.2717731541152641</v>
+        <v>0.273727896066402</v>
       </c>
       <c r="L264" t="n">
-        <v>0.2642238998342846</v>
+        <v>0.2589317935763262</v>
       </c>
       <c r="M264" t="n">
-        <v>0.05129694154084419</v>
+        <v>0.04378943403333646</v>
       </c>
       <c r="N264" t="n">
         <v>1</v>
       </c>
       <c r="O264" t="n">
-        <v>0.5503165860218741</v>
+        <v>0.5864101075026901</v>
       </c>
       <c r="P264" t="n">
-        <v>0.2961322443467427</v>
+        <v>0.2863208677608263</v>
       </c>
       <c r="Q264" t="n">
-        <v>0.153551169631383</v>
+        <v>0.1272690247364837</v>
       </c>
       <c r="R264" t="n">
         <v>1</v>
       </c>
       <c r="S264" t="n">
-        <v>0.086313639971423</v>
+        <v>0.1190697971454183</v>
       </c>
       <c r="T264" t="n">
         <v>1</v>
       </c>
       <c r="U264" t="n">
-        <v>0.086313639971423</v>
+        <v>0.1190697971454183</v>
       </c>
       <c r="V264" t="n">
-        <v>0.5503165860218741</v>
+        <v>0.5864101075026901</v>
       </c>
       <c r="W264" t="n">
         <v>2.05</v>
       </c>
       <c r="X264" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y264" t="n">
-        <v>3.685384482940665</v>
+        <v>2.533121778471427</v>
       </c>
       <c r="Z264" t="n">
-        <v>3.685384482940665</v>
+        <v>2.533121778471427</v>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
@@ -23973,42 +23973,42 @@
         <v>2</v>
       </c>
       <c r="O265" t="n">
-        <v>0.1768455743783334</v>
+        <v>0.190129093525317</v>
       </c>
       <c r="P265" t="n">
-        <v>0.3971475057747061</v>
+        <v>0.322978033860898</v>
       </c>
       <c r="Q265" t="n">
-        <v>0.4260069198469605</v>
+        <v>0.4868928726137849</v>
       </c>
       <c r="R265" t="n">
         <v>1</v>
       </c>
       <c r="S265" t="n">
-        <v>0.1073002223873762</v>
+        <v>0.1681861751542006</v>
       </c>
       <c r="T265" t="n">
         <v>2</v>
       </c>
       <c r="U265" t="n">
-        <v>0.1073002223873762</v>
+        <v>0.1681861751542006</v>
       </c>
       <c r="V265" t="n">
-        <v>0.4260069198469605</v>
+        <v>0.4868928726137849</v>
       </c>
       <c r="W265" t="n">
         <v>3</v>
       </c>
       <c r="X265" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y265" t="n">
-        <v>2.852902005695556</v>
+        <v>2.10323615439189</v>
       </c>
       <c r="Z265" t="n">
-        <v>2.852902005695556</v>
+        <v>2.10323615439189</v>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
@@ -24048,66 +24048,66 @@
         <v>591</v>
       </c>
       <c r="G266" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H266" t="n">
         <v>3.8</v>
       </c>
       <c r="I266" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J266" t="n">
-        <v>0.5093833780160858</v>
+        <v>0.5167364016736402</v>
       </c>
       <c r="K266" t="n">
-        <v>0.2453083109919571</v>
+        <v>0.2447698744769874</v>
       </c>
       <c r="L266" t="n">
-        <v>0.2453083109919571</v>
+        <v>0.2384937238493724</v>
       </c>
       <c r="M266" t="n">
-        <v>0.072763876905378</v>
+        <v>0.075123706702654</v>
       </c>
       <c r="N266" t="n">
         <v>1</v>
       </c>
       <c r="O266" t="n">
-        <v>0.4456707385012158</v>
+        <v>0.3834996490478769</v>
       </c>
       <c r="P266" t="n">
-        <v>0.3497857186364307</v>
+        <v>0.3345946163079804</v>
       </c>
       <c r="Q266" t="n">
-        <v>0.2045435428623534</v>
+        <v>0.2819057346441427</v>
       </c>
       <c r="R266" t="n">
         <v>1</v>
       </c>
       <c r="S266" t="n">
-        <v>-0.06371263951487</v>
+        <v>-0.1332367526257633</v>
       </c>
       <c r="T266" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U266" t="n">
-        <v>-0.06371263951487</v>
+        <v>0.1332367526257633</v>
       </c>
       <c r="V266" t="n">
-        <v>0.4456707385012158</v>
+        <v>0.6165003509521231</v>
       </c>
       <c r="W266" t="n">
-        <v>1.83</v>
+        <v>1.924675324675325</v>
       </c>
       <c r="X266" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="Y266" t="n">
-        <v>2.984587537232255</v>
+        <v>2.663102912878999</v>
       </c>
       <c r="Z266" t="n">
-        <v>2.984587537232255</v>
+        <v>2.663102912878999</v>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
@@ -24147,66 +24147,66 @@
         <v>591</v>
       </c>
       <c r="G267" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H267" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I267" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J267" t="n">
-        <v>0.3163064833005893</v>
+        <v>0.3057915057915058</v>
       </c>
       <c r="K267" t="n">
-        <v>0.2711198428290766</v>
+        <v>0.2633204633204633</v>
       </c>
       <c r="L267" t="n">
-        <v>0.4125736738703339</v>
+        <v>0.4308880308880308</v>
       </c>
       <c r="M267" t="n">
-        <v>0.0538302277432714</v>
+        <v>0.05490387748452275</v>
       </c>
       <c r="N267" t="n">
         <v>2</v>
       </c>
       <c r="O267" t="n">
-        <v>0.06742366949341573</v>
+        <v>0.06949278788174991</v>
       </c>
       <c r="P267" t="n">
-        <v>0.3980165281892039</v>
+        <v>0.3801217379633041</v>
       </c>
       <c r="Q267" t="n">
-        <v>0.5345598023173804</v>
+        <v>0.5503854741549461</v>
       </c>
       <c r="R267" t="n">
         <v>1</v>
       </c>
       <c r="S267" t="n">
-        <v>0.1219861284470465</v>
+        <v>0.1194974432669152</v>
       </c>
       <c r="T267" t="n">
         <v>2</v>
       </c>
       <c r="U267" t="n">
-        <v>0.1219861284470465</v>
+        <v>0.1194974432669152</v>
       </c>
       <c r="V267" t="n">
-        <v>0.5345598023173804</v>
+        <v>0.5503854741549461</v>
       </c>
       <c r="W267" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="X267" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y267" t="n">
-        <v>3.579863756070759</v>
+        <v>2.377505798925577</v>
       </c>
       <c r="Z267" t="n">
-        <v>3.579863756070759</v>
+        <v>2.377505798925577</v>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
@@ -24246,66 +24246,66 @@
         <v>591</v>
       </c>
       <c r="G268" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H268" t="n">
         <v>4.33</v>
       </c>
       <c r="I268" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="J268" t="n">
-        <v>0.6174990513369328</v>
+        <v>0.6098357297414951</v>
       </c>
       <c r="K268" t="n">
-        <v>0.2181925054377615</v>
+        <v>0.2183014736949925</v>
       </c>
       <c r="L268" t="n">
-        <v>0.1643084432253056</v>
+        <v>0.1718627965635123</v>
       </c>
       <c r="M268" t="n">
-        <v>0.05845469693718108</v>
+        <v>0.05792635435785254</v>
       </c>
       <c r="N268" t="n">
         <v>1</v>
       </c>
       <c r="O268" t="n">
-        <v>0.4150557608433468</v>
+        <v>0.4959298926532823</v>
       </c>
       <c r="P268" t="n">
-        <v>0.3583941456475557</v>
+        <v>0.3042471008390001</v>
       </c>
       <c r="Q268" t="n">
-        <v>0.2265500935090975</v>
+        <v>0.1998230065077176</v>
       </c>
       <c r="R268" t="n">
         <v>1</v>
       </c>
       <c r="S268" t="n">
-        <v>-0.202443290493586</v>
+        <v>-0.1139058370882128</v>
       </c>
       <c r="T268" t="n">
         <v>-1</v>
       </c>
       <c r="U268" t="n">
-        <v>0.202443290493586</v>
+        <v>0.1139058370882128</v>
       </c>
       <c r="V268" t="n">
-        <v>0.5849442391566532</v>
+        <v>0.5040701073467178</v>
       </c>
       <c r="W268" t="n">
-        <v>2.46999007936508</v>
+        <v>2.422685656154629</v>
       </c>
       <c r="X268" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="Y268" t="n">
-        <v>3.917280483870017</v>
+        <v>2.177436832107372</v>
       </c>
       <c r="Z268" t="n">
-        <v>3.917280483870017</v>
+        <v>2.177436832107372</v>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
@@ -24369,42 +24369,42 @@
         <v>2</v>
       </c>
       <c r="O269" t="n">
-        <v>0.08325612829513089</v>
+        <v>0.1086962288444902</v>
       </c>
       <c r="P269" t="n">
-        <v>0.4147978300959643</v>
+        <v>0.3402277316203847</v>
       </c>
       <c r="Q269" t="n">
-        <v>0.5019460416089049</v>
+        <v>0.5510760395351252</v>
       </c>
       <c r="R269" t="n">
         <v>1</v>
       </c>
       <c r="S269" t="n">
-        <v>0.0219460416089049</v>
+        <v>0.0710760395351252</v>
       </c>
       <c r="T269" t="n">
         <v>2</v>
       </c>
       <c r="U269" t="n">
-        <v>0.0219460416089049</v>
+        <v>0.0710760395351252</v>
       </c>
       <c r="V269" t="n">
-        <v>0.5019460416089049</v>
+        <v>0.5510760395351252</v>
       </c>
       <c r="W269" t="n">
         <v>1.95</v>
       </c>
       <c r="X269" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y269" t="n">
-        <v>3.361454479123075</v>
+        <v>2.380488841307707</v>
       </c>
       <c r="Z269" t="n">
-        <v>3.361454479123075</v>
+        <v>2.380488841307707</v>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
@@ -24465,45 +24465,45 @@
         <v>0.0592686002522067</v>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O270" t="n">
-        <v>0.2944486686154041</v>
+        <v>0.3986165358049383</v>
       </c>
       <c r="P270" t="n">
-        <v>0.4309788634890854</v>
+        <v>0.3950083384352972</v>
       </c>
       <c r="Q270" t="n">
-        <v>0.2745724678955104</v>
+        <v>0.2063751257597645</v>
       </c>
       <c r="R270" t="n">
         <v>1</v>
       </c>
       <c r="S270" t="n">
-        <v>0.1889153714255933</v>
+        <v>-0.1172564800680775</v>
       </c>
       <c r="T270" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U270" t="n">
-        <v>0.1889153714255933</v>
+        <v>0.1172564800680775</v>
       </c>
       <c r="V270" t="n">
-        <v>0.4309788634890854</v>
+        <v>0.6013834641950617</v>
       </c>
       <c r="W270" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="X270" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="Y270" t="n">
-        <v>2.886198338050719</v>
+        <v>2.597802341526172</v>
       </c>
       <c r="Z270" t="n">
-        <v>2.886198338050719</v>
+        <v>2.597802341526172</v>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
@@ -24564,45 +24564,45 @@
         <v>0.05273937532002049</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O271" t="n">
-        <v>0.2148120532559113</v>
+        <v>0.2124655061087739</v>
       </c>
       <c r="P271" t="n">
-        <v>0.4262078219006251</v>
+        <v>0.366165770768149</v>
       </c>
       <c r="Q271" t="n">
-        <v>0.3589801248434636</v>
+        <v>0.421368723123077</v>
       </c>
       <c r="R271" t="n">
         <v>1</v>
       </c>
       <c r="S271" t="n">
-        <v>0.1548070436905084</v>
+        <v>0.1149484896600421</v>
       </c>
       <c r="T271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U271" t="n">
-        <v>0.1548070436905084</v>
+        <v>0.1149484896600421</v>
       </c>
       <c r="V271" t="n">
-        <v>0.4262078219006251</v>
+        <v>0.421368723123077</v>
       </c>
       <c r="W271" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="X271" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="Y271" t="n">
-        <v>2.854247415465083</v>
+        <v>1.820190811265761</v>
       </c>
       <c r="Z271" t="n">
-        <v>2.854247415465083</v>
+        <v>1.820190811265761</v>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
@@ -24642,66 +24642,66 @@
         <v>591</v>
       </c>
       <c r="G272" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="H272" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="I272" t="n">
         <v>13</v>
       </c>
       <c r="J272" t="n">
-        <v>0.7803121248499399</v>
+        <v>0.771513353115727</v>
       </c>
       <c r="K272" t="n">
-        <v>0.1464585834333733</v>
+        <v>0.1543026706231454</v>
       </c>
       <c r="L272" t="n">
-        <v>0.07322929171668667</v>
+        <v>0.07418397626112759</v>
       </c>
       <c r="M272" t="n">
-        <v>0.05044136191677184</v>
+        <v>0.03692307692307706</v>
       </c>
       <c r="N272" t="n">
         <v>1</v>
       </c>
       <c r="O272" t="n">
-        <v>0.5568618094090434</v>
+        <v>0.614264058670636</v>
       </c>
       <c r="P272" t="n">
-        <v>0.2915849481069179</v>
+        <v>0.30388907837108</v>
       </c>
       <c r="Q272" t="n">
-        <v>0.1515532424840386</v>
+        <v>0.08184686295828413</v>
       </c>
       <c r="R272" t="n">
         <v>1</v>
       </c>
       <c r="S272" t="n">
-        <v>-0.2234503154408966</v>
+        <v>-0.1572492944450909</v>
       </c>
       <c r="T272" t="n">
         <v>-1</v>
       </c>
       <c r="U272" t="n">
-        <v>0.2234503154408966</v>
+        <v>0.1572492944450909</v>
       </c>
       <c r="V272" t="n">
-        <v>0.4431381905909566</v>
+        <v>0.385735941329364</v>
       </c>
       <c r="W272" t="n">
-        <v>4.333333333333333</v>
+        <v>4.220779220779221</v>
       </c>
       <c r="X272" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="Y272" t="n">
-        <v>2.967627458238012</v>
+        <v>1.666267516911969</v>
       </c>
       <c r="Z272" t="n">
-        <v>2.967627458238012</v>
+        <v>1.666267516911969</v>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
@@ -24744,63 +24744,63 @@
         <v>4.5</v>
       </c>
       <c r="H273" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I273" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="J273" t="n">
-        <v>0.2082831687936431</v>
+        <v>0.2069849407241269</v>
       </c>
       <c r="K273" t="n">
-        <v>0.2499398025523718</v>
+        <v>0.2451137455943608</v>
       </c>
       <c r="L273" t="n">
-        <v>0.5417770286539851</v>
+        <v>0.5479013136815124</v>
       </c>
       <c r="M273" t="n">
-        <v>0.06692357096981372</v>
+        <v>0.07361541107671132</v>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O273" t="n">
-        <v>0.227761609718552</v>
+        <v>0.1611302974373451</v>
       </c>
       <c r="P273" t="n">
-        <v>0.5077089800370994</v>
+        <v>0.3489183406711817</v>
       </c>
       <c r="Q273" t="n">
-        <v>0.2645294102443486</v>
+        <v>0.4899513618914735</v>
       </c>
       <c r="R273" t="n">
         <v>1</v>
       </c>
       <c r="S273" t="n">
-        <v>0.2577691774847276</v>
+        <v>-0.05794995179003892</v>
       </c>
       <c r="T273" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U273" t="n">
-        <v>0.2577691774847276</v>
+        <v>-0.05794995179003892</v>
       </c>
       <c r="V273" t="n">
-        <v>0.5077089800370994</v>
+        <v>0.4899513618914735</v>
       </c>
       <c r="W273" t="n">
-        <v>3.75</v>
+        <v>1.7</v>
       </c>
       <c r="X273" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y273" t="n">
-        <v>6.071232835041694</v>
+        <v>7.784599690070459</v>
       </c>
       <c r="Z273" t="n">
-        <v>6.071232835041694</v>
+        <v>7.784599690070459</v>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
@@ -24840,66 +24840,66 @@
         <v>771</v>
       </c>
       <c r="G274" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H274" t="n">
         <v>3</v>
       </c>
       <c r="I274" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="J274" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2853673345476624</v>
       </c>
       <c r="K274" t="n">
-        <v>0.3137254901960784</v>
+        <v>0.3139040680024286</v>
       </c>
       <c r="L274" t="n">
-        <v>0.392156862745098</v>
+        <v>0.4007285974499089</v>
       </c>
       <c r="M274" t="n">
-        <v>0.0625</v>
+        <v>0.06189555125725343</v>
       </c>
       <c r="N274" t="n">
         <v>0</v>
       </c>
       <c r="O274" t="n">
-        <v>0.2494446214443811</v>
+        <v>0.2473964910885989</v>
       </c>
       <c r="P274" t="n">
-        <v>0.4992820272245244</v>
+        <v>0.5366351868481504</v>
       </c>
       <c r="Q274" t="n">
-        <v>0.2512733513310944</v>
+        <v>0.2159683220632509</v>
       </c>
       <c r="R274" t="n">
         <v>1</v>
       </c>
       <c r="S274" t="n">
-        <v>0.185556537028446</v>
+        <v>0.2227311188457217</v>
       </c>
       <c r="T274" t="n">
         <v>0</v>
       </c>
       <c r="U274" t="n">
-        <v>0.185556537028446</v>
+        <v>0.2227311188457217</v>
       </c>
       <c r="V274" t="n">
-        <v>0.4992820272245244</v>
+        <v>0.5366351868481504</v>
       </c>
       <c r="W274" t="n">
         <v>3</v>
       </c>
       <c r="X274" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y274" t="n">
-        <v>5.970462522467522</v>
+        <v>8.526336355289789</v>
       </c>
       <c r="Z274" t="n">
-        <v>5.970462522467522</v>
+        <v>8.526336355289789</v>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>771</v>
       </c>
       <c r="G275" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="H275" t="n">
         <v>5.75</v>
@@ -24948,57 +24948,57 @@
         <v>13</v>
       </c>
       <c r="J275" t="n">
-        <v>0.765685019206146</v>
+        <v>0.7686375321336761</v>
       </c>
       <c r="K275" t="n">
-        <v>0.1624583866837388</v>
+        <v>0.1604113110539846</v>
       </c>
       <c r="L275" t="n">
-        <v>0.07185659411011523</v>
+        <v>0.07095115681233934</v>
       </c>
       <c r="M275" t="n">
-        <v>0.07050825154887885</v>
+        <v>0.08416945373467111</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O275" t="n">
-        <v>0.3548142223011568</v>
+        <v>0.5221684715876772</v>
       </c>
       <c r="P275" t="n">
-        <v>0.6079036799981532</v>
+        <v>0.3143532580490948</v>
       </c>
       <c r="Q275" t="n">
-        <v>0.03728209770069008</v>
+        <v>0.1634782703632281</v>
       </c>
       <c r="R275" t="n">
         <v>1</v>
       </c>
       <c r="S275" t="n">
-        <v>0.4454452933144144</v>
+        <v>-0.2464690605459989</v>
       </c>
       <c r="T275" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U275" t="n">
-        <v>0.4454452933144144</v>
+        <v>0.2464690605459989</v>
       </c>
       <c r="V275" t="n">
-        <v>0.6079036799981532</v>
+        <v>0.4778315284123228</v>
       </c>
       <c r="W275" t="n">
-        <v>5.75</v>
+        <v>3.986666666666666</v>
       </c>
       <c r="X275" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.2</t>
         </is>
       </c>
       <c r="Y275" t="n">
-        <v>7.269370697910006</v>
+        <v>7.592033530888314</v>
       </c>
       <c r="Z275" t="n">
-        <v>7.269370697910006</v>
+        <v>7.592033530888314</v>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
@@ -25062,42 +25062,42 @@
         <v>1</v>
       </c>
       <c r="O276" t="n">
-        <v>0.3913412764483071</v>
+        <v>0.4232531465071245</v>
       </c>
       <c r="P276" t="n">
-        <v>0.3695979301265658</v>
+        <v>0.3872790360206924</v>
       </c>
       <c r="Q276" t="n">
-        <v>0.239060793425127</v>
+        <v>0.1894678174721829</v>
       </c>
       <c r="R276" t="n">
         <v>1</v>
       </c>
       <c r="S276" t="n">
-        <v>0.02494835162202785</v>
+        <v>0.05686022168084531</v>
       </c>
       <c r="T276" t="n">
         <v>1</v>
       </c>
       <c r="U276" t="n">
-        <v>0.02494835162202785</v>
+        <v>0.05686022168084531</v>
       </c>
       <c r="V276" t="n">
-        <v>0.3913412764483071</v>
+        <v>0.4232531465071245</v>
       </c>
       <c r="W276" t="n">
         <v>2.55</v>
       </c>
       <c r="X276" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y276" t="n">
-        <v>4.679696638626476</v>
+        <v>6.724864077121464</v>
       </c>
       <c r="Z276" t="n">
-        <v>4.679696638626476</v>
+        <v>6.724864077121464</v>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
@@ -25137,66 +25137,66 @@
         <v>771</v>
       </c>
       <c r="G277" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="H277" t="n">
         <v>4.75</v>
       </c>
       <c r="I277" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="J277" t="n">
-        <v>0.6520784141452969</v>
+        <v>0.6621983914209115</v>
       </c>
       <c r="K277" t="n">
-        <v>0.1976827192356268</v>
+        <v>0.1951742627345844</v>
       </c>
       <c r="L277" t="n">
-        <v>0.1502388666190764</v>
+        <v>0.142627345844504</v>
       </c>
       <c r="M277" t="n">
-        <v>0.06497076023391801</v>
+        <v>0.07865818392134183</v>
       </c>
       <c r="N277" t="n">
         <v>1</v>
       </c>
       <c r="O277" t="n">
-        <v>0.4853421236630436</v>
+        <v>0.612149970858894</v>
       </c>
       <c r="P277" t="n">
-        <v>0.4169765865326328</v>
+        <v>0.2630621682794289</v>
       </c>
       <c r="Q277" t="n">
-        <v>0.09768128980432349</v>
+        <v>0.1247878608616769</v>
       </c>
       <c r="R277" t="n">
         <v>1</v>
       </c>
       <c r="S277" t="n">
-        <v>-0.1667362904822533</v>
+        <v>-0.05004842056201753</v>
       </c>
       <c r="T277" t="n">
         <v>1</v>
       </c>
       <c r="U277" t="n">
-        <v>-0.1667362904822533</v>
+        <v>-0.05004842056201753</v>
       </c>
       <c r="V277" t="n">
-        <v>0.4853421236630436</v>
+        <v>0.612149970858894</v>
       </c>
       <c r="W277" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X277" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y277" t="n">
-        <v>5.803767814381814</v>
+        <v>9.726154153400092</v>
       </c>
       <c r="Z277" t="n">
-        <v>5.803767814381814</v>
+        <v>9.726154153400092</v>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
@@ -25236,66 +25236,66 @@
         <v>771</v>
       </c>
       <c r="G278" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H278" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I278" t="n">
         <v>2.45</v>
       </c>
       <c r="J278" t="n">
-        <v>0.2964905203711174</v>
+        <v>0.30625</v>
       </c>
       <c r="K278" t="n">
-        <v>0.3162565550625252</v>
+        <v>0.30625</v>
       </c>
       <c r="L278" t="n">
-        <v>0.3872529245663574</v>
+        <v>0.3875</v>
       </c>
       <c r="M278" t="n">
-        <v>0.05399659863945572</v>
+        <v>0.05332455562870297</v>
       </c>
       <c r="N278" t="n">
         <v>0</v>
       </c>
       <c r="O278" t="n">
-        <v>0.3011335445351196</v>
+        <v>0.3423940561969125</v>
       </c>
       <c r="P278" t="n">
-        <v>0.3943942906419498</v>
+        <v>0.3868601733755462</v>
       </c>
       <c r="Q278" t="n">
-        <v>0.3044721648229305</v>
+        <v>0.2707457704275413</v>
       </c>
       <c r="R278" t="n">
         <v>1</v>
       </c>
       <c r="S278" t="n">
-        <v>0.07813773557942455</v>
+        <v>0.08061017337554616</v>
       </c>
       <c r="T278" t="n">
         <v>0</v>
       </c>
       <c r="U278" t="n">
-        <v>0.07813773557942455</v>
+        <v>0.08061017337554616</v>
       </c>
       <c r="V278" t="n">
-        <v>0.3943942906419498</v>
+        <v>0.3868601733755462</v>
       </c>
       <c r="W278" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X278" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y278" t="n">
-        <v>4.71620487611508</v>
+        <v>6.146633768163611</v>
       </c>
       <c r="Z278" t="n">
-        <v>4.71620487611508</v>
+        <v>6.146633768163611</v>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
@@ -25335,66 +25335,66 @@
         <v>771</v>
       </c>
       <c r="G279" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H279" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I279" t="n">
         <v>6.5</v>
       </c>
       <c r="J279" t="n">
-        <v>0.6180910495661476</v>
+        <v>0.6263219741480611</v>
       </c>
       <c r="K279" t="n">
-        <v>0.2364198264590515</v>
+        <v>0.2291421856639248</v>
       </c>
       <c r="L279" t="n">
-        <v>0.1454891239748009</v>
+        <v>0.1445358401880141</v>
       </c>
       <c r="M279" t="n">
-        <v>0.05744092508798393</v>
+        <v>0.06441525953721072</v>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O279" t="n">
-        <v>0.4047304121164457</v>
+        <v>0.4906738836434155</v>
       </c>
       <c r="P279" t="n">
-        <v>0.544595938961471</v>
+        <v>0.3237213004645519</v>
       </c>
       <c r="Q279" t="n">
-        <v>0.0506736489220834</v>
+        <v>0.1856048158920323</v>
       </c>
       <c r="R279" t="n">
         <v>1</v>
       </c>
       <c r="S279" t="n">
-        <v>0.3081761125024195</v>
+        <v>-0.1356480905046456</v>
       </c>
       <c r="T279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U279" t="n">
-        <v>0.3081761125024195</v>
+        <v>-0.1356480905046456</v>
       </c>
       <c r="V279" t="n">
-        <v>0.544595938961471</v>
+        <v>0.4906738836434155</v>
       </c>
       <c r="W279" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="X279" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y279" t="n">
-        <v>6.512330639122516</v>
+        <v>7.796079487951872</v>
       </c>
       <c r="Z279" t="n">
-        <v>6.512330639122516</v>
+        <v>7.796079487951872</v>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
@@ -25458,42 +25458,42 @@
         <v>1</v>
       </c>
       <c r="O280" t="n">
-        <v>0.4698015650685076</v>
+        <v>0.5077785756551436</v>
       </c>
       <c r="P280" t="n">
-        <v>0.4356256451304839</v>
+        <v>0.3279300497663408</v>
       </c>
       <c r="Q280" t="n">
-        <v>0.09457278980100886</v>
+        <v>0.1642913745785154</v>
       </c>
       <c r="R280" t="n">
         <v>1</v>
       </c>
       <c r="S280" t="n">
-        <v>-0.02863539220832462</v>
+        <v>0.009341618378311378</v>
       </c>
       <c r="T280" t="n">
         <v>1</v>
       </c>
       <c r="U280" t="n">
-        <v>-0.02863539220832462</v>
+        <v>0.009341618378311378</v>
       </c>
       <c r="V280" t="n">
-        <v>0.4698015650685076</v>
+        <v>0.5077785756551436</v>
       </c>
       <c r="W280" t="n">
         <v>1.9</v>
       </c>
       <c r="X280" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y280" t="n">
-        <v>5.617932319395805</v>
+        <v>8.067847647997814</v>
       </c>
       <c r="Z280" t="n">
-        <v>5.617932319395805</v>
+        <v>8.067847647997814</v>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
@@ -25533,66 +25533,66 @@
         <v>771</v>
       </c>
       <c r="G281" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="H281" t="n">
         <v>3.4</v>
       </c>
       <c r="I281" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J281" t="n">
-        <v>0.4509283819628648</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="K281" t="n">
-        <v>0.2785145888594165</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="L281" t="n">
-        <v>0.2705570291777188</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="M281" t="n">
-        <v>0.05602240896358524</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="N281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O281" t="n">
-        <v>0.4077903325582086</v>
+        <v>0.3875247714313318</v>
       </c>
       <c r="P281" t="n">
-        <v>0.3705398372557717</v>
+        <v>0.4773304199145214</v>
       </c>
       <c r="Q281" t="n">
-        <v>0.2216698301860197</v>
+        <v>0.1351448086541466</v>
       </c>
       <c r="R281" t="n">
         <v>1</v>
       </c>
       <c r="S281" t="n">
-        <v>-0.04313804940465615</v>
+        <v>0.1997824695572443</v>
       </c>
       <c r="T281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U281" t="n">
-        <v>-0.04313804940465615</v>
+        <v>0.1997824695572443</v>
       </c>
       <c r="V281" t="n">
-        <v>0.4077903325582086</v>
+        <v>0.4773304199145214</v>
       </c>
       <c r="W281" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="X281" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y281" t="n">
-        <v>4.876396034316858</v>
+        <v>7.584071660874081</v>
       </c>
       <c r="Z281" t="n">
-        <v>4.876396034316858</v>
+        <v>7.584071660874081</v>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
@@ -25632,66 +25632,66 @@
         <v>771</v>
       </c>
       <c r="G282" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="H282" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I282" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="J282" t="n">
-        <v>0.1789473684210526</v>
+        <v>0.171786153098837</v>
       </c>
       <c r="K282" t="n">
-        <v>0.2684210526315789</v>
+        <v>0.2624510672343344</v>
       </c>
       <c r="L282" t="n">
-        <v>0.5526315789473685</v>
+        <v>0.5657627796668286</v>
       </c>
       <c r="M282" t="n">
-        <v>0.06442577030812324</v>
+        <v>0.05839835480554045</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O282" t="n">
-        <v>0.2447844449708477</v>
+        <v>0.2064711616103093</v>
       </c>
       <c r="P282" t="n">
-        <v>0.4906401072297463</v>
+        <v>0.3726241564025167</v>
       </c>
       <c r="Q282" t="n">
-        <v>0.2645754477994058</v>
+        <v>0.4209046819871741</v>
       </c>
       <c r="R282" t="n">
         <v>1</v>
       </c>
       <c r="S282" t="n">
-        <v>0.2222190545981673</v>
+        <v>-0.1448580976796545</v>
       </c>
       <c r="T282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U282" t="n">
-        <v>0.2222190545981673</v>
+        <v>-0.1448580976796545</v>
       </c>
       <c r="V282" t="n">
-        <v>0.4906401072297463</v>
+        <v>0.4209046819871741</v>
       </c>
       <c r="W282" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="X282" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y282" t="n">
-        <v>5.867121611644423</v>
+        <v>6.687550462758663</v>
       </c>
       <c r="Z282" t="n">
-        <v>5.867121611644423</v>
+        <v>6.687550462758663</v>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
@@ -25731,66 +25731,66 @@
         <v>771</v>
       </c>
       <c r="G283" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="H283" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="I283" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="J283" t="n">
-        <v>0.2612136217442544</v>
+        <v>0.2447552447552447</v>
       </c>
       <c r="K283" t="n">
-        <v>0.2676019983629997</v>
+        <v>0.2657342657342657</v>
       </c>
       <c r="L283" t="n">
-        <v>0.4711843798927459</v>
+        <v>0.4895104895104894</v>
       </c>
       <c r="M283" t="n">
-        <v>0.0154600193462342</v>
+        <v>0.07518796992481214</v>
       </c>
       <c r="N283" t="n">
         <v>0</v>
       </c>
       <c r="O283" t="n">
-        <v>0.2975947611767379</v>
+        <v>0.1936345853165756</v>
       </c>
       <c r="P283" t="n">
-        <v>0.3631868868116307</v>
+        <v>0.4361463595751254</v>
       </c>
       <c r="Q283" t="n">
-        <v>0.3392183520116314</v>
+        <v>0.3702190551082988</v>
       </c>
       <c r="R283" t="n">
         <v>1</v>
       </c>
       <c r="S283" t="n">
-        <v>0.095584888448631</v>
+        <v>0.1704120938408597</v>
       </c>
       <c r="T283" t="n">
         <v>0</v>
       </c>
       <c r="U283" t="n">
-        <v>0.095584888448631</v>
+        <v>0.1704120938408597</v>
       </c>
       <c r="V283" t="n">
-        <v>0.3631868868116307</v>
+        <v>0.4361463595751254</v>
       </c>
       <c r="W283" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="X283" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y283" t="n">
-        <v>4.343023738335729</v>
+        <v>6.929718089702827</v>
       </c>
       <c r="Z283" t="n">
-        <v>4.343023738335729</v>
+        <v>6.929718089702827</v>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
@@ -25830,66 +25830,66 @@
         <v>771</v>
       </c>
       <c r="G284" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="H284" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="I284" t="n">
-        <v>4.71</v>
+        <v>4.33</v>
       </c>
       <c r="J284" t="n">
-        <v>0.5593495980395171</v>
+        <v>0.5513024344538721</v>
       </c>
       <c r="K284" t="n">
-        <v>0.2316365394234235</v>
+        <v>0.2360705296251196</v>
       </c>
       <c r="L284" t="n">
-        <v>0.2090138625370595</v>
+        <v>0.2126270359210083</v>
       </c>
       <c r="M284" t="n">
-        <v>0.01579016088195551</v>
+        <v>0.08615953383692743</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O284" t="n">
-        <v>0.4159339070538805</v>
+        <v>0.3935526852620704</v>
       </c>
       <c r="P284" t="n">
-        <v>0.5210881830161578</v>
+        <v>0.371993721964238</v>
       </c>
       <c r="Q284" t="n">
-        <v>0.06297790992996173</v>
+        <v>0.2344535927736916</v>
       </c>
       <c r="R284" t="n">
         <v>1</v>
       </c>
       <c r="S284" t="n">
-        <v>0.2894516435927342</v>
+        <v>-0.1577497491918016</v>
       </c>
       <c r="T284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U284" t="n">
-        <v>0.2894516435927342</v>
+        <v>-0.1577497491918016</v>
       </c>
       <c r="V284" t="n">
-        <v>0.5210881830161578</v>
+        <v>0.3935526852620704</v>
       </c>
       <c r="W284" t="n">
-        <v>4.25</v>
+        <v>1.67</v>
       </c>
       <c r="X284" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y284" t="n">
-        <v>6.231222631612185</v>
+        <v>6.252967845400383</v>
       </c>
       <c r="Z284" t="n">
-        <v>6.231222631612185</v>
+        <v>6.252967845400383</v>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
@@ -25929,66 +25929,66 @@
         <v>771</v>
       </c>
       <c r="G285" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="H285" t="n">
-        <v>4.08</v>
+        <v>3.8</v>
       </c>
       <c r="I285" t="n">
-        <v>6.42</v>
+        <v>5.75</v>
       </c>
       <c r="J285" t="n">
-        <v>0.6048129009018994</v>
+        <v>0.5961394175022167</v>
       </c>
       <c r="K285" t="n">
-        <v>0.2416286834485529</v>
+        <v>0.2431621308232726</v>
       </c>
       <c r="L285" t="n">
-        <v>0.1535584156495476</v>
+        <v>0.1606984516745106</v>
       </c>
       <c r="M285" t="n">
-        <v>0.01435821160641315</v>
+        <v>0.08223222853768375</v>
       </c>
       <c r="N285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
-        <v>0.4323510492548665</v>
+        <v>0.4075709952077734</v>
       </c>
       <c r="P285" t="n">
-        <v>0.3628227709264049</v>
+        <v>0.5033898896900657</v>
       </c>
       <c r="Q285" t="n">
-        <v>0.2048261798187285</v>
+        <v>0.08903911510216062</v>
       </c>
       <c r="R285" t="n">
         <v>1</v>
       </c>
       <c r="S285" t="n">
-        <v>-0.1724618516470329</v>
+        <v>0.2602277588667931</v>
       </c>
       <c r="T285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U285" t="n">
-        <v>-0.1724618516470329</v>
+        <v>0.2602277588667931</v>
       </c>
       <c r="V285" t="n">
-        <v>0.4323510492548665</v>
+        <v>0.5033898896900657</v>
       </c>
       <c r="W285" t="n">
-        <v>1.63</v>
+        <v>3.8</v>
       </c>
       <c r="X285" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y285" t="n">
-        <v>5.170095447807653</v>
+        <v>7.998117944070326</v>
       </c>
       <c r="Z285" t="n">
-        <v>5.170095447807653</v>
+        <v>7.998117944070326</v>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
@@ -26028,66 +26028,66 @@
         <v>771</v>
       </c>
       <c r="G286" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H286" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="I286" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="J286" t="n">
-        <v>0.4559666492965086</v>
+        <v>0.4417349590245853</v>
       </c>
       <c r="K286" t="n">
-        <v>0.2813965607087024</v>
+        <v>0.2854287427543474</v>
       </c>
       <c r="L286" t="n">
-        <v>0.262636789994789</v>
+        <v>0.2728362982210674</v>
       </c>
       <c r="M286" t="n">
-        <v>0.01534391534391522</v>
+        <v>0.07800043094160736</v>
       </c>
       <c r="N286" t="n">
         <v>0</v>
       </c>
       <c r="O286" t="n">
-        <v>0.3641919878950581</v>
+        <v>0.4104221367688528</v>
       </c>
       <c r="P286" t="n">
-        <v>0.3644408345692408</v>
+        <v>0.4561838127363048</v>
       </c>
       <c r="Q286" t="n">
-        <v>0.2713671775357012</v>
+        <v>0.1333940504948426</v>
       </c>
       <c r="R286" t="n">
         <v>1</v>
       </c>
       <c r="S286" t="n">
-        <v>0.08304427386053836</v>
+        <v>0.1707550699819573</v>
       </c>
       <c r="T286" t="n">
         <v>0</v>
       </c>
       <c r="U286" t="n">
-        <v>0.08304427386053836</v>
+        <v>0.1707550699819573</v>
       </c>
       <c r="V286" t="n">
-        <v>0.3644408345692408</v>
+        <v>0.4561838127363048</v>
       </c>
       <c r="W286" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="X286" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y286" t="n">
-        <v>4.358018566276084</v>
+        <v>7.248083470025761</v>
       </c>
       <c r="Z286" t="n">
-        <v>4.358018566276084</v>
+        <v>7.248083470025761</v>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
@@ -26127,66 +26127,66 @@
         <v>771</v>
       </c>
       <c r="G287" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="H287" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="I287" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="J287" t="n">
-        <v>0.3700853556983106</v>
+        <v>0.3682310469314079</v>
       </c>
       <c r="K287" t="n">
-        <v>0.2719411729716869</v>
+        <v>0.2707581227436823</v>
       </c>
       <c r="L287" t="n">
-        <v>0.3579734713300023</v>
+        <v>0.3610108303249098</v>
       </c>
       <c r="M287" t="n">
-        <v>0.01581930718307589</v>
+        <v>0.08627450980392171</v>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O287" t="n">
-        <v>0.287198406903329</v>
+        <v>0.2795094227396802</v>
       </c>
       <c r="P287" t="n">
-        <v>0.4118390211731896</v>
+        <v>0.3115092711484589</v>
       </c>
       <c r="Q287" t="n">
-        <v>0.3009625719234814</v>
+        <v>0.4089813061118608</v>
       </c>
       <c r="R287" t="n">
         <v>1</v>
       </c>
       <c r="S287" t="n">
-        <v>0.1398978482015028</v>
+        <v>0.04797047578695102</v>
       </c>
       <c r="T287" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U287" t="n">
-        <v>0.1398978482015028</v>
+        <v>0.04797047578695102</v>
       </c>
       <c r="V287" t="n">
-        <v>0.4118390211731896</v>
+        <v>0.4089813061118608</v>
       </c>
       <c r="W287" t="n">
-        <v>3.62</v>
+        <v>2.55</v>
       </c>
       <c r="X287" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y287" t="n">
-        <v>4.924810642339619</v>
+        <v>6.498105723213031</v>
       </c>
       <c r="Z287" t="n">
-        <v>4.924810642339619</v>
+        <v>6.498105723213031</v>
       </c>
       <c r="AA287" t="inlineStr">
         <is>
@@ -26226,66 +26226,66 @@
         <v>771</v>
       </c>
       <c r="G288" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="H288" t="n">
-        <v>4.66</v>
+        <v>4.33</v>
       </c>
       <c r="I288" t="n">
-        <v>6.57</v>
+        <v>5.5</v>
       </c>
       <c r="J288" t="n">
-        <v>0.639030356665776</v>
+        <v>0.6207739668538242</v>
       </c>
       <c r="K288" t="n">
-        <v>0.2111817058509217</v>
+        <v>0.2121814020655104</v>
       </c>
       <c r="L288" t="n">
-        <v>0.1497879374833021</v>
+        <v>0.1670446310806654</v>
       </c>
       <c r="M288" t="n">
-        <v>0.01614992555083106</v>
+        <v>0.08844073971094746</v>
       </c>
       <c r="N288" t="n">
         <v>1</v>
       </c>
       <c r="O288" t="n">
-        <v>0.4856329309544022</v>
+        <v>0.4792232529054484</v>
       </c>
       <c r="P288" t="n">
-        <v>0.4553411577455253</v>
+        <v>0.4005628360649574</v>
       </c>
       <c r="Q288" t="n">
-        <v>0.05902591130007249</v>
+        <v>0.1202139110295941</v>
       </c>
       <c r="R288" t="n">
         <v>1</v>
       </c>
       <c r="S288" t="n">
-        <v>-0.1533974257113738</v>
+        <v>-0.1415507139483758</v>
       </c>
       <c r="T288" t="n">
         <v>1</v>
       </c>
       <c r="U288" t="n">
-        <v>-0.1533974257113738</v>
+        <v>-0.1415507139483758</v>
       </c>
       <c r="V288" t="n">
-        <v>0.4856329309544022</v>
+        <v>0.4792232529054484</v>
       </c>
       <c r="W288" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="X288" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y288" t="n">
-        <v>5.807245315953358</v>
+        <v>7.614145966735057</v>
       </c>
       <c r="Z288" t="n">
-        <v>5.807245315953358</v>
+        <v>7.614145966735057</v>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
@@ -26325,66 +26325,66 @@
         <v>771</v>
       </c>
       <c r="G289" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="H289" t="n">
-        <v>4.56</v>
+        <v>4.33</v>
       </c>
       <c r="I289" t="n">
-        <v>6.78</v>
+        <v>5.75</v>
       </c>
       <c r="J289" t="n">
-        <v>0.6390356425329264</v>
+        <v>0.6253155146562052</v>
       </c>
       <c r="K289" t="n">
-        <v>0.215814668750155</v>
+        <v>0.213733709397502</v>
       </c>
       <c r="L289" t="n">
-        <v>0.1451496887169184</v>
+        <v>0.1609507759462928</v>
       </c>
       <c r="M289" t="n">
-        <v>0.01614152033341609</v>
+        <v>0.08053560137102656</v>
       </c>
       <c r="N289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O289" t="n">
-        <v>0.4491487214532782</v>
+        <v>0.3783718791484379</v>
       </c>
       <c r="P289" t="n">
-        <v>0.3811947650146074</v>
+        <v>0.4305596769287864</v>
       </c>
       <c r="Q289" t="n">
-        <v>0.1696565135321142</v>
+        <v>0.1910684439227755</v>
       </c>
       <c r="R289" t="n">
         <v>1</v>
       </c>
       <c r="S289" t="n">
-        <v>-0.1898869210796482</v>
+        <v>0.2168259675312844</v>
       </c>
       <c r="T289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U289" t="n">
-        <v>-0.1898869210796482</v>
+        <v>0.2168259675312844</v>
       </c>
       <c r="V289" t="n">
-        <v>0.4491487214532782</v>
+        <v>0.4305596769287864</v>
       </c>
       <c r="W289" t="n">
-        <v>1.54</v>
+        <v>4.33</v>
       </c>
       <c r="X289" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y289" t="n">
-        <v>5.370963628228279</v>
+        <v>6.840953997223694</v>
       </c>
       <c r="Z289" t="n">
-        <v>5.370963628228279</v>
+        <v>6.840953997223694</v>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
@@ -26424,66 +26424,66 @@
         <v>771</v>
       </c>
       <c r="G290" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="H290" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="I290" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J290" t="n">
-        <v>0.457992565055762</v>
+        <v>0.4513970877607241</v>
       </c>
       <c r="K290" t="n">
-        <v>0.2862453531598513</v>
+        <v>0.298504525777253</v>
       </c>
       <c r="L290" t="n">
-        <v>0.2557620817843866</v>
+        <v>0.2500983864620228</v>
       </c>
       <c r="M290" t="n">
-        <v>0.01555421322863193</v>
+        <v>0.08065579348034113</v>
       </c>
       <c r="N290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O290" t="n">
-        <v>0.4286117247174239</v>
+        <v>0.3379584018994157</v>
       </c>
       <c r="P290" t="n">
-        <v>0.3710820883539895</v>
+        <v>0.4105416940307048</v>
       </c>
       <c r="Q290" t="n">
-        <v>0.2003061869285866</v>
+        <v>0.2514999040698795</v>
       </c>
       <c r="R290" t="n">
         <v>1</v>
       </c>
       <c r="S290" t="n">
-        <v>-0.02938084033833815</v>
+        <v>0.1120371682534518</v>
       </c>
       <c r="T290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U290" t="n">
-        <v>-0.02938084033833815</v>
+        <v>0.1120371682534518</v>
       </c>
       <c r="V290" t="n">
-        <v>0.4286117247174239</v>
+        <v>0.4105416940307048</v>
       </c>
       <c r="W290" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="X290" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y290" t="n">
-        <v>5.125380245191107</v>
+        <v>6.522897970473105</v>
       </c>
       <c r="Z290" t="n">
-        <v>5.125380245191107</v>
+        <v>6.522897970473105</v>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
@@ -26523,66 +26523,66 @@
         <v>771</v>
       </c>
       <c r="G291" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="H291" t="n">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="I291" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J291" t="n">
-        <v>0.5084777611444821</v>
+        <v>0.5038814396612561</v>
       </c>
       <c r="K291" t="n">
-        <v>0.2673297714418144</v>
+        <v>0.2741707833450953</v>
       </c>
       <c r="L291" t="n">
-        <v>0.2241924674137034</v>
+        <v>0.2219477769936486</v>
       </c>
       <c r="M291" t="n">
-        <v>0.01373935482560085</v>
+        <v>0.07275342569460208</v>
       </c>
       <c r="N291" t="n">
         <v>1</v>
       </c>
       <c r="O291" t="n">
-        <v>0.4444813455119924</v>
+        <v>0.3737144766483231</v>
       </c>
       <c r="P291" t="n">
-        <v>0.3979370637554646</v>
+        <v>0.3732335341397709</v>
       </c>
       <c r="Q291" t="n">
-        <v>0.1575815907325429</v>
+        <v>0.2530519892119061</v>
       </c>
       <c r="R291" t="n">
         <v>1</v>
       </c>
       <c r="S291" t="n">
-        <v>-0.0639964156324897</v>
+        <v>-0.130166963012933</v>
       </c>
       <c r="T291" t="n">
         <v>1</v>
       </c>
       <c r="U291" t="n">
-        <v>-0.0639964156324897</v>
+        <v>-0.130166963012933</v>
       </c>
       <c r="V291" t="n">
-        <v>0.4444813455119924</v>
+        <v>0.3737144766483231</v>
       </c>
       <c r="W291" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="X291" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y291" t="n">
-        <v>5.31515069762747</v>
+        <v>5.937768165109796</v>
       </c>
       <c r="Z291" t="n">
-        <v>5.31515069762747</v>
+        <v>5.937768165109796</v>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
@@ -26622,66 +26622,66 @@
         <v>771</v>
       </c>
       <c r="G292" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="H292" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="I292" t="n">
-        <v>4.49</v>
+        <v>4.2</v>
       </c>
       <c r="J292" t="n">
-        <v>0.4879726526597545</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="K292" t="n">
-        <v>0.2924939935824048</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="L292" t="n">
-        <v>0.2195333537578406</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="M292" t="n">
-        <v>0.01450255921549548</v>
+        <v>0.09523809523809512</v>
       </c>
       <c r="N292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O292" t="n">
-        <v>0.445501270182507</v>
+        <v>0.4158686899707409</v>
       </c>
       <c r="P292" t="n">
-        <v>0.3785793296003209</v>
+        <v>0.4301014299472289</v>
       </c>
       <c r="Q292" t="n">
-        <v>0.1759194002171721</v>
+        <v>0.1540298800820306</v>
       </c>
       <c r="R292" t="n">
         <v>1</v>
       </c>
       <c r="S292" t="n">
-        <v>-0.04247138247724752</v>
+        <v>0.1692318647298376</v>
       </c>
       <c r="T292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U292" t="n">
-        <v>-0.04247138247724752</v>
+        <v>0.1692318647298376</v>
       </c>
       <c r="V292" t="n">
-        <v>0.445501270182507</v>
+        <v>0.4301014299472289</v>
       </c>
       <c r="W292" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="X292" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="Y292" t="n">
-        <v>5.327347054974636</v>
+        <v>6.833673133064369</v>
       </c>
       <c r="Z292" t="n">
-        <v>5.327347054974636</v>
+        <v>6.833673133064369</v>
       </c>
       <c r="AA292" t="inlineStr">
         <is>
@@ -26745,28 +26745,28 @@
         <v>1</v>
       </c>
       <c r="O293" t="n">
-        <v>0.4432017310763952</v>
+        <v>0.4284736097345697</v>
       </c>
       <c r="P293" t="n">
-        <v>0.2527220757181619</v>
+        <v>0.2555038255714536</v>
       </c>
       <c r="Q293" t="n">
-        <v>0.304076193205443</v>
+        <v>0.3160225646939767</v>
       </c>
       <c r="R293" t="n">
         <v>1</v>
       </c>
       <c r="S293" t="n">
-        <v>0.003201731076395209</v>
+        <v>-0.01152639026543034</v>
       </c>
       <c r="T293" t="n">
         <v>1</v>
       </c>
       <c r="U293" t="n">
-        <v>0.003201731076395209</v>
+        <v>-0.01152639026543034</v>
       </c>
       <c r="V293" t="n">
-        <v>0.4432017310763952</v>
+        <v>0.4284736097345697</v>
       </c>
       <c r="W293" t="n">
         <v>2.1</v>
@@ -26777,10 +26777,10 @@
         </is>
       </c>
       <c r="Y293" t="n">
-        <v>6.785595047757168</v>
+        <v>5.765995743033519</v>
       </c>
       <c r="Z293" t="n">
-        <v>6.785595047757168</v>
+        <v>5.765995743033519</v>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
@@ -26826,46 +26826,46 @@
         <v>3.6</v>
       </c>
       <c r="I294" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J294" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4064516129032258</v>
       </c>
       <c r="K294" t="n">
-        <v>0.2621082621082621</v>
+        <v>0.2596774193548387</v>
       </c>
       <c r="L294" t="n">
-        <v>0.3276353276353276</v>
+        <v>0.3338709677419355</v>
       </c>
       <c r="M294" t="n">
-        <v>0.05978260869565233</v>
+        <v>0.06970324361628721</v>
       </c>
       <c r="N294" t="n">
         <v>1</v>
       </c>
       <c r="O294" t="n">
-        <v>0.4053712514185447</v>
+        <v>0.3906618995084899</v>
       </c>
       <c r="P294" t="n">
-        <v>0.3364516127719515</v>
+        <v>0.3403036898509849</v>
       </c>
       <c r="Q294" t="n">
-        <v>0.2581771358095038</v>
+        <v>0.2690344106405253</v>
       </c>
       <c r="R294" t="n">
         <v>1</v>
       </c>
       <c r="S294" t="n">
-        <v>-0.0048851588378655</v>
+        <v>-0.01578971339473589</v>
       </c>
       <c r="T294" t="n">
         <v>1</v>
       </c>
       <c r="U294" t="n">
-        <v>-0.0048851588378655</v>
+        <v>-0.01578971339473589</v>
       </c>
       <c r="V294" t="n">
-        <v>0.4053712514185447</v>
+        <v>0.3906618995084899</v>
       </c>
       <c r="W294" t="n">
         <v>2.3</v>
@@ -26876,10 +26876,10 @@
         </is>
       </c>
       <c r="Y294" t="n">
-        <v>6.206395334802211</v>
+        <v>5.257161230832282</v>
       </c>
       <c r="Z294" t="n">
-        <v>6.206395334802211</v>
+        <v>5.257161230832282</v>
       </c>
       <c r="AA294" t="inlineStr">
         <is>
@@ -26975,10 +26975,10 @@
         </is>
       </c>
       <c r="Y295" t="n">
-        <v>7.530836117658744</v>
+        <v>6.619221981235865</v>
       </c>
       <c r="Z295" t="n">
-        <v>7.530836117658744</v>
+        <v>6.619221981235865</v>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
@@ -27074,10 +27074,10 @@
         </is>
       </c>
       <c r="Y296" t="n">
-        <v>10.60649533869987</v>
+        <v>9.322570029796969</v>
       </c>
       <c r="Z296" t="n">
-        <v>10.60649533869987</v>
+        <v>9.322570029796969</v>
       </c>
       <c r="AA296" t="inlineStr">
         <is>
@@ -27141,28 +27141,28 @@
         <v>2</v>
       </c>
       <c r="O297" t="n">
-        <v>0.1151454501749231</v>
+        <v>0.1152265855333144</v>
       </c>
       <c r="P297" t="n">
-        <v>0.3743238198393466</v>
+        <v>0.3748086521324477</v>
       </c>
       <c r="Q297" t="n">
-        <v>0.5105307299857302</v>
+        <v>0.5099647623342379</v>
       </c>
       <c r="R297" t="n">
         <v>1</v>
       </c>
       <c r="S297" t="n">
-        <v>0.06731743358683828</v>
+        <v>0.06675146593534598</v>
       </c>
       <c r="T297" t="n">
         <v>2</v>
       </c>
       <c r="U297" t="n">
-        <v>0.06731743358683828</v>
+        <v>0.06675146593534598</v>
       </c>
       <c r="V297" t="n">
-        <v>0.5105307299857302</v>
+        <v>0.5099647623342379</v>
       </c>
       <c r="W297" t="n">
         <v>2.1</v>
@@ -27173,10 +27173,10 @@
         </is>
       </c>
       <c r="Y297" t="n">
-        <v>7.816428840892513</v>
+        <v>6.862627200162609</v>
       </c>
       <c r="Z297" t="n">
-        <v>7.816428840892513</v>
+        <v>6.862627200162609</v>
       </c>
       <c r="AA297" t="inlineStr">
         <is>
@@ -27272,10 +27272,10 @@
         </is>
       </c>
       <c r="Y298" t="n">
-        <v>5.6762731161631</v>
+        <v>4.989155413155623</v>
       </c>
       <c r="Z298" t="n">
-        <v>5.6762731161631</v>
+        <v>4.989155413155623</v>
       </c>
       <c r="AA298" t="inlineStr">
         <is>
@@ -27371,10 +27371,10 @@
         </is>
       </c>
       <c r="Y299" t="n">
-        <v>5.109626040528882</v>
+        <v>4.491101449420304</v>
       </c>
       <c r="Z299" t="n">
-        <v>5.109626040528882</v>
+        <v>4.491101449420304</v>
       </c>
       <c r="AA299" t="inlineStr">
         <is>
@@ -27438,28 +27438,28 @@
         <v>2</v>
       </c>
       <c r="O300" t="n">
-        <v>0.2977768912470203</v>
+        <v>0.2994745283481771</v>
       </c>
       <c r="P300" t="n">
-        <v>0.3160042679908979</v>
+        <v>0.3158272070456328</v>
       </c>
       <c r="Q300" t="n">
-        <v>0.3862188407620817</v>
+        <v>0.3846982646061901</v>
       </c>
       <c r="R300" t="n">
         <v>1</v>
       </c>
       <c r="S300" t="n">
-        <v>0.09157778919484205</v>
+        <v>0.09005721303895037</v>
       </c>
       <c r="T300" t="n">
         <v>2</v>
       </c>
       <c r="U300" t="n">
-        <v>0.09157778919484205</v>
+        <v>0.09005721303895037</v>
       </c>
       <c r="V300" t="n">
-        <v>0.3862188407620817</v>
+        <v>0.3846982646061901</v>
       </c>
       <c r="W300" t="n">
         <v>3.2</v>
@@ -27470,10 +27470,10 @@
         </is>
       </c>
       <c r="Y300" t="n">
-        <v>5.913164298480501</v>
+        <v>5.176908228830668</v>
       </c>
       <c r="Z300" t="n">
-        <v>5.913164298480501</v>
+        <v>5.176908228830668</v>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
@@ -27569,10 +27569,10 @@
         </is>
       </c>
       <c r="Y301" t="n">
-        <v>6.389904151845228</v>
+        <v>5.616400803186471</v>
       </c>
       <c r="Z301" t="n">
-        <v>6.389904151845228</v>
+        <v>5.616400803186471</v>
       </c>
       <c r="AA301" t="inlineStr">
         <is>
@@ -27668,10 +27668,10 @@
         </is>
       </c>
       <c r="Y302" t="n">
-        <v>7.89020288480618</v>
+        <v>6.935087094652715</v>
       </c>
       <c r="Z302" t="n">
-        <v>7.89020288480618</v>
+        <v>6.935087094652715</v>
       </c>
       <c r="AA302" t="inlineStr">
         <is>
@@ -27767,10 +27767,10 @@
         </is>
       </c>
       <c r="Y303" t="n">
-        <v>6.251474904929034</v>
+        <v>5.494728534700238</v>
       </c>
       <c r="Z303" t="n">
-        <v>6.251474904929034</v>
+        <v>5.494728534700238</v>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
@@ -27866,10 +27866,10 @@
         </is>
       </c>
       <c r="Y304" t="n">
-        <v>7.31204145391586</v>
+        <v>6.426912598187672</v>
       </c>
       <c r="Z304" t="n">
-        <v>7.31204145391586</v>
+        <v>6.426912598187672</v>
       </c>
       <c r="AA304" t="inlineStr">
         <is>
@@ -27965,10 +27965,10 @@
         </is>
       </c>
       <c r="Y305" t="n">
-        <v>8.597172540364665</v>
+        <v>7.556477470306555</v>
       </c>
       <c r="Z305" t="n">
-        <v>8.597172540364665</v>
+        <v>7.556477470306555</v>
       </c>
       <c r="AA305" t="inlineStr">
         <is>
@@ -28064,10 +28064,10 @@
         </is>
       </c>
       <c r="Y306" t="n">
-        <v>10.14088564688088</v>
+        <v>8.91332278837341</v>
       </c>
       <c r="Z306" t="n">
-        <v>10.14088564688088</v>
+        <v>8.91332278837341</v>
       </c>
       <c r="AA306" t="inlineStr">
         <is>
@@ -28131,28 +28131,28 @@
         <v>1</v>
       </c>
       <c r="O307" t="n">
-        <v>0.5151387301867983</v>
+        <v>0.5132576304200798</v>
       </c>
       <c r="P307" t="n">
-        <v>0.300936599063943</v>
+        <v>0.3017161286840445</v>
       </c>
       <c r="Q307" t="n">
-        <v>0.1839246707492587</v>
+        <v>0.1850262408958759</v>
       </c>
       <c r="R307" t="n">
         <v>1</v>
       </c>
       <c r="S307" t="n">
-        <v>0.08859844582660881</v>
+        <v>0.08671734605989023</v>
       </c>
       <c r="T307" t="n">
         <v>1</v>
       </c>
       <c r="U307" t="n">
-        <v>0.08859844582660881</v>
+        <v>0.08671734605989023</v>
       </c>
       <c r="V307" t="n">
-        <v>0.5151387301867983</v>
+        <v>0.5132576304200798</v>
       </c>
       <c r="W307" t="n">
         <v>2.2</v>
@@ -28163,10 +28163,10 @@
         </is>
       </c>
       <c r="Y307" t="n">
-        <v>7.886979159521665</v>
+        <v>6.906939528702742</v>
       </c>
       <c r="Z307" t="n">
-        <v>7.886979159521665</v>
+        <v>6.906939528702742</v>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
@@ -28230,28 +28230,28 @@
         <v>1</v>
       </c>
       <c r="O308" t="n">
-        <v>0.6782378990541292</v>
+        <v>0.6781773006802799</v>
       </c>
       <c r="P308" t="n">
-        <v>0.2056992415104</v>
+        <v>0.2055595474375957</v>
       </c>
       <c r="Q308" t="n">
-        <v>0.1160628594354707</v>
+        <v>0.1162631518821245</v>
       </c>
       <c r="R308" t="n">
         <v>1</v>
       </c>
       <c r="S308" t="n">
-        <v>-0.01182364343637743</v>
+        <v>-0.01188424181022674</v>
       </c>
       <c r="T308" t="n">
         <v>1</v>
       </c>
       <c r="U308" t="n">
-        <v>-0.01182364343637743</v>
+        <v>-0.01188424181022674</v>
       </c>
       <c r="V308" t="n">
-        <v>0.6782378990541292</v>
+        <v>0.6781773006802799</v>
       </c>
       <c r="W308" t="n">
         <v>1.35</v>
@@ -28262,10 +28262,10 @@
         </is>
       </c>
       <c r="Y308" t="n">
-        <v>10.38409240380343</v>
+        <v>9.126273683849156</v>
       </c>
       <c r="Z308" t="n">
-        <v>10.38409240380343</v>
+        <v>9.126273683849156</v>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
@@ -28361,10 +28361,10 @@
         </is>
       </c>
       <c r="Y309" t="n">
-        <v>8.370656539952014</v>
+        <v>7.357381424979361</v>
       </c>
       <c r="Z309" t="n">
-        <v>8.370656539952014</v>
+        <v>7.357381424979361</v>
       </c>
       <c r="AA309" t="inlineStr">
         <is>
@@ -28460,10 +28460,10 @@
         </is>
       </c>
       <c r="Y310" t="n">
-        <v>8.89341366761057</v>
+        <v>7.81685835638296</v>
       </c>
       <c r="Z310" t="n">
-        <v>8.89341366761057</v>
+        <v>7.81685835638296</v>
       </c>
       <c r="AA310" t="inlineStr">
         <is>
@@ -28559,10 +28559,10 @@
         </is>
       </c>
       <c r="Y311" t="n">
-        <v>9.648065922450336</v>
+        <v>8.480159311998172</v>
       </c>
       <c r="Z311" t="n">
-        <v>9.648065922450336</v>
+        <v>8.480159311998172</v>
       </c>
       <c r="AA311" t="inlineStr">
         <is>
@@ -28638,10 +28638,10 @@
         </is>
       </c>
       <c r="Y312" t="n">
-        <v>5.129624520960094</v>
+        <v>4.508679096735082</v>
       </c>
       <c r="Z312" t="n">
-        <v>5.129624520960094</v>
+        <v>4.508679096735082</v>
       </c>
       <c r="AA312" t="inlineStr">
         <is>
@@ -28717,10 +28717,10 @@
         </is>
       </c>
       <c r="Y313" t="n">
-        <v>9.705874031254252</v>
+        <v>8.530969699916627</v>
       </c>
       <c r="Z313" t="n">
-        <v>9.705874031254252</v>
+        <v>8.530969699916627</v>
       </c>
       <c r="AA313" t="inlineStr">
         <is>
@@ -28770,13 +28770,13 @@
         <v>2</v>
       </c>
       <c r="O314" t="n">
-        <v>0.3013030370092886</v>
+        <v>0.3014346680382699</v>
       </c>
       <c r="P314" t="n">
-        <v>0.3452447177301354</v>
+        <v>0.3455993884842793</v>
       </c>
       <c r="Q314" t="n">
-        <v>0.353452245260576</v>
+        <v>0.3529659434774507</v>
       </c>
       <c r="R314" t="n">
         <v>1</v>
@@ -28787,7 +28787,7 @@
       </c>
       <c r="U314" t="inlineStr"/>
       <c r="V314" t="n">
-        <v>0.6465477547394241</v>
+        <v>0.6470340565225492</v>
       </c>
       <c r="W314" t="inlineStr"/>
       <c r="X314" t="inlineStr">
@@ -28796,10 +28796,10 @@
         </is>
       </c>
       <c r="Y314" t="n">
-        <v>9.898903670893205</v>
+        <v>8.707177130040463</v>
       </c>
       <c r="Z314" t="n">
-        <v>9.898903670893205</v>
+        <v>8.707177130040463</v>
       </c>
       <c r="AA314" t="inlineStr">
         <is>
@@ -28849,13 +28849,13 @@
         <v>2</v>
       </c>
       <c r="O315" t="n">
-        <v>0.273626796577441</v>
+        <v>0.2752378042204544</v>
       </c>
       <c r="P315" t="n">
-        <v>0.3300062404058863</v>
+        <v>0.3298825206222441</v>
       </c>
       <c r="Q315" t="n">
-        <v>0.3963669630166726</v>
+        <v>0.3948796751573014</v>
       </c>
       <c r="R315" t="n">
         <v>1</v>
@@ -28866,7 +28866,7 @@
       </c>
       <c r="U315" t="inlineStr"/>
       <c r="V315" t="n">
-        <v>0.6036330369833274</v>
+        <v>0.6051203248426986</v>
       </c>
       <c r="W315" t="inlineStr"/>
       <c r="X315" t="inlineStr">
@@ -28875,10 +28875,10 @@
         </is>
       </c>
       <c r="Y315" t="n">
-        <v>9.241862247398695</v>
+        <v>8.143141462615393</v>
       </c>
       <c r="Z315" t="n">
-        <v>9.241862247398695</v>
+        <v>8.143141462615393</v>
       </c>
       <c r="AA315" t="inlineStr">
         <is>
@@ -28954,10 +28954,10 @@
         </is>
       </c>
       <c r="Y316" t="n">
-        <v>8.119589276859568</v>
+        <v>7.136706068263869</v>
       </c>
       <c r="Z316" t="n">
-        <v>8.119589276859568</v>
+        <v>7.136706068263869</v>
       </c>
       <c r="AA316" t="inlineStr">
         <is>
@@ -29033,10 +29033,10 @@
         </is>
       </c>
       <c r="Y317" t="n">
-        <v>9.612945566563537</v>
+        <v>8.449290305151825</v>
       </c>
       <c r="Z317" t="n">
-        <v>9.612945566563537</v>
+        <v>8.449290305151825</v>
       </c>
       <c r="AA317" t="inlineStr">
         <is>
@@ -29112,10 +29112,10 @@
         </is>
       </c>
       <c r="Y318" t="n">
-        <v>9.82097492867906</v>
+        <v>8.632137535518275</v>
       </c>
       <c r="Z318" t="n">
-        <v>9.82097492867906</v>
+        <v>8.632137535518275</v>
       </c>
       <c r="AA318" t="inlineStr">
         <is>
@@ -29191,10 +29191,10 @@
         </is>
       </c>
       <c r="Y319" t="n">
-        <v>10.00229384660702</v>
+        <v>8.79150764375213</v>
       </c>
       <c r="Z319" t="n">
-        <v>10.00229384660702</v>
+        <v>8.79150764375213</v>
       </c>
       <c r="AA319" t="inlineStr">
         <is>
@@ -29270,10 +29270,10 @@
         </is>
       </c>
       <c r="Y320" t="n">
-        <v>8.778984417366186</v>
+        <v>7.716280864497578</v>
       </c>
       <c r="Z320" t="n">
-        <v>8.778984417366186</v>
+        <v>7.716280864497578</v>
       </c>
       <c r="AA320" t="inlineStr">
         <is>
@@ -29349,10 +29349,10 @@
         </is>
       </c>
       <c r="Y321" t="n">
-        <v>6.413266613450864</v>
+        <v>5.636935218884775</v>
       </c>
       <c r="Z321" t="n">
-        <v>6.413266613450864</v>
+        <v>5.636935218884775</v>
       </c>
       <c r="AA321" t="inlineStr">
         <is>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -38200,98 +38200,98 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B283" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45529.5</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F283" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G283" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="H283" t="n">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="I283" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J283" t="n">
-        <v>0.6658656253129068</v>
+        <v>0.8103727714748785</v>
       </c>
       <c r="K283" t="n">
-        <v>0.1990587764093321</v>
+        <v>0.126418152350081</v>
       </c>
       <c r="L283" t="n">
-        <v>0.1350755982777611</v>
+        <v>0.06320907617504051</v>
       </c>
       <c r="M283" t="n">
-        <v>0.05760881075929269</v>
+        <v>0.05470085470085473</v>
       </c>
       <c r="N283" t="n">
         <v>1</v>
       </c>
       <c r="O283" t="n">
-        <v>0.4871383652464762</v>
+        <v>0.6663278450323864</v>
       </c>
       <c r="P283" t="n">
-        <v>0.4134855108631623</v>
+        <v>0.3050264638899211</v>
       </c>
       <c r="Q283" t="n">
-        <v>0.09937612389036149</v>
+        <v>0.0286456910776924</v>
       </c>
       <c r="R283" t="n">
         <v>1</v>
       </c>
       <c r="S283" t="n">
-        <v>-0.1787272600664306</v>
+        <v>-0.1440449264424921</v>
       </c>
       <c r="T283" t="n">
         <v>1</v>
       </c>
       <c r="U283" t="n">
-        <v>-0.1787272600664306</v>
+        <v>-0.1440449264424921</v>
       </c>
       <c r="V283" t="n">
-        <v>0.4871383652464762</v>
+        <v>0.6663278450323864</v>
       </c>
       <c r="W283" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="X283" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y283" t="n">
-        <v>4.504232759138154</v>
+        <v>4.794443759594989</v>
       </c>
       <c r="Z283" t="n">
-        <v>4.504232759138154</v>
+        <v>4.794443759594989</v>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr"/>
@@ -38343,98 +38343,98 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F284" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G284" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="H284" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I284" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0.4210526315789474</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0.3157894736842106</v>
+      </c>
+      <c r="L284" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="M284" t="n">
+        <v>0.05555555555555536</v>
+      </c>
+      <c r="N284" t="n">
+        <v>1</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0.3872285443819356</v>
+      </c>
+      <c r="P284" t="n">
+        <v>0.3413351593230441</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>0.2714362962950203</v>
+      </c>
+      <c r="R284" t="n">
+        <v>1</v>
+      </c>
+      <c r="S284" t="n">
+        <v>-0.0338240871970118</v>
+      </c>
+      <c r="T284" t="n">
+        <v>1</v>
+      </c>
+      <c r="U284" t="n">
+        <v>-0.0338240871970118</v>
+      </c>
+      <c r="V284" t="n">
+        <v>0.3872285443819356</v>
+      </c>
+      <c r="W284" t="n">
         <v>2.25</v>
       </c>
-      <c r="J284" t="n">
-        <v>0.2798289933929266</v>
-      </c>
-      <c r="K284" t="n">
-        <v>0.2973183054799844</v>
-      </c>
-      <c r="L284" t="n">
-        <v>0.4228527011270889</v>
-      </c>
-      <c r="M284" t="n">
-        <v>0.05106209150326801</v>
-      </c>
-      <c r="N284" t="n">
-        <v>0</v>
-      </c>
-      <c r="O284" t="n">
-        <v>0.296795106668703</v>
-      </c>
-      <c r="P284" t="n">
-        <v>0.3972514661731673</v>
-      </c>
-      <c r="Q284" t="n">
-        <v>0.3059534271581297</v>
-      </c>
-      <c r="R284" t="n">
-        <v>1</v>
-      </c>
-      <c r="S284" t="n">
-        <v>0.09993316069318281</v>
-      </c>
-      <c r="T284" t="n">
-        <v>0</v>
-      </c>
-      <c r="U284" t="n">
-        <v>0.09993316069318281</v>
-      </c>
-      <c r="V284" t="n">
-        <v>0.3972514661731673</v>
-      </c>
-      <c r="W284" t="n">
-        <v>3.2</v>
-      </c>
       <c r="X284" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y284" t="n">
-        <v>7.261201837605509</v>
+        <v>3.244176162103757</v>
       </c>
       <c r="Z284" t="n">
-        <v>7.261201837605509</v>
+        <v>3.244176162103757</v>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr"/>
@@ -38486,98 +38486,98 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>45529.65625</v>
+        <v>45529.59375</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F285" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G285" t="n">
-        <v>1.45</v>
+        <v>2.45</v>
       </c>
       <c r="H285" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="I285" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="J285" t="n">
-        <v>0.6538661131292164</v>
+        <v>0.3875</v>
       </c>
       <c r="K285" t="n">
-        <v>0.210690192008303</v>
+        <v>0.30625</v>
       </c>
       <c r="L285" t="n">
-        <v>0.1354436948624805</v>
+        <v>0.30625</v>
       </c>
       <c r="M285" t="n">
-        <v>0.05473453749315826</v>
+        <v>0.05332455562870297</v>
       </c>
       <c r="N285" t="n">
         <v>0</v>
       </c>
       <c r="O285" t="n">
-        <v>0.4134914419577893</v>
+        <v>0.3263919874412956</v>
       </c>
       <c r="P285" t="n">
-        <v>0.5305119879743958</v>
+        <v>0.3664227486918926</v>
       </c>
       <c r="Q285" t="n">
-        <v>0.05599657006781505</v>
+        <v>0.3071852638668119</v>
       </c>
       <c r="R285" t="n">
         <v>1</v>
       </c>
       <c r="S285" t="n">
-        <v>0.3198217959660928</v>
+        <v>0.0601727486918926</v>
       </c>
       <c r="T285" t="n">
         <v>0</v>
       </c>
       <c r="U285" t="n">
-        <v>0.3198217959660928</v>
+        <v>0.0601727486918926</v>
       </c>
       <c r="V285" t="n">
-        <v>0.5305119879743958</v>
+        <v>0.3664227486918926</v>
       </c>
       <c r="W285" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="X285" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y285" t="n">
-        <v>12.41881768035136</v>
+        <v>3.916054014986857</v>
       </c>
       <c r="Z285" t="n">
-        <v>12.41881768035136</v>
+        <v>3.916054014986857</v>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr"/>
@@ -38629,98 +38629,98 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>45529.65625</v>
+        <v>45529.6875</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F286" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G286" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="H286" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="I286" t="n">
-        <v>4.1</v>
+        <v>5.75</v>
       </c>
       <c r="J286" t="n">
-        <v>0.4984369572768322</v>
+        <v>0.6174990513369328</v>
       </c>
       <c r="K286" t="n">
-        <v>0.2705800625217089</v>
+        <v>0.2181925054377615</v>
       </c>
       <c r="L286" t="n">
-        <v>0.2309829802014589</v>
+        <v>0.1643084432253056</v>
       </c>
       <c r="M286" t="n">
-        <v>0.05593251421236012</v>
+        <v>0.05845469693718108</v>
       </c>
       <c r="N286" t="n">
         <v>1</v>
       </c>
       <c r="O286" t="n">
-        <v>0.4739882954102477</v>
+        <v>0.5797813497031056</v>
       </c>
       <c r="P286" t="n">
-        <v>0.4229181611875265</v>
+        <v>0.3294347399719734</v>
       </c>
       <c r="Q286" t="n">
-        <v>0.1030935434022259</v>
+        <v>0.09078391032492103</v>
       </c>
       <c r="R286" t="n">
         <v>1</v>
       </c>
       <c r="S286" t="n">
-        <v>-0.02444866186658451</v>
+        <v>-0.03771770163382726</v>
       </c>
       <c r="T286" t="n">
         <v>1</v>
       </c>
       <c r="U286" t="n">
-        <v>-0.02444866186658451</v>
+        <v>-0.03771770163382726</v>
       </c>
       <c r="V286" t="n">
-        <v>0.4739882954102477</v>
+        <v>0.5797813497031056</v>
       </c>
       <c r="W286" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="X286" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y286" t="n">
-        <v>6.565363924740206</v>
+        <v>4.976026560098441</v>
       </c>
       <c r="Z286" t="n">
-        <v>6.565363924740206</v>
+        <v>4.976026560098441</v>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr"/>
@@ -38772,98 +38772,98 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>45530.5625</v>
+        <v>45530.6875</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F287" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G287" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="H287" t="n">
         <v>3.4</v>
       </c>
       <c r="I287" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J287" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.4844031193761248</v>
       </c>
       <c r="K287" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.2721205758848231</v>
       </c>
       <c r="L287" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.2434763047390522</v>
       </c>
       <c r="M287" t="n">
-        <v>0.06442577030812324</v>
+        <v>0.08083575121974929</v>
       </c>
       <c r="N287" t="n">
         <v>1</v>
       </c>
       <c r="O287" t="n">
-        <v>0.4092633779582805</v>
+        <v>0.5016740642422536</v>
       </c>
       <c r="P287" t="n">
-        <v>0.3821466677655259</v>
+        <v>0.3597433105455177</v>
       </c>
       <c r="Q287" t="n">
-        <v>0.2085899542761935</v>
+        <v>0.1385826252122287</v>
       </c>
       <c r="R287" t="n">
         <v>1</v>
       </c>
       <c r="S287" t="n">
-        <v>-0.03810504309435103</v>
+        <v>0.01727094486612873</v>
       </c>
       <c r="T287" t="n">
         <v>1</v>
       </c>
       <c r="U287" t="n">
-        <v>-0.03810504309435103</v>
+        <v>0.01727094486612873</v>
       </c>
       <c r="V287" t="n">
-        <v>0.4092633779582805</v>
+        <v>0.5016740642422536</v>
       </c>
       <c r="W287" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="X287" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y287" t="n">
-        <v>5.420633377469721</v>
+        <v>4.763802475505256</v>
       </c>
       <c r="Z287" t="n">
-        <v>5.420633377469721</v>
+        <v>4.763802475505256</v>
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr"/>
@@ -38915,98 +38915,98 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>45530.65625</v>
+        <v>45531.58333333334</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F288" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G288" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="H288" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="I288" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J288" t="n">
-        <v>0.1889456293181136</v>
+        <v>0.4243156199677939</v>
       </c>
       <c r="K288" t="n">
-        <v>0.2553319315109642</v>
+        <v>0.3011272141706924</v>
       </c>
       <c r="L288" t="n">
-        <v>0.5557224391709222</v>
+        <v>0.2745571658615137</v>
       </c>
       <c r="M288" t="n">
-        <v>0.05850556438791732</v>
+        <v>0.07124374676556844</v>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O288" t="n">
-        <v>0.2324751117409399</v>
+        <v>0.2500778026122632</v>
       </c>
       <c r="P288" t="n">
-        <v>0.5345253574679436</v>
+        <v>0.3726256843748756</v>
       </c>
       <c r="Q288" t="n">
-        <v>0.2329995307911163</v>
+        <v>0.3772965130128611</v>
       </c>
       <c r="R288" t="n">
         <v>1</v>
       </c>
       <c r="S288" t="n">
-        <v>0.2791934259569794</v>
+        <v>0.1027393471513474</v>
       </c>
       <c r="T288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U288" t="n">
-        <v>0.2791934259569794</v>
+        <v>0.1027393471513474</v>
       </c>
       <c r="V288" t="n">
-        <v>0.5345253574679436</v>
+        <v>0.3772965130128611</v>
       </c>
       <c r="W288" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="X288" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y288" t="n">
-        <v>11.88406882718736</v>
+        <v>4.406624938759072</v>
       </c>
       <c r="Z288" t="n">
-        <v>11.88406882718736</v>
+        <v>4.406624938759072</v>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr"/>
@@ -39058,98 +39058,98 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45531.6875</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F289" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G289" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="H289" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="I289" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="J289" t="n">
-        <v>0.2560834298957126</v>
+        <v>0.2069849407241269</v>
       </c>
       <c r="K289" t="n">
-        <v>0.2711471610660486</v>
+        <v>0.2451137455943608</v>
       </c>
       <c r="L289" t="n">
-        <v>0.4727694090382387</v>
+        <v>0.5479013136815124</v>
       </c>
       <c r="M289" t="n">
-        <v>0.08471593765711427</v>
+        <v>0.07361541107671132</v>
       </c>
       <c r="N289" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O289" t="n">
-        <v>0.2975947611767379</v>
+        <v>0.1928398026552932</v>
       </c>
       <c r="P289" t="n">
-        <v>0.3631868868116307</v>
+        <v>0.3569110152498295</v>
       </c>
       <c r="Q289" t="n">
-        <v>0.3392183520116314</v>
+        <v>0.4502491820948773</v>
       </c>
       <c r="R289" t="n">
         <v>1</v>
       </c>
       <c r="S289" t="n">
-        <v>0.09203972574558206</v>
+        <v>-0.0976521315866351</v>
       </c>
       <c r="T289" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U289" t="n">
-        <v>0.09203972574558206</v>
+        <v>-0.0976521315866351</v>
       </c>
       <c r="V289" t="n">
-        <v>0.3631868868116307</v>
+        <v>0.4502491820948773</v>
       </c>
       <c r="W289" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="X289" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y289" t="n">
-        <v>6.648420198470709</v>
+        <v>3.236764344170054</v>
       </c>
       <c r="Z289" t="n">
-        <v>6.648420198470709</v>
+        <v>3.236764344170054</v>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr"/>
@@ -39201,98 +39201,98 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B290" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F290" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G290" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="H290" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I290" t="n">
-        <v>4.1</v>
+        <v>6.25</v>
       </c>
       <c r="J290" t="n">
-        <v>0.528123658222413</v>
+        <v>0.607741694196846</v>
       </c>
       <c r="K290" t="n">
-        <v>0.2464577071704595</v>
+        <v>0.2415383656423362</v>
       </c>
       <c r="L290" t="n">
-        <v>0.2254186346071276</v>
+        <v>0.1507199401608178</v>
       </c>
       <c r="M290" t="n">
-        <v>0.08199767711962824</v>
+        <v>0.06157154673283705</v>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O290" t="n">
-        <v>0.4156206291348301</v>
+        <v>0.532728437829796</v>
       </c>
       <c r="P290" t="n">
-        <v>0.5214453905650241</v>
+        <v>0.335739327206231</v>
       </c>
       <c r="Q290" t="n">
-        <v>0.06293398030014599</v>
+        <v>0.131532234963973</v>
       </c>
       <c r="R290" t="n">
         <v>1</v>
       </c>
       <c r="S290" t="n">
-        <v>0.2749876833945647</v>
+        <v>-0.07501325636705003</v>
       </c>
       <c r="T290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U290" t="n">
-        <v>0.2749876833945647</v>
+        <v>-0.07501325636705003</v>
       </c>
       <c r="V290" t="n">
-        <v>0.5214453905650241</v>
+        <v>0.532728437829796</v>
       </c>
       <c r="W290" t="n">
-        <v>3.75</v>
+        <v>1.55</v>
       </c>
       <c r="X290" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y290" t="n">
-        <v>11.63161728594584</v>
+        <v>4.201725956040891</v>
       </c>
       <c r="Z290" t="n">
-        <v>11.63161728594584</v>
+        <v>4.201725956040891</v>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr"/>
@@ -39344,98 +39344,98 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F291" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G291" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="H291" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="I291" t="n">
-        <v>5.75</v>
+        <v>3.25</v>
       </c>
       <c r="J291" t="n">
-        <v>0.5961394175022167</v>
+        <v>0.40822528363047</v>
       </c>
       <c r="K291" t="n">
-        <v>0.2431621308232726</v>
+        <v>0.3028768233387358</v>
       </c>
       <c r="L291" t="n">
-        <v>0.1606984516745106</v>
+        <v>0.2888978930307942</v>
       </c>
       <c r="M291" t="n">
-        <v>0.08223222853768375</v>
+        <v>0.0650555615492503</v>
       </c>
       <c r="N291" t="n">
         <v>1</v>
       </c>
       <c r="O291" t="n">
-        <v>0.4323510492548665</v>
+        <v>0.5850525782619274</v>
       </c>
       <c r="P291" t="n">
-        <v>0.3628227709264049</v>
+        <v>0.2922211885621182</v>
       </c>
       <c r="Q291" t="n">
-        <v>0.2048261798187285</v>
+        <v>0.1227262331759545</v>
       </c>
       <c r="R291" t="n">
         <v>1</v>
       </c>
       <c r="S291" t="n">
-        <v>-0.1637883682473502</v>
+        <v>0.1768272946314574</v>
       </c>
       <c r="T291" t="n">
         <v>1</v>
       </c>
       <c r="U291" t="n">
-        <v>-0.1637883682473502</v>
+        <v>0.1768272946314574</v>
       </c>
       <c r="V291" t="n">
-        <v>0.4323510492548665</v>
+        <v>0.5850525782619274</v>
       </c>
       <c r="W291" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="X291" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y291" t="n">
-        <v>3.922260921732502</v>
+        <v>6.993891762757316</v>
       </c>
       <c r="Z291" t="n">
-        <v>3.922260921732502</v>
+        <v>6.993891762757316</v>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr"/>
@@ -39487,98 +39487,98 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45532.6875</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F292" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G292" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="H292" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="I292" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="J292" t="n">
-        <v>0.4417349590245853</v>
+        <v>0.6965944272445821</v>
       </c>
       <c r="K292" t="n">
-        <v>0.2854287427543474</v>
+        <v>0.2058823529411765</v>
       </c>
       <c r="L292" t="n">
-        <v>0.2728362982210674</v>
+        <v>0.09752321981424149</v>
       </c>
       <c r="M292" t="n">
-        <v>0.07800043094160736</v>
+        <v>0.07936507936507931</v>
       </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O292" t="n">
-        <v>0.3641919878950581</v>
+        <v>0.6290267712561337</v>
       </c>
       <c r="P292" t="n">
-        <v>0.3644408345692408</v>
+        <v>0.3258733632977319</v>
       </c>
       <c r="Q292" t="n">
-        <v>0.2713671775357012</v>
+        <v>0.04509986544613449</v>
       </c>
       <c r="R292" t="n">
         <v>1</v>
       </c>
       <c r="S292" t="n">
-        <v>0.07901209181489338</v>
+        <v>-0.06756765598844838</v>
       </c>
       <c r="T292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U292" t="n">
-        <v>0.07901209181489338</v>
+        <v>-0.06756765598844838</v>
       </c>
       <c r="V292" t="n">
-        <v>0.3644408345692408</v>
+        <v>0.6290267712561337</v>
       </c>
       <c r="W292" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="X292" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y292" t="n">
-        <v>6.476469765863448</v>
+        <v>5.154072736536484</v>
       </c>
       <c r="Z292" t="n">
-        <v>6.476469765863448</v>
+        <v>5.154072736536484</v>
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr"/>
@@ -39630,98 +39630,98 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B293" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45532.6875</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F293" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G293" t="n">
-        <v>2.7</v>
+        <v>1.65</v>
       </c>
       <c r="H293" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I293" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="J293" t="n">
-        <v>0.3425692695214105</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="K293" t="n">
-        <v>0.2720403022670025</v>
+        <v>0.2661290322580645</v>
       </c>
       <c r="L293" t="n">
-        <v>0.3853904282115869</v>
+        <v>0.1693548387096774</v>
       </c>
       <c r="M293" t="n">
-        <v>0.08115468409586057</v>
+        <v>0.07359307359307365</v>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O293" t="n">
-        <v>0.3014186925256958</v>
+        <v>0.5720953040503188</v>
       </c>
       <c r="P293" t="n">
-        <v>0.3995571376651378</v>
+        <v>0.3120385940186546</v>
       </c>
       <c r="Q293" t="n">
-        <v>0.2990241698091664</v>
+        <v>0.1158661019310265</v>
       </c>
       <c r="R293" t="n">
         <v>1</v>
       </c>
       <c r="S293" t="n">
-        <v>0.1275168353981353</v>
+        <v>0.007579175018060824</v>
       </c>
       <c r="T293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U293" t="n">
-        <v>0.1275168353981353</v>
+        <v>0.007579175018060824</v>
       </c>
       <c r="V293" t="n">
-        <v>0.3995571376651378</v>
+        <v>0.5720953040503188</v>
       </c>
       <c r="W293" t="n">
-        <v>3.4</v>
+        <v>1.65</v>
       </c>
       <c r="X293" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y293" t="n">
-        <v>7.697724939491898</v>
+        <v>5.321285820086639</v>
       </c>
       <c r="Z293" t="n">
-        <v>7.697724939491898</v>
+        <v>5.321285820086639</v>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr"/>
@@ -39773,98 +39773,98 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B294" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45533.58333333334</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F294" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G294" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="H294" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="I294" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="J294" t="n">
-        <v>0.6207739668538242</v>
+        <v>0.5977796754910334</v>
       </c>
       <c r="K294" t="n">
-        <v>0.2121814020655104</v>
+        <v>0.2234557358383149</v>
       </c>
       <c r="L294" t="n">
-        <v>0.1670446310806654</v>
+        <v>0.1787645886706519</v>
       </c>
       <c r="M294" t="n">
-        <v>0.08844073971094746</v>
+        <v>0.06551410373066413</v>
       </c>
       <c r="N294" t="n">
         <v>1</v>
       </c>
       <c r="O294" t="n">
-        <v>0.4924294811901441</v>
+        <v>0.4204619463354065</v>
       </c>
       <c r="P294" t="n">
-        <v>0.4422684721013385</v>
+        <v>0.4135484493303611</v>
       </c>
       <c r="Q294" t="n">
-        <v>0.06530204670851754</v>
+        <v>0.1659896043342324</v>
       </c>
       <c r="R294" t="n">
         <v>1</v>
       </c>
       <c r="S294" t="n">
-        <v>-0.1283444856636802</v>
+        <v>-0.1773177291556269</v>
       </c>
       <c r="T294" t="n">
         <v>1</v>
       </c>
       <c r="U294" t="n">
-        <v>-0.1283444856636802</v>
+        <v>-0.1773177291556269</v>
       </c>
       <c r="V294" t="n">
-        <v>0.4924294811901441</v>
+        <v>0.4204619463354065</v>
       </c>
       <c r="W294" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="X294" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y294" t="n">
-        <v>5.317329812114272</v>
+        <v>2.232011105947279</v>
       </c>
       <c r="Z294" t="n">
-        <v>5.317329812114272</v>
+        <v>2.232011105947279</v>
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr"/>
@@ -39916,98 +39916,98 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B295" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45533.6875</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F295" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G295" t="n">
-        <v>1.48</v>
+        <v>7</v>
       </c>
       <c r="H295" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="I295" t="n">
-        <v>5.75</v>
+        <v>1.4</v>
       </c>
       <c r="J295" t="n">
-        <v>0.6253155146562052</v>
+        <v>0.1338028169014084</v>
       </c>
       <c r="K295" t="n">
-        <v>0.213733709397502</v>
+        <v>0.1971830985915493</v>
       </c>
       <c r="L295" t="n">
-        <v>0.1609507759462928</v>
+        <v>0.6690140845070423</v>
       </c>
       <c r="M295" t="n">
-        <v>0.08053560137102656</v>
+        <v>0.06766917293233088</v>
       </c>
       <c r="N295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O295" t="n">
-        <v>0.4491487214532782</v>
+        <v>0.1095442695736866</v>
       </c>
       <c r="P295" t="n">
-        <v>0.3811947650146074</v>
+        <v>0.3716008263317628</v>
       </c>
       <c r="Q295" t="n">
-        <v>0.1696565135321142</v>
+        <v>0.5188549040945507</v>
       </c>
       <c r="R295" t="n">
         <v>1</v>
       </c>
       <c r="S295" t="n">
-        <v>-0.1761667932029269</v>
+        <v>-0.1501591804124915</v>
       </c>
       <c r="T295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U295" t="n">
-        <v>-0.1761667932029269</v>
+        <v>-0.1501591804124915</v>
       </c>
       <c r="V295" t="n">
-        <v>0.4491487214532782</v>
+        <v>0.5188549040945507</v>
       </c>
       <c r="W295" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="X295" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y295" t="n">
-        <v>3.986802430995884</v>
+        <v>3.384546667483164</v>
       </c>
       <c r="Z295" t="n">
-        <v>3.986802430995884</v>
+        <v>3.384546667483164</v>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr"/>
@@ -40059,98 +40059,74 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45535.5</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F296" t="n">
-        <v>771</v>
-      </c>
-      <c r="G296" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H296" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I296" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J296" t="n">
-        <v>0.4482827877083752</v>
-      </c>
-      <c r="K296" t="n">
-        <v>0.2964450692910223</v>
-      </c>
-      <c r="L296" t="n">
-        <v>0.2552721430006025</v>
-      </c>
-      <c r="M296" t="n">
-        <v>0.08816330098784864</v>
-      </c>
+        <v>1481</v>
+      </c>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
       <c r="N296" t="n">
         <v>1</v>
       </c>
       <c r="O296" t="n">
-        <v>0.4286117247174239</v>
+        <v>0.6026128975196423</v>
       </c>
       <c r="P296" t="n">
-        <v>0.3710820883539895</v>
+        <v>0.3283962066268059</v>
       </c>
       <c r="Q296" t="n">
-        <v>0.2003061869285866</v>
+        <v>0.06899089585355157</v>
       </c>
       <c r="R296" t="n">
         <v>1</v>
       </c>
-      <c r="S296" t="n">
-        <v>-0.01967106299095134</v>
-      </c>
+      <c r="S296" t="inlineStr"/>
       <c r="T296" t="n">
-        <v>1</v>
-      </c>
-      <c r="U296" t="n">
-        <v>-0.01967106299095134</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U296" t="inlineStr"/>
       <c r="V296" t="n">
-        <v>0.4286117247174239</v>
-      </c>
-      <c r="W296" t="n">
-        <v>2.05</v>
-      </c>
+        <v>0.3973871024803577</v>
+      </c>
+      <c r="W296" t="inlineStr"/>
       <c r="X296" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y296" t="n">
-        <v>5.972430610164642</v>
-      </c>
-      <c r="Z296" t="n">
-        <v>5.972430610164642</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr"/>
+      <c r="Z296" t="inlineStr"/>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr"/>
@@ -40202,98 +40178,74 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B297" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F297" t="n">
-        <v>771</v>
-      </c>
-      <c r="G297" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H297" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I297" t="n">
-        <v>4</v>
-      </c>
-      <c r="J297" t="n">
-        <v>0.4916847433116414</v>
-      </c>
-      <c r="K297" t="n">
-        <v>0.274765003615329</v>
-      </c>
-      <c r="L297" t="n">
-        <v>0.2335502530730297</v>
-      </c>
-      <c r="M297" t="n">
-        <v>0.07043343653250767</v>
-      </c>
+        <v>1481</v>
+      </c>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
       <c r="N297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O297" t="n">
-        <v>0.4444813455119924</v>
+        <v>0.2605763425862341</v>
       </c>
       <c r="P297" t="n">
-        <v>0.3979370637554646</v>
+        <v>0.3573867830214352</v>
       </c>
       <c r="Q297" t="n">
-        <v>0.1575815907325429</v>
+        <v>0.3820368743923306</v>
       </c>
       <c r="R297" t="n">
         <v>1</v>
       </c>
-      <c r="S297" t="n">
-        <v>-0.04720339779964899</v>
-      </c>
+      <c r="S297" t="inlineStr"/>
       <c r="T297" t="n">
-        <v>1</v>
-      </c>
-      <c r="U297" t="n">
-        <v>-0.04720339779964899</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U297" t="inlineStr"/>
       <c r="V297" t="n">
-        <v>0.4444813455119924</v>
-      </c>
-      <c r="W297" t="n">
-        <v>1.9</v>
-      </c>
+        <v>0.6179631256076694</v>
+      </c>
+      <c r="W297" t="inlineStr"/>
       <c r="X297" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y297" t="n">
-        <v>5.802100885843487</v>
-      </c>
-      <c r="Z297" t="n">
-        <v>5.802100885843487</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr"/>
+      <c r="Z297" t="inlineStr"/>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr"/>
@@ -40345,98 +40297,74 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B298" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45535.59375</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F298" t="n">
-        <v>771</v>
-      </c>
-      <c r="G298" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H298" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I298" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J298" t="n">
-        <v>0.5080174927113702</v>
-      </c>
-      <c r="K298" t="n">
-        <v>0.2689504373177842</v>
-      </c>
-      <c r="L298" t="n">
-        <v>0.2230320699708455</v>
-      </c>
-      <c r="M298" t="n">
-        <v>0.09357564163876941</v>
-      </c>
+        <v>1481</v>
+      </c>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
       <c r="N298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O298" t="n">
-        <v>0.4233629189166165</v>
+        <v>0.2907810647806508</v>
       </c>
       <c r="P298" t="n">
-        <v>0.366992783464725</v>
+        <v>0.382296953048974</v>
       </c>
       <c r="Q298" t="n">
-        <v>0.2096442976186587</v>
+        <v>0.3269219821703752</v>
       </c>
       <c r="R298" t="n">
         <v>1</v>
       </c>
-      <c r="S298" t="n">
-        <v>-0.08465457379475366</v>
-      </c>
+      <c r="S298" t="inlineStr"/>
       <c r="T298" t="n">
-        <v>1</v>
-      </c>
-      <c r="U298" t="n">
-        <v>-0.08465457379475366</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U298" t="inlineStr"/>
       <c r="V298" t="n">
-        <v>0.4233629189166165</v>
-      </c>
-      <c r="W298" t="n">
-        <v>1.8</v>
-      </c>
+        <v>0.617703046951026</v>
+      </c>
+      <c r="W298" t="inlineStr"/>
       <c r="X298" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y298" t="n">
-        <v>4.946713001792631</v>
-      </c>
-      <c r="Z298" t="n">
-        <v>4.946713001792631</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr"/>
+      <c r="Z298" t="inlineStr"/>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr"/>
@@ -40488,20 +40416,20 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B299" s="2" t="n">
-        <v>45529.5</v>
+        <v>45535.6875</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -40510,68 +40438,44 @@
       <c r="F299" t="n">
         <v>1481</v>
       </c>
-      <c r="G299" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H299" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I299" t="n">
-        <v>15</v>
-      </c>
-      <c r="J299" t="n">
-        <v>0.8103727714748785</v>
-      </c>
-      <c r="K299" t="n">
-        <v>0.126418152350081</v>
-      </c>
-      <c r="L299" t="n">
-        <v>0.06320907617504051</v>
-      </c>
-      <c r="M299" t="n">
-        <v>0.05470085470085473</v>
-      </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
       <c r="N299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O299" t="n">
-        <v>0.6663278450323864</v>
+        <v>0.2685651950715203</v>
       </c>
       <c r="P299" t="n">
-        <v>0.3050264638899211</v>
+        <v>0.3112031543727618</v>
       </c>
       <c r="Q299" t="n">
-        <v>0.0286456910776924</v>
+        <v>0.4202316505557179</v>
       </c>
       <c r="R299" t="n">
         <v>1</v>
       </c>
-      <c r="S299" t="n">
-        <v>-0.1440449264424921</v>
-      </c>
+      <c r="S299" t="inlineStr"/>
       <c r="T299" t="n">
-        <v>1</v>
-      </c>
-      <c r="U299" t="n">
-        <v>-0.1440449264424921</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U299" t="inlineStr"/>
       <c r="V299" t="n">
-        <v>0.6663278450323864</v>
-      </c>
-      <c r="W299" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0.5797683494442821</v>
+      </c>
+      <c r="W299" t="inlineStr"/>
       <c r="X299" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y299" t="n">
-        <v>4.794443759594989</v>
-      </c>
-      <c r="Z299" t="n">
-        <v>4.794443759594989</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr"/>
+      <c r="Z299" t="inlineStr"/>
       <c r="AA299" t="inlineStr">
         <is>
           <t>spain</t>
@@ -40631,20 +40535,20 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B300" s="2" t="n">
-        <v>45529.58333333334</v>
+        <v>45535.6875</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -40653,68 +40557,44 @@
       <c r="F300" t="n">
         <v>1481</v>
       </c>
-      <c r="G300" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H300" t="n">
-        <v>3</v>
-      </c>
-      <c r="I300" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J300" t="n">
-        <v>0.4210526315789474</v>
-      </c>
-      <c r="K300" t="n">
-        <v>0.3157894736842106</v>
-      </c>
-      <c r="L300" t="n">
-        <v>0.2631578947368421</v>
-      </c>
-      <c r="M300" t="n">
-        <v>0.05555555555555536</v>
-      </c>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
       <c r="N300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O300" t="n">
-        <v>0.3872285443819356</v>
+        <v>0.2203699945418482</v>
       </c>
       <c r="P300" t="n">
-        <v>0.3413351593230441</v>
+        <v>0.3530669975460241</v>
       </c>
       <c r="Q300" t="n">
-        <v>0.2714362962950203</v>
+        <v>0.4265630079121276</v>
       </c>
       <c r="R300" t="n">
         <v>1</v>
       </c>
-      <c r="S300" t="n">
-        <v>-0.0338240871970118</v>
-      </c>
+      <c r="S300" t="inlineStr"/>
       <c r="T300" t="n">
-        <v>1</v>
-      </c>
-      <c r="U300" t="n">
-        <v>-0.0338240871970118</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U300" t="inlineStr"/>
       <c r="V300" t="n">
-        <v>0.3872285443819356</v>
-      </c>
-      <c r="W300" t="n">
-        <v>2.25</v>
-      </c>
+        <v>0.5734369920878724</v>
+      </c>
+      <c r="W300" t="inlineStr"/>
       <c r="X300" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y300" t="n">
-        <v>3.244176162103757</v>
-      </c>
-      <c r="Z300" t="n">
-        <v>3.244176162103757</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr"/>
+      <c r="Z300" t="inlineStr"/>
       <c r="AA300" t="inlineStr">
         <is>
           <t>spain</t>
@@ -40774,11 +40654,11 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B301" s="2" t="n">
-        <v>45529.59375</v>
+        <v>45536.5</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -40787,7 +40667,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -40796,68 +40676,44 @@
       <c r="F301" t="n">
         <v>1481</v>
       </c>
-      <c r="G301" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H301" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I301" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J301" t="n">
-        <v>0.3875</v>
-      </c>
-      <c r="K301" t="n">
-        <v>0.30625</v>
-      </c>
-      <c r="L301" t="n">
-        <v>0.30625</v>
-      </c>
-      <c r="M301" t="n">
-        <v>0.05332455562870297</v>
-      </c>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
       <c r="N301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O301" t="n">
-        <v>0.3263919874412956</v>
+        <v>0.3834002009856136</v>
       </c>
       <c r="P301" t="n">
-        <v>0.3664227486918926</v>
+        <v>0.307801111427575</v>
       </c>
       <c r="Q301" t="n">
-        <v>0.3071852638668119</v>
+        <v>0.3087986875868114</v>
       </c>
       <c r="R301" t="n">
         <v>1</v>
       </c>
-      <c r="S301" t="n">
-        <v>0.0601727486918926</v>
-      </c>
+      <c r="S301" t="inlineStr"/>
       <c r="T301" t="n">
-        <v>0</v>
-      </c>
-      <c r="U301" t="n">
-        <v>0.0601727486918926</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U301" t="inlineStr"/>
       <c r="V301" t="n">
-        <v>0.3664227486918926</v>
-      </c>
-      <c r="W301" t="n">
-        <v>3.1</v>
-      </c>
+        <v>0.6165997990143864</v>
+      </c>
+      <c r="W301" t="inlineStr"/>
       <c r="X301" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y301" t="n">
-        <v>3.916054014986857</v>
-      </c>
-      <c r="Z301" t="n">
-        <v>3.916054014986857</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr"/>
+      <c r="Z301" t="inlineStr"/>
       <c r="AA301" t="inlineStr">
         <is>
           <t>spain</t>
@@ -40917,20 +40773,20 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B302" s="2" t="n">
-        <v>45529.6875</v>
+        <v>45536.5</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -40939,68 +40795,44 @@
       <c r="F302" t="n">
         <v>1481</v>
       </c>
-      <c r="G302" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H302" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I302" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J302" t="n">
-        <v>0.6174990513369328</v>
-      </c>
-      <c r="K302" t="n">
-        <v>0.2181925054377615</v>
-      </c>
-      <c r="L302" t="n">
-        <v>0.1643084432253056</v>
-      </c>
-      <c r="M302" t="n">
-        <v>0.05845469693718108</v>
-      </c>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+      <c r="J302" t="inlineStr"/>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
       <c r="N302" t="n">
         <v>1</v>
       </c>
       <c r="O302" t="n">
-        <v>0.5797813497031056</v>
+        <v>0.4448472741261926</v>
       </c>
       <c r="P302" t="n">
-        <v>0.3294347399719734</v>
+        <v>0.3287877790099757</v>
       </c>
       <c r="Q302" t="n">
-        <v>0.09078391032492103</v>
+        <v>0.2263649468638317</v>
       </c>
       <c r="R302" t="n">
         <v>1</v>
       </c>
-      <c r="S302" t="n">
-        <v>-0.03771770163382726</v>
-      </c>
+      <c r="S302" t="inlineStr"/>
       <c r="T302" t="n">
-        <v>1</v>
-      </c>
-      <c r="U302" t="n">
-        <v>-0.03771770163382726</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U302" t="inlineStr"/>
       <c r="V302" t="n">
-        <v>0.5797813497031056</v>
-      </c>
-      <c r="W302" t="n">
-        <v>1.53</v>
-      </c>
+        <v>0.5551527258738074</v>
+      </c>
+      <c r="W302" t="inlineStr"/>
       <c r="X302" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y302" t="n">
-        <v>4.976026560098441</v>
-      </c>
-      <c r="Z302" t="n">
-        <v>4.976026560098441</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr"/>
+      <c r="Z302" t="inlineStr"/>
       <c r="AA302" t="inlineStr">
         <is>
           <t>spain</t>
@@ -41060,20 +40892,20 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B303" s="2" t="n">
-        <v>45530.6875</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -41082,68 +40914,44 @@
       <c r="F303" t="n">
         <v>1481</v>
       </c>
-      <c r="G303" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H303" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I303" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J303" t="n">
-        <v>0.4844031193761248</v>
-      </c>
-      <c r="K303" t="n">
-        <v>0.2721205758848231</v>
-      </c>
-      <c r="L303" t="n">
-        <v>0.2434763047390522</v>
-      </c>
-      <c r="M303" t="n">
-        <v>0.08083575121974929</v>
-      </c>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr"/>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
       <c r="N303" t="n">
         <v>1</v>
       </c>
       <c r="O303" t="n">
-        <v>0.5016740642422536</v>
+        <v>0.4690429896587899</v>
       </c>
       <c r="P303" t="n">
-        <v>0.3597433105455177</v>
+        <v>0.3287270855983357</v>
       </c>
       <c r="Q303" t="n">
-        <v>0.1385826252122287</v>
+        <v>0.2022299247428744</v>
       </c>
       <c r="R303" t="n">
         <v>1</v>
       </c>
-      <c r="S303" t="n">
-        <v>0.01727094486612873</v>
-      </c>
+      <c r="S303" t="inlineStr"/>
       <c r="T303" t="n">
-        <v>1</v>
-      </c>
-      <c r="U303" t="n">
-        <v>0.01727094486612873</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U303" t="inlineStr"/>
       <c r="V303" t="n">
-        <v>0.5016740642422536</v>
-      </c>
-      <c r="W303" t="n">
-        <v>1.91</v>
-      </c>
+        <v>0.5309570103412101</v>
+      </c>
+      <c r="W303" t="inlineStr"/>
       <c r="X303" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y303" t="n">
-        <v>4.763802475505256</v>
-      </c>
-      <c r="Z303" t="n">
-        <v>4.763802475505256</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr"/>
+      <c r="Z303" t="inlineStr"/>
       <c r="AA303" t="inlineStr">
         <is>
           <t>spain</t>
@@ -41203,20 +41011,20 @@
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B304" s="2" t="n">
-        <v>45531.58333333334</v>
+        <v>45536.59375</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -41225,68 +41033,44 @@
       <c r="F304" t="n">
         <v>1481</v>
       </c>
-      <c r="G304" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H304" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I304" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J304" t="n">
-        <v>0.4243156199677939</v>
-      </c>
-      <c r="K304" t="n">
-        <v>0.3011272141706924</v>
-      </c>
-      <c r="L304" t="n">
-        <v>0.2745571658615137</v>
-      </c>
-      <c r="M304" t="n">
-        <v>0.07124374676556844</v>
-      </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
       <c r="N304" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O304" t="n">
-        <v>0.2500778026122632</v>
+        <v>0.3131008911554063</v>
       </c>
       <c r="P304" t="n">
-        <v>0.3726256843748756</v>
+        <v>0.3965117246275363</v>
       </c>
       <c r="Q304" t="n">
-        <v>0.3772965130128611</v>
+        <v>0.2903873842170576</v>
       </c>
       <c r="R304" t="n">
         <v>1</v>
       </c>
-      <c r="S304" t="n">
-        <v>0.1027393471513474</v>
-      </c>
+      <c r="S304" t="inlineStr"/>
       <c r="T304" t="n">
-        <v>2</v>
-      </c>
-      <c r="U304" t="n">
-        <v>0.1027393471513474</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U304" t="inlineStr"/>
       <c r="V304" t="n">
-        <v>0.3772965130128611</v>
-      </c>
-      <c r="W304" t="n">
-        <v>3.4</v>
-      </c>
+        <v>0.6034882753724637</v>
+      </c>
+      <c r="W304" t="inlineStr"/>
       <c r="X304" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y304" t="n">
-        <v>4.406624938759072</v>
-      </c>
-      <c r="Z304" t="n">
-        <v>4.406624938759072</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y304" t="inlineStr"/>
+      <c r="Z304" t="inlineStr"/>
       <c r="AA304" t="inlineStr">
         <is>
           <t>spain</t>
@@ -41346,20 +41130,20 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B305" s="2" t="n">
-        <v>45531.6875</v>
+        <v>45536.6875</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -41368,68 +41152,44 @@
       <c r="F305" t="n">
         <v>1481</v>
       </c>
-      <c r="G305" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H305" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I305" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J305" t="n">
-        <v>0.2069849407241269</v>
-      </c>
-      <c r="K305" t="n">
-        <v>0.2451137455943608</v>
-      </c>
-      <c r="L305" t="n">
-        <v>0.5479013136815124</v>
-      </c>
-      <c r="M305" t="n">
-        <v>0.07361541107671132</v>
-      </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+      <c r="J305" t="inlineStr"/>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
       <c r="N305" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O305" t="n">
-        <v>0.1928398026552932</v>
+        <v>0.6619200644201436</v>
       </c>
       <c r="P305" t="n">
-        <v>0.3569110152498295</v>
+        <v>0.2801399281488614</v>
       </c>
       <c r="Q305" t="n">
-        <v>0.4502491820948773</v>
+        <v>0.05794000743099485</v>
       </c>
       <c r="R305" t="n">
         <v>1</v>
       </c>
-      <c r="S305" t="n">
-        <v>-0.0976521315866351</v>
-      </c>
+      <c r="S305" t="inlineStr"/>
       <c r="T305" t="n">
-        <v>2</v>
-      </c>
-      <c r="U305" t="n">
-        <v>-0.0976521315866351</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U305" t="inlineStr"/>
       <c r="V305" t="n">
-        <v>0.4502491820948773</v>
-      </c>
-      <c r="W305" t="n">
-        <v>1.7</v>
-      </c>
+        <v>0.3380799355798564</v>
+      </c>
+      <c r="W305" t="inlineStr"/>
       <c r="X305" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y305" t="n">
-        <v>3.236764344170054</v>
-      </c>
-      <c r="Z305" t="n">
-        <v>3.236764344170054</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr"/>
+      <c r="Z305" t="inlineStr"/>
       <c r="AA305" t="inlineStr">
         <is>
           <t>spain</t>
@@ -41489,78 +41249,78 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B306" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45529.5625</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F306" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G306" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="H306" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="I306" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="J306" t="n">
-        <v>0.607741694196846</v>
+        <v>0.6658656253129068</v>
       </c>
       <c r="K306" t="n">
-        <v>0.2415383656423362</v>
+        <v>0.1990587764093321</v>
       </c>
       <c r="L306" t="n">
-        <v>0.1507199401608178</v>
+        <v>0.1350755982777611</v>
       </c>
       <c r="M306" t="n">
-        <v>0.06157154673283705</v>
+        <v>0.05760881075929269</v>
       </c>
       <c r="N306" t="n">
         <v>1</v>
       </c>
       <c r="O306" t="n">
-        <v>0.532728437829796</v>
+        <v>0.6299941404289507</v>
       </c>
       <c r="P306" t="n">
-        <v>0.335739327206231</v>
+        <v>0.2625197467596195</v>
       </c>
       <c r="Q306" t="n">
-        <v>0.131532234963973</v>
+        <v>0.1074861128114303</v>
       </c>
       <c r="R306" t="n">
         <v>1</v>
       </c>
       <c r="S306" t="n">
-        <v>-0.07501325636705003</v>
+        <v>-0.03587148488395608</v>
       </c>
       <c r="T306" t="n">
         <v>1</v>
       </c>
       <c r="U306" t="n">
-        <v>-0.07501325636705003</v>
+        <v>-0.03587148488395608</v>
       </c>
       <c r="V306" t="n">
-        <v>0.532728437829796</v>
+        <v>0.6299941404289507</v>
       </c>
       <c r="W306" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="X306" t="inlineStr">
         <is>
@@ -41568,19 +41328,19 @@
         </is>
       </c>
       <c r="Y306" t="n">
-        <v>4.201725956040891</v>
+        <v>8.676946721777972</v>
       </c>
       <c r="Z306" t="n">
-        <v>4.201725956040891</v>
+        <v>8.676946721777972</v>
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr"/>
@@ -41632,78 +41392,78 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B307" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45529.5625</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F307" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G307" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="H307" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I307" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="J307" t="n">
-        <v>0.40822528363047</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="K307" t="n">
-        <v>0.3028768233387358</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="L307" t="n">
-        <v>0.2888978930307942</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="M307" t="n">
-        <v>0.0650555615492503</v>
+        <v>0.05106209150326801</v>
       </c>
       <c r="N307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O307" t="n">
-        <v>0.5850525782619274</v>
+        <v>0.3096268775847986</v>
       </c>
       <c r="P307" t="n">
-        <v>0.2922211885621182</v>
+        <v>0.3635790846516872</v>
       </c>
       <c r="Q307" t="n">
-        <v>0.1227262331759545</v>
+        <v>0.3267940377635143</v>
       </c>
       <c r="R307" t="n">
         <v>1</v>
       </c>
       <c r="S307" t="n">
-        <v>0.1768272946314574</v>
+        <v>0.06626077917170275</v>
       </c>
       <c r="T307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U307" t="n">
-        <v>0.1768272946314574</v>
+        <v>0.06626077917170275</v>
       </c>
       <c r="V307" t="n">
-        <v>0.5850525782619274</v>
+        <v>0.3635790846516872</v>
       </c>
       <c r="W307" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="X307" t="inlineStr">
         <is>
@@ -41711,19 +41471,19 @@
         </is>
       </c>
       <c r="Y307" t="n">
-        <v>6.993891762757316</v>
+        <v>6.277655905699413</v>
       </c>
       <c r="Z307" t="n">
-        <v>6.993891762757316</v>
+        <v>6.277655905699413</v>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr"/>
@@ -41775,78 +41535,78 @@
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B308" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45529.65625</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F308" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G308" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="H308" t="n">
         <v>4.5</v>
       </c>
       <c r="I308" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="J308" t="n">
-        <v>0.6965944272445821</v>
+        <v>0.6538661131292164</v>
       </c>
       <c r="K308" t="n">
-        <v>0.2058823529411765</v>
+        <v>0.210690192008303</v>
       </c>
       <c r="L308" t="n">
-        <v>0.09752321981424149</v>
+        <v>0.1354436948624805</v>
       </c>
       <c r="M308" t="n">
-        <v>0.07936507936507931</v>
+        <v>0.05473453749315826</v>
       </c>
       <c r="N308" t="n">
         <v>1</v>
       </c>
       <c r="O308" t="n">
-        <v>0.6290267712561337</v>
+        <v>0.4530604260846444</v>
       </c>
       <c r="P308" t="n">
-        <v>0.3258733632977319</v>
+        <v>0.3271292930905851</v>
       </c>
       <c r="Q308" t="n">
-        <v>0.04509986544613449</v>
+        <v>0.2198102808247704</v>
       </c>
       <c r="R308" t="n">
         <v>1</v>
       </c>
       <c r="S308" t="n">
-        <v>-0.06756765598844838</v>
+        <v>-0.200805687044572</v>
       </c>
       <c r="T308" t="n">
         <v>1</v>
       </c>
       <c r="U308" t="n">
-        <v>-0.06756765598844838</v>
+        <v>-0.200805687044572</v>
       </c>
       <c r="V308" t="n">
-        <v>0.6290267712561337</v>
+        <v>0.4530604260846444</v>
       </c>
       <c r="W308" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="X308" t="inlineStr">
         <is>
@@ -41854,19 +41614,19 @@
         </is>
       </c>
       <c r="Y308" t="n">
-        <v>5.154072736536484</v>
+        <v>3.684089321520494</v>
       </c>
       <c r="Z308" t="n">
-        <v>5.154072736536484</v>
+        <v>3.684089321520494</v>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr"/>
@@ -41918,78 +41678,78 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B309" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45529.65625</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F309" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G309" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="H309" t="n">
         <v>3.5</v>
       </c>
       <c r="I309" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="J309" t="n">
-        <v>0.564516129032258</v>
+        <v>0.4984369572768322</v>
       </c>
       <c r="K309" t="n">
-        <v>0.2661290322580645</v>
+        <v>0.2705800625217089</v>
       </c>
       <c r="L309" t="n">
-        <v>0.1693548387096774</v>
+        <v>0.2309829802014589</v>
       </c>
       <c r="M309" t="n">
-        <v>0.07359307359307365</v>
+        <v>0.05593251421236012</v>
       </c>
       <c r="N309" t="n">
         <v>1</v>
       </c>
       <c r="O309" t="n">
-        <v>0.5720953040503188</v>
+        <v>0.5399574698548413</v>
       </c>
       <c r="P309" t="n">
-        <v>0.3120385940186546</v>
+        <v>0.3279534257770783</v>
       </c>
       <c r="Q309" t="n">
-        <v>0.1158661019310265</v>
+        <v>0.1320891043680803</v>
       </c>
       <c r="R309" t="n">
         <v>1</v>
       </c>
       <c r="S309" t="n">
-        <v>0.007579175018060824</v>
+        <v>0.04152051257800904</v>
       </c>
       <c r="T309" t="n">
         <v>1</v>
       </c>
       <c r="U309" t="n">
-        <v>0.007579175018060824</v>
+        <v>0.04152051257800904</v>
       </c>
       <c r="V309" t="n">
-        <v>0.5720953040503188</v>
+        <v>0.5399574698548413</v>
       </c>
       <c r="W309" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="X309" t="inlineStr">
         <is>
@@ -41997,19 +41757,19 @@
         </is>
       </c>
       <c r="Y309" t="n">
-        <v>5.321285820086639</v>
+        <v>8.492275839621946</v>
       </c>
       <c r="Z309" t="n">
-        <v>5.321285820086639</v>
+        <v>8.492275839621946</v>
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr"/>
@@ -42061,78 +41821,78 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B310" s="2" t="n">
-        <v>45533.58333333334</v>
+        <v>45530.5625</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F310" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G310" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="H310" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="I310" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="J310" t="n">
-        <v>0.5977796754910334</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="K310" t="n">
-        <v>0.2234557358383149</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="L310" t="n">
-        <v>0.1787645886706519</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="M310" t="n">
-        <v>0.06551410373066413</v>
+        <v>0.06442577030812324</v>
       </c>
       <c r="N310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O310" t="n">
-        <v>0.4204619463354065</v>
+        <v>0.3116787579932877</v>
       </c>
       <c r="P310" t="n">
-        <v>0.4135484493303611</v>
+        <v>0.5181862778996099</v>
       </c>
       <c r="Q310" t="n">
-        <v>0.1659896043342324</v>
+        <v>0.1701349641071023</v>
       </c>
       <c r="R310" t="n">
         <v>1</v>
       </c>
       <c r="S310" t="n">
-        <v>-0.1773177291556269</v>
+        <v>0.2418704884259257</v>
       </c>
       <c r="T310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U310" t="n">
-        <v>-0.1773177291556269</v>
+        <v>0.2418704884259257</v>
       </c>
       <c r="V310" t="n">
-        <v>0.4204619463354065</v>
+        <v>0.5181862778996099</v>
       </c>
       <c r="W310" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="X310" t="inlineStr">
         <is>
@@ -42140,19 +41900,19 @@
         </is>
       </c>
       <c r="Y310" t="n">
-        <v>2.232011105947279</v>
+        <v>11.10035445607421</v>
       </c>
       <c r="Z310" t="n">
-        <v>2.232011105947279</v>
+        <v>11.10035445607421</v>
       </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr"/>
@@ -42204,78 +41964,78 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B311" s="2" t="n">
-        <v>45533.6875</v>
+        <v>45530.65625</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F311" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G311" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H311" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="I311" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J311" t="n">
-        <v>0.1338028169014084</v>
+        <v>0.1889456293181136</v>
       </c>
       <c r="K311" t="n">
-        <v>0.1971830985915493</v>
+        <v>0.2553319315109642</v>
       </c>
       <c r="L311" t="n">
-        <v>0.6690140845070423</v>
+        <v>0.5557224391709222</v>
       </c>
       <c r="M311" t="n">
-        <v>0.06766917293233088</v>
+        <v>0.05850556438791732</v>
       </c>
       <c r="N311" t="n">
         <v>2</v>
       </c>
       <c r="O311" t="n">
-        <v>0.1095442695736866</v>
+        <v>0.267329570534093</v>
       </c>
       <c r="P311" t="n">
-        <v>0.3716008263317628</v>
+        <v>0.3127621238781438</v>
       </c>
       <c r="Q311" t="n">
-        <v>0.5188549040945507</v>
+        <v>0.4199083055877632</v>
       </c>
       <c r="R311" t="n">
         <v>1</v>
       </c>
       <c r="S311" t="n">
-        <v>-0.1501591804124915</v>
+        <v>-0.1358141335831591</v>
       </c>
       <c r="T311" t="n">
         <v>2</v>
       </c>
       <c r="U311" t="n">
-        <v>-0.1501591804124915</v>
+        <v>-0.1358141335831591</v>
       </c>
       <c r="V311" t="n">
-        <v>0.5188549040945507</v>
+        <v>0.4199083055877632</v>
       </c>
       <c r="W311" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="X311" t="inlineStr">
         <is>
@@ -42283,19 +42043,19 @@
         </is>
       </c>
       <c r="Y311" t="n">
-        <v>3.384546667483164</v>
+        <v>4.149092736061956</v>
       </c>
       <c r="Z311" t="n">
-        <v>3.384546667483164</v>
+        <v>4.149092736061956</v>
       </c>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr"/>
@@ -42347,74 +42107,98 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B312" s="2" t="n">
-        <v>45535.5</v>
+        <v>45534.5625</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F312" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
-      <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
-      <c r="M312" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G312" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H312" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I312" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J312" t="n">
+        <v>0.2560834298957126</v>
+      </c>
+      <c r="K312" t="n">
+        <v>0.2711471610660486</v>
+      </c>
+      <c r="L312" t="n">
+        <v>0.4727694090382387</v>
+      </c>
+      <c r="M312" t="n">
+        <v>0.08471593765711427</v>
+      </c>
       <c r="N312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O312" t="n">
-        <v>0.6026128975196423</v>
+        <v>0.1936345853165756</v>
       </c>
       <c r="P312" t="n">
-        <v>0.3283962066268059</v>
+        <v>0.4361463595751254</v>
       </c>
       <c r="Q312" t="n">
-        <v>0.06899089585355157</v>
+        <v>0.3702190551082988</v>
       </c>
       <c r="R312" t="n">
         <v>1</v>
       </c>
-      <c r="S312" t="inlineStr"/>
+      <c r="S312" t="n">
+        <v>0.1649991985090767</v>
+      </c>
       <c r="T312" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U312" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U312" t="n">
+        <v>0.1649991985090767</v>
+      </c>
       <c r="V312" t="n">
-        <v>0.3973871024803577</v>
-      </c>
-      <c r="W312" t="inlineStr"/>
+        <v>0.4361463595751254</v>
+      </c>
+      <c r="W312" t="n">
+        <v>3.4</v>
+      </c>
       <c r="X312" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y312" t="inlineStr"/>
-      <c r="Z312" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y312" t="n">
+        <v>8.77951367591818</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>8.77951367591818</v>
+      </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr"/>
@@ -42466,74 +42250,98 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B313" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45534.65625</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F313" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G313" t="inlineStr"/>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
-      <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
-      <c r="M313" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G313" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H313" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I313" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J313" t="n">
+        <v>0.528123658222413</v>
+      </c>
+      <c r="K313" t="n">
+        <v>0.2464577071704595</v>
+      </c>
+      <c r="L313" t="n">
+        <v>0.2254186346071276</v>
+      </c>
+      <c r="M313" t="n">
+        <v>0.08199767711962824</v>
+      </c>
       <c r="N313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O313" t="n">
-        <v>0.2605763425862341</v>
+        <v>0.3935526852620704</v>
       </c>
       <c r="P313" t="n">
-        <v>0.3573867830214352</v>
+        <v>0.371993721964238</v>
       </c>
       <c r="Q313" t="n">
-        <v>0.3820368743923306</v>
+        <v>0.2344535927736916</v>
       </c>
       <c r="R313" t="n">
         <v>1</v>
       </c>
-      <c r="S313" t="inlineStr"/>
+      <c r="S313" t="n">
+        <v>-0.1345709729603426</v>
+      </c>
       <c r="T313" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U313" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U313" t="n">
+        <v>-0.1345709729603426</v>
+      </c>
       <c r="V313" t="n">
-        <v>0.6179631256076694</v>
-      </c>
-      <c r="W313" t="inlineStr"/>
+        <v>0.3935526852620704</v>
+      </c>
+      <c r="W313" t="n">
+        <v>1.75</v>
+      </c>
       <c r="X313" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y313" t="inlineStr"/>
-      <c r="Z313" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y313" t="n">
+        <v>3.782334335484263</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>3.782334335484263</v>
+      </c>
       <c r="AA313" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr"/>
@@ -42585,74 +42393,98 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B314" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F314" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G314" t="inlineStr"/>
-      <c r="H314" t="inlineStr"/>
-      <c r="I314" t="inlineStr"/>
-      <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
-      <c r="M314" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G314" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H314" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I314" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J314" t="n">
+        <v>0.5961394175022167</v>
+      </c>
+      <c r="K314" t="n">
+        <v>0.2431621308232726</v>
+      </c>
+      <c r="L314" t="n">
+        <v>0.1606984516745106</v>
+      </c>
+      <c r="M314" t="n">
+        <v>0.08223222853768375</v>
+      </c>
       <c r="N314" t="n">
         <v>0</v>
       </c>
       <c r="O314" t="n">
-        <v>0.2907810647806508</v>
+        <v>0.4075709952077734</v>
       </c>
       <c r="P314" t="n">
-        <v>0.382296953048974</v>
+        <v>0.5033898896900657</v>
       </c>
       <c r="Q314" t="n">
-        <v>0.3269219821703752</v>
+        <v>0.08903911510216062</v>
       </c>
       <c r="R314" t="n">
         <v>1</v>
       </c>
-      <c r="S314" t="inlineStr"/>
+      <c r="S314" t="n">
+        <v>0.2602277588667931</v>
+      </c>
       <c r="T314" t="n">
         <v>0</v>
       </c>
-      <c r="U314" t="inlineStr"/>
+      <c r="U314" t="n">
+        <v>0.2602277588667931</v>
+      </c>
       <c r="V314" t="n">
-        <v>0.617703046951026</v>
-      </c>
-      <c r="W314" t="inlineStr"/>
+        <v>0.5033898896900657</v>
+      </c>
+      <c r="W314" t="n">
+        <v>3.8</v>
+      </c>
       <c r="X314" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y314" t="inlineStr"/>
-      <c r="Z314" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y314" t="n">
+        <v>11.15235985448032</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>11.15235985448032</v>
+      </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr"/>
@@ -42704,74 +42536,98 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B315" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45535.5625</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F315" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G315" t="inlineStr"/>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
-      <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr"/>
-      <c r="L315" t="inlineStr"/>
-      <c r="M315" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G315" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H315" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I315" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J315" t="n">
+        <v>0.4417349590245853</v>
+      </c>
+      <c r="K315" t="n">
+        <v>0.2854287427543474</v>
+      </c>
+      <c r="L315" t="n">
+        <v>0.2728362982210674</v>
+      </c>
+      <c r="M315" t="n">
+        <v>0.07800043094160736</v>
+      </c>
       <c r="N315" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O315" t="n">
-        <v>0.2685651950715203</v>
+        <v>0.4104221367688528</v>
       </c>
       <c r="P315" t="n">
-        <v>0.3112031543727618</v>
+        <v>0.4561838127363048</v>
       </c>
       <c r="Q315" t="n">
-        <v>0.4202316505557179</v>
+        <v>0.1333940504948426</v>
       </c>
       <c r="R315" t="n">
         <v>1</v>
       </c>
-      <c r="S315" t="inlineStr"/>
+      <c r="S315" t="n">
+        <v>0.1707550699819573</v>
+      </c>
       <c r="T315" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U315" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U315" t="n">
+        <v>0.1707550699819573</v>
+      </c>
       <c r="V315" t="n">
-        <v>0.5797683494442821</v>
-      </c>
-      <c r="W315" t="inlineStr"/>
+        <v>0.4561838127363048</v>
+      </c>
+      <c r="W315" t="n">
+        <v>3.25</v>
+      </c>
       <c r="X315" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y315" t="inlineStr"/>
-      <c r="Z315" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y315" t="n">
+        <v>9.156215862812502</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>9.156215862812502</v>
+      </c>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr"/>
@@ -42823,74 +42679,98 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B316" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45535.65625</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F316" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
-      <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
-      <c r="M316" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G316" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H316" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I316" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J316" t="n">
+        <v>0.3425692695214105</v>
+      </c>
+      <c r="K316" t="n">
+        <v>0.2720403022670025</v>
+      </c>
+      <c r="L316" t="n">
+        <v>0.3853904282115869</v>
+      </c>
+      <c r="M316" t="n">
+        <v>0.08115468409586057</v>
+      </c>
       <c r="N316" t="n">
         <v>2</v>
       </c>
       <c r="O316" t="n">
-        <v>0.2203699945418482</v>
+        <v>0.2701756319800689</v>
       </c>
       <c r="P316" t="n">
-        <v>0.3530669975460241</v>
+        <v>0.3158037836299356</v>
       </c>
       <c r="Q316" t="n">
-        <v>0.4265630079121276</v>
+        <v>0.4140205843899953</v>
       </c>
       <c r="R316" t="n">
         <v>1</v>
       </c>
-      <c r="S316" t="inlineStr"/>
+      <c r="S316" t="n">
+        <v>0.02863015617840836</v>
+      </c>
       <c r="T316" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U316" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U316" t="n">
+        <v>0.02863015617840836</v>
+      </c>
       <c r="V316" t="n">
-        <v>0.5734369920878724</v>
-      </c>
-      <c r="W316" t="inlineStr"/>
+        <v>0.4140205843899953</v>
+      </c>
+      <c r="W316" t="n">
+        <v>2.4</v>
+      </c>
       <c r="X316" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y316" t="inlineStr"/>
-      <c r="Z316" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y316" t="n">
+        <v>6.464754131862461</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>6.464754131862461</v>
+      </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr"/>
@@ -42942,74 +42822,98 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B317" s="2" t="n">
-        <v>45536.5</v>
+        <v>45535.65625</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F317" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G317" t="inlineStr"/>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr"/>
-      <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr"/>
-      <c r="L317" t="inlineStr"/>
-      <c r="M317" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G317" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H317" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I317" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0.6207739668538242</v>
+      </c>
+      <c r="K317" t="n">
+        <v>0.2121814020655104</v>
+      </c>
+      <c r="L317" t="n">
+        <v>0.1670446310806654</v>
+      </c>
+      <c r="M317" t="n">
+        <v>0.08844073971094746</v>
+      </c>
       <c r="N317" t="n">
         <v>1</v>
       </c>
       <c r="O317" t="n">
-        <v>0.3834002009856136</v>
+        <v>0.529849157913343</v>
       </c>
       <c r="P317" t="n">
-        <v>0.307801111427575</v>
+        <v>0.3184139663759257</v>
       </c>
       <c r="Q317" t="n">
-        <v>0.3087986875868114</v>
+        <v>0.1517368757107315</v>
       </c>
       <c r="R317" t="n">
         <v>1</v>
       </c>
-      <c r="S317" t="inlineStr"/>
+      <c r="S317" t="n">
+        <v>-0.09092480894048127</v>
+      </c>
       <c r="T317" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U317" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U317" t="n">
+        <v>-0.09092480894048127</v>
+      </c>
       <c r="V317" t="n">
-        <v>0.6165997990143864</v>
-      </c>
-      <c r="W317" t="inlineStr"/>
+        <v>0.529849157913343</v>
+      </c>
+      <c r="W317" t="n">
+        <v>1.48</v>
+      </c>
       <c r="X317" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y317" t="inlineStr"/>
-      <c r="Z317" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y317" t="n">
+        <v>6.410331528992118</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>6.410331528992118</v>
+      </c>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr"/>
@@ -43061,74 +42965,98 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B318" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.5625</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F318" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G318" t="inlineStr"/>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
-      <c r="J318" t="inlineStr"/>
-      <c r="K318" t="inlineStr"/>
-      <c r="L318" t="inlineStr"/>
-      <c r="M318" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G318" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H318" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I318" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0.6088400411164703</v>
+      </c>
+      <c r="K318" t="n">
+        <v>0.221791729263857</v>
+      </c>
+      <c r="L318" t="n">
+        <v>0.1693682296196727</v>
+      </c>
+      <c r="M318" t="n">
+        <v>0.07350819115524998</v>
+      </c>
       <c r="N318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O318" t="n">
-        <v>0.4448472741261926</v>
+        <v>0.37309299949497</v>
       </c>
       <c r="P318" t="n">
-        <v>0.3287877790099757</v>
+        <v>0.4350278896394806</v>
       </c>
       <c r="Q318" t="n">
-        <v>0.2263649468638317</v>
+        <v>0.1918791108655493</v>
       </c>
       <c r="R318" t="n">
         <v>1</v>
       </c>
-      <c r="S318" t="inlineStr"/>
+      <c r="S318" t="n">
+        <v>0.2132361603756235</v>
+      </c>
       <c r="T318" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U318" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U318" t="n">
+        <v>0.2132361603756235</v>
+      </c>
       <c r="V318" t="n">
-        <v>0.5551527258738074</v>
-      </c>
-      <c r="W318" t="inlineStr"/>
+        <v>0.4350278896394806</v>
+      </c>
+      <c r="W318" t="n">
+        <v>4.2</v>
+      </c>
       <c r="X318" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y318" t="inlineStr"/>
-      <c r="Z318" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y318" t="n">
+        <v>9.467662226186684</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>9.467662226186684</v>
+      </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr"/>
@@ -43180,74 +43108,98 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B319" s="2" t="n">
-        <v>45536.58333333334</v>
+        <v>45536.5625</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F319" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G319" t="inlineStr"/>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr"/>
-      <c r="J319" t="inlineStr"/>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
-      <c r="M319" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G319" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H319" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I319" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0.4482827877083752</v>
+      </c>
+      <c r="K319" t="n">
+        <v>0.2964450692910223</v>
+      </c>
+      <c r="L319" t="n">
+        <v>0.2552721430006025</v>
+      </c>
+      <c r="M319" t="n">
+        <v>0.08816330098784864</v>
+      </c>
       <c r="N319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O319" t="n">
-        <v>0.4690429896587899</v>
+        <v>0.3379584018994157</v>
       </c>
       <c r="P319" t="n">
-        <v>0.3287270855983357</v>
+        <v>0.4105416940307048</v>
       </c>
       <c r="Q319" t="n">
-        <v>0.2022299247428744</v>
+        <v>0.2514999040698795</v>
       </c>
       <c r="R319" t="n">
         <v>1</v>
       </c>
-      <c r="S319" t="inlineStr"/>
+      <c r="S319" t="n">
+        <v>0.1140966247396826</v>
+      </c>
       <c r="T319" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U319" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U319" t="n">
+        <v>0.1140966247396826</v>
+      </c>
       <c r="V319" t="n">
-        <v>0.5309570103412101</v>
-      </c>
-      <c r="W319" t="inlineStr"/>
+        <v>0.4105416940307048</v>
+      </c>
+      <c r="W319" t="n">
+        <v>3.1</v>
+      </c>
       <c r="X319" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y319" t="inlineStr"/>
-      <c r="Z319" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y319" t="n">
+        <v>7.662153088570553</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>7.662153088570553</v>
+      </c>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr"/>
@@ -43299,74 +43251,98 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B320" s="2" t="n">
-        <v>45536.59375</v>
+        <v>45536.65625</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F320" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
-      <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
-      <c r="M320" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G320" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H320" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I320" t="n">
+        <v>4</v>
+      </c>
+      <c r="J320" t="n">
+        <v>0.4916847433116414</v>
+      </c>
+      <c r="K320" t="n">
+        <v>0.274765003615329</v>
+      </c>
+      <c r="L320" t="n">
+        <v>0.2335502530730297</v>
+      </c>
+      <c r="M320" t="n">
+        <v>0.07043343653250767</v>
+      </c>
       <c r="N320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O320" t="n">
-        <v>0.3131008911554063</v>
+        <v>0.3737144766483231</v>
       </c>
       <c r="P320" t="n">
-        <v>0.3965117246275363</v>
+        <v>0.3732335341397709</v>
       </c>
       <c r="Q320" t="n">
-        <v>0.2903873842170576</v>
+        <v>0.2530519892119061</v>
       </c>
       <c r="R320" t="n">
         <v>1</v>
       </c>
-      <c r="S320" t="inlineStr"/>
+      <c r="S320" t="n">
+        <v>-0.1179702666633182</v>
+      </c>
       <c r="T320" t="n">
-        <v>0</v>
-      </c>
-      <c r="U320" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U320" t="n">
+        <v>-0.1179702666633182</v>
+      </c>
       <c r="V320" t="n">
-        <v>0.6034882753724637</v>
-      </c>
-      <c r="W320" t="inlineStr"/>
+        <v>0.3737144766483231</v>
+      </c>
+      <c r="W320" t="n">
+        <v>1.9</v>
+      </c>
       <c r="X320" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y320" t="inlineStr"/>
-      <c r="Z320" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y320" t="n">
+        <v>3.735051783890487</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>3.735051783890487</v>
+      </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr"/>
@@ -43418,74 +43394,98 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B321" s="2" t="n">
-        <v>45536.6875</v>
+        <v>45536.65625</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F321" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G321" t="inlineStr"/>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
-      <c r="M321" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G321" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H321" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I321" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J321" t="n">
+        <v>0.5080174927113702</v>
+      </c>
+      <c r="K321" t="n">
+        <v>0.2689504373177842</v>
+      </c>
+      <c r="L321" t="n">
+        <v>0.2230320699708455</v>
+      </c>
+      <c r="M321" t="n">
+        <v>0.09357564163876941</v>
+      </c>
       <c r="N321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O321" t="n">
-        <v>0.6619200644201436</v>
+        <v>0.4004031360012256</v>
       </c>
       <c r="P321" t="n">
-        <v>0.2801399281488614</v>
+        <v>0.440533898257623</v>
       </c>
       <c r="Q321" t="n">
-        <v>0.05794000743099485</v>
+        <v>0.1590629657411515</v>
       </c>
       <c r="R321" t="n">
         <v>1</v>
       </c>
-      <c r="S321" t="inlineStr"/>
+      <c r="S321" t="n">
+        <v>0.1715834609398388</v>
+      </c>
       <c r="T321" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U321" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U321" t="n">
+        <v>0.1715834609398388</v>
+      </c>
       <c r="V321" t="n">
-        <v>0.3380799355798564</v>
-      </c>
-      <c r="W321" t="inlineStr"/>
+        <v>0.440533898257623</v>
+      </c>
+      <c r="W321" t="n">
+        <v>3.4</v>
+      </c>
       <c r="X321" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="Y321" t="inlineStr"/>
-      <c r="Z321" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y321" t="n">
+        <v>8.939752866955878</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>8.939752866955878</v>
+      </c>
       <c r="AA321" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr"/>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -9843,9 +9843,7 @@
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
-      <c r="AD95" t="n">
-        <v>-0.03721448578066422</v>
-      </c>
+      <c r="AD95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -9945,9 +9943,7 @@
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
-      <c r="AD96" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="AD96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -10047,9 +10043,7 @@
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
-      <c r="AD97" t="n">
-        <v>0.02750504125801551</v>
-      </c>
+      <c r="AD97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -10149,9 +10143,7 @@
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
-      <c r="AD98" t="n">
-        <v>0.1438270766604026</v>
-      </c>
+      <c r="AD98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -10251,9 +10243,7 @@
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
-      <c r="AD99" t="n">
-        <v>0.1382933221609905</v>
-      </c>
+      <c r="AD99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -10353,9 +10343,7 @@
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
-      <c r="AD100" t="n">
-        <v>0.03866767769010454</v>
-      </c>
+      <c r="AD100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -10455,9 +10443,7 @@
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
-      <c r="AD101" t="n">
-        <v>-0.15</v>
-      </c>
+      <c r="AD101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -10557,9 +10543,7 @@
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
-      <c r="AD102" t="n">
-        <v>-0.02031536683348245</v>
-      </c>
+      <c r="AD102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -10659,9 +10643,7 @@
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
-      <c r="AD103" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="AD103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -10761,9 +10743,7 @@
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
-      <c r="AD104" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="AD104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -10863,9 +10843,7 @@
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
-      <c r="AD105" t="n">
-        <v>-0.0973109388294835</v>
-      </c>
+      <c r="AD105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -10965,9 +10943,7 @@
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
-      <c r="AD106" t="n">
-        <v>-0.114077909789345</v>
-      </c>
+      <c r="AD106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -11067,9 +11043,7 @@
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
-      <c r="AD107" t="n">
-        <v>0.09668380024054007</v>
-      </c>
+      <c r="AD107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -11169,9 +11143,7 @@
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
-      <c r="AD108" t="n">
-        <v>0.1348280654081961</v>
-      </c>
+      <c r="AD108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -11271,9 +11243,7 @@
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
-      <c r="AD109" t="n">
-        <v>0.1062599997429985</v>
-      </c>
+      <c r="AD109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -11373,9 +11343,7 @@
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
-      <c r="AD110" t="n">
-        <v>0.01676530014436484</v>
-      </c>
+      <c r="AD110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -11475,9 +11443,7 @@
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
-      <c r="AD111" t="n">
-        <v>-0.02661875682475789</v>
-      </c>
+      <c r="AD111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -11577,9 +11543,7 @@
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
-      <c r="AD112" t="n">
-        <v>0.03322870794303479</v>
-      </c>
+      <c r="AD112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -11679,9 +11643,7 @@
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
-      <c r="AD113" t="n">
-        <v>-0.07300246067568528</v>
-      </c>
+      <c r="AD113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -11781,9 +11743,7 @@
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
-      <c r="AD114" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="AD114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -11883,9 +11843,7 @@
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
-      <c r="AD115" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="AD115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -11985,9 +11943,7 @@
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
-      <c r="AD116" t="n">
-        <v>-0.05379582862154741</v>
-      </c>
+      <c r="AD116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -12087,9 +12043,7 @@
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
-      <c r="AD117" t="n">
-        <v>0.01521200981338677</v>
-      </c>
+      <c r="AD117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -12189,9 +12143,7 @@
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
-      <c r="AD118" t="n">
-        <v>-0.05342735586688685</v>
-      </c>
+      <c r="AD118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -12291,9 +12243,7 @@
         </is>
       </c>
       <c r="AC119" t="inlineStr"/>
-      <c r="AD119" t="n">
-        <v>0.005866453059369559</v>
-      </c>
+      <c r="AD119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -12393,9 +12343,7 @@
         </is>
       </c>
       <c r="AC120" t="inlineStr"/>
-      <c r="AD120" t="n">
-        <v>-0.1295815833400328</v>
-      </c>
+      <c r="AD120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -12495,9 +12443,7 @@
         </is>
       </c>
       <c r="AC121" t="inlineStr"/>
-      <c r="AD121" t="n">
-        <v>0.136174161489098</v>
-      </c>
+      <c r="AD121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -12597,9 +12543,7 @@
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
-      <c r="AD122" t="n">
-        <v>-0.1282913621669235</v>
-      </c>
+      <c r="AD122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -12699,9 +12643,7 @@
         </is>
       </c>
       <c r="AC123" t="inlineStr"/>
-      <c r="AD123" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="AD123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -12801,9 +12743,7 @@
         </is>
       </c>
       <c r="AC124" t="inlineStr"/>
-      <c r="AD124" t="n">
-        <v>-0.1495820083554838</v>
-      </c>
+      <c r="AD124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -12903,9 +12843,7 @@
         </is>
       </c>
       <c r="AC125" t="inlineStr"/>
-      <c r="AD125" t="n">
-        <v>0.1245917677014093</v>
-      </c>
+      <c r="AD125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -12957,28 +12895,28 @@
         <v>1</v>
       </c>
       <c r="O126" t="n">
-        <v>0.3992443537488397</v>
+        <v>0.3992443537488325</v>
       </c>
       <c r="P126" t="n">
-        <v>0.3843085722277485</v>
+        <v>0.3843085722277583</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.216447074023412</v>
+        <v>0.2164470740234089</v>
       </c>
       <c r="R126" t="n">
         <v>1</v>
       </c>
       <c r="S126" t="n">
-        <v>-0.1363261160498181</v>
+        <v>-0.1363261160498252</v>
       </c>
       <c r="T126" t="n">
         <v>1</v>
       </c>
       <c r="U126" t="n">
-        <v>-0.1363261160498181</v>
+        <v>-0.1363261160498252</v>
       </c>
       <c r="V126" t="n">
-        <v>0.3992443537488397</v>
+        <v>0.3992443537488325</v>
       </c>
       <c r="W126" t="n">
         <v>1.73</v>
@@ -12989,10 +12927,10 @@
         </is>
       </c>
       <c r="Y126" t="n">
-        <v>3.839825866605747</v>
+        <v>3.839825866605539</v>
       </c>
       <c r="Z126" t="n">
-        <v>3.839825866605747</v>
+        <v>3.839825866605539</v>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
@@ -13005,9 +12943,7 @@
         </is>
       </c>
       <c r="AC126" t="inlineStr"/>
-      <c r="AD126" t="n">
-        <v>-0.1363261160498181</v>
-      </c>
+      <c r="AD126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -13107,9 +13043,7 @@
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
-      <c r="AD127" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="AD127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -13209,9 +13143,7 @@
         </is>
       </c>
       <c r="AC128" t="inlineStr"/>
-      <c r="AD128" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="AD128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -13311,9 +13243,7 @@
         </is>
       </c>
       <c r="AC129" t="inlineStr"/>
-      <c r="AD129" t="n">
-        <v>0.02863015617840836</v>
-      </c>
+      <c r="AD129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -13413,9 +13343,7 @@
         </is>
       </c>
       <c r="AC130" t="inlineStr"/>
-      <c r="AD130" t="n">
-        <v>-0.09092480894048127</v>
-      </c>
+      <c r="AD130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -13515,9 +13443,7 @@
         </is>
       </c>
       <c r="AC131" t="inlineStr"/>
-      <c r="AD131" t="n">
-        <v>-0.1337314847539855</v>
-      </c>
+      <c r="AD131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -13617,9 +13543,7 @@
         </is>
       </c>
       <c r="AC132" t="inlineStr"/>
-      <c r="AD132" t="n">
-        <v>-0.04749455679634373</v>
-      </c>
+      <c r="AD132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -13719,9 +13643,7 @@
         </is>
       </c>
       <c r="AC133" t="inlineStr"/>
-      <c r="AD133" t="n">
-        <v>-0.1174528378092863</v>
-      </c>
+      <c r="AD133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -13821,9 +13743,7 @@
         </is>
       </c>
       <c r="AC134" t="inlineStr"/>
-      <c r="AD134" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="AD134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -13923,9 +13843,7 @@
         </is>
       </c>
       <c r="AC135" t="inlineStr"/>
-      <c r="AD135" t="n">
-        <v>0.008521401585363908</v>
-      </c>
+      <c r="AD135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -14025,9 +13943,7 @@
         </is>
       </c>
       <c r="AC136" t="inlineStr"/>
-      <c r="AD136" t="n">
-        <v>0.100125839458321</v>
-      </c>
+      <c r="AD136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -14127,9 +14043,7 @@
         </is>
       </c>
       <c r="AC137" t="inlineStr"/>
-      <c r="AD137" t="n">
-        <v>-0.09005305865534013</v>
-      </c>
+      <c r="AD137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -14229,9 +14143,7 @@
         </is>
       </c>
       <c r="AC138" t="inlineStr"/>
-      <c r="AD138" t="n">
-        <v>-0.07501354688794881</v>
-      </c>
+      <c r="AD138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -14283,28 +14195,28 @@
         <v>1</v>
       </c>
       <c r="O139" t="n">
-        <v>0.4687177755798147</v>
+        <v>0.4687177755798148</v>
       </c>
       <c r="P139" t="n">
-        <v>0.3442596753499815</v>
+        <v>0.3442596753499814</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.1870225490702038</v>
+        <v>0.1870225490702039</v>
       </c>
       <c r="R139" t="n">
         <v>1</v>
       </c>
       <c r="S139" t="n">
-        <v>0.0604924919493447</v>
+        <v>0.06049249194934475</v>
       </c>
       <c r="T139" t="n">
         <v>1</v>
       </c>
       <c r="U139" t="n">
-        <v>0.0604924919493447</v>
+        <v>0.06049249194934475</v>
       </c>
       <c r="V139" t="n">
-        <v>0.4687177755798147</v>
+        <v>0.4687177755798148</v>
       </c>
       <c r="W139" t="n">
         <v>2.3</v>
@@ -14331,9 +14243,7 @@
         </is>
       </c>
       <c r="AC139" t="inlineStr"/>
-      <c r="AD139" t="n">
-        <v>0.0604924919493447</v>
-      </c>
+      <c r="AD139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -14433,9 +14343,7 @@
         </is>
       </c>
       <c r="AC140" t="inlineStr"/>
-      <c r="AD140" t="n">
-        <v>-0.09327415049560084</v>
-      </c>
+      <c r="AD140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -14535,9 +14443,7 @@
         </is>
       </c>
       <c r="AC141" t="inlineStr"/>
-      <c r="AD141" t="n">
-        <v>0.02707816080800263</v>
-      </c>
+      <c r="AD141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -14637,9 +14543,7 @@
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
-      <c r="AD142" t="n">
-        <v>-0.15</v>
-      </c>
+      <c r="AD142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -14739,9 +14643,7 @@
         </is>
       </c>
       <c r="AC143" t="inlineStr"/>
-      <c r="AD143" t="n">
-        <v>-0.15</v>
-      </c>
+      <c r="AD143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -14779,13 +14681,13 @@
         <v>1</v>
       </c>
       <c r="O144" t="n">
-        <v>0.6568144180861284</v>
+        <v>0.6568144180861283</v>
       </c>
       <c r="P144" t="n">
-        <v>0.281495240464735</v>
+        <v>0.2814952404647352</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.06169034144913665</v>
+        <v>0.06169034144913662</v>
       </c>
       <c r="R144" t="n">
         <v>1</v>
@@ -14796,7 +14698,7 @@
       </c>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="n">
-        <v>0.3431855819138716</v>
+        <v>0.3431855819138717</v>
       </c>
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC153"/>
+  <dimension ref="A1:AC168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10145,98 +10145,98 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45535.35416666666</v>
+        <v>45534.65625</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F100" t="n">
-        <v>481</v>
+        <v>551</v>
       </c>
       <c r="G100" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="H100" t="n">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="I100" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="J100" t="n">
-        <v>0.7044320516583504</v>
+        <v>0.5399533013361008</v>
       </c>
       <c r="K100" t="n">
-        <v>0.1784561197534488</v>
+        <v>0.2524646517057984</v>
       </c>
       <c r="L100" t="n">
-        <v>0.1171118285882008</v>
+        <v>0.2075820469581009</v>
       </c>
       <c r="M100" t="n">
-        <v>0.06735588972431072</v>
+        <v>0.07052717457341728</v>
       </c>
       <c r="N100" t="n">
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>0.6628477424400651</v>
+        <v>0.4505903748520288</v>
       </c>
       <c r="P100" t="n">
-        <v>0.23756277683258</v>
+        <v>0.2988719079151199</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.09958948072735496</v>
+        <v>0.2505377172328513</v>
       </c>
       <c r="R100" t="n">
         <v>1</v>
       </c>
       <c r="S100" t="n">
-        <v>-0.04158430921828538</v>
+        <v>-0.08936292648407196</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>-0.04158430921828538</v>
+        <v>-0.08936292648407196</v>
       </c>
       <c r="V100" t="n">
-        <v>0.6628477424400651</v>
+        <v>0.4505903748520288</v>
       </c>
       <c r="W100" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y100" t="n">
-        <v>9.059073400882111</v>
+        <v>7.224548967359137</v>
       </c>
       <c r="Z100" t="n">
-        <v>9.059073400882111</v>
+        <v>7.224548967359137</v>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -10244,78 +10244,78 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45534.64583333334</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F101" t="n">
-        <v>481</v>
+        <v>591</v>
       </c>
       <c r="G101" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="H101" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="I101" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J101" t="n">
-        <v>0.5441860465116279</v>
+        <v>0.4803370786516853</v>
       </c>
       <c r="K101" t="n">
-        <v>0.244186046511628</v>
+        <v>0.2668539325842696</v>
       </c>
       <c r="L101" t="n">
-        <v>0.2116279069767442</v>
+        <v>0.2528089887640449</v>
       </c>
       <c r="M101" t="n">
-        <v>0.05006105006104988</v>
+        <v>0.04093567251461994</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.2695687867755708</v>
+        <v>0.6297801158206143</v>
       </c>
       <c r="P101" t="n">
-        <v>0.4381085430417852</v>
+        <v>0.2787482353976901</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.292322670182644</v>
+        <v>0.09147164878169556</v>
       </c>
       <c r="R101" t="n">
         <v>1</v>
       </c>
       <c r="S101" t="n">
-        <v>0.1939224965301572</v>
+        <v>0.149443037168929</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U101" t="n">
-        <v>0.1939224965301572</v>
+        <v>0.149443037168929</v>
       </c>
       <c r="V101" t="n">
-        <v>0.4381085430417852</v>
+        <v>0.6297801158206143</v>
       </c>
       <c r="W101" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -10323,19 +10323,19 @@
         </is>
       </c>
       <c r="Y101" t="n">
-        <v>7.84653422104285</v>
+        <v>2.762433692723559</v>
       </c>
       <c r="Z101" t="n">
-        <v>7.84653422104285</v>
+        <v>2.762433692723559</v>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -10343,98 +10343,98 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45534.5625</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="F102" t="n">
-        <v>481</v>
+        <v>771</v>
       </c>
       <c r="G102" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="H102" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
-        <v>0.3368721927317272</v>
+        <v>0.2591463414634146</v>
       </c>
       <c r="K102" t="n">
-        <v>0.2858309514087382</v>
+        <v>0.274390243902439</v>
       </c>
       <c r="L102" t="n">
-        <v>0.3772968558595345</v>
+        <v>0.4664634146341464</v>
       </c>
       <c r="M102" t="n">
-        <v>0.06017316017316032</v>
+        <v>0.07189542483660127</v>
       </c>
       <c r="N102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>0.3937602166575641</v>
+        <v>0.192076971736161</v>
       </c>
       <c r="P102" t="n">
-        <v>0.3135591315478707</v>
+        <v>0.440257744885126</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.292680651794565</v>
+        <v>0.3676652833787132</v>
       </c>
       <c r="R102" t="n">
         <v>1</v>
       </c>
       <c r="S102" t="n">
-        <v>0.05688802392583692</v>
+        <v>0.165867500982687</v>
       </c>
       <c r="T102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>0.05688802392583692</v>
+        <v>0.165867500982687</v>
       </c>
       <c r="V102" t="n">
-        <v>0.3937602166575641</v>
+        <v>0.440257744885126</v>
       </c>
       <c r="W102" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y102" t="n">
-        <v>6.571214835955183</v>
+        <v>2.196169694435367</v>
       </c>
       <c r="Z102" t="n">
-        <v>6.571214835955183</v>
+        <v>2.196169694435367</v>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -10442,98 +10442,98 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45534.65625</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="F103" t="n">
-        <v>481</v>
+        <v>771</v>
       </c>
       <c r="G103" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="H103" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="I103" t="n">
-        <v>2.35</v>
+        <v>4.75</v>
       </c>
       <c r="J103" t="n">
-        <v>0.3212510356255179</v>
+        <v>0.5693343167988197</v>
       </c>
       <c r="K103" t="n">
-        <v>0.2823115161557581</v>
+        <v>0.2364927162087406</v>
       </c>
       <c r="L103" t="n">
-        <v>0.3964374482187241</v>
+        <v>0.1941729669924396</v>
       </c>
       <c r="M103" t="n">
-        <v>0.07338980413081653</v>
+        <v>0.08422052281701409</v>
       </c>
       <c r="N103" t="n">
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>0.2838073991274223</v>
+        <v>0.3690156550322785</v>
       </c>
       <c r="P103" t="n">
-        <v>0.4200644398565816</v>
+        <v>0.4045176207318785</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.296128161015996</v>
+        <v>0.2264667242358431</v>
       </c>
       <c r="R103" t="n">
         <v>1</v>
       </c>
       <c r="S103" t="n">
-        <v>0.1377529237008235</v>
+        <v>0.168024904523138</v>
       </c>
       <c r="T103" t="n">
         <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>0.1377529237008235</v>
+        <v>0.168024904523138</v>
       </c>
       <c r="V103" t="n">
-        <v>0.4200644398565816</v>
+        <v>0.4045176207318785</v>
       </c>
       <c r="W103" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y103" t="n">
-        <v>7.583420626282964</v>
+        <v>2.050884636916369</v>
       </c>
       <c r="Z103" t="n">
-        <v>7.583420626282964</v>
+        <v>2.050884636916369</v>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -10541,98 +10541,98 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="F104" t="n">
-        <v>481</v>
+        <v>1481</v>
       </c>
       <c r="G104" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="H104" t="n">
         <v>3.8</v>
       </c>
       <c r="I104" t="n">
-        <v>1.73</v>
+        <v>5.75</v>
       </c>
       <c r="J104" t="n">
-        <v>0.2089704059251724</v>
+        <v>0.5854612684547574</v>
       </c>
       <c r="K104" t="n">
-        <v>0.2474649543850726</v>
+        <v>0.2495913828675545</v>
       </c>
       <c r="L104" t="n">
-        <v>0.543564639689755</v>
+        <v>0.1649473486776882</v>
       </c>
       <c r="M104" t="n">
-        <v>0.06341479903998914</v>
+        <v>0.05435488883238682</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>0.2646078634996389</v>
+        <v>0.5299375613515956</v>
       </c>
       <c r="P104" t="n">
-        <v>0.3891742873764772</v>
+        <v>0.3357546466828741</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.3462178491238836</v>
+        <v>0.1343077919655302</v>
       </c>
       <c r="R104" t="n">
         <v>1</v>
       </c>
       <c r="S104" t="n">
-        <v>0.1417093329914046</v>
+        <v>-0.05552370710316179</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U104" t="n">
-        <v>0.1417093329914046</v>
+        <v>-0.05552370710316179</v>
       </c>
       <c r="V104" t="n">
-        <v>0.3891742873764772</v>
+        <v>0.5299375613515956</v>
       </c>
       <c r="W104" t="n">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y104" t="n">
-        <v>7.132989869026711</v>
+        <v>4.711374581896096</v>
       </c>
       <c r="Z104" t="n">
-        <v>7.132989869026711</v>
+        <v>4.711374581896096</v>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -10640,98 +10640,98 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="F105" t="n">
-        <v>481</v>
+        <v>1481</v>
       </c>
       <c r="G105" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="H105" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I105" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J105" t="n">
-        <v>0.4569015166058744</v>
+        <v>0.4157043879907621</v>
       </c>
       <c r="K105" t="n">
-        <v>0.2676137454405835</v>
+        <v>0.3187066974595842</v>
       </c>
       <c r="L105" t="n">
-        <v>0.2754847379535419</v>
+        <v>0.2655889145496536</v>
       </c>
       <c r="M105" t="n">
-        <v>0.06763681082188988</v>
+        <v>0.04589371980676349</v>
       </c>
       <c r="N105" t="n">
         <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>0.5284225786984257</v>
+        <v>0.4679788688718871</v>
       </c>
       <c r="P105" t="n">
-        <v>0.2662849222737163</v>
+        <v>0.3424182063032361</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.2052924990278578</v>
+        <v>0.1896029248248768</v>
       </c>
       <c r="R105" t="n">
         <v>1</v>
       </c>
       <c r="S105" t="n">
-        <v>0.07152106209255127</v>
+        <v>0.05227448088112496</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
       </c>
       <c r="U105" t="n">
-        <v>0.07152106209255127</v>
+        <v>0.05227448088112496</v>
       </c>
       <c r="V105" t="n">
-        <v>0.5284225786984257</v>
+        <v>0.4679788688718871</v>
       </c>
       <c r="W105" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y105" t="n">
-        <v>8.748194707248672</v>
+        <v>5.16660377057429</v>
       </c>
       <c r="Z105" t="n">
-        <v>8.748194707248672</v>
+        <v>5.16660377057429</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -10739,98 +10739,98 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>INsZAAf3</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45532.6875</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="F106" t="n">
-        <v>481</v>
+        <v>1481</v>
       </c>
       <c r="G106" t="n">
-        <v>7</v>
+        <v>1.3</v>
       </c>
       <c r="H106" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="I106" t="n">
-        <v>1.42</v>
+        <v>11</v>
       </c>
       <c r="J106" t="n">
-        <v>0.1350755982777611</v>
+        <v>0.7321711568938194</v>
       </c>
       <c r="K106" t="n">
-        <v>0.1990587764093321</v>
+        <v>0.1812995245641839</v>
       </c>
       <c r="L106" t="n">
-        <v>0.6658656253129068</v>
+        <v>0.08652931854199684</v>
       </c>
       <c r="M106" t="n">
-        <v>0.05760881075929269</v>
+        <v>0.05061605061605046</v>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O106" t="n">
-        <v>0.2650283800996614</v>
+        <v>0.6358624453782491</v>
       </c>
       <c r="P106" t="n">
-        <v>0.3502749481669983</v>
+        <v>0.3086115268166349</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.3846966717333406</v>
+        <v>0.055526027805116</v>
       </c>
       <c r="R106" t="n">
         <v>1</v>
       </c>
       <c r="S106" t="n">
-        <v>-0.2811689535795662</v>
+        <v>-0.0963087115155703</v>
       </c>
       <c r="T106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U106" t="n">
-        <v>-0.2811689535795662</v>
+        <v>-0.0963087115155703</v>
       </c>
       <c r="V106" t="n">
-        <v>0.3846966717333406</v>
+        <v>0.6358624453782491</v>
       </c>
       <c r="W106" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y106" t="n">
-        <v>1.509609527342126</v>
+        <v>5.358274688910284</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.509609527342126</v>
+        <v>5.358274688910284</v>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -10838,98 +10838,98 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45536.39583333334</v>
+        <v>45532.6875</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="F107" t="n">
-        <v>481</v>
+        <v>1481</v>
       </c>
       <c r="G107" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H107" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="I107" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="J107" t="n">
-        <v>0.5879059350503919</v>
+        <v>0.5885015844273427</v>
       </c>
       <c r="K107" t="n">
-        <v>0.2239641657334826</v>
+        <v>0.2648257129923042</v>
       </c>
       <c r="L107" t="n">
-        <v>0.1881298992161254</v>
+        <v>0.1466727025803531</v>
       </c>
       <c r="M107" t="n">
-        <v>0.06309523809523809</v>
+        <v>0.04890788224121545</v>
       </c>
       <c r="N107" t="n">
         <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>0.5557722828627591</v>
+        <v>0.5915942898402606</v>
       </c>
       <c r="P107" t="n">
-        <v>0.2935787473574423</v>
+        <v>0.3204878649616577</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.1506489697797985</v>
+        <v>0.08791784519808173</v>
       </c>
       <c r="R107" t="n">
         <v>1</v>
       </c>
       <c r="S107" t="n">
-        <v>-0.03213365218763276</v>
+        <v>0.003092705412917951</v>
       </c>
       <c r="T107" t="n">
         <v>1</v>
       </c>
       <c r="U107" t="n">
-        <v>-0.03213365218763276</v>
+        <v>0.003092705412917951</v>
       </c>
       <c r="V107" t="n">
-        <v>0.5557722828627591</v>
+        <v>0.5915942898402606</v>
       </c>
       <c r="W107" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y107" t="n">
-        <v>7.635538383811432</v>
+        <v>5.905799690564663</v>
       </c>
       <c r="Z107" t="n">
-        <v>7.635538383811432</v>
+        <v>5.905799690564663</v>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -10937,98 +10937,98 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>45536.39583333334</v>
+        <v>45533.58333333334</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="F108" t="n">
-        <v>481</v>
+        <v>1481</v>
       </c>
       <c r="G108" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="H108" t="n">
         <v>4</v>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="J108" t="n">
-        <v>0.3857280617164899</v>
+        <v>0.550173120294781</v>
       </c>
       <c r="K108" t="n">
-        <v>0.2362584378013501</v>
+        <v>0.2338235761252819</v>
       </c>
       <c r="L108" t="n">
-        <v>0.3780135004821601</v>
+        <v>0.2160033035799371</v>
       </c>
       <c r="M108" t="n">
-        <v>0.05816326530612237</v>
+        <v>0.06918217633473711</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O108" t="n">
-        <v>0.1496592658274537</v>
+        <v>0.4567177506111351</v>
       </c>
       <c r="P108" t="n">
-        <v>0.4475438883580122</v>
+        <v>0.4011109620053718</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.4027968458145341</v>
+        <v>0.142171287383493</v>
       </c>
       <c r="R108" t="n">
         <v>1</v>
       </c>
       <c r="S108" t="n">
-        <v>0.2112854505566622</v>
+        <v>-0.09345536968364598</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U108" t="n">
-        <v>0.2112854505566622</v>
+        <v>-0.09345536968364598</v>
       </c>
       <c r="V108" t="n">
-        <v>0.4475438883580122</v>
+        <v>0.4567177506111351</v>
       </c>
       <c r="W108" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y108" t="n">
-        <v>7.984117541115475</v>
+        <v>3.607536189625261</v>
       </c>
       <c r="Z108" t="n">
-        <v>7.984117541115475</v>
+        <v>3.607536189625261</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -11036,98 +11036,98 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>45536.5</v>
+        <v>45533.6875</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="F109" t="n">
-        <v>481</v>
+        <v>1481</v>
       </c>
       <c r="G109" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="H109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I109" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="J109" t="n">
-        <v>0.2522368981678739</v>
+        <v>0.1190887124611667</v>
       </c>
       <c r="K109" t="n">
-        <v>0.2364720920323818</v>
+        <v>0.1905419399378667</v>
       </c>
       <c r="L109" t="n">
-        <v>0.5112910097997444</v>
+        <v>0.6903693476009666</v>
       </c>
       <c r="M109" t="n">
-        <v>0.05720720720720696</v>
+        <v>0.04963768115942035</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O109" t="n">
-        <v>0.3329908007186286</v>
+        <v>0.106492155857118</v>
       </c>
       <c r="P109" t="n">
-        <v>0.4435746912911929</v>
+        <v>0.3852108218483214</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.2234345079901784</v>
+        <v>0.5082970222945606</v>
       </c>
       <c r="R109" t="n">
         <v>1</v>
       </c>
       <c r="S109" t="n">
-        <v>0.2071025992588111</v>
+        <v>-0.1820723253064059</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U109" t="n">
-        <v>0.2071025992588111</v>
+        <v>-0.1820723253064059</v>
       </c>
       <c r="V109" t="n">
-        <v>0.4435746912911929</v>
+        <v>0.5082970222945606</v>
       </c>
       <c r="W109" t="n">
-        <v>4</v>
+        <v>1.38</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y109" t="n">
-        <v>7.926239923267577</v>
+        <v>3.23971724605642</v>
       </c>
       <c r="Z109" t="n">
-        <v>7.926239923267577</v>
+        <v>3.23971724605642</v>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -11135,98 +11135,98 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.35416666666</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F110" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G110" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="H110" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="I110" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="J110" t="n">
-        <v>0.5399533013361008</v>
+        <v>0.6942607775720708</v>
       </c>
       <c r="K110" t="n">
-        <v>0.2524646517057984</v>
+        <v>0.1798466014281936</v>
       </c>
       <c r="L110" t="n">
-        <v>0.2075820469581009</v>
+        <v>0.1258926209997355</v>
       </c>
       <c r="M110" t="n">
-        <v>0.07052717457341728</v>
+        <v>0.05910364145658265</v>
       </c>
       <c r="N110" t="n">
         <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>0.4505903748520288</v>
+        <v>0.6163991002140746</v>
       </c>
       <c r="P110" t="n">
-        <v>0.2988719079151199</v>
+        <v>0.2669066274600873</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.2505377172328513</v>
+        <v>0.116694272325838</v>
       </c>
       <c r="R110" t="n">
         <v>1</v>
       </c>
       <c r="S110" t="n">
-        <v>-0.08936292648407196</v>
+        <v>-0.07786167735799621</v>
       </c>
       <c r="T110" t="n">
         <v>1</v>
       </c>
       <c r="U110" t="n">
-        <v>-0.08936292648407196</v>
+        <v>-0.07786167735799621</v>
       </c>
       <c r="V110" t="n">
-        <v>0.4505903748520288</v>
+        <v>0.6163991002140746</v>
       </c>
       <c r="W110" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y110" t="n">
-        <v>7.224548967359137</v>
+        <v>7.852788015343426</v>
       </c>
       <c r="Z110" t="n">
-        <v>7.224548967359137</v>
+        <v>7.852788015343426</v>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -11234,98 +11234,98 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>45535.5</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F111" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G111" t="n">
         <v>1.75</v>
       </c>
       <c r="H111" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I111" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="J111" t="n">
-        <v>0.5327102803738317</v>
+        <v>0.539701816903434</v>
       </c>
       <c r="K111" t="n">
-        <v>0.2453271028037383</v>
+        <v>0.2421738922002589</v>
       </c>
       <c r="L111" t="n">
-        <v>0.2219626168224299</v>
+        <v>0.2181242908963071</v>
       </c>
       <c r="M111" t="n">
-        <v>0.07268170426065157</v>
+        <v>0.05878571005591793</v>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>0.4187152077083568</v>
+        <v>0.2397687640438481</v>
       </c>
       <c r="P111" t="n">
-        <v>0.3360071302665369</v>
+        <v>0.4655015758899603</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.2452776620251062</v>
+        <v>0.2947296600661913</v>
       </c>
       <c r="R111" t="n">
         <v>1</v>
       </c>
       <c r="S111" t="n">
-        <v>-0.1139950726654749</v>
+        <v>0.2233276836897014</v>
       </c>
       <c r="T111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U111" t="n">
-        <v>-0.1139950726654749</v>
+        <v>0.2233276836897014</v>
       </c>
       <c r="V111" t="n">
-        <v>0.4187152077083568</v>
+        <v>0.4655015758899603</v>
       </c>
       <c r="W111" t="n">
-        <v>1.75</v>
+        <v>3.9</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y111" t="n">
-        <v>6.094402700857637</v>
+        <v>8.245971049245494</v>
       </c>
       <c r="Z111" t="n">
-        <v>6.094402700857637</v>
+        <v>8.245971049245494</v>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -11333,98 +11333,98 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F112" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G112" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="H112" t="n">
         <v>3.4</v>
       </c>
       <c r="I112" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="J112" t="n">
-        <v>0.4243156199677939</v>
+        <v>0.3308443879577409</v>
       </c>
       <c r="K112" t="n">
-        <v>0.2745571658615137</v>
+        <v>0.2802446580347923</v>
       </c>
       <c r="L112" t="n">
-        <v>0.3011272141706924</v>
+        <v>0.3889109540074668</v>
       </c>
       <c r="M112" t="n">
-        <v>0.07124374676556844</v>
+        <v>0.04950313458716815</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>0.3401902429197773</v>
+        <v>0.3745906830557912</v>
       </c>
       <c r="P112" t="n">
-        <v>0.3711153917842178</v>
+        <v>0.3118302927967421</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.2886943652960049</v>
+        <v>0.3135790241474666</v>
       </c>
       <c r="R112" t="n">
         <v>1</v>
       </c>
       <c r="S112" t="n">
-        <v>0.09655822592270408</v>
+        <v>0.04374629509805034</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U112" t="n">
-        <v>0.09655822592270408</v>
+        <v>0.04374629509805034</v>
       </c>
       <c r="V112" t="n">
-        <v>0.3711153917842178</v>
+        <v>0.3745906830557912</v>
       </c>
       <c r="W112" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y112" t="n">
-        <v>9.353472354138436</v>
+        <v>6.100061887991398</v>
       </c>
       <c r="Z112" t="n">
-        <v>9.353472354138436</v>
+        <v>6.100061887991398</v>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -11432,98 +11432,98 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F113" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G113" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="H113" t="n">
         <v>3.5</v>
       </c>
       <c r="I113" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="J113" t="n">
-        <v>0.2478450273426638</v>
+        <v>0.3265184597062326</v>
       </c>
       <c r="K113" t="n">
-        <v>0.2655482435814255</v>
+        <v>0.2705438666137356</v>
       </c>
       <c r="L113" t="n">
-        <v>0.4866067290759106</v>
+        <v>0.4029376736800317</v>
       </c>
       <c r="M113" t="n">
-        <v>0.07594116180503629</v>
+        <v>0.05607378681479935</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>0.205900628522786</v>
+        <v>0.3422109501943484</v>
       </c>
       <c r="P113" t="n">
-        <v>0.4128971587303172</v>
+        <v>0.3722065463082159</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.3812022127468968</v>
+        <v>0.2855825034974356</v>
       </c>
       <c r="R113" t="n">
         <v>1</v>
       </c>
       <c r="S113" t="n">
-        <v>0.1473489151488917</v>
+        <v>0.1016626796944803</v>
       </c>
       <c r="T113" t="n">
         <v>0</v>
       </c>
       <c r="U113" t="n">
-        <v>0.1473489151488917</v>
+        <v>0.1016626796944803</v>
       </c>
       <c r="V113" t="n">
-        <v>0.4128971587303172</v>
+        <v>0.3722065463082159</v>
       </c>
       <c r="W113" t="n">
         <v>3.5</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y113" t="n">
-        <v>10.25794317460634</v>
+        <v>6.885571457504543</v>
       </c>
       <c r="Z113" t="n">
-        <v>10.25794317460634</v>
+        <v>6.885571457504543</v>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -11531,98 +11531,98 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45536.41666666666</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F114" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G114" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="H114" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I114" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="J114" t="n">
-        <v>0.5198358413132695</v>
+        <v>0.210304843837666</v>
       </c>
       <c r="K114" t="n">
-        <v>0.2462380300957592</v>
+        <v>0.2426594351973069</v>
       </c>
       <c r="L114" t="n">
-        <v>0.2339261285909713</v>
+        <v>0.5470357209650272</v>
       </c>
       <c r="M114" t="n">
-        <v>0.06871345029239762</v>
+        <v>0.0566671607134035</v>
       </c>
       <c r="N114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>0.3231971173837818</v>
+        <v>0.4197518560377545</v>
       </c>
       <c r="P114" t="n">
-        <v>0.3363035034021639</v>
+        <v>0.2740125834579001</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.3404993792140544</v>
+        <v>0.3062355605043455</v>
       </c>
       <c r="R114" t="n">
         <v>1</v>
       </c>
       <c r="S114" t="n">
-        <v>0.1065732506230831</v>
+        <v>0.2094470122000885</v>
       </c>
       <c r="T114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U114" t="n">
-        <v>0.1065732506230831</v>
+        <v>0.2094470122000885</v>
       </c>
       <c r="V114" t="n">
-        <v>0.3404993792140544</v>
+        <v>0.4197518560377545</v>
       </c>
       <c r="W114" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y114" t="n">
-        <v>8.809987584281087</v>
+        <v>7.57886262462496</v>
       </c>
       <c r="Z114" t="n">
-        <v>8.809987584281087</v>
+        <v>7.57886262462496</v>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -11630,98 +11630,98 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>45536.5</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F115" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G115" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="H115" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J115" t="n">
-        <v>0.226628895184136</v>
+        <v>0.4640029460504511</v>
       </c>
       <c r="K115" t="n">
-        <v>0.2974504249291784</v>
+        <v>0.2642238998342846</v>
       </c>
       <c r="L115" t="n">
-        <v>0.4759206798866855</v>
+        <v>0.2717731541152641</v>
       </c>
       <c r="M115" t="n">
-        <v>0.05059523809523814</v>
+        <v>0.05129694154084419</v>
       </c>
       <c r="N115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>0.1655462430110401</v>
+        <v>0.5144347736576399</v>
       </c>
       <c r="P115" t="n">
-        <v>0.3867544121901165</v>
+        <v>0.2801183045599838</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.4476993447988434</v>
+        <v>0.2054469217823763</v>
       </c>
       <c r="R115" t="n">
         <v>1</v>
       </c>
       <c r="S115" t="n">
-        <v>-0.02822133508784214</v>
+        <v>0.05043182760718884</v>
       </c>
       <c r="T115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U115" t="n">
-        <v>-0.02822133508784214</v>
+        <v>0.05043182760718884</v>
       </c>
       <c r="V115" t="n">
-        <v>0.4476993447988434</v>
+        <v>0.5144347736576399</v>
       </c>
       <c r="W115" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y115" t="n">
-        <v>8.389560194220024</v>
+        <v>8.236712043437064</v>
       </c>
       <c r="Z115" t="n">
-        <v>8.389560194220024</v>
+        <v>8.236712043437064</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
@@ -11729,98 +11729,98 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>45536.5</v>
+        <v>45535.5625</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F116" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G116" t="n">
-        <v>2.75</v>
+        <v>7</v>
       </c>
       <c r="H116" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="I116" t="n">
-        <v>2.7</v>
+        <v>1.38</v>
       </c>
       <c r="J116" t="n">
-        <v>0.3474763724110195</v>
+        <v>0.1361434977578475</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2986125075407199</v>
+        <v>0.1732735426008968</v>
       </c>
       <c r="L116" t="n">
-        <v>0.3539111200482606</v>
+        <v>0.6905829596412556</v>
       </c>
       <c r="M116" t="n">
-        <v>0.046506734006734</v>
+        <v>0.04931300583474507</v>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>0.3655381059203401</v>
+        <v>0.2405927808084823</v>
       </c>
       <c r="P116" t="n">
-        <v>0.3433379128503292</v>
+        <v>0.3822913669338626</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.2911239812293306</v>
+        <v>0.3771158522576549</v>
       </c>
       <c r="R116" t="n">
         <v>1</v>
       </c>
       <c r="S116" t="n">
-        <v>0.01806173350932061</v>
+        <v>0.2090178243329657</v>
       </c>
       <c r="T116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>0.01806173350932061</v>
+        <v>0.2090178243329657</v>
       </c>
       <c r="V116" t="n">
-        <v>0.3655381059203401</v>
+        <v>0.3822913669338626</v>
       </c>
       <c r="W116" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y116" t="n">
-        <v>7.671996788593215</v>
+        <v>7.032625227929575</v>
       </c>
       <c r="Z116" t="n">
-        <v>7.671996788593215</v>
+        <v>7.032625227929575</v>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -11828,98 +11828,98 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F117" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G117" t="n">
-        <v>2.88</v>
+        <v>1.62</v>
       </c>
       <c r="H117" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="I117" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J117" t="n">
-        <v>0.3251999676819907</v>
+        <v>0.5888816959792844</v>
       </c>
       <c r="K117" t="n">
-        <v>0.2675931162640381</v>
+        <v>0.2203206345234275</v>
       </c>
       <c r="L117" t="n">
-        <v>0.4072069160539711</v>
+        <v>0.1907976694972882</v>
       </c>
       <c r="M117" t="n">
-        <v>0.06771911663216024</v>
+        <v>0.0482308328343739</v>
       </c>
       <c r="N117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>0.2295701588034008</v>
+        <v>0.5550193491993652</v>
       </c>
       <c r="P117" t="n">
-        <v>0.3455015752053436</v>
+        <v>0.2950473748303297</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.4249282659912556</v>
+        <v>0.1499332759703048</v>
       </c>
       <c r="R117" t="n">
         <v>1</v>
       </c>
       <c r="S117" t="n">
-        <v>0.01772134993728453</v>
+        <v>-0.03386234677991917</v>
       </c>
       <c r="T117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U117" t="n">
-        <v>0.01772134993728453</v>
+        <v>-0.03386234677991917</v>
       </c>
       <c r="V117" t="n">
-        <v>0.4249282659912556</v>
+        <v>0.5550193491993652</v>
       </c>
       <c r="W117" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y117" t="n">
-        <v>8.852992318570802</v>
+        <v>7.599352039469022</v>
       </c>
       <c r="Z117" t="n">
-        <v>8.852992318570802</v>
+        <v>7.599352039469022</v>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -11927,98 +11927,98 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F118" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G118" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="H118" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I118" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="J118" t="n">
-        <v>0.2453841353742245</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="K118" t="n">
-        <v>0.2664170612634438</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="L118" t="n">
-        <v>0.4881988033623316</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="M118" t="n">
-        <v>0.07243238987521172</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="N118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>0.1845535855793215</v>
+        <v>0.1410078808304249</v>
       </c>
       <c r="P118" t="n">
-        <v>0.4059500178611531</v>
+        <v>0.4347808303596482</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.4094963965595253</v>
+        <v>0.4242112888099266</v>
       </c>
       <c r="R118" t="n">
         <v>1</v>
       </c>
       <c r="S118" t="n">
-        <v>-0.07870240680280627</v>
+        <v>0.1966855922644101</v>
       </c>
       <c r="T118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>-0.07870240680280627</v>
+        <v>0.1966855922644101</v>
       </c>
       <c r="V118" t="n">
-        <v>0.4094963965595253</v>
+        <v>0.4347808303596482</v>
       </c>
       <c r="W118" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y118" t="n">
-        <v>6.615879795134381</v>
+        <v>7.798010532326465</v>
       </c>
       <c r="Z118" t="n">
-        <v>6.615879795134381</v>
+        <v>7.798010532326465</v>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
@@ -12026,78 +12026,78 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>45534.64583333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F119" t="n">
-        <v>591</v>
+        <v>481</v>
       </c>
       <c r="G119" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="H119" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I119" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="J119" t="n">
-        <v>0.4803370786516853</v>
+        <v>0.2576687116564417</v>
       </c>
       <c r="K119" t="n">
-        <v>0.2668539325842696</v>
+        <v>0.2269938650306749</v>
       </c>
       <c r="L119" t="n">
-        <v>0.2528089887640449</v>
+        <v>0.5153374233128835</v>
       </c>
       <c r="M119" t="n">
-        <v>0.04093567251461994</v>
+        <v>0.04890604890604866</v>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>0.6297801158206143</v>
+        <v>0.3276785143971981</v>
       </c>
       <c r="P119" t="n">
-        <v>0.2787482353976901</v>
+        <v>0.4289925548951946</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.09147164878169556</v>
+        <v>0.2433289307076072</v>
       </c>
       <c r="R119" t="n">
         <v>1</v>
       </c>
       <c r="S119" t="n">
-        <v>0.149443037168929</v>
+        <v>0.2019986898645197</v>
       </c>
       <c r="T119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U119" t="n">
-        <v>0.149443037168929</v>
+        <v>0.2019986898645197</v>
       </c>
       <c r="V119" t="n">
-        <v>0.6297801158206143</v>
+        <v>0.4289925548951946</v>
       </c>
       <c r="W119" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
@@ -12105,19 +12105,19 @@
         </is>
       </c>
       <c r="Y119" t="n">
-        <v>2.762433692723559</v>
+        <v>7.71360766955844</v>
       </c>
       <c r="Z119" t="n">
-        <v>2.762433692723559</v>
+        <v>7.71360766955844</v>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr"/>
@@ -12125,78 +12125,78 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>2kGeEq1e</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45549.35416666666</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F120" t="n">
-        <v>591</v>
+        <v>481</v>
       </c>
       <c r="G120" t="n">
-        <v>2.55</v>
+        <v>4.33</v>
       </c>
       <c r="H120" t="n">
         <v>3.6</v>
       </c>
       <c r="I120" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
-        <v>0.3734248358279596</v>
+        <v>0.216998191681736</v>
       </c>
       <c r="K120" t="n">
-        <v>0.2645092587114714</v>
+        <v>0.2610006027727547</v>
       </c>
       <c r="L120" t="n">
-        <v>0.3620659054605692</v>
+        <v>0.5220012055455093</v>
       </c>
       <c r="M120" t="n">
-        <v>0.05016277740500508</v>
+        <v>0.0642802155504234</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
-        <v>0.2972399663468631</v>
+        <v>0.2546157729465405</v>
       </c>
       <c r="P120" t="n">
-        <v>0.4269036452393538</v>
+        <v>0.3710500625143644</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.275856388413783</v>
+        <v>0.374334164539095</v>
       </c>
       <c r="R120" t="n">
         <v>1</v>
       </c>
       <c r="S120" t="n">
-        <v>0.1623943865278825</v>
+        <v>-0.1476670410064144</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U120" t="n">
-        <v>0.1623943865278825</v>
+        <v>-0.1476670410064144</v>
       </c>
       <c r="V120" t="n">
-        <v>0.4269036452393538</v>
+        <v>0.374334164539095</v>
       </c>
       <c r="W120" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
@@ -12204,19 +12204,19 @@
         </is>
       </c>
       <c r="Y120" t="n">
-        <v>1.994486216976943</v>
+        <v>3.305190680547172</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.994486216976943</v>
+        <v>3.305190680547172</v>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr"/>
@@ -12224,78 +12224,78 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>2TvL16Hk</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F121" t="n">
-        <v>591</v>
+        <v>481</v>
       </c>
       <c r="G121" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="H121" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="I121" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J121" t="n">
-        <v>0.5198358413132695</v>
+        <v>0.6866642573183954</v>
       </c>
       <c r="K121" t="n">
-        <v>0.2462380300957592</v>
+        <v>0.1966028189374774</v>
       </c>
       <c r="L121" t="n">
-        <v>0.2339261285909713</v>
+        <v>0.1167329237441272</v>
       </c>
       <c r="M121" t="n">
-        <v>0.06871345029239762</v>
+        <v>0.07082043343653233</v>
       </c>
       <c r="N121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>0.4566852233153452</v>
+        <v>0.3545506353334584</v>
       </c>
       <c r="P121" t="n">
-        <v>0.3809080728794988</v>
+        <v>0.4686505586189422</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.1624067038051559</v>
+        <v>0.1767988060475996</v>
       </c>
       <c r="R121" t="n">
         <v>1</v>
       </c>
       <c r="S121" t="n">
-        <v>-0.06315061799792432</v>
+        <v>0.2720477396814647</v>
       </c>
       <c r="T121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>-0.06315061799792432</v>
+        <v>0.2720477396814647</v>
       </c>
       <c r="V121" t="n">
-        <v>0.4566852233153452</v>
+        <v>0.4686505586189422</v>
       </c>
       <c r="W121" t="n">
-        <v>1.8</v>
+        <v>4.75</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
@@ -12303,19 +12303,19 @@
         </is>
       </c>
       <c r="Y121" t="n">
-        <v>1.48964493470624</v>
+        <v>8.291888552440589</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.48964493470624</v>
+        <v>8.291888552440589</v>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr"/>
@@ -12323,78 +12323,78 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>beYTapn2</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F122" t="n">
-        <v>591</v>
+        <v>481</v>
       </c>
       <c r="G122" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="H122" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I122" t="n">
-        <v>2.15</v>
+        <v>5.75</v>
       </c>
       <c r="J122" t="n">
-        <v>0.296097934200459</v>
+        <v>0.5967984457957977</v>
       </c>
       <c r="K122" t="n">
-        <v>0.2631981637337414</v>
+        <v>0.2402496307434366</v>
       </c>
       <c r="L122" t="n">
-        <v>0.4407039020657995</v>
+        <v>0.1629519234607656</v>
       </c>
       <c r="M122" t="n">
-        <v>0.05539405684754528</v>
+        <v>0.06726597504775311</v>
       </c>
       <c r="N122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>0.1514538444399252</v>
+        <v>0.5336530787501176</v>
       </c>
       <c r="P122" t="n">
-        <v>0.3870476271589403</v>
+        <v>0.2644190970481768</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.4614985284011345</v>
+        <v>0.2019278242017057</v>
       </c>
       <c r="R122" t="n">
         <v>1</v>
       </c>
       <c r="S122" t="n">
-        <v>0.02079462633533496</v>
+        <v>-0.06314536704568008</v>
       </c>
       <c r="T122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U122" t="n">
-        <v>0.02079462633533496</v>
+        <v>-0.06314536704568008</v>
       </c>
       <c r="V122" t="n">
-        <v>0.4614985284011345</v>
+        <v>0.5336530787501176</v>
       </c>
       <c r="W122" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
@@ -12402,19 +12402,19 @@
         </is>
       </c>
       <c r="Y122" t="n">
-        <v>1.825622309421007</v>
+        <v>6.860799570815868</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.825622309421007</v>
+        <v>6.860799570815868</v>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
@@ -12422,78 +12422,78 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>jkLFNmv9</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F123" t="n">
-        <v>591</v>
+        <v>481</v>
       </c>
       <c r="G123" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="H123" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="I123" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J123" t="n">
-        <v>0.5816922989614663</v>
+        <v>0.3739565943238731</v>
       </c>
       <c r="K123" t="n">
-        <v>0.2298393961750184</v>
+        <v>0.2921535893155259</v>
       </c>
       <c r="L123" t="n">
-        <v>0.1884683048635151</v>
+        <v>0.333889816360601</v>
       </c>
       <c r="M123" t="n">
-        <v>0.06118638964167422</v>
+        <v>0.06964285714285712</v>
       </c>
       <c r="N123" t="n">
         <v>1</v>
       </c>
       <c r="O123" t="n">
-        <v>0.5411474257773473</v>
+        <v>0.4710277044786925</v>
       </c>
       <c r="P123" t="n">
-        <v>0.3218229682050365</v>
+        <v>0.2474972523761889</v>
       </c>
       <c r="Q123" t="n">
-        <v>0.1370296060176162</v>
+        <v>0.2814750431451186</v>
       </c>
       <c r="R123" t="n">
         <v>1</v>
       </c>
       <c r="S123" t="n">
-        <v>-0.04054487318411903</v>
+        <v>0.0970711101548194</v>
       </c>
       <c r="T123" t="n">
         <v>1</v>
       </c>
       <c r="U123" t="n">
-        <v>-0.04054487318411903</v>
+        <v>0.0970711101548194</v>
       </c>
       <c r="V123" t="n">
-        <v>0.5411474257773473</v>
+        <v>0.4710277044786925</v>
       </c>
       <c r="W123" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
@@ -12501,19 +12501,19 @@
         </is>
       </c>
       <c r="Y123" t="n">
-        <v>1.894928798370925</v>
+        <v>8.283843190368357</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.894928798370925</v>
+        <v>8.283843190368357</v>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr"/>
@@ -12521,78 +12521,78 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>AiyHLR8L</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F124" t="n">
-        <v>591</v>
+        <v>481</v>
       </c>
       <c r="G124" t="n">
-        <v>4.1</v>
+        <v>1.22</v>
       </c>
       <c r="H124" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="J124" t="n">
-        <v>0.2280041081821294</v>
+        <v>0.7700592353257942</v>
       </c>
       <c r="K124" t="n">
-        <v>0.2526532009585758</v>
+        <v>0.1445341949380722</v>
       </c>
       <c r="L124" t="n">
-        <v>0.5193426908592949</v>
+        <v>0.08540656973613354</v>
       </c>
       <c r="M124" t="n">
-        <v>0.06972826485021599</v>
+        <v>0.0644273759027858</v>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O124" t="n">
-        <v>0.1419416928438318</v>
+        <v>0.6549696850061787</v>
       </c>
       <c r="P124" t="n">
-        <v>0.3752684862615773</v>
+        <v>0.2246064160078307</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.4827898208945908</v>
+        <v>0.1204238989859904</v>
       </c>
       <c r="R124" t="n">
         <v>1</v>
       </c>
       <c r="S124" t="n">
-        <v>-0.03655286996470403</v>
+        <v>-0.1150895503196155</v>
       </c>
       <c r="T124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U124" t="n">
-        <v>-0.03655286996470403</v>
+        <v>-0.1150895503196155</v>
       </c>
       <c r="V124" t="n">
-        <v>0.4827898208945908</v>
+        <v>0.6549696850061787</v>
       </c>
       <c r="W124" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
@@ -12600,19 +12600,19 @@
         </is>
       </c>
       <c r="Y124" t="n">
-        <v>1.68913890836943</v>
+        <v>7.872367028654276</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.68913890836943</v>
+        <v>7.872367028654276</v>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr"/>
@@ -12620,78 +12620,78 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>tzSnG5Wr</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F125" t="n">
-        <v>591</v>
+        <v>481</v>
       </c>
       <c r="G125" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="H125" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I125" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="J125" t="n">
-        <v>0.5393258426966292</v>
+        <v>0.7841087297438578</v>
       </c>
       <c r="K125" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.123366440146367</v>
       </c>
       <c r="L125" t="n">
-        <v>0.2247191011235955</v>
+        <v>0.09252483010977522</v>
       </c>
       <c r="M125" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.08079096045197742</v>
       </c>
       <c r="N125" t="n">
         <v>1</v>
       </c>
       <c r="O125" t="n">
-        <v>0.3839512902815304</v>
+        <v>0.5933602491455227</v>
       </c>
       <c r="P125" t="n">
-        <v>0.3170760805874334</v>
+        <v>0.2377481209950953</v>
       </c>
       <c r="Q125" t="n">
-        <v>0.2989726291310363</v>
+        <v>0.1688916298593821</v>
       </c>
       <c r="R125" t="n">
         <v>1</v>
       </c>
       <c r="S125" t="n">
-        <v>-0.1553745524150988</v>
+        <v>-0.1907484805983352</v>
       </c>
       <c r="T125" t="n">
         <v>1</v>
       </c>
       <c r="U125" t="n">
-        <v>-0.1553745524150988</v>
+        <v>-0.1907484805983352</v>
       </c>
       <c r="V125" t="n">
-        <v>0.3839512902815304</v>
+        <v>0.5933602491455227</v>
       </c>
       <c r="W125" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
@@ -12699,19 +12699,19 @@
         </is>
       </c>
       <c r="Y125" t="n">
-        <v>0.8652305925669825</v>
+        <v>5.870761690276266</v>
       </c>
       <c r="Z125" t="n">
-        <v>0.8652305925669825</v>
+        <v>5.870761690276266</v>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr"/>
@@ -12719,78 +12719,78 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>Wplk7SgS</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>45536.4375</v>
+        <v>45549.5625</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F126" t="n">
-        <v>591</v>
+        <v>481</v>
       </c>
       <c r="G126" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="H126" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="I126" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="J126" t="n">
-        <v>0.3772968558595345</v>
+        <v>0.629537369997383</v>
       </c>
       <c r="K126" t="n">
-        <v>0.2858309514087382</v>
+        <v>0.2151767454032626</v>
       </c>
       <c r="L126" t="n">
-        <v>0.3368721927317272</v>
+        <v>0.1552858845993545</v>
       </c>
       <c r="M126" t="n">
-        <v>0.06017316017316032</v>
+        <v>0.07328922455943232</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O126" t="n">
-        <v>0.345798198928346</v>
+        <v>0.5736786495404097</v>
       </c>
       <c r="P126" t="n">
-        <v>0.4220051128978362</v>
+        <v>0.3034338078605047</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.2321966881738179</v>
+        <v>0.1228875425990855</v>
       </c>
       <c r="R126" t="n">
         <v>1</v>
       </c>
       <c r="S126" t="n">
-        <v>0.136174161489098</v>
+        <v>-0.05585872045697327</v>
       </c>
       <c r="T126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U126" t="n">
-        <v>0.136174161489098</v>
+        <v>-0.05585872045697327</v>
       </c>
       <c r="V126" t="n">
-        <v>0.4220051128978362</v>
+        <v>0.5736786495404097</v>
       </c>
       <c r="W126" t="n">
-        <v>3.3</v>
+        <v>1.48</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
@@ -12798,19 +12798,19 @@
         </is>
       </c>
       <c r="Y126" t="n">
-        <v>1.975943822505304</v>
+        <v>7.550691856560356</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.975943822505304</v>
+        <v>7.550691856560356</v>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr"/>
@@ -12818,78 +12818,78 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>AVat9lPF</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>45536.52083333334</v>
+        <v>45549.66666666666</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F127" t="n">
-        <v>591</v>
+        <v>481</v>
       </c>
       <c r="G127" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="H127" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="I127" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
-        <v>0.7809330628803246</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="K127" t="n">
-        <v>0.1338742393509128</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="L127" t="n">
-        <v>0.08519269776876268</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="M127" t="n">
-        <v>0.0670995670995671</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>0.6441791259908952</v>
+        <v>0.336389635295347</v>
       </c>
       <c r="P127" t="n">
-        <v>0.2630939763086747</v>
+        <v>0.4158726077244334</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.09272689770043006</v>
+        <v>0.2477377569802196</v>
       </c>
       <c r="R127" t="n">
         <v>1</v>
       </c>
       <c r="S127" t="n">
-        <v>-0.1367539368894294</v>
+        <v>0.1546785778736871</v>
       </c>
       <c r="T127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U127" t="n">
-        <v>-0.1367539368894294</v>
+        <v>0.1546785778736871</v>
       </c>
       <c r="V127" t="n">
-        <v>0.6441791259908952</v>
+        <v>0.4158726077244334</v>
       </c>
       <c r="W127" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
@@ -12897,19 +12897,19 @@
         </is>
       </c>
       <c r="Y127" t="n">
-        <v>1.920754496488732</v>
+        <v>7.522296611994244</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.920754496488732</v>
+        <v>7.522296611994244</v>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
@@ -12917,78 +12917,78 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.5</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F128" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G128" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="H128" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="J128" t="n">
-        <v>0.2591463414634146</v>
+        <v>0.5292717447246527</v>
       </c>
       <c r="K128" t="n">
-        <v>0.274390243902439</v>
+        <v>0.2507076685537828</v>
       </c>
       <c r="L128" t="n">
-        <v>0.4664634146341464</v>
+        <v>0.2200205867215646</v>
       </c>
       <c r="M128" t="n">
-        <v>0.07189542483660127</v>
+        <v>0.04966033250948776</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>0.192076971736161</v>
+        <v>0.4168363980473944</v>
       </c>
       <c r="P128" t="n">
-        <v>0.440257744885126</v>
+        <v>0.3361876592780073</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.3676652833787132</v>
+        <v>0.2469759426745984</v>
       </c>
       <c r="R128" t="n">
         <v>1</v>
       </c>
       <c r="S128" t="n">
-        <v>0.165867500982687</v>
+        <v>-0.1124353466772583</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U128" t="n">
-        <v>0.165867500982687</v>
+        <v>-0.1124353466772583</v>
       </c>
       <c r="V128" t="n">
-        <v>0.440257744885126</v>
+        <v>0.4168363980473944</v>
       </c>
       <c r="W128" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
@@ -12996,19 +12996,19 @@
         </is>
       </c>
       <c r="Y128" t="n">
-        <v>2.196169694435367</v>
+        <v>6.088021027402721</v>
       </c>
       <c r="Z128" t="n">
-        <v>2.196169694435367</v>
+        <v>6.088021027402721</v>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr"/>
@@ -13016,78 +13016,78 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F129" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G129" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="H129" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="I129" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="J129" t="n">
-        <v>0.5693343167988197</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="K129" t="n">
-        <v>0.2364927162087406</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="L129" t="n">
-        <v>0.1941729669924396</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="M129" t="n">
-        <v>0.08422052281701409</v>
+        <v>0.05106209150326801</v>
       </c>
       <c r="N129" t="n">
         <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>0.3690156550322785</v>
+        <v>0.3499727788496041</v>
       </c>
       <c r="P129" t="n">
-        <v>0.4045176207318785</v>
+        <v>0.3748518076772431</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.2264667242358431</v>
+        <v>0.2751754134731528</v>
       </c>
       <c r="R129" t="n">
         <v>1</v>
       </c>
       <c r="S129" t="n">
-        <v>0.168024904523138</v>
+        <v>0.09502281428431658</v>
       </c>
       <c r="T129" t="n">
         <v>0</v>
       </c>
       <c r="U129" t="n">
-        <v>0.168024904523138</v>
+        <v>0.09502281428431658</v>
       </c>
       <c r="V129" t="n">
-        <v>0.4045176207318785</v>
+        <v>0.3748518076772431</v>
       </c>
       <c r="W129" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
@@ -13095,19 +13095,19 @@
         </is>
       </c>
       <c r="Y129" t="n">
-        <v>2.050884636916369</v>
+        <v>9.397492439231193</v>
       </c>
       <c r="Z129" t="n">
-        <v>2.050884636916369</v>
+        <v>9.397492439231193</v>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr"/>
@@ -13115,78 +13115,78 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45535.66666666666</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F130" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G130" t="n">
-        <v>1.62</v>
+        <v>3.75</v>
       </c>
       <c r="H130" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I130" t="n">
-        <v>5.25</v>
+        <v>1.9</v>
       </c>
       <c r="J130" t="n">
-        <v>0.5686433793663688</v>
+        <v>0.2541152263374485</v>
       </c>
       <c r="K130" t="n">
-        <v>0.255889520714866</v>
+        <v>0.2443415637860083</v>
       </c>
       <c r="L130" t="n">
-        <v>0.1754670999187652</v>
+        <v>0.5015432098765432</v>
       </c>
       <c r="M130" t="n">
-        <v>0.08553791887125217</v>
+        <v>0.04939271255060729</v>
       </c>
       <c r="N130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>0.4611177657755759</v>
+        <v>0.2057851162449069</v>
       </c>
       <c r="P130" t="n">
-        <v>0.3812382020105381</v>
+        <v>0.4128255812086476</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.157644032213886</v>
+        <v>0.3813893025464455</v>
       </c>
       <c r="R130" t="n">
         <v>1</v>
       </c>
       <c r="S130" t="n">
-        <v>-0.1075256135907928</v>
+        <v>0.1684840174226393</v>
       </c>
       <c r="T130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U130" t="n">
-        <v>-0.1075256135907928</v>
+        <v>0.1684840174226393</v>
       </c>
       <c r="V130" t="n">
-        <v>0.4611177657755759</v>
+        <v>0.4128255812086476</v>
       </c>
       <c r="W130" t="n">
-        <v>1.62</v>
+        <v>3.9</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
@@ -13194,19 +13194,19 @@
         </is>
       </c>
       <c r="Y130" t="n">
-        <v>1.43736647215213</v>
+        <v>10.25651162417295</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.43736647215213</v>
+        <v>10.25651162417295</v>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr"/>
@@ -13214,78 +13214,78 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F131" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G131" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="H131" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="I131" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="J131" t="n">
-        <v>0.422936152907686</v>
+        <v>0.513157894736842</v>
       </c>
       <c r="K131" t="n">
-        <v>0.2907686051240341</v>
+        <v>0.243421052631579</v>
       </c>
       <c r="L131" t="n">
-        <v>0.2862952419682798</v>
+        <v>0.243421052631579</v>
       </c>
       <c r="M131" t="n">
-        <v>0.0747377622377623</v>
+        <v>0.05336105336105335</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>0.3643385543031154</v>
+        <v>0.3098674006714301</v>
       </c>
       <c r="P131" t="n">
-        <v>0.4539557341479734</v>
+        <v>0.3206823668450107</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.1817057115489108</v>
+        <v>0.3694502324835592</v>
       </c>
       <c r="R131" t="n">
         <v>1</v>
       </c>
       <c r="S131" t="n">
-        <v>0.1631871290239393</v>
+        <v>0.1260291798519802</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U131" t="n">
-        <v>0.1631871290239393</v>
+        <v>0.1260291798519802</v>
       </c>
       <c r="V131" t="n">
-        <v>0.4539557341479734</v>
+        <v>0.3694502324835592</v>
       </c>
       <c r="W131" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
@@ -13293,19 +13293,19 @@
         </is>
       </c>
       <c r="Y131" t="n">
-        <v>2.251852577612105</v>
+        <v>9.389004649671184</v>
       </c>
       <c r="Z131" t="n">
-        <v>2.251852577612105</v>
+        <v>9.389004649671184</v>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr"/>
@@ -13313,78 +13313,78 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F132" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G132" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="H132" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I132" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
-        <v>0.3397831171592601</v>
+        <v>0.2374100719424461</v>
       </c>
       <c r="K132" t="n">
-        <v>0.2698277695088242</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="L132" t="n">
-        <v>0.3903891133319158</v>
+        <v>0.4748201438848921</v>
       </c>
       <c r="M132" t="n">
-        <v>0.0900199323228108</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="N132" t="n">
         <v>2</v>
       </c>
       <c r="O132" t="n">
-        <v>0.2755417528022642</v>
+        <v>0.1636929323277636</v>
       </c>
       <c r="P132" t="n">
-        <v>0.3119780634014583</v>
+        <v>0.3826531137499105</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.4124801837962774</v>
+        <v>0.4536539539223259</v>
       </c>
       <c r="R132" t="n">
         <v>1</v>
       </c>
       <c r="S132" t="n">
-        <v>0.0220910704643616</v>
+        <v>-0.0211661899625662</v>
       </c>
       <c r="T132" t="n">
         <v>2</v>
       </c>
       <c r="U132" t="n">
-        <v>0.0220910704643616</v>
+        <v>-0.0211661899625662</v>
       </c>
       <c r="V132" t="n">
-        <v>0.4124801837962774</v>
+        <v>0.4536539539223259</v>
       </c>
       <c r="W132" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
@@ -13392,19 +13392,19 @@
         </is>
       </c>
       <c r="Y132" t="n">
-        <v>1.766549813890983</v>
+        <v>8.649755279195194</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.766549813890983</v>
+        <v>8.649755279195194</v>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr"/>
@@ -13412,78 +13412,78 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F133" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G133" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="H133" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="I133" t="n">
-        <v>5.75</v>
+        <v>2.6</v>
       </c>
       <c r="J133" t="n">
-        <v>0.6317126205512437</v>
+        <v>0.3458980044345898</v>
       </c>
       <c r="K133" t="n">
-        <v>0.2100845666498362</v>
+        <v>0.2882483370288249</v>
       </c>
       <c r="L133" t="n">
-        <v>0.1582028127989202</v>
+        <v>0.3658536585365853</v>
       </c>
       <c r="M133" t="n">
-        <v>0.09930437013979532</v>
+        <v>0.05128205128205132</v>
       </c>
       <c r="N133" t="n">
         <v>1</v>
       </c>
       <c r="O133" t="n">
-        <v>0.5093270547347218</v>
+        <v>0.351575000812226</v>
       </c>
       <c r="P133" t="n">
-        <v>0.2984430895688789</v>
+        <v>0.329399807331509</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.1922298556963995</v>
+        <v>0.319025191856265</v>
       </c>
       <c r="R133" t="n">
         <v>1</v>
       </c>
       <c r="S133" t="n">
-        <v>-0.1223855658165218</v>
+        <v>0.00567699637763619</v>
       </c>
       <c r="T133" t="n">
         <v>1</v>
       </c>
       <c r="U133" t="n">
-        <v>-0.1223855658165218</v>
+        <v>0.00567699637763619</v>
       </c>
       <c r="V133" t="n">
-        <v>0.5093270547347218</v>
+        <v>0.351575000812226</v>
       </c>
       <c r="W133" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
@@ -13491,19 +13491,19 @@
         </is>
       </c>
       <c r="Y133" t="n">
-        <v>1.572932881624008</v>
+        <v>7.145039943797244</v>
       </c>
       <c r="Z133" t="n">
-        <v>1.572932881624008</v>
+        <v>7.145039943797244</v>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr"/>
@@ -13511,78 +13511,78 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.5</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F134" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G134" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="H134" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I134" t="n">
-        <v>5</v>
+        <v>2.38</v>
       </c>
       <c r="J134" t="n">
-        <v>0.574915973819211</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="K134" t="n">
-        <v>0.2388112506633646</v>
+        <v>0.2719249862107005</v>
       </c>
       <c r="L134" t="n">
-        <v>0.1862727755174244</v>
+        <v>0.3998896856039714</v>
       </c>
       <c r="M134" t="n">
-        <v>0.07369420702754037</v>
+        <v>0.05070993914807298</v>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O134" t="n">
-        <v>0.4791085079664594</v>
+        <v>0.2331656206153008</v>
       </c>
       <c r="P134" t="n">
-        <v>0.3798535798145141</v>
+        <v>0.3511927884236702</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.1410379122190265</v>
+        <v>0.415641590961029</v>
       </c>
       <c r="R134" t="n">
         <v>1</v>
       </c>
       <c r="S134" t="n">
-        <v>-0.09580746585275157</v>
+        <v>0.01575190535705767</v>
       </c>
       <c r="T134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U134" t="n">
-        <v>-0.09580746585275157</v>
+        <v>0.01575190535705767</v>
       </c>
       <c r="V134" t="n">
-        <v>0.4791085079664594</v>
+        <v>0.415641590961029</v>
       </c>
       <c r="W134" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
@@ -13590,19 +13590,19 @@
         </is>
       </c>
       <c r="Y134" t="n">
-        <v>1.558134317379585</v>
+        <v>8.627869926361734</v>
       </c>
       <c r="Z134" t="n">
-        <v>1.558134317379585</v>
+        <v>8.627869926361734</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr"/>
@@ -13610,78 +13610,78 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F135" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="H135" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="I135" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J135" t="n">
-        <v>0.463395937140667</v>
+        <v>0.2295302013422819</v>
       </c>
       <c r="K135" t="n">
-        <v>0.2989651207359141</v>
+        <v>0.2476510067114094</v>
       </c>
       <c r="L135" t="n">
-        <v>0.237638942123419</v>
+        <v>0.5228187919463088</v>
       </c>
       <c r="M135" t="n">
-        <v>0.07899090157154665</v>
+        <v>0.06261588931678785</v>
       </c>
       <c r="N135" t="n">
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>0.3704447514747158</v>
+        <v>0.1923681207828232</v>
       </c>
       <c r="P135" t="n">
-        <v>0.4077449801290536</v>
+        <v>0.4145584372830421</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.2218102683962306</v>
+        <v>0.3930734419341346</v>
       </c>
       <c r="R135" t="n">
         <v>1</v>
       </c>
       <c r="S135" t="n">
-        <v>0.1087798593931395</v>
+        <v>0.1669074305716328</v>
       </c>
       <c r="T135" t="n">
         <v>0</v>
       </c>
       <c r="U135" t="n">
-        <v>0.1087798593931395</v>
+        <v>0.1669074305716328</v>
       </c>
       <c r="V135" t="n">
-        <v>0.4077449801290536</v>
+        <v>0.4145584372830421</v>
       </c>
       <c r="W135" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
@@ -13689,19 +13689,19 @@
         </is>
       </c>
       <c r="Y135" t="n">
-        <v>2.064003984058046</v>
+        <v>10.29116874566084</v>
       </c>
       <c r="Z135" t="n">
-        <v>2.064003984058046</v>
+        <v>10.29116874566084</v>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr"/>
@@ -13709,98 +13709,98 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45535.4375</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F136" t="n">
-        <v>771</v>
+        <v>591</v>
       </c>
       <c r="G136" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="H136" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I136" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="J136" t="n">
-        <v>0.5251667677380231</v>
+        <v>0.3533568904593639</v>
       </c>
       <c r="K136" t="n">
-        <v>0.2625833838690115</v>
+        <v>0.265017667844523</v>
       </c>
       <c r="L136" t="n">
-        <v>0.2122498483929654</v>
+        <v>0.3816254416961131</v>
       </c>
       <c r="M136" t="n">
-        <v>0.08808973935994713</v>
+        <v>0.04814814814814827</v>
       </c>
       <c r="N136" t="n">
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>0.3694247516053549</v>
+        <v>0.2938564130461177</v>
       </c>
       <c r="P136" t="n">
-        <v>0.3851395916103322</v>
+        <v>0.426822698542927</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.2454356567843127</v>
+        <v>0.2793208884109552</v>
       </c>
       <c r="R136" t="n">
         <v>1</v>
       </c>
       <c r="S136" t="n">
-        <v>0.1225562077413207</v>
+        <v>0.1618050306984041</v>
       </c>
       <c r="T136" t="n">
         <v>0</v>
       </c>
       <c r="U136" t="n">
-        <v>0.1225562077413207</v>
+        <v>0.1618050306984041</v>
       </c>
       <c r="V136" t="n">
-        <v>0.3851395916103322</v>
+        <v>0.426822698542927</v>
       </c>
       <c r="W136" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y136" t="n">
-        <v>1.9721121608204</v>
+        <v>1.994179809777464</v>
       </c>
       <c r="Z136" t="n">
-        <v>1.9721121608204</v>
+        <v>1.994179809777464</v>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr"/>
@@ -13808,98 +13808,98 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45535.4375</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F137" t="n">
-        <v>771</v>
+        <v>591</v>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H137" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="I137" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J137" t="n">
-        <v>0.4626168224299065</v>
+        <v>0.5290697674418605</v>
       </c>
       <c r="K137" t="n">
-        <v>0.2803738317757009</v>
+        <v>0.2267441860465116</v>
       </c>
       <c r="L137" t="n">
-        <v>0.2570093457943925</v>
+        <v>0.2441860465116279</v>
       </c>
       <c r="M137" t="n">
-        <v>0.08080808080808088</v>
+        <v>0.05006105006105011</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O137" t="n">
-        <v>0.3419065449955382</v>
+        <v>0.4708083309583022</v>
       </c>
       <c r="P137" t="n">
-        <v>0.4604020439379574</v>
+        <v>0.3811860625703036</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.1976914110665043</v>
+        <v>0.1480056064713942</v>
       </c>
       <c r="R137" t="n">
         <v>1</v>
       </c>
       <c r="S137" t="n">
-        <v>0.1800282121622565</v>
+        <v>-0.05826143648355836</v>
       </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U137" t="n">
-        <v>0.1800282121622565</v>
+        <v>-0.05826143648355836</v>
       </c>
       <c r="V137" t="n">
-        <v>0.4604020439379574</v>
+        <v>0.4708083309583022</v>
       </c>
       <c r="W137" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y137" t="n">
-        <v>2.278057088950883</v>
+        <v>1.561612075226278</v>
       </c>
       <c r="Z137" t="n">
-        <v>2.278057088950883</v>
+        <v>1.561612075226278</v>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr"/>
@@ -13907,98 +13907,98 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F138" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G138" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="H138" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I138" t="n">
-        <v>5.75</v>
+        <v>2.2</v>
       </c>
       <c r="J138" t="n">
-        <v>0.5854612684547574</v>
+        <v>0.3079833522512297</v>
       </c>
       <c r="K138" t="n">
-        <v>0.2495913828675545</v>
+        <v>0.2580401059402194</v>
       </c>
       <c r="L138" t="n">
-        <v>0.1649473486776882</v>
+        <v>0.4339765418085509</v>
       </c>
       <c r="M138" t="n">
-        <v>0.05435488883238682</v>
+        <v>0.04739636997701502</v>
       </c>
       <c r="N138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O138" t="n">
-        <v>0.5299375613515956</v>
+        <v>0.1581151798668755</v>
       </c>
       <c r="P138" t="n">
-        <v>0.3357546466828741</v>
+        <v>0.3901184052593505</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.1343077919655302</v>
+        <v>0.451766414873774</v>
       </c>
       <c r="R138" t="n">
         <v>1</v>
       </c>
       <c r="S138" t="n">
-        <v>-0.05552370710316179</v>
+        <v>0.01778987306522306</v>
       </c>
       <c r="T138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U138" t="n">
-        <v>-0.05552370710316179</v>
+        <v>0.01778987306522306</v>
       </c>
       <c r="V138" t="n">
-        <v>0.5299375613515956</v>
+        <v>0.451766414873774</v>
       </c>
       <c r="W138" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y138" t="n">
-        <v>4.711374581896096</v>
+        <v>1.777409499537162</v>
       </c>
       <c r="Z138" t="n">
-        <v>4.711374581896096</v>
+        <v>1.777409499537162</v>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr"/>
@@ -14006,98 +14006,98 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F139" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G139" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="H139" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="I139" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="J139" t="n">
-        <v>0.4157043879907621</v>
+        <v>0.5804311774461028</v>
       </c>
       <c r="K139" t="n">
-        <v>0.3187066974595842</v>
+        <v>0.2280265339966833</v>
       </c>
       <c r="L139" t="n">
-        <v>0.2655889145496536</v>
+        <v>0.1915422885572139</v>
       </c>
       <c r="M139" t="n">
-        <v>0.04589371980676349</v>
+        <v>0.04415584415584406</v>
       </c>
       <c r="N139" t="n">
         <v>1</v>
       </c>
       <c r="O139" t="n">
-        <v>0.4679788688718871</v>
+        <v>0.4902520027614342</v>
       </c>
       <c r="P139" t="n">
-        <v>0.3424182063032361</v>
+        <v>0.3267975762170628</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.1896029248248768</v>
+        <v>0.1829504210215032</v>
       </c>
       <c r="R139" t="n">
         <v>1</v>
       </c>
       <c r="S139" t="n">
-        <v>0.05227448088112496</v>
+        <v>-0.09017917468466868</v>
       </c>
       <c r="T139" t="n">
         <v>1</v>
       </c>
       <c r="U139" t="n">
-        <v>0.05227448088112496</v>
+        <v>-0.09017917468466868</v>
       </c>
       <c r="V139" t="n">
-        <v>0.4679788688718871</v>
+        <v>0.4902520027614342</v>
       </c>
       <c r="W139" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y139" t="n">
-        <v>5.16660377057429</v>
+        <v>1.514394042621623</v>
       </c>
       <c r="Z139" t="n">
-        <v>5.16660377057429</v>
+        <v>1.514394042621623</v>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr"/>
@@ -14105,98 +14105,98 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.4375</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F140" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G140" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="H140" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="I140" t="n">
-        <v>11</v>
+        <v>1.85</v>
       </c>
       <c r="J140" t="n">
-        <v>0.7321711568938194</v>
+        <v>0.2449114678139998</v>
       </c>
       <c r="K140" t="n">
-        <v>0.1812995245641839</v>
+        <v>0.2387886811186497</v>
       </c>
       <c r="L140" t="n">
-        <v>0.08652931854199684</v>
+        <v>0.5162998510673507</v>
       </c>
       <c r="M140" t="n">
-        <v>0.05061605061605046</v>
+        <v>0.04695079695079674</v>
       </c>
       <c r="N140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O140" t="n">
-        <v>0.6358624453782491</v>
+        <v>0.1355951324524358</v>
       </c>
       <c r="P140" t="n">
-        <v>0.3086115268166349</v>
+        <v>0.3623243469936115</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.055526027805116</v>
+        <v>0.5020805205539526</v>
       </c>
       <c r="R140" t="n">
         <v>1</v>
       </c>
       <c r="S140" t="n">
-        <v>-0.0963087115155703</v>
+        <v>-0.01421933051339808</v>
       </c>
       <c r="T140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U140" t="n">
-        <v>-0.0963087115155703</v>
+        <v>-0.01421933051339808</v>
       </c>
       <c r="V140" t="n">
-        <v>0.6358624453782491</v>
+        <v>0.5020805205539526</v>
       </c>
       <c r="W140" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y140" t="n">
-        <v>5.358274688910284</v>
+        <v>1.846698970723272</v>
       </c>
       <c r="Z140" t="n">
-        <v>5.358274688910284</v>
+        <v>1.846698970723272</v>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr"/>
@@ -14204,98 +14204,98 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.5625</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F141" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G141" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="H141" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I141" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="J141" t="n">
-        <v>0.5885015844273427</v>
+        <v>0.5424476295479603</v>
       </c>
       <c r="K141" t="n">
-        <v>0.2648257129923042</v>
+        <v>0.2260198456449835</v>
       </c>
       <c r="L141" t="n">
-        <v>0.1466727025803531</v>
+        <v>0.2315325248070562</v>
       </c>
       <c r="M141" t="n">
-        <v>0.04890788224121545</v>
+        <v>0.05342624854819977</v>
       </c>
       <c r="N141" t="n">
         <v>1</v>
       </c>
       <c r="O141" t="n">
-        <v>0.5915942898402606</v>
+        <v>0.4699022232407611</v>
       </c>
       <c r="P141" t="n">
-        <v>0.3204878649616577</v>
+        <v>0.3262462883616376</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.08791784519808173</v>
+        <v>0.2038514883976014</v>
       </c>
       <c r="R141" t="n">
         <v>1</v>
       </c>
       <c r="S141" t="n">
-        <v>0.003092705412917951</v>
+        <v>-0.07254540630719924</v>
       </c>
       <c r="T141" t="n">
         <v>1</v>
       </c>
       <c r="U141" t="n">
-        <v>0.003092705412917951</v>
+        <v>-0.07254540630719924</v>
       </c>
       <c r="V141" t="n">
-        <v>0.5915942898402606</v>
+        <v>0.4699022232407611</v>
       </c>
       <c r="W141" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y141" t="n">
-        <v>5.905799690564663</v>
+        <v>1.504113136730728</v>
       </c>
       <c r="Z141" t="n">
-        <v>5.905799690564663</v>
+        <v>1.504113136730728</v>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr"/>
@@ -14303,98 +14303,98 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>45533.58333333334</v>
+        <v>45536.4375</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F142" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G142" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="H142" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I142" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="J142" t="n">
-        <v>0.550173120294781</v>
+        <v>0.3883495145631068</v>
       </c>
       <c r="K142" t="n">
-        <v>0.2338235761252819</v>
+        <v>0.2718446601941747</v>
       </c>
       <c r="L142" t="n">
-        <v>0.2160033035799371</v>
+        <v>0.3398058252427185</v>
       </c>
       <c r="M142" t="n">
-        <v>0.06918217633473711</v>
+        <v>0.05102040816326525</v>
       </c>
       <c r="N142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>0.4567177506111351</v>
+        <v>0.3564029345553034</v>
       </c>
       <c r="P142" t="n">
-        <v>0.4011109620053718</v>
+        <v>0.4294844966159586</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.142171287383493</v>
+        <v>0.2141125688287381</v>
       </c>
       <c r="R142" t="n">
         <v>1</v>
       </c>
       <c r="S142" t="n">
-        <v>-0.09345536968364598</v>
+        <v>0.1576398364217838</v>
       </c>
       <c r="T142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>-0.09345536968364598</v>
+        <v>0.1576398364217838</v>
       </c>
       <c r="V142" t="n">
-        <v>0.4567177506111351</v>
+        <v>0.4294844966159586</v>
       </c>
       <c r="W142" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y142" t="n">
-        <v>3.607536189625261</v>
+        <v>2.004255503155188</v>
       </c>
       <c r="Z142" t="n">
-        <v>3.607536189625261</v>
+        <v>2.004255503155188</v>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
@@ -14402,98 +14402,98 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>45533.6875</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F143" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G143" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H143" t="n">
         <v>8</v>
       </c>
-      <c r="H143" t="n">
-        <v>5</v>
-      </c>
       <c r="I143" t="n">
-        <v>1.38</v>
+        <v>11</v>
       </c>
       <c r="J143" t="n">
-        <v>0.1190887124611667</v>
+        <v>0.7942238267148014</v>
       </c>
       <c r="K143" t="n">
-        <v>0.1905419399378667</v>
+        <v>0.1191335740072202</v>
       </c>
       <c r="L143" t="n">
-        <v>0.6903693476009666</v>
+        <v>0.08664259927797834</v>
       </c>
       <c r="M143" t="n">
-        <v>0.04963768115942035</v>
+        <v>0.04924242424242431</v>
       </c>
       <c r="N143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O143" t="n">
-        <v>0.106492155857118</v>
+        <v>0.6268951432858159</v>
       </c>
       <c r="P143" t="n">
-        <v>0.3852108218483214</v>
+        <v>0.2780414885682527</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.5082970222945606</v>
+        <v>0.09506336814593143</v>
       </c>
       <c r="R143" t="n">
         <v>1</v>
       </c>
       <c r="S143" t="n">
-        <v>-0.1820723253064059</v>
+        <v>-0.1673286834289855</v>
       </c>
       <c r="T143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U143" t="n">
-        <v>-0.1820723253064059</v>
+        <v>-0.1673286834289855</v>
       </c>
       <c r="V143" t="n">
-        <v>0.5082970222945606</v>
+        <v>0.6268951432858159</v>
       </c>
       <c r="W143" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y143" t="n">
-        <v>3.23971724605642</v>
+        <v>1.739595044086204</v>
       </c>
       <c r="Z143" t="n">
-        <v>3.23971724605642</v>
+        <v>1.739595044086204</v>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr"/>
@@ -14501,98 +14501,98 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>45535.5</v>
+        <v>45548.64583333334</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F144" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G144" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="H144" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="I144" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="J144" t="n">
-        <v>0.7566826593557231</v>
+        <v>0.7046463956269218</v>
       </c>
       <c r="K144" t="n">
-        <v>0.1644962302947224</v>
+        <v>0.1703963102152375</v>
       </c>
       <c r="L144" t="n">
-        <v>0.07882111034955448</v>
+        <v>0.1249572941578408</v>
       </c>
       <c r="M144" t="n">
-        <v>0.05724637681159428</v>
+        <v>0.06703121439963544</v>
       </c>
       <c r="N144" t="n">
         <v>1</v>
       </c>
       <c r="O144" t="n">
-        <v>0.641325106264287</v>
+        <v>0.6517349581870295</v>
       </c>
       <c r="P144" t="n">
-        <v>0.2969699696794604</v>
+        <v>0.2694621337434124</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.06170492405625271</v>
+        <v>0.078802908069558</v>
       </c>
       <c r="R144" t="n">
         <v>1</v>
       </c>
       <c r="S144" t="n">
-        <v>-0.1153575530914361</v>
+        <v>-0.05291143743989224</v>
       </c>
       <c r="T144" t="n">
         <v>1</v>
       </c>
       <c r="U144" t="n">
-        <v>-0.1153575530914361</v>
+        <v>-0.05291143743989224</v>
       </c>
       <c r="V144" t="n">
-        <v>0.641325106264287</v>
+        <v>0.6517349581870295</v>
       </c>
       <c r="W144" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y144" t="n">
-        <v>5.223351170564668</v>
+        <v>2.266724228087704</v>
       </c>
       <c r="Z144" t="n">
-        <v>5.223351170564668</v>
+        <v>2.266724228087704</v>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr"/>
@@ -14600,98 +14600,98 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45549.4375</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F145" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G145" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="H145" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="I145" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="J145" t="n">
-        <v>0.3342981186685962</v>
+        <v>0.3570181225503512</v>
       </c>
       <c r="K145" t="n">
-        <v>0.2836468885672938</v>
+        <v>0.2347394155768559</v>
       </c>
       <c r="L145" t="n">
-        <v>0.3820549927641099</v>
+        <v>0.4082424618727929</v>
       </c>
       <c r="M145" t="n">
-        <v>0.06833642547928265</v>
+        <v>0.06501074557778153</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O145" t="n">
-        <v>0.2432746552537438</v>
+        <v>0.2609738702362804</v>
       </c>
       <c r="P145" t="n">
-        <v>0.4059696229824164</v>
+        <v>0.3151971158037243</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.3507557217638398</v>
+        <v>0.4238290139599953</v>
       </c>
       <c r="R145" t="n">
         <v>1</v>
       </c>
       <c r="S145" t="n">
-        <v>0.1223227344151226</v>
+        <v>0.01558655208720239</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U145" t="n">
-        <v>0.1223227344151226</v>
+        <v>0.01558655208720239</v>
       </c>
       <c r="V145" t="n">
-        <v>0.4059696229824164</v>
+        <v>0.4238290139599953</v>
       </c>
       <c r="W145" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y145" t="n">
-        <v>5.024752965335175</v>
+        <v>1.663317948024701</v>
       </c>
       <c r="Z145" t="n">
-        <v>5.024752965335175</v>
+        <v>1.663317948024701</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr"/>
@@ -14699,98 +14699,98 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>vZqDdBhB</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45549.4375</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F146" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G146" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="H146" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="I146" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="J146" t="n">
-        <v>0.3599402826349265</v>
+        <v>0.5210981189628877</v>
       </c>
       <c r="K146" t="n">
-        <v>0.2958259197905802</v>
+        <v>0.2501270971021861</v>
       </c>
       <c r="L146" t="n">
-        <v>0.3442337975744933</v>
+        <v>0.2287747839349263</v>
       </c>
       <c r="M146" t="n">
-        <v>0.05636450051849295</v>
+        <v>0.06612466124661243</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O146" t="n">
-        <v>0.3608103508535314</v>
+        <v>0.5220803696232176</v>
       </c>
       <c r="P146" t="n">
-        <v>0.387361788609618</v>
+        <v>0.3572046928668826</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.2518278605368507</v>
+        <v>0.1207149375098998</v>
       </c>
       <c r="R146" t="n">
         <v>1</v>
       </c>
       <c r="S146" t="n">
-        <v>0.0915358688190378</v>
+        <v>0.0009822506603298642</v>
       </c>
       <c r="T146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U146" t="n">
-        <v>0.0915358688190378</v>
+        <v>0.0009822506603298642</v>
       </c>
       <c r="V146" t="n">
-        <v>0.387361788609618</v>
+        <v>0.5220803696232176</v>
       </c>
       <c r="W146" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y146" t="n">
-        <v>4.755902953368276</v>
+        <v>1.979946800894633</v>
       </c>
       <c r="Z146" t="n">
-        <v>4.755902953368276</v>
+        <v>1.979946800894633</v>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr"/>
@@ -14798,98 +14798,98 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>r7j4bXNb</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45549.4375</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F147" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G147" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="H147" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="I147" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="J147" t="n">
-        <v>0.3924050632911393</v>
+        <v>0.1877107530910453</v>
       </c>
       <c r="K147" t="n">
-        <v>0.3037974683544304</v>
+        <v>0.2502810041213938</v>
       </c>
       <c r="L147" t="n">
-        <v>0.3037974683544304</v>
+        <v>0.562008242787561</v>
       </c>
       <c r="M147" t="n">
-        <v>0.06182795698924726</v>
+        <v>0.06546906187624746</v>
       </c>
       <c r="N147" t="n">
         <v>2</v>
       </c>
       <c r="O147" t="n">
-        <v>0.2850745173118185</v>
+        <v>0.1885000430231332</v>
       </c>
       <c r="P147" t="n">
-        <v>0.3138896305174972</v>
+        <v>0.3498987717869242</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.4010358521706843</v>
+        <v>0.4616011851899426</v>
       </c>
       <c r="R147" t="n">
         <v>1</v>
       </c>
       <c r="S147" t="n">
-        <v>0.09723838381625388</v>
+        <v>-0.1004070575976184</v>
       </c>
       <c r="T147" t="n">
         <v>2</v>
       </c>
       <c r="U147" t="n">
-        <v>0.09723838381625388</v>
+        <v>-0.1004070575976184</v>
       </c>
       <c r="V147" t="n">
-        <v>0.4010358521706843</v>
+        <v>0.4616011851899426</v>
       </c>
       <c r="W147" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y147" t="n">
-        <v>4.948330554050862</v>
+        <v>1.367226656419602</v>
       </c>
       <c r="Z147" t="n">
-        <v>4.948330554050862</v>
+        <v>1.367226656419602</v>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr"/>
@@ -14897,98 +14897,98 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>WSMotj8U</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45549.4375</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F148" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G148" t="n">
-        <v>2.63</v>
+        <v>1.44</v>
       </c>
       <c r="H148" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I148" t="n">
-        <v>2.63</v>
+        <v>6.5</v>
       </c>
       <c r="J148" t="n">
-        <v>0.3605514316012725</v>
+        <v>0.6487025948103793</v>
       </c>
       <c r="K148" t="n">
-        <v>0.2788971367974549</v>
+        <v>0.2075848303393213</v>
       </c>
       <c r="L148" t="n">
-        <v>0.3605514316012725</v>
+        <v>0.1437125748502994</v>
       </c>
       <c r="M148" t="n">
-        <v>0.05457392082308221</v>
+        <v>0.07051282051282048</v>
       </c>
       <c r="N148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O148" t="n">
-        <v>0.2680095599457526</v>
+        <v>0.5556668482530058</v>
       </c>
       <c r="P148" t="n">
-        <v>0.3623258091734967</v>
+        <v>0.2890699526820363</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.3696646308807507</v>
+        <v>0.1552631990649579</v>
       </c>
       <c r="R148" t="n">
         <v>1</v>
       </c>
       <c r="S148" t="n">
-        <v>0.009113199279478179</v>
+        <v>-0.09303574655737346</v>
       </c>
       <c r="T148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U148" t="n">
-        <v>0.009113199279478179</v>
+        <v>-0.09303574655737346</v>
       </c>
       <c r="V148" t="n">
-        <v>0.3696646308807507</v>
+        <v>0.5556668482530058</v>
       </c>
       <c r="W148" t="n">
-        <v>2.63</v>
+        <v>1.44</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y148" t="n">
-        <v>3.761619154292541</v>
+        <v>1.751195620325689</v>
       </c>
       <c r="Z148" t="n">
-        <v>3.761619154292541</v>
+        <v>1.751195620325689</v>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr"/>
@@ -14996,98 +14996,98 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>tI0qkTpo</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.4375</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F149" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G149" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="H149" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I149" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="J149" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.3988317051062543</v>
       </c>
       <c r="K149" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2603484741665827</v>
       </c>
       <c r="L149" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.3408198207271628</v>
       </c>
       <c r="M149" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.06694605630775863</v>
       </c>
       <c r="N149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O149" t="n">
-        <v>0.3330507231381066</v>
+        <v>0.4341752177734234</v>
       </c>
       <c r="P149" t="n">
-        <v>0.2967069643730315</v>
+        <v>0.3142214322882965</v>
       </c>
       <c r="Q149" t="n">
-        <v>0.370242312488862</v>
+        <v>0.2516033499382802</v>
       </c>
       <c r="R149" t="n">
         <v>1</v>
       </c>
       <c r="S149" t="n">
-        <v>0.1081136927069891</v>
+        <v>0.03534351266716912</v>
       </c>
       <c r="T149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U149" t="n">
-        <v>0.1081136927069891</v>
+        <v>0.03534351266716912</v>
       </c>
       <c r="V149" t="n">
-        <v>0.370242312488862</v>
+        <v>0.4341752177734234</v>
       </c>
       <c r="W149" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y149" t="n">
-        <v>4.669947259238117</v>
+        <v>1.777267333291799</v>
       </c>
       <c r="Z149" t="n">
-        <v>4.669947259238117</v>
+        <v>1.777267333291799</v>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr"/>
@@ -15095,98 +15095,98 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>x4pn9lxH</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.5625</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F150" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G150" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="H150" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="I150" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
-        <v>0.4100200400801604</v>
+        <v>0.1100846805234796</v>
       </c>
       <c r="K150" t="n">
-        <v>0.2857715430861724</v>
+        <v>0.170130869899923</v>
       </c>
       <c r="L150" t="n">
-        <v>0.3042084168336673</v>
+        <v>0.7197844495765975</v>
       </c>
       <c r="M150" t="n">
-        <v>0.06039355688724557</v>
+        <v>0.06869600987248026</v>
       </c>
       <c r="N150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O150" t="n">
-        <v>0.499160581656248</v>
+        <v>0.05898923245477277</v>
       </c>
       <c r="P150" t="n">
-        <v>0.3154350035908005</v>
+        <v>0.299416402447634</v>
       </c>
       <c r="Q150" t="n">
-        <v>0.1854044147529515</v>
+        <v>0.6415943650975932</v>
       </c>
       <c r="R150" t="n">
         <v>1</v>
       </c>
       <c r="S150" t="n">
-        <v>0.0891405415760877</v>
+        <v>-0.07819008447900433</v>
       </c>
       <c r="T150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U150" t="n">
-        <v>0.0891405415760877</v>
+        <v>-0.07819008447900433</v>
       </c>
       <c r="V150" t="n">
-        <v>0.499160581656248</v>
+        <v>0.6415943650975932</v>
       </c>
       <c r="W150" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y150" t="n">
-        <v>5.842381991328407</v>
+        <v>2.132651923045866</v>
       </c>
       <c r="Z150" t="n">
-        <v>5.842381991328407</v>
+        <v>2.132651923045866</v>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr"/>
@@ -15194,78 +15194,78 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>45536.58333333334</v>
+        <v>45535.5625</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F151" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G151" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="H151" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I151" t="n">
-        <v>2.8</v>
+        <v>5.75</v>
       </c>
       <c r="J151" t="n">
-        <v>0.4064516129032258</v>
+        <v>0.5835193829916785</v>
       </c>
       <c r="K151" t="n">
-        <v>0.2596774193548387</v>
+        <v>0.2520803734524051</v>
       </c>
       <c r="L151" t="n">
-        <v>0.3338709677419355</v>
+        <v>0.1644002435559164</v>
       </c>
       <c r="M151" t="n">
-        <v>0.06970324361628721</v>
+        <v>0.05786366076221139</v>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>0.5018938258153822</v>
+        <v>0.4303029010699506</v>
       </c>
       <c r="P151" t="n">
-        <v>0.3319952681193868</v>
+        <v>0.4600072380500901</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.166110906065231</v>
+        <v>0.1096898608799593</v>
       </c>
       <c r="R151" t="n">
         <v>1</v>
       </c>
       <c r="S151" t="n">
-        <v>0.09544221291215643</v>
+        <v>0.2079268645976849</v>
       </c>
       <c r="T151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>0.09544221291215643</v>
+        <v>0.2079268645976849</v>
       </c>
       <c r="V151" t="n">
-        <v>0.5018938258153822</v>
+        <v>0.4600072380500901</v>
       </c>
       <c r="W151" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
@@ -15273,19 +15273,19 @@
         </is>
       </c>
       <c r="Y151" t="n">
-        <v>5.932107177118169</v>
+        <v>2.276452186967843</v>
       </c>
       <c r="Z151" t="n">
-        <v>5.932107177118169</v>
+        <v>2.276452186967843</v>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr"/>
@@ -15293,78 +15293,78 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>45536.59375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F152" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G152" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="H152" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I152" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J152" t="n">
-        <v>0.2606635071090047</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="K152" t="n">
-        <v>0.3127962085308056</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="L152" t="n">
-        <v>0.4265402843601895</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="M152" t="n">
-        <v>0.06565656565656575</v>
+        <v>0.05106209150326801</v>
       </c>
       <c r="N152" t="n">
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>0.3310321684477963</v>
+        <v>0.3654488747004993</v>
       </c>
       <c r="P152" t="n">
-        <v>0.3868944892678394</v>
+        <v>0.4495875931871142</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.2820733422843643</v>
+        <v>0.1849635321123865</v>
       </c>
       <c r="R152" t="n">
         <v>1</v>
       </c>
       <c r="S152" t="n">
-        <v>0.07409828073703378</v>
+        <v>0.1522692877071297</v>
       </c>
       <c r="T152" t="n">
         <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>0.07409828073703378</v>
+        <v>0.1522692877071297</v>
       </c>
       <c r="V152" t="n">
-        <v>0.3868944892678394</v>
+        <v>0.4495875931871142</v>
       </c>
       <c r="W152" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
@@ -15372,19 +15372,19 @@
         </is>
       </c>
       <c r="Y152" t="n">
-        <v>4.578090626125518</v>
+        <v>2.234095907041282</v>
       </c>
       <c r="Z152" t="n">
-        <v>4.578090626125518</v>
+        <v>2.234095907041282</v>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr"/>
@@ -15392,101 +15392,1586 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>77</v>
+      </c>
+      <c r="F153" t="n">
+        <v>771</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H153" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I153" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0.3266613290632506</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0.2786228983186549</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.3947157726180944</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0.05561189993238691</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0.3320283417355943</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0.3453296657883106</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0.322641992476095</v>
+      </c>
+      <c r="R153" t="n">
+        <v>1</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0.06670676746965576</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>0.06670676746965576</v>
+      </c>
+      <c r="V153" t="n">
+        <v>0.3453296657883106</v>
+      </c>
+      <c r="W153" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y153" t="n">
+        <v>1.674944850474646</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>1.674944850474646</v>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>77</v>
+      </c>
+      <c r="F154" t="n">
+        <v>771</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H154" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I154" t="n">
+        <v>7</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.643819671016857</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0.2200584556824361</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0.1361218733007069</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0.0494797007499086</v>
+      </c>
+      <c r="N154" t="n">
+        <v>1</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0.5061864550305712</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0.3036078548501754</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0.1902056901192534</v>
+      </c>
+      <c r="R154" t="n">
+        <v>1</v>
+      </c>
+      <c r="S154" t="n">
+        <v>-0.1376332159862858</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1</v>
+      </c>
+      <c r="U154" t="n">
+        <v>-0.1376332159862858</v>
+      </c>
+      <c r="V154" t="n">
+        <v>0.5061864550305712</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y154" t="n">
+        <v>1.498183898404188</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>1.498183898404188</v>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>77</v>
+      </c>
+      <c r="F155" t="n">
+        <v>771</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H155" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I155" t="n">
+        <v>5</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0.5674708261793209</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0.2429939178767861</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0.1895352559438931</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0.05521265161983724</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0.4017898345438949</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0.4042744950534848</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0.1939356704026204</v>
+      </c>
+      <c r="R155" t="n">
+        <v>1</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0.1612805771766987</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0.1612805771766987</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0.4042744950534848</v>
+      </c>
+      <c r="W155" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y155" t="n">
+        <v>2.04989632115064</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>2.04989632115064</v>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>77</v>
+      </c>
+      <c r="F156" t="n">
+        <v>771</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2</v>
+      </c>
+      <c r="H156" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I156" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0.471947194719472</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0.286028602860286</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0.2420242024202421</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0.05944055944055937</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0.250718210002577</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0.4444843561198077</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0.3047974338776155</v>
+      </c>
+      <c r="R156" t="n">
+        <v>1</v>
+      </c>
+      <c r="S156" t="n">
+        <v>0.1584557532595217</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>0.1584557532595217</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0.4444843561198077</v>
+      </c>
+      <c r="W156" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y156" t="n">
+        <v>2.213351040916095</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>2.213351040916095</v>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>77</v>
+      </c>
+      <c r="F157" t="n">
+        <v>771</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H157" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I157" t="n">
+        <v>5</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0.5446293494704992</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0.264750378214826</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.1906202723146747</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0.04920634920634925</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0.3793679277017606</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0.4314688135302905</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0.1891632587679486</v>
+      </c>
+      <c r="R157" t="n">
+        <v>1</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0.1667184353154645</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0.1667184353154645</v>
+      </c>
+      <c r="V157" t="n">
+        <v>0.4314688135302905</v>
+      </c>
+      <c r="W157" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y157" t="n">
+        <v>2.160442331207901</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>2.160442331207901</v>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>77</v>
+      </c>
+      <c r="F158" t="n">
+        <v>771</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I158" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0.4652011310772599</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0.2804889172671714</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0.2543099516555687</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0.04858919177427068</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0.3893097338466229</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0.4100645711018675</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0.2006256950515095</v>
+      </c>
+      <c r="R158" t="n">
+        <v>1</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0.1295756538346961</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0.1295756538346961</v>
+      </c>
+      <c r="V158" t="n">
+        <v>0.4100645711018675</v>
+      </c>
+      <c r="W158" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y158" t="n">
+        <v>2.073433215653907</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>2.073433215653907</v>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>148</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H159" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="I159" t="n">
+        <v>10</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.7547169811320755</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0.1509433962264151</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0.09433962264150944</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0.6508405784276196</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0.2865014175609947</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0.06265800401138578</v>
+      </c>
+      <c r="R159" t="n">
+        <v>1</v>
+      </c>
+      <c r="S159" t="n">
+        <v>-0.103876402704456</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1</v>
+      </c>
+      <c r="U159" t="n">
+        <v>-0.103876402704456</v>
+      </c>
+      <c r="V159" t="n">
+        <v>0.6508405784276196</v>
+      </c>
+      <c r="W159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y159" t="n">
+        <v>5.431867327720162</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>5.431867327720162</v>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>148</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H160" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I160" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0.3291472554182702</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0.2916751063398825</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0.3791776382418473</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0.05491452991452994</v>
+      </c>
+      <c r="N160" t="n">
+        <v>2</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0.2453936451940474</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0.3459244475367921</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0.4086819072691604</v>
+      </c>
+      <c r="R160" t="n">
+        <v>1</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0.02950426902731307</v>
+      </c>
+      <c r="T160" t="n">
+        <v>2</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0.02950426902731307</v>
+      </c>
+      <c r="V160" t="n">
+        <v>0.4086819072691604</v>
+      </c>
+      <c r="W160" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y160" t="n">
+        <v>4.351599757582885</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>4.351599757582885</v>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>45535.59375</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>148</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H161" t="n">
+        <v>3</v>
+      </c>
+      <c r="I161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0.3409090909090909</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0.3181818181818181</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0.3409090909090909</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0.04761904761904767</v>
+      </c>
+      <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0.3912910675884506</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0.3213656271933518</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0.2873433052181975</v>
+      </c>
+      <c r="R161" t="n">
+        <v>1</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0.05038197667935973</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0.05038197667935973</v>
+      </c>
+      <c r="V161" t="n">
+        <v>0.3912910675884506</v>
+      </c>
+      <c r="W161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y161" t="n">
+        <v>4.386227627286668</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>4.386227627286668</v>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>148</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3</v>
+      </c>
+      <c r="I162" t="n">
+        <v>3</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0.3658536585365854</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0.3170731707317074</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0.3170731707317074</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0.0512820512820511</v>
+      </c>
+      <c r="N162" t="n">
+        <v>2</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0.2799594354301689</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0.3087305780185021</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0.4113099865513289</v>
+      </c>
+      <c r="R162" t="n">
+        <v>1</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0.09423681581962157</v>
+      </c>
+      <c r="T162" t="n">
+        <v>2</v>
+      </c>
+      <c r="U162" t="n">
+        <v>0.09423681581962157</v>
+      </c>
+      <c r="V162" t="n">
+        <v>0.4113099865513289</v>
+      </c>
+      <c r="W162" t="n">
+        <v>3</v>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y162" t="n">
+        <v>5.020553960049551</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>5.020553960049551</v>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>148</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H163" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I163" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0.3437815975733064</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0.2780586450960567</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0.3781597573306371</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0.05775401069518704</v>
+      </c>
+      <c r="N163" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0.2925257078685912</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0.3520892050875199</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0.3553850870438891</v>
+      </c>
+      <c r="R163" t="n">
+        <v>1</v>
+      </c>
+      <c r="S163" t="n">
+        <v>-0.02277467028674796</v>
+      </c>
+      <c r="T163" t="n">
+        <v>2</v>
+      </c>
+      <c r="U163" t="n">
+        <v>-0.02277467028674796</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0.3553850870438891</v>
+      </c>
+      <c r="W163" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y163" t="n">
+        <v>3.303133433288927</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>3.303133433288927</v>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>148</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H164" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I164" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.4931894569255263</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0.2770564302140457</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0.2297541128604281</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0.06158029550729749</v>
+      </c>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0.4653383307022608</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0.3352370726217512</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0.199424596675988</v>
+      </c>
+      <c r="R164" t="n">
+        <v>1</v>
+      </c>
+      <c r="S164" t="n">
+        <v>-0.02785112622326552</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1</v>
+      </c>
+      <c r="U164" t="n">
+        <v>-0.02785112622326552</v>
+      </c>
+      <c r="V164" t="n">
+        <v>0.4653383307022608</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y164" t="n">
+        <v>4.344658311786481</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>4.344658311786481</v>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>148</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H165" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I165" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0.3800403225806452</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0.2923387096774194</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0.3276209677419355</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0.0525198938992042</v>
+      </c>
+      <c r="N165" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0.4257474503218577</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0.360667622841149</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0.2135849268369934</v>
+      </c>
+      <c r="R165" t="n">
+        <v>1</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0.04570712774121249</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1</v>
+      </c>
+      <c r="U165" t="n">
+        <v>0.04570712774121249</v>
+      </c>
+      <c r="V165" t="n">
+        <v>0.4257474503218577</v>
+      </c>
+      <c r="W165" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y165" t="n">
+        <v>4.681986193518147</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>4.681986193518147</v>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>148</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H166" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I166" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0.4120836560805577</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0.249419054996127</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0.3384972889233152</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0.05508336057535157</v>
+      </c>
+      <c r="N166" t="n">
+        <v>1</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0.4149069107896232</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0.3561979998417794</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>0.2288950893685975</v>
+      </c>
+      <c r="R166" t="n">
+        <v>1</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0.002823254709065526</v>
+      </c>
+      <c r="T166" t="n">
+        <v>1</v>
+      </c>
+      <c r="U166" t="n">
+        <v>0.002823254709065526</v>
+      </c>
+      <c r="V166" t="n">
+        <v>0.4149069107896232</v>
+      </c>
+      <c r="W166" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y166" t="n">
+        <v>4.14845238223409</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>4.14845238223409</v>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>45536.59375</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>148</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G167" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H167" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I167" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0.2719249862107005</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0.3281853281853282</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0.3998896856039714</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0.05070993914807298</v>
+      </c>
+      <c r="N167" t="n">
+        <v>1</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0.3616578616745702</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0.3606925673308696</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0.2776495709945602</v>
+      </c>
+      <c r="R167" t="n">
+        <v>1</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0.08973287546386971</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1</v>
+      </c>
+      <c r="U167" t="n">
+        <v>0.08973287546386971</v>
+      </c>
+      <c r="V167" t="n">
+        <v>0.3616578616745702</v>
+      </c>
+      <c r="W167" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y167" t="n">
+        <v>4.482733432872568</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>4.482733432872568</v>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
           <t>YN50iYWr</t>
         </is>
       </c>
-      <c r="B153" s="2" t="n">
+      <c r="B168" s="2" t="n">
         <v>45536.6875</v>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>real madrid</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>betis</t>
         </is>
       </c>
-      <c r="E153" t="n">
+      <c r="E168" t="n">
         <v>148</v>
       </c>
-      <c r="F153" t="n">
+      <c r="F168" t="n">
         <v>1481</v>
       </c>
-      <c r="G153" t="n">
+      <c r="G168" t="n">
         <v>1.29</v>
       </c>
-      <c r="H153" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I153" t="n">
-        <v>9</v>
-      </c>
-      <c r="J153" t="n">
-        <v>0.725753243897075</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0.1702221244776776</v>
-      </c>
-      <c r="L153" t="n">
-        <v>0.1040246316252474</v>
-      </c>
-      <c r="M153" t="n">
-        <v>0.06812309137890527</v>
-      </c>
-      <c r="N153" t="n">
-        <v>1</v>
-      </c>
-      <c r="O153" t="n">
-        <v>0.6587689867531538</v>
-      </c>
-      <c r="P153" t="n">
-        <v>0.2770756473041025</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>0.06415536594274387</v>
-      </c>
-      <c r="R153" t="n">
-        <v>1</v>
-      </c>
-      <c r="S153" t="n">
-        <v>-0.0669842571439212</v>
-      </c>
-      <c r="T153" t="n">
-        <v>1</v>
-      </c>
-      <c r="U153" t="n">
-        <v>-0.0669842571439212</v>
-      </c>
-      <c r="V153" t="n">
-        <v>0.6587689867531538</v>
-      </c>
-      <c r="W153" t="n">
+      <c r="H168" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I168" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0.7352198929977456</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0.164944984689929</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0.09983512231232546</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0.05436999982260993</v>
+      </c>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0.6602799744141538</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0.2757619916584588</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0.06395803392738757</v>
+      </c>
+      <c r="R168" t="n">
+        <v>1</v>
+      </c>
+      <c r="S168" t="n">
+        <v>-0.07493991858359184</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1</v>
+      </c>
+      <c r="U168" t="n">
+        <v>-0.07493991858359184</v>
+      </c>
+      <c r="V168" t="n">
+        <v>0.6602799744141538</v>
+      </c>
+      <c r="W168" t="n">
         <v>1.29</v>
       </c>
-      <c r="X153" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
-      <c r="Y153" t="n">
-        <v>5.876977470339962</v>
-      </c>
-      <c r="Z153" t="n">
-        <v>5.876977470339962</v>
-      </c>
-      <c r="AA153" t="inlineStr">
+      <c r="Y168" t="n">
+        <v>5.81297581449131</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>5.81297581449131</v>
+      </c>
+      <c r="AA168" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
+      <c r="AB168" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr"/>
+      <c r="AC168" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -28027,20 +28027,20 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>OAeKROjD</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B282" s="2" t="n">
-        <v>45558.65625</v>
+        <v>45562.65625</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -28050,55 +28050,55 @@
         <v>771</v>
       </c>
       <c r="G282" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="H282" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="I282" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="J282" t="n">
-        <v>0.6334721412704321</v>
+        <v>0.6989748369058714</v>
       </c>
       <c r="K282" t="n">
-        <v>0.2165216556767297</v>
+        <v>0.1770736253494874</v>
       </c>
       <c r="L282" t="n">
-        <v>0.1500062030528383</v>
+        <v>0.1239515377446412</v>
       </c>
       <c r="M282" t="n">
-        <v>0.06662255789276572</v>
+        <v>0.07568922305764403</v>
       </c>
       <c r="N282" t="n">
         <v>1</v>
       </c>
       <c r="O282" t="n">
-        <v>0.3867874089168166</v>
+        <v>0.5516144715110304</v>
       </c>
       <c r="P282" t="n">
-        <v>0.3710029627361938</v>
+        <v>0.3215636754423617</v>
       </c>
       <c r="Q282" t="n">
-        <v>0.2422096283469896</v>
+        <v>0.1268218530466079</v>
       </c>
       <c r="R282" t="n">
         <v>1</v>
       </c>
       <c r="S282" t="n">
-        <v>-0.2466847323536154</v>
+        <v>-0.147360365394841</v>
       </c>
       <c r="T282" t="n">
         <v>1</v>
       </c>
       <c r="U282" t="n">
-        <v>-0.2466847323536154</v>
+        <v>-0.147360365394841</v>
       </c>
       <c r="V282" t="n">
-        <v>0.3867874089168166</v>
+        <v>0.5516144715110304</v>
       </c>
       <c r="W282" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="X282" t="inlineStr">
         <is>
@@ -28106,10 +28106,10 @@
         </is>
       </c>
       <c r="Y282" t="n">
-        <v>1.878896575423982</v>
+        <v>5.42139289708825</v>
       </c>
       <c r="Z282" t="n">
-        <v>1.878896575423982</v>
+        <v>5.42139289708825</v>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
@@ -28126,20 +28126,20 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B283" s="2" t="n">
-        <v>45562.65625</v>
+        <v>45563.41666666666</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -28149,55 +28149,55 @@
         <v>771</v>
       </c>
       <c r="G283" t="n">
-        <v>1.33</v>
+        <v>6</v>
       </c>
       <c r="H283" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="I283" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="J283" t="n">
-        <v>0.6989748369058714</v>
+        <v>0.1547169811320755</v>
       </c>
       <c r="K283" t="n">
-        <v>0.1770736253494874</v>
+        <v>0.2264150943396227</v>
       </c>
       <c r="L283" t="n">
-        <v>0.1239515377446412</v>
+        <v>0.6188679245283019</v>
       </c>
       <c r="M283" t="n">
-        <v>0.07568922305764403</v>
+        <v>0.0772357723577235</v>
       </c>
       <c r="N283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O283" t="n">
-        <v>0.5516144715110304</v>
+        <v>0.1407836331480519</v>
       </c>
       <c r="P283" t="n">
-        <v>0.3215636754423617</v>
+        <v>0.4221012018591552</v>
       </c>
       <c r="Q283" t="n">
-        <v>0.1268218530466079</v>
+        <v>0.4371151649927928</v>
       </c>
       <c r="R283" t="n">
         <v>1</v>
       </c>
       <c r="S283" t="n">
-        <v>-0.147360365394841</v>
+        <v>-0.1817527595355091</v>
       </c>
       <c r="T283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U283" t="n">
-        <v>-0.147360365394841</v>
+        <v>-0.1817527595355091</v>
       </c>
       <c r="V283" t="n">
-        <v>0.5516144715110304</v>
+        <v>0.4371151649927928</v>
       </c>
       <c r="W283" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="X283" t="inlineStr">
         <is>
@@ -28205,10 +28205,10 @@
         </is>
       </c>
       <c r="Y283" t="n">
-        <v>5.42139289708825</v>
+        <v>3.424628000517036</v>
       </c>
       <c r="Z283" t="n">
-        <v>5.42139289708825</v>
+        <v>3.424628000517036</v>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
@@ -28225,20 +28225,20 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>45563.41666666666</v>
+        <v>45563.54166666666</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -28248,55 +28248,55 @@
         <v>771</v>
       </c>
       <c r="G284" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="H284" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="I284" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="J284" t="n">
-        <v>0.1547169811320755</v>
+        <v>0.2064566519135642</v>
       </c>
       <c r="K284" t="n">
-        <v>0.2264150943396227</v>
+        <v>0.2858630564957043</v>
       </c>
       <c r="L284" t="n">
-        <v>0.6188679245283019</v>
+        <v>0.5076802915907315</v>
       </c>
       <c r="M284" t="n">
-        <v>0.0772357723577235</v>
+        <v>0.07636261734622396</v>
       </c>
       <c r="N284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
-        <v>0.1407836331480519</v>
+        <v>0.3320141076950835</v>
       </c>
       <c r="P284" t="n">
-        <v>0.4221012018591552</v>
+        <v>0.3790377300990898</v>
       </c>
       <c r="Q284" t="n">
-        <v>0.4371151649927928</v>
+        <v>0.2889481622058268</v>
       </c>
       <c r="R284" t="n">
         <v>1</v>
       </c>
       <c r="S284" t="n">
-        <v>-0.1817527595355091</v>
+        <v>0.09317467360338549</v>
       </c>
       <c r="T284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U284" t="n">
-        <v>-0.1817527595355091</v>
+        <v>0.09317467360338549</v>
       </c>
       <c r="V284" t="n">
-        <v>0.4371151649927928</v>
+        <v>0.3790377300990898</v>
       </c>
       <c r="W284" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="X284" t="inlineStr">
         <is>
@@ -28304,10 +28304,10 @@
         </is>
       </c>
       <c r="Y284" t="n">
-        <v>3.424628000517036</v>
+        <v>5.083219753609731</v>
       </c>
       <c r="Z284" t="n">
-        <v>3.424628000517036</v>
+        <v>5.083219753609731</v>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
@@ -28324,20 +28324,20 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>45563.54166666666</v>
+        <v>45563.65625</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -28347,52 +28347,52 @@
         <v>771</v>
       </c>
       <c r="G285" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="H285" t="n">
         <v>3.25</v>
       </c>
       <c r="I285" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="J285" t="n">
-        <v>0.2064566519135642</v>
+        <v>0.3141116751269035</v>
       </c>
       <c r="K285" t="n">
-        <v>0.2858630564957043</v>
+        <v>0.2899492385786802</v>
       </c>
       <c r="L285" t="n">
-        <v>0.5076802915907315</v>
+        <v>0.3959390862944163</v>
       </c>
       <c r="M285" t="n">
-        <v>0.07636261734622396</v>
+        <v>0.06119370825253179</v>
       </c>
       <c r="N285" t="n">
         <v>0</v>
       </c>
       <c r="O285" t="n">
-        <v>0.3320141076950835</v>
+        <v>0.3677523027985431</v>
       </c>
       <c r="P285" t="n">
-        <v>0.3790377300990898</v>
+        <v>0.3888262886441129</v>
       </c>
       <c r="Q285" t="n">
-        <v>0.2889481622058268</v>
+        <v>0.2434214085573441</v>
       </c>
       <c r="R285" t="n">
         <v>1</v>
       </c>
       <c r="S285" t="n">
-        <v>0.09317467360338549</v>
+        <v>0.09887705006543268</v>
       </c>
       <c r="T285" t="n">
         <v>0</v>
       </c>
       <c r="U285" t="n">
-        <v>0.09317467360338549</v>
+        <v>0.09887705006543268</v>
       </c>
       <c r="V285" t="n">
-        <v>0.3790377300990898</v>
+        <v>0.3888262886441129</v>
       </c>
       <c r="W285" t="n">
         <v>3.25</v>
@@ -28403,10 +28403,10 @@
         </is>
       </c>
       <c r="Y285" t="n">
-        <v>5.083219753609731</v>
+        <v>5.214492685574628</v>
       </c>
       <c r="Z285" t="n">
-        <v>5.083219753609731</v>
+        <v>5.214492685574628</v>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
@@ -28423,20 +28423,20 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>45563.65625</v>
+        <v>45564.3125</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -28446,55 +28446,55 @@
         <v>771</v>
       </c>
       <c r="G286" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="H286" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I286" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="J286" t="n">
-        <v>0.3141116751269035</v>
+        <v>0.3441611842105263</v>
       </c>
       <c r="K286" t="n">
-        <v>0.2899492385786802</v>
+        <v>0.3053042763157894</v>
       </c>
       <c r="L286" t="n">
-        <v>0.3959390862944163</v>
+        <v>0.3505345394736841</v>
       </c>
       <c r="M286" t="n">
-        <v>0.06119370825253179</v>
+        <v>0.05658737916802448</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O286" t="n">
-        <v>0.3677523027985431</v>
+        <v>0.4378840346908894</v>
       </c>
       <c r="P286" t="n">
-        <v>0.3888262886441129</v>
+        <v>0.3651667074585944</v>
       </c>
       <c r="Q286" t="n">
-        <v>0.2434214085573441</v>
+        <v>0.1969492578505162</v>
       </c>
       <c r="R286" t="n">
         <v>1</v>
       </c>
       <c r="S286" t="n">
-        <v>0.09887705006543268</v>
+        <v>0.09372285048036316</v>
       </c>
       <c r="T286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U286" t="n">
-        <v>0.09887705006543268</v>
+        <v>0.09372285048036316</v>
       </c>
       <c r="V286" t="n">
-        <v>0.3888262886441129</v>
+        <v>0.4378840346908894</v>
       </c>
       <c r="W286" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="X286" t="inlineStr">
         <is>
@@ -28502,10 +28502,10 @@
         </is>
       </c>
       <c r="Y286" t="n">
-        <v>5.214492685574628</v>
+        <v>5.872398967641462</v>
       </c>
       <c r="Z286" t="n">
-        <v>5.214492685574628</v>
+        <v>5.872398967641462</v>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
@@ -28522,20 +28522,20 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>45564.3125</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -28545,55 +28545,55 @@
         <v>771</v>
       </c>
       <c r="G287" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="H287" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="I287" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="J287" t="n">
-        <v>0.3441611842105263</v>
+        <v>0.6690140845070423</v>
       </c>
       <c r="K287" t="n">
-        <v>0.3053042763157894</v>
+        <v>0.1971830985915493</v>
       </c>
       <c r="L287" t="n">
-        <v>0.3505345394736841</v>
+        <v>0.1338028169014084</v>
       </c>
       <c r="M287" t="n">
-        <v>0.05658737916802448</v>
+        <v>0.06766917293233088</v>
       </c>
       <c r="N287" t="n">
         <v>1</v>
       </c>
       <c r="O287" t="n">
-        <v>0.4378840346908894</v>
+        <v>0.487702311608233</v>
       </c>
       <c r="P287" t="n">
-        <v>0.3651667074585944</v>
+        <v>0.3320774123961673</v>
       </c>
       <c r="Q287" t="n">
-        <v>0.1969492578505162</v>
+        <v>0.1802202759956</v>
       </c>
       <c r="R287" t="n">
         <v>1</v>
       </c>
       <c r="S287" t="n">
-        <v>0.09372285048036316</v>
+        <v>-0.1813117728988093</v>
       </c>
       <c r="T287" t="n">
         <v>1</v>
       </c>
       <c r="U287" t="n">
-        <v>0.09372285048036316</v>
+        <v>-0.1813117728988093</v>
       </c>
       <c r="V287" t="n">
-        <v>0.4378840346908894</v>
+        <v>0.487702311608233</v>
       </c>
       <c r="W287" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="X287" t="inlineStr">
         <is>
@@ -28601,10 +28601,10 @@
         </is>
       </c>
       <c r="Y287" t="n">
-        <v>5.872398967641462</v>
+        <v>4.108958858211064</v>
       </c>
       <c r="Z287" t="n">
-        <v>5.872398967641462</v>
+        <v>4.108958858211064</v>
       </c>
       <c r="AA287" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
@@ -28629,12 +28629,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>como</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -28644,55 +28644,55 @@
         <v>771</v>
       </c>
       <c r="G288" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="H288" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="I288" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="J288" t="n">
-        <v>0.6690140845070423</v>
+        <v>0.4266958424507659</v>
       </c>
       <c r="K288" t="n">
-        <v>0.1971830985915493</v>
+        <v>0.2888402625820569</v>
       </c>
       <c r="L288" t="n">
-        <v>0.1338028169014084</v>
+        <v>0.2844638949671772</v>
       </c>
       <c r="M288" t="n">
-        <v>0.06766917293233088</v>
+        <v>0.06526806526806528</v>
       </c>
       <c r="N288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O288" t="n">
-        <v>0.487702311608233</v>
+        <v>0.3706641291075206</v>
       </c>
       <c r="P288" t="n">
-        <v>0.3320774123961673</v>
+        <v>0.3739962239464513</v>
       </c>
       <c r="Q288" t="n">
-        <v>0.1802202759956</v>
+        <v>0.2553396469460279</v>
       </c>
       <c r="R288" t="n">
         <v>1</v>
       </c>
       <c r="S288" t="n">
-        <v>-0.1813117728988093</v>
+        <v>0.08515596136439441</v>
       </c>
       <c r="T288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U288" t="n">
-        <v>-0.1813117728988093</v>
+        <v>0.08515596136439441</v>
       </c>
       <c r="V288" t="n">
-        <v>0.487702311608233</v>
+        <v>0.3739962239464513</v>
       </c>
       <c r="W288" t="n">
-        <v>1.4</v>
+        <v>3.25</v>
       </c>
       <c r="X288" t="inlineStr">
         <is>
@@ -28700,10 +28700,10 @@
         </is>
       </c>
       <c r="Y288" t="n">
-        <v>4.108958858211064</v>
+        <v>5.015608849396219</v>
       </c>
       <c r="Z288" t="n">
-        <v>4.108958858211064</v>
+        <v>5.015608849396219</v>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
@@ -28720,20 +28720,20 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45564.54166666666</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -28743,22 +28743,22 @@
         <v>771</v>
       </c>
       <c r="G289" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="H289" t="n">
         <v>3.25</v>
       </c>
       <c r="I289" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J289" t="n">
-        <v>0.4266958424507659</v>
+        <v>0.2844638949671772</v>
       </c>
       <c r="K289" t="n">
         <v>0.2888402625820569</v>
       </c>
       <c r="L289" t="n">
-        <v>0.2844638949671772</v>
+        <v>0.4266958424507659</v>
       </c>
       <c r="M289" t="n">
         <v>0.06526806526806528</v>
@@ -28767,28 +28767,28 @@
         <v>0</v>
       </c>
       <c r="O289" t="n">
-        <v>0.3706641291075206</v>
+        <v>0.283179633684656</v>
       </c>
       <c r="P289" t="n">
-        <v>0.3739962239464513</v>
+        <v>0.3783621777071274</v>
       </c>
       <c r="Q289" t="n">
-        <v>0.2553396469460279</v>
+        <v>0.3384581886082167</v>
       </c>
       <c r="R289" t="n">
         <v>1</v>
       </c>
       <c r="S289" t="n">
-        <v>0.08515596136439441</v>
+        <v>0.08952191512507046</v>
       </c>
       <c r="T289" t="n">
         <v>0</v>
       </c>
       <c r="U289" t="n">
-        <v>0.08515596136439441</v>
+        <v>0.08952191512507046</v>
       </c>
       <c r="V289" t="n">
-        <v>0.3739962239464513</v>
+        <v>0.3783621777071274</v>
       </c>
       <c r="W289" t="n">
         <v>3.25</v>
@@ -28799,10 +28799,10 @@
         </is>
       </c>
       <c r="Y289" t="n">
-        <v>5.015608849396219</v>
+        <v>5.074160018942885</v>
       </c>
       <c r="Z289" t="n">
-        <v>5.015608849396219</v>
+        <v>5.074160018942885</v>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
@@ -28819,20 +28819,20 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B290" s="2" t="n">
-        <v>45564.54166666666</v>
+        <v>45564.65625</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -28842,55 +28842,55 @@
         <v>771</v>
       </c>
       <c r="G290" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="H290" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="I290" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="J290" t="n">
-        <v>0.2844638949671772</v>
+        <v>0.6728971962616822</v>
       </c>
       <c r="K290" t="n">
-        <v>0.2888402625820569</v>
+        <v>0.2093457943925233</v>
       </c>
       <c r="L290" t="n">
-        <v>0.4266958424507659</v>
+        <v>0.1177570093457944</v>
       </c>
       <c r="M290" t="n">
-        <v>0.06526806526806528</v>
+        <v>0.06150793650793651</v>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O290" t="n">
-        <v>0.283179633684656</v>
+        <v>0.5927423185729692</v>
       </c>
       <c r="P290" t="n">
-        <v>0.3783621777071274</v>
+        <v>0.2629712806694237</v>
       </c>
       <c r="Q290" t="n">
-        <v>0.3384581886082167</v>
+        <v>0.144286400757607</v>
       </c>
       <c r="R290" t="n">
         <v>1</v>
       </c>
       <c r="S290" t="n">
-        <v>0.08952191512507046</v>
+        <v>-0.08015487768871299</v>
       </c>
       <c r="T290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U290" t="n">
-        <v>0.08952191512507046</v>
+        <v>-0.08015487768871299</v>
       </c>
       <c r="V290" t="n">
-        <v>0.3783621777071274</v>
+        <v>0.5927423185729692</v>
       </c>
       <c r="W290" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="X290" t="inlineStr">
         <is>
@@ -28898,10 +28898,10 @@
         </is>
       </c>
       <c r="Y290" t="n">
-        <v>5.074160018942885</v>
+        <v>6.874235460079252</v>
       </c>
       <c r="Z290" t="n">
-        <v>5.074160018942885</v>
+        <v>6.874235460079252</v>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
@@ -28918,20 +28918,20 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>45564.65625</v>
+        <v>45565.65625</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -28941,55 +28941,55 @@
         <v>771</v>
       </c>
       <c r="G291" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="H291" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I291" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="J291" t="n">
-        <v>0.6728971962616822</v>
+        <v>0.4415584415584415</v>
       </c>
       <c r="K291" t="n">
-        <v>0.2093457943925233</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="L291" t="n">
-        <v>0.1177570093457944</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="M291" t="n">
-        <v>0.06150793650793651</v>
+        <v>0.05335157318741457</v>
       </c>
       <c r="N291" t="n">
         <v>1</v>
       </c>
       <c r="O291" t="n">
-        <v>0.5927423185729692</v>
+        <v>0.4354236745886679</v>
       </c>
       <c r="P291" t="n">
-        <v>0.2629712806694237</v>
+        <v>0.355077973981165</v>
       </c>
       <c r="Q291" t="n">
-        <v>0.144286400757607</v>
+        <v>0.2094983514301671</v>
       </c>
       <c r="R291" t="n">
         <v>1</v>
       </c>
       <c r="S291" t="n">
-        <v>-0.08015487768871299</v>
+        <v>-0.006134766969773664</v>
       </c>
       <c r="T291" t="n">
         <v>1</v>
       </c>
       <c r="U291" t="n">
-        <v>-0.08015487768871299</v>
+        <v>-0.006134766969773664</v>
       </c>
       <c r="V291" t="n">
-        <v>0.5927423185729692</v>
+        <v>0.4354236745886679</v>
       </c>
       <c r="W291" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="X291" t="inlineStr">
         <is>
@@ -28997,10 +28997,10 @@
         </is>
       </c>
       <c r="Y291" t="n">
-        <v>6.874235460079252</v>
+        <v>5.757130971218705</v>
       </c>
       <c r="Z291" t="n">
-        <v>6.874235460079252</v>
+        <v>5.757130971218705</v>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
@@ -29017,20 +29017,20 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>z3jsi9f5</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>45565.65625</v>
+        <v>45569.5625</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -29040,66 +29040,66 @@
         <v>771</v>
       </c>
       <c r="G292" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="H292" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I292" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="J292" t="n">
-        <v>0.4415584415584415</v>
+        <v>0.6471238938053098</v>
       </c>
       <c r="K292" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.2085176991150442</v>
       </c>
       <c r="L292" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.144358407079646</v>
       </c>
       <c r="M292" t="n">
-        <v>0.05335157318741457</v>
+        <v>0.06572354848216921</v>
       </c>
       <c r="N292" t="n">
         <v>1</v>
       </c>
       <c r="O292" t="n">
-        <v>0.4354236745886679</v>
+        <v>0.3807951109694707</v>
       </c>
       <c r="P292" t="n">
-        <v>0.355077973981165</v>
+        <v>0.3713259172087673</v>
       </c>
       <c r="Q292" t="n">
-        <v>0.2094983514301671</v>
+        <v>0.2478789718217618</v>
       </c>
       <c r="R292" t="n">
         <v>1</v>
       </c>
       <c r="S292" t="n">
-        <v>-0.006134766969773664</v>
+        <v>-0.2663287828358391</v>
       </c>
       <c r="T292" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U292" t="n">
-        <v>-0.006134766969773664</v>
+        <v>0.2663287828358391</v>
       </c>
       <c r="V292" t="n">
-        <v>0.4354236745886679</v>
+        <v>0.6192048890305293</v>
       </c>
       <c r="W292" t="n">
-        <v>2.15</v>
+        <v>2.659090909090909</v>
       </c>
       <c r="X292" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y292" t="n">
-        <v>5.757130971218705</v>
+        <v>8.304066517675851</v>
       </c>
       <c r="Z292" t="n">
-        <v>5.757130971218705</v>
+        <v>8.304066517675851</v>
       </c>
       <c r="AA292" t="inlineStr">
         <is>
@@ -29116,20 +29116,20 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>8SWavWAa</t>
         </is>
       </c>
       <c r="B293" s="2" t="n">
-        <v>45569.5625</v>
+        <v>45569.65625</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -29139,66 +29139,66 @@
         <v>771</v>
       </c>
       <c r="G293" t="n">
-        <v>1.45</v>
+        <v>2.05</v>
       </c>
       <c r="H293" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I293" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="J293" t="n">
-        <v>0.6471238938053098</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="K293" t="n">
-        <v>0.2085176991150442</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="L293" t="n">
-        <v>0.144358407079646</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="M293" t="n">
-        <v>0.06572354848216921</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="N293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O293" t="n">
-        <v>0.3807951109694707</v>
+        <v>0.3646889468749105</v>
       </c>
       <c r="P293" t="n">
-        <v>0.3713259172087673</v>
+        <v>0.376808570749315</v>
       </c>
       <c r="Q293" t="n">
-        <v>0.2478789718217618</v>
+        <v>0.2585024823757745</v>
       </c>
       <c r="R293" t="n">
         <v>1</v>
       </c>
       <c r="S293" t="n">
-        <v>-0.2663287828358391</v>
+        <v>0.09926062039203781</v>
       </c>
       <c r="T293" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U293" t="n">
-        <v>0.2663287828358391</v>
+        <v>0.09926062039203781</v>
       </c>
       <c r="V293" t="n">
-        <v>0.6192048890305293</v>
+        <v>0.376808570749315</v>
       </c>
       <c r="W293" t="n">
-        <v>2.659090909090909</v>
+        <v>3.4</v>
       </c>
       <c r="X293" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y293" t="n">
-        <v>8.304066517675851</v>
+        <v>5.053324822469876</v>
       </c>
       <c r="Z293" t="n">
-        <v>8.304066517675851</v>
+        <v>5.053324822469876</v>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
@@ -29215,20 +29215,20 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>WUqjkmPH</t>
         </is>
       </c>
       <c r="B294" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45570.41666666666</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -29238,55 +29238,55 @@
         <v>771</v>
       </c>
       <c r="G294" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="H294" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I294" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J294" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.4689603590127151</v>
       </c>
       <c r="K294" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2842183994016455</v>
       </c>
       <c r="L294" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2468212415856395</v>
       </c>
       <c r="M294" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.06618819776714502</v>
       </c>
       <c r="N294" t="n">
         <v>0</v>
       </c>
       <c r="O294" t="n">
-        <v>0.3646889468749105</v>
+        <v>0.366967809925877</v>
       </c>
       <c r="P294" t="n">
-        <v>0.376808570749315</v>
+        <v>0.3768738347457878</v>
       </c>
       <c r="Q294" t="n">
-        <v>0.2585024823757745</v>
+        <v>0.2561583553283352</v>
       </c>
       <c r="R294" t="n">
         <v>1</v>
       </c>
       <c r="S294" t="n">
-        <v>0.09926062039203781</v>
+        <v>0.09265543534414228</v>
       </c>
       <c r="T294" t="n">
         <v>0</v>
       </c>
       <c r="U294" t="n">
-        <v>0.09926062039203781</v>
+        <v>0.09265543534414228</v>
       </c>
       <c r="V294" t="n">
-        <v>0.376808570749315</v>
+        <v>0.3768738347457878</v>
       </c>
       <c r="W294" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="X294" t="inlineStr">
         <is>
@@ -29294,10 +29294,10 @@
         </is>
       </c>
       <c r="Y294" t="n">
-        <v>5.053324822469876</v>
+        <v>5.054200068414346</v>
       </c>
       <c r="Z294" t="n">
-        <v>5.053324822469876</v>
+        <v>5.054200068414346</v>
       </c>
       <c r="AA294" t="inlineStr">
         <is>
@@ -29314,20 +29314,20 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B295" s="2" t="n">
-        <v>45570.41666666666</v>
+        <v>45570.54166666666</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -29337,55 +29337,55 @@
         <v>771</v>
       </c>
       <c r="G295" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H295" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="I295" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="J295" t="n">
-        <v>0.4689603590127151</v>
+        <v>0.6264014466546112</v>
       </c>
       <c r="K295" t="n">
-        <v>0.2842183994016455</v>
+        <v>0.216998191681736</v>
       </c>
       <c r="L295" t="n">
-        <v>0.2468212415856395</v>
+        <v>0.1566003616636528</v>
       </c>
       <c r="M295" t="n">
-        <v>0.06618819776714502</v>
+        <v>0.0642802155504234</v>
       </c>
       <c r="N295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O295" t="n">
-        <v>0.366967809925877</v>
+        <v>0.4690041039744517</v>
       </c>
       <c r="P295" t="n">
-        <v>0.3768738347457878</v>
+        <v>0.3495857899250586</v>
       </c>
       <c r="Q295" t="n">
-        <v>0.2561583553283352</v>
+        <v>0.1814101061004897</v>
       </c>
       <c r="R295" t="n">
         <v>1</v>
       </c>
       <c r="S295" t="n">
-        <v>0.09265543534414228</v>
+        <v>-0.1573973426801594</v>
       </c>
       <c r="T295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U295" t="n">
-        <v>0.09265543534414228</v>
+        <v>-0.1573973426801594</v>
       </c>
       <c r="V295" t="n">
-        <v>0.3768738347457878</v>
+        <v>0.4690041039744517</v>
       </c>
       <c r="W295" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="X295" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="Y295" t="n">
-        <v>5.054200068414346</v>
+        <v>4.178912859032295</v>
       </c>
       <c r="Z295" t="n">
-        <v>5.054200068414346</v>
+        <v>4.178912859032295</v>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
@@ -29413,20 +29413,20 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>45570.54166666666</v>
+        <v>45570.65625</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -29436,55 +29436,55 @@
         <v>771</v>
       </c>
       <c r="G296" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="H296" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="I296" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="J296" t="n">
-        <v>0.6264014466546112</v>
+        <v>0.6965944272445821</v>
       </c>
       <c r="K296" t="n">
-        <v>0.216998191681736</v>
+        <v>0.2058823529411765</v>
       </c>
       <c r="L296" t="n">
-        <v>0.1566003616636528</v>
+        <v>0.09752321981424149</v>
       </c>
       <c r="M296" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.07936507936507931</v>
       </c>
       <c r="N296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O296" t="n">
-        <v>0.4690041039744517</v>
+        <v>0.3687691030089816</v>
       </c>
       <c r="P296" t="n">
-        <v>0.3495857899250586</v>
+        <v>0.3778563752403633</v>
       </c>
       <c r="Q296" t="n">
-        <v>0.1814101061004897</v>
+        <v>0.2533745217506556</v>
       </c>
       <c r="R296" t="n">
         <v>1</v>
       </c>
       <c r="S296" t="n">
-        <v>-0.1573973426801594</v>
+        <v>0.1719740222991868</v>
       </c>
       <c r="T296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U296" t="n">
-        <v>-0.1573973426801594</v>
+        <v>0.1719740222991868</v>
       </c>
       <c r="V296" t="n">
-        <v>0.4690041039744517</v>
+        <v>0.3778563752403633</v>
       </c>
       <c r="W296" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="X296" t="inlineStr">
         <is>
@@ -29492,10 +29492,10 @@
         </is>
       </c>
       <c r="Y296" t="n">
-        <v>4.178912859032295</v>
+        <v>5.06737677578182</v>
       </c>
       <c r="Z296" t="n">
-        <v>4.178912859032295</v>
+        <v>5.06737677578182</v>
       </c>
       <c r="AA296" t="inlineStr">
         <is>
@@ -29512,20 +29512,20 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B297" s="2" t="n">
-        <v>45570.65625</v>
+        <v>45571.3125</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -29535,55 +29535,55 @@
         <v>771</v>
       </c>
       <c r="G297" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="H297" t="n">
         <v>4.5</v>
       </c>
       <c r="I297" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="J297" t="n">
-        <v>0.6965944272445821</v>
+        <v>0.6676557863501484</v>
       </c>
       <c r="K297" t="n">
-        <v>0.2058823529411765</v>
+        <v>0.2077151335311573</v>
       </c>
       <c r="L297" t="n">
-        <v>0.09752321981424149</v>
+        <v>0.1246290801186944</v>
       </c>
       <c r="M297" t="n">
-        <v>0.07936507936507931</v>
+        <v>0.06984126984126982</v>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O297" t="n">
-        <v>0.3687691030089816</v>
+        <v>0.4452259396352466</v>
       </c>
       <c r="P297" t="n">
-        <v>0.3778563752403633</v>
+        <v>0.3547929447640126</v>
       </c>
       <c r="Q297" t="n">
-        <v>0.2533745217506556</v>
+        <v>0.1999811156007407</v>
       </c>
       <c r="R297" t="n">
         <v>1</v>
       </c>
       <c r="S297" t="n">
-        <v>0.1719740222991868</v>
+        <v>-0.2224298467149018</v>
       </c>
       <c r="T297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U297" t="n">
-        <v>0.1719740222991868</v>
+        <v>-0.2224298467149018</v>
       </c>
       <c r="V297" t="n">
-        <v>0.3778563752403633</v>
+        <v>0.4452259396352466</v>
       </c>
       <c r="W297" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="X297" t="inlineStr">
         <is>
@@ -29591,10 +29591,10 @@
         </is>
       </c>
       <c r="Y297" t="n">
-        <v>5.06737677578182</v>
+        <v>2.9878859296242</v>
       </c>
       <c r="Z297" t="n">
-        <v>5.06737677578182</v>
+        <v>2.9878859296242</v>
       </c>
       <c r="AA297" t="inlineStr">
         <is>
@@ -29611,20 +29611,20 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B298" s="2" t="n">
-        <v>45571.3125</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -29634,55 +29634,55 @@
         <v>771</v>
       </c>
       <c r="G298" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="H298" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I298" t="n">
         <v>4.5</v>
       </c>
-      <c r="I298" t="n">
-        <v>7.5</v>
-      </c>
       <c r="J298" t="n">
-        <v>0.6676557863501484</v>
+        <v>0.5389221556886228</v>
       </c>
       <c r="K298" t="n">
-        <v>0.2077151335311573</v>
+        <v>0.251497005988024</v>
       </c>
       <c r="L298" t="n">
-        <v>0.1246290801186944</v>
+        <v>0.2095808383233533</v>
       </c>
       <c r="M298" t="n">
-        <v>0.06984126984126982</v>
+        <v>0.0603174603174601</v>
       </c>
       <c r="N298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O298" t="n">
-        <v>0.4452259396352466</v>
+        <v>0.2884561946384767</v>
       </c>
       <c r="P298" t="n">
-        <v>0.3547929447640126</v>
+        <v>0.3718053828229426</v>
       </c>
       <c r="Q298" t="n">
-        <v>0.1999811156007407</v>
+        <v>0.3397384225385808</v>
       </c>
       <c r="R298" t="n">
         <v>1</v>
       </c>
       <c r="S298" t="n">
-        <v>-0.2224298467149018</v>
+        <v>0.1203083768349186</v>
       </c>
       <c r="T298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U298" t="n">
-        <v>-0.2224298467149018</v>
+        <v>0.1203083768349186</v>
       </c>
       <c r="V298" t="n">
-        <v>0.4452259396352466</v>
+        <v>0.3718053828229426</v>
       </c>
       <c r="W298" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="X298" t="inlineStr">
         <is>
@@ -29690,10 +29690,10 @@
         </is>
       </c>
       <c r="Y298" t="n">
-        <v>2.9878859296242</v>
+        <v>4.986227798403936</v>
       </c>
       <c r="Z298" t="n">
-        <v>2.9878859296242</v>
+        <v>4.986227798403936</v>
       </c>
       <c r="AA298" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B299" s="2" t="n">
@@ -29718,12 +29718,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -29733,55 +29733,55 @@
         <v>771</v>
       </c>
       <c r="G299" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="H299" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I299" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="J299" t="n">
-        <v>0.5389221556886228</v>
+        <v>0.6263219741480611</v>
       </c>
       <c r="K299" t="n">
-        <v>0.251497005988024</v>
+        <v>0.2291421856639248</v>
       </c>
       <c r="L299" t="n">
-        <v>0.2095808383233533</v>
+        <v>0.1445358401880141</v>
       </c>
       <c r="M299" t="n">
-        <v>0.0603174603174601</v>
+        <v>0.06441525953721072</v>
       </c>
       <c r="N299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O299" t="n">
-        <v>0.2884561946384767</v>
+        <v>0.5401047277622434</v>
       </c>
       <c r="P299" t="n">
-        <v>0.3718053828229426</v>
+        <v>0.3495822726155097</v>
       </c>
       <c r="Q299" t="n">
-        <v>0.3397384225385808</v>
+        <v>0.110312999622247</v>
       </c>
       <c r="R299" t="n">
         <v>1</v>
       </c>
       <c r="S299" t="n">
-        <v>0.1203083768349186</v>
+        <v>-0.08621724638581774</v>
       </c>
       <c r="T299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U299" t="n">
-        <v>0.1203083768349186</v>
+        <v>-0.08621724638581774</v>
       </c>
       <c r="V299" t="n">
-        <v>0.3718053828229426</v>
+        <v>0.5401047277622434</v>
       </c>
       <c r="W299" t="n">
-        <v>3.75</v>
+        <v>1.5</v>
       </c>
       <c r="X299" t="inlineStr">
         <is>
@@ -29789,10 +29789,10 @@
         </is>
       </c>
       <c r="Y299" t="n">
-        <v>4.986227798403936</v>
+        <v>6.087018858638833</v>
       </c>
       <c r="Z299" t="n">
-        <v>4.986227798403936</v>
+        <v>6.087018858638833</v>
       </c>
       <c r="AA299" t="inlineStr">
         <is>
@@ -29809,20 +29809,20 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B300" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45571.54166666666</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -29832,55 +29832,55 @@
         <v>771</v>
       </c>
       <c r="G300" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="H300" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="I300" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="J300" t="n">
-        <v>0.6263219741480611</v>
+        <v>0.2492917847025495</v>
       </c>
       <c r="K300" t="n">
-        <v>0.2291421856639248</v>
+        <v>0.28328611898017</v>
       </c>
       <c r="L300" t="n">
-        <v>0.1445358401880141</v>
+        <v>0.4674220963172804</v>
       </c>
       <c r="M300" t="n">
-        <v>0.06441525953721072</v>
+        <v>0.06969696969696981</v>
       </c>
       <c r="N300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O300" t="n">
-        <v>0.5401047277622434</v>
+        <v>0.3563723800574224</v>
       </c>
       <c r="P300" t="n">
-        <v>0.3495822726155097</v>
+        <v>0.3741454843807208</v>
       </c>
       <c r="Q300" t="n">
-        <v>0.110312999622247</v>
+        <v>0.2694821355618568</v>
       </c>
       <c r="R300" t="n">
         <v>1</v>
       </c>
       <c r="S300" t="n">
-        <v>-0.08621724638581774</v>
+        <v>0.09085936540055078</v>
       </c>
       <c r="T300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U300" t="n">
-        <v>-0.08621724638581774</v>
+        <v>0.09085936540055078</v>
       </c>
       <c r="V300" t="n">
-        <v>0.5401047277622434</v>
+        <v>0.3741454843807208</v>
       </c>
       <c r="W300" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="X300" t="inlineStr">
         <is>
@@ -29888,10 +29888,10 @@
         </is>
       </c>
       <c r="Y300" t="n">
-        <v>6.087018858638833</v>
+        <v>5.017610559325497</v>
       </c>
       <c r="Z300" t="n">
-        <v>6.087018858638833</v>
+        <v>5.017610559325497</v>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
@@ -29908,20 +29908,20 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B301" s="2" t="n">
-        <v>45571.54166666666</v>
+        <v>45571.65625</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -29931,55 +29931,55 @@
         <v>771</v>
       </c>
       <c r="G301" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="H301" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I301" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="J301" t="n">
-        <v>0.2492917847025495</v>
+        <v>0.3480113636363636</v>
       </c>
       <c r="K301" t="n">
-        <v>0.28328611898017</v>
+        <v>0.2684659090909091</v>
       </c>
       <c r="L301" t="n">
-        <v>0.4674220963172804</v>
+        <v>0.3835227272727272</v>
       </c>
       <c r="M301" t="n">
-        <v>0.06969696969696981</v>
+        <v>0.06424792139077851</v>
       </c>
       <c r="N301" t="n">
         <v>0</v>
       </c>
       <c r="O301" t="n">
-        <v>0.3563723800574224</v>
+        <v>0.3581358117196171</v>
       </c>
       <c r="P301" t="n">
-        <v>0.3741454843807208</v>
+        <v>0.3758257404424035</v>
       </c>
       <c r="Q301" t="n">
-        <v>0.2694821355618568</v>
+        <v>0.2660384478379793</v>
       </c>
       <c r="R301" t="n">
         <v>1</v>
       </c>
       <c r="S301" t="n">
-        <v>0.09085936540055078</v>
+        <v>0.1073598313514945</v>
       </c>
       <c r="T301" t="n">
         <v>0</v>
       </c>
       <c r="U301" t="n">
-        <v>0.09085936540055078</v>
+        <v>0.1073598313514945</v>
       </c>
       <c r="V301" t="n">
-        <v>0.3741454843807208</v>
+        <v>0.3758257404424035</v>
       </c>
       <c r="W301" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="X301" t="inlineStr">
         <is>
@@ -29987,10 +29987,10 @@
         </is>
       </c>
       <c r="Y301" t="n">
-        <v>5.017610559325497</v>
+        <v>5.040144228471404</v>
       </c>
       <c r="Z301" t="n">
-        <v>5.017610559325497</v>
+        <v>5.040144228471404</v>
       </c>
       <c r="AA301" t="inlineStr">
         <is>
@@ -30007,98 +30007,98 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B302" s="2" t="n">
-        <v>45571.65625</v>
+        <v>45558.66666666666</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F302" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G302" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="H302" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I302" t="n">
-        <v>2.45</v>
+        <v>5.25</v>
       </c>
       <c r="J302" t="n">
-        <v>0.3480113636363636</v>
+        <v>0.5411140583554376</v>
       </c>
       <c r="K302" t="n">
-        <v>0.2684659090909091</v>
+        <v>0.2785145888594164</v>
       </c>
       <c r="L302" t="n">
-        <v>0.3835227272727272</v>
+        <v>0.1803713527851459</v>
       </c>
       <c r="M302" t="n">
-        <v>0.06424792139077851</v>
+        <v>0.05602240896358546</v>
       </c>
       <c r="N302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O302" t="n">
-        <v>0.3581358117196171</v>
+        <v>0.5408109176634674</v>
       </c>
       <c r="P302" t="n">
-        <v>0.3758257404424035</v>
+        <v>0.3944881060949174</v>
       </c>
       <c r="Q302" t="n">
-        <v>0.2660384478379793</v>
+        <v>0.06470097624161518</v>
       </c>
       <c r="R302" t="n">
         <v>1</v>
       </c>
       <c r="S302" t="n">
-        <v>0.1073598313514945</v>
+        <v>-0.0003031406919701274</v>
       </c>
       <c r="T302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U302" t="n">
-        <v>0.1073598313514945</v>
+        <v>-0.0003031406919701274</v>
       </c>
       <c r="V302" t="n">
-        <v>0.3758257404424035</v>
+        <v>0.5408109176634674</v>
       </c>
       <c r="W302" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="X302" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y302" t="n">
-        <v>5.040144228471404</v>
+        <v>4.376545042026021</v>
       </c>
       <c r="Z302" t="n">
-        <v>5.040144228471404</v>
+        <v>4.376545042026021</v>
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr"/>
@@ -30106,15 +30106,15 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>445r4WXo</t>
+          <t>06X4YYrf</t>
         </is>
       </c>
       <c r="B303" s="2" t="n">
-        <v>45558.66666666666</v>
+        <v>45562.66666666666</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -30129,55 +30129,55 @@
         <v>1481</v>
       </c>
       <c r="G303" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="H303" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="I303" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="J303" t="n">
-        <v>0.5411140583554376</v>
+        <v>0.3366583541147132</v>
       </c>
       <c r="K303" t="n">
-        <v>0.2785145888594164</v>
+        <v>0.314214463840399</v>
       </c>
       <c r="L303" t="n">
-        <v>0.1803713527851459</v>
+        <v>0.3491271820448877</v>
       </c>
       <c r="M303" t="n">
-        <v>0.05602240896358546</v>
+        <v>0.06084656084656093</v>
       </c>
       <c r="N303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O303" t="n">
-        <v>0.5408109176634674</v>
+        <v>0.3503245575112786</v>
       </c>
       <c r="P303" t="n">
-        <v>0.3944881060949174</v>
+        <v>0.4602492737597988</v>
       </c>
       <c r="Q303" t="n">
-        <v>0.06470097624161518</v>
+        <v>0.1894261687289225</v>
       </c>
       <c r="R303" t="n">
         <v>1</v>
       </c>
       <c r="S303" t="n">
-        <v>-0.0003031406919701274</v>
+        <v>0.1460348099193999</v>
       </c>
       <c r="T303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U303" t="n">
-        <v>-0.0003031406919701274</v>
+        <v>0.1460348099193999</v>
       </c>
       <c r="V303" t="n">
-        <v>0.5408109176634674</v>
+        <v>0.4602492737597988</v>
       </c>
       <c r="W303" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="X303" t="inlineStr">
         <is>
@@ -30185,10 +30185,10 @@
         </is>
       </c>
       <c r="Y303" t="n">
-        <v>4.376545042026021</v>
+        <v>3.726683986779611</v>
       </c>
       <c r="Z303" t="n">
-        <v>4.376545042026021</v>
+        <v>3.726683986779611</v>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
@@ -30205,20 +30205,20 @@
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>rkN7RQV9</t>
+          <t>hMoEUjrJ</t>
         </is>
       </c>
       <c r="B304" s="2" t="n">
-        <v>45559.58333333334</v>
+        <v>45563.375</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -30228,55 +30228,55 @@
         <v>1481</v>
       </c>
       <c r="G304" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="H304" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="I304" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J304" t="n">
-        <v>0.5557224391709222</v>
+        <v>0.3997567403202919</v>
       </c>
       <c r="K304" t="n">
-        <v>0.2553319315109642</v>
+        <v>0.323940806811271</v>
       </c>
       <c r="L304" t="n">
-        <v>0.1889456293181136</v>
+        <v>0.2763024528684371</v>
       </c>
       <c r="M304" t="n">
-        <v>0.05850556438791732</v>
+        <v>0.06447714815933714</v>
       </c>
       <c r="N304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O304" t="n">
-        <v>0.5081509698904012</v>
+        <v>0.2580355187292688</v>
       </c>
       <c r="P304" t="n">
-        <v>0.417731030004452</v>
+        <v>0.2854832990992498</v>
       </c>
       <c r="Q304" t="n">
-        <v>0.07411800010514685</v>
+        <v>0.4564811821714815</v>
       </c>
       <c r="R304" t="n">
         <v>1</v>
       </c>
       <c r="S304" t="n">
-        <v>-0.04757146928052103</v>
+        <v>0.1801787293030445</v>
       </c>
       <c r="T304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U304" t="n">
-        <v>-0.04757146928052103</v>
+        <v>0.1801787293030445</v>
       </c>
       <c r="V304" t="n">
-        <v>0.5081509698904012</v>
+        <v>0.4564811821714815</v>
       </c>
       <c r="W304" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="X304" t="inlineStr">
         <is>
@@ -30284,10 +30284,10 @@
         </is>
       </c>
       <c r="Y304" t="n">
-        <v>3.729357866314824</v>
+        <v>3.696173375718376</v>
       </c>
       <c r="Z304" t="n">
-        <v>3.729357866314824</v>
+        <v>3.696173375718376</v>
       </c>
       <c r="AA304" t="inlineStr">
         <is>
@@ -30304,20 +30304,20 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>bwZsTw7E</t>
+          <t>KSw0hfzQ</t>
         </is>
       </c>
       <c r="B305" s="2" t="n">
-        <v>45559.58333333334</v>
+        <v>45563.46875</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -30327,55 +30327,55 @@
         <v>1481</v>
       </c>
       <c r="G305" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="H305" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I305" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="J305" t="n">
-        <v>0.4512126339537507</v>
+        <v>0.4904913518630066</v>
       </c>
       <c r="K305" t="n">
-        <v>0.2961082910321489</v>
+        <v>0.3122794940194475</v>
       </c>
       <c r="L305" t="n">
-        <v>0.2526790750141004</v>
+        <v>0.1972291541175458</v>
       </c>
       <c r="M305" t="n">
-        <v>0.05535714285714288</v>
+        <v>0.06741985854689081</v>
       </c>
       <c r="N305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O305" t="n">
-        <v>0.3344448302385079</v>
+        <v>0.6185229515125987</v>
       </c>
       <c r="P305" t="n">
-        <v>0.3424000685835993</v>
+        <v>0.3144900159986573</v>
       </c>
       <c r="Q305" t="n">
-        <v>0.3231551011778929</v>
+        <v>0.06698703248874409</v>
       </c>
       <c r="R305" t="n">
         <v>1</v>
       </c>
       <c r="S305" t="n">
-        <v>0.04629177755145036</v>
+        <v>0.1280315996495921</v>
       </c>
       <c r="T305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U305" t="n">
-        <v>0.04629177755145036</v>
+        <v>0.1280315996495921</v>
       </c>
       <c r="V305" t="n">
-        <v>0.3424000685835993</v>
+        <v>0.6185229515125987</v>
       </c>
       <c r="W305" t="n">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="X305" t="inlineStr">
         <is>
@@ -30383,10 +30383,10 @@
         </is>
       </c>
       <c r="Y305" t="n">
-        <v>2.772447291961801</v>
+        <v>5.008241642681329</v>
       </c>
       <c r="Z305" t="n">
-        <v>2.772447291961801</v>
+        <v>5.008241642681329</v>
       </c>
       <c r="AA305" t="inlineStr">
         <is>
@@ -30403,20 +30403,20 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>f5SjRHyR</t>
+          <t>YemQuHjK</t>
         </is>
       </c>
       <c r="B306" s="2" t="n">
-        <v>45559.66666666666</v>
+        <v>45563.5625</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -30426,55 +30426,55 @@
         <v>1481</v>
       </c>
       <c r="G306" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="H306" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="I306" t="n">
-        <v>13</v>
+        <v>5.25</v>
       </c>
       <c r="J306" t="n">
-        <v>0.783132530120482</v>
+        <v>0.5439668439257036</v>
       </c>
       <c r="K306" t="n">
-        <v>0.1445783132530121</v>
+        <v>0.2767831294092551</v>
       </c>
       <c r="L306" t="n">
-        <v>0.07228915662650603</v>
+        <v>0.1792500266650414</v>
       </c>
       <c r="M306" t="n">
-        <v>0.0641025641025641</v>
+        <v>0.06262851961593885</v>
       </c>
       <c r="N306" t="n">
         <v>1</v>
       </c>
       <c r="O306" t="n">
-        <v>0.6847641344606475</v>
+        <v>0.4916837424854436</v>
       </c>
       <c r="P306" t="n">
-        <v>0.2397935592263166</v>
+        <v>0.4236096024691185</v>
       </c>
       <c r="Q306" t="n">
-        <v>0.07544230631303583</v>
+        <v>0.08470665504543799</v>
       </c>
       <c r="R306" t="n">
         <v>1</v>
       </c>
       <c r="S306" t="n">
-        <v>-0.09836839565983446</v>
+        <v>-0.05228310144026005</v>
       </c>
       <c r="T306" t="n">
         <v>1</v>
       </c>
       <c r="U306" t="n">
-        <v>-0.09836839565983446</v>
+        <v>-0.05228310144026005</v>
       </c>
       <c r="V306" t="n">
-        <v>0.6847641344606475</v>
+        <v>0.4916837424854436</v>
       </c>
       <c r="W306" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="X306" t="inlineStr">
         <is>
@@ -30482,10 +30482,10 @@
         </is>
       </c>
       <c r="Y306" t="n">
-        <v>4.74810441709744</v>
+        <v>3.557870541297988</v>
       </c>
       <c r="Z306" t="n">
-        <v>4.74810441709744</v>
+        <v>3.557870541297988</v>
       </c>
       <c r="AA306" t="inlineStr">
         <is>
@@ -30502,20 +30502,20 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>ddsD5q9j</t>
+          <t>4vvdzeEs</t>
         </is>
       </c>
       <c r="B307" s="2" t="n">
-        <v>45560.58333333334</v>
+        <v>45563.66666666666</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -30525,55 +30525,55 @@
         <v>1481</v>
       </c>
       <c r="G307" t="n">
-        <v>1.73</v>
+        <v>7</v>
       </c>
       <c r="H307" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="I307" t="n">
-        <v>4.5</v>
+        <v>1.48</v>
       </c>
       <c r="J307" t="n">
-        <v>0.5399533013361008</v>
+        <v>0.1361218733007069</v>
       </c>
       <c r="K307" t="n">
-        <v>0.2524646517057984</v>
+        <v>0.2200584556824361</v>
       </c>
       <c r="L307" t="n">
-        <v>0.2075820469581009</v>
+        <v>0.643819671016857</v>
       </c>
       <c r="M307" t="n">
-        <v>0.07052717457341728</v>
+        <v>0.0494797007499086</v>
       </c>
       <c r="N307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O307" t="n">
-        <v>0.4551515200405018</v>
+        <v>0.1367878370483812</v>
       </c>
       <c r="P307" t="n">
-        <v>0.45805835461747</v>
+        <v>0.2824706381613762</v>
       </c>
       <c r="Q307" t="n">
-        <v>0.08679012534202812</v>
+        <v>0.5807415247902425</v>
       </c>
       <c r="R307" t="n">
         <v>1</v>
       </c>
       <c r="S307" t="n">
-        <v>0.2055937029116716</v>
+        <v>-0.06307814622661445</v>
       </c>
       <c r="T307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U307" t="n">
-        <v>0.2055937029116716</v>
+        <v>-0.06307814622661445</v>
       </c>
       <c r="V307" t="n">
-        <v>0.45805835461747</v>
+        <v>0.5807415247902425</v>
       </c>
       <c r="W307" t="n">
-        <v>3.7</v>
+        <v>1.48</v>
       </c>
       <c r="X307" t="inlineStr">
         <is>
@@ -30581,10 +30581,10 @@
         </is>
       </c>
       <c r="Y307" t="n">
-        <v>3.708943897333415</v>
+        <v>4.1915716839178</v>
       </c>
       <c r="Z307" t="n">
-        <v>3.708943897333415</v>
+        <v>4.1915716839178</v>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
@@ -30601,20 +30601,20 @@
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>QDjsB5oT</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B308" s="2" t="n">
-        <v>45560.66666666666</v>
+        <v>45564.375</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -30624,55 +30624,55 @@
         <v>1481</v>
       </c>
       <c r="G308" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="H308" t="n">
-        <v>6.25</v>
+        <v>3.6</v>
       </c>
       <c r="I308" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="J308" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.4664634146341464</v>
       </c>
       <c r="K308" t="n">
-        <v>0.1509433962264151</v>
+        <v>0.2591463414634146</v>
       </c>
       <c r="L308" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.274390243902439</v>
       </c>
       <c r="M308" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.07189542483660127</v>
       </c>
       <c r="N308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O308" t="n">
-        <v>0.6285554208465365</v>
+        <v>0.3065355097973315</v>
       </c>
       <c r="P308" t="n">
-        <v>0.3277309695226326</v>
+        <v>0.3817064870898392</v>
       </c>
       <c r="Q308" t="n">
-        <v>0.0437136096308308</v>
+        <v>0.3117580031128292</v>
       </c>
       <c r="R308" t="n">
         <v>1</v>
       </c>
       <c r="S308" t="n">
-        <v>-0.126161560285539</v>
+        <v>0.1225601456264246</v>
       </c>
       <c r="T308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U308" t="n">
-        <v>-0.126161560285539</v>
+        <v>0.1225601456264246</v>
       </c>
       <c r="V308" t="n">
-        <v>0.6285554208465365</v>
+        <v>0.3817064870898392</v>
       </c>
       <c r="W308" t="n">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="X308" t="inlineStr">
         <is>
@@ -30680,10 +30680,10 @@
         </is>
       </c>
       <c r="Y308" t="n">
-        <v>4.067932883227492</v>
+        <v>3.09071525842319</v>
       </c>
       <c r="Z308" t="n">
-        <v>4.067932883227492</v>
+        <v>3.09071525842319</v>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
@@ -30700,20 +30700,20 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>bqbA3PNE</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B309" s="2" t="n">
-        <v>45561.58333333334</v>
+        <v>45564.46875</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E309" t="n">
@@ -30723,55 +30723,55 @@
         <v>1481</v>
       </c>
       <c r="G309" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="H309" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I309" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="J309" t="n">
-        <v>0.2906808305166586</v>
+        <v>0.5557224391709222</v>
       </c>
       <c r="K309" t="n">
-        <v>0.269917914051183</v>
+        <v>0.2553319315109642</v>
       </c>
       <c r="L309" t="n">
-        <v>0.4394012554321584</v>
+        <v>0.1889456293181136</v>
       </c>
       <c r="M309" t="n">
-        <v>0.0585228724763609</v>
+        <v>0.05850556438791732</v>
       </c>
       <c r="N309" t="n">
         <v>1</v>
       </c>
       <c r="O309" t="n">
-        <v>0.3604871467035078</v>
+        <v>0.4763735152800625</v>
       </c>
       <c r="P309" t="n">
-        <v>0.3100354078201349</v>
+        <v>0.3957119312550064</v>
       </c>
       <c r="Q309" t="n">
-        <v>0.3294774454763573</v>
+        <v>0.1279145534649311</v>
       </c>
       <c r="R309" t="n">
         <v>1</v>
       </c>
       <c r="S309" t="n">
-        <v>0.06980631618684924</v>
+        <v>-0.07934892389085973</v>
       </c>
       <c r="T309" t="n">
         <v>1</v>
       </c>
       <c r="U309" t="n">
-        <v>0.06980631618684924</v>
+        <v>-0.07934892389085973</v>
       </c>
       <c r="V309" t="n">
-        <v>0.3604871467035078</v>
+        <v>0.4763735152800625</v>
       </c>
       <c r="W309" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="X309" t="inlineStr">
         <is>
@@ -30779,10 +30779,10 @@
         </is>
       </c>
       <c r="Y309" t="n">
-        <v>2.918900156181361</v>
+        <v>3.214747467173726</v>
       </c>
       <c r="Z309" t="n">
-        <v>2.918900156181361</v>
+        <v>3.214747467173726</v>
       </c>
       <c r="AA309" t="inlineStr">
         <is>
@@ -30799,20 +30799,20 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>6VWd5zF7</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B310" s="2" t="n">
-        <v>45561.58333333334</v>
+        <v>45564.5625</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -30822,55 +30822,55 @@
         <v>1481</v>
       </c>
       <c r="G310" t="n">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="H310" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="I310" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="J310" t="n">
-        <v>0.3037974683544304</v>
+        <v>0.5960720381078533</v>
       </c>
       <c r="K310" t="n">
-        <v>0.3037974683544304</v>
+        <v>0.2599536388414805</v>
       </c>
       <c r="L310" t="n">
-        <v>0.3924050632911393</v>
+        <v>0.1439743230506661</v>
       </c>
       <c r="M310" t="n">
-        <v>0.06182795698924726</v>
+        <v>0.06856660678316739</v>
       </c>
       <c r="N310" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O310" t="n">
-        <v>0.1229073394296955</v>
+        <v>0.6082259867265751</v>
       </c>
       <c r="P310" t="n">
-        <v>0.3658289508101885</v>
+        <v>0.3281564338314107</v>
       </c>
       <c r="Q310" t="n">
-        <v>0.511263709760116</v>
+        <v>0.06361757944201411</v>
       </c>
       <c r="R310" t="n">
         <v>1</v>
       </c>
       <c r="S310" t="n">
-        <v>0.1188586464689768</v>
+        <v>0.01215394861872188</v>
       </c>
       <c r="T310" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U310" t="n">
-        <v>0.1188586464689768</v>
+        <v>0.01215394861872188</v>
       </c>
       <c r="V310" t="n">
-        <v>0.511263709760116</v>
+        <v>0.6082259867265751</v>
       </c>
       <c r="W310" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="X310" t="inlineStr">
         <is>
@@ -30878,10 +30878,10 @@
         </is>
       </c>
       <c r="Y310" t="n">
-        <v>4.139752931318989</v>
+        <v>4.924866098235528</v>
       </c>
       <c r="Z310" t="n">
-        <v>4.139752931318989</v>
+        <v>4.924866098235528</v>
       </c>
       <c r="AA310" t="inlineStr">
         <is>
@@ -30898,20 +30898,20 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>pGrl7dpe</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B311" s="2" t="n">
-        <v>45561.66666666666</v>
+        <v>45564.66666666666</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -30921,55 +30921,55 @@
         <v>1481</v>
       </c>
       <c r="G311" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="H311" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I311" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="J311" t="n">
-        <v>0.2547632008709852</v>
+        <v>0.3067869752844252</v>
       </c>
       <c r="K311" t="n">
-        <v>0.2618399564507349</v>
+        <v>0.2797175362887406</v>
       </c>
       <c r="L311" t="n">
-        <v>0.4833968426782798</v>
+        <v>0.413495488426834</v>
       </c>
       <c r="M311" t="n">
-        <v>0.06086856086856107</v>
+        <v>0.05148090091576618</v>
       </c>
       <c r="N311" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O311" t="n">
-        <v>0.1661497387236976</v>
+        <v>0.2611593032482083</v>
       </c>
       <c r="P311" t="n">
-        <v>0.4027355240033786</v>
+        <v>0.4156629691983781</v>
       </c>
       <c r="Q311" t="n">
-        <v>0.4311147372729238</v>
+        <v>0.3231777275534136</v>
       </c>
       <c r="R311" t="n">
         <v>1</v>
       </c>
       <c r="S311" t="n">
-        <v>-0.05228210540535594</v>
+        <v>0.1359454329096375</v>
       </c>
       <c r="T311" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U311" t="n">
-        <v>-0.05228210540535594</v>
+        <v>0.1359454329096375</v>
       </c>
       <c r="V311" t="n">
-        <v>0.4311147372729238</v>
+        <v>0.4156629691983781</v>
       </c>
       <c r="W311" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="X311" t="inlineStr">
         <is>
@@ -30977,10 +30977,10 @@
         </is>
       </c>
       <c r="Y311" t="n">
-        <v>3.067445367849172</v>
+        <v>3.365664259618797</v>
       </c>
       <c r="Z311" t="n">
-        <v>3.067445367849172</v>
+        <v>3.365664259618797</v>
       </c>
       <c r="AA311" t="inlineStr">
         <is>
@@ -30997,20 +30997,20 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>06X4YYrf</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B312" s="2" t="n">
-        <v>45562.66666666666</v>
+        <v>45565.66666666666</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -31020,55 +31020,55 @@
         <v>1481</v>
       </c>
       <c r="G312" t="n">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="H312" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I312" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="J312" t="n">
-        <v>0.3366583541147132</v>
+        <v>0.6106870229007634</v>
       </c>
       <c r="K312" t="n">
-        <v>0.314214463840399</v>
+        <v>0.233587786259542</v>
       </c>
       <c r="L312" t="n">
-        <v>0.3491271820448877</v>
+        <v>0.1557251908396947</v>
       </c>
       <c r="M312" t="n">
-        <v>0.06084656084656093</v>
+        <v>0.0702614379084967</v>
       </c>
       <c r="N312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O312" t="n">
-        <v>0.3503245575112786</v>
+        <v>0.5468963056995511</v>
       </c>
       <c r="P312" t="n">
-        <v>0.4602492737597988</v>
+        <v>0.3267484368818821</v>
       </c>
       <c r="Q312" t="n">
-        <v>0.1894261687289225</v>
+        <v>0.1263552574185668</v>
       </c>
       <c r="R312" t="n">
         <v>1</v>
       </c>
       <c r="S312" t="n">
-        <v>0.1460348099193999</v>
+        <v>-0.06379071720121232</v>
       </c>
       <c r="T312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U312" t="n">
-        <v>0.1460348099193999</v>
+        <v>-0.06379071720121232</v>
       </c>
       <c r="V312" t="n">
-        <v>0.4602492737597988</v>
+        <v>0.5468963056995511</v>
       </c>
       <c r="W312" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="X312" t="inlineStr">
         <is>
@@ -31076,10 +31076,10 @@
         </is>
       </c>
       <c r="Y312" t="n">
-        <v>3.726683986779611</v>
+        <v>3.911753832598348</v>
       </c>
       <c r="Z312" t="n">
-        <v>3.726683986779611</v>
+        <v>3.911753832598348</v>
       </c>
       <c r="AA312" t="inlineStr">
         <is>
@@ -31096,20 +31096,20 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
+          <t>QmPfsURO</t>
         </is>
       </c>
       <c r="B313" s="2" t="n">
-        <v>45563.375</v>
+        <v>45569.66666666666</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -31118,68 +31118,44 @@
       <c r="F313" t="n">
         <v>1481</v>
       </c>
-      <c r="G313" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="H313" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I313" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J313" t="n">
-        <v>0.3997567403202919</v>
-      </c>
-      <c r="K313" t="n">
-        <v>0.323940806811271</v>
-      </c>
-      <c r="L313" t="n">
-        <v>0.2763024528684371</v>
-      </c>
-      <c r="M313" t="n">
-        <v>0.06447714815933714</v>
-      </c>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr"/>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
       <c r="N313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O313" t="n">
-        <v>0.2580355187292688</v>
+        <v>0.4256642360700815</v>
       </c>
       <c r="P313" t="n">
-        <v>0.2854832990992498</v>
+        <v>0.3982294511643811</v>
       </c>
       <c r="Q313" t="n">
-        <v>0.4564811821714815</v>
+        <v>0.1761063127655375</v>
       </c>
       <c r="R313" t="n">
         <v>1</v>
       </c>
-      <c r="S313" t="n">
-        <v>0.1801787293030445</v>
-      </c>
+      <c r="S313" t="inlineStr"/>
       <c r="T313" t="n">
-        <v>2</v>
-      </c>
-      <c r="U313" t="n">
-        <v>0.1801787293030445</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U313" t="inlineStr"/>
       <c r="V313" t="n">
-        <v>0.4564811821714815</v>
-      </c>
-      <c r="W313" t="n">
-        <v>3.4</v>
-      </c>
+        <v>0.5743357639299185</v>
+      </c>
+      <c r="W313" t="inlineStr"/>
       <c r="X313" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y313" t="n">
-        <v>3.696173375718376</v>
-      </c>
-      <c r="Z313" t="n">
-        <v>3.696173375718376</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr"/>
+      <c r="Z313" t="inlineStr"/>
       <c r="AA313" t="inlineStr">
         <is>
           <t>spain</t>
@@ -31195,20 +31171,20 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>0AJjqex0</t>
         </is>
       </c>
       <c r="B314" s="2" t="n">
-        <v>45563.46875</v>
+        <v>45570.375</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -31217,68 +31193,44 @@
       <c r="F314" t="n">
         <v>1481</v>
       </c>
-      <c r="G314" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H314" t="n">
-        <v>3</v>
-      </c>
-      <c r="I314" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="J314" t="n">
-        <v>0.4904913518630066</v>
-      </c>
-      <c r="K314" t="n">
-        <v>0.3122794940194475</v>
-      </c>
-      <c r="L314" t="n">
-        <v>0.1972291541175458</v>
-      </c>
-      <c r="M314" t="n">
-        <v>0.06741985854689081</v>
-      </c>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+      <c r="J314" t="inlineStr"/>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
       <c r="N314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O314" t="n">
-        <v>0.6185229515125987</v>
+        <v>0.3647594496461781</v>
       </c>
       <c r="P314" t="n">
-        <v>0.3144900159986573</v>
+        <v>0.4586169653408992</v>
       </c>
       <c r="Q314" t="n">
-        <v>0.06698703248874409</v>
+        <v>0.1766235850129228</v>
       </c>
       <c r="R314" t="n">
         <v>1</v>
       </c>
-      <c r="S314" t="n">
-        <v>0.1280315996495921</v>
-      </c>
+      <c r="S314" t="inlineStr"/>
       <c r="T314" t="n">
-        <v>1</v>
-      </c>
-      <c r="U314" t="n">
-        <v>0.1280315996495921</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U314" t="inlineStr"/>
       <c r="V314" t="n">
-        <v>0.6185229515125987</v>
-      </c>
-      <c r="W314" t="n">
-        <v>1.91</v>
-      </c>
+        <v>0.5413830346591008</v>
+      </c>
+      <c r="W314" t="inlineStr"/>
       <c r="X314" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y314" t="n">
-        <v>5.008241642681329</v>
-      </c>
-      <c r="Z314" t="n">
-        <v>5.008241642681329</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr"/>
+      <c r="Z314" t="inlineStr"/>
       <c r="AA314" t="inlineStr">
         <is>
           <t>spain</t>
@@ -31294,20 +31246,20 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>40FWnYcm</t>
         </is>
       </c>
       <c r="B315" s="2" t="n">
-        <v>45563.5625</v>
+        <v>45570.46875</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -31316,68 +31268,44 @@
       <c r="F315" t="n">
         <v>1481</v>
       </c>
-      <c r="G315" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H315" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I315" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="J315" t="n">
-        <v>0.5439668439257036</v>
-      </c>
-      <c r="K315" t="n">
-        <v>0.2767831294092551</v>
-      </c>
-      <c r="L315" t="n">
-        <v>0.1792500266650414</v>
-      </c>
-      <c r="M315" t="n">
-        <v>0.06262851961593885</v>
-      </c>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
+      <c r="J315" t="inlineStr"/>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
       <c r="N315" t="n">
         <v>1</v>
       </c>
       <c r="O315" t="n">
-        <v>0.4916837424854436</v>
+        <v>0.4545384437128644</v>
       </c>
       <c r="P315" t="n">
-        <v>0.4236096024691185</v>
+        <v>0.3444309532001786</v>
       </c>
       <c r="Q315" t="n">
-        <v>0.08470665504543799</v>
+        <v>0.2010306030869569</v>
       </c>
       <c r="R315" t="n">
         <v>1</v>
       </c>
-      <c r="S315" t="n">
-        <v>-0.05228310144026005</v>
-      </c>
+      <c r="S315" t="inlineStr"/>
       <c r="T315" t="n">
-        <v>1</v>
-      </c>
-      <c r="U315" t="n">
-        <v>-0.05228310144026005</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U315" t="inlineStr"/>
       <c r="V315" t="n">
-        <v>0.4916837424854436</v>
-      </c>
-      <c r="W315" t="n">
-        <v>1.73</v>
-      </c>
+        <v>0.5454615562871357</v>
+      </c>
+      <c r="W315" t="inlineStr"/>
       <c r="X315" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y315" t="n">
-        <v>3.557870541297988</v>
-      </c>
-      <c r="Z315" t="n">
-        <v>3.557870541297988</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr"/>
+      <c r="Z315" t="inlineStr"/>
       <c r="AA315" t="inlineStr">
         <is>
           <t>spain</t>
@@ -31393,20 +31321,20 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>KApUeTtI</t>
         </is>
       </c>
       <c r="B316" s="2" t="n">
-        <v>45563.66666666666</v>
+        <v>45570.5625</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -31415,68 +31343,44 @@
       <c r="F316" t="n">
         <v>1481</v>
       </c>
-      <c r="G316" t="n">
-        <v>7</v>
-      </c>
-      <c r="H316" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I316" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J316" t="n">
-        <v>0.1361218733007069</v>
-      </c>
-      <c r="K316" t="n">
-        <v>0.2200584556824361</v>
-      </c>
-      <c r="L316" t="n">
-        <v>0.643819671016857</v>
-      </c>
-      <c r="M316" t="n">
-        <v>0.0494797007499086</v>
-      </c>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+      <c r="J316" t="inlineStr"/>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
       <c r="N316" t="n">
         <v>2</v>
       </c>
       <c r="O316" t="n">
-        <v>0.1367878370483812</v>
+        <v>0.2683675776041386</v>
       </c>
       <c r="P316" t="n">
-        <v>0.2824706381613762</v>
+        <v>0.3637864018196887</v>
       </c>
       <c r="Q316" t="n">
-        <v>0.5807415247902425</v>
+        <v>0.3678460205761727</v>
       </c>
       <c r="R316" t="n">
         <v>1</v>
       </c>
-      <c r="S316" t="n">
-        <v>-0.06307814622661445</v>
-      </c>
+      <c r="S316" t="inlineStr"/>
       <c r="T316" t="n">
-        <v>2</v>
-      </c>
-      <c r="U316" t="n">
-        <v>-0.06307814622661445</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U316" t="inlineStr"/>
       <c r="V316" t="n">
-        <v>0.5807415247902425</v>
-      </c>
-      <c r="W316" t="n">
-        <v>1.48</v>
-      </c>
+        <v>0.6321539794238273</v>
+      </c>
+      <c r="W316" t="inlineStr"/>
       <c r="X316" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y316" t="n">
-        <v>4.1915716839178</v>
-      </c>
-      <c r="Z316" t="n">
-        <v>4.1915716839178</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr"/>
+      <c r="Z316" t="inlineStr"/>
       <c r="AA316" t="inlineStr">
         <is>
           <t>spain</t>
@@ -31492,20 +31396,20 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B317" s="2" t="n">
-        <v>45564.375</v>
+        <v>45570.5625</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -31514,68 +31418,44 @@
       <c r="F317" t="n">
         <v>1481</v>
       </c>
-      <c r="G317" t="n">
-        <v>2</v>
-      </c>
-      <c r="H317" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I317" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J317" t="n">
-        <v>0.4664634146341464</v>
-      </c>
-      <c r="K317" t="n">
-        <v>0.2591463414634146</v>
-      </c>
-      <c r="L317" t="n">
-        <v>0.274390243902439</v>
-      </c>
-      <c r="M317" t="n">
-        <v>0.07189542483660127</v>
-      </c>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317" t="inlineStr"/>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
       <c r="N317" t="n">
         <v>0</v>
       </c>
       <c r="O317" t="n">
-        <v>0.3065355097973315</v>
+        <v>0.2969499861157854</v>
       </c>
       <c r="P317" t="n">
-        <v>0.3817064870898392</v>
+        <v>0.4909456141240842</v>
       </c>
       <c r="Q317" t="n">
-        <v>0.3117580031128292</v>
+        <v>0.2121043997601303</v>
       </c>
       <c r="R317" t="n">
         <v>1</v>
       </c>
-      <c r="S317" t="n">
-        <v>0.1225601456264246</v>
-      </c>
+      <c r="S317" t="inlineStr"/>
       <c r="T317" t="n">
         <v>0</v>
       </c>
-      <c r="U317" t="n">
-        <v>0.1225601456264246</v>
-      </c>
+      <c r="U317" t="inlineStr"/>
       <c r="V317" t="n">
-        <v>0.3817064870898392</v>
-      </c>
-      <c r="W317" t="n">
-        <v>3.6</v>
-      </c>
+        <v>0.5090543858759158</v>
+      </c>
+      <c r="W317" t="inlineStr"/>
       <c r="X317" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y317" t="n">
-        <v>3.09071525842319</v>
-      </c>
-      <c r="Z317" t="n">
-        <v>3.09071525842319</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr"/>
+      <c r="Z317" t="inlineStr"/>
       <c r="AA317" t="inlineStr">
         <is>
           <t>spain</t>
@@ -31591,20 +31471,20 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>CQIvoCSa</t>
         </is>
       </c>
       <c r="B318" s="2" t="n">
-        <v>45564.46875</v>
+        <v>45570.66666666666</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -31613,68 +31493,44 @@
       <c r="F318" t="n">
         <v>1481</v>
       </c>
-      <c r="G318" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H318" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I318" t="n">
-        <v>5</v>
-      </c>
-      <c r="J318" t="n">
-        <v>0.5557224391709222</v>
-      </c>
-      <c r="K318" t="n">
-        <v>0.2553319315109642</v>
-      </c>
-      <c r="L318" t="n">
-        <v>0.1889456293181136</v>
-      </c>
-      <c r="M318" t="n">
-        <v>0.05850556438791732</v>
-      </c>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+      <c r="J318" t="inlineStr"/>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
       <c r="N318" t="n">
         <v>1</v>
       </c>
       <c r="O318" t="n">
-        <v>0.4763735152800625</v>
+        <v>0.744151399906815</v>
       </c>
       <c r="P318" t="n">
-        <v>0.3957119312550064</v>
+        <v>0.2003635295287127</v>
       </c>
       <c r="Q318" t="n">
-        <v>0.1279145534649311</v>
+        <v>0.05548507056447213</v>
       </c>
       <c r="R318" t="n">
         <v>1</v>
       </c>
-      <c r="S318" t="n">
-        <v>-0.07934892389085973</v>
-      </c>
+      <c r="S318" t="inlineStr"/>
       <c r="T318" t="n">
-        <v>1</v>
-      </c>
-      <c r="U318" t="n">
-        <v>-0.07934892389085973</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U318" t="inlineStr"/>
       <c r="V318" t="n">
-        <v>0.4763735152800625</v>
-      </c>
-      <c r="W318" t="n">
-        <v>1.7</v>
-      </c>
+        <v>0.255848600093185</v>
+      </c>
+      <c r="W318" t="inlineStr"/>
       <c r="X318" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y318" t="n">
-        <v>3.214747467173726</v>
-      </c>
-      <c r="Z318" t="n">
-        <v>3.214747467173726</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr"/>
+      <c r="Z318" t="inlineStr"/>
       <c r="AA318" t="inlineStr">
         <is>
           <t>spain</t>
@@ -31690,20 +31546,20 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B319" s="2" t="n">
-        <v>45564.5625</v>
+        <v>45571.375</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -31712,68 +31568,44 @@
       <c r="F319" t="n">
         <v>1481</v>
       </c>
-      <c r="G319" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H319" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I319" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J319" t="n">
-        <v>0.5960720381078533</v>
-      </c>
-      <c r="K319" t="n">
-        <v>0.2599536388414805</v>
-      </c>
-      <c r="L319" t="n">
-        <v>0.1439743230506661</v>
-      </c>
-      <c r="M319" t="n">
-        <v>0.06856660678316739</v>
-      </c>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
       <c r="N319" t="n">
         <v>1</v>
       </c>
       <c r="O319" t="n">
-        <v>0.6082259867265751</v>
+        <v>0.4741021754920535</v>
       </c>
       <c r="P319" t="n">
-        <v>0.3281564338314107</v>
+        <v>0.3518987645354678</v>
       </c>
       <c r="Q319" t="n">
-        <v>0.06361757944201411</v>
+        <v>0.1739990599724787</v>
       </c>
       <c r="R319" t="n">
         <v>1</v>
       </c>
-      <c r="S319" t="n">
-        <v>0.01215394861872188</v>
-      </c>
+      <c r="S319" t="inlineStr"/>
       <c r="T319" t="n">
-        <v>1</v>
-      </c>
-      <c r="U319" t="n">
-        <v>0.01215394861872188</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U319" t="inlineStr"/>
       <c r="V319" t="n">
-        <v>0.6082259867265751</v>
-      </c>
-      <c r="W319" t="n">
-        <v>1.57</v>
-      </c>
+        <v>0.5258978245079465</v>
+      </c>
+      <c r="W319" t="inlineStr"/>
       <c r="X319" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y319" t="n">
-        <v>4.924866098235528</v>
-      </c>
-      <c r="Z319" t="n">
-        <v>4.924866098235528</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr"/>
+      <c r="Z319" t="inlineStr"/>
       <c r="AA319" t="inlineStr">
         <is>
           <t>spain</t>
@@ -31789,20 +31621,20 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B320" s="2" t="n">
-        <v>45564.66666666666</v>
+        <v>45571.46875</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -31811,68 +31643,44 @@
       <c r="F320" t="n">
         <v>1481</v>
       </c>
-      <c r="G320" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H320" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I320" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J320" t="n">
-        <v>0.3067869752844252</v>
-      </c>
-      <c r="K320" t="n">
-        <v>0.2797175362887406</v>
-      </c>
-      <c r="L320" t="n">
-        <v>0.413495488426834</v>
-      </c>
-      <c r="M320" t="n">
-        <v>0.05148090091576618</v>
-      </c>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
       <c r="N320" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O320" t="n">
-        <v>0.2611593032482083</v>
+        <v>0.2509885528074592</v>
       </c>
       <c r="P320" t="n">
-        <v>0.4156629691983781</v>
+        <v>0.3180380645265662</v>
       </c>
       <c r="Q320" t="n">
-        <v>0.3231777275534136</v>
+        <v>0.4309733826659747</v>
       </c>
       <c r="R320" t="n">
         <v>1</v>
       </c>
-      <c r="S320" t="n">
-        <v>0.1359454329096375</v>
-      </c>
+      <c r="S320" t="inlineStr"/>
       <c r="T320" t="n">
-        <v>0</v>
-      </c>
-      <c r="U320" t="n">
-        <v>0.1359454329096375</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U320" t="inlineStr"/>
       <c r="V320" t="n">
-        <v>0.4156629691983781</v>
-      </c>
-      <c r="W320" t="n">
-        <v>3.4</v>
-      </c>
+        <v>0.5690266173340253</v>
+      </c>
+      <c r="W320" t="inlineStr"/>
       <c r="X320" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y320" t="n">
-        <v>3.365664259618797</v>
-      </c>
-      <c r="Z320" t="n">
-        <v>3.365664259618797</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr"/>
+      <c r="Z320" t="inlineStr"/>
       <c r="AA320" t="inlineStr">
         <is>
           <t>spain</t>
@@ -31888,20 +31696,20 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B321" s="2" t="n">
-        <v>45565.66666666666</v>
+        <v>45571.5625</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -31910,68 +31718,44 @@
       <c r="F321" t="n">
         <v>1481</v>
       </c>
-      <c r="G321" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H321" t="n">
-        <v>4</v>
-      </c>
-      <c r="I321" t="n">
-        <v>6</v>
-      </c>
-      <c r="J321" t="n">
-        <v>0.6106870229007634</v>
-      </c>
-      <c r="K321" t="n">
-        <v>0.233587786259542</v>
-      </c>
-      <c r="L321" t="n">
-        <v>0.1557251908396947</v>
-      </c>
-      <c r="M321" t="n">
-        <v>0.0702614379084967</v>
-      </c>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
       <c r="N321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O321" t="n">
-        <v>0.5468963056995511</v>
+        <v>0.258492267271013</v>
       </c>
       <c r="P321" t="n">
-        <v>0.3267484368818821</v>
+        <v>0.3871427701810209</v>
       </c>
       <c r="Q321" t="n">
-        <v>0.1263552574185668</v>
+        <v>0.3543649625479661</v>
       </c>
       <c r="R321" t="n">
         <v>1</v>
       </c>
-      <c r="S321" t="n">
-        <v>-0.06379071720121232</v>
-      </c>
+      <c r="S321" t="inlineStr"/>
       <c r="T321" t="n">
-        <v>1</v>
-      </c>
-      <c r="U321" t="n">
-        <v>-0.06379071720121232</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U321" t="inlineStr"/>
       <c r="V321" t="n">
-        <v>0.5468963056995511</v>
-      </c>
-      <c r="W321" t="n">
-        <v>1.53</v>
-      </c>
+        <v>0.6128572298189791</v>
+      </c>
+      <c r="W321" t="inlineStr"/>
       <c r="X321" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y321" t="n">
-        <v>3.911753832598348</v>
-      </c>
-      <c r="Z321" t="n">
-        <v>3.911753832598348</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr"/>
+      <c r="Z321" t="inlineStr"/>
       <c r="AA321" t="inlineStr">
         <is>
           <t>spain</t>
@@ -31987,20 +31771,20 @@
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B322" s="2" t="n">
-        <v>45569.66666666666</v>
+        <v>45571.66666666666</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -32017,27 +31801,27 @@
       <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr"/>
       <c r="N322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O322" t="n">
-        <v>0.4256642360700815</v>
+        <v>0.1457162461664724</v>
       </c>
       <c r="P322" t="n">
-        <v>0.3982294511643811</v>
+        <v>0.4079395198484711</v>
       </c>
       <c r="Q322" t="n">
-        <v>0.1761063127655375</v>
+        <v>0.4463442339850565</v>
       </c>
       <c r="R322" t="n">
         <v>1</v>
       </c>
       <c r="S322" t="inlineStr"/>
       <c r="T322" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="U322" t="inlineStr"/>
       <c r="V322" t="n">
-        <v>0.5743357639299185</v>
+        <v>0.5536557660149435</v>
       </c>
       <c r="W322" t="inlineStr"/>
       <c r="X322" t="inlineStr">
@@ -32062,74 +31846,98 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B323" s="2" t="n">
-        <v>45570.375</v>
+        <v>45559.65625</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F323" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G323" t="inlineStr"/>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
-      <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
-      <c r="M323" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="G323" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H323" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I323" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J323" t="n">
+        <v>0.6386964914272737</v>
+      </c>
+      <c r="K323" t="n">
+        <v>0.2100601794027478</v>
+      </c>
+      <c r="L323" t="n">
+        <v>0.1512433291699784</v>
+      </c>
+      <c r="M323" t="n">
+        <v>0.0578978978978979</v>
+      </c>
       <c r="N323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O323" t="n">
-        <v>0.3647594496461781</v>
+        <v>0.3867874089168166</v>
       </c>
       <c r="P323" t="n">
-        <v>0.4586169653408992</v>
+        <v>0.3710029627361938</v>
       </c>
       <c r="Q323" t="n">
-        <v>0.1766235850129228</v>
+        <v>0.2422096283469896</v>
       </c>
       <c r="R323" t="n">
         <v>1</v>
       </c>
-      <c r="S323" t="inlineStr"/>
+      <c r="S323" t="n">
+        <v>-0.2519090825104571</v>
+      </c>
       <c r="T323" t="n">
-        <v>0</v>
-      </c>
-      <c r="U323" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="U323" t="n">
+        <v>0.2519090825104571</v>
+      </c>
       <c r="V323" t="n">
-        <v>0.5413830346591008</v>
-      </c>
-      <c r="W323" t="inlineStr"/>
+        <v>0.6132125910831834</v>
+      </c>
+      <c r="W323" t="n">
+        <v>2.616279069767442</v>
+      </c>
       <c r="X323" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y323" t="inlineStr"/>
-      <c r="Z323" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y323" t="n">
+        <v>8.223704683281422</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>8.223704683281422</v>
+      </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr"/>
@@ -32137,20 +31945,20 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B324" s="2" t="n">
-        <v>45570.46875</v>
+        <v>45559.58333333334</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -32159,44 +31967,68 @@
       <c r="F324" t="n">
         <v>1481</v>
       </c>
-      <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
-      <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
-      <c r="M324" t="inlineStr"/>
+      <c r="G324" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H324" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I324" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J324" t="n">
+        <v>0.5884729329383249</v>
+      </c>
+      <c r="K324" t="n">
+        <v>0.2477780770266631</v>
+      </c>
+      <c r="L324" t="n">
+        <v>0.1637489900350121</v>
+      </c>
+      <c r="M324" t="n">
+        <v>0.06207093821510279</v>
+      </c>
       <c r="N324" t="n">
         <v>1</v>
       </c>
       <c r="O324" t="n">
-        <v>0.4545384437128644</v>
+        <v>0.5081509698904012</v>
       </c>
       <c r="P324" t="n">
-        <v>0.3444309532001786</v>
+        <v>0.417731030004452</v>
       </c>
       <c r="Q324" t="n">
-        <v>0.2010306030869569</v>
+        <v>0.07411800010514685</v>
       </c>
       <c r="R324" t="n">
         <v>1</v>
       </c>
-      <c r="S324" t="inlineStr"/>
+      <c r="S324" t="n">
+        <v>-0.08032196304792372</v>
+      </c>
       <c r="T324" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U324" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U324" t="n">
+        <v>-0.08032196304792372</v>
+      </c>
       <c r="V324" t="n">
-        <v>0.5454615562871357</v>
-      </c>
-      <c r="W324" t="inlineStr"/>
+        <v>0.5081509698904012</v>
+      </c>
+      <c r="W324" t="n">
+        <v>1.6</v>
+      </c>
       <c r="X324" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y324" t="inlineStr"/>
-      <c r="Z324" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y324" t="n">
+        <v>3.464173872247725</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>3.464173872247725</v>
+      </c>
       <c r="AA324" t="inlineStr">
         <is>
           <t>spain</t>
@@ -32212,20 +32044,20 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B325" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45559.58333333334</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -32234,44 +32066,68 @@
       <c r="F325" t="n">
         <v>1481</v>
       </c>
-      <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
-      <c r="J325" t="inlineStr"/>
-      <c r="K325" t="inlineStr"/>
-      <c r="L325" t="inlineStr"/>
-      <c r="M325" t="inlineStr"/>
+      <c r="G325" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H325" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I325" t="n">
+        <v>4</v>
+      </c>
+      <c r="J325" t="n">
+        <v>0.4600259692079391</v>
+      </c>
+      <c r="K325" t="n">
+        <v>0.3042107215729919</v>
+      </c>
+      <c r="L325" t="n">
+        <v>0.2357633092190688</v>
+      </c>
+      <c r="M325" t="n">
+        <v>0.06038552321007096</v>
+      </c>
       <c r="N325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O325" t="n">
-        <v>0.2683675776041386</v>
+        <v>0.3344433851488954</v>
       </c>
       <c r="P325" t="n">
-        <v>0.3637864018196887</v>
+        <v>0.3423132665106267</v>
       </c>
       <c r="Q325" t="n">
-        <v>0.3678460205761727</v>
+        <v>0.3232433483404779</v>
       </c>
       <c r="R325" t="n">
         <v>1</v>
       </c>
-      <c r="S325" t="inlineStr"/>
+      <c r="S325" t="n">
+        <v>0.03810254493763476</v>
+      </c>
       <c r="T325" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U325" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U325" t="n">
+        <v>0.03810254493763476</v>
+      </c>
       <c r="V325" t="n">
-        <v>0.6321539794238273</v>
-      </c>
-      <c r="W325" t="inlineStr"/>
+        <v>0.3423132665106267</v>
+      </c>
+      <c r="W325" t="n">
+        <v>3.1</v>
+      </c>
       <c r="X325" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y325" t="inlineStr"/>
-      <c r="Z325" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y325" t="n">
+        <v>2.771744446973642</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>2.771744446973642</v>
+      </c>
       <c r="AA325" t="inlineStr">
         <is>
           <t>spain</t>
@@ -32287,20 +32143,20 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B326" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45559.66666666666</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -32309,44 +32165,68 @@
       <c r="F326" t="n">
         <v>1481</v>
       </c>
-      <c r="G326" t="inlineStr"/>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
-      <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr"/>
-      <c r="L326" t="inlineStr"/>
-      <c r="M326" t="inlineStr"/>
+      <c r="G326" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H326" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I326" t="n">
+        <v>12</v>
+      </c>
+      <c r="J326" t="n">
+        <v>0.7784431137724551</v>
+      </c>
+      <c r="K326" t="n">
+        <v>0.1437125748502994</v>
+      </c>
+      <c r="L326" t="n">
+        <v>0.07784431137724551</v>
+      </c>
+      <c r="M326" t="n">
+        <v>0.07051282051282048</v>
+      </c>
       <c r="N326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O326" t="n">
-        <v>0.2969499861157854</v>
+        <v>0.6847900085472095</v>
       </c>
       <c r="P326" t="n">
-        <v>0.4909456141240842</v>
+        <v>0.2397372511165876</v>
       </c>
       <c r="Q326" t="n">
-        <v>0.2121043997601303</v>
+        <v>0.0754727403362029</v>
       </c>
       <c r="R326" t="n">
         <v>1</v>
       </c>
-      <c r="S326" t="inlineStr"/>
+      <c r="S326" t="n">
+        <v>-0.09365310522524561</v>
+      </c>
       <c r="T326" t="n">
-        <v>0</v>
-      </c>
-      <c r="U326" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U326" t="n">
+        <v>-0.09365310522524561</v>
+      </c>
       <c r="V326" t="n">
-        <v>0.5090543858759158</v>
-      </c>
-      <c r="W326" t="inlineStr"/>
+        <v>0.6847900085472095</v>
+      </c>
+      <c r="W326" t="n">
+        <v>1.2</v>
+      </c>
       <c r="X326" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y326" t="inlineStr"/>
-      <c r="Z326" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y326" t="n">
+        <v>4.786494096140978</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>4.786494096140978</v>
+      </c>
       <c r="AA326" t="inlineStr">
         <is>
           <t>spain</t>
@@ -32362,20 +32242,20 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>ddsD5q9j</t>
         </is>
       </c>
       <c r="B327" s="2" t="n">
-        <v>45570.66666666666</v>
+        <v>45560.58333333334</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -32384,44 +32264,68 @@
       <c r="F327" t="n">
         <v>1481</v>
       </c>
-      <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr"/>
-      <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
-      <c r="M327" t="inlineStr"/>
+      <c r="G327" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H327" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I327" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J327" t="n">
+        <v>0.5399533013361008</v>
+      </c>
+      <c r="K327" t="n">
+        <v>0.2524646517057984</v>
+      </c>
+      <c r="L327" t="n">
+        <v>0.2075820469581009</v>
+      </c>
+      <c r="M327" t="n">
+        <v>0.07052717457341728</v>
+      </c>
       <c r="N327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O327" t="n">
-        <v>0.744151399906815</v>
+        <v>0.455178067425352</v>
       </c>
       <c r="P327" t="n">
-        <v>0.2003635295287127</v>
+        <v>0.4579952692095922</v>
       </c>
       <c r="Q327" t="n">
-        <v>0.05548507056447213</v>
+        <v>0.08682666336505597</v>
       </c>
       <c r="R327" t="n">
         <v>1</v>
       </c>
-      <c r="S327" t="inlineStr"/>
+      <c r="S327" t="n">
+        <v>0.2055306175037938</v>
+      </c>
       <c r="T327" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U327" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U327" t="n">
+        <v>0.2055306175037938</v>
+      </c>
       <c r="V327" t="n">
-        <v>0.255848600093185</v>
-      </c>
-      <c r="W327" t="inlineStr"/>
+        <v>0.4579952692095922</v>
+      </c>
+      <c r="W327" t="n">
+        <v>3.7</v>
+      </c>
       <c r="X327" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y327" t="inlineStr"/>
-      <c r="Z327" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y327" t="n">
+        <v>3.708433088533181</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>3.708433088533181</v>
+      </c>
       <c r="AA327" t="inlineStr">
         <is>
           <t>spain</t>
@@ -32437,20 +32341,20 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>QDjsB5oT</t>
         </is>
       </c>
       <c r="B328" s="2" t="n">
-        <v>45571.375</v>
+        <v>45560.66666666666</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -32459,44 +32363,68 @@
       <c r="F328" t="n">
         <v>1481</v>
       </c>
-      <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
-      <c r="L328" t="inlineStr"/>
-      <c r="M328" t="inlineStr"/>
+      <c r="G328" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H328" t="n">
+        <v>7</v>
+      </c>
+      <c r="I328" t="n">
+        <v>11</v>
+      </c>
+      <c r="J328" t="n">
+        <v>0.7780921584478578</v>
+      </c>
+      <c r="K328" t="n">
+        <v>0.1356103476151981</v>
+      </c>
+      <c r="L328" t="n">
+        <v>0.08629749393694423</v>
+      </c>
+      <c r="M328" t="n">
+        <v>0.05343836491377463</v>
+      </c>
       <c r="N328" t="n">
         <v>1</v>
       </c>
       <c r="O328" t="n">
-        <v>0.4741021754920535</v>
+        <v>0.6285929293662166</v>
       </c>
       <c r="P328" t="n">
-        <v>0.3518987645354678</v>
+        <v>0.3276743139384044</v>
       </c>
       <c r="Q328" t="n">
-        <v>0.1739990599724787</v>
+        <v>0.04373275669537902</v>
       </c>
       <c r="R328" t="n">
         <v>1</v>
       </c>
-      <c r="S328" t="inlineStr"/>
+      <c r="S328" t="n">
+        <v>-0.1494992290816413</v>
+      </c>
       <c r="T328" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U328" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U328" t="n">
+        <v>-0.1494992290816413</v>
+      </c>
       <c r="V328" t="n">
-        <v>0.5258978245079465</v>
-      </c>
-      <c r="W328" t="inlineStr"/>
+        <v>0.6285929293662166</v>
+      </c>
+      <c r="W328" t="n">
+        <v>1.22</v>
+      </c>
       <c r="X328" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y328" t="inlineStr"/>
-      <c r="Z328" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y328" t="n">
+        <v>3.879269176097217</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>3.879269176097217</v>
+      </c>
       <c r="AA328" t="inlineStr">
         <is>
           <t>spain</t>
@@ -32512,20 +32440,20 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>bqbA3PNE</t>
         </is>
       </c>
       <c r="B329" s="2" t="n">
-        <v>45571.46875</v>
+        <v>45561.58333333334</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -32534,44 +32462,68 @@
       <c r="F329" t="n">
         <v>1481</v>
       </c>
-      <c r="G329" t="inlineStr"/>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr"/>
-      <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr"/>
-      <c r="L329" t="inlineStr"/>
-      <c r="M329" t="inlineStr"/>
+      <c r="G329" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H329" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I329" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J329" t="n">
+        <v>0.2906808305166586</v>
+      </c>
+      <c r="K329" t="n">
+        <v>0.269917914051183</v>
+      </c>
+      <c r="L329" t="n">
+        <v>0.4394012554321584</v>
+      </c>
+      <c r="M329" t="n">
+        <v>0.0585228724763609</v>
+      </c>
       <c r="N329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O329" t="n">
-        <v>0.2509885528074592</v>
+        <v>0.3604836284255615</v>
       </c>
       <c r="P329" t="n">
-        <v>0.3180380645265662</v>
+        <v>0.3099523964448786</v>
       </c>
       <c r="Q329" t="n">
-        <v>0.4309733826659747</v>
+        <v>0.3295639751295599</v>
       </c>
       <c r="R329" t="n">
         <v>1</v>
       </c>
-      <c r="S329" t="inlineStr"/>
+      <c r="S329" t="n">
+        <v>0.06980279790890292</v>
+      </c>
       <c r="T329" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U329" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U329" t="n">
+        <v>0.06980279790890292</v>
+      </c>
       <c r="V329" t="n">
-        <v>0.5690266173340253</v>
-      </c>
-      <c r="W329" t="inlineStr"/>
+        <v>0.3604836284255615</v>
+      </c>
+      <c r="W329" t="n">
+        <v>3.25</v>
+      </c>
       <c r="X329" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y329" t="inlineStr"/>
-      <c r="Z329" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y329" t="n">
+        <v>2.91887166833612</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>2.91887166833612</v>
+      </c>
       <c r="AA329" t="inlineStr">
         <is>
           <t>spain</t>
@@ -32587,15 +32539,15 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>6VWd5zF7</t>
         </is>
       </c>
       <c r="B330" s="2" t="n">
-        <v>45571.5625</v>
+        <v>45561.58333333334</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -32609,44 +32561,68 @@
       <c r="F330" t="n">
         <v>1481</v>
       </c>
-      <c r="G330" t="inlineStr"/>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
-      <c r="L330" t="inlineStr"/>
-      <c r="M330" t="inlineStr"/>
+      <c r="G330" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H330" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I330" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J330" t="n">
+        <v>0.2920934043424826</v>
+      </c>
+      <c r="K330" t="n">
+        <v>0.3015157722244982</v>
+      </c>
+      <c r="L330" t="n">
+        <v>0.4063908234330194</v>
+      </c>
+      <c r="M330" t="n">
+        <v>0.06986325385694236</v>
+      </c>
       <c r="N330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O330" t="n">
-        <v>0.258492267271013</v>
+        <v>0.1453172769338086</v>
       </c>
       <c r="P330" t="n">
-        <v>0.3871427701810209</v>
+        <v>0.3228440243595109</v>
       </c>
       <c r="Q330" t="n">
-        <v>0.3543649625479661</v>
+        <v>0.5318386987066804</v>
       </c>
       <c r="R330" t="n">
         <v>1</v>
       </c>
-      <c r="S330" t="inlineStr"/>
+      <c r="S330" t="n">
+        <v>0.1254478752736611</v>
+      </c>
       <c r="T330" t="n">
-        <v>0</v>
-      </c>
-      <c r="U330" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U330" t="n">
+        <v>0.1254478752736611</v>
+      </c>
       <c r="V330" t="n">
-        <v>0.6128572298189791</v>
-      </c>
-      <c r="W330" t="inlineStr"/>
+        <v>0.5318386987066804</v>
+      </c>
+      <c r="W330" t="n">
+        <v>2.3</v>
+      </c>
       <c r="X330" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y330" t="inlineStr"/>
-      <c r="Z330" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y330" t="n">
+        <v>4.306350656088775</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>4.306350656088775</v>
+      </c>
       <c r="AA330" t="inlineStr">
         <is>
           <t>spain</t>
@@ -32662,15 +32638,15 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>pGrl7dpe</t>
         </is>
       </c>
       <c r="B331" s="2" t="n">
-        <v>45571.66666666666</v>
+        <v>45561.66666666666</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -32684,44 +32660,68 @@
       <c r="F331" t="n">
         <v>1481</v>
       </c>
-      <c r="G331" t="inlineStr"/>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr"/>
-      <c r="J331" t="inlineStr"/>
-      <c r="K331" t="inlineStr"/>
-      <c r="L331" t="inlineStr"/>
-      <c r="M331" t="inlineStr"/>
+      <c r="G331" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H331" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I331" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J331" t="n">
+        <v>0.2489695261581821</v>
+      </c>
+      <c r="K331" t="n">
+        <v>0.2556984322705654</v>
+      </c>
+      <c r="L331" t="n">
+        <v>0.4953320415712524</v>
+      </c>
+      <c r="M331" t="n">
+        <v>0.05698837443119609</v>
+      </c>
       <c r="N331" t="n">
         <v>2</v>
       </c>
       <c r="O331" t="n">
-        <v>0.1457162461664724</v>
+        <v>0.1661497387236976</v>
       </c>
       <c r="P331" t="n">
-        <v>0.4079395198484711</v>
+        <v>0.4027355240033786</v>
       </c>
       <c r="Q331" t="n">
-        <v>0.4463442339850565</v>
+        <v>0.4311147372729238</v>
       </c>
       <c r="R331" t="n">
         <v>1</v>
       </c>
-      <c r="S331" t="inlineStr"/>
+      <c r="S331" t="n">
+        <v>-0.06421730429832861</v>
+      </c>
       <c r="T331" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U331" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U331" t="n">
+        <v>-0.06421730429832861</v>
+      </c>
       <c r="V331" t="n">
-        <v>0.5536557660149435</v>
-      </c>
-      <c r="W331" t="inlineStr"/>
+        <v>0.4311147372729238</v>
+      </c>
+      <c r="W331" t="n">
+        <v>1.91</v>
+      </c>
       <c r="X331" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y331" t="inlineStr"/>
-      <c r="Z331" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y331" t="n">
+        <v>2.970804879467469</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>2.970804879467469</v>
+      </c>
       <c r="AA331" t="inlineStr">
         <is>
           <t>spain</t>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -41496,7 +41496,7 @@
       </c>
       <c r="Y411" t="inlineStr"/>
       <c r="Z411" t="n">
-        <v>7.725158059933142</v>
+        <v>6.910764987531603</v>
       </c>
       <c r="AA411" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
       </c>
       <c r="Y412" t="inlineStr"/>
       <c r="Z412" t="n">
-        <v>6.615509907496792</v>
+        <v>5.918096935843527</v>
       </c>
       <c r="AA412" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
       </c>
       <c r="Y413" t="inlineStr"/>
       <c r="Z413" t="n">
-        <v>4.62303247103263</v>
+        <v>4.135668252891451</v>
       </c>
       <c r="AA413" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
       </c>
       <c r="Y414" t="inlineStr"/>
       <c r="Z414" t="n">
-        <v>5.666965942883383</v>
+        <v>5.069549324399381</v>
       </c>
       <c r="AA414" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
       </c>
       <c r="Y415" t="inlineStr"/>
       <c r="Z415" t="n">
-        <v>6.003093546483254</v>
+        <v>5.370242055380344</v>
       </c>
       <c r="AA415" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
       </c>
       <c r="Y416" t="inlineStr"/>
       <c r="Z416" t="n">
-        <v>4.520240557811974</v>
+        <v>4.043712755104155</v>
       </c>
       <c r="AA416" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
       </c>
       <c r="Y417" t="inlineStr"/>
       <c r="Z417" t="n">
-        <v>8.41495176344549</v>
+        <v>7.527840021837651</v>
       </c>
       <c r="AA417" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
       </c>
       <c r="Y418" t="inlineStr"/>
       <c r="Z418" t="n">
-        <v>6.838631540274855</v>
+        <v>6.11769688652426</v>
       </c>
       <c r="AA418" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
       </c>
       <c r="Y419" t="inlineStr"/>
       <c r="Z419" t="n">
-        <v>8.699869703916461</v>
+        <v>7.782721658180952</v>
       </c>
       <c r="AA419" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
       </c>
       <c r="Y420" t="inlineStr"/>
       <c r="Z420" t="n">
-        <v>5.206441212048274</v>
+        <v>4.657573522602617</v>
       </c>
       <c r="AA420" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
       </c>
       <c r="Y421" t="inlineStr"/>
       <c r="Z421" t="n">
-        <v>4.283385300585495</v>
+        <v>3.831826990948319</v>
       </c>
       <c r="AA421" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
       </c>
       <c r="Y422" t="inlineStr"/>
       <c r="Z422" t="n">
-        <v>4.642359039779012</v>
+        <v>4.152957397474051</v>
       </c>
       <c r="AA422" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
       </c>
       <c r="Y423" t="inlineStr"/>
       <c r="Z423" t="n">
-        <v>6.031706845278793</v>
+        <v>5.395838914623856</v>
       </c>
       <c r="AA423" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
       </c>
       <c r="Y424" t="inlineStr"/>
       <c r="Z424" t="n">
-        <v>4.500651453251951</v>
+        <v>4.026188751468212</v>
       </c>
       <c r="AA424" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
       </c>
       <c r="Y425" t="inlineStr"/>
       <c r="Z425" t="n">
-        <v>6.100878994884513</v>
+        <v>5.457718874347508</v>
       </c>
       <c r="AA425" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
       </c>
       <c r="Y426" t="inlineStr"/>
       <c r="Z426" t="n">
-        <v>4.257836874547366</v>
+        <v>3.808971902834773</v>
       </c>
       <c r="AA426" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
       </c>
       <c r="Y427" t="inlineStr"/>
       <c r="Z427" t="n">
-        <v>6.477320852853209</v>
+        <v>5.794475894942879</v>
       </c>
       <c r="AA427" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
       </c>
       <c r="Y428" t="inlineStr"/>
       <c r="Z428" t="n">
-        <v>4.308542510312627</v>
+        <v>3.854332105124294</v>
       </c>
       <c r="AA428" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
       </c>
       <c r="Y429" t="inlineStr"/>
       <c r="Z429" t="n">
-        <v>4.702605993479978</v>
+        <v>4.206853063428317</v>
       </c>
       <c r="AA429" t="inlineStr">
         <is>
@@ -43381,7 +43381,7 @@
       </c>
       <c r="Y430" t="inlineStr"/>
       <c r="Z430" t="n">
-        <v>4.248365575956424</v>
+        <v>3.800499077012837</v>
       </c>
       <c r="AA430" t="inlineStr">
         <is>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE430"/>
+  <dimension ref="A1:AE435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33626,46 +33626,46 @@
         <v>5</v>
       </c>
       <c r="I332" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="J332" t="n">
-        <v>0.6306306306306306</v>
+        <v>0.6406685236768802</v>
       </c>
       <c r="K332" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.1922005571030641</v>
       </c>
       <c r="L332" t="n">
-        <v>0.1801801801801802</v>
+        <v>0.1671309192200557</v>
       </c>
       <c r="M332" t="n">
-        <v>0.05714285714285716</v>
+        <v>0.04057971014492745</v>
       </c>
       <c r="N332" t="n">
         <v>1</v>
       </c>
       <c r="O332" t="n">
-        <v>0.4802414178848267</v>
+        <v>0.4629707038402557</v>
       </c>
       <c r="P332" t="n">
-        <v>0.3722254633903503</v>
+        <v>0.3904054462909698</v>
       </c>
       <c r="Q332" t="n">
-        <v>0.1475331038236618</v>
+        <v>0.1466238349676132</v>
       </c>
       <c r="R332" t="n">
         <v>1</v>
       </c>
       <c r="S332" t="n">
-        <v>-0.150389212745804</v>
+        <v>-0.1776978198366245</v>
       </c>
       <c r="T332" t="n">
         <v>1</v>
       </c>
       <c r="U332" t="n">
-        <v>-0.150389212745804</v>
+        <v>-0.1776978198366245</v>
       </c>
       <c r="V332" t="n">
-        <v>0.4802414178848267</v>
+        <v>0.4629707038402557</v>
       </c>
       <c r="W332" t="n">
         <v>1.5</v>
@@ -33677,7 +33677,7 @@
       </c>
       <c r="Y332" t="inlineStr"/>
       <c r="Z332" t="n">
-        <v>4.997862501327692</v>
+        <v>4.616279480864103</v>
       </c>
       <c r="AA332" t="inlineStr">
         <is>
@@ -33689,9 +33689,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC332" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC332" t="inlineStr"/>
       <c r="AD332" t="inlineStr"/>
       <c r="AE332" t="inlineStr"/>
     </row>
@@ -33721,55 +33719,55 @@
         <v>481</v>
       </c>
       <c r="G333" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="H333" t="n">
         <v>3.5</v>
       </c>
       <c r="I333" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J333" t="n">
-        <v>0.4020260838352012</v>
+        <v>0.3883495145631068</v>
       </c>
       <c r="K333" t="n">
-        <v>0.2699317991464922</v>
+        <v>0.2718446601941747</v>
       </c>
       <c r="L333" t="n">
-        <v>0.3280421170183065</v>
+        <v>0.3398058252427185</v>
       </c>
       <c r="M333" t="n">
-        <v>0.0584684228301251</v>
+        <v>0.05102040816326525</v>
       </c>
       <c r="N333" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O333" t="n">
-        <v>0.2029433697462082</v>
+        <v>0.2126755714416504</v>
       </c>
       <c r="P333" t="n">
-        <v>0.3414356410503387</v>
+        <v>0.4157065749168396</v>
       </c>
       <c r="Q333" t="n">
-        <v>0.4556211531162262</v>
+        <v>0.37161785364151</v>
       </c>
       <c r="R333" t="n">
         <v>1</v>
       </c>
       <c r="S333" t="n">
-        <v>0.1275790360979197</v>
+        <v>0.1438619147226649</v>
       </c>
       <c r="T333" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U333" t="n">
-        <v>0.1275790360979197</v>
+        <v>0.1438619147226649</v>
       </c>
       <c r="V333" t="n">
-        <v>0.4556211531162262</v>
+        <v>0.4157065749168396</v>
       </c>
       <c r="W333" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="X333" t="inlineStr">
         <is>
@@ -33778,7 +33776,7 @@
       </c>
       <c r="Y333" t="inlineStr"/>
       <c r="Z333" t="n">
-        <v>5.621898040553345</v>
+        <v>5.12939305601984</v>
       </c>
       <c r="AA333" t="inlineStr">
         <is>
@@ -33790,9 +33788,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC333" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC333" t="inlineStr"/>
       <c r="AD333" t="inlineStr"/>
       <c r="AE333" t="inlineStr"/>
     </row>
@@ -33822,7 +33818,7 @@
         <v>481</v>
       </c>
       <c r="G334" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H334" t="n">
         <v>3.3</v>
@@ -33831,46 +33827,46 @@
         <v>3</v>
       </c>
       <c r="J334" t="n">
-        <v>0.3976861894432394</v>
+        <v>0.3956834532374101</v>
       </c>
       <c r="K334" t="n">
-        <v>0.2868161002651242</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="L334" t="n">
-        <v>0.3154977102916365</v>
+        <v>0.316546762589928</v>
       </c>
       <c r="M334" t="n">
-        <v>0.05653170359052706</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="N334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O334" t="n">
-        <v>0.3545161485671997</v>
+        <v>0.3598228693008423</v>
       </c>
       <c r="P334" t="n">
-        <v>0.3959226608276367</v>
+        <v>0.34445720911026</v>
       </c>
       <c r="Q334" t="n">
-        <v>0.24956114590168</v>
+        <v>0.2957199215888977</v>
       </c>
       <c r="R334" t="n">
         <v>1</v>
       </c>
       <c r="S334" t="n">
-        <v>0.1091065605625126</v>
+        <v>-0.03586058393656782</v>
       </c>
       <c r="T334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U334" t="n">
-        <v>0.1091065605625126</v>
+        <v>-0.03586058393656782</v>
       </c>
       <c r="V334" t="n">
-        <v>0.3959226608276367</v>
+        <v>0.3598228693008423</v>
       </c>
       <c r="W334" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="X334" t="inlineStr">
         <is>
@@ -33879,7 +33875,7 @@
       </c>
       <c r="Y334" t="inlineStr"/>
       <c r="Z334" t="n">
-        <v>4.885279833681822</v>
+        <v>4.439845406722504</v>
       </c>
       <c r="AA334" t="inlineStr">
         <is>
@@ -33891,9 +33887,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC334" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC334" t="inlineStr"/>
       <c r="AD334" t="inlineStr"/>
       <c r="AE334" t="inlineStr"/>
     </row>
@@ -33923,55 +33917,55 @@
         <v>481</v>
       </c>
       <c r="G335" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="H335" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="I335" t="n">
         <v>4.5</v>
       </c>
       <c r="J335" t="n">
-        <v>0.5766567227786064</v>
+        <v>0.5609973285841497</v>
       </c>
       <c r="K335" t="n">
-        <v>0.2157468570210952</v>
+        <v>0.2270703472840606</v>
       </c>
       <c r="L335" t="n">
-        <v>0.2075964202002983</v>
+        <v>0.2119323241317899</v>
       </c>
       <c r="M335" t="n">
-        <v>0.07045305505659627</v>
+        <v>0.0485527544351072</v>
       </c>
       <c r="N335" t="n">
         <v>1</v>
       </c>
       <c r="O335" t="n">
-        <v>0.5418547987937927</v>
+        <v>0.531466007232666</v>
       </c>
       <c r="P335" t="n">
-        <v>0.3147798776626587</v>
+        <v>0.3264229893684387</v>
       </c>
       <c r="Q335" t="n">
-        <v>0.1433653831481934</v>
+        <v>0.1421109735965729</v>
       </c>
       <c r="R335" t="n">
         <v>1</v>
       </c>
       <c r="S335" t="n">
-        <v>-0.03480192398481363</v>
+        <v>-0.02953132135148373</v>
       </c>
       <c r="T335" t="n">
         <v>1</v>
       </c>
       <c r="U335" t="n">
-        <v>-0.03480192398481363</v>
+        <v>-0.02953132135148373</v>
       </c>
       <c r="V335" t="n">
-        <v>0.5418547987937927</v>
+        <v>0.531466007232666</v>
       </c>
       <c r="W335" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="X335" t="inlineStr">
         <is>
@@ -33980,7 +33974,7 @@
       </c>
       <c r="Y335" t="inlineStr"/>
       <c r="Z335" t="n">
-        <v>6.685932843039379</v>
+        <v>6.557745803166986</v>
       </c>
       <c r="AA335" t="inlineStr">
         <is>
@@ -33992,9 +33986,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC335" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC335" t="inlineStr"/>
       <c r="AD335" t="inlineStr"/>
       <c r="AE335" t="inlineStr"/>
     </row>
@@ -34030,46 +34022,46 @@
         <v>3.75</v>
       </c>
       <c r="I336" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J336" t="n">
-        <v>0.4814305364511692</v>
+        <v>0.4850444624090541</v>
       </c>
       <c r="K336" t="n">
-        <v>0.2503438789546079</v>
+        <v>0.2522231204527081</v>
       </c>
       <c r="L336" t="n">
-        <v>0.2682255845942227</v>
+        <v>0.2627324171382376</v>
       </c>
       <c r="M336" t="n">
-        <v>0.06520146520146541</v>
+        <v>0.05726495726495751</v>
       </c>
       <c r="N336" t="n">
         <v>1</v>
       </c>
       <c r="O336" t="n">
-        <v>0.6030269861221313</v>
+        <v>0.5834006071090698</v>
       </c>
       <c r="P336" t="n">
-        <v>0.2290270328521729</v>
+        <v>0.2403881400823593</v>
       </c>
       <c r="Q336" t="n">
-        <v>0.1679459363222122</v>
+        <v>0.1762113869190216</v>
       </c>
       <c r="R336" t="n">
         <v>1</v>
       </c>
       <c r="S336" t="n">
-        <v>0.1215964496709622</v>
+        <v>0.09835614470001569</v>
       </c>
       <c r="T336" t="n">
         <v>1</v>
       </c>
       <c r="U336" t="n">
-        <v>0.1215964496709622</v>
+        <v>0.09835614470001569</v>
       </c>
       <c r="V336" t="n">
-        <v>0.6030269861221313</v>
+        <v>0.5834006071090698</v>
       </c>
       <c r="W336" t="n">
         <v>1.95</v>
@@ -34081,7 +34073,7 @@
       </c>
       <c r="Y336" t="inlineStr"/>
       <c r="Z336" t="n">
-        <v>7.440734936237675</v>
+        <v>7.198565535273666</v>
       </c>
       <c r="AA336" t="inlineStr">
         <is>
@@ -34093,9 +34085,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC336" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC336" t="inlineStr"/>
       <c r="AD336" t="inlineStr"/>
       <c r="AE336" t="inlineStr"/>
     </row>
@@ -34125,55 +34115,55 @@
         <v>481</v>
       </c>
       <c r="G337" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="H337" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I337" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J337" t="n">
-        <v>0.3997567403202919</v>
+        <v>0.4125736738703341</v>
       </c>
       <c r="K337" t="n">
-        <v>0.2763024528684371</v>
+        <v>0.2711198428290766</v>
       </c>
       <c r="L337" t="n">
-        <v>0.323940806811271</v>
+        <v>0.3163064833005894</v>
       </c>
       <c r="M337" t="n">
-        <v>0.06447714815933714</v>
+        <v>0.05383022774327118</v>
       </c>
       <c r="N337" t="n">
         <v>0</v>
       </c>
       <c r="O337" t="n">
-        <v>0.2403905987739563</v>
+        <v>0.2406667470932007</v>
       </c>
       <c r="P337" t="n">
-        <v>0.4160029888153076</v>
+        <v>0.4178179502487183</v>
       </c>
       <c r="Q337" t="n">
-        <v>0.3436063826084137</v>
+        <v>0.3415153324604034</v>
       </c>
       <c r="R337" t="n">
         <v>1</v>
       </c>
       <c r="S337" t="n">
-        <v>0.1397005359468705</v>
+        <v>0.1466981074196416</v>
       </c>
       <c r="T337" t="n">
         <v>0</v>
       </c>
       <c r="U337" t="n">
-        <v>0.1397005359468705</v>
+        <v>0.1466981074196416</v>
       </c>
       <c r="V337" t="n">
-        <v>0.4160029888153076</v>
+        <v>0.4178179502487183</v>
       </c>
       <c r="W337" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="X337" t="inlineStr">
         <is>
@@ -34182,7 +34172,7 @@
       </c>
       <c r="Y337" t="inlineStr"/>
       <c r="Z337" t="n">
-        <v>5.13305049971751</v>
+        <v>5.155445263561076</v>
       </c>
       <c r="AA337" t="inlineStr">
         <is>
@@ -34194,9 +34184,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC337" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC337" t="inlineStr"/>
       <c r="AD337" t="inlineStr"/>
       <c r="AE337" t="inlineStr"/>
     </row>
@@ -34226,7 +34214,7 @@
         <v>481</v>
       </c>
       <c r="G338" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="H338" t="n">
         <v>3.9</v>
@@ -34235,43 +34223,43 @@
         <v>1.67</v>
       </c>
       <c r="J338" t="n">
-        <v>0.197540225352967</v>
+        <v>0.1895352559438931</v>
       </c>
       <c r="K338" t="n">
-        <v>0.2405938642119471</v>
+        <v>0.2429939178767861</v>
       </c>
       <c r="L338" t="n">
-        <v>0.5618659104350859</v>
+        <v>0.5674708261793209</v>
       </c>
       <c r="M338" t="n">
-        <v>0.06573896740931096</v>
+        <v>0.05521265161983724</v>
       </c>
       <c r="N338" t="n">
         <v>2</v>
       </c>
       <c r="O338" t="n">
-        <v>0.1511439085006714</v>
+        <v>0.1538346707820892</v>
       </c>
       <c r="P338" t="n">
-        <v>0.3679043650627136</v>
+        <v>0.3727922737598419</v>
       </c>
       <c r="Q338" t="n">
-        <v>0.4809516966342926</v>
+        <v>0.4733730852603912</v>
       </c>
       <c r="R338" t="n">
         <v>1</v>
       </c>
       <c r="S338" t="n">
-        <v>-0.08091421380079333</v>
+        <v>-0.09409774091892964</v>
       </c>
       <c r="T338" t="n">
         <v>2</v>
       </c>
       <c r="U338" t="n">
-        <v>-0.08091421380079333</v>
+        <v>-0.09409774091892964</v>
       </c>
       <c r="V338" t="n">
-        <v>0.4809516966342926</v>
+        <v>0.4733730852603912</v>
       </c>
       <c r="W338" t="n">
         <v>1.67</v>
@@ -34283,7 +34271,7 @@
       </c>
       <c r="Y338" t="inlineStr"/>
       <c r="Z338" t="n">
-        <v>5.934450985025705</v>
+        <v>5.840938688369491</v>
       </c>
       <c r="AA338" t="inlineStr">
         <is>
@@ -34295,9 +34283,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC338" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC338" t="inlineStr"/>
       <c r="AD338" t="inlineStr"/>
       <c r="AE338" t="inlineStr"/>
     </row>
@@ -34330,52 +34316,52 @@
         <v>8</v>
       </c>
       <c r="H339" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="I339" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="J339" t="n">
-        <v>0.1185698650127691</v>
+        <v>0.1197838486940859</v>
       </c>
       <c r="K339" t="n">
-        <v>0.1517694272163444</v>
+        <v>0.1597117982587811</v>
       </c>
       <c r="L339" t="n">
-        <v>0.7296607077708864</v>
+        <v>0.7205043530471329</v>
       </c>
       <c r="M339" t="n">
-        <v>0.0542307692307693</v>
+        <v>0.043546365914787</v>
       </c>
       <c r="N339" t="n">
         <v>2</v>
       </c>
       <c r="O339" t="n">
-        <v>0.1943183243274689</v>
+        <v>0.1648818552494049</v>
       </c>
       <c r="P339" t="n">
-        <v>0.2882589101791382</v>
+        <v>0.2964842617511749</v>
       </c>
       <c r="Q339" t="n">
-        <v>0.5174227356910706</v>
+        <v>0.5386338233947754</v>
       </c>
       <c r="R339" t="n">
         <v>1</v>
       </c>
       <c r="S339" t="n">
-        <v>-0.2122379720798159</v>
+        <v>-0.1818705296523575</v>
       </c>
       <c r="T339" t="n">
         <v>2</v>
       </c>
       <c r="U339" t="n">
-        <v>-0.2122379720798159</v>
+        <v>-0.1818705296523575</v>
       </c>
       <c r="V339" t="n">
-        <v>0.5174227356910706</v>
+        <v>0.5386338233947754</v>
       </c>
       <c r="W339" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X339" t="inlineStr">
         <is>
@@ -34384,7 +34370,7 @@
       </c>
       <c r="Y339" t="inlineStr"/>
       <c r="Z339" t="n">
-        <v>5.075066704917142</v>
+        <v>5.524141344098878</v>
       </c>
       <c r="AA339" t="inlineStr">
         <is>
@@ -34396,9 +34382,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC339" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC339" t="inlineStr"/>
       <c r="AD339" t="inlineStr"/>
       <c r="AE339" t="inlineStr"/>
     </row>
@@ -34428,55 +34412,55 @@
         <v>481</v>
       </c>
       <c r="G340" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="H340" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I340" t="n">
         <v>4.75</v>
       </c>
       <c r="J340" t="n">
-        <v>0.5714914533049666</v>
+        <v>0.5608856088560886</v>
       </c>
       <c r="K340" t="n">
-        <v>0.2299904629154134</v>
+        <v>0.2383763837638377</v>
       </c>
       <c r="L340" t="n">
-        <v>0.19851808377962</v>
+        <v>0.2007380073800738</v>
       </c>
       <c r="M340" t="n">
-        <v>0.06048936087446988</v>
+        <v>0.04876160990712064</v>
       </c>
       <c r="N340" t="n">
         <v>1</v>
       </c>
       <c r="O340" t="n">
-        <v>0.5172398686408997</v>
+        <v>0.5502976775169373</v>
       </c>
       <c r="P340" t="n">
-        <v>0.3701968193054199</v>
+        <v>0.3375295698642731</v>
       </c>
       <c r="Q340" t="n">
-        <v>0.1125633493065834</v>
+        <v>0.1121727451682091</v>
       </c>
       <c r="R340" t="n">
         <v>1</v>
       </c>
       <c r="S340" t="n">
-        <v>-0.05425158466406699</v>
+        <v>-0.01058793133915137</v>
       </c>
       <c r="T340" t="n">
         <v>1</v>
       </c>
       <c r="U340" t="n">
-        <v>-0.05425158466406699</v>
+        <v>-0.01058793133915137</v>
       </c>
       <c r="V340" t="n">
-        <v>0.5172398686408997</v>
+        <v>0.5502976775169373</v>
       </c>
       <c r="W340" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X340" t="inlineStr">
         <is>
@@ -34485,7 +34469,7 @@
       </c>
       <c r="Y340" t="inlineStr"/>
       <c r="Z340" t="n">
-        <v>6.382209834025338</v>
+        <v>6.790109312954435</v>
       </c>
       <c r="AA340" t="inlineStr">
         <is>
@@ -34497,9 +34481,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC340" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC340" t="inlineStr"/>
       <c r="AD340" t="inlineStr"/>
       <c r="AE340" t="inlineStr"/>
     </row>
@@ -34535,49 +34517,49 @@
         <v>3.5</v>
       </c>
       <c r="I341" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J341" t="n">
-        <v>0.4081222356252514</v>
+        <v>0.4125736738703341</v>
       </c>
       <c r="K341" t="n">
-        <v>0.268194611982308</v>
+        <v>0.2711198428290766</v>
       </c>
       <c r="L341" t="n">
-        <v>0.3236831523924407</v>
+        <v>0.3163064833005894</v>
       </c>
       <c r="M341" t="n">
-        <v>0.06532448061683449</v>
+        <v>0.05383022774327118</v>
       </c>
       <c r="N341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O341" t="n">
-        <v>0.2508946657180786</v>
+        <v>0.2533594071865082</v>
       </c>
       <c r="P341" t="n">
-        <v>0.37337726354599</v>
+        <v>0.376624584197998</v>
       </c>
       <c r="Q341" t="n">
-        <v>0.3757281303405762</v>
+        <v>0.3700159192085266</v>
       </c>
       <c r="R341" t="n">
         <v>1</v>
       </c>
       <c r="S341" t="n">
-        <v>0.05204497794813545</v>
+        <v>0.1055047413689214</v>
       </c>
       <c r="T341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U341" t="n">
-        <v>0.05204497794813545</v>
+        <v>0.1055047413689214</v>
       </c>
       <c r="V341" t="n">
-        <v>0.3757281303405762</v>
+        <v>0.376624584197998</v>
       </c>
       <c r="W341" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="X341" t="inlineStr">
         <is>
@@ -34586,7 +34568,7 @@
       </c>
       <c r="Y341" t="inlineStr"/>
       <c r="Z341" t="n">
-        <v>4.636100025855518</v>
+        <v>4.647161347635723</v>
       </c>
       <c r="AA341" t="inlineStr">
         <is>
@@ -34598,9 +34580,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC341" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC341" t="inlineStr"/>
       <c r="AD341" t="inlineStr"/>
       <c r="AE341" t="inlineStr"/>
     </row>
@@ -34630,52 +34610,52 @@
         <v>481</v>
       </c>
       <c r="G342" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="H342" t="n">
         <v>3.4</v>
       </c>
       <c r="I342" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="J342" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.3371104815864023</v>
       </c>
       <c r="K342" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2776203966005666</v>
       </c>
       <c r="L342" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.3852691218130311</v>
       </c>
       <c r="M342" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.05942376950780304</v>
       </c>
       <c r="N342" t="n">
         <v>0</v>
       </c>
       <c r="O342" t="n">
-        <v>0.3111074566841125</v>
+        <v>0.3169910907745361</v>
       </c>
       <c r="P342" t="n">
-        <v>0.4535876512527466</v>
+        <v>0.4297073781490326</v>
       </c>
       <c r="Q342" t="n">
-        <v>0.2353049218654633</v>
+        <v>0.2533015012741089</v>
       </c>
       <c r="R342" t="n">
         <v>1</v>
       </c>
       <c r="S342" t="n">
-        <v>0.175237135788829</v>
+        <v>0.152086981548466</v>
       </c>
       <c r="T342" t="n">
         <v>0</v>
       </c>
       <c r="U342" t="n">
-        <v>0.175237135788829</v>
+        <v>0.152086981548466</v>
       </c>
       <c r="V342" t="n">
-        <v>0.4535876512527466</v>
+        <v>0.4297073781490326</v>
       </c>
       <c r="W342" t="n">
         <v>3.4</v>
@@ -34687,7 +34667,7 @@
       </c>
       <c r="Y342" t="inlineStr"/>
       <c r="Z342" t="n">
-        <v>5.596806711795741</v>
+        <v>5.302148617781828</v>
       </c>
       <c r="AA342" t="inlineStr">
         <is>
@@ -34699,9 +34679,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC342" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC342" t="inlineStr"/>
       <c r="AD342" t="inlineStr"/>
       <c r="AE342" t="inlineStr"/>
     </row>
@@ -34755,28 +34733,28 @@
         <v>0</v>
       </c>
       <c r="O343" t="n">
-        <v>0.3935825228691101</v>
+        <v>0.3607814013957977</v>
       </c>
       <c r="P343" t="n">
-        <v>0.4183503687381744</v>
+        <v>0.4571996331214905</v>
       </c>
       <c r="Q343" t="n">
-        <v>0.1880670338869095</v>
+        <v>0.1820190101861954</v>
       </c>
       <c r="R343" t="n">
         <v>1</v>
       </c>
       <c r="S343" t="n">
-        <v>0.1764787017847941</v>
+        <v>0.2153279661681101</v>
       </c>
       <c r="T343" t="n">
         <v>0</v>
       </c>
       <c r="U343" t="n">
-        <v>0.1764787017847941</v>
+        <v>0.2153279661681101</v>
       </c>
       <c r="V343" t="n">
-        <v>0.4183503687381744</v>
+        <v>0.4571996331214905</v>
       </c>
       <c r="W343" t="n">
         <v>3.9</v>
@@ -34788,7 +34766,7 @@
       </c>
       <c r="Y343" t="inlineStr"/>
       <c r="Z343" t="n">
-        <v>5.162014762018634</v>
+        <v>5.641374865955225</v>
       </c>
       <c r="AA343" t="inlineStr">
         <is>
@@ -34800,9 +34778,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC343" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC343" t="inlineStr"/>
       <c r="AD343" t="inlineStr"/>
       <c r="AE343" t="inlineStr"/>
     </row>
@@ -34832,55 +34808,55 @@
         <v>481</v>
       </c>
       <c r="G344" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H344" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="I344" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J344" t="n">
-        <v>0.5490012957333573</v>
+        <v>0.5360824742268041</v>
       </c>
       <c r="K344" t="n">
-        <v>0.2193469380181774</v>
+        <v>0.2233676975945017</v>
       </c>
       <c r="L344" t="n">
-        <v>0.2316517662484654</v>
+        <v>0.2405498281786942</v>
       </c>
       <c r="M344" t="n">
-        <v>0.05288400332240517</v>
+        <v>0.06593406593406592</v>
       </c>
       <c r="N344" t="n">
         <v>1</v>
       </c>
       <c r="O344" t="n">
-        <v>0.373563140630722</v>
+        <v>0.3838088512420654</v>
       </c>
       <c r="P344" t="n">
-        <v>0.3170212209224701</v>
+        <v>0.2944603562355042</v>
       </c>
       <c r="Q344" t="n">
-        <v>0.3094155788421631</v>
+        <v>0.3217307925224304</v>
       </c>
       <c r="R344" t="n">
         <v>1</v>
       </c>
       <c r="S344" t="n">
-        <v>-0.1754381551026353</v>
+        <v>-0.1522736229847387</v>
       </c>
       <c r="T344" t="n">
         <v>1</v>
       </c>
       <c r="U344" t="n">
-        <v>-0.1754381551026353</v>
+        <v>-0.1522736229847387</v>
       </c>
       <c r="V344" t="n">
-        <v>0.373563140630722</v>
+        <v>0.3838088512420654</v>
       </c>
       <c r="W344" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X344" t="inlineStr">
         <is>
@@ -34889,7 +34865,7 @@
       </c>
       <c r="Y344" t="inlineStr"/>
       <c r="Z344" t="n">
-        <v>3.527022762527397</v>
+        <v>3.796357622054108</v>
       </c>
       <c r="AA344" t="inlineStr">
         <is>
@@ -34901,9 +34877,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC344" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC344" t="inlineStr"/>
       <c r="AD344" t="inlineStr"/>
       <c r="AE344" t="inlineStr"/>
     </row>
@@ -34957,28 +34931,28 @@
         <v>1</v>
       </c>
       <c r="O345" t="n">
-        <v>0.5057827234268188</v>
+        <v>0.5222343802452087</v>
       </c>
       <c r="P345" t="n">
-        <v>0.3135067522525787</v>
+        <v>0.2484476268291473</v>
       </c>
       <c r="Q345" t="n">
-        <v>0.18071049451828</v>
+        <v>0.2293179929256439</v>
       </c>
       <c r="R345" t="n">
         <v>1</v>
       </c>
       <c r="S345" t="n">
-        <v>-0.1121948046630687</v>
+        <v>-0.09574314784467886</v>
       </c>
       <c r="T345" t="n">
         <v>1</v>
       </c>
       <c r="U345" t="n">
-        <v>-0.1121948046630687</v>
+        <v>-0.09574314784467886</v>
       </c>
       <c r="V345" t="n">
-        <v>0.5057827234268188</v>
+        <v>0.5222343802452087</v>
       </c>
       <c r="W345" t="n">
         <v>1.53</v>
@@ -34990,7 +34964,7 @@
       </c>
       <c r="Y345" t="inlineStr"/>
       <c r="Z345" t="n">
-        <v>5.548655957345954</v>
+        <v>6.443836988097844</v>
       </c>
       <c r="AA345" t="inlineStr">
         <is>
@@ -35002,9 +34976,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC345" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC345" t="inlineStr"/>
       <c r="AD345" t="inlineStr"/>
       <c r="AE345" t="inlineStr"/>
     </row>
@@ -35058,28 +35030,28 @@
         <v>1</v>
       </c>
       <c r="O346" t="n">
-        <v>0.8248028755187988</v>
+        <v>0.846028208732605</v>
       </c>
       <c r="P346" t="n">
-        <v>0.1331712007522583</v>
+        <v>0.1117368414998055</v>
       </c>
       <c r="Q346" t="n">
-        <v>0.04202590882778168</v>
+        <v>0.04223495721817017</v>
       </c>
       <c r="R346" t="n">
         <v>1</v>
       </c>
       <c r="S346" t="n">
-        <v>-0.02018753845549637</v>
+        <v>0.001037794758309785</v>
       </c>
       <c r="T346" t="n">
         <v>1</v>
       </c>
       <c r="U346" t="n">
-        <v>-0.02018753845549637</v>
+        <v>0.001037794758309785</v>
       </c>
       <c r="V346" t="n">
-        <v>0.8248028755187988</v>
+        <v>0.846028208732605</v>
       </c>
       <c r="W346" t="n">
         <v>1.11</v>
@@ -35091,7 +35063,7 @@
       </c>
       <c r="Y346" t="inlineStr"/>
       <c r="Z346" t="n">
-        <v>10.17722210219472</v>
+        <v>10.43912095914781</v>
       </c>
       <c r="AA346" t="inlineStr">
         <is>
@@ -35103,9 +35075,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC346" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC346" t="inlineStr"/>
       <c r="AD346" t="inlineStr"/>
       <c r="AE346" t="inlineStr"/>
     </row>
@@ -35138,52 +35108,52 @@
         <v>2.7</v>
       </c>
       <c r="H347" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I347" t="n">
         <v>2.6</v>
       </c>
       <c r="J347" t="n">
-        <v>0.3530351437699681</v>
+        <v>0.3500611995104039</v>
       </c>
       <c r="K347" t="n">
-        <v>0.2803514376996806</v>
+        <v>0.2864137086903305</v>
       </c>
       <c r="L347" t="n">
-        <v>0.3666134185303515</v>
+        <v>0.3635250917992656</v>
       </c>
       <c r="M347" t="n">
-        <v>0.04910340204457841</v>
+        <v>0.05801605801605803</v>
       </c>
       <c r="N347" t="n">
         <v>0</v>
       </c>
       <c r="O347" t="n">
-        <v>0.3205142021179199</v>
+        <v>0.3225607573986053</v>
       </c>
       <c r="P347" t="n">
-        <v>0.3738568127155304</v>
+        <v>0.3748155534267426</v>
       </c>
       <c r="Q347" t="n">
-        <v>0.3056288659572601</v>
+        <v>0.3026237189769745</v>
       </c>
       <c r="R347" t="n">
         <v>1</v>
       </c>
       <c r="S347" t="n">
-        <v>0.09350537501584982</v>
+        <v>0.08840184473641205</v>
       </c>
       <c r="T347" t="n">
         <v>0</v>
       </c>
       <c r="U347" t="n">
-        <v>0.09350537501584982</v>
+        <v>0.08840184473641205</v>
       </c>
       <c r="V347" t="n">
-        <v>0.3738568127155304</v>
+        <v>0.3748155534267426</v>
       </c>
       <c r="W347" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="X347" t="inlineStr">
         <is>
@@ -35192,7 +35162,7 @@
       </c>
       <c r="Y347" t="inlineStr"/>
       <c r="Z347" t="n">
-        <v>4.613009884369452</v>
+        <v>4.624839762084519</v>
       </c>
       <c r="AA347" t="inlineStr">
         <is>
@@ -35204,9 +35174,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC347" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC347" t="inlineStr"/>
       <c r="AD347" t="inlineStr"/>
       <c r="AE347" t="inlineStr"/>
     </row>
@@ -35260,28 +35228,28 @@
         <v>0</v>
       </c>
       <c r="O348" t="n">
-        <v>0.2984151542186737</v>
+        <v>0.3361214995384216</v>
       </c>
       <c r="P348" t="n">
-        <v>0.4624479711055756</v>
+        <v>0.4123643636703491</v>
       </c>
       <c r="Q348" t="n">
-        <v>0.2391369342803955</v>
+        <v>0.2515142261981964</v>
       </c>
       <c r="R348" t="n">
         <v>1</v>
       </c>
       <c r="S348" t="n">
-        <v>0.2267791812966584</v>
+        <v>0.1766955738614319</v>
       </c>
       <c r="T348" t="n">
         <v>0</v>
       </c>
       <c r="U348" t="n">
-        <v>0.2267791812966584</v>
+        <v>0.1766955738614319</v>
       </c>
       <c r="V348" t="n">
-        <v>0.4624479711055756</v>
+        <v>0.4123643636703491</v>
       </c>
       <c r="W348" t="n">
         <v>4</v>
@@ -35293,7 +35261,7 @@
       </c>
       <c r="Y348" t="inlineStr"/>
       <c r="Z348" t="n">
-        <v>5.706133977394818</v>
+        <v>5.088153594837564</v>
       </c>
       <c r="AA348" t="inlineStr">
         <is>
@@ -35305,9 +35273,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC348" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC348" t="inlineStr"/>
       <c r="AD348" t="inlineStr"/>
       <c r="AE348" t="inlineStr"/>
     </row>
@@ -35337,55 +35303,55 @@
         <v>481</v>
       </c>
       <c r="G349" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H349" t="n">
         <v>3.6</v>
       </c>
       <c r="I349" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="J349" t="n">
-        <v>0.2775479503572772</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="K349" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="L349" t="n">
-        <v>0.46032342986085</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="M349" t="n">
-        <v>0.05970030288538175</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="N349" t="n">
         <v>2</v>
       </c>
       <c r="O349" t="n">
-        <v>0.2369374632835388</v>
+        <v>0.2351477593183517</v>
       </c>
       <c r="P349" t="n">
-        <v>0.3419689536094666</v>
+        <v>0.3429699242115021</v>
       </c>
       <c r="Q349" t="n">
-        <v>0.4210935235023499</v>
+        <v>0.4218823909759521</v>
       </c>
       <c r="R349" t="n">
         <v>1</v>
       </c>
       <c r="S349" t="n">
-        <v>-0.03922990635850016</v>
+        <v>-0.04826686275539116</v>
       </c>
       <c r="T349" t="n">
         <v>2</v>
       </c>
       <c r="U349" t="n">
-        <v>-0.03922990635850016</v>
+        <v>-0.04826686275539116</v>
       </c>
       <c r="V349" t="n">
-        <v>0.4210935235023499</v>
+        <v>0.4218823909759521</v>
       </c>
       <c r="W349" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="X349" t="inlineStr">
         <is>
@@ -35394,7 +35360,7 @@
       </c>
       <c r="Y349" t="inlineStr"/>
       <c r="Z349" t="n">
-        <v>5.195862480212083</v>
+        <v>5.205596296286619</v>
       </c>
       <c r="AA349" t="inlineStr">
         <is>
@@ -35406,9 +35372,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC349" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC349" t="inlineStr"/>
       <c r="AD349" t="inlineStr"/>
       <c r="AE349" t="inlineStr"/>
     </row>
@@ -35462,28 +35426,28 @@
         <v>0</v>
       </c>
       <c r="O350" t="n">
-        <v>0.273058295249939</v>
+        <v>0.2728021442890167</v>
       </c>
       <c r="P350" t="n">
-        <v>0.366264671087265</v>
+        <v>0.3646692931652069</v>
       </c>
       <c r="Q350" t="n">
-        <v>0.3606770038604736</v>
+        <v>0.3625285625457764</v>
       </c>
       <c r="R350" t="n">
         <v>1</v>
       </c>
       <c r="S350" t="n">
-        <v>0.1118197876419865</v>
+        <v>0.1102244097199284</v>
       </c>
       <c r="T350" t="n">
         <v>0</v>
       </c>
       <c r="U350" t="n">
-        <v>0.1118197876419865</v>
+        <v>0.1102244097199284</v>
       </c>
       <c r="V350" t="n">
-        <v>0.366264671087265</v>
+        <v>0.3646692931652069</v>
       </c>
       <c r="W350" t="n">
         <v>3.7</v>
@@ -35495,7 +35459,7 @@
       </c>
       <c r="Y350" t="inlineStr"/>
       <c r="Z350" t="n">
-        <v>4.519330638242219</v>
+        <v>4.499645309866624</v>
       </c>
       <c r="AA350" t="inlineStr">
         <is>
@@ -35507,9 +35471,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC350" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC350" t="inlineStr"/>
       <c r="AD350" t="inlineStr"/>
       <c r="AE350" t="inlineStr"/>
     </row>
@@ -35545,46 +35507,46 @@
         <v>3.4</v>
       </c>
       <c r="I351" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J351" t="n">
-        <v>0.4302959501557632</v>
+        <v>0.4322033898305084</v>
       </c>
       <c r="K351" t="n">
-        <v>0.2784267912772586</v>
+        <v>0.2796610169491525</v>
       </c>
       <c r="L351" t="n">
-        <v>0.2912772585669782</v>
+        <v>0.288135593220339</v>
       </c>
       <c r="M351" t="n">
-        <v>0.05635540929658589</v>
+        <v>0.05169340463458116</v>
       </c>
       <c r="N351" t="n">
         <v>0</v>
       </c>
       <c r="O351" t="n">
-        <v>0.3594544529914856</v>
+        <v>0.354951411485672</v>
       </c>
       <c r="P351" t="n">
-        <v>0.4124374985694885</v>
+        <v>0.4376508295536041</v>
       </c>
       <c r="Q351" t="n">
-        <v>0.2281080931425095</v>
+        <v>0.2073977738618851</v>
       </c>
       <c r="R351" t="n">
         <v>1</v>
       </c>
       <c r="S351" t="n">
-        <v>0.13401070729223</v>
+        <v>0.1579898126044516</v>
       </c>
       <c r="T351" t="n">
         <v>0</v>
       </c>
       <c r="U351" t="n">
-        <v>0.13401070729223</v>
+        <v>0.1579898126044516</v>
       </c>
       <c r="V351" t="n">
-        <v>0.4124374985694885</v>
+        <v>0.4376508295536041</v>
       </c>
       <c r="W351" t="n">
         <v>3.4</v>
@@ -35596,7 +35558,7 @@
       </c>
       <c r="Y351" t="inlineStr"/>
       <c r="Z351" t="n">
-        <v>5.08905600453333</v>
+        <v>5.400162666473724</v>
       </c>
       <c r="AA351" t="inlineStr">
         <is>
@@ -35608,9 +35570,7 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="AC351" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC351" t="inlineStr"/>
       <c r="AD351" t="inlineStr"/>
       <c r="AE351" t="inlineStr"/>
     </row>
@@ -35664,38 +35624,40 @@
         <v>0</v>
       </c>
       <c r="O352" t="n">
-        <v>0.3344002962112427</v>
+        <v>0.3346467614173889</v>
       </c>
       <c r="P352" t="n">
-        <v>0.3353081941604614</v>
+        <v>0.3450775742530823</v>
       </c>
       <c r="Q352" t="n">
-        <v>0.3302915394306183</v>
-      </c>
-      <c r="R352" t="inlineStr"/>
+        <v>0.3202756941318512</v>
+      </c>
+      <c r="R352" t="n">
+        <v>1</v>
+      </c>
       <c r="S352" t="n">
-        <v>0.07609240719644422</v>
+        <v>0.08586178728906507</v>
       </c>
       <c r="T352" t="n">
         <v>0</v>
       </c>
       <c r="U352" t="n">
-        <v>0.07609240719644422</v>
+        <v>0.08586178728906507</v>
       </c>
       <c r="V352" t="n">
-        <v>0.3353081941604614</v>
+        <v>0.3450775742530823</v>
       </c>
       <c r="W352" t="n">
         <v>3.6</v>
       </c>
       <c r="X352" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y352" t="inlineStr"/>
       <c r="Z352" t="n">
-        <v>4.712983501565553</v>
+        <v>7.68083370541765</v>
       </c>
       <c r="AA352" t="inlineStr">
         <is>
@@ -35707,11 +35669,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC352" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD352" t="inlineStr"/>
-      <c r="AE352" t="inlineStr"/>
+      <c r="AC352" t="inlineStr"/>
+      <c r="AD352" t="n">
+        <v>9.318433358119083</v>
+      </c>
+      <c r="AE352" t="n">
+        <v>0.1863686671623817</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
@@ -35739,62 +35703,64 @@
         <v>551</v>
       </c>
       <c r="G353" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H353" t="n">
         <v>3.1</v>
       </c>
       <c r="I353" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="J353" t="n">
-        <v>0.3132604660754795</v>
+        <v>0.323051271363068</v>
       </c>
       <c r="K353" t="n">
-        <v>0.303155289750464</v>
+        <v>0.3022092538557732</v>
       </c>
       <c r="L353" t="n">
-        <v>0.3835842441740565</v>
+        <v>0.3747394747811589</v>
       </c>
       <c r="M353" t="n">
-        <v>0.06407724380074598</v>
+        <v>0.06740823136818674</v>
       </c>
       <c r="N353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O353" t="n">
-        <v>0.368676096200943</v>
+        <v>0.2640608847141266</v>
       </c>
       <c r="P353" t="n">
-        <v>0.3269496262073517</v>
+        <v>0.3405673503875732</v>
       </c>
       <c r="Q353" t="n">
-        <v>0.3043742775917053</v>
-      </c>
-      <c r="R353" t="inlineStr"/>
+        <v>0.3953717947006226</v>
+      </c>
+      <c r="R353" t="n">
+        <v>1</v>
+      </c>
       <c r="S353" t="n">
-        <v>0.05541563012546347</v>
+        <v>0.02063231991946368</v>
       </c>
       <c r="T353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U353" t="n">
-        <v>0.05541563012546347</v>
+        <v>0.02063231991946368</v>
       </c>
       <c r="V353" t="n">
-        <v>0.368676096200943</v>
+        <v>0.3953717947006226</v>
       </c>
       <c r="W353" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="X353" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y353" t="inlineStr"/>
       <c r="Z353" t="n">
-        <v>5.181991937796573</v>
+        <v>6.973628856481748</v>
       </c>
       <c r="AA353" t="inlineStr">
         <is>
@@ -35806,11 +35772,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC353" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD353" t="inlineStr"/>
-      <c r="AE353" t="inlineStr"/>
+      <c r="AC353" t="inlineStr"/>
+      <c r="AD353" t="n">
+        <v>-0.7713675498962402</v>
+      </c>
+      <c r="AE353" t="n">
+        <v>-0.0154273509979248</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
@@ -35862,40 +35830,40 @@
         <v>2</v>
       </c>
       <c r="O354" t="n">
-        <v>0.2557234466075897</v>
+        <v>0.1881287693977356</v>
       </c>
       <c r="P354" t="n">
-        <v>0.3476332426071167</v>
+        <v>0.3416143357753754</v>
       </c>
       <c r="Q354" t="n">
-        <v>0.396643340587616</v>
+        <v>0.470256894826889</v>
       </c>
       <c r="R354" t="n">
         <v>1</v>
       </c>
       <c r="S354" t="n">
-        <v>-0.1701824350687087</v>
+        <v>-0.0965688808294356</v>
       </c>
       <c r="T354" t="n">
         <v>2</v>
       </c>
       <c r="U354" t="n">
-        <v>-0.1701824350687087</v>
+        <v>-0.0965688808294356</v>
       </c>
       <c r="V354" t="n">
-        <v>0.396643340587616</v>
+        <v>0.470256894826889</v>
       </c>
       <c r="W354" t="n">
         <v>1.65</v>
       </c>
       <c r="X354" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y354" t="inlineStr"/>
       <c r="Z354" t="n">
-        <v>4.379075851409317</v>
+        <v>4.696733791177587</v>
       </c>
       <c r="AA354" t="inlineStr">
         <is>
@@ -35907,11 +35875,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC354" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD354" t="inlineStr"/>
-      <c r="AE354" t="inlineStr"/>
+      <c r="AC354" t="inlineStr"/>
+      <c r="AD354" t="n">
+        <v>-34.47324977471279</v>
+      </c>
+      <c r="AE354" t="n">
+        <v>-0.6894649954942558</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
@@ -35945,58 +35915,58 @@
         <v>5.5</v>
       </c>
       <c r="I355" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J355" t="n">
-        <v>0.725753243897075</v>
+        <v>0.7297486033519555</v>
       </c>
       <c r="K355" t="n">
-        <v>0.1702221244776776</v>
+        <v>0.171159217877095</v>
       </c>
       <c r="L355" t="n">
-        <v>0.1040246316252474</v>
+        <v>0.09909217877094974</v>
       </c>
       <c r="M355" t="n">
-        <v>0.06812309137890527</v>
+        <v>0.06227513816253083</v>
       </c>
       <c r="N355" t="n">
         <v>1</v>
       </c>
       <c r="O355" t="n">
-        <v>0.4910662770271301</v>
+        <v>0.8723052144050598</v>
       </c>
       <c r="P355" t="n">
-        <v>0.3343507051467896</v>
+        <v>0.08643115311861038</v>
       </c>
       <c r="Q355" t="n">
-        <v>0.1745830029249191</v>
+        <v>0.04126355051994324</v>
       </c>
       <c r="R355" t="n">
         <v>1</v>
       </c>
       <c r="S355" t="n">
-        <v>-0.2346869668699448</v>
+        <v>0.1425566110531044</v>
       </c>
       <c r="T355" t="n">
         <v>1</v>
       </c>
       <c r="U355" t="n">
-        <v>-0.2346869668699448</v>
+        <v>0.1425566110531044</v>
       </c>
       <c r="V355" t="n">
-        <v>0.4910662770271301</v>
+        <v>0.8723052144050598</v>
       </c>
       <c r="W355" t="n">
         <v>1.29</v>
       </c>
       <c r="X355" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y355" t="inlineStr"/>
       <c r="Z355" t="n">
-        <v>5.252926683670414</v>
+        <v>9.887980995955333</v>
       </c>
       <c r="AA355" t="inlineStr">
         <is>
@@ -36008,11 +35978,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC355" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD355" t="inlineStr"/>
-      <c r="AE355" t="inlineStr"/>
+      <c r="AC355" t="inlineStr"/>
+      <c r="AD355" t="n">
+        <v>43.19783675259558</v>
+      </c>
+      <c r="AE355" t="n">
+        <v>0.8639567350519115</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
@@ -36040,62 +36012,64 @@
         <v>551</v>
       </c>
       <c r="G356" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H356" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I356" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="J356" t="n">
-        <v>0.2440775305096913</v>
+        <v>0.2384279475982533</v>
       </c>
       <c r="K356" t="n">
-        <v>0.2799712849964106</v>
+        <v>0.2724890829694323</v>
       </c>
       <c r="L356" t="n">
-        <v>0.4759511844938981</v>
+        <v>0.4890829694323144</v>
       </c>
       <c r="M356" t="n">
-        <v>0.05052790346907998</v>
+        <v>0.04853479853479858</v>
       </c>
       <c r="N356" t="n">
         <v>2</v>
       </c>
       <c r="O356" t="n">
-        <v>0.2576711177825928</v>
+        <v>0.1843647658824921</v>
       </c>
       <c r="P356" t="n">
-        <v>0.2776345908641815</v>
+        <v>0.315530925989151</v>
       </c>
       <c r="Q356" t="n">
-        <v>0.4646942615509033</v>
-      </c>
-      <c r="R356" t="inlineStr"/>
+        <v>0.5001042485237122</v>
+      </c>
+      <c r="R356" t="n">
+        <v>1</v>
+      </c>
       <c r="S356" t="n">
-        <v>-0.01125692294299474</v>
+        <v>0.01102127909139772</v>
       </c>
       <c r="T356" t="n">
         <v>2</v>
       </c>
       <c r="U356" t="n">
-        <v>-0.01125692294299474</v>
+        <v>0.01102127909139772</v>
       </c>
       <c r="V356" t="n">
-        <v>0.4646942615509033</v>
+        <v>0.5001042485237122</v>
       </c>
       <c r="W356" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="X356" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y356" t="inlineStr"/>
       <c r="Z356" t="n">
-        <v>6.531592207118942</v>
+        <v>6.844440624874321</v>
       </c>
       <c r="AA356" t="inlineStr">
         <is>
@@ -36110,8 +36084,12 @@
       <c r="AC356" t="n">
         <v>1</v>
       </c>
-      <c r="AD356" t="inlineStr"/>
-      <c r="AE356" t="inlineStr"/>
+      <c r="AD356" t="n">
+        <v>-2.610180566185405</v>
+      </c>
+      <c r="AE356" t="n">
+        <v>-0.0522036113237081</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
@@ -36160,43 +36138,43 @@
         <v>0.06650264668605077</v>
       </c>
       <c r="N357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O357" t="n">
-        <v>0.4987886846065521</v>
+        <v>0.2249245345592499</v>
       </c>
       <c r="P357" t="n">
-        <v>0.3277627229690552</v>
+        <v>0.3867079615592957</v>
       </c>
       <c r="Q357" t="n">
-        <v>0.1734485775232315</v>
+        <v>0.3883674442768097</v>
       </c>
       <c r="R357" t="n">
         <v>1</v>
       </c>
       <c r="S357" t="n">
-        <v>0.1310850844667408</v>
+        <v>0.03184874452147934</v>
       </c>
       <c r="T357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U357" t="n">
-        <v>0.1310850844667408</v>
+        <v>0.03184874452147934</v>
       </c>
       <c r="V357" t="n">
-        <v>0.4987886846065521</v>
+        <v>0.3883674442768097</v>
       </c>
       <c r="W357" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="X357" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y357" t="inlineStr"/>
       <c r="Z357" t="n">
-        <v>7.010812387702339</v>
+        <v>7.120127764607157</v>
       </c>
       <c r="AA357" t="inlineStr">
         <is>
@@ -36208,11 +36186,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC357" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD357" t="inlineStr"/>
-      <c r="AE357" t="inlineStr"/>
+      <c r="AC357" t="inlineStr"/>
+      <c r="AD357" t="n">
+        <v>1.313274751411625</v>
+      </c>
+      <c r="AE357" t="n">
+        <v>0.0262654950282325</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
@@ -36261,41 +36241,43 @@
         <v>0.06061256005490723</v>
       </c>
       <c r="N358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O358" t="n">
-        <v>0.4733425676822662</v>
+        <v>0.2409812957048416</v>
       </c>
       <c r="P358" t="n">
-        <v>0.3165914714336395</v>
+        <v>0.3268633782863617</v>
       </c>
       <c r="Q358" t="n">
-        <v>0.2100659310817719</v>
-      </c>
-      <c r="R358" t="inlineStr"/>
+        <v>0.4321553409099579</v>
+      </c>
+      <c r="R358" t="n">
+        <v>1</v>
+      </c>
       <c r="S358" t="n">
-        <v>0.1787015161150265</v>
+        <v>0.03094199409499321</v>
       </c>
       <c r="T358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U358" t="n">
-        <v>0.1787015161150265</v>
+        <v>0.03094199409499321</v>
       </c>
       <c r="V358" t="n">
-        <v>0.4733425676822662</v>
+        <v>0.4321553409099579</v>
       </c>
       <c r="W358" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="X358" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y358" t="inlineStr"/>
       <c r="Z358" t="n">
-        <v>6.653150000287863</v>
+        <v>7.108863293003022</v>
       </c>
       <c r="AA358" t="inlineStr">
         <is>
@@ -36307,11 +36289,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC358" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD358" t="inlineStr"/>
-      <c r="AE358" t="inlineStr"/>
+      <c r="AC358" t="inlineStr"/>
+      <c r="AD358" t="n">
+        <v>1.152966750992673</v>
+      </c>
+      <c r="AE358" t="n">
+        <v>0.02305933501985347</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
@@ -36339,64 +36323,64 @@
         <v>551</v>
       </c>
       <c r="G359" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H359" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I359" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="J359" t="n">
-        <v>0.6104945747546898</v>
+        <v>0.6019261637239165</v>
       </c>
       <c r="K359" t="n">
-        <v>0.245804394572283</v>
+        <v>0.2487961476725522</v>
       </c>
       <c r="L359" t="n">
-        <v>0.143701030673027</v>
+        <v>0.1492776886035313</v>
       </c>
       <c r="M359" t="n">
-        <v>0.07059881982482619</v>
+        <v>0.07182795698924727</v>
       </c>
       <c r="N359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O359" t="n">
-        <v>0.239532545208931</v>
+        <v>0.4390694499015808</v>
       </c>
       <c r="P359" t="n">
-        <v>0.3506380021572113</v>
+        <v>0.3360454440116882</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.4098294973373413</v>
+        <v>0.2248851656913757</v>
       </c>
       <c r="R359" t="n">
         <v>1</v>
       </c>
       <c r="S359" t="n">
-        <v>0.2661284666643143</v>
+        <v>-0.1628567138223357</v>
       </c>
       <c r="T359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U359" t="n">
-        <v>0.2661284666643143</v>
+        <v>-0.1628567138223357</v>
       </c>
       <c r="V359" t="n">
-        <v>0.4098294973373413</v>
+        <v>0.4390694499015808</v>
       </c>
       <c r="W359" t="n">
-        <v>6.5</v>
+        <v>1.55</v>
       </c>
       <c r="X359" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y359" t="inlineStr"/>
       <c r="Z359" t="n">
-        <v>5.760430830632986</v>
+        <v>3.350523642920814</v>
       </c>
       <c r="AA359" t="inlineStr">
         <is>
@@ -36411,8 +36395,12 @@
       <c r="AC359" t="n">
         <v>1</v>
       </c>
-      <c r="AD359" t="inlineStr"/>
-      <c r="AE359" t="inlineStr"/>
+      <c r="AD359" t="n">
+        <v>-58.08042775500903</v>
+      </c>
+      <c r="AE359" t="n">
+        <v>-1.161608555100181</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
@@ -36464,38 +36452,40 @@
         <v>2</v>
       </c>
       <c r="O360" t="n">
-        <v>0.3060559630393982</v>
+        <v>0.2203381955623627</v>
       </c>
       <c r="P360" t="n">
-        <v>0.3130795061588287</v>
+        <v>0.2964183688163757</v>
       </c>
       <c r="Q360" t="n">
-        <v>0.3808645606040955</v>
-      </c>
-      <c r="R360" t="inlineStr"/>
+        <v>0.4832434952259064</v>
+      </c>
+      <c r="R360" t="n">
+        <v>1</v>
+      </c>
       <c r="S360" t="n">
-        <v>-0.1649756141151846</v>
+        <v>-0.06259667949337366</v>
       </c>
       <c r="T360" t="n">
         <v>2</v>
       </c>
       <c r="U360" t="n">
-        <v>-0.1649756141151846</v>
+        <v>-0.06259667949337366</v>
       </c>
       <c r="V360" t="n">
-        <v>0.3808645606040955</v>
+        <v>0.4832434952259064</v>
       </c>
       <c r="W360" t="n">
         <v>1.73</v>
       </c>
       <c r="X360" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y360" t="inlineStr"/>
       <c r="Z360" t="n">
-        <v>4.193887119986108</v>
+        <v>5.475121074899095</v>
       </c>
       <c r="AA360" t="inlineStr">
         <is>
@@ -36507,11 +36497,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC360" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD360" t="inlineStr"/>
-      <c r="AE360" t="inlineStr"/>
+      <c r="AC360" t="inlineStr"/>
+      <c r="AD360" t="n">
+        <v>-22.46421277523041</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>-0.4492842555046082</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
@@ -36538,43 +36530,65 @@
       <c r="F361" t="n">
         <v>551</v>
       </c>
-      <c r="G361" t="inlineStr"/>
-      <c r="H361" t="inlineStr"/>
-      <c r="I361" t="inlineStr"/>
-      <c r="J361" t="inlineStr"/>
-      <c r="K361" t="inlineStr"/>
-      <c r="L361" t="inlineStr"/>
-      <c r="M361" t="inlineStr"/>
+      <c r="G361" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H361" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I361" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J361" t="n">
+        <v>0.5847731156255933</v>
+      </c>
+      <c r="K361" t="n">
+        <v>0.2460603759255743</v>
+      </c>
+      <c r="L361" t="n">
+        <v>0.1691665084488324</v>
+      </c>
+      <c r="M361" t="n">
+        <v>0.05559563892897224</v>
+      </c>
       <c r="N361" t="n">
         <v>1</v>
       </c>
       <c r="O361" t="n">
-        <v>0.3864976167678833</v>
+        <v>0.6890357732772827</v>
       </c>
       <c r="P361" t="n">
-        <v>0.380326896905899</v>
+        <v>0.2420719861984253</v>
       </c>
       <c r="Q361" t="n">
-        <v>0.2331754714250565</v>
-      </c>
-      <c r="R361" t="inlineStr"/>
-      <c r="S361" t="inlineStr"/>
+        <v>0.0688922256231308</v>
+      </c>
+      <c r="R361" t="n">
+        <v>1</v>
+      </c>
+      <c r="S361" t="n">
+        <v>0.1042626576516894</v>
+      </c>
       <c r="T361" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U361" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U361" t="n">
+        <v>0.1042626576516894</v>
+      </c>
       <c r="V361" t="n">
-        <v>0.6135023832321167</v>
-      </c>
-      <c r="W361" t="inlineStr"/>
+        <v>0.6890357732772827</v>
+      </c>
+      <c r="W361" t="n">
+        <v>1.62</v>
+      </c>
       <c r="X361" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y361" t="inlineStr"/>
       <c r="Z361" t="n">
-        <v>8.623191024554632</v>
+        <v>8.330198126753396</v>
       </c>
       <c r="AA361" t="inlineStr">
         <is>
@@ -36586,11 +36600,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC361" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD361" t="inlineStr"/>
-      <c r="AE361" t="inlineStr"/>
+      <c r="AC361" t="inlineStr"/>
+      <c r="AD361" t="n">
+        <v>18.74805688858033</v>
+      </c>
+      <c r="AE361" t="n">
+        <v>0.3749611377716067</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
@@ -36617,45 +36633,65 @@
       <c r="F362" t="n">
         <v>551</v>
       </c>
-      <c r="G362" t="inlineStr"/>
-      <c r="H362" t="inlineStr"/>
-      <c r="I362" t="inlineStr"/>
-      <c r="J362" t="inlineStr"/>
-      <c r="K362" t="inlineStr"/>
-      <c r="L362" t="inlineStr"/>
-      <c r="M362" t="inlineStr"/>
+      <c r="G362" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H362" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I362" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J362" t="n">
+        <v>0.4109950200175764</v>
+      </c>
+      <c r="K362" t="n">
+        <v>0.2763792598379064</v>
+      </c>
+      <c r="L362" t="n">
+        <v>0.3126257201445171</v>
+      </c>
+      <c r="M362" t="n">
+        <v>0.04875840768140538</v>
+      </c>
       <c r="N362" t="n">
         <v>2</v>
       </c>
       <c r="O362" t="n">
-        <v>0.326279878616333</v>
+        <v>0.2380098849534988</v>
       </c>
       <c r="P362" t="n">
-        <v>0.3250846564769745</v>
+        <v>0.3764864206314087</v>
       </c>
       <c r="Q362" t="n">
-        <v>0.3486354947090149</v>
+        <v>0.3855035901069641</v>
       </c>
       <c r="R362" t="n">
         <v>1</v>
       </c>
-      <c r="S362" t="inlineStr"/>
+      <c r="S362" t="n">
+        <v>0.072877869962447</v>
+      </c>
       <c r="T362" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U362" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U362" t="n">
+        <v>0.072877869962447</v>
+      </c>
       <c r="V362" t="n">
-        <v>0.6513645052909851</v>
-      </c>
-      <c r="W362" t="inlineStr"/>
+        <v>0.3855035901069641</v>
+      </c>
+      <c r="W362" t="n">
+        <v>3.05</v>
+      </c>
       <c r="X362" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y362" t="inlineStr"/>
       <c r="Z362" t="n">
-        <v>9.155368763438981</v>
+        <v>7.628997354429545</v>
       </c>
       <c r="AA362" t="inlineStr">
         <is>
@@ -36667,11 +36703,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC362" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD362" t="inlineStr"/>
-      <c r="AE362" t="inlineStr"/>
+      <c r="AC362" t="inlineStr"/>
+      <c r="AD362" t="n">
+        <v>8.574924381767829</v>
+      </c>
+      <c r="AE362" t="n">
+        <v>0.1714984876353566</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
@@ -36698,45 +36736,65 @@
       <c r="F363" t="n">
         <v>551</v>
       </c>
-      <c r="G363" t="inlineStr"/>
-      <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr"/>
-      <c r="J363" t="inlineStr"/>
-      <c r="K363" t="inlineStr"/>
-      <c r="L363" t="inlineStr"/>
-      <c r="M363" t="inlineStr"/>
+      <c r="G363" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H363" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I363" t="n">
+        <v>3</v>
+      </c>
+      <c r="J363" t="n">
+        <v>0.4057630108791532</v>
+      </c>
+      <c r="K363" t="n">
+        <v>0.2763892972655101</v>
+      </c>
+      <c r="L363" t="n">
+        <v>0.3178476918553366</v>
+      </c>
+      <c r="M363" t="n">
+        <v>0.04872032069071852</v>
+      </c>
       <c r="N363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O363" t="n">
-        <v>0.2713271677494049</v>
+        <v>0.3797436356544495</v>
       </c>
       <c r="P363" t="n">
-        <v>0.2626653611660004</v>
+        <v>0.3001792132854462</v>
       </c>
       <c r="Q363" t="n">
-        <v>0.4660075008869171</v>
+        <v>0.3200770914554596</v>
       </c>
       <c r="R363" t="n">
         <v>1</v>
       </c>
-      <c r="S363" t="inlineStr"/>
+      <c r="S363" t="n">
+        <v>-0.02601937522470371</v>
+      </c>
       <c r="T363" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U363" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U363" t="n">
+        <v>-0.02601937522470371</v>
+      </c>
       <c r="V363" t="n">
-        <v>0.5339924991130829</v>
-      </c>
-      <c r="W363" t="inlineStr"/>
+        <v>0.3797436356544495</v>
+      </c>
+      <c r="W363" t="n">
+        <v>2.35</v>
+      </c>
       <c r="X363" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y363" t="inlineStr"/>
       <c r="Z363" t="n">
-        <v>7.505625815620105</v>
+        <v>6.468863935991153</v>
       </c>
       <c r="AA363" t="inlineStr">
         <is>
@@ -36748,11 +36806,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC363" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD363" t="inlineStr"/>
-      <c r="AE363" t="inlineStr"/>
+      <c r="AC363" t="inlineStr"/>
+      <c r="AD363" t="n">
+        <v>-7.970552312003237</v>
+      </c>
+      <c r="AE363" t="n">
+        <v>-0.1594110462400647</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
@@ -36779,43 +36839,65 @@
       <c r="F364" t="n">
         <v>551</v>
       </c>
-      <c r="G364" t="inlineStr"/>
-      <c r="H364" t="inlineStr"/>
-      <c r="I364" t="inlineStr"/>
-      <c r="J364" t="inlineStr"/>
-      <c r="K364" t="inlineStr"/>
-      <c r="L364" t="inlineStr"/>
-      <c r="M364" t="inlineStr"/>
+      <c r="G364" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H364" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I364" t="n">
+        <v>3</v>
+      </c>
+      <c r="J364" t="n">
+        <v>0.3993959384811032</v>
+      </c>
+      <c r="K364" t="n">
+        <v>0.2837499503238882</v>
+      </c>
+      <c r="L364" t="n">
+        <v>0.3168541111950086</v>
+      </c>
+      <c r="M364" t="n">
+        <v>0.05200886324679121</v>
+      </c>
       <c r="N364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O364" t="n">
-        <v>0.2850092947483063</v>
+        <v>0.3628287613391876</v>
       </c>
       <c r="P364" t="n">
-        <v>0.313154011964798</v>
+        <v>0.2963537275791168</v>
       </c>
       <c r="Q364" t="n">
-        <v>0.4018366634845734</v>
-      </c>
-      <c r="R364" t="inlineStr"/>
-      <c r="S364" t="inlineStr"/>
+        <v>0.3408175408840179</v>
+      </c>
+      <c r="R364" t="n">
+        <v>1</v>
+      </c>
+      <c r="S364" t="n">
+        <v>-0.0365671771419156</v>
+      </c>
       <c r="T364" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U364" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U364" t="n">
+        <v>-0.0365671771419156</v>
+      </c>
       <c r="V364" t="n">
-        <v>0.5981633365154266</v>
-      </c>
-      <c r="W364" t="inlineStr"/>
+        <v>0.3628287613391876</v>
+      </c>
+      <c r="W364" t="n">
+        <v>2.38</v>
+      </c>
       <c r="X364" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y364" t="inlineStr"/>
       <c r="Z364" t="n">
-        <v>8.407590346239841</v>
+        <v>6.335115248596375</v>
       </c>
       <c r="AA364" t="inlineStr">
         <is>
@@ -36827,11 +36909,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC364" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD364" t="inlineStr"/>
-      <c r="AE364" t="inlineStr"/>
+      <c r="AC364" t="inlineStr"/>
+      <c r="AD364" t="n">
+        <v>-9.888952754545905</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>-0.1977790550909181</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
@@ -36858,45 +36942,65 @@
       <c r="F365" t="n">
         <v>551</v>
       </c>
-      <c r="G365" t="inlineStr"/>
-      <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
-      <c r="J365" t="inlineStr"/>
-      <c r="K365" t="inlineStr"/>
-      <c r="L365" t="inlineStr"/>
-      <c r="M365" t="inlineStr"/>
+      <c r="G365" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H365" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="I365" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J365" t="n">
+        <v>0.5937667920472864</v>
+      </c>
+      <c r="K365" t="n">
+        <v>0.2235357334766254</v>
+      </c>
+      <c r="L365" t="n">
+        <v>0.1826974744760881</v>
+      </c>
+      <c r="M365" t="n">
+        <v>0.05260180995475117</v>
+      </c>
       <c r="N365" t="n">
         <v>1</v>
       </c>
       <c r="O365" t="n">
-        <v>0.3621496558189392</v>
+        <v>0.6867887377738953</v>
       </c>
       <c r="P365" t="n">
-        <v>0.3006593585014343</v>
+        <v>0.2254644185304642</v>
       </c>
       <c r="Q365" t="n">
-        <v>0.3371908068656921</v>
+        <v>0.0877467542886734</v>
       </c>
       <c r="R365" t="n">
         <v>1</v>
       </c>
-      <c r="S365" t="inlineStr"/>
+      <c r="S365" t="n">
+        <v>0.09302194572660882</v>
+      </c>
       <c r="T365" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U365" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U365" t="n">
+        <v>0.09302194572660882</v>
+      </c>
       <c r="V365" t="n">
-        <v>0.6378503441810608</v>
-      </c>
-      <c r="W365" t="inlineStr"/>
+        <v>0.6867887377738953</v>
+      </c>
+      <c r="W365" t="n">
+        <v>1.6</v>
+      </c>
       <c r="X365" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y365" t="inlineStr"/>
       <c r="Z365" t="n">
-        <v>8.965418086844144</v>
+        <v>8.175448130953953</v>
       </c>
       <c r="AA365" t="inlineStr">
         <is>
@@ -36911,8 +37015,12 @@
       <c r="AC365" t="n">
         <v>1</v>
       </c>
-      <c r="AD365" t="inlineStr"/>
-      <c r="AE365" t="inlineStr"/>
+      <c r="AD365" t="n">
+        <v>16.47699673970541</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>0.3295399347941081</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
@@ -36939,43 +37047,65 @@
       <c r="F366" t="n">
         <v>551</v>
       </c>
-      <c r="G366" t="inlineStr"/>
-      <c r="H366" t="inlineStr"/>
-      <c r="I366" t="inlineStr"/>
-      <c r="J366" t="inlineStr"/>
-      <c r="K366" t="inlineStr"/>
-      <c r="L366" t="inlineStr"/>
-      <c r="M366" t="inlineStr"/>
+      <c r="G366" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H366" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I366" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J366" t="n">
+        <v>0.3056782334384858</v>
+      </c>
+      <c r="K366" t="n">
+        <v>0.2787066246056782</v>
+      </c>
+      <c r="L366" t="n">
+        <v>0.415615141955836</v>
+      </c>
+      <c r="M366" t="n">
+        <v>0.05529478344818406</v>
+      </c>
       <c r="N366" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O366" t="n">
-        <v>0.2453643530607224</v>
+        <v>0.3393153846263885</v>
       </c>
       <c r="P366" t="n">
-        <v>0.3385154902935028</v>
+        <v>0.3494101762771606</v>
       </c>
       <c r="Q366" t="n">
-        <v>0.416120171546936</v>
-      </c>
-      <c r="R366" t="inlineStr"/>
-      <c r="S366" t="inlineStr"/>
+        <v>0.311274379491806</v>
+      </c>
+      <c r="R366" t="n">
+        <v>1</v>
+      </c>
+      <c r="S366" t="n">
+        <v>0.0707035516714824</v>
+      </c>
       <c r="T366" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U366" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U366" t="n">
+        <v>0.0707035516714824</v>
+      </c>
       <c r="V366" t="n">
-        <v>0.583879828453064</v>
-      </c>
-      <c r="W366" t="inlineStr"/>
+        <v>0.3494101762771606</v>
+      </c>
+      <c r="W366" t="n">
+        <v>3.4</v>
+      </c>
       <c r="X366" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y366" t="inlineStr"/>
       <c r="Z366" t="n">
-        <v>8.206825977772963</v>
+        <v>7.577213274792085</v>
       </c>
       <c r="AA366" t="inlineStr">
         <is>
@@ -36990,8 +37120,12 @@
       <c r="AC366" t="n">
         <v>1</v>
       </c>
-      <c r="AD366" t="inlineStr"/>
-      <c r="AE366" t="inlineStr"/>
+      <c r="AD366" t="n">
+        <v>7.833108305931091</v>
+      </c>
+      <c r="AE366" t="n">
+        <v>0.1566621661186218</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
@@ -37018,43 +37152,65 @@
       <c r="F367" t="n">
         <v>551</v>
       </c>
-      <c r="G367" t="inlineStr"/>
-      <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr"/>
-      <c r="J367" t="inlineStr"/>
-      <c r="K367" t="inlineStr"/>
-      <c r="L367" t="inlineStr"/>
-      <c r="M367" t="inlineStr"/>
+      <c r="G367" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H367" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I367" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J367" t="n">
+        <v>0.3227705287942705</v>
+      </c>
+      <c r="K367" t="n">
+        <v>0.272049445698028</v>
+      </c>
+      <c r="L367" t="n">
+        <v>0.4051800255077014</v>
+      </c>
+      <c r="M367" t="n">
+        <v>0.05022925145536039</v>
+      </c>
       <c r="N367" t="n">
         <v>2</v>
       </c>
       <c r="O367" t="n">
-        <v>0.2858667969703674</v>
+        <v>0.3121911287307739</v>
       </c>
       <c r="P367" t="n">
-        <v>0.3045541644096375</v>
+        <v>0.3159999251365662</v>
       </c>
       <c r="Q367" t="n">
-        <v>0.4095790386199951</v>
-      </c>
-      <c r="R367" t="inlineStr"/>
-      <c r="S367" t="inlineStr"/>
+        <v>0.3718088865280151</v>
+      </c>
+      <c r="R367" t="n">
+        <v>1</v>
+      </c>
+      <c r="S367" t="n">
+        <v>-0.03337113897968624</v>
+      </c>
       <c r="T367" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U367" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U367" t="n">
+        <v>-0.03337113897968624</v>
+      </c>
       <c r="V367" t="n">
-        <v>0.5904209613800049</v>
-      </c>
-      <c r="W367" t="inlineStr"/>
+        <v>0.3718088865280151</v>
+      </c>
+      <c r="W367" t="n">
+        <v>2.35</v>
+      </c>
       <c r="X367" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y367" t="inlineStr"/>
       <c r="Z367" t="n">
-        <v>8.298766026072132</v>
+        <v>6.372519093944861</v>
       </c>
       <c r="AA367" t="inlineStr">
         <is>
@@ -37066,11 +37222,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC367" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD367" t="inlineStr"/>
-      <c r="AE367" t="inlineStr"/>
+      <c r="AC367" t="inlineStr"/>
+      <c r="AD367" t="n">
+        <v>-9.35178641919736</v>
+      </c>
+      <c r="AE367" t="n">
+        <v>-0.1870357283839472</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
@@ -37097,45 +37255,65 @@
       <c r="F368" t="n">
         <v>551</v>
       </c>
-      <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
-      <c r="I368" t="inlineStr"/>
-      <c r="J368" t="inlineStr"/>
-      <c r="K368" t="inlineStr"/>
-      <c r="L368" t="inlineStr"/>
-      <c r="M368" t="inlineStr"/>
+      <c r="G368" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H368" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I368" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J368" t="n">
+        <v>0.4801453178375839</v>
+      </c>
+      <c r="K368" t="n">
+        <v>0.2741699351130552</v>
+      </c>
+      <c r="L368" t="n">
+        <v>0.2456847470493611</v>
+      </c>
+      <c r="M368" t="n">
+        <v>0.05720954540199719</v>
+      </c>
       <c r="N368" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O368" t="n">
-        <v>0.2797775268554688</v>
+        <v>0.2764882743358612</v>
       </c>
       <c r="P368" t="n">
-        <v>0.3573216199874878</v>
+        <v>0.3680079281330109</v>
       </c>
       <c r="Q368" t="n">
-        <v>0.3629008233547211</v>
+        <v>0.3555037379264832</v>
       </c>
       <c r="R368" t="n">
         <v>1</v>
       </c>
-      <c r="S368" t="inlineStr"/>
+      <c r="S368" t="n">
+        <v>0.09383799301995571</v>
+      </c>
       <c r="T368" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U368" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U368" t="n">
+        <v>0.09383799301995571</v>
+      </c>
       <c r="V368" t="n">
-        <v>0.6370991766452789</v>
-      </c>
-      <c r="W368" t="inlineStr"/>
+        <v>0.3680079281330109</v>
+      </c>
+      <c r="W368" t="n">
+        <v>3.45</v>
+      </c>
       <c r="X368" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y368" t="inlineStr"/>
       <c r="Z368" t="n">
-        <v>8.954859918971405</v>
+        <v>7.79815837521222</v>
       </c>
       <c r="AA368" t="inlineStr">
         <is>
@@ -37147,11 +37325,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC368" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD368" t="inlineStr"/>
-      <c r="AE368" t="inlineStr"/>
+      <c r="AC368" t="inlineStr"/>
+      <c r="AD368" t="n">
+        <v>11.0051980432199</v>
+      </c>
+      <c r="AE368" t="n">
+        <v>0.220103960864398</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
@@ -37178,43 +37358,65 @@
       <c r="F369" t="n">
         <v>551</v>
       </c>
-      <c r="G369" t="inlineStr"/>
-      <c r="H369" t="inlineStr"/>
-      <c r="I369" t="inlineStr"/>
-      <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr"/>
-      <c r="L369" t="inlineStr"/>
-      <c r="M369" t="inlineStr"/>
+      <c r="G369" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H369" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I369" t="n">
+        <v>2</v>
+      </c>
+      <c r="J369" t="n">
+        <v>0.2752625860195582</v>
+      </c>
+      <c r="K369" t="n">
+        <v>0.2499094530967041</v>
+      </c>
+      <c r="L369" t="n">
+        <v>0.4748279608837379</v>
+      </c>
+      <c r="M369" t="n">
+        <v>0.05301296720061011</v>
+      </c>
       <c r="N369" t="n">
         <v>2</v>
       </c>
       <c r="O369" t="n">
-        <v>0.2457175552845001</v>
+        <v>0.1746932119131088</v>
       </c>
       <c r="P369" t="n">
-        <v>0.2875540256500244</v>
+        <v>0.2149975001811981</v>
       </c>
       <c r="Q369" t="n">
-        <v>0.4667284488677979</v>
-      </c>
-      <c r="R369" t="inlineStr"/>
-      <c r="S369" t="inlineStr"/>
+        <v>0.6103093028068542</v>
+      </c>
+      <c r="R369" t="n">
+        <v>1</v>
+      </c>
+      <c r="S369" t="n">
+        <v>0.1354813419231164</v>
+      </c>
       <c r="T369" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U369" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U369" t="n">
+        <v>0.1354813419231164</v>
+      </c>
       <c r="V369" t="n">
-        <v>0.5332715511322021</v>
-      </c>
-      <c r="W369" t="inlineStr"/>
+        <v>0.6103093028068542</v>
+      </c>
+      <c r="W369" t="n">
+        <v>2</v>
+      </c>
       <c r="X369" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y369" t="inlineStr"/>
       <c r="Z369" t="n">
-        <v>7.495492404034726</v>
+        <v>8.553635253790617</v>
       </c>
       <c r="AA369" t="inlineStr">
         <is>
@@ -37226,11 +37428,13 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="AC369" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD369" t="inlineStr"/>
-      <c r="AE369" t="inlineStr"/>
+      <c r="AC369" t="inlineStr"/>
+      <c r="AD369" t="n">
+        <v>22.06186056137085</v>
+      </c>
+      <c r="AE369" t="n">
+        <v>0.441237211227417</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
@@ -37258,55 +37462,55 @@
         <v>591</v>
       </c>
       <c r="G370" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H370" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="I370" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="J370" t="n">
-        <v>0.7238489169478611</v>
+        <v>0.7197844495765973</v>
       </c>
       <c r="K370" t="n">
-        <v>0.177860019592903</v>
+        <v>0.170130869899923</v>
       </c>
       <c r="L370" t="n">
-        <v>0.09829106345923588</v>
+        <v>0.1100846805234796</v>
       </c>
       <c r="M370" t="n">
-        <v>0.07093314682053964</v>
+        <v>0.06869600987248048</v>
       </c>
       <c r="N370" t="n">
         <v>1</v>
       </c>
       <c r="O370" t="n">
-        <v>0.533005595670592</v>
+        <v>0.5334666201787054</v>
       </c>
       <c r="P370" t="n">
-        <v>0.3102523233424003</v>
+        <v>0.3101993965773246</v>
       </c>
       <c r="Q370" t="n">
-        <v>0.1567420809870077</v>
+        <v>0.15633398324397</v>
       </c>
       <c r="R370" t="n">
         <v>1</v>
       </c>
       <c r="S370" t="n">
-        <v>-0.1908433212772691</v>
+        <v>-0.1863178293978919</v>
       </c>
       <c r="T370" t="n">
         <v>1</v>
       </c>
       <c r="U370" t="n">
-        <v>-0.1908433212772691</v>
+        <v>-0.1863178293978919</v>
       </c>
       <c r="V370" t="n">
-        <v>0.533005595670592</v>
+        <v>0.5334666201787054</v>
       </c>
       <c r="W370" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X370" t="inlineStr">
         <is>
@@ -37315,7 +37519,7 @@
       </c>
       <c r="Y370" t="inlineStr"/>
       <c r="Z370" t="n">
-        <v>0.1882573947523236</v>
+        <v>0.2078875170719314</v>
       </c>
       <c r="AA370" t="inlineStr">
         <is>
@@ -37327,14 +37531,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC370" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC370" t="inlineStr"/>
       <c r="AD370" t="n">
-        <v>-107.731993649978</v>
+        <v>-102.1644645892276</v>
       </c>
       <c r="AE370" t="n">
-        <v>-2.15463987299956</v>
+        <v>-2.043289291784553</v>
       </c>
     </row>
     <row r="371">
@@ -37369,46 +37571,46 @@
         <v>3.5</v>
       </c>
       <c r="I371" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="J371" t="n">
-        <v>0.5140093406910212</v>
+        <v>0.5105762217359592</v>
       </c>
       <c r="K371" t="n">
-        <v>0.2687534552755911</v>
+        <v>0.2669584245076587</v>
       </c>
       <c r="L371" t="n">
-        <v>0.2172372040333877</v>
+        <v>0.2224653537563822</v>
       </c>
       <c r="M371" t="n">
-        <v>0.06310925536306966</v>
+        <v>0.07025761124121765</v>
       </c>
       <c r="N371" t="n">
         <v>1</v>
       </c>
       <c r="O371" t="n">
-        <v>0.3594975492852748</v>
+        <v>0.3589086568094497</v>
       </c>
       <c r="P371" t="n">
-        <v>0.3482094466124229</v>
+        <v>0.3481517232265687</v>
       </c>
       <c r="Q371" t="n">
-        <v>0.2922930041023024</v>
+        <v>0.2929396199639817</v>
       </c>
       <c r="R371" t="n">
         <v>1</v>
       </c>
       <c r="S371" t="n">
-        <v>-0.1545117914057464</v>
+        <v>-0.1516675649265095</v>
       </c>
       <c r="T371" t="n">
         <v>1</v>
       </c>
       <c r="U371" t="n">
-        <v>-0.1545117914057464</v>
+        <v>-0.1516675649265095</v>
       </c>
       <c r="V371" t="n">
-        <v>0.3594975492852748</v>
+        <v>0.3589086568094497</v>
       </c>
       <c r="W371" t="n">
         <v>1.83</v>
@@ -37420,7 +37622,7 @@
       </c>
       <c r="Y371" t="inlineStr"/>
       <c r="Z371" t="n">
-        <v>0.5523395234174531</v>
+        <v>0.55134294039892</v>
       </c>
       <c r="AA371" t="inlineStr">
         <is>
@@ -37432,14 +37634,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC371" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC371" t="inlineStr"/>
       <c r="AD371" t="n">
-        <v>-41.21921503710206</v>
+        <v>-41.34905518538639</v>
       </c>
       <c r="AE371" t="n">
-        <v>-0.8243843007420412</v>
+        <v>-0.8269811037077278</v>
       </c>
     </row>
     <row r="372">
@@ -37468,55 +37668,55 @@
         <v>591</v>
       </c>
       <c r="G372" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="H372" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="I372" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="J372" t="n">
-        <v>0.6690140845070423</v>
+        <v>0.6449948400412796</v>
       </c>
       <c r="K372" t="n">
-        <v>0.1971830985915493</v>
+        <v>0.2063983488132095</v>
       </c>
       <c r="L372" t="n">
-        <v>0.1338028169014084</v>
+        <v>0.1486068111455108</v>
       </c>
       <c r="M372" t="n">
-        <v>0.06766917293233088</v>
+        <v>0.07666666666666666</v>
       </c>
       <c r="N372" t="n">
         <v>1</v>
       </c>
       <c r="O372" t="n">
-        <v>0.489689331131483</v>
+        <v>0.4967959899678761</v>
       </c>
       <c r="P372" t="n">
-        <v>0.3271781694361988</v>
+        <v>0.3253100089473399</v>
       </c>
       <c r="Q372" t="n">
-        <v>0.1831324994323181</v>
+        <v>0.1778940010847841</v>
       </c>
       <c r="R372" t="n">
         <v>1</v>
       </c>
       <c r="S372" t="n">
-        <v>-0.1793247533755593</v>
+        <v>-0.1481988500734035</v>
       </c>
       <c r="T372" t="n">
         <v>1</v>
       </c>
       <c r="U372" t="n">
-        <v>-0.1793247533755593</v>
+        <v>-0.1481988500734035</v>
       </c>
       <c r="V372" t="n">
-        <v>0.489689331131483</v>
+        <v>0.4967959899678761</v>
       </c>
       <c r="W372" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X372" t="inlineStr">
         <is>
@@ -37525,7 +37725,7 @@
       </c>
       <c r="Y372" t="inlineStr"/>
       <c r="Z372" t="n">
-        <v>0.3114838652546875</v>
+        <v>0.3899783839213068</v>
       </c>
       <c r="AA372" t="inlineStr">
         <is>
@@ -37537,14 +37737,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC372" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC372" t="inlineStr"/>
       <c r="AD372" t="n">
-        <v>-78.60873410398099</v>
+        <v>-64.68494873778602</v>
       </c>
       <c r="AE372" t="n">
-        <v>-1.57217468207962</v>
+        <v>-1.29369897475572</v>
       </c>
     </row>
     <row r="373">
@@ -37597,28 +37795,28 @@
         <v>1</v>
       </c>
       <c r="O373" t="n">
-        <v>0.3864998697000389</v>
+        <v>0.3876746774015735</v>
       </c>
       <c r="P373" t="n">
-        <v>0.335577206624032</v>
+        <v>0.3355014801438096</v>
       </c>
       <c r="Q373" t="n">
-        <v>0.2779229236759292</v>
+        <v>0.2768238424546168</v>
       </c>
       <c r="R373" t="n">
         <v>1</v>
       </c>
       <c r="S373" t="n">
-        <v>-0.1692225694708834</v>
+        <v>-0.1680477617693488</v>
       </c>
       <c r="T373" t="n">
         <v>1</v>
       </c>
       <c r="U373" t="n">
-        <v>-0.1692225694708834</v>
+        <v>-0.1680477617693488</v>
       </c>
       <c r="V373" t="n">
-        <v>0.3864998697000389</v>
+        <v>0.3876746774015735</v>
       </c>
       <c r="W373" t="n">
         <v>1.7</v>
@@ -37630,7 +37828,7 @@
       </c>
       <c r="Y373" t="inlineStr"/>
       <c r="Z373" t="n">
-        <v>0.4945137693516743</v>
+        <v>0.4965680991946713</v>
       </c>
       <c r="AA373" t="inlineStr">
         <is>
@@ -37642,14 +37840,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC373" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC373" t="inlineStr"/>
       <c r="AD373" t="n">
-        <v>-48.99288878713343</v>
+        <v>-48.70757834533216</v>
       </c>
       <c r="AE373" t="n">
-        <v>-0.9798577757426686</v>
+        <v>-0.9741515669066432</v>
       </c>
     </row>
     <row r="374">
@@ -37678,55 +37874,55 @@
         <v>591</v>
       </c>
       <c r="G374" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H374" t="n">
         <v>4</v>
       </c>
       <c r="I374" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="J374" t="n">
-        <v>0.5682242990654205</v>
+        <v>0.5590930268675262</v>
       </c>
       <c r="K374" t="n">
-        <v>0.234392523364486</v>
+        <v>0.2334213387171921</v>
       </c>
       <c r="L374" t="n">
-        <v>0.1973831775700934</v>
+        <v>0.2074856344152819</v>
       </c>
       <c r="M374" t="n">
-        <v>0.06658692185007986</v>
+        <v>0.07102461743180299</v>
       </c>
       <c r="N374" t="n">
         <v>1</v>
       </c>
       <c r="O374" t="n">
-        <v>0.3824937066336742</v>
+        <v>0.3857783886646933</v>
       </c>
       <c r="P374" t="n">
-        <v>0.344658366537651</v>
+        <v>0.3445749432805242</v>
       </c>
       <c r="Q374" t="n">
-        <v>0.2728479268286748</v>
+        <v>0.2696466680547824</v>
       </c>
       <c r="R374" t="n">
         <v>1</v>
       </c>
       <c r="S374" t="n">
-        <v>-0.1857305924317463</v>
+        <v>-0.1733146382028328</v>
       </c>
       <c r="T374" t="n">
         <v>1</v>
       </c>
       <c r="U374" t="n">
-        <v>-0.1857305924317463</v>
+        <v>-0.1733146382028328</v>
       </c>
       <c r="V374" t="n">
-        <v>0.3824937066336742</v>
+        <v>0.3857783886646933</v>
       </c>
       <c r="W374" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X374" t="inlineStr">
         <is>
@@ -37735,7 +37931,7 @@
       </c>
       <c r="Y374" t="inlineStr"/>
       <c r="Z374" t="n">
-        <v>0.4407240064816078</v>
+        <v>0.4655568086901336</v>
       </c>
       <c r="AA374" t="inlineStr">
         <is>
@@ -37747,14 +37943,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC374" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC374" t="inlineStr"/>
       <c r="AD374" t="n">
-        <v>-56.75159754683656</v>
+        <v>-53.0970284970093</v>
       </c>
       <c r="AE374" t="n">
-        <v>-1.135031950936731</v>
+        <v>-1.061940569940186</v>
       </c>
     </row>
     <row r="375">
@@ -37783,55 +37977,55 @@
         <v>591</v>
       </c>
       <c r="G375" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H375" t="n">
         <v>3.7</v>
       </c>
       <c r="I375" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="J375" t="n">
-        <v>0.2237903225806452</v>
+        <v>0.2299619616899878</v>
       </c>
       <c r="K375" t="n">
-        <v>0.2540322580645161</v>
+        <v>0.2548227143051216</v>
       </c>
       <c r="L375" t="n">
-        <v>0.5221774193548387</v>
+        <v>0.5152153240048907</v>
       </c>
       <c r="M375" t="n">
-        <v>0.06392106392106389</v>
+        <v>0.06062079672635434</v>
       </c>
       <c r="N375" t="n">
         <v>2</v>
       </c>
       <c r="O375" t="n">
-        <v>0.1964973149715032</v>
+        <v>0.1969229322402854</v>
       </c>
       <c r="P375" t="n">
-        <v>0.3791722029115259</v>
+        <v>0.3791724152914838</v>
       </c>
       <c r="Q375" t="n">
-        <v>0.4243304821169709</v>
+        <v>0.4239046524682308</v>
       </c>
       <c r="R375" t="n">
         <v>1</v>
       </c>
       <c r="S375" t="n">
-        <v>-0.0978469372378678</v>
+        <v>-0.09131067153665989</v>
       </c>
       <c r="T375" t="n">
         <v>2</v>
       </c>
       <c r="U375" t="n">
-        <v>-0.0978469372378678</v>
+        <v>-0.09131067153665989</v>
       </c>
       <c r="V375" t="n">
-        <v>0.4243304821169709</v>
+        <v>0.4239046524682308</v>
       </c>
       <c r="W375" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X375" t="inlineStr">
         <is>
@@ -37840,7 +38034,7 @@
       </c>
       <c r="Y375" t="inlineStr"/>
       <c r="Z375" t="n">
-        <v>0.6459865863227952</v>
+        <v>0.6669756887033489</v>
       </c>
       <c r="AA375" t="inlineStr">
         <is>
@@ -37852,14 +38046,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC375" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC375" t="inlineStr"/>
       <c r="AD375" t="n">
-        <v>-29.52564152368154</v>
+        <v>-27.01861276905272</v>
       </c>
       <c r="AE375" t="n">
-        <v>-0.5905128304736308</v>
+        <v>-0.5403722553810545</v>
       </c>
     </row>
     <row r="376">
@@ -37912,28 +38104,28 @@
         <v>1</v>
       </c>
       <c r="O376" t="n">
-        <v>0.4901233034693709</v>
+        <v>0.4955682892105192</v>
       </c>
       <c r="P376" t="n">
-        <v>0.3136940934930733</v>
+        <v>0.3126776390602697</v>
       </c>
       <c r="Q376" t="n">
-        <v>0.1961826030375558</v>
+        <v>0.1917540717292111</v>
       </c>
       <c r="R376" t="n">
         <v>1</v>
       </c>
       <c r="S376" t="n">
-        <v>-0.2033579725361769</v>
+        <v>-0.1979129867950286</v>
       </c>
       <c r="T376" t="n">
         <v>1</v>
       </c>
       <c r="U376" t="n">
-        <v>-0.2033579725361769</v>
+        <v>-0.1979129867950286</v>
       </c>
       <c r="V376" t="n">
-        <v>0.4901233034693709</v>
+        <v>0.4955682892105192</v>
       </c>
       <c r="W376" t="n">
         <v>1.36</v>
@@ -37945,7 +38137,7 @@
       </c>
       <c r="Y376" t="inlineStr"/>
       <c r="Z376" t="n">
-        <v>0.2456825891514715</v>
+        <v>0.254551181255875</v>
       </c>
       <c r="AA376" t="inlineStr">
         <is>
@@ -37957,14 +38149,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC376" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC376" t="inlineStr"/>
       <c r="AD376" t="n">
-        <v>-92.62008535601542</v>
+        <v>-90.56309074269269</v>
       </c>
       <c r="AE376" t="n">
-        <v>-1.852401707120308</v>
+        <v>-1.811261814853854</v>
       </c>
     </row>
     <row r="377">
@@ -37993,55 +38183,55 @@
         <v>591</v>
       </c>
       <c r="G377" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H377" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I377" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="J377" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2768780487804878</v>
       </c>
       <c r="K377" t="n">
-        <v>0.2775479503572772</v>
+        <v>0.2852682926829269</v>
       </c>
       <c r="L377" t="n">
-        <v>0.46032342986085</v>
+        <v>0.4378536585365854</v>
       </c>
       <c r="M377" t="n">
-        <v>0.05970030288538175</v>
+        <v>0.06226422915889396</v>
       </c>
       <c r="N377" t="n">
         <v>2</v>
       </c>
       <c r="O377" t="n">
-        <v>0.2176548029257694</v>
+        <v>0.2190719802106852</v>
       </c>
       <c r="P377" t="n">
-        <v>0.3766298803319589</v>
+        <v>0.3763810442695905</v>
       </c>
       <c r="Q377" t="n">
-        <v>0.4057153167422716</v>
+        <v>0.4045469755197244</v>
       </c>
       <c r="R377" t="n">
         <v>1</v>
       </c>
       <c r="S377" t="n">
-        <v>-0.05460811311857838</v>
+        <v>-0.03330668301686096</v>
       </c>
       <c r="T377" t="n">
         <v>2</v>
       </c>
       <c r="U377" t="n">
-        <v>-0.05460811311857838</v>
+        <v>-0.03330668301686096</v>
       </c>
       <c r="V377" t="n">
-        <v>0.4057153167422716</v>
+        <v>0.4045469755197244</v>
       </c>
       <c r="W377" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="X377" t="inlineStr">
         <is>
@@ -38050,7 +38240,7 @@
       </c>
       <c r="Y377" t="inlineStr"/>
       <c r="Z377" t="n">
-        <v>0.7619992912455799</v>
+        <v>0.8038143256144191</v>
       </c>
       <c r="AA377" t="inlineStr">
         <is>
@@ -38062,14 +38252,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC377" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC377" t="inlineStr"/>
       <c r="AD377" t="n">
-        <v>-16.02700958841365</v>
+        <v>-11.32382631587762</v>
       </c>
       <c r="AE377" t="n">
-        <v>-0.320540191768273</v>
+        <v>-0.2264765263175523</v>
       </c>
     </row>
     <row r="378">
@@ -38104,19 +38292,19 @@
         <v>3.4</v>
       </c>
       <c r="I378" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J378" t="n">
-        <v>0.4697535474234503</v>
+        <v>0.4664634146341463</v>
       </c>
       <c r="K378" t="n">
-        <v>0.2763256161314414</v>
+        <v>0.274390243902439</v>
       </c>
       <c r="L378" t="n">
-        <v>0.2539208364451083</v>
+        <v>0.2591463414634146</v>
       </c>
       <c r="M378" t="n">
-        <v>0.06438791732909377</v>
+        <v>0.0718954248366015</v>
       </c>
       <c r="N378" t="n">
         <v>1</v>
@@ -38134,13 +38322,13 @@
         <v>1</v>
       </c>
       <c r="S378" t="n">
-        <v>-0.1112569772367052</v>
+        <v>-0.1079668444474011</v>
       </c>
       <c r="T378" t="n">
         <v>1</v>
       </c>
       <c r="U378" t="n">
-        <v>-0.1112569772367052</v>
+        <v>-0.1079668444474011</v>
       </c>
       <c r="V378" t="n">
         <v>0.3584965701867451</v>
@@ -38167,9 +38355,7 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC378" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC378" t="inlineStr"/>
       <c r="AD378" t="n">
         <v>-28.30068596265098</v>
       </c>
@@ -38203,55 +38389,55 @@
         <v>591</v>
       </c>
       <c r="G379" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H379" t="n">
         <v>3.7</v>
       </c>
       <c r="I379" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J379" t="n">
-        <v>0.4352087825916487</v>
+        <v>0.4454368932038835</v>
       </c>
       <c r="K379" t="n">
-        <v>0.2528915898843364</v>
+        <v>0.2528155339805825</v>
       </c>
       <c r="L379" t="n">
-        <v>0.3118996275240149</v>
+        <v>0.301747572815534</v>
       </c>
       <c r="M379" t="n">
-        <v>0.06871988267337104</v>
+        <v>0.06904139162203671</v>
       </c>
       <c r="N379" t="n">
         <v>2</v>
       </c>
       <c r="O379" t="n">
-        <v>0.3152064586474116</v>
+        <v>0.3148017923440429</v>
       </c>
       <c r="P379" t="n">
-        <v>0.3401004086964048</v>
+        <v>0.3401414299776316</v>
       </c>
       <c r="Q379" t="n">
-        <v>0.3446931326561834</v>
+        <v>0.3450567776783255</v>
       </c>
       <c r="R379" t="n">
         <v>1</v>
       </c>
       <c r="S379" t="n">
-        <v>0.0327935051321685</v>
+        <v>0.04330920486279155</v>
       </c>
       <c r="T379" t="n">
         <v>2</v>
       </c>
       <c r="U379" t="n">
-        <v>0.0327935051321685</v>
+        <v>0.04330920486279155</v>
       </c>
       <c r="V379" t="n">
-        <v>0.3446931326561834</v>
+        <v>0.3450567776783255</v>
       </c>
       <c r="W379" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X379" t="inlineStr">
         <is>
@@ -38260,7 +38446,7 @@
       </c>
       <c r="Y379" t="inlineStr"/>
       <c r="Z379" t="n">
-        <v>0.921404276934878</v>
+        <v>0.9360164891007222</v>
       </c>
       <c r="AA379" t="inlineStr">
         <is>
@@ -38272,14 +38458,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC379" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC379" t="inlineStr"/>
       <c r="AD379" t="n">
-        <v>1.70396989842751</v>
+        <v>3.317905276324246</v>
       </c>
       <c r="AE379" t="n">
-        <v>0.0340793979685502</v>
+        <v>0.06635810552648491</v>
       </c>
     </row>
     <row r="380">
@@ -38332,28 +38516,28 @@
         <v>2</v>
       </c>
       <c r="O380" t="n">
-        <v>0.1672306140399552</v>
+        <v>0.1669980959623882</v>
       </c>
       <c r="P380" t="n">
-        <v>0.3865776432051026</v>
+        <v>0.3866322058421756</v>
       </c>
       <c r="Q380" t="n">
-        <v>0.4461917427549421</v>
+        <v>0.4463696981954363</v>
       </c>
       <c r="R380" t="n">
         <v>1</v>
       </c>
       <c r="S380" t="n">
-        <v>-0.06607851441857215</v>
+        <v>-0.06590055897807801</v>
       </c>
       <c r="T380" t="n">
         <v>2</v>
       </c>
       <c r="U380" t="n">
-        <v>-0.06607851441857215</v>
+        <v>-0.06590055897807801</v>
       </c>
       <c r="V380" t="n">
-        <v>0.4461917427549421</v>
+        <v>0.4463696981954363</v>
       </c>
       <c r="W380" t="n">
         <v>1.83</v>
@@ -38365,7 +38549,7 @@
       </c>
       <c r="Y380" t="inlineStr"/>
       <c r="Z380" t="n">
-        <v>0.7089058532387609</v>
+        <v>0.7092445293022357</v>
       </c>
       <c r="AA380" t="inlineStr">
         <is>
@@ -38377,14 +38561,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC380" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC380" t="inlineStr"/>
       <c r="AD380" t="n">
-        <v>-22.104712139573</v>
+        <v>-22.06547618100621</v>
       </c>
       <c r="AE380" t="n">
-        <v>-0.44209424279146</v>
+        <v>-0.4413095236201243</v>
       </c>
     </row>
     <row r="381">
@@ -38437,28 +38619,28 @@
         <v>1</v>
       </c>
       <c r="O381" t="n">
-        <v>0.4417751078536791</v>
+        <v>0.4404587456083536</v>
       </c>
       <c r="P381" t="n">
-        <v>0.3064274967257183</v>
+        <v>0.3064480657429559</v>
       </c>
       <c r="Q381" t="n">
-        <v>0.2517973954206027</v>
+        <v>0.2530931886486905</v>
       </c>
       <c r="R381" t="n">
         <v>1</v>
       </c>
       <c r="S381" t="n">
-        <v>-0.1626573971832585</v>
+        <v>-0.1639737594285839</v>
       </c>
       <c r="T381" t="n">
         <v>1</v>
       </c>
       <c r="U381" t="n">
-        <v>-0.1626573971832585</v>
+        <v>-0.1639737594285839</v>
       </c>
       <c r="V381" t="n">
-        <v>0.4417751078536791</v>
+        <v>0.4404587456083536</v>
       </c>
       <c r="W381" t="n">
         <v>1.55</v>
@@ -38470,7 +38652,7 @@
       </c>
       <c r="Y381" t="inlineStr"/>
       <c r="Z381" t="n">
-        <v>0.4369573186783126</v>
+        <v>0.4345018672277963</v>
       </c>
       <c r="AA381" t="inlineStr">
         <is>
@@ -38482,14 +38664,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC381" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC381" t="inlineStr"/>
       <c r="AD381" t="n">
-        <v>-57.3179241503268</v>
+        <v>-57.68889896491852</v>
       </c>
       <c r="AE381" t="n">
-        <v>-1.146358483006536</v>
+        <v>-1.15377797929837</v>
       </c>
     </row>
     <row r="382">
@@ -38542,28 +38722,28 @@
         <v>2</v>
       </c>
       <c r="O382" t="n">
-        <v>0.238150866720009</v>
+        <v>0.2378793258306978</v>
       </c>
       <c r="P382" t="n">
-        <v>0.3571376583882965</v>
+        <v>0.3570999288367895</v>
       </c>
       <c r="Q382" t="n">
-        <v>0.4047114748916944</v>
+        <v>0.4050207453325126</v>
       </c>
       <c r="R382" t="n">
         <v>1</v>
       </c>
       <c r="S382" t="n">
-        <v>0.04300934723211997</v>
+        <v>0.04331861767293821</v>
       </c>
       <c r="T382" t="n">
         <v>2</v>
       </c>
       <c r="U382" t="n">
-        <v>0.04300934723211997</v>
+        <v>0.04331861767293821</v>
       </c>
       <c r="V382" t="n">
-        <v>0.4047114748916944</v>
+        <v>0.4050207453325126</v>
       </c>
       <c r="W382" t="n">
         <v>2.6</v>
@@ -38575,7 +38755,7 @@
       </c>
       <c r="Y382" t="inlineStr"/>
       <c r="Z382" t="n">
-        <v>0.9355432657260341</v>
+        <v>0.9359980805170577</v>
       </c>
       <c r="AA382" t="inlineStr">
         <is>
@@ -38587,14 +38767,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC382" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC382" t="inlineStr"/>
       <c r="AD382" t="n">
-        <v>3.265614669900346</v>
+        <v>3.315871116533309</v>
       </c>
       <c r="AE382" t="n">
-        <v>0.06531229339800693</v>
+        <v>0.06631742233066618</v>
       </c>
     </row>
     <row r="383">
@@ -38629,46 +38807,46 @@
         <v>5.75</v>
       </c>
       <c r="I383" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J383" t="n">
-        <v>0.7449392712550608</v>
+        <v>0.7512991833704529</v>
       </c>
       <c r="K383" t="n">
-        <v>0.1619433198380567</v>
+        <v>0.1633259094283593</v>
       </c>
       <c r="L383" t="n">
-        <v>0.0931174089068826</v>
+        <v>0.08537490720118782</v>
       </c>
       <c r="M383" t="n">
-        <v>0.07391304347826089</v>
+        <v>0.06482213438735185</v>
       </c>
       <c r="N383" t="n">
         <v>1</v>
       </c>
       <c r="O383" t="n">
-        <v>0.5091481278053708</v>
+        <v>0.5084470222710094</v>
       </c>
       <c r="P383" t="n">
-        <v>0.2794691730686739</v>
+        <v>0.2795301883910938</v>
       </c>
       <c r="Q383" t="n">
-        <v>0.2113826991259553</v>
+        <v>0.2120227893378969</v>
       </c>
       <c r="R383" t="n">
         <v>1</v>
       </c>
       <c r="S383" t="n">
-        <v>-0.23579114344969</v>
+        <v>-0.2428521610994435</v>
       </c>
       <c r="T383" t="n">
         <v>1</v>
       </c>
       <c r="U383" t="n">
-        <v>-0.23579114344969</v>
+        <v>-0.2428521610994435</v>
       </c>
       <c r="V383" t="n">
-        <v>0.5091481278053708</v>
+        <v>0.5084470222710094</v>
       </c>
       <c r="W383" t="n">
         <v>1.25</v>
@@ -38680,7 +38858,7 @@
       </c>
       <c r="Y383" t="inlineStr"/>
       <c r="Z383" t="n">
-        <v>0.09373883260926454</v>
+        <v>0.09311757953811441</v>
       </c>
       <c r="AA383" t="inlineStr">
         <is>
@@ -38692,14 +38870,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC383" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC383" t="inlineStr"/>
       <c r="AD383" t="n">
-        <v>-145.4259360973146</v>
+        <v>-145.7764888644953</v>
       </c>
       <c r="AE383" t="n">
-        <v>-2.908518721946292</v>
+        <v>-2.915529777289906</v>
       </c>
     </row>
     <row r="384">
@@ -38734,49 +38910,49 @@
         <v>5</v>
       </c>
       <c r="I384" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="J384" t="n">
-        <v>0.1994210357027983</v>
+        <v>0.197840563780953</v>
       </c>
       <c r="K384" t="n">
-        <v>0.1894499839176584</v>
+        <v>0.1879485355919054</v>
       </c>
       <c r="L384" t="n">
-        <v>0.6111289803795432</v>
+        <v>0.6142109006271417</v>
       </c>
       <c r="M384" t="n">
-        <v>0.05568760611205437</v>
+        <v>0.06412108703130381</v>
       </c>
       <c r="N384" t="n">
         <v>2</v>
       </c>
       <c r="O384" t="n">
-        <v>0.1242853202011915</v>
+        <v>0.1195523256994929</v>
       </c>
       <c r="P384" t="n">
-        <v>0.3841806166704361</v>
+        <v>0.3853122815084659</v>
       </c>
       <c r="Q384" t="n">
-        <v>0.4915340631283723</v>
+        <v>0.4951353927920412</v>
       </c>
       <c r="R384" t="n">
         <v>1</v>
       </c>
       <c r="S384" t="n">
-        <v>-0.1195949172511709</v>
+        <v>-0.1190755078351005</v>
       </c>
       <c r="T384" t="n">
         <v>2</v>
       </c>
       <c r="U384" t="n">
-        <v>-0.1195949172511709</v>
+        <v>-0.1190755078351005</v>
       </c>
       <c r="V384" t="n">
-        <v>0.4915340631283723</v>
+        <v>0.4951353927920412</v>
       </c>
       <c r="W384" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X384" t="inlineStr">
         <is>
@@ -38785,7 +38961,7 @@
       </c>
       <c r="Y384" t="inlineStr"/>
       <c r="Z384" t="n">
-        <v>0.5365296150664491</v>
+        <v>0.5182185083656299</v>
       </c>
       <c r="AA384" t="inlineStr">
         <is>
@@ -38797,14 +38973,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC384" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC384" t="inlineStr"/>
       <c r="AD384" t="n">
-        <v>-43.29494584564055</v>
+        <v>-45.7439337789013</v>
       </c>
       <c r="AE384" t="n">
-        <v>-0.865898916912811</v>
+        <v>-0.914878675578026</v>
       </c>
     </row>
     <row r="385">
@@ -38839,49 +39013,49 @@
         <v>8</v>
       </c>
       <c r="I385" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="J385" t="n">
-        <v>0.1052404571921501</v>
+        <v>0.1038961038961039</v>
       </c>
       <c r="K385" t="n">
-        <v>0.1183955143411689</v>
+        <v>0.1168831168831169</v>
       </c>
       <c r="L385" t="n">
-        <v>0.7763640284666811</v>
+        <v>0.7792207792207793</v>
       </c>
       <c r="M385" t="n">
-        <v>0.05578324225865217</v>
+        <v>0.06944444444444442</v>
       </c>
       <c r="N385" t="n">
         <v>2</v>
       </c>
       <c r="O385" t="n">
-        <v>0.09214327017688557</v>
+        <v>0.08973593565029485</v>
       </c>
       <c r="P385" t="n">
-        <v>0.4096576064363935</v>
+        <v>0.4100188559815401</v>
       </c>
       <c r="Q385" t="n">
-        <v>0.4981991233867209</v>
+        <v>0.500245208368165</v>
       </c>
       <c r="R385" t="n">
         <v>1</v>
       </c>
       <c r="S385" t="n">
-        <v>-0.2781649050799602</v>
+        <v>-0.2789755708526143</v>
       </c>
       <c r="T385" t="n">
         <v>2</v>
       </c>
       <c r="U385" t="n">
-        <v>-0.2781649050799602</v>
+        <v>-0.2789755708526143</v>
       </c>
       <c r="V385" t="n">
-        <v>0.4981991233867209</v>
+        <v>0.500245208368165</v>
       </c>
       <c r="W385" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X385" t="inlineStr">
         <is>
@@ -38890,7 +39064,7 @@
       </c>
       <c r="Y385" t="inlineStr"/>
       <c r="Z385" t="n">
-        <v>0.04984067368227356</v>
+        <v>0.03268417827542294</v>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
@@ -38902,14 +39076,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC385" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC385" t="inlineStr"/>
       <c r="AD385" t="n">
-        <v>-178.2713952128184</v>
+        <v>-199.852874979101</v>
       </c>
       <c r="AE385" t="n">
-        <v>-3.565427904256369</v>
+        <v>-3.997057499582021</v>
       </c>
     </row>
     <row r="386">
@@ -38962,28 +39134,28 @@
         <v>0</v>
       </c>
       <c r="O386" t="n">
-        <v>0.271833047385438</v>
+        <v>0.2701630991415704</v>
       </c>
       <c r="P386" t="n">
-        <v>0.3725647627838288</v>
+        <v>0.3727973553968514</v>
       </c>
       <c r="Q386" t="n">
-        <v>0.3556021898307333</v>
+        <v>0.3570395454615783</v>
       </c>
       <c r="R386" t="n">
         <v>1</v>
       </c>
       <c r="S386" t="n">
-        <v>0.08615105409349827</v>
+        <v>0.08638364670652088</v>
       </c>
       <c r="T386" t="n">
         <v>0</v>
       </c>
       <c r="U386" t="n">
-        <v>0.08615105409349827</v>
+        <v>0.08638364670652088</v>
       </c>
       <c r="V386" t="n">
-        <v>0.3725647627838288</v>
+        <v>0.3727973553968514</v>
       </c>
       <c r="W386" t="n">
         <v>3.3</v>
@@ -38995,7 +39167,7 @@
       </c>
       <c r="Y386" t="inlineStr"/>
       <c r="Z386" t="n">
-        <v>0.9960552430807968</v>
+        <v>0.9963545832864301</v>
       </c>
       <c r="AA386" t="inlineStr">
         <is>
@@ -39007,14 +39179,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC386" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC386" t="inlineStr"/>
       <c r="AD386" t="n">
-        <v>9.976683355940647</v>
+        <v>10.01005533954823</v>
       </c>
       <c r="AE386" t="n">
-        <v>0.1995336671188129</v>
+        <v>0.2002011067909647</v>
       </c>
     </row>
     <row r="387">
@@ -39067,28 +39237,28 @@
         <v>0</v>
       </c>
       <c r="O387" t="n">
-        <v>0.3171114500406904</v>
+        <v>0.3149298234116497</v>
       </c>
       <c r="P387" t="n">
-        <v>0.3436295775216426</v>
+        <v>0.3436526017499043</v>
       </c>
       <c r="Q387" t="n">
-        <v>0.3392589724376669</v>
+        <v>0.3414175748384461</v>
       </c>
       <c r="R387" t="n">
         <v>1</v>
       </c>
       <c r="S387" t="n">
-        <v>0.07371166347045965</v>
+        <v>0.07373468769872127</v>
       </c>
       <c r="T387" t="n">
         <v>0</v>
       </c>
       <c r="U387" t="n">
-        <v>0.07371166347045965</v>
+        <v>0.07373468769872127</v>
       </c>
       <c r="V387" t="n">
-        <v>0.3436295775216426</v>
+        <v>0.3436526017499043</v>
       </c>
       <c r="W387" t="n">
         <v>3.5</v>
@@ -39100,7 +39270,7 @@
       </c>
       <c r="Y387" t="inlineStr"/>
       <c r="Z387" t="n">
-        <v>0.979264980562929</v>
+        <v>0.9792939922506444</v>
       </c>
       <c r="AA387" t="inlineStr">
         <is>
@@ -39112,14 +39282,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="AC387" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC387" t="inlineStr"/>
       <c r="AD387" t="n">
-        <v>8.108140853029971</v>
+        <v>8.111364244986591</v>
       </c>
       <c r="AE387" t="n">
-        <v>0.1621628170605994</v>
+        <v>0.1622272848997318</v>
       </c>
     </row>
     <row r="388">
@@ -39251,55 +39419,55 @@
         <v>771</v>
       </c>
       <c r="G389" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="H389" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I389" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="J389" t="n">
-        <v>0.3041456016177958</v>
+        <v>0.2606635071090047</v>
       </c>
       <c r="K389" t="n">
-        <v>0.2946410515672397</v>
+        <v>0.3127962085308056</v>
       </c>
       <c r="L389" t="n">
-        <v>0.4012133468149647</v>
+        <v>0.4265402843601895</v>
       </c>
       <c r="M389" t="n">
-        <v>0.06061256005490723</v>
+        <v>0.06565656565656575</v>
       </c>
       <c r="N389" t="n">
         <v>0</v>
       </c>
       <c r="O389" t="n">
-        <v>0.2415841668844223</v>
+        <v>0.2407787889242172</v>
       </c>
       <c r="P389" t="n">
-        <v>0.4831582605838776</v>
+        <v>0.4815475344657898</v>
       </c>
       <c r="Q389" t="n">
-        <v>0.2752576172351837</v>
+        <v>0.277673751115799</v>
       </c>
       <c r="R389" t="n">
         <v>1</v>
       </c>
       <c r="S389" t="n">
-        <v>0.1885172090166379</v>
+        <v>0.1687513259349842</v>
       </c>
       <c r="T389" t="n">
         <v>0</v>
       </c>
       <c r="U389" t="n">
-        <v>0.1885172090166379</v>
+        <v>0.1687513259349842</v>
       </c>
       <c r="V389" t="n">
-        <v>0.4831582605838776</v>
+        <v>0.4815475344657898</v>
       </c>
       <c r="W389" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="X389" t="inlineStr">
         <is>
@@ -39308,7 +39476,7 @@
       </c>
       <c r="Y389" t="inlineStr"/>
       <c r="Z389" t="n">
-        <v>4.813990811434202</v>
+        <v>4.719028315433033</v>
       </c>
       <c r="AA389" t="inlineStr">
         <is>
@@ -39322,10 +39490,10 @@
       </c>
       <c r="AC389" t="inlineStr"/>
       <c r="AD389" t="n">
-        <v>24.82301972129128</v>
+        <v>22.23213016986847</v>
       </c>
       <c r="AE389" t="n">
-        <v>0.4964603944258257</v>
+        <v>0.4446426033973694</v>
       </c>
     </row>
     <row r="390">
@@ -39378,28 +39546,28 @@
         <v>1</v>
       </c>
       <c r="O390" t="n">
-        <v>0.6114410161972046</v>
+        <v>0.6118006706237793</v>
       </c>
       <c r="P390" t="n">
-        <v>0.1967238336801529</v>
+        <v>0.1970229148864746</v>
       </c>
       <c r="Q390" t="n">
-        <v>0.1918351799249649</v>
+        <v>0.1911764591932297</v>
       </c>
       <c r="R390" t="n">
         <v>1</v>
       </c>
       <c r="S390" t="n">
-        <v>-0.06461532183096441</v>
+        <v>-0.0642556674043897</v>
       </c>
       <c r="T390" t="n">
         <v>1</v>
       </c>
       <c r="U390" t="n">
-        <v>-0.06461532183096441</v>
+        <v>-0.0642556674043897</v>
       </c>
       <c r="V390" t="n">
-        <v>0.6114410161972046</v>
+        <v>0.6118006706237793</v>
       </c>
       <c r="W390" t="n">
         <v>1.38</v>
@@ -39411,7 +39579,7 @@
       </c>
       <c r="Y390" t="inlineStr"/>
       <c r="Z390" t="n">
-        <v>2.364330063299158</v>
+        <v>2.368622800881497</v>
       </c>
       <c r="AA390" t="inlineStr">
         <is>
@@ -39425,10 +39593,10 @@
       </c>
       <c r="AC390" t="inlineStr"/>
       <c r="AD390" t="n">
-        <v>-41.10826253890993</v>
+        <v>-40.97765119452228</v>
       </c>
       <c r="AE390" t="n">
-        <v>-0.8221652507781987</v>
+        <v>-0.8195530238904456</v>
       </c>
     </row>
     <row r="391">
@@ -39457,55 +39625,55 @@
         <v>771</v>
       </c>
       <c r="G391" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="H391" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I391" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="J391" t="n">
-        <v>0.4713975380159305</v>
+        <v>0.4592557701365992</v>
       </c>
       <c r="K391" t="n">
-        <v>0.3041274438812455</v>
+        <v>0.2896844088553933</v>
       </c>
       <c r="L391" t="n">
-        <v>0.224475018102824</v>
+        <v>0.2510598210080076</v>
       </c>
       <c r="M391" t="n">
-        <v>0.0606758832565284</v>
+        <v>0.06216385240775479</v>
       </c>
       <c r="N391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O391" t="n">
-        <v>0.4005041122436523</v>
+        <v>0.3887141346931458</v>
       </c>
       <c r="P391" t="n">
-        <v>0.3911901116371155</v>
+        <v>0.4021904170513153</v>
       </c>
       <c r="Q391" t="n">
-        <v>0.2083057314157486</v>
+        <v>0.2090954631567001</v>
       </c>
       <c r="R391" t="n">
         <v>1</v>
       </c>
       <c r="S391" t="n">
-        <v>-0.07089342577227814</v>
+        <v>0.112506008195922</v>
       </c>
       <c r="T391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U391" t="n">
-        <v>-0.07089342577227814</v>
+        <v>0.112506008195922</v>
       </c>
       <c r="V391" t="n">
-        <v>0.4005041122436523</v>
+        <v>0.4021904170513153</v>
       </c>
       <c r="W391" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="X391" t="inlineStr">
         <is>
@@ -39514,7 +39682,7 @@
       </c>
       <c r="Y391" t="inlineStr"/>
       <c r="Z391" t="n">
-        <v>3.11158646863163</v>
+        <v>4.397359967987123</v>
       </c>
       <c r="AA391" t="inlineStr">
         <is>
@@ -39528,10 +39696,10 @@
       </c>
       <c r="AC391" t="inlineStr"/>
       <c r="AD391" t="n">
-        <v>-19.89917755126953</v>
+        <v>13.64972690741221</v>
       </c>
       <c r="AE391" t="n">
-        <v>-0.3979835510253906</v>
+        <v>0.2729945381482443</v>
       </c>
     </row>
     <row r="392">
@@ -39566,49 +39734,49 @@
         <v>3.5</v>
       </c>
       <c r="I392" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="J392" t="n">
-        <v>0.1705075845974329</v>
+        <v>0.1693548387096774</v>
       </c>
       <c r="K392" t="n">
-        <v>0.2679404900816802</v>
+        <v>0.2661290322580645</v>
       </c>
       <c r="L392" t="n">
-        <v>0.5615519253208868</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="M392" t="n">
-        <v>0.06633486274204836</v>
+        <v>0.07359307359307365</v>
       </c>
       <c r="N392" t="n">
         <v>2</v>
       </c>
       <c r="O392" t="n">
-        <v>0.197742834687233</v>
+        <v>0.1967838853597641</v>
       </c>
       <c r="P392" t="n">
-        <v>0.3996880054473877</v>
+        <v>0.3952086269855499</v>
       </c>
       <c r="Q392" t="n">
-        <v>0.4025692045688629</v>
+        <v>0.4080075025558472</v>
       </c>
       <c r="R392" t="n">
         <v>1</v>
       </c>
       <c r="S392" t="n">
-        <v>-0.1589827207520239</v>
+        <v>-0.1565086264764108</v>
       </c>
       <c r="T392" t="n">
         <v>2</v>
       </c>
       <c r="U392" t="n">
-        <v>-0.1589827207520239</v>
+        <v>-0.1565086264764108</v>
       </c>
       <c r="V392" t="n">
-        <v>0.4025692045688629</v>
+        <v>0.4080075025558472</v>
       </c>
       <c r="W392" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X392" t="inlineStr">
         <is>
@@ -39617,7 +39785,7 @@
       </c>
       <c r="Y392" t="inlineStr"/>
       <c r="Z392" t="n">
-        <v>2.116032311931075</v>
+        <v>2.074365822863361</v>
       </c>
       <c r="AA392" t="inlineStr">
         <is>
@@ -39631,10 +39799,10 @@
       </c>
       <c r="AC392" t="inlineStr"/>
       <c r="AD392" t="n">
-        <v>-48.91185498059687</v>
+        <v>-50.27501858197727</v>
       </c>
       <c r="AE392" t="n">
-        <v>-0.9782370996119374</v>
+        <v>-1.005500371639545</v>
       </c>
     </row>
     <row r="393">
@@ -39687,28 +39855,28 @@
         <v>0</v>
       </c>
       <c r="O393" t="n">
-        <v>0.2050438672304153</v>
+        <v>0.2051650583744049</v>
       </c>
       <c r="P393" t="n">
-        <v>0.3989062011241913</v>
+        <v>0.4007787704467773</v>
       </c>
       <c r="Q393" t="n">
-        <v>0.396049976348877</v>
+        <v>0.3940562009811401</v>
       </c>
       <c r="R393" t="n">
         <v>1</v>
       </c>
       <c r="S393" t="n">
-        <v>0.1104151525308408</v>
+        <v>0.1122877218534269</v>
       </c>
       <c r="T393" t="n">
         <v>0</v>
       </c>
       <c r="U393" t="n">
-        <v>0.1104151525308408</v>
+        <v>0.1122877218534269</v>
       </c>
       <c r="V393" t="n">
-        <v>0.3989062011241913</v>
+        <v>0.4007787704467773</v>
       </c>
       <c r="W393" t="n">
         <v>3.25</v>
@@ -39720,7 +39888,7 @@
       </c>
       <c r="Y393" t="inlineStr"/>
       <c r="Z393" t="n">
-        <v>4.379317847126009</v>
+        <v>4.389607765574908</v>
       </c>
       <c r="AA393" t="inlineStr">
         <is>
@@ -39734,10 +39902,10 @@
       </c>
       <c r="AC393" t="inlineStr"/>
       <c r="AD393" t="n">
-        <v>13.17534016238319</v>
+        <v>13.44582239786784</v>
       </c>
       <c r="AE393" t="n">
-        <v>0.2635068032476637</v>
+        <v>0.2689164479573568</v>
       </c>
     </row>
     <row r="394">
@@ -39790,28 +39958,28 @@
         <v>2</v>
       </c>
       <c r="O394" t="n">
-        <v>0.2844262421131134</v>
+        <v>0.2839991748332977</v>
       </c>
       <c r="P394" t="n">
-        <v>0.3307288587093353</v>
+        <v>0.3246980309486389</v>
       </c>
       <c r="Q394" t="n">
-        <v>0.3848448693752289</v>
+        <v>0.391302764415741</v>
       </c>
       <c r="R394" t="n">
         <v>1</v>
       </c>
       <c r="S394" t="n">
-        <v>-0.1870751478253732</v>
+        <v>-0.1806172527848611</v>
       </c>
       <c r="T394" t="n">
         <v>2</v>
       </c>
       <c r="U394" t="n">
-        <v>-0.1870751478253732</v>
+        <v>-0.1806172527848611</v>
       </c>
       <c r="V394" t="n">
-        <v>0.3848448693752289</v>
+        <v>0.391302764415741</v>
       </c>
       <c r="W394" t="n">
         <v>1.65</v>
@@ -39823,7 +39991,7 @@
       </c>
       <c r="Y394" t="inlineStr"/>
       <c r="Z394" t="n">
-        <v>1.900712209893403</v>
+        <v>1.948125900469534</v>
       </c>
       <c r="AA394" t="inlineStr">
         <is>
@@ -39837,10 +40005,10 @@
       </c>
       <c r="AC394" t="inlineStr"/>
       <c r="AD394" t="n">
-        <v>-56.15476392782652</v>
+        <v>-54.51545210985038</v>
       </c>
       <c r="AE394" t="n">
-        <v>-1.12309527855653</v>
+        <v>-1.090309042197008</v>
       </c>
     </row>
     <row r="395">
@@ -39869,52 +40037,52 @@
         <v>771</v>
       </c>
       <c r="G395" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="H395" t="n">
         <v>3.1</v>
       </c>
       <c r="I395" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="J395" t="n">
-        <v>0.3355537052456287</v>
+        <v>0.3409799042261768</v>
       </c>
       <c r="K395" t="n">
-        <v>0.3030807660283097</v>
+        <v>0.3024821731038665</v>
       </c>
       <c r="L395" t="n">
-        <v>0.3613655287260616</v>
+        <v>0.3565379226699568</v>
       </c>
       <c r="M395" t="n">
-        <v>0.06433888691953205</v>
+        <v>0.06644514567978321</v>
       </c>
       <c r="N395" t="n">
         <v>0</v>
       </c>
       <c r="O395" t="n">
-        <v>0.2580694854259491</v>
+        <v>0.2547066509723663</v>
       </c>
       <c r="P395" t="n">
-        <v>0.493230402469635</v>
+        <v>0.4998339414596558</v>
       </c>
       <c r="Q395" t="n">
-        <v>0.2487001568078995</v>
+        <v>0.2454594075679779</v>
       </c>
       <c r="R395" t="n">
         <v>1</v>
       </c>
       <c r="S395" t="n">
-        <v>0.1901496364413253</v>
+        <v>0.1973517683557893</v>
       </c>
       <c r="T395" t="n">
         <v>0</v>
       </c>
       <c r="U395" t="n">
-        <v>0.1901496364413253</v>
+        <v>0.1973517683557893</v>
       </c>
       <c r="V395" t="n">
-        <v>0.493230402469635</v>
+        <v>0.4998339414596558</v>
       </c>
       <c r="W395" t="n">
         <v>3.1</v>
@@ -39926,7 +40094,7 @@
       </c>
       <c r="Y395" t="inlineStr"/>
       <c r="Z395" t="n">
-        <v>4.827389785450539</v>
+        <v>4.862751560675377</v>
       </c>
       <c r="AA395" t="inlineStr">
         <is>
@@ -39940,10 +40108,10 @@
       </c>
       <c r="AC395" t="inlineStr"/>
       <c r="AD395" t="n">
-        <v>25.19115465027946</v>
+        <v>26.16596278690156</v>
       </c>
       <c r="AE395" t="n">
-        <v>0.5038230930055891</v>
+        <v>0.5233192557380313</v>
       </c>
     </row>
     <row r="396">
@@ -39972,55 +40140,55 @@
         <v>771</v>
       </c>
       <c r="G396" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H396" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I396" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="J396" t="n">
-        <v>0.2309829802014589</v>
+        <v>0.2264963612060003</v>
       </c>
       <c r="K396" t="n">
-        <v>0.2705800625217089</v>
+        <v>0.2536759245507204</v>
       </c>
       <c r="L396" t="n">
-        <v>0.4984369572768322</v>
+        <v>0.5198277142432793</v>
       </c>
       <c r="M396" t="n">
-        <v>0.05593251421236012</v>
+        <v>0.05120999219359867</v>
       </c>
       <c r="N396" t="n">
         <v>0</v>
       </c>
       <c r="O396" t="n">
-        <v>0.2348176240921021</v>
+        <v>0.2347460687160492</v>
       </c>
       <c r="P396" t="n">
-        <v>0.3905291259288788</v>
+        <v>0.3904101252555847</v>
       </c>
       <c r="Q396" t="n">
-        <v>0.3746532499790192</v>
+        <v>0.3748438358306885</v>
       </c>
       <c r="R396" t="n">
         <v>1</v>
       </c>
       <c r="S396" t="n">
-        <v>0.1199490634071699</v>
+        <v>0.1367342007048644</v>
       </c>
       <c r="T396" t="n">
         <v>0</v>
       </c>
       <c r="U396" t="n">
-        <v>0.1199490634071699</v>
+        <v>0.1367342007048644</v>
       </c>
       <c r="V396" t="n">
-        <v>0.3905291259288788</v>
+        <v>0.3904101252555847</v>
       </c>
       <c r="W396" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="X396" t="inlineStr">
         <is>
@@ -40029,7 +40197,7 @@
       </c>
       <c r="Y396" t="inlineStr"/>
       <c r="Z396" t="n">
-        <v>4.436238437977979</v>
+        <v>4.519337485526357</v>
       </c>
       <c r="AA396" t="inlineStr">
         <is>
@@ -40043,10 +40211,10 @@
       </c>
       <c r="AC396" t="inlineStr"/>
       <c r="AD396" t="n">
-        <v>14.67407763004303</v>
+        <v>16.87410798939792</v>
       </c>
       <c r="AE396" t="n">
-        <v>0.2934815526008606</v>
+        <v>0.3374821597879583</v>
       </c>
     </row>
     <row r="397">
@@ -40099,28 +40267,28 @@
         <v>0</v>
       </c>
       <c r="O397" t="n">
-        <v>0.2818354666233063</v>
+        <v>0.2750804722309113</v>
       </c>
       <c r="P397" t="n">
-        <v>0.4845733940601349</v>
+        <v>0.4914714097976685</v>
       </c>
       <c r="Q397" t="n">
-        <v>0.2335911393165588</v>
+        <v>0.2334481477737427</v>
       </c>
       <c r="R397" t="n">
         <v>1</v>
       </c>
       <c r="S397" t="n">
-        <v>0.1711405582392393</v>
+        <v>0.1780385739767729</v>
       </c>
       <c r="T397" t="n">
         <v>0</v>
       </c>
       <c r="U397" t="n">
-        <v>0.1711405582392393</v>
+        <v>0.1780385739767729</v>
       </c>
       <c r="V397" t="n">
-        <v>0.4845733940601349</v>
+        <v>0.4914714097976685</v>
       </c>
       <c r="W397" t="n">
         <v>3</v>
@@ -40132,7 +40300,7 @@
       </c>
       <c r="Y397" t="inlineStr"/>
       <c r="Z397" t="n">
-        <v>4.735745385533121</v>
+        <v>4.773727756281637</v>
       </c>
       <c r="AA397" t="inlineStr">
         <is>
@@ -40146,10 +40314,10 @@
       </c>
       <c r="AC397" t="inlineStr"/>
       <c r="AD397" t="n">
-        <v>22.68600910902023</v>
+        <v>23.72071146965027</v>
       </c>
       <c r="AE397" t="n">
-        <v>0.4537201821804047</v>
+        <v>0.4744142293930054</v>
       </c>
     </row>
     <row r="398">
@@ -40281,25 +40449,25 @@
         <v>771</v>
       </c>
       <c r="G399" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H399" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I399" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J399" t="n">
-        <v>0.4713493530499075</v>
+        <v>0.4471544715447154</v>
       </c>
       <c r="K399" t="n">
-        <v>0.2772643253234751</v>
+        <v>0.2845528455284553</v>
       </c>
       <c r="L399" t="n">
-        <v>0.2513863216266174</v>
+        <v>0.2682926829268292</v>
       </c>
       <c r="M399" t="n">
-        <v>0.0607843137254902</v>
+        <v>0.06493506493506507</v>
       </c>
       <c r="N399" t="n">
         <v>0</v>
@@ -40317,19 +40485,19 @@
         <v>1</v>
       </c>
       <c r="S399" t="n">
-        <v>0.1455484047504538</v>
+        <v>0.1382598845454736</v>
       </c>
       <c r="T399" t="n">
         <v>0</v>
       </c>
       <c r="U399" t="n">
-        <v>0.1455484047504538</v>
+        <v>0.1382598845454736</v>
       </c>
       <c r="V399" t="n">
         <v>0.4228127300739288</v>
       </c>
       <c r="W399" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="X399" t="inlineStr">
         <is>
@@ -40338,7 +40506,7 @@
       </c>
       <c r="Y399" t="inlineStr"/>
       <c r="Z399" t="n">
-        <v>4.570320891610544</v>
+        <v>4.531077175621822</v>
       </c>
       <c r="AA399" t="inlineStr">
         <is>
@@ -40352,10 +40520,10 @@
       </c>
       <c r="AC399" t="inlineStr"/>
       <c r="AD399" t="n">
-        <v>18.23180342713992</v>
+        <v>17.186174314955</v>
       </c>
       <c r="AE399" t="n">
-        <v>0.3646360685427983</v>
+        <v>0.3437234862991001</v>
       </c>
     </row>
     <row r="400">
@@ -40717,28 +40885,28 @@
         <v>1</v>
       </c>
       <c r="O403" t="n">
-        <v>0.4993608295917511</v>
+        <v>0.4984340965747833</v>
       </c>
       <c r="P403" t="n">
-        <v>0.3011950552463531</v>
+        <v>0.3016817271709442</v>
       </c>
       <c r="Q403" t="n">
-        <v>0.1994441449642181</v>
+        <v>0.1998841911554337</v>
       </c>
       <c r="R403" t="n">
         <v>1</v>
       </c>
       <c r="S403" t="n">
-        <v>0.02663355686447838</v>
+        <v>0.02570682384751061</v>
       </c>
       <c r="T403" t="n">
         <v>1</v>
       </c>
       <c r="U403" t="n">
-        <v>0.02663355686447838</v>
+        <v>0.02570682384751061</v>
       </c>
       <c r="V403" t="n">
-        <v>0.4993608295917511</v>
+        <v>0.4984340965747833</v>
       </c>
       <c r="W403" t="n">
         <v>2</v>
@@ -40750,7 +40918,7 @@
       </c>
       <c r="Y403" t="inlineStr"/>
       <c r="Z403" t="n">
-        <v>3.86713875579124</v>
+        <v>3.859962008037489</v>
       </c>
       <c r="AA403" t="inlineStr">
         <is>
@@ -40764,10 +40932,10 @@
       </c>
       <c r="AC403" t="inlineStr"/>
       <c r="AD403" t="n">
-        <v>-0.1278340816497803</v>
+        <v>-0.313180685043335</v>
       </c>
       <c r="AE403" t="n">
-        <v>-0.002556681632995605</v>
+        <v>-0.006263613700866699</v>
       </c>
     </row>
     <row r="404">
@@ -40802,46 +40970,46 @@
         <v>4</v>
       </c>
       <c r="I404" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="J404" t="n">
-        <v>0.5958549222797929</v>
+        <v>0.5913978494623655</v>
       </c>
       <c r="K404" t="n">
-        <v>0.2383419689119171</v>
+        <v>0.2365591397849462</v>
       </c>
       <c r="L404" t="n">
-        <v>0.1658031088082902</v>
+        <v>0.1720430107526882</v>
       </c>
       <c r="M404" t="n">
-        <v>0.04891304347826075</v>
+        <v>0.05681818181818188</v>
       </c>
       <c r="N404" t="n">
         <v>1</v>
       </c>
       <c r="O404" t="n">
-        <v>0.5561535358428955</v>
+        <v>0.5579578280448914</v>
       </c>
       <c r="P404" t="n">
-        <v>0.2530986368656158</v>
+        <v>0.2512670159339905</v>
       </c>
       <c r="Q404" t="n">
-        <v>0.1907478421926498</v>
+        <v>0.1907751858234406</v>
       </c>
       <c r="R404" t="n">
         <v>1</v>
       </c>
       <c r="S404" t="n">
-        <v>-0.03970138643689736</v>
+        <v>-0.03344002141747415</v>
       </c>
       <c r="T404" t="n">
         <v>1</v>
       </c>
       <c r="U404" t="n">
-        <v>-0.03970138643689736</v>
+        <v>-0.03344002141747415</v>
       </c>
       <c r="V404" t="n">
-        <v>0.5561535358428955</v>
+        <v>0.5579578280448914</v>
       </c>
       <c r="W404" t="n">
         <v>1.6</v>
@@ -40853,7 +41021,7 @@
       </c>
       <c r="Y404" t="inlineStr"/>
       <c r="Z404" t="n">
-        <v>3.16909025635755</v>
+        <v>3.187122113791959</v>
       </c>
       <c r="AA404" t="inlineStr">
         <is>
@@ -40867,10 +41035,10 @@
       </c>
       <c r="AC404" t="inlineStr"/>
       <c r="AD404" t="n">
-        <v>-18.35905710856118</v>
+        <v>-17.87791252136229</v>
       </c>
       <c r="AE404" t="n">
-        <v>-0.3671811421712236</v>
+        <v>-0.3575582504272459</v>
       </c>
     </row>
     <row r="405">
@@ -40923,28 +41091,28 @@
         <v>0</v>
       </c>
       <c r="O405" t="n">
-        <v>0.3966474533081055</v>
+        <v>0.3982662856578827</v>
       </c>
       <c r="P405" t="n">
-        <v>0.4159072637557983</v>
+        <v>0.4135233759880066</v>
       </c>
       <c r="Q405" t="n">
-        <v>0.1874452829360962</v>
+        <v>0.1882103085517883</v>
       </c>
       <c r="R405" t="n">
         <v>1</v>
       </c>
       <c r="S405" t="n">
-        <v>0.1210889195032671</v>
+        <v>0.1187050317354753</v>
       </c>
       <c r="T405" t="n">
         <v>0</v>
       </c>
       <c r="U405" t="n">
-        <v>0.1210889195032671</v>
+        <v>0.1187050317354753</v>
       </c>
       <c r="V405" t="n">
-        <v>0.4159072637557983</v>
+        <v>0.4135233759880066</v>
       </c>
       <c r="W405" t="n">
         <v>3.2</v>
@@ -40956,7 +41124,7 @@
       </c>
       <c r="Y405" t="inlineStr"/>
       <c r="Z405" t="n">
-        <v>4.450139054942939</v>
+        <v>4.437005171721267</v>
       </c>
       <c r="AA405" t="inlineStr">
         <is>
@@ -40970,10 +41138,10 @@
       </c>
       <c r="AC405" t="inlineStr"/>
       <c r="AD405" t="n">
-        <v>15.04105654629794</v>
+        <v>14.69430923461914</v>
       </c>
       <c r="AE405" t="n">
-        <v>0.3008211309259589</v>
+        <v>0.2938861846923828</v>
       </c>
     </row>
     <row r="406">
@@ -41129,28 +41297,28 @@
         <v>0</v>
       </c>
       <c r="O407" t="n">
-        <v>0.3564672470092773</v>
+        <v>0.355811208486557</v>
       </c>
       <c r="P407" t="n">
-        <v>0.391137421131134</v>
+        <v>0.3904175758361816</v>
       </c>
       <c r="Q407" t="n">
-        <v>0.2523953020572662</v>
+        <v>0.2537712454795837</v>
       </c>
       <c r="R407" t="n">
         <v>1</v>
       </c>
       <c r="S407" t="n">
-        <v>0.1074905325638403</v>
+        <v>0.1067706872688879</v>
       </c>
       <c r="T407" t="n">
         <v>0</v>
       </c>
       <c r="U407" t="n">
-        <v>0.1074905325638403</v>
+        <v>0.1067706872688879</v>
       </c>
       <c r="V407" t="n">
-        <v>0.391137421131134</v>
+        <v>0.3904175758361816</v>
       </c>
       <c r="W407" t="n">
         <v>3.3</v>
@@ -41162,7 +41330,7 @@
       </c>
       <c r="Y407" t="inlineStr"/>
       <c r="Z407" t="n">
-        <v>4.358986096114766</v>
+        <v>4.355049644522281</v>
       </c>
       <c r="AA407" t="inlineStr">
         <is>
@@ -41176,10 +41344,10 @@
       </c>
       <c r="AC407" t="inlineStr"/>
       <c r="AD407" t="n">
-        <v>12.64145607533662</v>
+        <v>12.53817392432171</v>
       </c>
       <c r="AE407" t="n">
-        <v>0.2528291215067324</v>
+        <v>0.2507634784864342</v>
       </c>
     </row>
     <row r="408">
@@ -41372,13 +41540,13 @@
         <v>0</v>
       </c>
       <c r="O410" t="n">
-        <v>0.3984679281711578</v>
+        <v>0.3932410478591919</v>
       </c>
       <c r="P410" t="n">
-        <v>0.4165040552616119</v>
+        <v>0.4201231896877289</v>
       </c>
       <c r="Q410" t="n">
-        <v>0.1850280165672302</v>
+        <v>0.1866357922554016</v>
       </c>
       <c r="R410" t="n">
         <v>1</v>
@@ -41389,7 +41557,7 @@
       </c>
       <c r="U410" t="inlineStr"/>
       <c r="V410" t="n">
-        <v>0.5834959447383881</v>
+        <v>0.5798768103122711</v>
       </c>
       <c r="W410" t="inlineStr"/>
       <c r="X410" t="inlineStr">
@@ -41416,96 +41584,74 @@
     <row r="411">
       <c r="A411" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>IFm4IHT9</t>
         </is>
       </c>
       <c r="B411" s="2" t="n">
-        <v>45583.66666666666</v>
+        <v>45595.60416666666</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F411" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G411" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H411" t="n">
-        <v>4</v>
-      </c>
-      <c r="I411" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J411" t="n">
-        <v>0.5546995377503853</v>
-      </c>
-      <c r="K411" t="n">
-        <v>0.2357473035439137</v>
-      </c>
-      <c r="L411" t="n">
-        <v>0.2095531587057011</v>
-      </c>
-      <c r="M411" t="n">
-        <v>0.06045751633986929</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="inlineStr"/>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
       <c r="N411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O411" t="n">
-        <v>0.6673498749732971</v>
+        <v>0.2193145006895065</v>
       </c>
       <c r="P411" t="n">
-        <v>0.2307066023349762</v>
+        <v>0.3615515828132629</v>
       </c>
       <c r="Q411" t="n">
-        <v>0.1019435897469521</v>
+        <v>0.4191339612007141</v>
       </c>
       <c r="R411" t="n">
         <v>1</v>
       </c>
-      <c r="S411" t="n">
-        <v>0.1126503372229118</v>
-      </c>
+      <c r="S411" t="inlineStr"/>
       <c r="T411" t="n">
-        <v>1</v>
-      </c>
-      <c r="U411" t="n">
-        <v>0.1126503372229118</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U411" t="inlineStr"/>
       <c r="V411" t="n">
-        <v>0.6673498749732971</v>
-      </c>
-      <c r="W411" t="n">
-        <v>1.7</v>
-      </c>
+        <v>0.5808660387992859</v>
+      </c>
+      <c r="W411" t="inlineStr"/>
       <c r="X411" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
         </is>
       </c>
       <c r="Y411" t="inlineStr"/>
-      <c r="Z411" t="n">
-        <v>6.910764987531603</v>
-      </c>
+      <c r="Z411" t="inlineStr"/>
       <c r="AA411" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB411" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC411" t="inlineStr"/>
@@ -41515,96 +41661,74 @@
     <row r="412">
       <c r="A412" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>0b5fTYsS</t>
         </is>
       </c>
       <c r="B412" s="2" t="n">
-        <v>45584.375</v>
+        <v>45595.60416666666</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F412" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G412" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H412" t="n">
-        <v>4</v>
-      </c>
-      <c r="I412" t="n">
-        <v>7</v>
-      </c>
-      <c r="J412" t="n">
-        <v>0.6292134831460674</v>
-      </c>
-      <c r="K412" t="n">
-        <v>0.2359550561797753</v>
-      </c>
-      <c r="L412" t="n">
-        <v>0.1348314606741573</v>
-      </c>
-      <c r="M412" t="n">
-        <v>0.05952380952380953</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr"/>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
       <c r="N412" t="n">
         <v>1</v>
       </c>
       <c r="O412" t="n">
-        <v>0.5714911818504333</v>
+        <v>0.4081339836120605</v>
       </c>
       <c r="P412" t="n">
-        <v>0.267119973897934</v>
+        <v>0.3379647433757782</v>
       </c>
       <c r="Q412" t="n">
-        <v>0.1613888591527939</v>
+        <v>0.2539012432098389</v>
       </c>
       <c r="R412" t="n">
         <v>1</v>
       </c>
-      <c r="S412" t="n">
-        <v>-0.05772230129563405</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
       <c r="T412" t="n">
-        <v>1</v>
-      </c>
-      <c r="U412" t="n">
-        <v>-0.05772230129563405</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U412" t="inlineStr"/>
       <c r="V412" t="n">
-        <v>0.5714911818504333</v>
-      </c>
-      <c r="W412" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0.5918660163879395</v>
+      </c>
+      <c r="W412" t="inlineStr"/>
       <c r="X412" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
         </is>
       </c>
       <c r="Y412" t="inlineStr"/>
-      <c r="Z412" t="n">
-        <v>5.918096935843527</v>
-      </c>
+      <c r="Z412" t="inlineStr"/>
       <c r="AA412" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB412" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC412" t="inlineStr"/>
@@ -41614,96 +41738,74 @@
     <row r="413">
       <c r="A413" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>Y96v2dqT</t>
         </is>
       </c>
       <c r="B413" s="2" t="n">
-        <v>45584.46875</v>
+        <v>45595.69791666666</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F413" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G413" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H413" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I413" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J413" t="n">
-        <v>0.3617021276595744</v>
-      </c>
-      <c r="K413" t="n">
-        <v>0.2765957446808511</v>
-      </c>
-      <c r="L413" t="n">
-        <v>0.3617021276595744</v>
-      </c>
-      <c r="M413" t="n">
-        <v>0.06334841628959276</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O413" t="n">
-        <v>0.2678379118442535</v>
+        <v>0.4542271494865417</v>
       </c>
       <c r="P413" t="n">
-        <v>0.332794189453125</v>
+        <v>0.3409821391105652</v>
       </c>
       <c r="Q413" t="n">
-        <v>0.3993678987026215</v>
+        <v>0.2047907114028931</v>
       </c>
       <c r="R413" t="n">
         <v>1</v>
       </c>
-      <c r="S413" t="n">
-        <v>0.03766577104304702</v>
-      </c>
+      <c r="S413" t="inlineStr"/>
       <c r="T413" t="n">
-        <v>2</v>
-      </c>
-      <c r="U413" t="n">
-        <v>0.03766577104304702</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U413" t="inlineStr"/>
       <c r="V413" t="n">
-        <v>0.3993678987026215</v>
-      </c>
-      <c r="W413" t="n">
-        <v>2.6</v>
-      </c>
+        <v>0.5457728505134583</v>
+      </c>
+      <c r="W413" t="inlineStr"/>
       <c r="X413" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
         </is>
       </c>
       <c r="Y413" t="inlineStr"/>
-      <c r="Z413" t="n">
-        <v>4.135668252891451</v>
-      </c>
+      <c r="Z413" t="inlineStr"/>
       <c r="AA413" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB413" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC413" t="inlineStr"/>
@@ -41713,96 +41815,74 @@
     <row r="414">
       <c r="A414" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>rcXrBZLq</t>
         </is>
       </c>
       <c r="B414" s="2" t="n">
-        <v>45584.5625</v>
+        <v>45595.69791666666</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F414" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G414" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H414" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I414" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J414" t="n">
-        <v>0.3938223938223938</v>
-      </c>
-      <c r="K414" t="n">
-        <v>0.277992277992278</v>
-      </c>
-      <c r="L414" t="n">
-        <v>0.3281853281853282</v>
-      </c>
-      <c r="M414" t="n">
-        <v>0.05800653594771243</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr"/>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" t="n">
         <v>1</v>
       </c>
       <c r="O414" t="n">
-        <v>0.4895497262477875</v>
+        <v>0.5638784170150757</v>
       </c>
       <c r="P414" t="n">
-        <v>0.3255585432052612</v>
+        <v>0.2269687056541443</v>
       </c>
       <c r="Q414" t="n">
-        <v>0.1848916709423065</v>
+        <v>0.2091528922319412</v>
       </c>
       <c r="R414" t="n">
         <v>1</v>
       </c>
-      <c r="S414" t="n">
-        <v>0.09572733242539366</v>
-      </c>
+      <c r="S414" t="inlineStr"/>
       <c r="T414" t="n">
-        <v>1</v>
-      </c>
-      <c r="U414" t="n">
-        <v>0.09572733242539366</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U414" t="inlineStr"/>
       <c r="V414" t="n">
-        <v>0.4895497262477875</v>
-      </c>
-      <c r="W414" t="n">
-        <v>2.4</v>
-      </c>
+        <v>0.4361215829849243</v>
+      </c>
+      <c r="W414" t="inlineStr"/>
       <c r="X414" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
         </is>
       </c>
       <c r="Y414" t="inlineStr"/>
-      <c r="Z414" t="n">
-        <v>5.069549324399381</v>
-      </c>
+      <c r="Z414" t="inlineStr"/>
       <c r="AA414" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB414" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC414" t="inlineStr"/>
@@ -41812,96 +41892,74 @@
     <row r="415">
       <c r="A415" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>EssDGebM</t>
         </is>
       </c>
       <c r="B415" s="2" t="n">
-        <v>45584.66666666666</v>
+        <v>45596.60416666666</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F415" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G415" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="H415" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I415" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="J415" t="n">
-        <v>0.2177314211212516</v>
-      </c>
-      <c r="K415" t="n">
-        <v>0.2177314211212516</v>
-      </c>
-      <c r="L415" t="n">
-        <v>0.5645371577574968</v>
-      </c>
-      <c r="M415" t="n">
-        <v>0.06069615964376096</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr"/>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O415" t="n">
-        <v>0.1781003326177597</v>
+        <v>0.2376536726951599</v>
       </c>
       <c r="P415" t="n">
-        <v>0.3033130168914795</v>
+        <v>0.4278645217418671</v>
       </c>
       <c r="Q415" t="n">
-        <v>0.5185866355895996</v>
+        <v>0.3344818353652954</v>
       </c>
       <c r="R415" t="n">
         <v>1</v>
       </c>
-      <c r="S415" t="n">
-        <v>-0.04595052216789719</v>
-      </c>
+      <c r="S415" t="inlineStr"/>
       <c r="T415" t="n">
-        <v>2</v>
-      </c>
-      <c r="U415" t="n">
-        <v>-0.04595052216789719</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U415" t="inlineStr"/>
       <c r="V415" t="n">
-        <v>0.5185866355895996</v>
-      </c>
-      <c r="W415" t="n">
-        <v>1.67</v>
-      </c>
+        <v>0.5721354782581329</v>
+      </c>
+      <c r="W415" t="inlineStr"/>
       <c r="X415" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
         </is>
       </c>
       <c r="Y415" t="inlineStr"/>
-      <c r="Z415" t="n">
-        <v>5.370242055380344</v>
-      </c>
+      <c r="Z415" t="inlineStr"/>
       <c r="AA415" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB415" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC415" t="inlineStr"/>
@@ -41911,20 +41969,20 @@
     <row r="416">
       <c r="A416" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B416" s="2" t="n">
-        <v>45585.375</v>
+        <v>45583.66666666666</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E416" t="n">
@@ -41934,55 +41992,55 @@
         <v>1481</v>
       </c>
       <c r="G416" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H416" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="I416" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="J416" t="n">
-        <v>0.472913616398243</v>
+        <v>0.5689677299756157</v>
       </c>
       <c r="K416" t="n">
-        <v>0.2781844802342606</v>
+        <v>0.2500463444892837</v>
       </c>
       <c r="L416" t="n">
-        <v>0.2489019033674963</v>
+        <v>0.1809859255351006</v>
       </c>
       <c r="M416" t="n">
-        <v>0.05727554179566563</v>
+        <v>0.0524364804226134</v>
       </c>
       <c r="N416" t="n">
         <v>1</v>
       </c>
       <c r="O416" t="n">
-        <v>0.3904880583286285</v>
+        <v>0.669661283493042</v>
       </c>
       <c r="P416" t="n">
-        <v>0.358215719461441</v>
+        <v>0.2293326407670975</v>
       </c>
       <c r="Q416" t="n">
-        <v>0.2512962818145752</v>
+        <v>0.1010061129927635</v>
       </c>
       <c r="R416" t="n">
         <v>1</v>
       </c>
       <c r="S416" t="n">
-        <v>-0.08242555806961449</v>
+        <v>0.1006935535174263</v>
       </c>
       <c r="T416" t="n">
         <v>1</v>
       </c>
       <c r="U416" t="n">
-        <v>-0.08242555806961449</v>
+        <v>0.1006935535174263</v>
       </c>
       <c r="V416" t="n">
-        <v>0.3904880583286285</v>
+        <v>0.669661283493042</v>
       </c>
       <c r="W416" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="X416" t="inlineStr">
         <is>
@@ -41991,7 +42049,7 @@
       </c>
       <c r="Y416" t="inlineStr"/>
       <c r="Z416" t="n">
-        <v>4.043712755104155</v>
+        <v>6.934700859357118</v>
       </c>
       <c r="AA416" t="inlineStr">
         <is>
@@ -42010,20 +42068,20 @@
     <row r="417">
       <c r="A417" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B417" s="2" t="n">
-        <v>45585.46875</v>
+        <v>45584.375</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E417" t="n">
@@ -42033,55 +42091,55 @@
         <v>1481</v>
       </c>
       <c r="G417" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="H417" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="I417" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J417" t="n">
-        <v>0.7077140835102618</v>
+        <v>0.6417212738428149</v>
       </c>
       <c r="K417" t="n">
-        <v>0.1981599433828733</v>
+        <v>0.2316457281188698</v>
       </c>
       <c r="L417" t="n">
-        <v>0.09412597310686482</v>
+        <v>0.1266329980383155</v>
       </c>
       <c r="M417" t="n">
-        <v>0.06240601503759402</v>
+        <v>0.0529114480333992</v>
       </c>
       <c r="N417" t="n">
         <v>1</v>
       </c>
       <c r="O417" t="n">
-        <v>0.726938784122467</v>
+        <v>0.5714911818504333</v>
       </c>
       <c r="P417" t="n">
-        <v>0.1874948590993881</v>
+        <v>0.267119973897934</v>
       </c>
       <c r="Q417" t="n">
-        <v>0.08556638658046722</v>
+        <v>0.1613888591527939</v>
       </c>
       <c r="R417" t="n">
         <v>1</v>
       </c>
       <c r="S417" t="n">
-        <v>0.01922470061220527</v>
+        <v>-0.0702300919923815</v>
       </c>
       <c r="T417" t="n">
         <v>1</v>
       </c>
       <c r="U417" t="n">
-        <v>0.01922470061220527</v>
+        <v>-0.0702300919923815</v>
       </c>
       <c r="V417" t="n">
-        <v>0.726938784122467</v>
+        <v>0.5714911818504333</v>
       </c>
       <c r="W417" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="X417" t="inlineStr">
         <is>
@@ -42090,7 +42148,7 @@
       </c>
       <c r="Y417" t="inlineStr"/>
       <c r="Z417" t="n">
-        <v>7.527840021837651</v>
+        <v>5.918096935843527</v>
       </c>
       <c r="AA417" t="inlineStr">
         <is>
@@ -42102,29 +42160,27 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC417" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC417" t="inlineStr"/>
       <c r="AD417" t="inlineStr"/>
       <c r="AE417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B418" s="2" t="n">
-        <v>45585.5625</v>
+        <v>45584.46875</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E418" t="n">
@@ -42134,55 +42190,55 @@
         <v>1481</v>
       </c>
       <c r="G418" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="H418" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="I418" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J418" t="n">
-        <v>0.5370967741935485</v>
+        <v>0.3617021276595744</v>
       </c>
       <c r="K418" t="n">
-        <v>0.2540322580645161</v>
+        <v>0.2765957446808511</v>
       </c>
       <c r="L418" t="n">
-        <v>0.2088709677419355</v>
+        <v>0.3617021276595744</v>
       </c>
       <c r="M418" t="n">
-        <v>0.06392106392106367</v>
+        <v>0.06334841628959276</v>
       </c>
       <c r="N418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O418" t="n">
-        <v>0.5907658934593201</v>
+        <v>0.2668277025222778</v>
       </c>
       <c r="P418" t="n">
-        <v>0.2744113206863403</v>
+        <v>0.3323536515235901</v>
       </c>
       <c r="Q418" t="n">
-        <v>0.1348228305578232</v>
+        <v>0.4008186161518097</v>
       </c>
       <c r="R418" t="n">
         <v>1</v>
       </c>
       <c r="S418" t="n">
-        <v>0.05366911926577156</v>
+        <v>0.03911648849223526</v>
       </c>
       <c r="T418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U418" t="n">
-        <v>0.05366911926577156</v>
+        <v>0.03911648849223526</v>
       </c>
       <c r="V418" t="n">
-        <v>0.5907658934593201</v>
+        <v>0.4008186161518097</v>
       </c>
       <c r="W418" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="X418" t="inlineStr">
         <is>
@@ -42191,7 +42247,7 @@
       </c>
       <c r="Y418" t="inlineStr"/>
       <c r="Z418" t="n">
-        <v>6.11769688652426</v>
+        <v>4.15069120821163</v>
       </c>
       <c r="AA418" t="inlineStr">
         <is>
@@ -42210,20 +42266,20 @@
     <row r="419">
       <c r="A419" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B419" s="2" t="n">
-        <v>45585.66666666666</v>
+        <v>45584.5625</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E419" t="n">
@@ -42233,55 +42289,55 @@
         <v>1481</v>
       </c>
       <c r="G419" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="H419" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="I419" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="J419" t="n">
-        <v>0.7250755287009064</v>
+        <v>0.3947157726180945</v>
       </c>
       <c r="K419" t="n">
-        <v>0.1570996978851964</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="L419" t="n">
-        <v>0.1178247734138973</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="M419" t="n">
-        <v>0.06089743589743568</v>
+        <v>0.05561189993238669</v>
       </c>
       <c r="N419" t="n">
         <v>1</v>
       </c>
       <c r="O419" t="n">
-        <v>0.7515518665313721</v>
+        <v>0.4895497262477875</v>
       </c>
       <c r="P419" t="n">
-        <v>0.170487567782402</v>
+        <v>0.3255585432052612</v>
       </c>
       <c r="Q419" t="n">
-        <v>0.07796047627925873</v>
+        <v>0.1848916709423065</v>
       </c>
       <c r="R419" t="n">
         <v>1</v>
       </c>
       <c r="S419" t="n">
-        <v>0.02647633783046566</v>
+        <v>0.09483395362969294</v>
       </c>
       <c r="T419" t="n">
         <v>1</v>
       </c>
       <c r="U419" t="n">
-        <v>0.02647633783046566</v>
+        <v>0.09483395362969294</v>
       </c>
       <c r="V419" t="n">
-        <v>0.7515518665313721</v>
+        <v>0.4895497262477875</v>
       </c>
       <c r="W419" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="X419" t="inlineStr">
         <is>
@@ -42290,7 +42346,7 @@
       </c>
       <c r="Y419" t="inlineStr"/>
       <c r="Z419" t="n">
-        <v>7.782721658180952</v>
+        <v>5.069549324399381</v>
       </c>
       <c r="AA419" t="inlineStr">
         <is>
@@ -42309,20 +42365,20 @@
     <row r="420">
       <c r="A420" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B420" s="2" t="n">
-        <v>45586.66666666666</v>
+        <v>45584.66666666666</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E420" t="n">
@@ -42332,55 +42388,55 @@
         <v>1481</v>
       </c>
       <c r="G420" t="n">
-        <v>1.75</v>
+        <v>4.5</v>
       </c>
       <c r="H420" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I420" t="n">
-        <v>4.75</v>
+        <v>1.6</v>
       </c>
       <c r="J420" t="n">
-        <v>0.5392195506503745</v>
+        <v>0.2077922077922078</v>
       </c>
       <c r="K420" t="n">
-        <v>0.2621206148994876</v>
+        <v>0.2077922077922078</v>
       </c>
       <c r="L420" t="n">
-        <v>0.198659834450138</v>
+        <v>0.5844155844155844</v>
       </c>
       <c r="M420" t="n">
-        <v>0.05973266499582275</v>
+        <v>0.06944444444444442</v>
       </c>
       <c r="N420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O420" t="n">
-        <v>0.4497665762901306</v>
+        <v>0.178535208106041</v>
       </c>
       <c r="P420" t="n">
-        <v>0.3399279117584229</v>
+        <v>0.3037036061286926</v>
       </c>
       <c r="Q420" t="n">
-        <v>0.2103055566549301</v>
+        <v>0.5177611708641052</v>
       </c>
       <c r="R420" t="n">
         <v>1</v>
       </c>
       <c r="S420" t="n">
-        <v>-0.08945297436024391</v>
+        <v>-0.06665441355147916</v>
       </c>
       <c r="T420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U420" t="n">
-        <v>-0.08945297436024391</v>
+        <v>-0.06665441355147916</v>
       </c>
       <c r="V420" t="n">
-        <v>0.4497665762901306</v>
+        <v>0.5177611708641052</v>
       </c>
       <c r="W420" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="X420" t="inlineStr">
         <is>
@@ -42389,7 +42445,7 @@
       </c>
       <c r="Y420" t="inlineStr"/>
       <c r="Z420" t="n">
-        <v>4.657573522602617</v>
+        <v>5.361693926524222</v>
       </c>
       <c r="AA420" t="inlineStr">
         <is>
@@ -42408,20 +42464,20 @@
     <row r="421">
       <c r="A421" s="1" t="inlineStr">
         <is>
-          <t>vymauDyP</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B421" s="2" t="n">
-        <v>45590.66666666666</v>
+        <v>45585.375</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E421" t="n">
@@ -42431,55 +42487,55 @@
         <v>1481</v>
       </c>
       <c r="G421" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="H421" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I421" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="J421" t="n">
-        <v>0.3480113636363636</v>
+        <v>0.4745960470954284</v>
       </c>
       <c r="K421" t="n">
-        <v>0.2684659090909091</v>
+        <v>0.3061909981260828</v>
       </c>
       <c r="L421" t="n">
-        <v>0.3835227272727272</v>
+        <v>0.2192129547784888</v>
       </c>
       <c r="M421" t="n">
-        <v>0.06424792139077851</v>
+        <v>0.0535275273783804</v>
       </c>
       <c r="N421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O421" t="n">
-        <v>0.3013800978660583</v>
+        <v>0.3904880583286285</v>
       </c>
       <c r="P421" t="n">
-        <v>0.3700269460678101</v>
+        <v>0.358215719461441</v>
       </c>
       <c r="Q421" t="n">
-        <v>0.3285929262638092</v>
+        <v>0.2512962818145752</v>
       </c>
       <c r="R421" t="n">
         <v>1</v>
       </c>
       <c r="S421" t="n">
-        <v>0.101561036976901</v>
+        <v>-0.08410798876679981</v>
       </c>
       <c r="T421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U421" t="n">
-        <v>0.101561036976901</v>
+        <v>-0.08410798876679981</v>
       </c>
       <c r="V421" t="n">
-        <v>0.3700269460678101</v>
+        <v>0.3904880583286285</v>
       </c>
       <c r="W421" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="X421" t="inlineStr">
         <is>
@@ -42488,7 +42544,7 @@
       </c>
       <c r="Y421" t="inlineStr"/>
       <c r="Z421" t="n">
-        <v>3.831826990948319</v>
+        <v>4.043712755104155</v>
       </c>
       <c r="AA421" t="inlineStr">
         <is>
@@ -42507,20 +42563,20 @@
     <row r="422">
       <c r="A422" s="1" t="inlineStr">
         <is>
-          <t>x88gL4RQ</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B422" s="2" t="n">
-        <v>45591.375</v>
+        <v>45585.46875</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E422" t="n">
@@ -42530,55 +42586,55 @@
         <v>1481</v>
       </c>
       <c r="G422" t="n">
-        <v>3.6</v>
+        <v>1.33</v>
       </c>
       <c r="H422" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="I422" t="n">
-        <v>1.95</v>
+        <v>10</v>
       </c>
       <c r="J422" t="n">
-        <v>0.2627324171382376</v>
+        <v>0.7077140835102618</v>
       </c>
       <c r="K422" t="n">
-        <v>0.2522231204527081</v>
+        <v>0.1981599433828733</v>
       </c>
       <c r="L422" t="n">
-        <v>0.4850444624090541</v>
+        <v>0.09412597310686482</v>
       </c>
       <c r="M422" t="n">
-        <v>0.05726495726495751</v>
+        <v>0.06240601503759402</v>
       </c>
       <c r="N422" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O422" t="n">
-        <v>0.2713927626609802</v>
+        <v>0.7285870909690857</v>
       </c>
       <c r="P422" t="n">
-        <v>0.3275697231292725</v>
+        <v>0.1864692121744156</v>
       </c>
       <c r="Q422" t="n">
-        <v>0.4010374546051025</v>
+        <v>0.08494370430707932</v>
       </c>
       <c r="R422" t="n">
         <v>1</v>
       </c>
       <c r="S422" t="n">
-        <v>-0.08400700780395159</v>
+        <v>0.02087300745882392</v>
       </c>
       <c r="T422" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U422" t="n">
-        <v>-0.08400700780395159</v>
+        <v>0.02087300745882392</v>
       </c>
       <c r="V422" t="n">
-        <v>0.4010374546051025</v>
+        <v>0.7285870909690857</v>
       </c>
       <c r="W422" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="X422" t="inlineStr">
         <is>
@@ -42587,7 +42643,7 @@
       </c>
       <c r="Y422" t="inlineStr"/>
       <c r="Z422" t="n">
-        <v>4.152957397474051</v>
+        <v>7.54490912107855</v>
       </c>
       <c r="AA422" t="inlineStr">
         <is>
@@ -42599,27 +42655,29 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC422" t="inlineStr"/>
+      <c r="AC422" t="n">
+        <v>1</v>
+      </c>
       <c r="AD422" t="inlineStr"/>
       <c r="AE422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="1" t="inlineStr">
         <is>
-          <t>dhkQFrkl</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B423" s="2" t="n">
-        <v>45591.46875</v>
+        <v>45585.5625</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E423" t="n">
@@ -42629,55 +42687,55 @@
         <v>1481</v>
       </c>
       <c r="G423" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="H423" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="I423" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J423" t="n">
-        <v>0.4365343242714649</v>
+        <v>0.5370967741935485</v>
       </c>
       <c r="K423" t="n">
-        <v>0.3027576765108547</v>
+        <v>0.2540322580645161</v>
       </c>
       <c r="L423" t="n">
-        <v>0.2607079992176805</v>
+        <v>0.2088709677419355</v>
       </c>
       <c r="M423" t="n">
-        <v>0.06547470200883554</v>
+        <v>0.06392106392106367</v>
       </c>
       <c r="N423" t="n">
         <v>1</v>
       </c>
       <c r="O423" t="n">
-        <v>0.5210584402084351</v>
+        <v>0.5907658934593201</v>
       </c>
       <c r="P423" t="n">
-        <v>0.2715503573417664</v>
+        <v>0.2744113206863403</v>
       </c>
       <c r="Q423" t="n">
-        <v>0.207391157746315</v>
+        <v>0.1348228305578232</v>
       </c>
       <c r="R423" t="n">
         <v>1</v>
       </c>
       <c r="S423" t="n">
-        <v>0.08452411593697018</v>
+        <v>0.05366911926577156</v>
       </c>
       <c r="T423" t="n">
         <v>1</v>
       </c>
       <c r="U423" t="n">
-        <v>0.08452411593697018</v>
+        <v>0.05366911926577156</v>
       </c>
       <c r="V423" t="n">
-        <v>0.5210584402084351</v>
+        <v>0.5907658934593201</v>
       </c>
       <c r="W423" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="X423" t="inlineStr">
         <is>
@@ -42686,7 +42744,7 @@
       </c>
       <c r="Y423" t="inlineStr"/>
       <c r="Z423" t="n">
-        <v>5.395838914623856</v>
+        <v>6.11769688652426</v>
       </c>
       <c r="AA423" t="inlineStr">
         <is>
@@ -42705,20 +42763,20 @@
     <row r="424">
       <c r="A424" s="1" t="inlineStr">
         <is>
-          <t>8Sp1FEw8</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B424" s="2" t="n">
-        <v>45591.5625</v>
+        <v>45585.66666666666</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E424" t="n">
@@ -42728,55 +42786,55 @@
         <v>1481</v>
       </c>
       <c r="G424" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="H424" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="I424" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J424" t="n">
-        <v>0.2611940298507463</v>
+        <v>0.7201565557729942</v>
       </c>
       <c r="K424" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.1628180039138943</v>
       </c>
       <c r="L424" t="n">
-        <v>0.4701492537313433</v>
+        <v>0.1170254403131116</v>
       </c>
       <c r="M424" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.06814381270902992</v>
       </c>
       <c r="N424" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O424" t="n">
-        <v>0.2521133720874786</v>
+        <v>0.7510959506034851</v>
       </c>
       <c r="P424" t="n">
-        <v>0.3590907752513885</v>
+        <v>0.1708084046840668</v>
       </c>
       <c r="Q424" t="n">
-        <v>0.3887958228588104</v>
+        <v>0.07809565961360931</v>
       </c>
       <c r="R424" t="n">
         <v>1</v>
       </c>
       <c r="S424" t="n">
-        <v>-0.08135343087253288</v>
+        <v>0.03093939483049091</v>
       </c>
       <c r="T424" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U424" t="n">
-        <v>-0.08135343087253288</v>
+        <v>0.03093939483049091</v>
       </c>
       <c r="V424" t="n">
-        <v>0.3887958228588104</v>
+        <v>0.7510959506034851</v>
       </c>
       <c r="W424" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="X424" t="inlineStr">
         <is>
@@ -42785,7 +42843,7 @@
       </c>
       <c r="Y424" t="inlineStr"/>
       <c r="Z424" t="n">
-        <v>4.026188751468212</v>
+        <v>7.778000404832661</v>
       </c>
       <c r="AA424" t="inlineStr">
         <is>
@@ -42804,20 +42862,20 @@
     <row r="425">
       <c r="A425" s="1" t="inlineStr">
         <is>
-          <t>4zlpJdvq</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B425" s="2" t="n">
-        <v>45591.66666666666</v>
+        <v>45586.66666666666</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E425" t="n">
@@ -42827,55 +42885,55 @@
         <v>1481</v>
       </c>
       <c r="G425" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H425" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I425" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="J425" t="n">
-        <v>0.54584017471928</v>
+        <v>0.5392195506503745</v>
       </c>
       <c r="K425" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.2621206148994876</v>
       </c>
       <c r="L425" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.198659834450138</v>
       </c>
       <c r="M425" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.05973266499582275</v>
       </c>
       <c r="N425" t="n">
         <v>1</v>
       </c>
       <c r="O425" t="n">
-        <v>0.5270339846611023</v>
+        <v>0.4499695599079132</v>
       </c>
       <c r="P425" t="n">
-        <v>0.2914429605007172</v>
+        <v>0.3398557603359222</v>
       </c>
       <c r="Q425" t="n">
-        <v>0.1815229505300522</v>
+        <v>0.2101746201515198</v>
       </c>
       <c r="R425" t="n">
         <v>1</v>
       </c>
       <c r="S425" t="n">
-        <v>-0.01880619005817774</v>
+        <v>-0.08924999074246132</v>
       </c>
       <c r="T425" t="n">
         <v>1</v>
       </c>
       <c r="U425" t="n">
-        <v>-0.01880619005817774</v>
+        <v>-0.08924999074246132</v>
       </c>
       <c r="V425" t="n">
-        <v>0.5270339846611023</v>
+        <v>0.4499695599079132</v>
       </c>
       <c r="W425" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X425" t="inlineStr">
         <is>
@@ -42884,7 +42942,7 @@
       </c>
       <c r="Y425" t="inlineStr"/>
       <c r="Z425" t="n">
-        <v>5.457718874347508</v>
+        <v>4.659675526560992</v>
       </c>
       <c r="AA425" t="inlineStr">
         <is>
@@ -42903,20 +42961,20 @@
     <row r="426">
       <c r="A426" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B426" s="2" t="n">
-        <v>45592.41666666666</v>
+        <v>45590.66666666666</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E426" t="n">
@@ -42926,55 +42984,55 @@
         <v>1481</v>
       </c>
       <c r="G426" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="H426" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I426" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="J426" t="n">
-        <v>0.3236326109391125</v>
+        <v>0.3411167512690355</v>
       </c>
       <c r="K426" t="n">
-        <v>0.2932920536635707</v>
+        <v>0.2680203045685279</v>
       </c>
       <c r="L426" t="n">
-        <v>0.3830753353973168</v>
+        <v>0.3908629441624366</v>
       </c>
       <c r="M426" t="n">
-        <v>0.06549085151301903</v>
+        <v>0.06601731601731609</v>
       </c>
       <c r="N426" t="n">
         <v>0</v>
       </c>
       <c r="O426" t="n">
-        <v>0.313975602388382</v>
+        <v>0.3017470240592957</v>
       </c>
       <c r="P426" t="n">
-        <v>0.3678199052810669</v>
+        <v>0.3700113892555237</v>
       </c>
       <c r="Q426" t="n">
-        <v>0.3182044327259064</v>
+        <v>0.3282416462898254</v>
       </c>
       <c r="R426" t="n">
         <v>1</v>
       </c>
       <c r="S426" t="n">
-        <v>0.0745278516174962</v>
+        <v>0.1019910846869958</v>
       </c>
       <c r="T426" t="n">
         <v>0</v>
       </c>
       <c r="U426" t="n">
-        <v>0.0745278516174962</v>
+        <v>0.1019910846869958</v>
       </c>
       <c r="V426" t="n">
-        <v>0.3678199052810669</v>
+        <v>0.3700113892555237</v>
       </c>
       <c r="W426" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="X426" t="inlineStr">
         <is>
@@ -42983,7 +43041,7 @@
       </c>
       <c r="Y426" t="inlineStr"/>
       <c r="Z426" t="n">
-        <v>3.808971902834773</v>
+        <v>3.831665891834199</v>
       </c>
       <c r="AA426" t="inlineStr">
         <is>
@@ -42995,29 +43053,27 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC426" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC426" t="inlineStr"/>
       <c r="AD426" t="inlineStr"/>
       <c r="AE426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B427" s="2" t="n">
-        <v>45592.51041666666</v>
+        <v>45591.375</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E427" t="n">
@@ -43027,55 +43083,55 @@
         <v>1481</v>
       </c>
       <c r="G427" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="H427" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="I427" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J427" t="n">
-        <v>0.4378536585365854</v>
+        <v>0.2705667276051188</v>
       </c>
       <c r="K427" t="n">
-        <v>0.2768780487804878</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="L427" t="n">
-        <v>0.2852682926829269</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="M427" t="n">
-        <v>0.06226422915889396</v>
+        <v>0.05598455598455598</v>
       </c>
       <c r="N427" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O427" t="n">
-        <v>0.5595535039901733</v>
+        <v>0.2713698446750641</v>
       </c>
       <c r="P427" t="n">
-        <v>0.2826571762561798</v>
+        <v>0.3275195956230164</v>
       </c>
       <c r="Q427" t="n">
-        <v>0.157789409160614</v>
+        <v>0.4011105298995972</v>
       </c>
       <c r="R427" t="n">
         <v>1</v>
       </c>
       <c r="S427" t="n">
-        <v>0.121699845453588</v>
+        <v>-0.07238124340936081</v>
       </c>
       <c r="T427" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U427" t="n">
-        <v>0.121699845453588</v>
+        <v>-0.07238124340936081</v>
       </c>
       <c r="V427" t="n">
-        <v>0.5595535039901733</v>
+        <v>0.4011105298995972</v>
       </c>
       <c r="W427" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="X427" t="inlineStr">
         <is>
@@ -43084,7 +43140,7 @@
       </c>
       <c r="Y427" t="inlineStr"/>
       <c r="Z427" t="n">
-        <v>5.794475894942879</v>
+        <v>4.153714131243825</v>
       </c>
       <c r="AA427" t="inlineStr">
         <is>
@@ -43103,20 +43159,20 @@
     <row r="428">
       <c r="A428" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B428" s="2" t="n">
-        <v>45592.60416666666</v>
+        <v>45591.46875</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E428" t="n">
@@ -43126,55 +43182,55 @@
         <v>1481</v>
       </c>
       <c r="G428" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="H428" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I428" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="J428" t="n">
-        <v>0.3271028037383177</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="K428" t="n">
-        <v>0.2770753161077515</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="L428" t="n">
-        <v>0.3958218801539307</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="M428" t="n">
-        <v>0.06150793650793651</v>
+        <v>0.0625</v>
       </c>
       <c r="N428" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O428" t="n">
-        <v>0.3088712990283966</v>
+        <v>0.5164309144020081</v>
       </c>
       <c r="P428" t="n">
-        <v>0.3722001910209656</v>
+        <v>0.2730623781681061</v>
       </c>
       <c r="Q428" t="n">
-        <v>0.3189284801483154</v>
+        <v>0.2105065882205963</v>
       </c>
       <c r="R428" t="n">
         <v>1</v>
       </c>
       <c r="S428" t="n">
-        <v>0.09512487491321403</v>
+        <v>0.04584267910789042</v>
       </c>
       <c r="T428" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U428" t="n">
-        <v>0.09512487491321403</v>
+        <v>0.04584267910789042</v>
       </c>
       <c r="V428" t="n">
-        <v>0.3722001910209656</v>
+        <v>0.5164309144020081</v>
       </c>
       <c r="W428" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="X428" t="inlineStr">
         <is>
@@ -43183,7 +43239,7 @@
       </c>
       <c r="Y428" t="inlineStr"/>
       <c r="Z428" t="n">
-        <v>3.854332105124294</v>
+        <v>5.347918409171998</v>
       </c>
       <c r="AA428" t="inlineStr">
         <is>
@@ -43202,20 +43258,20 @@
     <row r="429">
       <c r="A429" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B429" s="2" t="n">
-        <v>45592.70833333334</v>
+        <v>45591.5625</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E429" t="n">
@@ -43225,55 +43281,55 @@
         <v>1481</v>
       </c>
       <c r="G429" t="n">
-        <v>1.65</v>
+        <v>3.6</v>
       </c>
       <c r="H429" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I429" t="n">
-        <v>5.25</v>
+        <v>2</v>
       </c>
       <c r="J429" t="n">
-        <v>0.5681070410177671</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="K429" t="n">
-        <v>0.2533450318052204</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="L429" t="n">
-        <v>0.1785479271770125</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="M429" t="n">
-        <v>0.06680706680706683</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="N429" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O429" t="n">
-        <v>0.4601970016956329</v>
+        <v>0.2520309388637543</v>
       </c>
       <c r="P429" t="n">
-        <v>0.3222656846046448</v>
+        <v>0.3590537309646606</v>
       </c>
       <c r="Q429" t="n">
-        <v>0.2175373435020447</v>
+        <v>0.3889154195785522</v>
       </c>
       <c r="R429" t="n">
         <v>1</v>
       </c>
       <c r="S429" t="n">
-        <v>-0.1079100393221342</v>
+        <v>-0.08123383415279106</v>
       </c>
       <c r="T429" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U429" t="n">
-        <v>-0.1079100393221342</v>
+        <v>-0.08123383415279106</v>
       </c>
       <c r="V429" t="n">
-        <v>0.4601970016956329</v>
+        <v>0.3889154195785522</v>
       </c>
       <c r="W429" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="X429" t="inlineStr">
         <is>
@@ -43282,7 +43338,7 @@
       </c>
       <c r="Y429" t="inlineStr"/>
       <c r="Z429" t="n">
-        <v>4.206853063428317</v>
+        <v>4.027427239485383</v>
       </c>
       <c r="AA429" t="inlineStr">
         <is>
@@ -43301,20 +43357,20 @@
     <row r="430">
       <c r="A430" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B430" s="2" t="n">
-        <v>45593.70833333334</v>
+        <v>45591.66666666666</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E430" t="n">
@@ -43324,55 +43380,55 @@
         <v>1481</v>
       </c>
       <c r="G430" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="H430" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="I430" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J430" t="n">
-        <v>0.3156822810590631</v>
+        <v>0.4918386424102969</v>
       </c>
       <c r="K430" t="n">
-        <v>0.3054989816700611</v>
+        <v>0.2472136334220176</v>
       </c>
       <c r="L430" t="n">
-        <v>0.3788187372708758</v>
+        <v>0.2609477241676853</v>
       </c>
       <c r="M430" t="n">
-        <v>0.05591397849462365</v>
+        <v>0.06449588193870381</v>
       </c>
       <c r="N430" t="n">
         <v>1</v>
       </c>
       <c r="O430" t="n">
-        <v>0.3670017123222351</v>
+        <v>0.5266638994216919</v>
       </c>
       <c r="P430" t="n">
-        <v>0.3658300042152405</v>
+        <v>0.291552871465683</v>
       </c>
       <c r="Q430" t="n">
-        <v>0.2671682834625244</v>
+        <v>0.1817832738161087</v>
       </c>
       <c r="R430" t="n">
         <v>1</v>
       </c>
       <c r="S430" t="n">
-        <v>0.05131943126317201</v>
+        <v>0.03482525701139499</v>
       </c>
       <c r="T430" t="n">
         <v>1</v>
       </c>
       <c r="U430" t="n">
-        <v>0.05131943126317201</v>
+        <v>0.03482525701139499</v>
       </c>
       <c r="V430" t="n">
-        <v>0.3670017123222351</v>
+        <v>0.5266638994216919</v>
       </c>
       <c r="W430" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="X430" t="inlineStr">
         <is>
@@ -43381,7 +43437,7 @@
       </c>
       <c r="Y430" t="inlineStr"/>
       <c r="Z430" t="n">
-        <v>3.800499077012837</v>
+        <v>5.45388644369781</v>
       </c>
       <c r="AA430" t="inlineStr">
         <is>
@@ -43396,6 +43452,503 @@
       <c r="AC430" t="inlineStr"/>
       <c r="AD430" t="inlineStr"/>
       <c r="AE430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="n">
+        <v>45592.41666666666</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>148</v>
+      </c>
+      <c r="F431" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G431" t="n">
+        <v>3</v>
+      </c>
+      <c r="H431" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I431" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J431" t="n">
+        <v>0.3162565550625252</v>
+      </c>
+      <c r="K431" t="n">
+        <v>0.2964905203711174</v>
+      </c>
+      <c r="L431" t="n">
+        <v>0.3872529245663574</v>
+      </c>
+      <c r="M431" t="n">
+        <v>0.05399659863945572</v>
+      </c>
+      <c r="N431" t="n">
+        <v>0</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0.3127180337905884</v>
+      </c>
+      <c r="P431" t="n">
+        <v>0.3681450188159943</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>0.3191368877887726</v>
+      </c>
+      <c r="R431" t="n">
+        <v>1</v>
+      </c>
+      <c r="S431" t="n">
+        <v>0.07165449844487687</v>
+      </c>
+      <c r="T431" t="n">
+        <v>0</v>
+      </c>
+      <c r="U431" t="n">
+        <v>0.07165449844487687</v>
+      </c>
+      <c r="V431" t="n">
+        <v>0.3681450188159943</v>
+      </c>
+      <c r="W431" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X431" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y431" t="inlineStr"/>
+      <c r="Z431" t="n">
+        <v>3.812338627424687</v>
+      </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB431" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC431" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD431" t="inlineStr"/>
+      <c r="AE431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="n">
+        <v>45592.51041666666</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>148</v>
+      </c>
+      <c r="F432" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G432" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H432" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I432" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J432" t="n">
+        <v>0.415347137637028</v>
+      </c>
+      <c r="K432" t="n">
+        <v>0.2831912302070646</v>
+      </c>
+      <c r="L432" t="n">
+        <v>0.3014616321559074</v>
+      </c>
+      <c r="M432" t="n">
+        <v>0.07005539263603766</v>
+      </c>
+      <c r="N432" t="n">
+        <v>1</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0.5595623254776001</v>
+      </c>
+      <c r="P432" t="n">
+        <v>0.282652735710144</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>0.1577849239110947</v>
+      </c>
+      <c r="R432" t="n">
+        <v>1</v>
+      </c>
+      <c r="S432" t="n">
+        <v>0.1442151878405721</v>
+      </c>
+      <c r="T432" t="n">
+        <v>1</v>
+      </c>
+      <c r="U432" t="n">
+        <v>0.1442151878405721</v>
+      </c>
+      <c r="V432" t="n">
+        <v>0.5595623254776001</v>
+      </c>
+      <c r="W432" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y432" t="inlineStr"/>
+      <c r="Z432" t="n">
+        <v>5.79456724616468</v>
+      </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB432" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC432" t="inlineStr"/>
+      <c r="AD432" t="inlineStr"/>
+      <c r="AE432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="n">
+        <v>45592.60416666666</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>148</v>
+      </c>
+      <c r="F433" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G433" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H433" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I433" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J433" t="n">
+        <v>0.3211498973305955</v>
+      </c>
+      <c r="K433" t="n">
+        <v>0.2739219712525667</v>
+      </c>
+      <c r="L433" t="n">
+        <v>0.4049281314168378</v>
+      </c>
+      <c r="M433" t="n">
+        <v>0.0737278419613725</v>
+      </c>
+      <c r="N433" t="n">
+        <v>0</v>
+      </c>
+      <c r="O433" t="n">
+        <v>0.3088712990283966</v>
+      </c>
+      <c r="P433" t="n">
+        <v>0.3722001910209656</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>0.3189284801483154</v>
+      </c>
+      <c r="R433" t="n">
+        <v>1</v>
+      </c>
+      <c r="S433" t="n">
+        <v>0.0982782197683989</v>
+      </c>
+      <c r="T433" t="n">
+        <v>0</v>
+      </c>
+      <c r="U433" t="n">
+        <v>0.0982782197683989</v>
+      </c>
+      <c r="V433" t="n">
+        <v>0.3722001910209656</v>
+      </c>
+      <c r="W433" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y433" t="inlineStr"/>
+      <c r="Z433" t="n">
+        <v>3.854332105124294</v>
+      </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB433" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC433" t="inlineStr"/>
+      <c r="AD433" t="inlineStr"/>
+      <c r="AE433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="n">
+        <v>45592.70833333334</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>148</v>
+      </c>
+      <c r="F434" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G434" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H434" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I434" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J434" t="n">
+        <v>0.5223880597014926</v>
+      </c>
+      <c r="K434" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="L434" t="n">
+        <v>0.208955223880597</v>
+      </c>
+      <c r="M434" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="N434" t="n">
+        <v>1</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0.4631039500236511</v>
+      </c>
+      <c r="P434" t="n">
+        <v>0.3212946355342865</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>0.2156014740467072</v>
+      </c>
+      <c r="R434" t="n">
+        <v>1</v>
+      </c>
+      <c r="S434" t="n">
+        <v>-0.05928410967784148</v>
+      </c>
+      <c r="T434" t="n">
+        <v>1</v>
+      </c>
+      <c r="U434" t="n">
+        <v>-0.05928410967784148</v>
+      </c>
+      <c r="V434" t="n">
+        <v>0.4631039500236511</v>
+      </c>
+      <c r="W434" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y434" t="inlineStr"/>
+      <c r="Z434" t="n">
+        <v>4.79568916310817</v>
+      </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB434" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC434" t="inlineStr"/>
+      <c r="AD434" t="inlineStr"/>
+      <c r="AE434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="n">
+        <v>45593.70833333334</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>148</v>
+      </c>
+      <c r="F435" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G435" t="n">
+        <v>3</v>
+      </c>
+      <c r="H435" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I435" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J435" t="n">
+        <v>0.3156822810590631</v>
+      </c>
+      <c r="K435" t="n">
+        <v>0.3054989816700611</v>
+      </c>
+      <c r="L435" t="n">
+        <v>0.3788187372708758</v>
+      </c>
+      <c r="M435" t="n">
+        <v>0.05591397849462365</v>
+      </c>
+      <c r="N435" t="n">
+        <v>1</v>
+      </c>
+      <c r="O435" t="n">
+        <v>0.3670017123222351</v>
+      </c>
+      <c r="P435" t="n">
+        <v>0.3658300042152405</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>0.2671682834625244</v>
+      </c>
+      <c r="R435" t="n">
+        <v>1</v>
+      </c>
+      <c r="S435" t="n">
+        <v>0.05131943126317201</v>
+      </c>
+      <c r="T435" t="n">
+        <v>1</v>
+      </c>
+      <c r="U435" t="n">
+        <v>0.05131943126317201</v>
+      </c>
+      <c r="V435" t="n">
+        <v>0.3670017123222351</v>
+      </c>
+      <c r="W435" t="n">
+        <v>3</v>
+      </c>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y435" t="inlineStr"/>
+      <c r="Z435" t="n">
+        <v>3.800499077012837</v>
+      </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB435" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC435" t="inlineStr"/>
+      <c r="AD435" t="inlineStr"/>
+      <c r="AE435" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE435"/>
+  <dimension ref="A1:AE437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33620,25 +33620,25 @@
         <v>481</v>
       </c>
       <c r="G332" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="H332" t="n">
         <v>5</v>
       </c>
       <c r="I332" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="J332" t="n">
-        <v>0.6406685236768802</v>
+        <v>0.6389405204460966</v>
       </c>
       <c r="K332" t="n">
-        <v>0.1922005571030641</v>
+        <v>0.1891263940520446</v>
       </c>
       <c r="L332" t="n">
-        <v>0.1671309192200557</v>
+        <v>0.1719330855018587</v>
       </c>
       <c r="M332" t="n">
-        <v>0.04057971014492745</v>
+        <v>0.05749385749385749</v>
       </c>
       <c r="N332" t="n">
         <v>1</v>
@@ -33656,19 +33656,19 @@
         <v>1</v>
       </c>
       <c r="S332" t="n">
-        <v>-0.1776978198366245</v>
+        <v>-0.1759698166058409</v>
       </c>
       <c r="T332" t="n">
         <v>1</v>
       </c>
       <c r="U332" t="n">
-        <v>-0.1776978198366245</v>
+        <v>-0.1759698166058409</v>
       </c>
       <c r="V332" t="n">
         <v>0.4629707038402557</v>
       </c>
       <c r="W332" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X332" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
       </c>
       <c r="Y332" t="inlineStr"/>
       <c r="Z332" t="n">
-        <v>4.616279480864103</v>
+        <v>4.626940375239582</v>
       </c>
       <c r="AA332" t="inlineStr">
         <is>
@@ -33740,34 +33740,34 @@
         <v>0.05102040816326525</v>
       </c>
       <c r="N333" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O333" t="n">
-        <v>0.2126755714416504</v>
+        <v>0.2106043696403503</v>
       </c>
       <c r="P333" t="n">
-        <v>0.4157065749168396</v>
+        <v>0.3789964616298676</v>
       </c>
       <c r="Q333" t="n">
-        <v>0.37161785364151</v>
+        <v>0.4103991985321045</v>
       </c>
       <c r="R333" t="n">
         <v>1</v>
       </c>
       <c r="S333" t="n">
-        <v>0.1438619147226649</v>
+        <v>0.07059337328938603</v>
       </c>
       <c r="T333" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U333" t="n">
-        <v>0.1438619147226649</v>
+        <v>0.07059337328938603</v>
       </c>
       <c r="V333" t="n">
-        <v>0.4157065749168396</v>
+        <v>0.4103991985321045</v>
       </c>
       <c r="W333" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="X333" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
       </c>
       <c r="Y333" t="inlineStr"/>
       <c r="Z333" t="n">
-        <v>5.12939305601984</v>
+        <v>5.063905471227634</v>
       </c>
       <c r="AA333" t="inlineStr">
         <is>
@@ -33842,28 +33842,28 @@
         <v>1</v>
       </c>
       <c r="O334" t="n">
-        <v>0.3598228693008423</v>
+        <v>0.3562606275081635</v>
       </c>
       <c r="P334" t="n">
-        <v>0.34445720911026</v>
+        <v>0.3404795527458191</v>
       </c>
       <c r="Q334" t="n">
-        <v>0.2957199215888977</v>
+        <v>0.3032599091529846</v>
       </c>
       <c r="R334" t="n">
         <v>1</v>
       </c>
       <c r="S334" t="n">
-        <v>-0.03586058393656782</v>
+        <v>-0.03942282572924666</v>
       </c>
       <c r="T334" t="n">
         <v>1</v>
       </c>
       <c r="U334" t="n">
-        <v>-0.03586058393656782</v>
+        <v>-0.03942282572924666</v>
       </c>
       <c r="V334" t="n">
-        <v>0.3598228693008423</v>
+        <v>0.3562606275081635</v>
       </c>
       <c r="W334" t="n">
         <v>2.4</v>
@@ -33875,7 +33875,7 @@
       </c>
       <c r="Y334" t="inlineStr"/>
       <c r="Z334" t="n">
-        <v>4.439845406722504</v>
+        <v>4.395890994120572</v>
       </c>
       <c r="AA334" t="inlineStr">
         <is>
@@ -33941,28 +33941,28 @@
         <v>1</v>
       </c>
       <c r="O335" t="n">
-        <v>0.531466007232666</v>
+        <v>0.5347434282302856</v>
       </c>
       <c r="P335" t="n">
-        <v>0.3264229893684387</v>
+        <v>0.3243873119354248</v>
       </c>
       <c r="Q335" t="n">
-        <v>0.1421109735965729</v>
+        <v>0.1408692300319672</v>
       </c>
       <c r="R335" t="n">
         <v>1</v>
       </c>
       <c r="S335" t="n">
-        <v>-0.02953132135148373</v>
+        <v>-0.0262539003538641</v>
       </c>
       <c r="T335" t="n">
         <v>1</v>
       </c>
       <c r="U335" t="n">
-        <v>-0.02953132135148373</v>
+        <v>-0.0262539003538641</v>
       </c>
       <c r="V335" t="n">
-        <v>0.531466007232666</v>
+        <v>0.5347434282302856</v>
       </c>
       <c r="W335" t="n">
         <v>1.7</v>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="Y335" t="inlineStr"/>
       <c r="Z335" t="n">
-        <v>6.557745803166986</v>
+        <v>6.598185819084961</v>
       </c>
       <c r="AA335" t="inlineStr">
         <is>
@@ -34019,49 +34019,49 @@
         <v>1.95</v>
       </c>
       <c r="H336" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I336" t="n">
         <v>3.6</v>
       </c>
       <c r="J336" t="n">
-        <v>0.4850444624090541</v>
+        <v>0.4833968426782798</v>
       </c>
       <c r="K336" t="n">
-        <v>0.2522231204527081</v>
+        <v>0.2547632008709852</v>
       </c>
       <c r="L336" t="n">
-        <v>0.2627324171382376</v>
+        <v>0.2618399564507349</v>
       </c>
       <c r="M336" t="n">
-        <v>0.05726495726495751</v>
+        <v>0.06086856086856107</v>
       </c>
       <c r="N336" t="n">
         <v>1</v>
       </c>
       <c r="O336" t="n">
-        <v>0.5834006071090698</v>
+        <v>0.5999532341957092</v>
       </c>
       <c r="P336" t="n">
-        <v>0.2403881400823593</v>
+        <v>0.2258628904819489</v>
       </c>
       <c r="Q336" t="n">
-        <v>0.1762113869190216</v>
+        <v>0.1741838157176971</v>
       </c>
       <c r="R336" t="n">
         <v>1</v>
       </c>
       <c r="S336" t="n">
-        <v>0.09835614470001569</v>
+        <v>0.1165563915174295</v>
       </c>
       <c r="T336" t="n">
         <v>1</v>
       </c>
       <c r="U336" t="n">
-        <v>0.09835614470001569</v>
+        <v>0.1165563915174295</v>
       </c>
       <c r="V336" t="n">
-        <v>0.5834006071090698</v>
+        <v>0.5999532341957092</v>
       </c>
       <c r="W336" t="n">
         <v>1.95</v>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="Y336" t="inlineStr"/>
       <c r="Z336" t="n">
-        <v>7.198565535273666</v>
+        <v>7.402807987907663</v>
       </c>
       <c r="AA336" t="inlineStr">
         <is>
@@ -34139,28 +34139,28 @@
         <v>0</v>
       </c>
       <c r="O337" t="n">
-        <v>0.2406667470932007</v>
+        <v>0.2432092428207397</v>
       </c>
       <c r="P337" t="n">
-        <v>0.4178179502487183</v>
+        <v>0.4212515652179718</v>
       </c>
       <c r="Q337" t="n">
-        <v>0.3415153324604034</v>
+        <v>0.3355391025543213</v>
       </c>
       <c r="R337" t="n">
         <v>1</v>
       </c>
       <c r="S337" t="n">
-        <v>0.1466981074196416</v>
+        <v>0.1501317223888952</v>
       </c>
       <c r="T337" t="n">
         <v>0</v>
       </c>
       <c r="U337" t="n">
-        <v>0.1466981074196416</v>
+        <v>0.1501317223888952</v>
       </c>
       <c r="V337" t="n">
-        <v>0.4178179502487183</v>
+        <v>0.4212515652179718</v>
       </c>
       <c r="W337" t="n">
         <v>3.5</v>
@@ -34172,7 +34172,7 @@
       </c>
       <c r="Y337" t="inlineStr"/>
       <c r="Z337" t="n">
-        <v>5.155445263561076</v>
+        <v>5.197812552998002</v>
       </c>
       <c r="AA337" t="inlineStr">
         <is>
@@ -34220,49 +34220,49 @@
         <v>3.9</v>
       </c>
       <c r="I338" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="J338" t="n">
-        <v>0.1895352559438931</v>
+        <v>0.1882404563405002</v>
       </c>
       <c r="K338" t="n">
-        <v>0.2429939178767861</v>
+        <v>0.2413339183852567</v>
       </c>
       <c r="L338" t="n">
-        <v>0.5674708261793209</v>
+        <v>0.5704256252742431</v>
       </c>
       <c r="M338" t="n">
-        <v>0.05521265161983724</v>
+        <v>0.06247086247086253</v>
       </c>
       <c r="N338" t="n">
         <v>2</v>
       </c>
       <c r="O338" t="n">
-        <v>0.1538346707820892</v>
+        <v>0.1528116166591644</v>
       </c>
       <c r="P338" t="n">
-        <v>0.3727922737598419</v>
+        <v>0.3622519373893738</v>
       </c>
       <c r="Q338" t="n">
-        <v>0.4733730852603912</v>
+        <v>0.484936386346817</v>
       </c>
       <c r="R338" t="n">
         <v>1</v>
       </c>
       <c r="S338" t="n">
-        <v>-0.09409774091892964</v>
+        <v>-0.0854892389274261</v>
       </c>
       <c r="T338" t="n">
         <v>2</v>
       </c>
       <c r="U338" t="n">
-        <v>-0.09409774091892964</v>
+        <v>-0.0854892389274261</v>
       </c>
       <c r="V338" t="n">
-        <v>0.4733730852603912</v>
+        <v>0.484936386346817</v>
       </c>
       <c r="W338" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X338" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
       </c>
       <c r="Y338" t="inlineStr"/>
       <c r="Z338" t="n">
-        <v>5.840938688369491</v>
+        <v>5.983617971970536</v>
       </c>
       <c r="AA338" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>481</v>
       </c>
       <c r="G339" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="H339" t="n">
         <v>6</v>
@@ -34322,43 +34322,43 @@
         <v>1.33</v>
       </c>
       <c r="J339" t="n">
-        <v>0.1197838486940859</v>
+        <v>0.1267572075291875</v>
       </c>
       <c r="K339" t="n">
-        <v>0.1597117982587811</v>
+        <v>0.1584465094114844</v>
       </c>
       <c r="L339" t="n">
-        <v>0.7205043530471329</v>
+        <v>0.7147962830593281</v>
       </c>
       <c r="M339" t="n">
-        <v>0.043546365914787</v>
+        <v>0.0518796992481203</v>
       </c>
       <c r="N339" t="n">
         <v>2</v>
       </c>
       <c r="O339" t="n">
-        <v>0.1648818552494049</v>
+        <v>0.1729756444692612</v>
       </c>
       <c r="P339" t="n">
-        <v>0.2964842617511749</v>
+        <v>0.296008825302124</v>
       </c>
       <c r="Q339" t="n">
-        <v>0.5386338233947754</v>
+        <v>0.5310155153274536</v>
       </c>
       <c r="R339" t="n">
         <v>1</v>
       </c>
       <c r="S339" t="n">
-        <v>-0.1818705296523575</v>
+        <v>-0.1837807677318745</v>
       </c>
       <c r="T339" t="n">
         <v>2</v>
       </c>
       <c r="U339" t="n">
-        <v>-0.1818705296523575</v>
+        <v>-0.1837807677318745</v>
       </c>
       <c r="V339" t="n">
-        <v>0.5386338233947754</v>
+        <v>0.5310155153274536</v>
       </c>
       <c r="W339" t="n">
         <v>1.33</v>
@@ -34370,7 +34370,7 @@
       </c>
       <c r="Y339" t="inlineStr"/>
       <c r="Z339" t="n">
-        <v>5.524141344098878</v>
+        <v>5.418354040931621</v>
       </c>
       <c r="AA339" t="inlineStr">
         <is>
@@ -34412,25 +34412,25 @@
         <v>481</v>
       </c>
       <c r="G340" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="H340" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I340" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="J340" t="n">
-        <v>0.5608856088560886</v>
+        <v>0.5772208925805997</v>
       </c>
       <c r="K340" t="n">
-        <v>0.2383763837638377</v>
+        <v>0.2322962128678023</v>
       </c>
       <c r="L340" t="n">
-        <v>0.2007380073800738</v>
+        <v>0.1904828945515979</v>
       </c>
       <c r="M340" t="n">
-        <v>0.04876160990712064</v>
+        <v>0.04996304508499638</v>
       </c>
       <c r="N340" t="n">
         <v>1</v>
@@ -34448,19 +34448,19 @@
         <v>1</v>
       </c>
       <c r="S340" t="n">
-        <v>-0.01058793133915137</v>
+        <v>-0.02692321506366246</v>
       </c>
       <c r="T340" t="n">
         <v>1</v>
       </c>
       <c r="U340" t="n">
-        <v>-0.01058793133915137</v>
+        <v>-0.02692321506366246</v>
       </c>
       <c r="V340" t="n">
         <v>0.5502976775169373</v>
       </c>
       <c r="W340" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="X340" t="inlineStr">
         <is>
@@ -34535,28 +34535,28 @@
         <v>0</v>
       </c>
       <c r="O341" t="n">
-        <v>0.2533594071865082</v>
+        <v>0.2538716197013855</v>
       </c>
       <c r="P341" t="n">
-        <v>0.376624584197998</v>
+        <v>0.375970184803009</v>
       </c>
       <c r="Q341" t="n">
-        <v>0.3700159192085266</v>
+        <v>0.3701580762863159</v>
       </c>
       <c r="R341" t="n">
         <v>1</v>
       </c>
       <c r="S341" t="n">
-        <v>0.1055047413689214</v>
+        <v>0.1048503419739324</v>
       </c>
       <c r="T341" t="n">
         <v>0</v>
       </c>
       <c r="U341" t="n">
-        <v>0.1055047413689214</v>
+        <v>0.1048503419739324</v>
       </c>
       <c r="V341" t="n">
-        <v>0.376624584197998</v>
+        <v>0.375970184803009</v>
       </c>
       <c r="W341" t="n">
         <v>3.5</v>
@@ -34568,7 +34568,7 @@
       </c>
       <c r="Y341" t="inlineStr"/>
       <c r="Z341" t="n">
-        <v>4.647161347635723</v>
+        <v>4.639086729828218</v>
       </c>
       <c r="AA341" t="inlineStr">
         <is>
@@ -34610,25 +34610,25 @@
         <v>481</v>
       </c>
       <c r="G342" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H342" t="n">
         <v>3.4</v>
       </c>
       <c r="I342" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="J342" t="n">
-        <v>0.3371104815864023</v>
+        <v>0.3479328694228407</v>
       </c>
       <c r="K342" t="n">
-        <v>0.2776203966005666</v>
+        <v>0.2762996316004912</v>
       </c>
       <c r="L342" t="n">
-        <v>0.3852691218130311</v>
+        <v>0.375767498976668</v>
       </c>
       <c r="M342" t="n">
-        <v>0.05942376950780304</v>
+        <v>0.06448801742919397</v>
       </c>
       <c r="N342" t="n">
         <v>0</v>
@@ -34646,13 +34646,13 @@
         <v>1</v>
       </c>
       <c r="S342" t="n">
-        <v>0.152086981548466</v>
+        <v>0.1534077465485414</v>
       </c>
       <c r="T342" t="n">
         <v>0</v>
       </c>
       <c r="U342" t="n">
-        <v>0.152086981548466</v>
+        <v>0.1534077465485414</v>
       </c>
       <c r="V342" t="n">
         <v>0.4297073781490326</v>
@@ -34808,7 +34808,7 @@
         <v>481</v>
       </c>
       <c r="G344" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H344" t="n">
         <v>4.2</v>
@@ -34817,46 +34817,46 @@
         <v>3.9</v>
       </c>
       <c r="J344" t="n">
-        <v>0.5360824742268041</v>
+        <v>0.5403800475059383</v>
       </c>
       <c r="K344" t="n">
-        <v>0.2233676975945017</v>
+        <v>0.221298495645289</v>
       </c>
       <c r="L344" t="n">
-        <v>0.2405498281786942</v>
+        <v>0.2383214568487728</v>
       </c>
       <c r="M344" t="n">
-        <v>0.06593406593406592</v>
+        <v>0.07590084334270375</v>
       </c>
       <c r="N344" t="n">
         <v>1</v>
       </c>
       <c r="O344" t="n">
-        <v>0.3838088512420654</v>
+        <v>0.3818604648113251</v>
       </c>
       <c r="P344" t="n">
-        <v>0.2944603562355042</v>
+        <v>0.294249564409256</v>
       </c>
       <c r="Q344" t="n">
-        <v>0.3217307925224304</v>
+        <v>0.3238899409770966</v>
       </c>
       <c r="R344" t="n">
         <v>1</v>
       </c>
       <c r="S344" t="n">
-        <v>-0.1522736229847387</v>
+        <v>-0.1585195826946132</v>
       </c>
       <c r="T344" t="n">
         <v>1</v>
       </c>
       <c r="U344" t="n">
-        <v>-0.1522736229847387</v>
+        <v>-0.1585195826946132</v>
       </c>
       <c r="V344" t="n">
-        <v>0.3838088512420654</v>
+        <v>0.3818604648113251</v>
       </c>
       <c r="W344" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="X344" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
       </c>
       <c r="Y344" t="inlineStr"/>
       <c r="Z344" t="n">
-        <v>3.796357622054108</v>
+        <v>3.733782159985721</v>
       </c>
       <c r="AA344" t="inlineStr">
         <is>
@@ -35303,55 +35303,55 @@
         <v>481</v>
       </c>
       <c r="G349" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H349" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I349" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="J349" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.2618399564507349</v>
       </c>
       <c r="K349" t="n">
-        <v>0.2611940298507463</v>
+        <v>0.2547632008709852</v>
       </c>
       <c r="L349" t="n">
-        <v>0.4701492537313433</v>
+        <v>0.4833968426782798</v>
       </c>
       <c r="M349" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.06086856086856107</v>
       </c>
       <c r="N349" t="n">
         <v>2</v>
       </c>
       <c r="O349" t="n">
-        <v>0.2351477593183517</v>
+        <v>0.2331060171127319</v>
       </c>
       <c r="P349" t="n">
-        <v>0.3429699242115021</v>
+        <v>0.3418344557285309</v>
       </c>
       <c r="Q349" t="n">
-        <v>0.4218823909759521</v>
+        <v>0.4250595569610596</v>
       </c>
       <c r="R349" t="n">
         <v>1</v>
       </c>
       <c r="S349" t="n">
-        <v>-0.04826686275539116</v>
+        <v>-0.05833728571722019</v>
       </c>
       <c r="T349" t="n">
         <v>2</v>
       </c>
       <c r="U349" t="n">
-        <v>-0.04826686275539116</v>
+        <v>-0.05833728571722019</v>
       </c>
       <c r="V349" t="n">
-        <v>0.4218823909759521</v>
+        <v>0.4250595569610596</v>
       </c>
       <c r="W349" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="X349" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
       </c>
       <c r="Y349" t="inlineStr"/>
       <c r="Z349" t="n">
-        <v>5.205596296286619</v>
+        <v>5.244799268106568</v>
       </c>
       <c r="AA349" t="inlineStr">
         <is>
@@ -35600,25 +35600,25 @@
         <v>551</v>
       </c>
       <c r="G352" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="H352" t="n">
         <v>3.6</v>
       </c>
       <c r="I352" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J352" t="n">
-        <v>0.4885742581520743</v>
+        <v>0.4866595517609392</v>
       </c>
       <c r="K352" t="n">
-        <v>0.2592157869640172</v>
+        <v>0.263607257203842</v>
       </c>
       <c r="L352" t="n">
-        <v>0.2522099548839086</v>
+        <v>0.2497331910352188</v>
       </c>
       <c r="M352" t="n">
-        <v>0.07160825747213173</v>
+        <v>0.05375618533513271</v>
       </c>
       <c r="N352" t="n">
         <v>0</v>
@@ -35636,13 +35636,13 @@
         <v>1</v>
       </c>
       <c r="S352" t="n">
-        <v>0.08586178728906507</v>
+        <v>0.08147031704924024</v>
       </c>
       <c r="T352" t="n">
         <v>0</v>
       </c>
       <c r="U352" t="n">
-        <v>0.08586178728906507</v>
+        <v>0.08147031704924024</v>
       </c>
       <c r="V352" t="n">
         <v>0.3450775742530823</v>
@@ -35706,22 +35706,22 @@
         <v>2.9</v>
       </c>
       <c r="H353" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I353" t="n">
         <v>2.5</v>
       </c>
       <c r="J353" t="n">
-        <v>0.323051271363068</v>
+        <v>0.3276209677419355</v>
       </c>
       <c r="K353" t="n">
-        <v>0.3022092538557732</v>
+        <v>0.2923387096774194</v>
       </c>
       <c r="L353" t="n">
-        <v>0.3747394747811589</v>
+        <v>0.3800403225806452</v>
       </c>
       <c r="M353" t="n">
-        <v>0.06740823136818674</v>
+        <v>0.0525198938992042</v>
       </c>
       <c r="N353" t="n">
         <v>2</v>
@@ -35739,13 +35739,13 @@
         <v>1</v>
       </c>
       <c r="S353" t="n">
-        <v>0.02063231991946368</v>
+        <v>0.01533147211997737</v>
       </c>
       <c r="T353" t="n">
         <v>2</v>
       </c>
       <c r="U353" t="n">
-        <v>0.02063231991946368</v>
+        <v>0.01533147211997737</v>
       </c>
       <c r="V353" t="n">
         <v>0.3953717947006226</v>
@@ -35806,25 +35806,25 @@
         <v>551</v>
       </c>
       <c r="G354" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="H354" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I354" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="J354" t="n">
-        <v>0.1870525059665871</v>
+        <v>0.1803845322963923</v>
       </c>
       <c r="K354" t="n">
-        <v>0.2461217183770883</v>
+        <v>0.2525383452149492</v>
       </c>
       <c r="L354" t="n">
-        <v>0.5668257756563246</v>
+        <v>0.5670771224886585</v>
       </c>
       <c r="M354" t="n">
-        <v>0.06921850079744818</v>
+        <v>0.05594525235243797</v>
       </c>
       <c r="N354" t="n">
         <v>2</v>
@@ -35842,19 +35842,19 @@
         <v>1</v>
       </c>
       <c r="S354" t="n">
-        <v>-0.0965688808294356</v>
+        <v>-0.09682022766176945</v>
       </c>
       <c r="T354" t="n">
         <v>2</v>
       </c>
       <c r="U354" t="n">
-        <v>-0.0965688808294356</v>
+        <v>-0.09682022766176945</v>
       </c>
       <c r="V354" t="n">
         <v>0.470256894826889</v>
       </c>
       <c r="W354" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X354" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
       </c>
       <c r="Y354" t="inlineStr"/>
       <c r="Z354" t="n">
-        <v>4.696733791177587</v>
+        <v>4.850103827675385</v>
       </c>
       <c r="AA354" t="inlineStr">
         <is>
@@ -35877,10 +35877,10 @@
       </c>
       <c r="AC354" t="inlineStr"/>
       <c r="AD354" t="n">
-        <v>-34.47324977471279</v>
+        <v>-32.04044561777543</v>
       </c>
       <c r="AE354" t="n">
-        <v>-0.6894649954942558</v>
+        <v>-0.6408089123555085</v>
       </c>
     </row>
     <row r="355">
@@ -35909,25 +35909,25 @@
         <v>551</v>
       </c>
       <c r="G355" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="H355" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="I355" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J355" t="n">
-        <v>0.7297486033519555</v>
+        <v>0.7419115512402826</v>
       </c>
       <c r="K355" t="n">
-        <v>0.171159217877095</v>
+        <v>0.1638656817522016</v>
       </c>
       <c r="L355" t="n">
-        <v>0.09909217877094974</v>
+        <v>0.0942227670075159</v>
       </c>
       <c r="M355" t="n">
-        <v>0.06227513816253083</v>
+        <v>0.06131461828141038</v>
       </c>
       <c r="N355" t="n">
         <v>1</v>
@@ -35945,19 +35945,19 @@
         <v>1</v>
       </c>
       <c r="S355" t="n">
-        <v>0.1425566110531044</v>
+        <v>0.1303936631647772</v>
       </c>
       <c r="T355" t="n">
         <v>1</v>
       </c>
       <c r="U355" t="n">
-        <v>0.1425566110531044</v>
+        <v>0.1303936631647772</v>
       </c>
       <c r="V355" t="n">
         <v>0.8723052144050598</v>
       </c>
       <c r="W355" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X355" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
       </c>
       <c r="Y355" t="inlineStr"/>
       <c r="Z355" t="n">
-        <v>9.887980995955333</v>
+        <v>9.694218060996834</v>
       </c>
       <c r="AA355" t="inlineStr">
         <is>
@@ -35980,10 +35980,10 @@
       </c>
       <c r="AC355" t="inlineStr"/>
       <c r="AD355" t="n">
-        <v>43.19783675259558</v>
+        <v>39.93615640534296</v>
       </c>
       <c r="AE355" t="n">
-        <v>0.8639567350519115</v>
+        <v>0.7987231281068591</v>
       </c>
     </row>
     <row r="356">
@@ -36012,25 +36012,25 @@
         <v>551</v>
       </c>
       <c r="G356" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="H356" t="n">
         <v>3.5</v>
       </c>
       <c r="I356" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="J356" t="n">
-        <v>0.2384279475982533</v>
+        <v>0.253393665158371</v>
       </c>
       <c r="K356" t="n">
-        <v>0.2724890829694323</v>
+        <v>0.2714932126696832</v>
       </c>
       <c r="L356" t="n">
-        <v>0.4890829694323144</v>
+        <v>0.4751131221719457</v>
       </c>
       <c r="M356" t="n">
-        <v>0.04853479853479858</v>
+        <v>0.05238095238095242</v>
       </c>
       <c r="N356" t="n">
         <v>2</v>
@@ -36048,19 +36048,19 @@
         <v>1</v>
       </c>
       <c r="S356" t="n">
-        <v>0.01102127909139772</v>
+        <v>0.02499112635176648</v>
       </c>
       <c r="T356" t="n">
         <v>2</v>
       </c>
       <c r="U356" t="n">
-        <v>0.01102127909139772</v>
+        <v>0.02499112635176648</v>
       </c>
       <c r="V356" t="n">
         <v>0.5001042485237122</v>
       </c>
       <c r="W356" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="X356" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
       </c>
       <c r="Y356" t="inlineStr"/>
       <c r="Z356" t="n">
-        <v>6.844440624874321</v>
+        <v>7.029303528502626</v>
       </c>
       <c r="AA356" t="inlineStr">
         <is>
@@ -36085,10 +36085,10 @@
         <v>1</v>
       </c>
       <c r="AD356" t="n">
-        <v>-2.610180566185405</v>
+        <v>0.02084970474243164</v>
       </c>
       <c r="AE356" t="n">
-        <v>-0.0522036113237081</v>
+        <v>0.0004169940948486328</v>
       </c>
     </row>
     <row r="357">
@@ -36117,25 +36117,25 @@
         <v>551</v>
       </c>
       <c r="G357" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="H357" t="n">
         <v>3.4</v>
       </c>
       <c r="I357" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="J357" t="n">
-        <v>0.3677036001398113</v>
+        <v>0.3590576766856215</v>
       </c>
       <c r="K357" t="n">
-        <v>0.2757777001048585</v>
+        <v>0.2777416734362307</v>
       </c>
       <c r="L357" t="n">
-        <v>0.3565186997553303</v>
+        <v>0.3632006498781478</v>
       </c>
       <c r="M357" t="n">
-        <v>0.06650264668605077</v>
+        <v>0.05896116855633737</v>
       </c>
       <c r="N357" t="n">
         <v>2</v>
@@ -36153,19 +36153,19 @@
         <v>1</v>
       </c>
       <c r="S357" t="n">
-        <v>0.03184874452147934</v>
+        <v>0.02516679439866187</v>
       </c>
       <c r="T357" t="n">
         <v>2</v>
       </c>
       <c r="U357" t="n">
-        <v>0.03184874452147934</v>
+        <v>0.02516679439866187</v>
       </c>
       <c r="V357" t="n">
         <v>0.3883674442768097</v>
       </c>
       <c r="W357" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="X357" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
       </c>
       <c r="Y357" t="inlineStr"/>
       <c r="Z357" t="n">
-        <v>7.120127764607157</v>
+        <v>7.070687125165502</v>
       </c>
       <c r="AA357" t="inlineStr">
         <is>
@@ -36188,10 +36188,10 @@
       </c>
       <c r="AC357" t="inlineStr"/>
       <c r="AD357" t="n">
-        <v>1.313274751411625</v>
+        <v>0.609709694981575</v>
       </c>
       <c r="AE357" t="n">
-        <v>0.0262654950282325</v>
+        <v>0.0121941938996315</v>
       </c>
     </row>
     <row r="358">
@@ -36220,25 +36220,25 @@
         <v>551</v>
       </c>
       <c r="G358" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H358" t="n">
         <v>3.1</v>
       </c>
       <c r="I358" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="J358" t="n">
-        <v>0.2946410515672397</v>
+        <v>0.2929172621883437</v>
       </c>
       <c r="K358" t="n">
-        <v>0.3041456016177958</v>
+        <v>0.3070906781006829</v>
       </c>
       <c r="L358" t="n">
-        <v>0.4012133468149647</v>
+        <v>0.3999920597109735</v>
       </c>
       <c r="M358" t="n">
-        <v>0.06061256005490723</v>
+        <v>0.05044102008048879</v>
       </c>
       <c r="N358" t="n">
         <v>2</v>
@@ -36256,19 +36256,19 @@
         <v>1</v>
       </c>
       <c r="S358" t="n">
-        <v>0.03094199409499321</v>
+        <v>0.03216328119898443</v>
       </c>
       <c r="T358" t="n">
         <v>2</v>
       </c>
       <c r="U358" t="n">
-        <v>0.03094199409499321</v>
+        <v>0.03216328119898443</v>
       </c>
       <c r="V358" t="n">
         <v>0.4321553409099579</v>
       </c>
       <c r="W358" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="X358" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
       </c>
       <c r="Y358" t="inlineStr"/>
       <c r="Z358" t="n">
-        <v>7.108863293003022</v>
+        <v>7.173108996102808</v>
       </c>
       <c r="AA358" t="inlineStr">
         <is>
@@ -36291,10 +36291,10 @@
       </c>
       <c r="AC358" t="inlineStr"/>
       <c r="AD358" t="n">
-        <v>1.152966750992673</v>
+        <v>2.067370388818823</v>
       </c>
       <c r="AE358" t="n">
-        <v>0.02305933501985347</v>
+        <v>0.04134740777637647</v>
       </c>
     </row>
     <row r="359">
@@ -36323,25 +36323,25 @@
         <v>551</v>
       </c>
       <c r="G359" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H359" t="n">
         <v>3.75</v>
       </c>
       <c r="I359" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="J359" t="n">
-        <v>0.6019261637239165</v>
+        <v>0.6069472111553785</v>
       </c>
       <c r="K359" t="n">
-        <v>0.2487961476725522</v>
+        <v>0.2492529880478088</v>
       </c>
       <c r="L359" t="n">
-        <v>0.1492776886035313</v>
+        <v>0.1437998007968128</v>
       </c>
       <c r="M359" t="n">
-        <v>0.07182795698924727</v>
+        <v>0.0698634698634697</v>
       </c>
       <c r="N359" t="n">
         <v>1</v>
@@ -36359,19 +36359,19 @@
         <v>1</v>
       </c>
       <c r="S359" t="n">
-        <v>-0.1628567138223357</v>
+        <v>-0.1678777612537977</v>
       </c>
       <c r="T359" t="n">
         <v>1</v>
       </c>
       <c r="U359" t="n">
-        <v>-0.1628567138223357</v>
+        <v>-0.1678777612537977</v>
       </c>
       <c r="V359" t="n">
         <v>0.4390694499015808</v>
       </c>
       <c r="W359" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X359" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
       </c>
       <c r="Y359" t="inlineStr"/>
       <c r="Z359" t="n">
-        <v>3.350523642920814</v>
+        <v>3.255087138862695</v>
       </c>
       <c r="AA359" t="inlineStr">
         <is>
@@ -36396,10 +36396,10 @@
         <v>1</v>
       </c>
       <c r="AD359" t="n">
-        <v>-58.08042775500903</v>
+        <v>-59.96908280584547</v>
       </c>
       <c r="AE359" t="n">
-        <v>-1.161608555100181</v>
+        <v>-1.19938165611691</v>
       </c>
     </row>
     <row r="360">
@@ -37362,22 +37362,22 @@
         <v>3.45</v>
       </c>
       <c r="H369" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I369" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="J369" t="n">
-        <v>0.2752625860195582</v>
+        <v>0.2748364069006543</v>
       </c>
       <c r="K369" t="n">
-        <v>0.2499094530967041</v>
+        <v>0.246281975014872</v>
       </c>
       <c r="L369" t="n">
-        <v>0.4748279608837379</v>
+        <v>0.4788816180844735</v>
       </c>
       <c r="M369" t="n">
-        <v>0.05301296720061011</v>
+        <v>0.05464583725453309</v>
       </c>
       <c r="N369" t="n">
         <v>2</v>
@@ -37395,19 +37395,19 @@
         <v>1</v>
       </c>
       <c r="S369" t="n">
-        <v>0.1354813419231164</v>
+        <v>0.1314276847223808</v>
       </c>
       <c r="T369" t="n">
         <v>2</v>
       </c>
       <c r="U369" t="n">
-        <v>0.1354813419231164</v>
+        <v>0.1314276847223808</v>
       </c>
       <c r="V369" t="n">
         <v>0.6103093028068542</v>
       </c>
       <c r="W369" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X369" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
       </c>
       <c r="Y369" t="inlineStr"/>
       <c r="Z369" t="n">
-        <v>8.553635253790617</v>
+        <v>8.500287257679332</v>
       </c>
       <c r="AA369" t="inlineStr">
         <is>
@@ -37430,10 +37430,10 @@
       </c>
       <c r="AC369" t="inlineStr"/>
       <c r="AD369" t="n">
-        <v>22.06186056137085</v>
+        <v>21.26657342424198</v>
       </c>
       <c r="AE369" t="n">
-        <v>0.441237211227417</v>
+        <v>0.4253314684848396</v>
       </c>
     </row>
     <row r="370">
@@ -37465,49 +37465,49 @@
         <v>1.3</v>
       </c>
       <c r="H370" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="I370" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J370" t="n">
-        <v>0.7197844495765973</v>
+        <v>0.7296439901304195</v>
       </c>
       <c r="K370" t="n">
-        <v>0.170130869899923</v>
+        <v>0.1649629890729644</v>
       </c>
       <c r="L370" t="n">
-        <v>0.1100846805234796</v>
+        <v>0.1053930207966162</v>
       </c>
       <c r="M370" t="n">
-        <v>0.06869600987248048</v>
+        <v>0.05425492382014108</v>
       </c>
       <c r="N370" t="n">
         <v>1</v>
       </c>
       <c r="O370" t="n">
-        <v>0.5334666201787054</v>
+        <v>0.5331592001430043</v>
       </c>
       <c r="P370" t="n">
-        <v>0.3101993965773246</v>
+        <v>0.3100206384208382</v>
       </c>
       <c r="Q370" t="n">
-        <v>0.15633398324397</v>
+        <v>0.1568201614361574</v>
       </c>
       <c r="R370" t="n">
         <v>1</v>
       </c>
       <c r="S370" t="n">
-        <v>-0.1863178293978919</v>
+        <v>-0.1964847899874151</v>
       </c>
       <c r="T370" t="n">
         <v>1</v>
       </c>
       <c r="U370" t="n">
-        <v>-0.1863178293978919</v>
+        <v>-0.1964847899874151</v>
       </c>
       <c r="V370" t="n">
-        <v>0.5334666201787054</v>
+        <v>0.5331592001430043</v>
       </c>
       <c r="W370" t="n">
         <v>1.3</v>
@@ -37519,7 +37519,7 @@
       </c>
       <c r="Y370" t="inlineStr"/>
       <c r="Z370" t="n">
-        <v>0.2078875170719314</v>
+        <v>0.2073976914330725</v>
       </c>
       <c r="AA370" t="inlineStr">
         <is>
@@ -37533,10 +37533,10 @@
       </c>
       <c r="AC370" t="inlineStr"/>
       <c r="AD370" t="n">
-        <v>-102.1644645892276</v>
+        <v>-102.2976799380314</v>
       </c>
       <c r="AE370" t="n">
-        <v>-2.043289291784553</v>
+        <v>-2.045953598760629</v>
       </c>
     </row>
     <row r="371">
@@ -37565,25 +37565,25 @@
         <v>591</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H371" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I371" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J371" t="n">
-        <v>0.5105762217359592</v>
+        <v>0.5125</v>
       </c>
       <c r="K371" t="n">
-        <v>0.2669584245076587</v>
+        <v>0.25625</v>
       </c>
       <c r="L371" t="n">
-        <v>0.2224653537563822</v>
+        <v>0.23125</v>
       </c>
       <c r="M371" t="n">
-        <v>0.07025761124121765</v>
+        <v>0.05471324983520098</v>
       </c>
       <c r="N371" t="n">
         <v>1</v>
@@ -37601,19 +37601,19 @@
         <v>1</v>
       </c>
       <c r="S371" t="n">
-        <v>-0.1516675649265095</v>
+        <v>-0.1535913431905503</v>
       </c>
       <c r="T371" t="n">
         <v>1</v>
       </c>
       <c r="U371" t="n">
-        <v>-0.1516675649265095</v>
+        <v>-0.1535913431905503</v>
       </c>
       <c r="V371" t="n">
         <v>0.3589086568094497</v>
       </c>
       <c r="W371" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="X371" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
       </c>
       <c r="Y371" t="inlineStr"/>
       <c r="Z371" t="n">
-        <v>0.55134294039892</v>
+        <v>0.5653836566430673</v>
       </c>
       <c r="AA371" t="inlineStr">
         <is>
@@ -37636,10 +37636,10 @@
       </c>
       <c r="AC371" t="inlineStr"/>
       <c r="AD371" t="n">
-        <v>-41.34905518538639</v>
+        <v>-39.53164528264918</v>
       </c>
       <c r="AE371" t="n">
-        <v>-0.8269811037077278</v>
+        <v>-0.7906329056529836</v>
       </c>
     </row>
     <row r="372">
@@ -37671,22 +37671,22 @@
         <v>1.44</v>
       </c>
       <c r="H372" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="I372" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="J372" t="n">
-        <v>0.6449948400412796</v>
+        <v>0.6558682952734998</v>
       </c>
       <c r="K372" t="n">
-        <v>0.2063983488132095</v>
+        <v>0.1988316516197557</v>
       </c>
       <c r="L372" t="n">
-        <v>0.1486068111455108</v>
+        <v>0.1453000531067446</v>
       </c>
       <c r="M372" t="n">
-        <v>0.07666666666666666</v>
+        <v>0.05881691408007184</v>
       </c>
       <c r="N372" t="n">
         <v>1</v>
@@ -37704,13 +37704,13 @@
         <v>1</v>
       </c>
       <c r="S372" t="n">
-        <v>-0.1481988500734035</v>
+        <v>-0.1590723053056237</v>
       </c>
       <c r="T372" t="n">
         <v>1</v>
       </c>
       <c r="U372" t="n">
-        <v>-0.1481988500734035</v>
+        <v>-0.1590723053056237</v>
       </c>
       <c r="V372" t="n">
         <v>0.4967959899678761</v>
@@ -37771,55 +37771,55 @@
         <v>591</v>
       </c>
       <c r="G373" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="H373" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I373" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="J373" t="n">
-        <v>0.5557224391709222</v>
+        <v>0.5477819635580841</v>
       </c>
       <c r="K373" t="n">
-        <v>0.2553319315109642</v>
+        <v>0.2527100791881294</v>
       </c>
       <c r="L373" t="n">
-        <v>0.1889456293181136</v>
+        <v>0.1995079572537864</v>
       </c>
       <c r="M373" t="n">
-        <v>0.05850556438791732</v>
+        <v>0.05522766453706529</v>
       </c>
       <c r="N373" t="n">
         <v>1</v>
       </c>
       <c r="O373" t="n">
-        <v>0.3876746774015735</v>
+        <v>0.387086895390314</v>
       </c>
       <c r="P373" t="n">
-        <v>0.3355014801438096</v>
+        <v>0.3356173100422264</v>
       </c>
       <c r="Q373" t="n">
-        <v>0.2768238424546168</v>
+        <v>0.2772957945674596</v>
       </c>
       <c r="R373" t="n">
         <v>1</v>
       </c>
       <c r="S373" t="n">
-        <v>-0.1680477617693488</v>
+        <v>-0.16069506816777</v>
       </c>
       <c r="T373" t="n">
         <v>1</v>
       </c>
       <c r="U373" t="n">
-        <v>-0.1680477617693488</v>
+        <v>-0.16069506816777</v>
       </c>
       <c r="V373" t="n">
-        <v>0.3876746774015735</v>
+        <v>0.387086895390314</v>
       </c>
       <c r="W373" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X373" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="Y373" t="inlineStr"/>
       <c r="Z373" t="n">
-        <v>0.4965680991946713</v>
+        <v>0.5218664632633849</v>
       </c>
       <c r="AA373" t="inlineStr">
         <is>
@@ -37842,10 +37842,10 @@
       </c>
       <c r="AC373" t="inlineStr"/>
       <c r="AD373" t="n">
-        <v>-48.70757834533216</v>
+        <v>-45.25200972256941</v>
       </c>
       <c r="AE373" t="n">
-        <v>-0.9741515669066432</v>
+        <v>-0.9050401944513883</v>
       </c>
     </row>
     <row r="374">
@@ -37877,49 +37877,49 @@
         <v>1.67</v>
       </c>
       <c r="H374" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I374" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="J374" t="n">
-        <v>0.5590930268675262</v>
+        <v>0.5692192187805826</v>
       </c>
       <c r="K374" t="n">
-        <v>0.2334213387171921</v>
+        <v>0.2112435767474606</v>
       </c>
       <c r="L374" t="n">
-        <v>0.2074856344152819</v>
+        <v>0.2195372044719568</v>
       </c>
       <c r="M374" t="n">
-        <v>0.07102461743180299</v>
+        <v>0.05197149964889314</v>
       </c>
       <c r="N374" t="n">
         <v>1</v>
       </c>
       <c r="O374" t="n">
-        <v>0.3857783886646933</v>
+        <v>0.3848862879181934</v>
       </c>
       <c r="P374" t="n">
-        <v>0.3445749432805242</v>
+        <v>0.3446340222656522</v>
       </c>
       <c r="Q374" t="n">
-        <v>0.2696466680547824</v>
+        <v>0.2704796898161545</v>
       </c>
       <c r="R374" t="n">
         <v>1</v>
       </c>
       <c r="S374" t="n">
-        <v>-0.1733146382028328</v>
+        <v>-0.1843329308623892</v>
       </c>
       <c r="T374" t="n">
         <v>1</v>
       </c>
       <c r="U374" t="n">
-        <v>-0.1733146382028328</v>
+        <v>-0.1843329308623892</v>
       </c>
       <c r="V374" t="n">
-        <v>0.3857783886646933</v>
+        <v>0.3848862879181934</v>
       </c>
       <c r="W374" t="n">
         <v>1.67</v>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="Y374" t="inlineStr"/>
       <c r="Z374" t="n">
-        <v>0.4655568086901336</v>
+        <v>0.4640200243159465</v>
       </c>
       <c r="AA374" t="inlineStr">
         <is>
@@ -37945,10 +37945,10 @@
       </c>
       <c r="AC374" t="inlineStr"/>
       <c r="AD374" t="n">
-        <v>-53.0970284970093</v>
+        <v>-53.31938793680852</v>
       </c>
       <c r="AE374" t="n">
-        <v>-1.061940569940186</v>
+        <v>-1.066387758736171</v>
       </c>
     </row>
     <row r="375">
@@ -37977,25 +37977,25 @@
         <v>591</v>
       </c>
       <c r="G375" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="H375" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I375" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="J375" t="n">
-        <v>0.2299619616899878</v>
+        <v>0.25</v>
       </c>
       <c r="K375" t="n">
-        <v>0.2548227143051216</v>
+        <v>0.25</v>
       </c>
       <c r="L375" t="n">
-        <v>0.5152153240048907</v>
+        <v>0.5</v>
       </c>
       <c r="M375" t="n">
-        <v>0.06062079672635434</v>
+        <v>0.05263157894736836</v>
       </c>
       <c r="N375" t="n">
         <v>2</v>
@@ -38013,19 +38013,19 @@
         <v>1</v>
       </c>
       <c r="S375" t="n">
-        <v>-0.09131067153665989</v>
+        <v>-0.07609534753176922</v>
       </c>
       <c r="T375" t="n">
         <v>2</v>
       </c>
       <c r="U375" t="n">
-        <v>-0.09131067153665989</v>
+        <v>-0.07609534753176922</v>
       </c>
       <c r="V375" t="n">
         <v>0.4239046524682308</v>
       </c>
       <c r="W375" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="X375" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
       </c>
       <c r="Y375" t="inlineStr"/>
       <c r="Z375" t="n">
-        <v>0.6669756887033489</v>
+        <v>0.7130926913106456</v>
       </c>
       <c r="AA375" t="inlineStr">
         <is>
@@ -38048,10 +38048,10 @@
       </c>
       <c r="AC375" t="inlineStr"/>
       <c r="AD375" t="n">
-        <v>-27.01861276905272</v>
+        <v>-21.6201289233735</v>
       </c>
       <c r="AE375" t="n">
-        <v>-0.5403722553810545</v>
+        <v>-0.43240257846747</v>
       </c>
     </row>
     <row r="376">
@@ -38083,22 +38083,22 @@
         <v>1.36</v>
       </c>
       <c r="H376" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="I376" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J376" t="n">
-        <v>0.6934812760055478</v>
+        <v>0.6942607775720708</v>
       </c>
       <c r="K376" t="n">
-        <v>0.188626907073509</v>
+        <v>0.1798466014281936</v>
       </c>
       <c r="L376" t="n">
-        <v>0.1178918169209431</v>
+        <v>0.1258926209997355</v>
       </c>
       <c r="M376" t="n">
-        <v>0.06029411764705883</v>
+        <v>0.05910364145658265</v>
       </c>
       <c r="N376" t="n">
         <v>1</v>
@@ -38116,13 +38116,13 @@
         <v>1</v>
       </c>
       <c r="S376" t="n">
-        <v>-0.1979129867950286</v>
+        <v>-0.1986924883615516</v>
       </c>
       <c r="T376" t="n">
         <v>1</v>
       </c>
       <c r="U376" t="n">
-        <v>-0.1979129867950286</v>
+        <v>-0.1986924883615516</v>
       </c>
       <c r="V376" t="n">
         <v>0.4955682892105192</v>
@@ -38183,7 +38183,7 @@
         <v>591</v>
       </c>
       <c r="G377" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H377" t="n">
         <v>3.3</v>
@@ -38192,16 +38192,16 @@
         <v>2.15</v>
       </c>
       <c r="J377" t="n">
-        <v>0.2768780487804878</v>
+        <v>0.2711119602598395</v>
       </c>
       <c r="K377" t="n">
-        <v>0.2852682926829269</v>
+        <v>0.2875429881543752</v>
       </c>
       <c r="L377" t="n">
-        <v>0.4378536585365854</v>
+        <v>0.4413450515857852</v>
       </c>
       <c r="M377" t="n">
-        <v>0.06226422915889396</v>
+        <v>0.05386086781435617</v>
       </c>
       <c r="N377" t="n">
         <v>2</v>
@@ -38219,13 +38219,13 @@
         <v>1</v>
       </c>
       <c r="S377" t="n">
-        <v>-0.03330668301686096</v>
+        <v>-0.03679807606606084</v>
       </c>
       <c r="T377" t="n">
         <v>2</v>
       </c>
       <c r="U377" t="n">
-        <v>-0.03330668301686096</v>
+        <v>-0.03679807606606084</v>
       </c>
       <c r="V377" t="n">
         <v>0.4045469755197244</v>
@@ -38286,25 +38286,25 @@
         <v>591</v>
       </c>
       <c r="G378" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="H378" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I378" t="n">
         <v>3.6</v>
       </c>
       <c r="J378" t="n">
-        <v>0.4664634146341463</v>
+        <v>0.4640029460504511</v>
       </c>
       <c r="K378" t="n">
-        <v>0.274390243902439</v>
+        <v>0.2717731541152641</v>
       </c>
       <c r="L378" t="n">
-        <v>0.2591463414634146</v>
+        <v>0.2642238998342846</v>
       </c>
       <c r="M378" t="n">
-        <v>0.0718954248366015</v>
+        <v>0.05129694154084419</v>
       </c>
       <c r="N378" t="n">
         <v>1</v>
@@ -38322,19 +38322,19 @@
         <v>1</v>
       </c>
       <c r="S378" t="n">
-        <v>-0.1079668444474011</v>
+        <v>-0.1055063758637059</v>
       </c>
       <c r="T378" t="n">
         <v>1</v>
       </c>
       <c r="U378" t="n">
-        <v>-0.1079668444474011</v>
+        <v>-0.1055063758637059</v>
       </c>
       <c r="V378" t="n">
         <v>0.3584965701867451</v>
       </c>
       <c r="W378" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="X378" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
       </c>
       <c r="Y378" t="inlineStr"/>
       <c r="Z378" t="n">
-        <v>0.6562058192716992</v>
+        <v>0.6819868445388029</v>
       </c>
       <c r="AA378" t="inlineStr">
         <is>
@@ -38357,10 +38357,10 @@
       </c>
       <c r="AC378" t="inlineStr"/>
       <c r="AD378" t="n">
-        <v>-28.30068596265098</v>
+        <v>-25.24590772544501</v>
       </c>
       <c r="AE378" t="n">
-        <v>-0.5660137192530196</v>
+        <v>-0.5049181545089002</v>
       </c>
     </row>
     <row r="379">
@@ -38389,25 +38389,25 @@
         <v>591</v>
       </c>
       <c r="G379" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="H379" t="n">
         <v>3.7</v>
       </c>
       <c r="I379" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J379" t="n">
-        <v>0.4454368932038835</v>
+        <v>0.4352087825916487</v>
       </c>
       <c r="K379" t="n">
-        <v>0.2528155339805825</v>
+        <v>0.2528915898843364</v>
       </c>
       <c r="L379" t="n">
-        <v>0.301747572815534</v>
+        <v>0.3118996275240149</v>
       </c>
       <c r="M379" t="n">
-        <v>0.06904139162203671</v>
+        <v>0.06871988267337104</v>
       </c>
       <c r="N379" t="n">
         <v>2</v>
@@ -38425,19 +38425,19 @@
         <v>1</v>
       </c>
       <c r="S379" t="n">
-        <v>0.04330920486279155</v>
+        <v>0.03315715015431064</v>
       </c>
       <c r="T379" t="n">
         <v>2</v>
       </c>
       <c r="U379" t="n">
-        <v>0.04330920486279155</v>
+        <v>0.03315715015431064</v>
       </c>
       <c r="V379" t="n">
         <v>0.3450567776783255</v>
       </c>
       <c r="W379" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X379" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
       </c>
       <c r="Y379" t="inlineStr"/>
       <c r="Z379" t="n">
-        <v>0.9360164891007222</v>
+        <v>0.9218983051547678</v>
       </c>
       <c r="AA379" t="inlineStr">
         <is>
@@ -38460,10 +38460,10 @@
       </c>
       <c r="AC379" t="inlineStr"/>
       <c r="AD379" t="n">
-        <v>3.317905276324246</v>
+        <v>1.758516651748832</v>
       </c>
       <c r="AE379" t="n">
-        <v>0.06635810552648491</v>
+        <v>0.03517033303497663</v>
       </c>
     </row>
     <row r="380">
@@ -38516,28 +38516,28 @@
         <v>2</v>
       </c>
       <c r="O380" t="n">
-        <v>0.1669980959623882</v>
+        <v>0.1675011224249515</v>
       </c>
       <c r="P380" t="n">
-        <v>0.3866322058421756</v>
+        <v>0.3865535043308641</v>
       </c>
       <c r="Q380" t="n">
-        <v>0.4463696981954363</v>
+        <v>0.4459453732441845</v>
       </c>
       <c r="R380" t="n">
         <v>1</v>
       </c>
       <c r="S380" t="n">
-        <v>-0.06590055897807801</v>
+        <v>-0.06632488392932973</v>
       </c>
       <c r="T380" t="n">
         <v>2</v>
       </c>
       <c r="U380" t="n">
-        <v>-0.06590055897807801</v>
+        <v>-0.06632488392932973</v>
       </c>
       <c r="V380" t="n">
-        <v>0.4463696981954363</v>
+        <v>0.4459453732441845</v>
       </c>
       <c r="W380" t="n">
         <v>1.83</v>
@@ -38549,7 +38549,7 @@
       </c>
       <c r="Y380" t="inlineStr"/>
       <c r="Z380" t="n">
-        <v>0.7092445293022357</v>
+        <v>0.7084370703004019</v>
       </c>
       <c r="AA380" t="inlineStr">
         <is>
@@ -38563,10 +38563,10 @@
       </c>
       <c r="AC380" t="inlineStr"/>
       <c r="AD380" t="n">
-        <v>-22.06547618100621</v>
+        <v>-22.15903216423401</v>
       </c>
       <c r="AE380" t="n">
-        <v>-0.4413095236201243</v>
+        <v>-0.4431806432846802</v>
       </c>
     </row>
     <row r="381">
@@ -39031,28 +39031,28 @@
         <v>2</v>
       </c>
       <c r="O385" t="n">
-        <v>0.08973593565029485</v>
+        <v>0.09018482993288715</v>
       </c>
       <c r="P385" t="n">
-        <v>0.4100188559815401</v>
+        <v>0.4100386714906</v>
       </c>
       <c r="Q385" t="n">
-        <v>0.500245208368165</v>
+        <v>0.4997764985765128</v>
       </c>
       <c r="R385" t="n">
         <v>1</v>
       </c>
       <c r="S385" t="n">
-        <v>-0.2789755708526143</v>
+        <v>-0.2794442806442665</v>
       </c>
       <c r="T385" t="n">
         <v>2</v>
       </c>
       <c r="U385" t="n">
-        <v>-0.2789755708526143</v>
+        <v>-0.2794442806442665</v>
       </c>
       <c r="V385" t="n">
-        <v>0.500245208368165</v>
+        <v>0.4997764985765128</v>
       </c>
       <c r="W385" t="n">
         <v>1.2</v>
@@ -39064,7 +39064,7 @@
       </c>
       <c r="Y385" t="inlineStr"/>
       <c r="Z385" t="n">
-        <v>0.03268417827542294</v>
+        <v>0.0325041500601822</v>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
@@ -39078,10 +39078,10 @@
       </c>
       <c r="AC385" t="inlineStr"/>
       <c r="AD385" t="n">
-        <v>-199.852874979101</v>
+        <v>-200.1341008540924</v>
       </c>
       <c r="AE385" t="n">
-        <v>-3.997057499582021</v>
+        <v>-4.002682017081848</v>
       </c>
     </row>
     <row r="386">
@@ -39337,43 +39337,43 @@
         <v>0.06449588193870359</v>
       </c>
       <c r="N388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O388" t="n">
-        <v>0.3707099854946136</v>
+        <v>0.4555390179157257</v>
       </c>
       <c r="P388" t="n">
-        <v>0.3809841573238373</v>
+        <v>0.3114481568336487</v>
       </c>
       <c r="Q388" t="n">
-        <v>0.2483058571815491</v>
+        <v>0.233012855052948</v>
       </c>
       <c r="R388" t="n">
         <v>1</v>
       </c>
       <c r="S388" t="n">
-        <v>0.1200364331561519</v>
+        <v>-0.0362996244945713</v>
       </c>
       <c r="T388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U388" t="n">
-        <v>0.1200364331561519</v>
+        <v>-0.0362996244945713</v>
       </c>
       <c r="V388" t="n">
-        <v>0.3809841573238373</v>
+        <v>0.4555390179157257</v>
       </c>
       <c r="W388" t="n">
-        <v>3.6</v>
+        <v>1.91</v>
       </c>
       <c r="X388" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y388" t="inlineStr"/>
       <c r="Z388" t="n">
-        <v>4.421678553541527</v>
+        <v>3.322997153937215</v>
       </c>
       <c r="AA388" t="inlineStr">
         <is>
@@ -39387,10 +39387,10 @@
       </c>
       <c r="AC388" t="inlineStr"/>
       <c r="AD388" t="n">
-        <v>14.29011409099286</v>
+        <v>-14.27697536054549</v>
       </c>
       <c r="AE388" t="n">
-        <v>0.2858022818198571</v>
+        <v>-0.2855395072109097</v>
       </c>
     </row>
     <row r="389">
@@ -39419,64 +39419,64 @@
         <v>771</v>
       </c>
       <c r="G389" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="H389" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I389" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J389" t="n">
-        <v>0.2606635071090047</v>
+        <v>0.2478111914731633</v>
       </c>
       <c r="K389" t="n">
-        <v>0.3127962085308056</v>
+        <v>0.303768557289684</v>
       </c>
       <c r="L389" t="n">
-        <v>0.4265402843601895</v>
+        <v>0.4484202512371526</v>
       </c>
       <c r="M389" t="n">
-        <v>0.06565656565656575</v>
+        <v>0.06192901608860857</v>
       </c>
       <c r="N389" t="n">
         <v>0</v>
       </c>
       <c r="O389" t="n">
-        <v>0.2407787889242172</v>
+        <v>0.229819729924202</v>
       </c>
       <c r="P389" t="n">
-        <v>0.4815475344657898</v>
+        <v>0.419565886259079</v>
       </c>
       <c r="Q389" t="n">
-        <v>0.277673751115799</v>
+        <v>0.3506143987178802</v>
       </c>
       <c r="R389" t="n">
         <v>1</v>
       </c>
       <c r="S389" t="n">
-        <v>0.1687513259349842</v>
+        <v>0.1157973289693949</v>
       </c>
       <c r="T389" t="n">
         <v>0</v>
       </c>
       <c r="U389" t="n">
-        <v>0.1687513259349842</v>
+        <v>0.1157973289693949</v>
       </c>
       <c r="V389" t="n">
-        <v>0.4815475344657898</v>
+        <v>0.419565886259079</v>
       </c>
       <c r="W389" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X389" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y389" t="inlineStr"/>
       <c r="Z389" t="n">
-        <v>4.719028315433033</v>
+        <v>4.422693615227984</v>
       </c>
       <c r="AA389" t="inlineStr">
         <is>
@@ -39490,10 +39490,10 @@
       </c>
       <c r="AC389" t="inlineStr"/>
       <c r="AD389" t="n">
-        <v>22.23213016986847</v>
+        <v>14.31686892395928</v>
       </c>
       <c r="AE389" t="n">
-        <v>0.4446426033973694</v>
+        <v>0.2863373784791856</v>
       </c>
     </row>
     <row r="390">
@@ -39522,7 +39522,7 @@
         <v>771</v>
       </c>
       <c r="G390" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="H390" t="n">
         <v>4.5</v>
@@ -39531,55 +39531,55 @@
         <v>8</v>
       </c>
       <c r="J390" t="n">
-        <v>0.676056338028169</v>
+        <v>0.6728971962616822</v>
       </c>
       <c r="K390" t="n">
-        <v>0.2073239436619718</v>
+        <v>0.2093457943925233</v>
       </c>
       <c r="L390" t="n">
-        <v>0.1166197183098591</v>
+        <v>0.1177570093457944</v>
       </c>
       <c r="M390" t="n">
-        <v>0.07185990338164272</v>
+        <v>0.06150793650793651</v>
       </c>
       <c r="N390" t="n">
         <v>1</v>
       </c>
       <c r="O390" t="n">
-        <v>0.6118006706237793</v>
+        <v>0.5407603979110718</v>
       </c>
       <c r="P390" t="n">
-        <v>0.1970229148864746</v>
+        <v>0.2689046859741211</v>
       </c>
       <c r="Q390" t="n">
-        <v>0.1911764591932297</v>
+        <v>0.1903348863124847</v>
       </c>
       <c r="R390" t="n">
         <v>1</v>
       </c>
       <c r="S390" t="n">
-        <v>-0.0642556674043897</v>
+        <v>-0.1321367983506104</v>
       </c>
       <c r="T390" t="n">
         <v>1</v>
       </c>
       <c r="U390" t="n">
-        <v>-0.0642556674043897</v>
+        <v>-0.1321367983506104</v>
       </c>
       <c r="V390" t="n">
-        <v>0.6118006706237793</v>
+        <v>0.5407603979110718</v>
       </c>
       <c r="W390" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X390" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y390" t="inlineStr"/>
       <c r="Z390" t="n">
-        <v>2.368622800881497</v>
+        <v>1.772444826141101</v>
       </c>
       <c r="AA390" t="inlineStr">
         <is>
@@ -39593,10 +39593,10 @@
       </c>
       <c r="AC390" t="inlineStr"/>
       <c r="AD390" t="n">
-        <v>-40.97765119452228</v>
+        <v>-60.7338607311249</v>
       </c>
       <c r="AE390" t="n">
-        <v>-0.8195530238904456</v>
+        <v>-1.214677214622498</v>
       </c>
     </row>
     <row r="391">
@@ -39631,58 +39631,58 @@
         <v>3.25</v>
       </c>
       <c r="I391" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J391" t="n">
-        <v>0.4592557701365992</v>
+        <v>0.4607779125081616</v>
       </c>
       <c r="K391" t="n">
-        <v>0.2896844088553933</v>
+        <v>0.290644529428225</v>
       </c>
       <c r="L391" t="n">
-        <v>0.2510598210080076</v>
+        <v>0.2485775580636135</v>
       </c>
       <c r="M391" t="n">
-        <v>0.06216385240775479</v>
+        <v>0.05865508047793022</v>
       </c>
       <c r="N391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O391" t="n">
-        <v>0.3887141346931458</v>
+        <v>0.4482164680957794</v>
       </c>
       <c r="P391" t="n">
-        <v>0.4021904170513153</v>
+        <v>0.3220472037792206</v>
       </c>
       <c r="Q391" t="n">
-        <v>0.2090954631567001</v>
+        <v>0.2297362983226776</v>
       </c>
       <c r="R391" t="n">
         <v>1</v>
       </c>
       <c r="S391" t="n">
-        <v>0.112506008195922</v>
+        <v>-0.01256144441238222</v>
       </c>
       <c r="T391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U391" t="n">
-        <v>0.112506008195922</v>
+        <v>-0.01256144441238222</v>
       </c>
       <c r="V391" t="n">
-        <v>0.4021904170513153</v>
+        <v>0.4482164680957794</v>
       </c>
       <c r="W391" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="X391" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y391" t="inlineStr"/>
       <c r="Z391" t="n">
-        <v>4.397359967987123</v>
+        <v>3.573403001735672</v>
       </c>
       <c r="AA391" t="inlineStr">
         <is>
@@ -39696,10 +39696,10 @@
       </c>
       <c r="AC391" t="inlineStr"/>
       <c r="AD391" t="n">
-        <v>13.64972690741221</v>
+        <v>-7.729165752728784</v>
       </c>
       <c r="AE391" t="n">
-        <v>0.2729945381482443</v>
+        <v>-0.1545833150545757</v>
       </c>
     </row>
     <row r="392">
@@ -39728,64 +39728,64 @@
         <v>771</v>
       </c>
       <c r="G392" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="H392" t="n">
         <v>3.5</v>
       </c>
       <c r="I392" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="J392" t="n">
-        <v>0.1693548387096774</v>
+        <v>0.1643123199100429</v>
       </c>
       <c r="K392" t="n">
-        <v>0.2661290322580645</v>
+        <v>0.2699416684236418</v>
       </c>
       <c r="L392" t="n">
-        <v>0.564516129032258</v>
+        <v>0.5657460116663153</v>
       </c>
       <c r="M392" t="n">
-        <v>0.07359307359307365</v>
+        <v>0.05842972440212746</v>
       </c>
       <c r="N392" t="n">
         <v>2</v>
       </c>
       <c r="O392" t="n">
-        <v>0.1967838853597641</v>
+        <v>0.2226104885339737</v>
       </c>
       <c r="P392" t="n">
-        <v>0.3952086269855499</v>
+        <v>0.3797981739044189</v>
       </c>
       <c r="Q392" t="n">
-        <v>0.4080075025558472</v>
+        <v>0.3975913524627686</v>
       </c>
       <c r="R392" t="n">
         <v>1</v>
       </c>
       <c r="S392" t="n">
-        <v>-0.1565086264764108</v>
+        <v>-0.1681546592035468</v>
       </c>
       <c r="T392" t="n">
         <v>2</v>
       </c>
       <c r="U392" t="n">
-        <v>-0.1565086264764108</v>
+        <v>-0.1681546592035468</v>
       </c>
       <c r="V392" t="n">
-        <v>0.4080075025558472</v>
+        <v>0.3975913524627686</v>
       </c>
       <c r="W392" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X392" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y392" t="inlineStr"/>
       <c r="Z392" t="n">
-        <v>2.074365822863361</v>
+        <v>2.078086237775435</v>
       </c>
       <c r="AA392" t="inlineStr">
         <is>
@@ -39799,10 +39799,10 @@
       </c>
       <c r="AC392" t="inlineStr"/>
       <c r="AD392" t="n">
-        <v>-50.27501858197727</v>
+        <v>-50.1526031921159</v>
       </c>
       <c r="AE392" t="n">
-        <v>-1.005500371639545</v>
+        <v>-1.003052063842318</v>
       </c>
     </row>
     <row r="393">
@@ -39855,40 +39855,40 @@
         <v>0</v>
       </c>
       <c r="O393" t="n">
-        <v>0.2051650583744049</v>
+        <v>0.2736625373363495</v>
       </c>
       <c r="P393" t="n">
-        <v>0.4007787704467773</v>
+        <v>0.3879785537719727</v>
       </c>
       <c r="Q393" t="n">
-        <v>0.3940562009811401</v>
+        <v>0.3383588790893555</v>
       </c>
       <c r="R393" t="n">
         <v>1</v>
       </c>
       <c r="S393" t="n">
-        <v>0.1122877218534269</v>
+        <v>0.0994875051786222</v>
       </c>
       <c r="T393" t="n">
         <v>0</v>
       </c>
       <c r="U393" t="n">
-        <v>0.1122877218534269</v>
+        <v>0.0994875051786222</v>
       </c>
       <c r="V393" t="n">
-        <v>0.4007787704467773</v>
+        <v>0.3879785537719727</v>
       </c>
       <c r="W393" t="n">
         <v>3.25</v>
       </c>
       <c r="X393" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y393" t="inlineStr"/>
       <c r="Z393" t="n">
-        <v>4.389607765574908</v>
+        <v>4.319128672295433</v>
       </c>
       <c r="AA393" t="inlineStr">
         <is>
@@ -39902,10 +39902,10 @@
       </c>
       <c r="AC393" t="inlineStr"/>
       <c r="AD393" t="n">
-        <v>13.44582239786784</v>
+        <v>11.59690221150716</v>
       </c>
       <c r="AE393" t="n">
-        <v>0.2689164479573568</v>
+        <v>0.2319380442301432</v>
       </c>
     </row>
     <row r="394">
@@ -39955,43 +39955,43 @@
         <v>0.05969469127363869</v>
       </c>
       <c r="N394" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O394" t="n">
-        <v>0.2839991748332977</v>
+        <v>0.277310848236084</v>
       </c>
       <c r="P394" t="n">
-        <v>0.3246980309486389</v>
+        <v>0.4322807788848877</v>
       </c>
       <c r="Q394" t="n">
-        <v>0.391302764415741</v>
+        <v>0.2904083728790283</v>
       </c>
       <c r="R394" t="n">
         <v>1</v>
       </c>
       <c r="S394" t="n">
-        <v>-0.1806172527848611</v>
+        <v>0.183947087205679</v>
       </c>
       <c r="T394" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U394" t="n">
-        <v>-0.1806172527848611</v>
+        <v>0.183947087205679</v>
       </c>
       <c r="V394" t="n">
-        <v>0.391302764415741</v>
+        <v>0.4322807788848877</v>
       </c>
       <c r="W394" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="X394" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y394" t="inlineStr"/>
       <c r="Z394" t="n">
-        <v>1.948125900469534</v>
+        <v>4.745540953559955</v>
       </c>
       <c r="AA394" t="inlineStr">
         <is>
@@ -40005,10 +40005,10 @@
       </c>
       <c r="AC394" t="inlineStr"/>
       <c r="AD394" t="n">
-        <v>-54.51545210985038</v>
+        <v>22.9523914200919</v>
       </c>
       <c r="AE394" t="n">
-        <v>-1.090309042197008</v>
+        <v>0.459047828401838</v>
       </c>
     </row>
     <row r="395">
@@ -40058,43 +40058,43 @@
         <v>0.06644514567978321</v>
       </c>
       <c r="N395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O395" t="n">
-        <v>0.2547066509723663</v>
+        <v>0.4131496548652649</v>
       </c>
       <c r="P395" t="n">
-        <v>0.4998339414596558</v>
+        <v>0.3523286283016205</v>
       </c>
       <c r="Q395" t="n">
-        <v>0.2454594075679779</v>
+        <v>0.234521672129631</v>
       </c>
       <c r="R395" t="n">
         <v>1</v>
       </c>
       <c r="S395" t="n">
-        <v>0.1973517683557893</v>
+        <v>0.07216975063908809</v>
       </c>
       <c r="T395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U395" t="n">
-        <v>0.1973517683557893</v>
+        <v>0.07216975063908809</v>
       </c>
       <c r="V395" t="n">
-        <v>0.4998339414596558</v>
+        <v>0.4131496548652649</v>
       </c>
       <c r="W395" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="X395" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y395" t="inlineStr"/>
       <c r="Z395" t="n">
-        <v>4.862751560675377</v>
+        <v>4.172756163879149</v>
       </c>
       <c r="AA395" t="inlineStr">
         <is>
@@ -40108,10 +40108,10 @@
       </c>
       <c r="AC395" t="inlineStr"/>
       <c r="AD395" t="n">
-        <v>26.16596278690156</v>
+        <v>7.780660050255911</v>
       </c>
       <c r="AE395" t="n">
-        <v>0.5233192557380313</v>
+        <v>0.1556132010051182</v>
       </c>
     </row>
     <row r="396">
@@ -40146,58 +40146,58 @@
         <v>3.75</v>
       </c>
       <c r="I396" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="J396" t="n">
-        <v>0.2264963612060003</v>
+        <v>0.2245508982035928</v>
       </c>
       <c r="K396" t="n">
-        <v>0.2536759245507204</v>
+        <v>0.2514970059880239</v>
       </c>
       <c r="L396" t="n">
-        <v>0.5198277142432793</v>
+        <v>0.5239520958083832</v>
       </c>
       <c r="M396" t="n">
-        <v>0.05120999219359867</v>
+        <v>0.06031746031746033</v>
       </c>
       <c r="N396" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O396" t="n">
-        <v>0.2347460687160492</v>
+        <v>0.2289363145828247</v>
       </c>
       <c r="P396" t="n">
-        <v>0.3904101252555847</v>
+        <v>0.3368021845817566</v>
       </c>
       <c r="Q396" t="n">
-        <v>0.3748438358306885</v>
+        <v>0.4342615604400635</v>
       </c>
       <c r="R396" t="n">
         <v>1</v>
       </c>
       <c r="S396" t="n">
-        <v>0.1367342007048644</v>
+        <v>-0.08969053536831972</v>
       </c>
       <c r="T396" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U396" t="n">
-        <v>0.1367342007048644</v>
+        <v>-0.08969053536831972</v>
       </c>
       <c r="V396" t="n">
-        <v>0.3904101252555847</v>
+        <v>0.4342615604400635</v>
       </c>
       <c r="W396" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="X396" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y396" t="inlineStr"/>
       <c r="Z396" t="n">
-        <v>4.519337485526357</v>
+        <v>2.840827902245843</v>
       </c>
       <c r="AA396" t="inlineStr">
         <is>
@@ -40211,10 +40211,10 @@
       </c>
       <c r="AC396" t="inlineStr"/>
       <c r="AD396" t="n">
-        <v>16.87410798939792</v>
+        <v>-27.29114890098572</v>
       </c>
       <c r="AE396" t="n">
-        <v>0.3374821597879583</v>
+        <v>-0.5458229780197144</v>
       </c>
     </row>
     <row r="397">
@@ -40243,64 +40243,64 @@
         <v>771</v>
       </c>
       <c r="G397" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="H397" t="n">
         <v>3</v>
       </c>
       <c r="I397" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J397" t="n">
-        <v>0.4179104477611941</v>
+        <v>0.3976861894432394</v>
       </c>
       <c r="K397" t="n">
-        <v>0.3134328358208956</v>
+        <v>0.3154977102916365</v>
       </c>
       <c r="L397" t="n">
-        <v>0.2686567164179105</v>
+        <v>0.2868161002651242</v>
       </c>
       <c r="M397" t="n">
-        <v>0.06349206349206327</v>
+        <v>0.05653170359052706</v>
       </c>
       <c r="N397" t="n">
         <v>0</v>
       </c>
       <c r="O397" t="n">
-        <v>0.2750804722309113</v>
+        <v>0.3031558096408844</v>
       </c>
       <c r="P397" t="n">
-        <v>0.4914714097976685</v>
+        <v>0.4847221970558167</v>
       </c>
       <c r="Q397" t="n">
-        <v>0.2334481477737427</v>
+        <v>0.2121219485998154</v>
       </c>
       <c r="R397" t="n">
         <v>1</v>
       </c>
       <c r="S397" t="n">
-        <v>0.1780385739767729</v>
+        <v>0.1692244867641801</v>
       </c>
       <c r="T397" t="n">
         <v>0</v>
       </c>
       <c r="U397" t="n">
-        <v>0.1780385739767729</v>
+        <v>0.1692244867641801</v>
       </c>
       <c r="V397" t="n">
-        <v>0.4914714097976685</v>
+        <v>0.4847221970558167</v>
       </c>
       <c r="W397" t="n">
         <v>3</v>
       </c>
       <c r="X397" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y397" t="inlineStr"/>
       <c r="Z397" t="n">
-        <v>4.773727756281637</v>
+        <v>4.736566615024762</v>
       </c>
       <c r="AA397" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
       </c>
       <c r="AC397" t="inlineStr"/>
       <c r="AD397" t="n">
-        <v>23.72071146965027</v>
+        <v>22.7083295583725</v>
       </c>
       <c r="AE397" t="n">
-        <v>0.4744142293930054</v>
+        <v>0.45416659116745</v>
       </c>
     </row>
     <row r="398">
@@ -40346,64 +40346,64 @@
         <v>771</v>
       </c>
       <c r="G398" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="H398" t="n">
         <v>3.4</v>
       </c>
       <c r="I398" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J398" t="n">
-        <v>0.4509283819628648</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="K398" t="n">
-        <v>0.2785145888594165</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="L398" t="n">
-        <v>0.2705570291777188</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="M398" t="n">
-        <v>0.05602240896358524</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="N398" t="n">
         <v>0</v>
       </c>
       <c r="O398" t="n">
-        <v>0.2727443277835846</v>
+        <v>0.3143502473831177</v>
       </c>
       <c r="P398" t="n">
-        <v>0.5135457515716553</v>
+        <v>0.3924648463726044</v>
       </c>
       <c r="Q398" t="n">
-        <v>0.2137099206447601</v>
+        <v>0.293184906244278</v>
       </c>
       <c r="R398" t="n">
         <v>1</v>
       </c>
       <c r="S398" t="n">
-        <v>0.2350311627122388</v>
+        <v>0.1149168960153272</v>
       </c>
       <c r="T398" t="n">
         <v>0</v>
       </c>
       <c r="U398" t="n">
-        <v>0.2350311627122388</v>
+        <v>0.1149168960153272</v>
       </c>
       <c r="V398" t="n">
-        <v>0.5135457515716553</v>
+        <v>0.3924648463726044</v>
       </c>
       <c r="W398" t="n">
         <v>3.4</v>
       </c>
       <c r="X398" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y398" t="inlineStr"/>
       <c r="Z398" t="n">
-        <v>5.038423912602905</v>
+        <v>4.408104305573904</v>
       </c>
       <c r="AA398" t="inlineStr">
         <is>
@@ -40417,10 +40417,10 @@
       </c>
       <c r="AC398" t="inlineStr"/>
       <c r="AD398" t="n">
-        <v>31.08564813931783</v>
+        <v>13.93251990278562</v>
       </c>
       <c r="AE398" t="n">
-        <v>0.6217129627863566</v>
+        <v>0.2786503980557123</v>
       </c>
     </row>
     <row r="399">
@@ -40449,64 +40449,64 @@
         <v>771</v>
       </c>
       <c r="G399" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H399" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I399" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J399" t="n">
-        <v>0.4471544715447154</v>
+        <v>0.4283464566929133</v>
       </c>
       <c r="K399" t="n">
-        <v>0.2845528455284553</v>
+        <v>0.2944881889763779</v>
       </c>
       <c r="L399" t="n">
-        <v>0.2682926829268292</v>
+        <v>0.2771653543307087</v>
       </c>
       <c r="M399" t="n">
-        <v>0.06493506493506507</v>
+        <v>0.06116310160427818</v>
       </c>
       <c r="N399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O399" t="n">
-        <v>0.3790987432003021</v>
+        <v>0.390830397605896</v>
       </c>
       <c r="P399" t="n">
-        <v>0.4228127300739288</v>
+        <v>0.3785349428653717</v>
       </c>
       <c r="Q399" t="n">
-        <v>0.1980884820222855</v>
+        <v>0.2306346595287323</v>
       </c>
       <c r="R399" t="n">
         <v>1</v>
       </c>
       <c r="S399" t="n">
-        <v>0.1382598845454736</v>
+        <v>-0.03751605908701733</v>
       </c>
       <c r="T399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U399" t="n">
-        <v>0.1382598845454736</v>
+        <v>-0.03751605908701733</v>
       </c>
       <c r="V399" t="n">
-        <v>0.4228127300739288</v>
+        <v>0.390830397605896</v>
       </c>
       <c r="W399" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="X399" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y399" t="inlineStr"/>
       <c r="Z399" t="n">
-        <v>4.531077175621822</v>
+        <v>3.421832325895922</v>
       </c>
       <c r="AA399" t="inlineStr">
         <is>
@@ -40520,10 +40520,10 @@
       </c>
       <c r="AC399" t="inlineStr"/>
       <c r="AD399" t="n">
-        <v>17.186174314955</v>
+        <v>-11.68109377225239</v>
       </c>
       <c r="AE399" t="n">
-        <v>0.3437234862991001</v>
+        <v>-0.2336218754450478</v>
       </c>
     </row>
     <row r="400">
@@ -40576,40 +40576,40 @@
         <v>1</v>
       </c>
       <c r="O400" t="n">
-        <v>0.5880753993988037</v>
+        <v>0.4581892788410187</v>
       </c>
       <c r="P400" t="n">
-        <v>0.2146428823471069</v>
+        <v>0.3139846622943878</v>
       </c>
       <c r="Q400" t="n">
-        <v>0.1972817182540894</v>
+        <v>0.2278260737657547</v>
       </c>
       <c r="R400" t="n">
         <v>1</v>
       </c>
       <c r="S400" t="n">
-        <v>-0.1076121514555495</v>
+        <v>-0.2374982720133345</v>
       </c>
       <c r="T400" t="n">
         <v>1</v>
       </c>
       <c r="U400" t="n">
-        <v>-0.1076121514555495</v>
+        <v>-0.2374982720133345</v>
       </c>
       <c r="V400" t="n">
-        <v>0.5880753993988037</v>
+        <v>0.4581892788410187</v>
       </c>
       <c r="W400" t="n">
         <v>1.36</v>
       </c>
       <c r="X400" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y400" t="inlineStr"/>
       <c r="Z400" t="n">
-        <v>1.91620968213335</v>
+        <v>0.849633141370759</v>
       </c>
       <c r="AA400" t="inlineStr">
         <is>
@@ -40623,10 +40623,10 @@
       </c>
       <c r="AC400" t="inlineStr"/>
       <c r="AD400" t="n">
-        <v>-55.61596022711856</v>
+        <v>-104.6840502156151</v>
       </c>
       <c r="AE400" t="n">
-        <v>-1.112319204542371</v>
+        <v>-2.093681004312303</v>
       </c>
     </row>
     <row r="401">
@@ -40676,43 +40676,43 @@
         <v>0.05555555555555558</v>
       </c>
       <c r="N401" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O401" t="n">
-        <v>0.2532491683959961</v>
+        <v>0.2810186743736267</v>
       </c>
       <c r="P401" t="n">
-        <v>0.4272058010101318</v>
+        <v>0.3277459740638733</v>
       </c>
       <c r="Q401" t="n">
-        <v>0.3195449709892273</v>
+        <v>0.3912353515625</v>
       </c>
       <c r="R401" t="n">
         <v>1</v>
       </c>
       <c r="S401" t="n">
-        <v>0.1640479062732897</v>
+        <v>-0.08244885896381576</v>
       </c>
       <c r="T401" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U401" t="n">
-        <v>0.1640479062732897</v>
+        <v>-0.08244885896381576</v>
       </c>
       <c r="V401" t="n">
-        <v>0.4272058010101318</v>
+        <v>0.3912353515625</v>
       </c>
       <c r="W401" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="X401" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y401" t="inlineStr"/>
       <c r="Z401" t="n">
-        <v>4.661985844183937</v>
+        <v>3.042834635866988</v>
       </c>
       <c r="AA401" t="inlineStr">
         <is>
@@ -40726,10 +40726,10 @@
       </c>
       <c r="AC401" t="inlineStr"/>
       <c r="AD401" t="n">
-        <v>20.69003398601826</v>
+        <v>-21.7529296875</v>
       </c>
       <c r="AE401" t="n">
-        <v>0.4138006797203652</v>
+        <v>-0.43505859375</v>
       </c>
     </row>
     <row r="402">
@@ -40782,40 +40782,40 @@
         <v>1</v>
       </c>
       <c r="O402" t="n">
-        <v>0.5402875542640686</v>
+        <v>0.4912830591201782</v>
       </c>
       <c r="P402" t="n">
-        <v>0.2680294513702393</v>
+        <v>0.2733020484447479</v>
       </c>
       <c r="Q402" t="n">
-        <v>0.1916830092668533</v>
+        <v>0.2354148924350739</v>
       </c>
       <c r="R402" t="n">
         <v>1</v>
       </c>
       <c r="S402" t="n">
-        <v>-0.1187874879492059</v>
+        <v>-0.1677919830930963</v>
       </c>
       <c r="T402" t="n">
         <v>1</v>
       </c>
       <c r="U402" t="n">
-        <v>-0.1187874879492059</v>
+        <v>-0.1677919830930963</v>
       </c>
       <c r="V402" t="n">
-        <v>0.5402875542640686</v>
+        <v>0.4912830591201782</v>
       </c>
       <c r="W402" t="n">
         <v>1.42</v>
       </c>
       <c r="X402" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y402" t="inlineStr"/>
       <c r="Z402" t="n">
-        <v>1.92167662372342</v>
+        <v>1.483486439464415</v>
       </c>
       <c r="AA402" t="inlineStr">
         <is>
@@ -40829,10 +40829,10 @@
       </c>
       <c r="AC402" t="inlineStr"/>
       <c r="AD402" t="n">
-        <v>-55.42658879643396</v>
+        <v>-71.99477524984452</v>
       </c>
       <c r="AE402" t="n">
-        <v>-1.108531775928679</v>
+        <v>-1.43989550499689</v>
       </c>
     </row>
     <row r="403">
@@ -40885,40 +40885,40 @@
         <v>1</v>
       </c>
       <c r="O403" t="n">
-        <v>0.4984340965747833</v>
+        <v>0.4295498132705688</v>
       </c>
       <c r="P403" t="n">
-        <v>0.3016817271709442</v>
+        <v>0.3659041523933411</v>
       </c>
       <c r="Q403" t="n">
-        <v>0.1998841911554337</v>
+        <v>0.2045460790395737</v>
       </c>
       <c r="R403" t="n">
         <v>1</v>
       </c>
       <c r="S403" t="n">
-        <v>0.02570682384751061</v>
+        <v>-0.04317745945670387</v>
       </c>
       <c r="T403" t="n">
         <v>1</v>
       </c>
       <c r="U403" t="n">
-        <v>0.02570682384751061</v>
+        <v>-0.04317745945670387</v>
       </c>
       <c r="V403" t="n">
-        <v>0.4984340965747833</v>
+        <v>0.4295498132705688</v>
       </c>
       <c r="W403" t="n">
         <v>2</v>
       </c>
       <c r="X403" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y403" t="inlineStr"/>
       <c r="Z403" t="n">
-        <v>3.859962008037489</v>
+        <v>3.330091872102586</v>
       </c>
       <c r="AA403" t="inlineStr">
         <is>
@@ -40932,10 +40932,10 @@
       </c>
       <c r="AC403" t="inlineStr"/>
       <c r="AD403" t="n">
-        <v>-0.313180685043335</v>
+        <v>-14.09003734588623</v>
       </c>
       <c r="AE403" t="n">
-        <v>-0.006263613700866699</v>
+        <v>-0.2818007469177246</v>
       </c>
     </row>
     <row r="404">
@@ -40988,40 +40988,40 @@
         <v>1</v>
       </c>
       <c r="O404" t="n">
-        <v>0.5579578280448914</v>
+        <v>0.5241793990135193</v>
       </c>
       <c r="P404" t="n">
-        <v>0.2512670159339905</v>
+        <v>0.2750292420387268</v>
       </c>
       <c r="Q404" t="n">
-        <v>0.1907751858234406</v>
+        <v>0.2007913738489151</v>
       </c>
       <c r="R404" t="n">
         <v>1</v>
       </c>
       <c r="S404" t="n">
-        <v>-0.03344002141747415</v>
+        <v>-0.06721845044884622</v>
       </c>
       <c r="T404" t="n">
         <v>1</v>
       </c>
       <c r="U404" t="n">
-        <v>-0.03344002141747415</v>
+        <v>-0.06721845044884622</v>
       </c>
       <c r="V404" t="n">
-        <v>0.5579578280448914</v>
+        <v>0.5241793990135193</v>
       </c>
       <c r="W404" t="n">
         <v>1.6</v>
       </c>
       <c r="X404" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y404" t="inlineStr"/>
       <c r="Z404" t="n">
-        <v>3.187122113791959</v>
+        <v>2.855436775002356</v>
       </c>
       <c r="AA404" t="inlineStr">
         <is>
@@ -41035,10 +41035,10 @@
       </c>
       <c r="AC404" t="inlineStr"/>
       <c r="AD404" t="n">
-        <v>-17.87791252136229</v>
+        <v>-26.88549359639485</v>
       </c>
       <c r="AE404" t="n">
-        <v>-0.3575582504272459</v>
+        <v>-0.537709871927897</v>
       </c>
     </row>
     <row r="405">
@@ -41088,43 +41088,43 @@
         <v>0.0599747474747474</v>
       </c>
       <c r="N405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O405" t="n">
-        <v>0.3982662856578827</v>
+        <v>0.4098120331764221</v>
       </c>
       <c r="P405" t="n">
-        <v>0.4135233759880066</v>
+        <v>0.3692823052406311</v>
       </c>
       <c r="Q405" t="n">
-        <v>0.1882103085517883</v>
+        <v>0.2209056466817856</v>
       </c>
       <c r="R405" t="n">
         <v>1</v>
       </c>
       <c r="S405" t="n">
-        <v>0.1187050317354753</v>
+        <v>-0.009485167538289041</v>
       </c>
       <c r="T405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U405" t="n">
-        <v>0.1187050317354753</v>
+        <v>-0.009485167538289041</v>
       </c>
       <c r="V405" t="n">
-        <v>0.4135233759880066</v>
+        <v>0.4098120331764221</v>
       </c>
       <c r="W405" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="X405" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y405" t="inlineStr"/>
       <c r="Z405" t="n">
-        <v>4.437005171721267</v>
+        <v>3.631021212398295</v>
       </c>
       <c r="AA405" t="inlineStr">
         <is>
@@ -41138,10 +41138,10 @@
       </c>
       <c r="AC405" t="inlineStr"/>
       <c r="AD405" t="n">
-        <v>14.69430923461914</v>
+        <v>-6.233834028244018</v>
       </c>
       <c r="AE405" t="n">
-        <v>0.2938861846923828</v>
+        <v>-0.1246766805648803</v>
       </c>
     </row>
     <row r="406">
@@ -41191,43 +41191,43 @@
         <v>0.06633486274204836</v>
       </c>
       <c r="N406" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O406" t="n">
-        <v>0.5426689982414246</v>
+        <v>0.2942396402359009</v>
       </c>
       <c r="P406" t="n">
-        <v>0.2397459447383881</v>
+        <v>0.4335629940032959</v>
       </c>
       <c r="Q406" t="n">
-        <v>0.2175850570201874</v>
+        <v>0.2721973657608032</v>
       </c>
       <c r="R406" t="n">
         <v>1</v>
       </c>
       <c r="S406" t="n">
-        <v>-0.01888292707946226</v>
+        <v>0.1656225039216156</v>
       </c>
       <c r="T406" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U406" t="n">
-        <v>-0.01888292707946226</v>
+        <v>0.1656225039216156</v>
       </c>
       <c r="V406" t="n">
-        <v>0.5426689982414246</v>
+        <v>0.4335629940032959</v>
       </c>
       <c r="W406" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="X406" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y406" t="inlineStr"/>
       <c r="Z406" t="n">
-        <v>3.33383465403003</v>
+        <v>4.662311851891576</v>
       </c>
       <c r="AA406" t="inlineStr">
         <is>
@@ -41241,10 +41241,10 @@
       </c>
       <c r="AC406" t="inlineStr"/>
       <c r="AD406" t="n">
-        <v>-13.99145864728673</v>
+        <v>20.69881916046143</v>
       </c>
       <c r="AE406" t="n">
-        <v>-0.2798291729457345</v>
+        <v>0.4139763832092285</v>
       </c>
     </row>
     <row r="407">
@@ -41294,43 +41294,43 @@
         <v>0.06833642547928265</v>
       </c>
       <c r="N407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O407" t="n">
-        <v>0.355811208486557</v>
+        <v>0.4296035468578339</v>
       </c>
       <c r="P407" t="n">
-        <v>0.3904175758361816</v>
+        <v>0.3527367413043976</v>
       </c>
       <c r="Q407" t="n">
-        <v>0.2537712454795837</v>
+        <v>0.2176597267389297</v>
       </c>
       <c r="R407" t="n">
         <v>1</v>
       </c>
       <c r="S407" t="n">
-        <v>0.1067706872688879</v>
+        <v>0.04754855409372394</v>
       </c>
       <c r="T407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U407" t="n">
-        <v>0.1067706872688879</v>
+        <v>0.04754855409372394</v>
       </c>
       <c r="V407" t="n">
-        <v>0.3904175758361816</v>
+        <v>0.4296035468578339</v>
       </c>
       <c r="W407" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="X407" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y407" t="inlineStr"/>
       <c r="Z407" t="n">
-        <v>4.355049644522281</v>
+        <v>4.012300195619332</v>
       </c>
       <c r="AA407" t="inlineStr">
         <is>
@@ -41344,10 +41344,10 @@
       </c>
       <c r="AC407" t="inlineStr"/>
       <c r="AD407" t="n">
-        <v>12.53817392432171</v>
+        <v>3.622668262185724</v>
       </c>
       <c r="AE407" t="n">
-        <v>0.2507634784864342</v>
+        <v>0.07245336524371448</v>
       </c>
     </row>
     <row r="408">
@@ -41386,13 +41386,13 @@
         <v>0</v>
       </c>
       <c r="O408" t="n">
-        <v>0.2392067015171051</v>
+        <v>0.2258505523204803</v>
       </c>
       <c r="P408" t="n">
-        <v>0.4226315915584564</v>
+        <v>0.4242788851261139</v>
       </c>
       <c r="Q408" t="n">
-        <v>0.3381616771221161</v>
+        <v>0.3498705923557281</v>
       </c>
       <c r="R408" t="n">
         <v>1</v>
@@ -41403,12 +41403,12 @@
       </c>
       <c r="U408" t="inlineStr"/>
       <c r="V408" t="n">
-        <v>0.5773684084415436</v>
+        <v>0.5757211148738861</v>
       </c>
       <c r="W408" t="inlineStr"/>
       <c r="X408" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y408" t="inlineStr"/>
@@ -41460,32 +41460,32 @@
       <c r="L409" t="inlineStr"/>
       <c r="M409" t="inlineStr"/>
       <c r="N409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O409" t="n">
-        <v>0.3399296402931213</v>
+        <v>0.3696960508823395</v>
       </c>
       <c r="P409" t="n">
-        <v>0.454637885093689</v>
+        <v>0.3662590682506561</v>
       </c>
       <c r="Q409" t="n">
-        <v>0.2054324597120285</v>
+        <v>0.2640449106693268</v>
       </c>
       <c r="R409" t="n">
         <v>1</v>
       </c>
       <c r="S409" t="inlineStr"/>
       <c r="T409" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U409" t="inlineStr"/>
       <c r="V409" t="n">
-        <v>0.545362114906311</v>
+        <v>0.6303039491176605</v>
       </c>
       <c r="W409" t="inlineStr"/>
       <c r="X409" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y409" t="inlineStr"/>
@@ -41540,13 +41540,13 @@
         <v>0</v>
       </c>
       <c r="O410" t="n">
-        <v>0.3932410478591919</v>
+        <v>0.3659267425537109</v>
       </c>
       <c r="P410" t="n">
-        <v>0.4201231896877289</v>
+        <v>0.4188465178012848</v>
       </c>
       <c r="Q410" t="n">
-        <v>0.1866357922554016</v>
+        <v>0.2152266949415207</v>
       </c>
       <c r="R410" t="n">
         <v>1</v>
@@ -41557,12 +41557,12 @@
       </c>
       <c r="U410" t="inlineStr"/>
       <c r="V410" t="n">
-        <v>0.5798768103122711</v>
+        <v>0.5811534821987152</v>
       </c>
       <c r="W410" t="inlineStr"/>
       <c r="X410" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y410" t="inlineStr"/>
@@ -41617,13 +41617,13 @@
         <v>2</v>
       </c>
       <c r="O411" t="n">
-        <v>0.2193145006895065</v>
+        <v>0.2375688552856445</v>
       </c>
       <c r="P411" t="n">
-        <v>0.3615515828132629</v>
+        <v>0.3329222202301025</v>
       </c>
       <c r="Q411" t="n">
-        <v>0.4191339612007141</v>
+        <v>0.4295089244842529</v>
       </c>
       <c r="R411" t="n">
         <v>1</v>
@@ -41634,12 +41634,12 @@
       </c>
       <c r="U411" t="inlineStr"/>
       <c r="V411" t="n">
-        <v>0.5808660387992859</v>
+        <v>0.5704910755157471</v>
       </c>
       <c r="W411" t="inlineStr"/>
       <c r="X411" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y411" t="inlineStr"/>
@@ -41691,32 +41691,32 @@
       <c r="L412" t="inlineStr"/>
       <c r="M412" t="inlineStr"/>
       <c r="N412" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O412" t="n">
-        <v>0.4081339836120605</v>
+        <v>0.2688276767730713</v>
       </c>
       <c r="P412" t="n">
-        <v>0.3379647433757782</v>
+        <v>0.4891399443149567</v>
       </c>
       <c r="Q412" t="n">
-        <v>0.2539012432098389</v>
+        <v>0.2420324236154556</v>
       </c>
       <c r="R412" t="n">
         <v>1</v>
       </c>
       <c r="S412" t="inlineStr"/>
       <c r="T412" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U412" t="inlineStr"/>
       <c r="V412" t="n">
-        <v>0.5918660163879395</v>
+        <v>0.5108600556850433</v>
       </c>
       <c r="W412" t="inlineStr"/>
       <c r="X412" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y412" t="inlineStr"/>
@@ -41771,13 +41771,13 @@
         <v>1</v>
       </c>
       <c r="O413" t="n">
-        <v>0.4542271494865417</v>
+        <v>0.5161313414573669</v>
       </c>
       <c r="P413" t="n">
-        <v>0.3409821391105652</v>
+        <v>0.2838864624500275</v>
       </c>
       <c r="Q413" t="n">
-        <v>0.2047907114028931</v>
+        <v>0.199982225894928</v>
       </c>
       <c r="R413" t="n">
         <v>1</v>
@@ -41788,12 +41788,12 @@
       </c>
       <c r="U413" t="inlineStr"/>
       <c r="V413" t="n">
-        <v>0.5457728505134583</v>
+        <v>0.4838686585426331</v>
       </c>
       <c r="W413" t="inlineStr"/>
       <c r="X413" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y413" t="inlineStr"/>
@@ -41848,13 +41848,13 @@
         <v>1</v>
       </c>
       <c r="O414" t="n">
-        <v>0.5638784170150757</v>
+        <v>0.5492764115333557</v>
       </c>
       <c r="P414" t="n">
-        <v>0.2269687056541443</v>
+        <v>0.2409570813179016</v>
       </c>
       <c r="Q414" t="n">
-        <v>0.2091528922319412</v>
+        <v>0.2097665220499039</v>
       </c>
       <c r="R414" t="n">
         <v>1</v>
@@ -41865,12 +41865,12 @@
       </c>
       <c r="U414" t="inlineStr"/>
       <c r="V414" t="n">
-        <v>0.4361215829849243</v>
+        <v>0.4507235884666443</v>
       </c>
       <c r="W414" t="inlineStr"/>
       <c r="X414" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y414" t="inlineStr"/>
@@ -41925,13 +41925,13 @@
         <v>0</v>
       </c>
       <c r="O415" t="n">
-        <v>0.2376536726951599</v>
+        <v>0.2368633151054382</v>
       </c>
       <c r="P415" t="n">
-        <v>0.4278645217418671</v>
+        <v>0.4070692658424377</v>
       </c>
       <c r="Q415" t="n">
-        <v>0.3344818353652954</v>
+        <v>0.3560674488544464</v>
       </c>
       <c r="R415" t="n">
         <v>1</v>
@@ -41942,12 +41942,12 @@
       </c>
       <c r="U415" t="inlineStr"/>
       <c r="V415" t="n">
-        <v>0.5721354782581329</v>
+        <v>0.5929307341575623</v>
       </c>
       <c r="W415" t="inlineStr"/>
       <c r="X415" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y415" t="inlineStr"/>
@@ -41969,96 +41969,74 @@
     <row r="416">
       <c r="A416" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>Sp7nVfDF</t>
         </is>
       </c>
       <c r="B416" s="2" t="n">
-        <v>45583.66666666666</v>
+        <v>45596.69791666666</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F416" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G416" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="H416" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I416" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="J416" t="n">
-        <v>0.5689677299756157</v>
-      </c>
-      <c r="K416" t="n">
-        <v>0.2500463444892837</v>
-      </c>
-      <c r="L416" t="n">
-        <v>0.1809859255351006</v>
-      </c>
-      <c r="M416" t="n">
-        <v>0.0524364804226134</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr"/>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
       <c r="N416" t="n">
         <v>1</v>
       </c>
       <c r="O416" t="n">
-        <v>0.669661283493042</v>
+        <v>0.5628480911254883</v>
       </c>
       <c r="P416" t="n">
-        <v>0.2293326407670975</v>
+        <v>0.2632296681404114</v>
       </c>
       <c r="Q416" t="n">
-        <v>0.1010061129927635</v>
+        <v>0.1739222705364227</v>
       </c>
       <c r="R416" t="n">
         <v>1</v>
       </c>
-      <c r="S416" t="n">
-        <v>0.1006935535174263</v>
-      </c>
+      <c r="S416" t="inlineStr"/>
       <c r="T416" t="n">
-        <v>1</v>
-      </c>
-      <c r="U416" t="n">
-        <v>0.1006935535174263</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U416" t="inlineStr"/>
       <c r="V416" t="n">
-        <v>0.669661283493042</v>
-      </c>
-      <c r="W416" t="n">
-        <v>1.67</v>
-      </c>
+        <v>0.4371519088745117</v>
+      </c>
+      <c r="W416" t="inlineStr"/>
       <c r="X416" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y416" t="inlineStr"/>
-      <c r="Z416" t="n">
-        <v>6.934700859357118</v>
-      </c>
+      <c r="Z416" t="inlineStr"/>
       <c r="AA416" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB416" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC416" t="inlineStr"/>
@@ -42068,96 +42046,74 @@
     <row r="417">
       <c r="A417" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>p2kdKwac</t>
         </is>
       </c>
       <c r="B417" s="2" t="n">
-        <v>45584.375</v>
+        <v>45596.69791666666</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>como</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F417" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G417" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H417" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I417" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J417" t="n">
-        <v>0.6417212738428149</v>
-      </c>
-      <c r="K417" t="n">
-        <v>0.2316457281188698</v>
-      </c>
-      <c r="L417" t="n">
-        <v>0.1266329980383155</v>
-      </c>
-      <c r="M417" t="n">
-        <v>0.0529114480333992</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr"/>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
       <c r="N417" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O417" t="n">
-        <v>0.5714911818504333</v>
+        <v>0.2143705636262894</v>
       </c>
       <c r="P417" t="n">
-        <v>0.267119973897934</v>
+        <v>0.3562891185283661</v>
       </c>
       <c r="Q417" t="n">
-        <v>0.1613888591527939</v>
+        <v>0.4293403029441833</v>
       </c>
       <c r="R417" t="n">
         <v>1</v>
       </c>
-      <c r="S417" t="n">
-        <v>-0.0702300919923815</v>
-      </c>
+      <c r="S417" t="inlineStr"/>
       <c r="T417" t="n">
-        <v>1</v>
-      </c>
-      <c r="U417" t="n">
-        <v>-0.0702300919923815</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U417" t="inlineStr"/>
       <c r="V417" t="n">
-        <v>0.5714911818504333</v>
-      </c>
-      <c r="W417" t="n">
-        <v>1.48</v>
-      </c>
+        <v>0.5706596970558167</v>
+      </c>
+      <c r="W417" t="inlineStr"/>
       <c r="X417" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y417" t="inlineStr"/>
-      <c r="Z417" t="n">
-        <v>5.918096935843527</v>
-      </c>
+      <c r="Z417" t="inlineStr"/>
       <c r="AA417" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB417" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC417" t="inlineStr"/>
@@ -42167,20 +42123,20 @@
     <row r="418">
       <c r="A418" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B418" s="2" t="n">
-        <v>45584.46875</v>
+        <v>45583.66666666666</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E418" t="n">
@@ -42190,55 +42146,55 @@
         <v>1481</v>
       </c>
       <c r="G418" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="H418" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="I418" t="n">
-        <v>2.6</v>
+        <v>5.25</v>
       </c>
       <c r="J418" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.5689677299756157</v>
       </c>
       <c r="K418" t="n">
-        <v>0.2765957446808511</v>
+        <v>0.2500463444892837</v>
       </c>
       <c r="L418" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.1809859255351006</v>
       </c>
       <c r="M418" t="n">
-        <v>0.06334841628959276</v>
+        <v>0.0524364804226134</v>
       </c>
       <c r="N418" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O418" t="n">
-        <v>0.2668277025222778</v>
+        <v>0.669661283493042</v>
       </c>
       <c r="P418" t="n">
-        <v>0.3323536515235901</v>
+        <v>0.2293326407670975</v>
       </c>
       <c r="Q418" t="n">
-        <v>0.4008186161518097</v>
+        <v>0.1010061129927635</v>
       </c>
       <c r="R418" t="n">
         <v>1</v>
       </c>
       <c r="S418" t="n">
-        <v>0.03911648849223526</v>
+        <v>0.1006935535174263</v>
       </c>
       <c r="T418" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U418" t="n">
-        <v>0.03911648849223526</v>
+        <v>0.1006935535174263</v>
       </c>
       <c r="V418" t="n">
-        <v>0.4008186161518097</v>
+        <v>0.669661283493042</v>
       </c>
       <c r="W418" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="X418" t="inlineStr">
         <is>
@@ -42247,7 +42203,7 @@
       </c>
       <c r="Y418" t="inlineStr"/>
       <c r="Z418" t="n">
-        <v>4.15069120821163</v>
+        <v>6.934700859357118</v>
       </c>
       <c r="AA418" t="inlineStr">
         <is>
@@ -42266,20 +42222,20 @@
     <row r="419">
       <c r="A419" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B419" s="2" t="n">
-        <v>45584.5625</v>
+        <v>45584.375</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E419" t="n">
@@ -42289,55 +42245,55 @@
         <v>1481</v>
       </c>
       <c r="G419" t="n">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="H419" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="I419" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J419" t="n">
-        <v>0.3947157726180945</v>
+        <v>0.6499535747446611</v>
       </c>
       <c r="K419" t="n">
-        <v>0.2786228983186549</v>
+        <v>0.2243887341380377</v>
       </c>
       <c r="L419" t="n">
-        <v>0.3266613290632506</v>
+        <v>0.1256576911173011</v>
       </c>
       <c r="M419" t="n">
-        <v>0.05561189993238669</v>
+        <v>0.06108374384236459</v>
       </c>
       <c r="N419" t="n">
         <v>1</v>
       </c>
       <c r="O419" t="n">
-        <v>0.4895497262477875</v>
+        <v>0.5714911818504333</v>
       </c>
       <c r="P419" t="n">
-        <v>0.3255585432052612</v>
+        <v>0.267119973897934</v>
       </c>
       <c r="Q419" t="n">
-        <v>0.1848916709423065</v>
+        <v>0.1613888591527939</v>
       </c>
       <c r="R419" t="n">
         <v>1</v>
       </c>
       <c r="S419" t="n">
-        <v>0.09483395362969294</v>
+        <v>-0.07846239289422774</v>
       </c>
       <c r="T419" t="n">
         <v>1</v>
       </c>
       <c r="U419" t="n">
-        <v>0.09483395362969294</v>
+        <v>-0.07846239289422774</v>
       </c>
       <c r="V419" t="n">
-        <v>0.4895497262477875</v>
+        <v>0.5714911818504333</v>
       </c>
       <c r="W419" t="n">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="X419" t="inlineStr">
         <is>
@@ -42346,7 +42302,7 @@
       </c>
       <c r="Y419" t="inlineStr"/>
       <c r="Z419" t="n">
-        <v>5.069549324399381</v>
+        <v>5.918096935843527</v>
       </c>
       <c r="AA419" t="inlineStr">
         <is>
@@ -42365,20 +42321,20 @@
     <row r="420">
       <c r="A420" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B420" s="2" t="n">
-        <v>45584.66666666666</v>
+        <v>45584.46875</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E420" t="n">
@@ -42388,55 +42344,55 @@
         <v>1481</v>
       </c>
       <c r="G420" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="H420" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I420" t="n">
-        <v>1.6</v>
+        <v>2.63</v>
       </c>
       <c r="J420" t="n">
-        <v>0.2077922077922078</v>
+        <v>0.3677036001398113</v>
       </c>
       <c r="K420" t="n">
-        <v>0.2077922077922078</v>
+        <v>0.2757777001048585</v>
       </c>
       <c r="L420" t="n">
-        <v>0.5844155844155844</v>
+        <v>0.3565186997553303</v>
       </c>
       <c r="M420" t="n">
-        <v>0.06944444444444442</v>
+        <v>0.06650264668605077</v>
       </c>
       <c r="N420" t="n">
         <v>2</v>
       </c>
       <c r="O420" t="n">
-        <v>0.178535208106041</v>
+        <v>0.2668277025222778</v>
       </c>
       <c r="P420" t="n">
-        <v>0.3037036061286926</v>
+        <v>0.3323536515235901</v>
       </c>
       <c r="Q420" t="n">
-        <v>0.5177611708641052</v>
+        <v>0.4008186161518097</v>
       </c>
       <c r="R420" t="n">
         <v>1</v>
       </c>
       <c r="S420" t="n">
-        <v>-0.06665441355147916</v>
+        <v>0.04429991639647934</v>
       </c>
       <c r="T420" t="n">
         <v>2</v>
       </c>
       <c r="U420" t="n">
-        <v>-0.06665441355147916</v>
+        <v>0.04429991639647934</v>
       </c>
       <c r="V420" t="n">
-        <v>0.5177611708641052</v>
+        <v>0.4008186161518097</v>
       </c>
       <c r="W420" t="n">
-        <v>1.6</v>
+        <v>2.63</v>
       </c>
       <c r="X420" t="inlineStr">
         <is>
@@ -42445,7 +42401,7 @@
       </c>
       <c r="Y420" t="inlineStr"/>
       <c r="Z420" t="n">
-        <v>5.361693926524222</v>
+        <v>4.15069120821163</v>
       </c>
       <c r="AA420" t="inlineStr">
         <is>
@@ -42464,20 +42420,20 @@
     <row r="421">
       <c r="A421" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B421" s="2" t="n">
-        <v>45585.375</v>
+        <v>45584.5625</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E421" t="n">
@@ -42487,55 +42443,55 @@
         <v>1481</v>
       </c>
       <c r="G421" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H421" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="I421" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="J421" t="n">
-        <v>0.4745960470954284</v>
+        <v>0.3947157726180945</v>
       </c>
       <c r="K421" t="n">
-        <v>0.3061909981260828</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="L421" t="n">
-        <v>0.2192129547784888</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="M421" t="n">
-        <v>0.0535275273783804</v>
+        <v>0.05561189993238669</v>
       </c>
       <c r="N421" t="n">
         <v>1</v>
       </c>
       <c r="O421" t="n">
-        <v>0.3904880583286285</v>
+        <v>0.4895497262477875</v>
       </c>
       <c r="P421" t="n">
-        <v>0.358215719461441</v>
+        <v>0.3255585432052612</v>
       </c>
       <c r="Q421" t="n">
-        <v>0.2512962818145752</v>
+        <v>0.1848916709423065</v>
       </c>
       <c r="R421" t="n">
         <v>1</v>
       </c>
       <c r="S421" t="n">
-        <v>-0.08410798876679981</v>
+        <v>0.09483395362969294</v>
       </c>
       <c r="T421" t="n">
         <v>1</v>
       </c>
       <c r="U421" t="n">
-        <v>-0.08410798876679981</v>
+        <v>0.09483395362969294</v>
       </c>
       <c r="V421" t="n">
-        <v>0.3904880583286285</v>
+        <v>0.4895497262477875</v>
       </c>
       <c r="W421" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="X421" t="inlineStr">
         <is>
@@ -42544,7 +42500,7 @@
       </c>
       <c r="Y421" t="inlineStr"/>
       <c r="Z421" t="n">
-        <v>4.043712755104155</v>
+        <v>5.069549324399381</v>
       </c>
       <c r="AA421" t="inlineStr">
         <is>
@@ -42563,20 +42519,20 @@
     <row r="422">
       <c r="A422" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B422" s="2" t="n">
-        <v>45585.46875</v>
+        <v>45584.66666666666</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E422" t="n">
@@ -42586,55 +42542,55 @@
         <v>1481</v>
       </c>
       <c r="G422" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="H422" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="I422" t="n">
-        <v>10</v>
+        <v>1.6</v>
       </c>
       <c r="J422" t="n">
-        <v>0.7077140835102618</v>
+        <v>0.1990324809951624</v>
       </c>
       <c r="K422" t="n">
-        <v>0.1981599433828733</v>
+        <v>0.2100898410504492</v>
       </c>
       <c r="L422" t="n">
-        <v>0.09412597310686482</v>
+        <v>0.5908776779543885</v>
       </c>
       <c r="M422" t="n">
-        <v>0.06240601503759402</v>
+        <v>0.05774853801169577</v>
       </c>
       <c r="N422" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O422" t="n">
-        <v>0.7285870909690857</v>
+        <v>0.178535208106041</v>
       </c>
       <c r="P422" t="n">
-        <v>0.1864692121744156</v>
+        <v>0.3037036061286926</v>
       </c>
       <c r="Q422" t="n">
-        <v>0.08494370430707932</v>
+        <v>0.5177611708641052</v>
       </c>
       <c r="R422" t="n">
         <v>1</v>
       </c>
       <c r="S422" t="n">
-        <v>0.02087300745882392</v>
+        <v>-0.07311650709028328</v>
       </c>
       <c r="T422" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U422" t="n">
-        <v>0.02087300745882392</v>
+        <v>-0.07311650709028328</v>
       </c>
       <c r="V422" t="n">
-        <v>0.7285870909690857</v>
+        <v>0.5177611708641052</v>
       </c>
       <c r="W422" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="X422" t="inlineStr">
         <is>
@@ -42643,7 +42599,7 @@
       </c>
       <c r="Y422" t="inlineStr"/>
       <c r="Z422" t="n">
-        <v>7.54490912107855</v>
+        <v>5.361693926524222</v>
       </c>
       <c r="AA422" t="inlineStr">
         <is>
@@ -42655,29 +42611,27 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC422" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC422" t="inlineStr"/>
       <c r="AD422" t="inlineStr"/>
       <c r="AE422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B423" s="2" t="n">
-        <v>45585.5625</v>
+        <v>45585.375</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E423" t="n">
@@ -42687,55 +42641,55 @@
         <v>1481</v>
       </c>
       <c r="G423" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="H423" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="I423" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J423" t="n">
-        <v>0.5370967741935485</v>
+        <v>0.4600259692079391</v>
       </c>
       <c r="K423" t="n">
-        <v>0.2540322580645161</v>
+        <v>0.3042107215729919</v>
       </c>
       <c r="L423" t="n">
-        <v>0.2088709677419355</v>
+        <v>0.2357633092190688</v>
       </c>
       <c r="M423" t="n">
-        <v>0.06392106392106367</v>
+        <v>0.06038552321007096</v>
       </c>
       <c r="N423" t="n">
         <v>1</v>
       </c>
       <c r="O423" t="n">
-        <v>0.5907658934593201</v>
+        <v>0.3904880583286285</v>
       </c>
       <c r="P423" t="n">
-        <v>0.2744113206863403</v>
+        <v>0.358215719461441</v>
       </c>
       <c r="Q423" t="n">
-        <v>0.1348228305578232</v>
+        <v>0.2512962818145752</v>
       </c>
       <c r="R423" t="n">
         <v>1</v>
       </c>
       <c r="S423" t="n">
-        <v>0.05366911926577156</v>
+        <v>-0.0695379108793106</v>
       </c>
       <c r="T423" t="n">
         <v>1</v>
       </c>
       <c r="U423" t="n">
-        <v>0.05366911926577156</v>
+        <v>-0.0695379108793106</v>
       </c>
       <c r="V423" t="n">
-        <v>0.5907658934593201</v>
+        <v>0.3904880583286285</v>
       </c>
       <c r="W423" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="X423" t="inlineStr">
         <is>
@@ -42744,7 +42698,7 @@
       </c>
       <c r="Y423" t="inlineStr"/>
       <c r="Z423" t="n">
-        <v>6.11769688652426</v>
+        <v>4.043712755104155</v>
       </c>
       <c r="AA423" t="inlineStr">
         <is>
@@ -42763,20 +42717,20 @@
     <row r="424">
       <c r="A424" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B424" s="2" t="n">
-        <v>45585.66666666666</v>
+        <v>45585.46875</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E424" t="n">
@@ -42786,55 +42740,55 @@
         <v>1481</v>
       </c>
       <c r="G424" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="H424" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="I424" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J424" t="n">
-        <v>0.7201565557729942</v>
+        <v>0.7077140835102618</v>
       </c>
       <c r="K424" t="n">
-        <v>0.1628180039138943</v>
+        <v>0.1981599433828733</v>
       </c>
       <c r="L424" t="n">
-        <v>0.1170254403131116</v>
+        <v>0.09412597310686482</v>
       </c>
       <c r="M424" t="n">
-        <v>0.06814381270902992</v>
+        <v>0.06240601503759402</v>
       </c>
       <c r="N424" t="n">
         <v>1</v>
       </c>
       <c r="O424" t="n">
-        <v>0.7510959506034851</v>
+        <v>0.7285851240158081</v>
       </c>
       <c r="P424" t="n">
-        <v>0.1708084046840668</v>
+        <v>0.1864701211452484</v>
       </c>
       <c r="Q424" t="n">
-        <v>0.07809565961360931</v>
+        <v>0.08494473248720169</v>
       </c>
       <c r="R424" t="n">
         <v>1</v>
       </c>
       <c r="S424" t="n">
-        <v>0.03093939483049091</v>
+        <v>0.02087104050554633</v>
       </c>
       <c r="T424" t="n">
         <v>1</v>
       </c>
       <c r="U424" t="n">
-        <v>0.03093939483049091</v>
+        <v>0.02087104050554633</v>
       </c>
       <c r="V424" t="n">
-        <v>0.7510959506034851</v>
+        <v>0.7285851240158081</v>
       </c>
       <c r="W424" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X424" t="inlineStr">
         <is>
@@ -42843,7 +42797,7 @@
       </c>
       <c r="Y424" t="inlineStr"/>
       <c r="Z424" t="n">
-        <v>7.778000404832661</v>
+        <v>7.544888752225041</v>
       </c>
       <c r="AA424" t="inlineStr">
         <is>
@@ -42855,27 +42809,29 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC424" t="inlineStr"/>
+      <c r="AC424" t="n">
+        <v>1</v>
+      </c>
       <c r="AD424" t="inlineStr"/>
       <c r="AE424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B425" s="2" t="n">
-        <v>45586.66666666666</v>
+        <v>45585.5625</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E425" t="n">
@@ -42888,49 +42844,49 @@
         <v>1.75</v>
       </c>
       <c r="H425" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I425" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="J425" t="n">
-        <v>0.5392195506503745</v>
+        <v>0.5370967741935485</v>
       </c>
       <c r="K425" t="n">
-        <v>0.2621206148994876</v>
+        <v>0.2540322580645161</v>
       </c>
       <c r="L425" t="n">
-        <v>0.198659834450138</v>
+        <v>0.2088709677419355</v>
       </c>
       <c r="M425" t="n">
-        <v>0.05973266499582275</v>
+        <v>0.06392106392106367</v>
       </c>
       <c r="N425" t="n">
         <v>1</v>
       </c>
       <c r="O425" t="n">
-        <v>0.4499695599079132</v>
+        <v>0.5907658934593201</v>
       </c>
       <c r="P425" t="n">
-        <v>0.3398557603359222</v>
+        <v>0.2744113206863403</v>
       </c>
       <c r="Q425" t="n">
-        <v>0.2101746201515198</v>
+        <v>0.1348228305578232</v>
       </c>
       <c r="R425" t="n">
         <v>1</v>
       </c>
       <c r="S425" t="n">
-        <v>-0.08924999074246132</v>
+        <v>0.05366911926577156</v>
       </c>
       <c r="T425" t="n">
         <v>1</v>
       </c>
       <c r="U425" t="n">
-        <v>-0.08924999074246132</v>
+        <v>0.05366911926577156</v>
       </c>
       <c r="V425" t="n">
-        <v>0.4499695599079132</v>
+        <v>0.5907658934593201</v>
       </c>
       <c r="W425" t="n">
         <v>1.75</v>
@@ -42942,7 +42898,7 @@
       </c>
       <c r="Y425" t="inlineStr"/>
       <c r="Z425" t="n">
-        <v>4.659675526560992</v>
+        <v>6.11769688652426</v>
       </c>
       <c r="AA425" t="inlineStr">
         <is>
@@ -42961,15 +42917,15 @@
     <row r="426">
       <c r="A426" s="1" t="inlineStr">
         <is>
-          <t>vymauDyP</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B426" s="2" t="n">
-        <v>45590.66666666666</v>
+        <v>45585.66666666666</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -42984,55 +42940,55 @@
         <v>1481</v>
       </c>
       <c r="G426" t="n">
-        <v>2.75</v>
+        <v>1.3</v>
       </c>
       <c r="H426" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="I426" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="J426" t="n">
-        <v>0.3411167512690355</v>
+        <v>0.7201565557729942</v>
       </c>
       <c r="K426" t="n">
-        <v>0.2680203045685279</v>
+        <v>0.1628180039138943</v>
       </c>
       <c r="L426" t="n">
-        <v>0.3908629441624366</v>
+        <v>0.1170254403131116</v>
       </c>
       <c r="M426" t="n">
-        <v>0.06601731601731609</v>
+        <v>0.06814381270902992</v>
       </c>
       <c r="N426" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O426" t="n">
-        <v>0.3017470240592957</v>
+        <v>0.7480214834213257</v>
       </c>
       <c r="P426" t="n">
-        <v>0.3700113892555237</v>
+        <v>0.1728740930557251</v>
       </c>
       <c r="Q426" t="n">
-        <v>0.3282416462898254</v>
+        <v>0.07910438627004623</v>
       </c>
       <c r="R426" t="n">
         <v>1</v>
       </c>
       <c r="S426" t="n">
-        <v>0.1019910846869958</v>
+        <v>0.02786492764833148</v>
       </c>
       <c r="T426" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U426" t="n">
-        <v>0.1019910846869958</v>
+        <v>0.02786492764833148</v>
       </c>
       <c r="V426" t="n">
-        <v>0.3700113892555237</v>
+        <v>0.7480214834213257</v>
       </c>
       <c r="W426" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="X426" t="inlineStr">
         <is>
@@ -43041,7 +42997,7 @@
       </c>
       <c r="Y426" t="inlineStr"/>
       <c r="Z426" t="n">
-        <v>3.831665891834199</v>
+        <v>7.746162652321457</v>
       </c>
       <c r="AA426" t="inlineStr">
         <is>
@@ -43060,20 +43016,20 @@
     <row r="427">
       <c r="A427" s="1" t="inlineStr">
         <is>
-          <t>x88gL4RQ</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B427" s="2" t="n">
-        <v>45591.375</v>
+        <v>45586.66666666666</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E427" t="n">
@@ -43083,55 +43039,55 @@
         <v>1481</v>
       </c>
       <c r="G427" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="H427" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I427" t="n">
-        <v>2</v>
+        <v>4.75</v>
       </c>
       <c r="J427" t="n">
-        <v>0.2705667276051188</v>
+        <v>0.5392195506503745</v>
       </c>
       <c r="K427" t="n">
-        <v>0.2559414990859232</v>
+        <v>0.2621206148994876</v>
       </c>
       <c r="L427" t="n">
-        <v>0.473491773308958</v>
+        <v>0.198659834450138</v>
       </c>
       <c r="M427" t="n">
-        <v>0.05598455598455598</v>
+        <v>0.05973266499582275</v>
       </c>
       <c r="N427" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O427" t="n">
-        <v>0.2713698446750641</v>
+        <v>0.4536928236484528</v>
       </c>
       <c r="P427" t="n">
-        <v>0.3275195956230164</v>
+        <v>0.3383599817752838</v>
       </c>
       <c r="Q427" t="n">
-        <v>0.4011105298995972</v>
+        <v>0.207947164773941</v>
       </c>
       <c r="R427" t="n">
         <v>1</v>
       </c>
       <c r="S427" t="n">
-        <v>-0.07238124340936081</v>
+        <v>-0.08552672700192177</v>
       </c>
       <c r="T427" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U427" t="n">
-        <v>-0.07238124340936081</v>
+        <v>-0.08552672700192177</v>
       </c>
       <c r="V427" t="n">
-        <v>0.4011105298995972</v>
+        <v>0.4536928236484528</v>
       </c>
       <c r="W427" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="X427" t="inlineStr">
         <is>
@@ -43140,7 +43096,7 @@
       </c>
       <c r="Y427" t="inlineStr"/>
       <c r="Z427" t="n">
-        <v>4.153714131243825</v>
+        <v>4.69823191454038</v>
       </c>
       <c r="AA427" t="inlineStr">
         <is>
@@ -43159,20 +43115,20 @@
     <row r="428">
       <c r="A428" s="1" t="inlineStr">
         <is>
-          <t>dhkQFrkl</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B428" s="2" t="n">
-        <v>45591.46875</v>
+        <v>45590.66666666666</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E428" t="n">
@@ -43182,55 +43138,55 @@
         <v>1481</v>
       </c>
       <c r="G428" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="H428" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I428" t="n">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="J428" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.3359683794466403</v>
       </c>
       <c r="K428" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2687747035573123</v>
       </c>
       <c r="L428" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.3952569169960474</v>
       </c>
       <c r="M428" t="n">
-        <v>0.0625</v>
+        <v>0.06302521008403361</v>
       </c>
       <c r="N428" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O428" t="n">
-        <v>0.5164309144020081</v>
+        <v>0.301744818687439</v>
       </c>
       <c r="P428" t="n">
-        <v>0.2730623781681061</v>
+        <v>0.3700104951858521</v>
       </c>
       <c r="Q428" t="n">
-        <v>0.2105065882205963</v>
+        <v>0.3282446563243866</v>
       </c>
       <c r="R428" t="n">
         <v>1</v>
       </c>
       <c r="S428" t="n">
-        <v>0.04584267910789042</v>
+        <v>0.1012357916285398</v>
       </c>
       <c r="T428" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U428" t="n">
-        <v>0.04584267910789042</v>
+        <v>0.1012357916285398</v>
       </c>
       <c r="V428" t="n">
-        <v>0.5164309144020081</v>
+        <v>0.3700104951858521</v>
       </c>
       <c r="W428" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="X428" t="inlineStr">
         <is>
@@ -43239,7 +43195,7 @@
       </c>
       <c r="Y428" t="inlineStr"/>
       <c r="Z428" t="n">
-        <v>5.347918409171998</v>
+        <v>3.831656633264422</v>
       </c>
       <c r="AA428" t="inlineStr">
         <is>
@@ -43258,20 +43214,20 @@
     <row r="429">
       <c r="A429" s="1" t="inlineStr">
         <is>
-          <t>8Sp1FEw8</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B429" s="2" t="n">
-        <v>45591.5625</v>
+        <v>45591.375</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E429" t="n">
@@ -43281,52 +43237,52 @@
         <v>1481</v>
       </c>
       <c r="G429" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H429" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I429" t="n">
         <v>2</v>
       </c>
       <c r="J429" t="n">
-        <v>0.2611940298507463</v>
+        <v>0.2705667276051188</v>
       </c>
       <c r="K429" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="L429" t="n">
-        <v>0.4701492537313433</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="M429" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.05598455598455598</v>
       </c>
       <c r="N429" t="n">
         <v>2</v>
       </c>
       <c r="O429" t="n">
-        <v>0.2520309388637543</v>
+        <v>0.2713698446750641</v>
       </c>
       <c r="P429" t="n">
-        <v>0.3590537309646606</v>
+        <v>0.3275195956230164</v>
       </c>
       <c r="Q429" t="n">
-        <v>0.3889154195785522</v>
+        <v>0.4011105298995972</v>
       </c>
       <c r="R429" t="n">
         <v>1</v>
       </c>
       <c r="S429" t="n">
-        <v>-0.08123383415279106</v>
+        <v>-0.07238124340936081</v>
       </c>
       <c r="T429" t="n">
         <v>2</v>
       </c>
       <c r="U429" t="n">
-        <v>-0.08123383415279106</v>
+        <v>-0.07238124340936081</v>
       </c>
       <c r="V429" t="n">
-        <v>0.3889154195785522</v>
+        <v>0.4011105298995972</v>
       </c>
       <c r="W429" t="n">
         <v>2</v>
@@ -43338,7 +43294,7 @@
       </c>
       <c r="Y429" t="inlineStr"/>
       <c r="Z429" t="n">
-        <v>4.027427239485383</v>
+        <v>4.153714131243825</v>
       </c>
       <c r="AA429" t="inlineStr">
         <is>
@@ -43357,20 +43313,20 @@
     <row r="430">
       <c r="A430" s="1" t="inlineStr">
         <is>
-          <t>4zlpJdvq</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B430" s="2" t="n">
-        <v>45591.66666666666</v>
+        <v>45591.46875</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E430" t="n">
@@ -43380,55 +43336,55 @@
         <v>1481</v>
       </c>
       <c r="G430" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="H430" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="I430" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J430" t="n">
-        <v>0.4918386424102969</v>
+        <v>0.4733044733044733</v>
       </c>
       <c r="K430" t="n">
-        <v>0.2472136334220176</v>
+        <v>0.2958152958152958</v>
       </c>
       <c r="L430" t="n">
-        <v>0.2609477241676853</v>
+        <v>0.2308802308802309</v>
       </c>
       <c r="M430" t="n">
-        <v>0.06449588193870381</v>
+        <v>0.05640243902439024</v>
       </c>
       <c r="N430" t="n">
         <v>1</v>
       </c>
       <c r="O430" t="n">
-        <v>0.5266638994216919</v>
+        <v>0.5164309144020081</v>
       </c>
       <c r="P430" t="n">
-        <v>0.291552871465683</v>
+        <v>0.2730623781681061</v>
       </c>
       <c r="Q430" t="n">
-        <v>0.1817832738161087</v>
+        <v>0.2105065882205963</v>
       </c>
       <c r="R430" t="n">
         <v>1</v>
       </c>
       <c r="S430" t="n">
-        <v>0.03482525701139499</v>
+        <v>0.04312644109753477</v>
       </c>
       <c r="T430" t="n">
         <v>1</v>
       </c>
       <c r="U430" t="n">
-        <v>0.03482525701139499</v>
+        <v>0.04312644109753477</v>
       </c>
       <c r="V430" t="n">
-        <v>0.5266638994216919</v>
+        <v>0.5164309144020081</v>
       </c>
       <c r="W430" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="X430" t="inlineStr">
         <is>
@@ -43437,7 +43393,7 @@
       </c>
       <c r="Y430" t="inlineStr"/>
       <c r="Z430" t="n">
-        <v>5.45388644369781</v>
+        <v>5.347918409171998</v>
       </c>
       <c r="AA430" t="inlineStr">
         <is>
@@ -43456,20 +43412,20 @@
     <row r="431">
       <c r="A431" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B431" s="2" t="n">
-        <v>45592.41666666666</v>
+        <v>45591.5625</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E431" t="n">
@@ -43479,55 +43435,55 @@
         <v>1481</v>
       </c>
       <c r="G431" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="H431" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I431" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="J431" t="n">
-        <v>0.3162565550625252</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="K431" t="n">
-        <v>0.2964905203711174</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="L431" t="n">
-        <v>0.3872529245663574</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="M431" t="n">
-        <v>0.05399659863945572</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="N431" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O431" t="n">
-        <v>0.3127180337905884</v>
+        <v>0.2520247101783752</v>
       </c>
       <c r="P431" t="n">
-        <v>0.3681450188159943</v>
+        <v>0.3590483963489532</v>
       </c>
       <c r="Q431" t="n">
-        <v>0.3191368877887726</v>
+        <v>0.3889268934726715</v>
       </c>
       <c r="R431" t="n">
         <v>1</v>
       </c>
       <c r="S431" t="n">
-        <v>0.07165449844487687</v>
+        <v>-0.0812223602586718</v>
       </c>
       <c r="T431" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U431" t="n">
-        <v>0.07165449844487687</v>
+        <v>-0.0812223602586718</v>
       </c>
       <c r="V431" t="n">
-        <v>0.3681450188159943</v>
+        <v>0.3889268934726715</v>
       </c>
       <c r="W431" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="X431" t="inlineStr">
         <is>
@@ -43536,7 +43492,7 @@
       </c>
       <c r="Y431" t="inlineStr"/>
       <c r="Z431" t="n">
-        <v>3.812338627424687</v>
+        <v>4.027546057797522</v>
       </c>
       <c r="AA431" t="inlineStr">
         <is>
@@ -43548,29 +43504,27 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC431" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC431" t="inlineStr"/>
       <c r="AD431" t="inlineStr"/>
       <c r="AE431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B432" s="2" t="n">
-        <v>45592.51041666666</v>
+        <v>45591.66666666666</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E432" t="n">
@@ -43580,55 +43534,55 @@
         <v>1481</v>
       </c>
       <c r="G432" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="H432" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="I432" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J432" t="n">
-        <v>0.415347137637028</v>
+        <v>0.4918386424102969</v>
       </c>
       <c r="K432" t="n">
-        <v>0.2831912302070646</v>
+        <v>0.2472136334220176</v>
       </c>
       <c r="L432" t="n">
-        <v>0.3014616321559074</v>
+        <v>0.2609477241676853</v>
       </c>
       <c r="M432" t="n">
-        <v>0.07005539263603766</v>
+        <v>0.06449588193870381</v>
       </c>
       <c r="N432" t="n">
         <v>1</v>
       </c>
       <c r="O432" t="n">
-        <v>0.5595623254776001</v>
+        <v>0.5309537649154663</v>
       </c>
       <c r="P432" t="n">
-        <v>0.282652735710144</v>
+        <v>0.2891775071620941</v>
       </c>
       <c r="Q432" t="n">
-        <v>0.1577849239110947</v>
+        <v>0.1798686534166336</v>
       </c>
       <c r="R432" t="n">
         <v>1</v>
       </c>
       <c r="S432" t="n">
-        <v>0.1442151878405721</v>
+        <v>0.03911512250516941</v>
       </c>
       <c r="T432" t="n">
         <v>1</v>
       </c>
       <c r="U432" t="n">
-        <v>0.1442151878405721</v>
+        <v>0.03911512250516941</v>
       </c>
       <c r="V432" t="n">
-        <v>0.5595623254776001</v>
+        <v>0.5309537649154663</v>
       </c>
       <c r="W432" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="X432" t="inlineStr">
         <is>
@@ -43637,7 +43591,7 @@
       </c>
       <c r="Y432" t="inlineStr"/>
       <c r="Z432" t="n">
-        <v>5.79456724616468</v>
+        <v>5.498310295963884</v>
       </c>
       <c r="AA432" t="inlineStr">
         <is>
@@ -43656,20 +43610,20 @@
     <row r="433">
       <c r="A433" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>02sgHz9e</t>
         </is>
       </c>
       <c r="B433" s="2" t="n">
-        <v>45592.60416666666</v>
+        <v>45592.41666666666</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E433" t="n">
@@ -43679,55 +43633,55 @@
         <v>1481</v>
       </c>
       <c r="G433" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H433" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I433" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="J433" t="n">
-        <v>0.3211498973305955</v>
+        <v>0.3162565550625252</v>
       </c>
       <c r="K433" t="n">
-        <v>0.2739219712525667</v>
+        <v>0.2964905203711174</v>
       </c>
       <c r="L433" t="n">
-        <v>0.4049281314168378</v>
+        <v>0.3872529245663574</v>
       </c>
       <c r="M433" t="n">
-        <v>0.0737278419613725</v>
+        <v>0.05399659863945572</v>
       </c>
       <c r="N433" t="n">
         <v>0</v>
       </c>
       <c r="O433" t="n">
-        <v>0.3088712990283966</v>
+        <v>0.3127173781394958</v>
       </c>
       <c r="P433" t="n">
-        <v>0.3722001910209656</v>
+        <v>0.3681437373161316</v>
       </c>
       <c r="Q433" t="n">
-        <v>0.3189284801483154</v>
+        <v>0.3191388547420502</v>
       </c>
       <c r="R433" t="n">
         <v>1</v>
       </c>
       <c r="S433" t="n">
-        <v>0.0982782197683989</v>
+        <v>0.0716532169450142</v>
       </c>
       <c r="T433" t="n">
         <v>0</v>
       </c>
       <c r="U433" t="n">
-        <v>0.0982782197683989</v>
+        <v>0.0716532169450142</v>
       </c>
       <c r="V433" t="n">
-        <v>0.3722001910209656</v>
+        <v>0.3681437373161316</v>
       </c>
       <c r="W433" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="X433" t="inlineStr">
         <is>
@@ -43736,7 +43690,7 @@
       </c>
       <c r="Y433" t="inlineStr"/>
       <c r="Z433" t="n">
-        <v>3.854332105124294</v>
+        <v>3.812325356808007</v>
       </c>
       <c r="AA433" t="inlineStr">
         <is>
@@ -43748,27 +43702,29 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC433" t="inlineStr"/>
+      <c r="AC433" t="n">
+        <v>1</v>
+      </c>
       <c r="AD433" t="inlineStr"/>
       <c r="AE433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>naHJ2yf2</t>
         </is>
       </c>
       <c r="B434" s="2" t="n">
-        <v>45592.70833333334</v>
+        <v>45592.51041666666</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E434" t="n">
@@ -43778,55 +43734,55 @@
         <v>1481</v>
       </c>
       <c r="G434" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="H434" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I434" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="J434" t="n">
-        <v>0.5223880597014926</v>
+        <v>0.4192972007147112</v>
       </c>
       <c r="K434" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.2858844550327576</v>
       </c>
       <c r="L434" t="n">
-        <v>0.208955223880597</v>
+        <v>0.2948183442525313</v>
       </c>
       <c r="M434" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.0599747474747474</v>
       </c>
       <c r="N434" t="n">
         <v>1</v>
       </c>
       <c r="O434" t="n">
-        <v>0.4631039500236511</v>
+        <v>0.5567981600761414</v>
       </c>
       <c r="P434" t="n">
-        <v>0.3212946355342865</v>
+        <v>0.2840888202190399</v>
       </c>
       <c r="Q434" t="n">
-        <v>0.2156014740467072</v>
+        <v>0.1591130346059799</v>
       </c>
       <c r="R434" t="n">
         <v>1</v>
       </c>
       <c r="S434" t="n">
-        <v>-0.05928410967784148</v>
+        <v>0.1375009593614302</v>
       </c>
       <c r="T434" t="n">
         <v>1</v>
       </c>
       <c r="U434" t="n">
-        <v>-0.05928410967784148</v>
+        <v>0.1375009593614302</v>
       </c>
       <c r="V434" t="n">
-        <v>0.4631039500236511</v>
+        <v>0.5567981600761414</v>
       </c>
       <c r="W434" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="X434" t="inlineStr">
         <is>
@@ -43835,7 +43791,7 @@
       </c>
       <c r="Y434" t="inlineStr"/>
       <c r="Z434" t="n">
-        <v>4.79568916310817</v>
+        <v>5.765942834604084</v>
       </c>
       <c r="AA434" t="inlineStr">
         <is>
@@ -43854,20 +43810,20 @@
     <row r="435">
       <c r="A435" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>842EOIGL</t>
         </is>
       </c>
       <c r="B435" s="2" t="n">
-        <v>45593.70833333334</v>
+        <v>45592.60416666666</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E435" t="n">
@@ -43880,52 +43836,52 @@
         <v>3</v>
       </c>
       <c r="H435" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="I435" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J435" t="n">
-        <v>0.3156822810590631</v>
+        <v>0.3138041733547351</v>
       </c>
       <c r="K435" t="n">
-        <v>0.3054989816700611</v>
+        <v>0.2768860353130016</v>
       </c>
       <c r="L435" t="n">
-        <v>0.3788187372708758</v>
+        <v>0.4093097913322633</v>
       </c>
       <c r="M435" t="n">
-        <v>0.05591397849462365</v>
+        <v>0.06223358908780918</v>
       </c>
       <c r="N435" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O435" t="n">
-        <v>0.3670017123222351</v>
+        <v>0.3088712990283966</v>
       </c>
       <c r="P435" t="n">
-        <v>0.3658300042152405</v>
+        <v>0.3722001910209656</v>
       </c>
       <c r="Q435" t="n">
-        <v>0.2671682834625244</v>
+        <v>0.3189284801483154</v>
       </c>
       <c r="R435" t="n">
         <v>1</v>
       </c>
       <c r="S435" t="n">
-        <v>0.05131943126317201</v>
+        <v>0.09531415570796398</v>
       </c>
       <c r="T435" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U435" t="n">
-        <v>0.05131943126317201</v>
+        <v>0.09531415570796398</v>
       </c>
       <c r="V435" t="n">
-        <v>0.3670017123222351</v>
+        <v>0.3722001910209656</v>
       </c>
       <c r="W435" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="X435" t="inlineStr">
         <is>
@@ -43934,7 +43890,7 @@
       </c>
       <c r="Y435" t="inlineStr"/>
       <c r="Z435" t="n">
-        <v>3.800499077012837</v>
+        <v>3.854332105124294</v>
       </c>
       <c r="AA435" t="inlineStr">
         <is>
@@ -43949,6 +43905,204 @@
       <c r="AC435" t="inlineStr"/>
       <c r="AD435" t="inlineStr"/>
       <c r="AE435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="n">
+        <v>45592.70833333334</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>148</v>
+      </c>
+      <c r="F436" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G436" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H436" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I436" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J436" t="n">
+        <v>0.5140093406910212</v>
+      </c>
+      <c r="K436" t="n">
+        <v>0.2687534552755911</v>
+      </c>
+      <c r="L436" t="n">
+        <v>0.2172372040333877</v>
+      </c>
+      <c r="M436" t="n">
+        <v>0.06310925536306966</v>
+      </c>
+      <c r="N436" t="n">
+        <v>1</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0.4631039500236511</v>
+      </c>
+      <c r="P436" t="n">
+        <v>0.3212946355342865</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>0.2156014740467072</v>
+      </c>
+      <c r="R436" t="n">
+        <v>1</v>
+      </c>
+      <c r="S436" t="n">
+        <v>-0.0509053906673701</v>
+      </c>
+      <c r="T436" t="n">
+        <v>1</v>
+      </c>
+      <c r="U436" t="n">
+        <v>-0.0509053906673701</v>
+      </c>
+      <c r="V436" t="n">
+        <v>0.4631039500236511</v>
+      </c>
+      <c r="W436" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y436" t="inlineStr"/>
+      <c r="Z436" t="n">
+        <v>4.79568916310817</v>
+      </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB436" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC436" t="inlineStr"/>
+      <c r="AD436" t="inlineStr"/>
+      <c r="AE436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="n">
+        <v>45593.70833333334</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>148</v>
+      </c>
+      <c r="F437" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G437" t="n">
+        <v>3</v>
+      </c>
+      <c r="H437" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I437" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J437" t="n">
+        <v>0.3156822810590631</v>
+      </c>
+      <c r="K437" t="n">
+        <v>0.3054989816700611</v>
+      </c>
+      <c r="L437" t="n">
+        <v>0.3788187372708758</v>
+      </c>
+      <c r="M437" t="n">
+        <v>0.05591397849462365</v>
+      </c>
+      <c r="N437" t="n">
+        <v>1</v>
+      </c>
+      <c r="O437" t="n">
+        <v>0.3670017123222351</v>
+      </c>
+      <c r="P437" t="n">
+        <v>0.3658300042152405</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>0.2671682834625244</v>
+      </c>
+      <c r="R437" t="n">
+        <v>1</v>
+      </c>
+      <c r="S437" t="n">
+        <v>0.05131943126317201</v>
+      </c>
+      <c r="T437" t="n">
+        <v>1</v>
+      </c>
+      <c r="U437" t="n">
+        <v>0.05131943126317201</v>
+      </c>
+      <c r="V437" t="n">
+        <v>0.3670017123222351</v>
+      </c>
+      <c r="W437" t="n">
+        <v>3</v>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y437" t="inlineStr"/>
+      <c r="Z437" t="n">
+        <v>3.800499077012837</v>
+      </c>
+      <c r="AA437" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB437" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC437" t="inlineStr"/>
+      <c r="AD437" t="inlineStr"/>
+      <c r="AE437" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -49219,7 +49219,7 @@
       </c>
       <c r="Y486" t="inlineStr"/>
       <c r="Z486" t="n">
-        <v>13.38596147096674</v>
+        <v>12.28400986287721</v>
       </c>
       <c r="AA486" t="inlineStr">
         <is>
@@ -49318,7 +49318,7 @@
       </c>
       <c r="Y487" t="inlineStr"/>
       <c r="Z487" t="n">
-        <v>12.16285389166539</v>
+        <v>11.16159025931827</v>
       </c>
       <c r="AA487" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
       </c>
       <c r="Y488" t="inlineStr"/>
       <c r="Z488" t="n">
-        <v>9.432542124333931</v>
+        <v>8.656041685062059</v>
       </c>
       <c r="AA488" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
       </c>
       <c r="Y489" t="inlineStr"/>
       <c r="Z489" t="n">
-        <v>7.516728527958243</v>
+        <v>6.897940620423809</v>
       </c>
       <c r="AA489" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
       </c>
       <c r="Y490" t="inlineStr"/>
       <c r="Z490" t="n">
-        <v>14.24434379429987</v>
+        <v>13.07172891830805</v>
       </c>
       <c r="AA490" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
       </c>
       <c r="Y491" t="inlineStr"/>
       <c r="Z491" t="n">
-        <v>13.19219515347669</v>
+        <v>12.10619466743505</v>
       </c>
       <c r="AA491" t="inlineStr">
         <is>
@@ -49813,7 +49813,7 @@
       </c>
       <c r="Y492" t="inlineStr"/>
       <c r="Z492" t="n">
-        <v>16.18788745518694</v>
+        <v>14.85527726864893</v>
       </c>
       <c r="AA492" t="inlineStr">
         <is>
@@ -49912,7 +49912,7 @@
       </c>
       <c r="Y493" t="inlineStr"/>
       <c r="Z493" t="n">
-        <v>12.15173231857726</v>
+        <v>11.15138423012854</v>
       </c>
       <c r="AA493" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
       </c>
       <c r="Y494" t="inlineStr"/>
       <c r="Z494" t="n">
-        <v>19.68530135609057</v>
+        <v>18.06477902513062</v>
       </c>
       <c r="AA494" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
       </c>
       <c r="Y495" t="inlineStr"/>
       <c r="Z495" t="n">
-        <v>15.49998151217767</v>
+        <v>14.22400073263127</v>
       </c>
       <c r="AA495" t="inlineStr">
         <is>
@@ -50176,28 +50176,28 @@
         <v>1</v>
       </c>
       <c r="O496" t="n">
-        <v>0.5085573792457581</v>
+        <v>0.5085121989250183</v>
       </c>
       <c r="P496" t="n">
-        <v>0.3101730644702911</v>
+        <v>0.3100310564041138</v>
       </c>
       <c r="Q496" t="n">
-        <v>0.1812696158885956</v>
+        <v>0.1814567893743515</v>
       </c>
       <c r="R496" t="n">
         <v>1</v>
       </c>
       <c r="S496" t="n">
-        <v>-0.1570170626956714</v>
+        <v>-0.1570622430164111</v>
       </c>
       <c r="T496" t="n">
         <v>1</v>
       </c>
       <c r="U496" t="n">
-        <v>-0.1570170626956714</v>
+        <v>-0.1570622430164111</v>
       </c>
       <c r="V496" t="n">
-        <v>0.5085573792457581</v>
+        <v>0.5085121989250183</v>
       </c>
       <c r="W496" t="n">
         <v>1.42</v>
@@ -50275,28 +50275,28 @@
         <v>2</v>
       </c>
       <c r="O497" t="n">
-        <v>0.1855943948030472</v>
+        <v>0.1853174269199371</v>
       </c>
       <c r="P497" t="n">
-        <v>0.3393366932868958</v>
+        <v>0.3390077650547028</v>
       </c>
       <c r="Q497" t="n">
-        <v>0.4750689566135406</v>
+        <v>0.4756748080253601</v>
       </c>
       <c r="R497" t="n">
         <v>1</v>
       </c>
       <c r="S497" t="n">
-        <v>-4.416555840502934e-05</v>
+        <v>0.0005616858534144287</v>
       </c>
       <c r="T497" t="n">
         <v>2</v>
       </c>
       <c r="U497" t="n">
-        <v>-4.416555840502934e-05</v>
+        <v>0.0005616858534144287</v>
       </c>
       <c r="V497" t="n">
-        <v>0.4750689566135406</v>
+        <v>0.4756748080253601</v>
       </c>
       <c r="W497" t="n">
         <v>2</v>
@@ -50308,7 +50308,7 @@
       </c>
       <c r="Y497" t="inlineStr"/>
       <c r="Z497" t="n">
-        <v>2.519128285749723</v>
+        <v>2.820301222802751</v>
       </c>
       <c r="AA497" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
       </c>
       <c r="Y498" t="inlineStr"/>
       <c r="Z498" t="n">
-        <v>0.8441729349990058</v>
+        <v>0.9391071414650825</v>
       </c>
       <c r="AA498" t="inlineStr">
         <is>
@@ -50473,28 +50473,28 @@
         <v>2</v>
       </c>
       <c r="O499" t="n">
-        <v>0.06276359409093857</v>
+        <v>0.06264857202768326</v>
       </c>
       <c r="P499" t="n">
-        <v>0.1480340659618378</v>
+        <v>0.1477329879999161</v>
       </c>
       <c r="Q499" t="n">
-        <v>0.7892023921012878</v>
+        <v>0.7896184921264648</v>
       </c>
       <c r="R499" t="n">
         <v>1</v>
       </c>
       <c r="S499" t="n">
-        <v>0.02291886719707326</v>
+        <v>0.02333496722225026</v>
       </c>
       <c r="T499" t="n">
         <v>2</v>
       </c>
       <c r="U499" t="n">
-        <v>0.02291886719707326</v>
+        <v>0.02333496722225026</v>
       </c>
       <c r="V499" t="n">
-        <v>0.7892023921012878</v>
+        <v>0.7896184921264648</v>
       </c>
       <c r="W499" t="n">
         <v>1.22</v>
@@ -50506,7 +50506,7 @@
       </c>
       <c r="Y499" t="inlineStr"/>
       <c r="Z499" t="n">
-        <v>4.672731821338811</v>
+        <v>5.210496446033526</v>
       </c>
       <c r="AA499" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
       </c>
       <c r="Y500" t="inlineStr"/>
       <c r="Z500" t="n">
-        <v>2.787309144712135</v>
+        <v>3.100765038473047</v>
       </c>
       <c r="AA500" t="inlineStr">
         <is>
@@ -50671,28 +50671,28 @@
         <v>2</v>
       </c>
       <c r="O501" t="n">
-        <v>0.2060934454202652</v>
+        <v>0.2061669230461121</v>
       </c>
       <c r="P501" t="n">
-        <v>0.3389766216278076</v>
+        <v>0.3389227092266083</v>
       </c>
       <c r="Q501" t="n">
-        <v>0.4549299478530884</v>
+        <v>0.4549104273319244</v>
       </c>
       <c r="R501" t="n">
         <v>1</v>
       </c>
       <c r="S501" t="n">
-        <v>0.04097463621059516</v>
+        <v>0.04095511568943122</v>
       </c>
       <c r="T501" t="n">
         <v>2</v>
       </c>
       <c r="U501" t="n">
-        <v>0.04097463621059516</v>
+        <v>0.04095511568943122</v>
       </c>
       <c r="V501" t="n">
-        <v>0.4549299478530884</v>
+        <v>0.4549104273319244</v>
       </c>
       <c r="W501" t="n">
         <v>2.3</v>
@@ -50704,7 +50704,7 @@
       </c>
       <c r="Y501" t="inlineStr"/>
       <c r="Z501" t="n">
-        <v>3.282656674841461</v>
+        <v>3.651242511770958</v>
       </c>
       <c r="AA501" t="inlineStr">
         <is>
@@ -50803,7 +50803,7 @@
       </c>
       <c r="Y502" t="inlineStr"/>
       <c r="Z502" t="n">
-        <v>3.514102811972055</v>
+        <v>3.90929264578871</v>
       </c>
       <c r="AA502" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
       </c>
       <c r="Y503" t="inlineStr"/>
       <c r="Z503" t="n">
-        <v>3.690297397196375</v>
+        <v>4.105301764787334</v>
       </c>
       <c r="AA503" t="inlineStr">
         <is>
@@ -50968,28 +50968,28 @@
         <v>1</v>
       </c>
       <c r="O504" t="n">
-        <v>0.505291223526001</v>
+        <v>0.5053238868713379</v>
       </c>
       <c r="P504" t="n">
-        <v>0.3376038670539856</v>
+        <v>0.3375245332717896</v>
       </c>
       <c r="Q504" t="n">
-        <v>0.1571048200130463</v>
+        <v>0.1571515053510666</v>
       </c>
       <c r="R504" t="n">
         <v>1</v>
       </c>
       <c r="S504" t="n">
-        <v>-0.2049016584044323</v>
+        <v>-0.2048689950590954</v>
       </c>
       <c r="T504" t="n">
         <v>1</v>
       </c>
       <c r="U504" t="n">
-        <v>-0.2049016584044323</v>
+        <v>-0.2048689950590954</v>
       </c>
       <c r="V504" t="n">
-        <v>0.505291223526001</v>
+        <v>0.5053238868713379</v>
       </c>
       <c r="W504" t="n">
         <v>1.33</v>
@@ -51100,7 +51100,7 @@
       </c>
       <c r="Y505" t="inlineStr"/>
       <c r="Z505" t="n">
-        <v>1.397047696174947</v>
+        <v>1.676625605937493</v>
       </c>
       <c r="AA505" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
       </c>
       <c r="Y506" t="inlineStr"/>
       <c r="Z506" t="n">
-        <v>0.1629316684886378</v>
+        <v>0.1955376385173613</v>
       </c>
       <c r="AA506" t="inlineStr">
         <is>
@@ -51298,7 +51298,7 @@
       </c>
       <c r="Y507" t="inlineStr"/>
       <c r="Z507" t="n">
-        <v>1.501028171805223</v>
+        <v>1.801414708297137</v>
       </c>
       <c r="AA507" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
       </c>
       <c r="Y508" t="inlineStr"/>
       <c r="Z508" t="n">
-        <v>0.1761572854563473</v>
+        <v>0.2114099728142472</v>
       </c>
       <c r="AA508" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
       </c>
       <c r="Y509" t="inlineStr"/>
       <c r="Z509" t="n">
-        <v>0.3942980193213431</v>
+        <v>0.4732051435141655</v>
       </c>
       <c r="AA509" t="inlineStr">
         <is>
@@ -51595,7 +51595,7 @@
       </c>
       <c r="Y510" t="inlineStr"/>
       <c r="Z510" t="n">
-        <v>0.4214405542530009</v>
+        <v>0.5057794566181982</v>
       </c>
       <c r="AA510" t="inlineStr">
         <is>
@@ -51694,7 +51694,7 @@
       </c>
       <c r="Y511" t="inlineStr"/>
       <c r="Z511" t="n">
-        <v>1.486650659962105</v>
+        <v>1.784159961324759</v>
       </c>
       <c r="AA511" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
       </c>
       <c r="Y512" t="inlineStr"/>
       <c r="Z512" t="n">
-        <v>1.386564562383858</v>
+        <v>1.664044581973364</v>
       </c>
       <c r="AA512" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
       </c>
       <c r="Y513" t="inlineStr"/>
       <c r="Z513" t="n">
-        <v>1.456245623602304</v>
+        <v>1.747670253314161</v>
       </c>
       <c r="AA513" t="inlineStr">
         <is>
@@ -51960,10 +51960,10 @@
         <v>0</v>
       </c>
       <c r="O514" t="n">
-        <v>0.1616330260227122</v>
+        <v>0.1616330260227123</v>
       </c>
       <c r="P514" t="n">
-        <v>0.4255251614233782</v>
+        <v>0.4255251614233783</v>
       </c>
       <c r="Q514" t="n">
         <v>0.4128418125539094</v>
@@ -51972,16 +51972,16 @@
         <v>1</v>
       </c>
       <c r="S514" t="n">
-        <v>0.1408625847362616</v>
+        <v>0.1408625847362617</v>
       </c>
       <c r="T514" t="n">
         <v>0</v>
       </c>
       <c r="U514" t="n">
-        <v>0.1408625847362616</v>
+        <v>0.1408625847362617</v>
       </c>
       <c r="V514" t="n">
-        <v>0.4255251614233782</v>
+        <v>0.4255251614233783</v>
       </c>
       <c r="W514" t="n">
         <v>3.3</v>
@@ -51993,7 +51993,7 @@
       </c>
       <c r="Y514" t="inlineStr"/>
       <c r="Z514" t="n">
-        <v>0.3566595291653734</v>
+        <v>0.851050322846756</v>
       </c>
       <c r="AA514" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
       </c>
       <c r="Y515" t="inlineStr"/>
       <c r="Z515" t="n">
-        <v>0.1352685800823947</v>
+        <v>0.3227738482679543</v>
       </c>
       <c r="AA515" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
       </c>
       <c r="Y516" t="inlineStr"/>
       <c r="Z516" t="n">
-        <v>0.2484338069929679</v>
+        <v>0.5928053349427814</v>
       </c>
       <c r="AA516" t="inlineStr">
         <is>
@@ -52259,28 +52259,28 @@
         <v>2</v>
       </c>
       <c r="O517" t="n">
-        <v>0.08274019555151663</v>
+        <v>0.08274019555151668</v>
       </c>
       <c r="P517" t="n">
-        <v>0.404406029122148</v>
+        <v>0.4044060291221481</v>
       </c>
       <c r="Q517" t="n">
-        <v>0.5128537753263354</v>
+        <v>0.5128537753263355</v>
       </c>
       <c r="R517" t="n">
         <v>1</v>
       </c>
       <c r="S517" t="n">
-        <v>-0.0610343164957593</v>
+        <v>-0.06103431649575919</v>
       </c>
       <c r="T517" t="n">
         <v>2</v>
       </c>
       <c r="U517" t="n">
-        <v>-0.0610343164957593</v>
+        <v>-0.06103431649575919</v>
       </c>
       <c r="V517" t="n">
-        <v>0.5128537753263354</v>
+        <v>0.5128537753263355</v>
       </c>
       <c r="W517" t="n">
         <v>1.65</v>
@@ -52292,7 +52292,7 @@
       </c>
       <c r="Y517" t="inlineStr"/>
       <c r="Z517" t="n">
-        <v>0.2252282882186293</v>
+        <v>0.5374330186865971</v>
       </c>
       <c r="AA517" t="inlineStr">
         <is>
@@ -52490,7 +52490,7 @@
       </c>
       <c r="Y519" t="inlineStr"/>
       <c r="Z519" t="n">
-        <v>0.4126951296057076</v>
+        <v>0.984760800055248</v>
       </c>
       <c r="AA519" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
       </c>
       <c r="Y520" t="inlineStr"/>
       <c r="Z520" t="n">
-        <v>0.00358905403721724</v>
+        <v>0.008564093616777896</v>
       </c>
       <c r="AA520" t="inlineStr">
         <is>
@@ -52688,7 +52688,7 @@
       </c>
       <c r="Y521" t="inlineStr"/>
       <c r="Z521" t="n">
-        <v>0.3582674572546474</v>
+        <v>0.8548871128596099</v>
       </c>
       <c r="AA521" t="inlineStr">
         <is>
@@ -52787,7 +52787,7 @@
       </c>
       <c r="Y522" t="inlineStr"/>
       <c r="Z522" t="n">
-        <v>0.3041650612283984</v>
+        <v>0.7257895903213214</v>
       </c>
       <c r="AA522" t="inlineStr">
         <is>
@@ -52886,7 +52886,7 @@
       </c>
       <c r="Y523" t="inlineStr"/>
       <c r="Z523" t="n">
-        <v>0.3292969115842702</v>
+        <v>0.7857584614998165</v>
       </c>
       <c r="AA523" t="inlineStr">
         <is>
@@ -52985,7 +52985,7 @@
       </c>
       <c r="Y524" t="inlineStr"/>
       <c r="Z524" t="n">
-        <v>7.133388347319908</v>
+        <v>7.02978622343648</v>
       </c>
       <c r="AA524" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
       </c>
       <c r="Y525" t="inlineStr"/>
       <c r="Z525" t="n">
-        <v>7.94466924918703</v>
+        <v>7.829284446384814</v>
       </c>
       <c r="AA525" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
       </c>
       <c r="Y526" t="inlineStr"/>
       <c r="Z526" t="n">
-        <v>6.468217403907484</v>
+        <v>6.374275923623946</v>
       </c>
       <c r="AA526" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
       </c>
       <c r="Y527" t="inlineStr"/>
       <c r="Z527" t="n">
-        <v>5.944465669057267</v>
+        <v>5.858130923396344</v>
       </c>
       <c r="AA527" t="inlineStr">
         <is>
@@ -53381,7 +53381,7 @@
       </c>
       <c r="Y528" t="inlineStr"/>
       <c r="Z528" t="n">
-        <v>4.130779702332097</v>
+        <v>4.070786115887732</v>
       </c>
       <c r="AA528" t="inlineStr">
         <is>
@@ -53480,7 +53480,7 @@
       </c>
       <c r="Y529" t="inlineStr"/>
       <c r="Z529" t="n">
-        <v>4.70811765009296</v>
+        <v>4.639739066971805</v>
       </c>
       <c r="AA529" t="inlineStr">
         <is>
@@ -53581,7 +53581,7 @@
       </c>
       <c r="Y530" t="inlineStr"/>
       <c r="Z530" t="n">
-        <v>4.231745166142808</v>
+        <v>4.170285202714552</v>
       </c>
       <c r="AA530" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
       </c>
       <c r="Y531" t="inlineStr"/>
       <c r="Z531" t="n">
-        <v>4.256881895497528</v>
+        <v>4.195056857518185</v>
       </c>
       <c r="AA531" t="inlineStr">
         <is>
@@ -53779,7 +53779,7 @@
       </c>
       <c r="Y532" t="inlineStr"/>
       <c r="Z532" t="n">
-        <v>3.493430441874344</v>
+        <v>3.442693429420341</v>
       </c>
       <c r="AA532" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
       </c>
       <c r="Y533" t="inlineStr"/>
       <c r="Z533" t="n">
-        <v>5.577967784331351</v>
+        <v>5.496955889103862</v>
       </c>
       <c r="AA533" t="inlineStr">
         <is>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE533"/>
+  <dimension ref="A1:AE558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49139,177 +49139,179 @@
     <row r="486">
       <c r="A486" s="1" t="inlineStr">
         <is>
-          <t>nX2mpxRQ</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B486" s="2" t="n">
-        <v>45605.5</v>
+        <v>45603.69791666666</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E486" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="F486" t="n">
-        <v>481</v>
+        <v>771</v>
       </c>
       <c r="G486" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H486" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I486" t="n">
         <v>2.4</v>
       </c>
-      <c r="H486" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I486" t="n">
-        <v>2.7</v>
-      </c>
       <c r="J486" t="n">
-        <v>0.3940828402366864</v>
+        <v>0.3239263803680982</v>
       </c>
       <c r="K486" t="n">
-        <v>0.2556213017751479</v>
+        <v>0.2846625766871166</v>
       </c>
       <c r="L486" t="n">
-        <v>0.3502958579881656</v>
+        <v>0.3914110429447853</v>
       </c>
       <c r="M486" t="n">
-        <v>0.05730730730730738</v>
+        <v>0.0645245559038663</v>
       </c>
       <c r="N486" t="n">
         <v>0</v>
       </c>
       <c r="O486" t="n">
-        <v>0.3078418672084808</v>
+        <v>0.1616330260227123</v>
       </c>
       <c r="P486" t="n">
-        <v>0.361346960067749</v>
+        <v>0.4255251614233783</v>
       </c>
       <c r="Q486" t="n">
-        <v>0.3308112323284149</v>
+        <v>0.4128418125539094</v>
       </c>
       <c r="R486" t="n">
         <v>1</v>
       </c>
       <c r="S486" t="n">
-        <v>0.1057256582926012</v>
+        <v>0.1408625847362617</v>
       </c>
       <c r="T486" t="n">
         <v>0</v>
       </c>
       <c r="U486" t="n">
-        <v>0.1057256582926012</v>
+        <v>0.1408625847362617</v>
       </c>
       <c r="V486" t="n">
-        <v>0.361346960067749</v>
+        <v>0.4255251614233783</v>
       </c>
       <c r="W486" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="X486" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="Y486" t="inlineStr"/>
       <c r="Z486" t="n">
-        <v>12.28400986287721</v>
+        <v>0.851050322846756</v>
       </c>
       <c r="AA486" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB486" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="AC486" t="inlineStr"/>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC486" t="n">
+        <v>1</v>
+      </c>
       <c r="AD486" t="inlineStr"/>
       <c r="AE486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="1" t="inlineStr">
         <is>
-          <t>YTzyyYmD</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B487" s="2" t="n">
-        <v>45605.5</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E487" t="n">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="F487" t="n">
-        <v>481</v>
+        <v>1481</v>
       </c>
       <c r="G487" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="H487" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="I487" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J487" t="n">
-        <v>0.3864042933810376</v>
+        <v>0.3592517652888467</v>
       </c>
       <c r="K487" t="n">
-        <v>0.262969588550984</v>
+        <v>0.3258041871412644</v>
       </c>
       <c r="L487" t="n">
-        <v>0.3506261180679786</v>
+        <v>0.3149440475698889</v>
       </c>
       <c r="M487" t="n">
-        <v>0.05631141345427038</v>
+        <v>0.05838905642235925</v>
       </c>
       <c r="N487" t="n">
         <v>1</v>
       </c>
       <c r="O487" t="n">
-        <v>0.4053996801376343</v>
+        <v>0.5252802968025208</v>
       </c>
       <c r="P487" t="n">
-        <v>0.3239441215991974</v>
+        <v>0.3036795258522034</v>
       </c>
       <c r="Q487" t="n">
-        <v>0.2706562578678131</v>
+        <v>0.1710400879383087</v>
       </c>
       <c r="R487" t="n">
         <v>1</v>
       </c>
       <c r="S487" t="n">
-        <v>0.01899538675659668</v>
+        <v>0.1660285315136741</v>
       </c>
       <c r="T487" t="n">
         <v>1</v>
       </c>
       <c r="U487" t="n">
-        <v>0.01899538675659668</v>
+        <v>0.1660285315136741</v>
       </c>
       <c r="V487" t="n">
-        <v>0.4053996801376343</v>
+        <v>0.5252802968025208</v>
       </c>
       <c r="W487" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="X487" t="inlineStr">
         <is>
@@ -49318,16 +49320,16 @@
       </c>
       <c r="Y487" t="inlineStr"/>
       <c r="Z487" t="n">
-        <v>11.16159025931827</v>
+        <v>5.858130923396344</v>
       </c>
       <c r="AA487" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB487" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC487" t="inlineStr"/>
@@ -49337,7 +49339,7 @@
     <row r="488">
       <c r="A488" s="1" t="inlineStr">
         <is>
-          <t>K0RAmBXI</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B488" s="2" t="n">
@@ -49345,12 +49347,12 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>west ham</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="E488" t="n">
@@ -49360,55 +49362,55 @@
         <v>481</v>
       </c>
       <c r="G488" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="H488" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I488" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J488" t="n">
-        <v>0.4505119453924914</v>
+        <v>0.3787575150300601</v>
       </c>
       <c r="K488" t="n">
-        <v>0.2866894197952218</v>
+        <v>0.2705410821643286</v>
       </c>
       <c r="L488" t="n">
-        <v>0.2627986348122867</v>
+        <v>0.3507014028056112</v>
       </c>
       <c r="M488" t="n">
-        <v>0.05699855699855716</v>
+        <v>0.05608465608465618</v>
       </c>
       <c r="N488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O488" t="n">
-        <v>0.3898195028305054</v>
+        <v>0.2797083581673301</v>
       </c>
       <c r="P488" t="n">
-        <v>0.3265766799449921</v>
+        <v>0.197922895538261</v>
       </c>
       <c r="Q488" t="n">
-        <v>0.2836038172245026</v>
+        <v>0.5223687462944088</v>
       </c>
       <c r="R488" t="n">
         <v>1</v>
       </c>
       <c r="S488" t="n">
-        <v>-0.06069244256198603</v>
+        <v>0.1716673434887976</v>
       </c>
       <c r="T488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U488" t="n">
-        <v>-0.06069244256198603</v>
+        <v>0.1716673434887976</v>
       </c>
       <c r="V488" t="n">
-        <v>0.3898195028305054</v>
+        <v>0.5223687462944088</v>
       </c>
       <c r="W488" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="X488" t="inlineStr">
         <is>
@@ -49417,7 +49419,7 @@
       </c>
       <c r="Y488" t="inlineStr"/>
       <c r="Z488" t="n">
-        <v>8.656041685062059</v>
+        <v>6.045190601247996</v>
       </c>
       <c r="AA488" t="inlineStr">
         <is>
@@ -49436,7 +49438,7 @@
     <row r="489">
       <c r="A489" s="1" t="inlineStr">
         <is>
-          <t>0d4cBEPP</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B489" s="2" t="n">
@@ -49444,12 +49446,12 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>southampton</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="E489" t="n">
@@ -49459,55 +49461,55 @@
         <v>481</v>
       </c>
       <c r="G489" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="H489" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="I489" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J489" t="n">
-        <v>0.4950053514092044</v>
+        <v>0.3465346534653466</v>
       </c>
       <c r="K489" t="n">
-        <v>0.2508027113806636</v>
+        <v>0.2722772277227723</v>
       </c>
       <c r="L489" t="n">
-        <v>0.254191937210132</v>
+        <v>0.3811881188118812</v>
       </c>
       <c r="M489" t="n">
-        <v>0.06325272641062107</v>
+        <v>0.04935064935064926</v>
       </c>
       <c r="N489" t="n">
         <v>1</v>
       </c>
       <c r="O489" t="n">
-        <v>0.3786422312259674</v>
+        <v>0.5492019214616395</v>
       </c>
       <c r="P489" t="n">
-        <v>0.3237687945365906</v>
+        <v>0.2663478059471888</v>
       </c>
       <c r="Q489" t="n">
-        <v>0.297588974237442</v>
+        <v>0.1844502725911718</v>
       </c>
       <c r="R489" t="n">
         <v>1</v>
       </c>
       <c r="S489" t="n">
-        <v>-0.116363120183237</v>
+        <v>0.2026672679962929</v>
       </c>
       <c r="T489" t="n">
         <v>1</v>
       </c>
       <c r="U489" t="n">
-        <v>-0.116363120183237</v>
+        <v>0.2026672679962929</v>
       </c>
       <c r="V489" t="n">
-        <v>0.3786422312259674</v>
+        <v>0.5492019214616395</v>
       </c>
       <c r="W489" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="X489" t="inlineStr">
         <is>
@@ -49516,7 +49518,7 @@
       </c>
       <c r="Y489" t="inlineStr"/>
       <c r="Z489" t="n">
-        <v>6.897940620423809</v>
+        <v>6.799354967234056</v>
       </c>
       <c r="AA489" t="inlineStr">
         <is>
@@ -49535,20 +49537,20 @@
     <row r="490">
       <c r="A490" s="1" t="inlineStr">
         <is>
-          <t>6HqKvGll</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B490" s="2" t="n">
-        <v>45605.60416666666</v>
+        <v>45605.5</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="E490" t="n">
@@ -49558,55 +49560,55 @@
         <v>481</v>
       </c>
       <c r="G490" t="n">
-        <v>4.5</v>
+        <v>2.15</v>
       </c>
       <c r="H490" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="I490" t="n">
-        <v>1.73</v>
+        <v>3.4</v>
       </c>
       <c r="J490" t="n">
-        <v>0.210304843837666</v>
+        <v>0.4415584415584415</v>
       </c>
       <c r="K490" t="n">
-        <v>0.2426594351973069</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="L490" t="n">
-        <v>0.5470357209650272</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="M490" t="n">
-        <v>0.0566671607134035</v>
+        <v>0.05335157318741457</v>
       </c>
       <c r="N490" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O490" t="n">
-        <v>0.1807558834552765</v>
+        <v>0.508869364374401</v>
       </c>
       <c r="P490" t="n">
-        <v>0.2972142100334167</v>
+        <v>0.4028344811580645</v>
       </c>
       <c r="Q490" t="n">
-        <v>0.5220298171043396</v>
+        <v>0.0882961544675344</v>
       </c>
       <c r="R490" t="n">
         <v>1</v>
       </c>
       <c r="S490" t="n">
-        <v>-0.02500590386068757</v>
+        <v>0.06731092281595946</v>
       </c>
       <c r="T490" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U490" t="n">
-        <v>-0.02500590386068757</v>
+        <v>0.06731092281595946</v>
       </c>
       <c r="V490" t="n">
-        <v>0.5220298171043396</v>
+        <v>0.508869364374401</v>
       </c>
       <c r="W490" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="X490" t="inlineStr">
         <is>
@@ -49615,7 +49617,7 @@
       </c>
       <c r="Y490" t="inlineStr"/>
       <c r="Z490" t="n">
-        <v>13.07172891830805</v>
+        <v>3.890565278191194</v>
       </c>
       <c r="AA490" t="inlineStr">
         <is>
@@ -49634,20 +49636,20 @@
     <row r="491">
       <c r="A491" s="1" t="inlineStr">
         <is>
-          <t>0zTMbytK</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B491" s="2" t="n">
-        <v>45605.70833333334</v>
+        <v>45605.5</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="E491" t="n">
@@ -49657,55 +49659,55 @@
         <v>481</v>
       </c>
       <c r="G491" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="H491" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="I491" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="J491" t="n">
-        <v>0.6389405204460966</v>
+        <v>0.4953764861294584</v>
       </c>
       <c r="K491" t="n">
-        <v>0.1891263940520446</v>
+        <v>0.2523117569352708</v>
       </c>
       <c r="L491" t="n">
-        <v>0.1719330855018587</v>
+        <v>0.2523117569352708</v>
       </c>
       <c r="M491" t="n">
-        <v>0.05749385749385749</v>
+        <v>0.05689354275741709</v>
       </c>
       <c r="N491" t="n">
         <v>1</v>
       </c>
       <c r="O491" t="n">
-        <v>0.5496260523796082</v>
+        <v>0.47726904936604</v>
       </c>
       <c r="P491" t="n">
-        <v>0.2800574898719788</v>
+        <v>0.2400526308861448</v>
       </c>
       <c r="Q491" t="n">
-        <v>0.1703164726495743</v>
+        <v>0.2826783197478153</v>
       </c>
       <c r="R491" t="n">
         <v>1</v>
       </c>
       <c r="S491" t="n">
-        <v>-0.08931446806648846</v>
+        <v>-0.01810743676341842</v>
       </c>
       <c r="T491" t="n">
         <v>1</v>
       </c>
       <c r="U491" t="n">
-        <v>-0.08931446806648846</v>
+        <v>-0.01810743676341842</v>
       </c>
       <c r="V491" t="n">
-        <v>0.5496260523796082</v>
+        <v>0.47726904936604</v>
       </c>
       <c r="W491" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="X491" t="inlineStr">
         <is>
@@ -49714,7 +49716,7 @@
       </c>
       <c r="Y491" t="inlineStr"/>
       <c r="Z491" t="n">
-        <v>12.10619466743505</v>
+        <v>2.024196511561831</v>
       </c>
       <c r="AA491" t="inlineStr">
         <is>
@@ -49733,20 +49735,20 @@
     <row r="492">
       <c r="A492" s="1" t="inlineStr">
         <is>
-          <t>KK9ggF3s</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B492" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="E492" t="n">
@@ -49756,55 +49758,55 @@
         <v>481</v>
       </c>
       <c r="G492" t="n">
-        <v>1.38</v>
+        <v>4.1</v>
       </c>
       <c r="H492" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="I492" t="n">
-        <v>6.25</v>
+        <v>1.75</v>
       </c>
       <c r="J492" t="n">
-        <v>0.6845564074479737</v>
+        <v>0.2315325248070562</v>
       </c>
       <c r="K492" t="n">
-        <v>0.1642935377875137</v>
+        <v>0.2260198456449835</v>
       </c>
       <c r="L492" t="n">
-        <v>0.1511500547645126</v>
+        <v>0.5424476295479603</v>
       </c>
       <c r="M492" t="n">
-        <v>0.0585507246376813</v>
+        <v>0.05342624854819977</v>
       </c>
       <c r="N492" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O492" t="n">
-        <v>0.6246979236602783</v>
+        <v>0.05587305509160116</v>
       </c>
       <c r="P492" t="n">
-        <v>0.2300899177789688</v>
+        <v>0.3446916743651515</v>
       </c>
       <c r="Q492" t="n">
-        <v>0.1452121138572693</v>
+        <v>0.5994352705432473</v>
       </c>
       <c r="R492" t="n">
         <v>1</v>
       </c>
       <c r="S492" t="n">
-        <v>-0.05985848378769543</v>
+        <v>0.05698764099528697</v>
       </c>
       <c r="T492" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U492" t="n">
-        <v>-0.05985848378769543</v>
+        <v>0.05698764099528697</v>
       </c>
       <c r="V492" t="n">
-        <v>0.6246979236602783</v>
+        <v>0.5994352705432473</v>
       </c>
       <c r="W492" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="X492" t="inlineStr">
         <is>
@@ -49813,7 +49815,7 @@
       </c>
       <c r="Y492" t="inlineStr"/>
       <c r="Z492" t="n">
-        <v>14.85527726864893</v>
+        <v>4.136929172621976</v>
       </c>
       <c r="AA492" t="inlineStr">
         <is>
@@ -49832,20 +49834,20 @@
     <row r="493">
       <c r="A493" s="1" t="inlineStr">
         <is>
-          <t>hY71igYg</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B493" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="E493" t="n">
@@ -49855,55 +49857,55 @@
         <v>481</v>
       </c>
       <c r="G493" t="n">
-        <v>2.63</v>
+        <v>1.42</v>
       </c>
       <c r="H493" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="I493" t="n">
-        <v>2.55</v>
+        <v>6.5</v>
       </c>
       <c r="J493" t="n">
-        <v>0.3593501499808749</v>
+        <v>0.6716197598897855</v>
       </c>
       <c r="K493" t="n">
-        <v>0.2700259698427717</v>
+        <v>0.1816571541035229</v>
       </c>
       <c r="L493" t="n">
-        <v>0.3706238801763534</v>
+        <v>0.1467230860066916</v>
       </c>
       <c r="M493" t="n">
-        <v>0.05809928534151299</v>
+        <v>0.04854769643502044</v>
       </c>
       <c r="N493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O493" t="n">
-        <v>0.2653241157531738</v>
+        <v>0.6018557569807923</v>
       </c>
       <c r="P493" t="n">
-        <v>0.3373605012893677</v>
+        <v>0.3202946445129535</v>
       </c>
       <c r="Q493" t="n">
-        <v>0.3973154425621033</v>
+        <v>0.07784959850625414</v>
       </c>
       <c r="R493" t="n">
         <v>1</v>
       </c>
       <c r="S493" t="n">
-        <v>0.02669156238574988</v>
+        <v>-0.06976400290899321</v>
       </c>
       <c r="T493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U493" t="n">
-        <v>0.02669156238574988</v>
+        <v>-0.06976400290899321</v>
       </c>
       <c r="V493" t="n">
-        <v>0.3973154425621033</v>
+        <v>0.6018557569807923</v>
       </c>
       <c r="W493" t="n">
-        <v>2.55</v>
+        <v>1.42</v>
       </c>
       <c r="X493" t="inlineStr">
         <is>
@@ -49912,7 +49914,7 @@
       </c>
       <c r="Y493" t="inlineStr"/>
       <c r="Z493" t="n">
-        <v>11.15138423012854</v>
+        <v>1.613998726724097</v>
       </c>
       <c r="AA493" t="inlineStr">
         <is>
@@ -49931,7 +49933,7 @@
     <row r="494">
       <c r="A494" s="1" t="inlineStr">
         <is>
-          <t>CzO2kX26</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B494" s="2" t="n">
@@ -49939,12 +49941,12 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E494" t="n">
@@ -49954,55 +49956,55 @@
         <v>481</v>
       </c>
       <c r="G494" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="H494" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="I494" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J494" t="n">
-        <v>0.7612456747404844</v>
+        <v>0.6936936936936937</v>
       </c>
       <c r="K494" t="n">
-        <v>0.1522491349480969</v>
+        <v>0.1715315315315316</v>
       </c>
       <c r="L494" t="n">
-        <v>0.08650519031141868</v>
+        <v>0.1347747747747748</v>
       </c>
       <c r="M494" t="n">
-        <v>0.05090909090909101</v>
+        <v>0.05996944232238333</v>
       </c>
       <c r="N494" t="n">
         <v>1</v>
       </c>
       <c r="O494" t="n">
-        <v>0.7240597009658813</v>
+        <v>0.5736403463949913</v>
       </c>
       <c r="P494" t="n">
-        <v>0.1891239732503891</v>
+        <v>0.3644374378711059</v>
       </c>
       <c r="Q494" t="n">
-        <v>0.08681630343198776</v>
+        <v>0.06192221573390277</v>
       </c>
       <c r="R494" t="n">
         <v>1</v>
       </c>
       <c r="S494" t="n">
-        <v>-0.03718597377460309</v>
+        <v>-0.1200533472987024</v>
       </c>
       <c r="T494" t="n">
         <v>1</v>
       </c>
       <c r="U494" t="n">
-        <v>-0.03718597377460309</v>
+        <v>-0.1200533472987024</v>
       </c>
       <c r="V494" t="n">
-        <v>0.7240597009658813</v>
+        <v>0.5736403463949913</v>
       </c>
       <c r="W494" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="X494" t="inlineStr">
         <is>
@@ -50011,7 +50013,7 @@
       </c>
       <c r="Y494" t="inlineStr"/>
       <c r="Z494" t="n">
-        <v>18.06477902513062</v>
+        <v>0.4671347860009079</v>
       </c>
       <c r="AA494" t="inlineStr">
         <is>
@@ -50030,20 +50032,20 @@
     <row r="495">
       <c r="A495" s="1" t="inlineStr">
         <is>
-          <t>CEnSxfJ0</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B495" s="2" t="n">
-        <v>45606.5625</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="E495" t="n">
@@ -50053,55 +50055,55 @@
         <v>481</v>
       </c>
       <c r="G495" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="H495" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I495" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="J495" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.3515188335358444</v>
       </c>
       <c r="K495" t="n">
-        <v>0.2777017783857729</v>
+        <v>0.287606318347509</v>
       </c>
       <c r="L495" t="n">
-        <v>0.3967168262653898</v>
+        <v>0.3608748481166464</v>
       </c>
       <c r="M495" t="n">
-        <v>0.05911330049261099</v>
+        <v>0.05362881028280286</v>
       </c>
       <c r="N495" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O495" t="n">
-        <v>0.2332454323768616</v>
+        <v>0.1919490033785586</v>
       </c>
       <c r="P495" t="n">
-        <v>0.4092691540718079</v>
+        <v>0.3633721987060077</v>
       </c>
       <c r="Q495" t="n">
-        <v>0.3574853837490082</v>
+        <v>0.4446787979154337</v>
       </c>
       <c r="R495" t="n">
         <v>1</v>
       </c>
       <c r="S495" t="n">
-        <v>0.131567375686035</v>
+        <v>0.08380394979878736</v>
       </c>
       <c r="T495" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U495" t="n">
-        <v>0.131567375686035</v>
+        <v>0.08380394979878736</v>
       </c>
       <c r="V495" t="n">
-        <v>0.4092691540718079</v>
+        <v>0.4446787979154337</v>
       </c>
       <c r="W495" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="X495" t="inlineStr">
         <is>
@@ -50110,7 +50112,7 @@
       </c>
       <c r="Y495" t="inlineStr"/>
       <c r="Z495" t="n">
-        <v>14.22400073263127</v>
+        <v>3.899472985552916</v>
       </c>
       <c r="AA495" t="inlineStr">
         <is>
@@ -50129,78 +50131,78 @@
     <row r="496">
       <c r="A496" s="1" t="inlineStr">
         <is>
-          <t>Gp6AbAAT</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B496" s="2" t="n">
-        <v>45604.69791666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F496" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G496" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="H496" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I496" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="J496" t="n">
-        <v>0.6655744419414295</v>
+        <v>0.7561209793566971</v>
       </c>
       <c r="K496" t="n">
-        <v>0.189023141511366</v>
+        <v>0.1371819491118579</v>
       </c>
       <c r="L496" t="n">
-        <v>0.1454024165472046</v>
+        <v>0.106697071531445</v>
       </c>
       <c r="M496" t="n">
-        <v>0.05807150595882993</v>
+        <v>0.04136982877140349</v>
       </c>
       <c r="N496" t="n">
         <v>1</v>
       </c>
       <c r="O496" t="n">
-        <v>0.5085121989250183</v>
+        <v>0.6484027698424354</v>
       </c>
       <c r="P496" t="n">
-        <v>0.3100310564041138</v>
+        <v>0.3011042777339618</v>
       </c>
       <c r="Q496" t="n">
-        <v>0.1814567893743515</v>
+        <v>0.05049295242360272</v>
       </c>
       <c r="R496" t="n">
         <v>1</v>
       </c>
       <c r="S496" t="n">
-        <v>-0.1570622430164111</v>
+        <v>-0.1077182095142617</v>
       </c>
       <c r="T496" t="n">
         <v>1</v>
       </c>
       <c r="U496" t="n">
-        <v>-0.1570622430164111</v>
+        <v>-0.1077182095142617</v>
       </c>
       <c r="V496" t="n">
-        <v>0.5085121989250183</v>
+        <v>0.6484027698424354</v>
       </c>
       <c r="W496" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="X496" t="inlineStr">
         <is>
@@ -50209,16 +50211,16 @@
       </c>
       <c r="Y496" t="inlineStr"/>
       <c r="Z496" t="n">
-        <v>0</v>
+        <v>1.087649658926943</v>
       </c>
       <c r="AA496" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB496" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC496" t="inlineStr"/>
@@ -50228,78 +50230,78 @@
     <row r="497">
       <c r="A497" s="1" t="inlineStr">
         <is>
-          <t>figxD9PM</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B497" s="2" t="n">
-        <v>45605.54166666666</v>
+        <v>45606.5625</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F497" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G497" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="H497" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="I497" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="J497" t="n">
-        <v>0.2714932126696832</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="K497" t="n">
-        <v>0.253393665158371</v>
+        <v>0.2783505154639175</v>
       </c>
       <c r="L497" t="n">
-        <v>0.4751131221719457</v>
+        <v>0.3711340206185567</v>
       </c>
       <c r="M497" t="n">
-        <v>0.05238095238095242</v>
+        <v>0.05664488017429203</v>
       </c>
       <c r="N497" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O497" t="n">
-        <v>0.1853174269199371</v>
+        <v>0.5423281239799856</v>
       </c>
       <c r="P497" t="n">
-        <v>0.3390077650547028</v>
+        <v>0.1883515769780034</v>
       </c>
       <c r="Q497" t="n">
-        <v>0.4756748080253601</v>
+        <v>0.2693202990420109</v>
       </c>
       <c r="R497" t="n">
         <v>1</v>
       </c>
       <c r="S497" t="n">
-        <v>0.0005616858534144287</v>
+        <v>0.1918126600624599</v>
       </c>
       <c r="T497" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U497" t="n">
-        <v>0.0005616858534144287</v>
+        <v>0.1918126600624599</v>
       </c>
       <c r="V497" t="n">
-        <v>0.4756748080253601</v>
+        <v>0.5423281239799856</v>
       </c>
       <c r="W497" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="X497" t="inlineStr">
         <is>
@@ -50308,16 +50310,16 @@
       </c>
       <c r="Y497" t="inlineStr"/>
       <c r="Z497" t="n">
-        <v>2.820301222802751</v>
+        <v>6.547893821149127</v>
       </c>
       <c r="AA497" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB497" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC497" t="inlineStr"/>
@@ -50327,78 +50329,78 @@
     <row r="498">
       <c r="A498" s="1" t="inlineStr">
         <is>
-          <t>bJl87mmp</t>
+          <t>EubK3NNG</t>
         </is>
       </c>
       <c r="B498" s="2" t="n">
-        <v>45605.625</v>
+        <v>45619.39583333334</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F498" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G498" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="H498" t="n">
         <v>4</v>
       </c>
       <c r="I498" t="n">
-        <v>5.5</v>
+        <v>1.65</v>
       </c>
       <c r="J498" t="n">
-        <v>0.5913978494623655</v>
+        <v>0.1893830703012913</v>
       </c>
       <c r="K498" t="n">
-        <v>0.2365591397849462</v>
+        <v>0.236728837876614</v>
       </c>
       <c r="L498" t="n">
-        <v>0.1720430107526882</v>
+        <v>0.5738880918220947</v>
       </c>
       <c r="M498" t="n">
-        <v>0.05681818181818188</v>
+        <v>0.05606060606060614</v>
       </c>
       <c r="N498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O498" t="n">
-        <v>0.5049460530281067</v>
+        <v>0.1413065091688256</v>
       </c>
       <c r="P498" t="n">
-        <v>0.2904142141342163</v>
+        <v>0.4078634062770092</v>
       </c>
       <c r="Q498" t="n">
-        <v>0.2046397030353546</v>
+        <v>0.4508300845541651</v>
       </c>
       <c r="R498" t="n">
         <v>1</v>
       </c>
       <c r="S498" t="n">
-        <v>-0.08645179643425882</v>
+        <v>-0.1230580072679295</v>
       </c>
       <c r="T498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U498" t="n">
-        <v>-0.08645179643425882</v>
+        <v>-0.1230580072679295</v>
       </c>
       <c r="V498" t="n">
-        <v>0.5049460530281067</v>
+        <v>0.4508300845541651</v>
       </c>
       <c r="W498" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="X498" t="inlineStr">
         <is>
@@ -50407,16 +50409,16 @@
       </c>
       <c r="Y498" t="inlineStr"/>
       <c r="Z498" t="n">
-        <v>0.9391071414650825</v>
+        <v>0</v>
       </c>
       <c r="AA498" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB498" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC498" t="inlineStr"/>
@@ -50426,78 +50428,78 @@
     <row r="499">
       <c r="A499" s="1" t="inlineStr">
         <is>
-          <t>dYK8BH5F</t>
+          <t>Cl3y4WHa</t>
         </is>
       </c>
       <c r="B499" s="2" t="n">
-        <v>45605.70833333334</v>
+        <v>45619.5</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F499" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G499" t="n">
-        <v>12</v>
+        <v>1.33</v>
       </c>
       <c r="H499" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="I499" t="n">
-        <v>1.22</v>
+        <v>8</v>
       </c>
       <c r="J499" t="n">
-        <v>0.07790549169859515</v>
+        <v>0.7155356795644564</v>
       </c>
       <c r="K499" t="n">
-        <v>0.1558109833971903</v>
+        <v>0.1655065137079526</v>
       </c>
       <c r="L499" t="n">
-        <v>0.7662835249042146</v>
+        <v>0.1189578067275909</v>
       </c>
       <c r="M499" t="n">
-        <v>0.06967213114754101</v>
+        <v>0.05079274272638123</v>
       </c>
       <c r="N499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O499" t="n">
-        <v>0.06264857202768326</v>
+        <v>0.7501533031177688</v>
       </c>
       <c r="P499" t="n">
-        <v>0.1477329879999161</v>
+        <v>0.1480937774734568</v>
       </c>
       <c r="Q499" t="n">
-        <v>0.7896184921264648</v>
+        <v>0.1017529194087745</v>
       </c>
       <c r="R499" t="n">
         <v>1</v>
       </c>
       <c r="S499" t="n">
-        <v>0.02333496722225026</v>
+        <v>0.03461762355331244</v>
       </c>
       <c r="T499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U499" t="n">
-        <v>0.02333496722225026</v>
+        <v>0.03461762355331244</v>
       </c>
       <c r="V499" t="n">
-        <v>0.7896184921264648</v>
+        <v>0.7501533031177688</v>
       </c>
       <c r="W499" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="X499" t="inlineStr">
         <is>
@@ -50506,16 +50508,16 @@
       </c>
       <c r="Y499" t="inlineStr"/>
       <c r="Z499" t="n">
-        <v>5.210496446033526</v>
+        <v>4.443118986655093</v>
       </c>
       <c r="AA499" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB499" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC499" t="inlineStr"/>
@@ -50525,78 +50527,78 @@
     <row r="500">
       <c r="A500" s="1" t="inlineStr">
         <is>
-          <t>l8H0Dwy3</t>
+          <t>p21q2AnC</t>
         </is>
       </c>
       <c r="B500" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45619.5</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="E500" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F500" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G500" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="H500" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="I500" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="J500" t="n">
-        <v>0.3872529245663574</v>
+        <v>0.5574781823653325</v>
       </c>
       <c r="K500" t="n">
-        <v>0.2964905203711174</v>
+        <v>0.2430033102618116</v>
       </c>
       <c r="L500" t="n">
-        <v>0.3162565550625252</v>
+        <v>0.1995185073728558</v>
       </c>
       <c r="M500" t="n">
-        <v>0.05399659863945572</v>
+        <v>0.05517186631737725</v>
       </c>
       <c r="N500" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O500" t="n">
-        <v>0.295372486114502</v>
+        <v>0.318295233421524</v>
       </c>
       <c r="P500" t="n">
-        <v>0.3465326130390167</v>
+        <v>0.467122865816885</v>
       </c>
       <c r="Q500" t="n">
-        <v>0.3580949008464813</v>
+        <v>0.2145819007615911</v>
       </c>
       <c r="R500" t="n">
         <v>1</v>
       </c>
       <c r="S500" t="n">
-        <v>0.04183834578395612</v>
+        <v>0.2241195555550734</v>
       </c>
       <c r="T500" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U500" t="n">
-        <v>0.04183834578395612</v>
+        <v>0.2241195555550734</v>
       </c>
       <c r="V500" t="n">
-        <v>0.3580949008464813</v>
+        <v>0.467122865816885</v>
       </c>
       <c r="W500" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="X500" t="inlineStr">
         <is>
@@ -50605,16 +50607,16 @@
       </c>
       <c r="Y500" t="inlineStr"/>
       <c r="Z500" t="n">
-        <v>3.100765038473047</v>
+        <v>6.818005440185892</v>
       </c>
       <c r="AA500" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB500" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC500" t="inlineStr"/>
@@ -50624,78 +50626,78 @@
     <row r="501">
       <c r="A501" s="1" t="inlineStr">
         <is>
-          <t>nRkUEVfA</t>
+          <t>WveT5hmm</t>
         </is>
       </c>
       <c r="B501" s="2" t="n">
-        <v>45606.54166666666</v>
+        <v>45619.5</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="E501" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F501" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G501" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="H501" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I501" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="J501" t="n">
-        <v>0.2885143081144649</v>
+        <v>0.4302959501557632</v>
       </c>
       <c r="K501" t="n">
-        <v>0.297530380243042</v>
+        <v>0.2784267912772586</v>
       </c>
       <c r="L501" t="n">
-        <v>0.4139553116424932</v>
+        <v>0.2912772585669782</v>
       </c>
       <c r="M501" t="n">
-        <v>0.05031291172595509</v>
+        <v>0.05635540929658589</v>
       </c>
       <c r="N501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O501" t="n">
-        <v>0.2061669230461121</v>
+        <v>0.740850919529086</v>
       </c>
       <c r="P501" t="n">
-        <v>0.3389227092266083</v>
+        <v>0.1916123727298028</v>
       </c>
       <c r="Q501" t="n">
-        <v>0.4549104273319244</v>
+        <v>0.06753670774111104</v>
       </c>
       <c r="R501" t="n">
         <v>1</v>
       </c>
       <c r="S501" t="n">
-        <v>0.04095511568943122</v>
+        <v>0.3105549693733228</v>
       </c>
       <c r="T501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U501" t="n">
-        <v>0.04095511568943122</v>
+        <v>0.3105549693733228</v>
       </c>
       <c r="V501" t="n">
-        <v>0.4549104273319244</v>
+        <v>0.740850919529086</v>
       </c>
       <c r="W501" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="X501" t="inlineStr">
         <is>
@@ -50704,16 +50706,16 @@
       </c>
       <c r="Y501" t="inlineStr"/>
       <c r="Z501" t="n">
-        <v>3.651242511770958</v>
+        <v>9.915353985111887</v>
       </c>
       <c r="AA501" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB501" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC501" t="inlineStr"/>
@@ -50723,78 +50725,78 @@
     <row r="502">
       <c r="A502" s="1" t="inlineStr">
         <is>
-          <t>QB1LGiQc</t>
+          <t>v3JHq2Wp</t>
         </is>
       </c>
       <c r="B502" s="2" t="n">
-        <v>45606.54166666666</v>
+        <v>45619.5</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="E502" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F502" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G502" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="H502" t="n">
         <v>3.5</v>
       </c>
       <c r="I502" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J502" t="n">
+        <v>0.4081222356252514</v>
+      </c>
+      <c r="K502" t="n">
+        <v>0.268194611982308</v>
+      </c>
+      <c r="L502" t="n">
+        <v>0.3236831523924407</v>
+      </c>
+      <c r="M502" t="n">
+        <v>0.06532448061683449</v>
+      </c>
+      <c r="N502" t="n">
+        <v>1</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0.4102408758399712</v>
+      </c>
+      <c r="P502" t="n">
+        <v>0.2792937644542169</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>0.3104653597058119</v>
+      </c>
+      <c r="R502" t="n">
+        <v>1</v>
+      </c>
+      <c r="S502" t="n">
+        <v>0.002118640214719858</v>
+      </c>
+      <c r="T502" t="n">
+        <v>1</v>
+      </c>
+      <c r="U502" t="n">
+        <v>0.002118640214719858</v>
+      </c>
+      <c r="V502" t="n">
+        <v>0.4102408758399712</v>
+      </c>
+      <c r="W502" t="n">
         <v>2.3</v>
-      </c>
-      <c r="J502" t="n">
-        <v>0.3163064833005893</v>
-      </c>
-      <c r="K502" t="n">
-        <v>0.2711198428290766</v>
-      </c>
-      <c r="L502" t="n">
-        <v>0.4125736738703339</v>
-      </c>
-      <c r="M502" t="n">
-        <v>0.0538302277432714</v>
-      </c>
-      <c r="N502" t="n">
-        <v>0</v>
-      </c>
-      <c r="O502" t="n">
-        <v>0.3323381841182709</v>
-      </c>
-      <c r="P502" t="n">
-        <v>0.3493877649307251</v>
-      </c>
-      <c r="Q502" t="n">
-        <v>0.3182739913463593</v>
-      </c>
-      <c r="R502" t="n">
-        <v>1</v>
-      </c>
-      <c r="S502" t="n">
-        <v>0.07826792210164851</v>
-      </c>
-      <c r="T502" t="n">
-        <v>0</v>
-      </c>
-      <c r="U502" t="n">
-        <v>0.07826792210164851</v>
-      </c>
-      <c r="V502" t="n">
-        <v>0.3493877649307251</v>
-      </c>
-      <c r="W502" t="n">
-        <v>3.5</v>
       </c>
       <c r="X502" t="inlineStr">
         <is>
@@ -50803,16 +50805,16 @@
       </c>
       <c r="Y502" t="inlineStr"/>
       <c r="Z502" t="n">
-        <v>3.90929264578871</v>
+        <v>2.093577183494253</v>
       </c>
       <c r="AA502" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB502" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC502" t="inlineStr"/>
@@ -50822,78 +50824,78 @@
     <row r="503">
       <c r="A503" s="1" t="inlineStr">
         <is>
-          <t>WWnG5RHd</t>
+          <t>69B375Oi</t>
         </is>
       </c>
       <c r="B503" s="2" t="n">
-        <v>45606.54166666666</v>
+        <v>45619.5</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="E503" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F503" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G503" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="H503" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="I503" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="J503" t="n">
-        <v>0.4415584415584415</v>
+        <v>0.5574781823653325</v>
       </c>
       <c r="K503" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.2430033102618116</v>
       </c>
       <c r="L503" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.1995185073728558</v>
       </c>
       <c r="M503" t="n">
-        <v>0.05335157318741457</v>
+        <v>0.05517186631737725</v>
       </c>
       <c r="N503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O503" t="n">
-        <v>0.4923816919326782</v>
+        <v>0.3357476902870436</v>
       </c>
       <c r="P503" t="n">
-        <v>0.3072681128978729</v>
+        <v>0.2702324548598613</v>
       </c>
       <c r="Q503" t="n">
-        <v>0.2003500908613205</v>
+        <v>0.3940198548530951</v>
       </c>
       <c r="R503" t="n">
         <v>1</v>
       </c>
       <c r="S503" t="n">
-        <v>0.05082325037423668</v>
+        <v>0.1945013474802393</v>
       </c>
       <c r="T503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U503" t="n">
-        <v>0.05082325037423668</v>
+        <v>0.1945013474802393</v>
       </c>
       <c r="V503" t="n">
-        <v>0.4923816919326782</v>
+        <v>0.3940198548530951</v>
       </c>
       <c r="W503" t="n">
-        <v>2.15</v>
+        <v>4.75</v>
       </c>
       <c r="X503" t="inlineStr">
         <is>
@@ -50902,16 +50904,16 @@
       </c>
       <c r="Y503" t="inlineStr"/>
       <c r="Z503" t="n">
-        <v>4.105301764787334</v>
+        <v>5.860126223870261</v>
       </c>
       <c r="AA503" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB503" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC503" t="inlineStr"/>
@@ -50921,78 +50923,78 @@
     <row r="504">
       <c r="A504" s="1" t="inlineStr">
         <is>
-          <t>b59ZhlYj</t>
+          <t>A7iT11hT</t>
         </is>
       </c>
       <c r="B504" s="2" t="n">
-        <v>45606.69791666666</v>
+        <v>45619.60416666666</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="E504" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F504" t="n">
-        <v>551</v>
+        <v>481</v>
       </c>
       <c r="G504" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="H504" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I504" t="n">
         <v>5.5</v>
       </c>
-      <c r="I504" t="n">
-        <v>8</v>
-      </c>
       <c r="J504" t="n">
-        <v>0.7101928819304333</v>
+        <v>0.6026768243366641</v>
       </c>
       <c r="K504" t="n">
-        <v>0.1717375514486321</v>
+        <v>0.2252863367163244</v>
       </c>
       <c r="L504" t="n">
-        <v>0.1180695666209345</v>
+        <v>0.1720368389470114</v>
       </c>
       <c r="M504" t="n">
-        <v>0.05869788106630214</v>
+        <v>0.05685609507265554</v>
       </c>
       <c r="N504" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O504" t="n">
-        <v>0.5053238868713379</v>
+        <v>0.2355670630895556</v>
       </c>
       <c r="P504" t="n">
-        <v>0.3375245332717896</v>
+        <v>0.6893672198989927</v>
       </c>
       <c r="Q504" t="n">
-        <v>0.1571515053510666</v>
+        <v>0.07506571701145179</v>
       </c>
       <c r="R504" t="n">
         <v>1</v>
       </c>
       <c r="S504" t="n">
-        <v>-0.2048689950590954</v>
+        <v>0.4640808831826683</v>
       </c>
       <c r="T504" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U504" t="n">
-        <v>-0.2048689950590954</v>
+        <v>0.4640808831826683</v>
       </c>
       <c r="V504" t="n">
-        <v>0.5053238868713379</v>
+        <v>0.6893672198989927</v>
       </c>
       <c r="W504" t="n">
-        <v>1.33</v>
+        <v>4.2</v>
       </c>
       <c r="X504" t="inlineStr">
         <is>
@@ -51001,16 +51003,16 @@
       </c>
       <c r="Y504" t="inlineStr"/>
       <c r="Z504" t="n">
-        <v>0</v>
+        <v>12.72845376314833</v>
       </c>
       <c r="AA504" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB504" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC504" t="inlineStr"/>
@@ -51020,96 +51022,96 @@
     <row r="505">
       <c r="A505" s="1" t="inlineStr">
         <is>
-          <t>v3DAZKP9</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B505" s="2" t="n">
-        <v>45604.6875</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E505" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F505" t="n">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="G505" t="n">
-        <v>2.38</v>
+        <v>1.36</v>
       </c>
       <c r="H505" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="I505" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="J505" t="n">
-        <v>0.3967168262653899</v>
+        <v>0.6997667444185273</v>
       </c>
       <c r="K505" t="n">
-        <v>0.2777017783857729</v>
+        <v>0.1812729090303233</v>
       </c>
       <c r="L505" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.1189603465511496</v>
       </c>
       <c r="M505" t="n">
-        <v>0.05911330049261077</v>
+        <v>0.05077030812324912</v>
       </c>
       <c r="N505" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O505" t="n">
-        <v>0.2832338194838178</v>
+        <v>0.5933453961434054</v>
       </c>
       <c r="P505" t="n">
-        <v>0.3599540243199423</v>
+        <v>0.2785554211040788</v>
       </c>
       <c r="Q505" t="n">
-        <v>0.35681215619624</v>
+        <v>0.1280991827525158</v>
       </c>
       <c r="R505" t="n">
         <v>1</v>
       </c>
       <c r="S505" t="n">
-        <v>0.08225224593416935</v>
+        <v>-0.1064213482751218</v>
       </c>
       <c r="T505" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U505" t="n">
-        <v>0.08225224593416935</v>
+        <v>-0.1064213482751218</v>
       </c>
       <c r="V505" t="n">
-        <v>0.3599540243199423</v>
+        <v>0.5933453961434054</v>
       </c>
       <c r="W505" t="n">
-        <v>3.4</v>
+        <v>1.36</v>
       </c>
       <c r="X505" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y505" t="inlineStr"/>
       <c r="Z505" t="n">
-        <v>1.676625605937493</v>
+        <v>5.933453961434054</v>
       </c>
       <c r="AA505" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB505" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC505" t="inlineStr"/>
@@ -51119,96 +51121,96 @@
     <row r="506">
       <c r="A506" s="1" t="inlineStr">
         <is>
-          <t>biQrHC9r</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B506" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45605.54166666666</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="E506" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F506" t="n">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="G506" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="H506" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="I506" t="n">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="J506" t="n">
-        <v>0.118454363757495</v>
+        <v>0.2763256161314414</v>
       </c>
       <c r="K506" t="n">
-        <v>0.1353764157228514</v>
+        <v>0.2539208364451083</v>
       </c>
       <c r="L506" t="n">
-        <v>0.7461692205196536</v>
+        <v>0.4697535474234503</v>
       </c>
       <c r="M506" t="n">
-        <v>0.05525871766029233</v>
+        <v>0.06438791732909377</v>
       </c>
       <c r="N506" t="n">
         <v>2</v>
       </c>
       <c r="O506" t="n">
-        <v>0.08413534972857876</v>
+        <v>0.213938813213297</v>
       </c>
       <c r="P506" t="n">
-        <v>0.4044252063169132</v>
+        <v>0.3080877883666737</v>
       </c>
       <c r="Q506" t="n">
-        <v>0.511439443954508</v>
+        <v>0.4779733984200293</v>
       </c>
       <c r="R506" t="n">
         <v>1</v>
       </c>
       <c r="S506" t="n">
-        <v>-0.2347297765651456</v>
+        <v>0.008219850996579015</v>
       </c>
       <c r="T506" t="n">
         <v>2</v>
       </c>
       <c r="U506" t="n">
-        <v>-0.2347297765651456</v>
+        <v>0.008219850996579015</v>
       </c>
       <c r="V506" t="n">
-        <v>0.511439443954508</v>
+        <v>0.4779733984200293</v>
       </c>
       <c r="W506" t="n">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="X506" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y506" t="inlineStr"/>
       <c r="Z506" t="n">
-        <v>0.1955376385173613</v>
+        <v>4.779733984200293</v>
       </c>
       <c r="AA506" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB506" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC506" t="inlineStr"/>
@@ -51218,96 +51220,96 @@
     <row r="507">
       <c r="A507" s="1" t="inlineStr">
         <is>
-          <t>nee3ysec</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B507" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45605.625</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E507" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F507" t="n">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="G507" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="H507" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I507" t="n">
-        <v>2.05</v>
+        <v>5.75</v>
       </c>
       <c r="J507" t="n">
-        <v>0.2775479503572772</v>
+        <v>0.5922355737488446</v>
       </c>
       <c r="K507" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2429684405123466</v>
       </c>
       <c r="L507" t="n">
-        <v>0.46032342986085</v>
+        <v>0.1647959857388089</v>
       </c>
       <c r="M507" t="n">
-        <v>0.05970030288538175</v>
+        <v>0.05532329988851714</v>
       </c>
       <c r="N507" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O507" t="n">
-        <v>0.1800605865798936</v>
+        <v>0.4584897570020434</v>
       </c>
       <c r="P507" t="n">
-        <v>0.384142145981388</v>
+        <v>0.3112641842728145</v>
       </c>
       <c r="Q507" t="n">
-        <v>0.4357972674387184</v>
+        <v>0.2302460587251422</v>
       </c>
       <c r="R507" t="n">
         <v>1</v>
       </c>
       <c r="S507" t="n">
-        <v>-0.02452616242213157</v>
+        <v>-0.1337458167468012</v>
       </c>
       <c r="T507" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U507" t="n">
-        <v>-0.02452616242213157</v>
+        <v>-0.1337458167468012</v>
       </c>
       <c r="V507" t="n">
-        <v>0.4357972674387184</v>
+        <v>0.4584897570020434</v>
       </c>
       <c r="W507" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="X507" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y507" t="inlineStr"/>
       <c r="Z507" t="n">
-        <v>1.801414708297137</v>
+        <v>4.584897570020433</v>
       </c>
       <c r="AA507" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB507" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC507" t="inlineStr"/>
@@ -51317,96 +51319,96 @@
     <row r="508">
       <c r="A508" s="1" t="inlineStr">
         <is>
-          <t>6HTjFjve</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B508" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E508" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F508" t="n">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="G508" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H508" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="I508" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="J508" t="n">
-        <v>0.08639711319471147</v>
+        <v>0.07839407803423636</v>
       </c>
       <c r="K508" t="n">
-        <v>0.1652814339377089</v>
+        <v>0.1505166298257338</v>
       </c>
       <c r="L508" t="n">
-        <v>0.7483214528675796</v>
+        <v>0.7710892921400297</v>
       </c>
       <c r="M508" t="n">
-        <v>0.05222370919050134</v>
+        <v>0.06300546448087441</v>
       </c>
       <c r="N508" t="n">
         <v>2</v>
       </c>
       <c r="O508" t="n">
-        <v>0.0810188790521271</v>
+        <v>0.03045557869308633</v>
       </c>
       <c r="P508" t="n">
-        <v>0.4049709805722032</v>
+        <v>0.1237471865783788</v>
       </c>
       <c r="Q508" t="n">
-        <v>0.5140101403756697</v>
+        <v>0.8457972347285347</v>
       </c>
       <c r="R508" t="n">
         <v>1</v>
       </c>
       <c r="S508" t="n">
-        <v>-0.2343113124919098</v>
+        <v>0.07470794258850499</v>
       </c>
       <c r="T508" t="n">
         <v>2</v>
       </c>
       <c r="U508" t="n">
-        <v>-0.2343113124919098</v>
+        <v>0.07470794258850499</v>
       </c>
       <c r="V508" t="n">
-        <v>0.5140101403756697</v>
+        <v>0.8457972347285347</v>
       </c>
       <c r="W508" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="X508" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y508" t="inlineStr"/>
       <c r="Z508" t="n">
-        <v>0.2114099728142472</v>
+        <v>8.457972347285347</v>
       </c>
       <c r="AA508" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB508" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC508" t="inlineStr"/>
@@ -51416,96 +51418,96 @@
     <row r="509">
       <c r="A509" s="1" t="inlineStr">
         <is>
-          <t>YmumZjET</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B509" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E509" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F509" t="n">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="G509" t="n">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="H509" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="I509" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="J509" t="n">
-        <v>0.5830269494941478</v>
+        <v>0.373666196899537</v>
       </c>
       <c r="K509" t="n">
-        <v>0.2181301750994271</v>
+        <v>0.2977652506543185</v>
       </c>
       <c r="L509" t="n">
-        <v>0.1988428754064251</v>
+        <v>0.3285685524461445</v>
       </c>
       <c r="M509" t="n">
-        <v>0.05875714862384762</v>
+        <v>0.04948444895199478</v>
       </c>
       <c r="N509" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O509" t="n">
-        <v>0.4225487020193431</v>
+        <v>0.2956078794391212</v>
       </c>
       <c r="P509" t="n">
-        <v>0.3240030133796011</v>
+        <v>0.3572410901173454</v>
       </c>
       <c r="Q509" t="n">
-        <v>0.2534482846010558</v>
+        <v>0.3471510304435335</v>
       </c>
       <c r="R509" t="n">
         <v>1</v>
       </c>
       <c r="S509" t="n">
-        <v>-0.1604782474748047</v>
+        <v>0.05947583946302692</v>
       </c>
       <c r="T509" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U509" t="n">
-        <v>-0.1604782474748047</v>
+        <v>0.05947583946302692</v>
       </c>
       <c r="V509" t="n">
-        <v>0.4225487020193431</v>
+        <v>0.3572410901173454</v>
       </c>
       <c r="W509" t="n">
-        <v>1.62</v>
+        <v>3.2</v>
       </c>
       <c r="X509" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y509" t="inlineStr"/>
       <c r="Z509" t="n">
-        <v>0.4732051435141655</v>
+        <v>3.572410901173454</v>
       </c>
       <c r="AA509" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB509" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC509" t="inlineStr"/>
@@ -51515,96 +51517,96 @@
     <row r="510">
       <c r="A510" s="1" t="inlineStr">
         <is>
-          <t>j5mWxZE4</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B510" s="2" t="n">
-        <v>45605.60416666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F510" t="n">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="G510" t="n">
-        <v>1.48</v>
+        <v>3.3</v>
       </c>
       <c r="H510" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="I510" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="J510" t="n">
-        <v>0.6346967559943583</v>
+        <v>0.2885143081144649</v>
       </c>
       <c r="K510" t="n">
-        <v>0.2087447108603667</v>
+        <v>0.297530380243042</v>
       </c>
       <c r="L510" t="n">
-        <v>0.156558533145275</v>
+        <v>0.4139553116424932</v>
       </c>
       <c r="M510" t="n">
-        <v>0.0645645645645645</v>
+        <v>0.05031291172595509</v>
       </c>
       <c r="N510" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O510" t="n">
-        <v>0.4593263614046247</v>
+        <v>0.1593014358863176</v>
       </c>
       <c r="P510" t="n">
-        <v>0.3181009218034846</v>
+        <v>0.2837467808408203</v>
       </c>
       <c r="Q510" t="n">
-        <v>0.2225727167918907</v>
+        <v>0.5569517832728622</v>
       </c>
       <c r="R510" t="n">
         <v>1</v>
       </c>
       <c r="S510" t="n">
-        <v>-0.1753703945897336</v>
+        <v>0.142996471630369</v>
       </c>
       <c r="T510" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U510" t="n">
-        <v>-0.1753703945897336</v>
+        <v>0.142996471630369</v>
       </c>
       <c r="V510" t="n">
-        <v>0.4593263614046247</v>
+        <v>0.5569517832728622</v>
       </c>
       <c r="W510" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="X510" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y510" t="inlineStr"/>
       <c r="Z510" t="n">
-        <v>0.5057794566181982</v>
+        <v>5.569517832728622</v>
       </c>
       <c r="AA510" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB510" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC510" t="inlineStr"/>
@@ -51614,197 +51616,195 @@
     <row r="511">
       <c r="A511" s="1" t="inlineStr">
         <is>
-          <t>UJQITUyi</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B511" s="2" t="n">
-        <v>45606.47916666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F511" t="n">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="G511" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="H511" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="I511" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="J511" t="n">
-        <v>0.4512126339537507</v>
+        <v>0.2875429881543752</v>
       </c>
       <c r="K511" t="n">
-        <v>0.2526790750141004</v>
+        <v>0.2711119602598395</v>
       </c>
       <c r="L511" t="n">
-        <v>0.2961082910321489</v>
+        <v>0.4413450515857852</v>
       </c>
       <c r="M511" t="n">
-        <v>0.05535714285714288</v>
+        <v>0.05386086781435617</v>
       </c>
       <c r="N511" t="n">
         <v>2</v>
       </c>
       <c r="O511" t="n">
-        <v>0.2659409384668499</v>
+        <v>0.3191279762580632</v>
       </c>
       <c r="P511" t="n">
-        <v>0.3510185330841873</v>
+        <v>0.3286445238624505</v>
       </c>
       <c r="Q511" t="n">
-        <v>0.3830405284489628</v>
+        <v>0.3522274998794863</v>
       </c>
       <c r="R511" t="n">
         <v>1</v>
       </c>
       <c r="S511" t="n">
-        <v>0.08693223741681388</v>
+        <v>-0.08911755170629893</v>
       </c>
       <c r="T511" t="n">
         <v>2</v>
       </c>
       <c r="U511" t="n">
-        <v>0.08693223741681388</v>
+        <v>-0.08911755170629893</v>
       </c>
       <c r="V511" t="n">
-        <v>0.3830405284489628</v>
+        <v>0.3522274998794863</v>
       </c>
       <c r="W511" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="X511" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y511" t="inlineStr"/>
       <c r="Z511" t="n">
-        <v>1.784159961324759</v>
+        <v>3.522274998794863</v>
       </c>
       <c r="AA511" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB511" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="AC511" t="n">
-        <v>1</v>
-      </c>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="AC511" t="inlineStr"/>
       <c r="AD511" t="inlineStr"/>
       <c r="AE511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="1" t="inlineStr">
         <is>
-          <t>UkaNveph</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B512" s="2" t="n">
-        <v>45606.5625</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="E512" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F512" t="n">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="G512" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="H512" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I512" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J512" t="n">
-        <v>0.5293737895416398</v>
+        <v>0.4415584415584415</v>
       </c>
       <c r="K512" t="n">
-        <v>0.2324080051646223</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="L512" t="n">
-        <v>0.2382182052937379</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="M512" t="n">
-        <v>0.04945799457994582</v>
+        <v>0.05335157318741457</v>
       </c>
       <c r="N512" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O512" t="n">
-        <v>0.3145255144579812</v>
+        <v>0.4771835695487086</v>
       </c>
       <c r="P512" t="n">
-        <v>0.3572530097404699</v>
+        <v>0.332348546930707</v>
       </c>
       <c r="Q512" t="n">
-        <v>0.3282214758015489</v>
+        <v>0.1904678835205843</v>
       </c>
       <c r="R512" t="n">
         <v>1</v>
       </c>
       <c r="S512" t="n">
-        <v>0.1248450045758476</v>
+        <v>0.03562512799026707</v>
       </c>
       <c r="T512" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U512" t="n">
-        <v>0.1248450045758476</v>
+        <v>0.03562512799026707</v>
       </c>
       <c r="V512" t="n">
-        <v>0.3572530097404699</v>
+        <v>0.4771835695487086</v>
       </c>
       <c r="W512" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="X512" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y512" t="inlineStr"/>
       <c r="Z512" t="n">
-        <v>1.664044581973364</v>
+        <v>4.771835695487086</v>
       </c>
       <c r="AA512" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB512" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC512" t="inlineStr"/>
@@ -51814,296 +51814,296 @@
     <row r="513">
       <c r="A513" s="1" t="inlineStr">
         <is>
-          <t>xMovyDqH</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B513" s="2" t="n">
-        <v>45606.64583333334</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E513" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F513" t="n">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="G513" t="n">
-        <v>2.63</v>
+        <v>1.33</v>
       </c>
       <c r="H513" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="I513" t="n">
-        <v>2.55</v>
+        <v>8</v>
       </c>
       <c r="J513" t="n">
-        <v>0.3593501499808749</v>
+        <v>0.7101928819304333</v>
       </c>
       <c r="K513" t="n">
-        <v>0.2700259698427717</v>
+        <v>0.1717375514486321</v>
       </c>
       <c r="L513" t="n">
-        <v>0.3706238801763534</v>
+        <v>0.1180695666209345</v>
       </c>
       <c r="M513" t="n">
-        <v>0.05809928534151299</v>
+        <v>0.05869788106630214</v>
       </c>
       <c r="N513" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O513" t="n">
-        <v>0.2609290332921262</v>
+        <v>0.2506771451402429</v>
       </c>
       <c r="P513" t="n">
-        <v>0.3638643978490307</v>
+        <v>0.3926451799139036</v>
       </c>
       <c r="Q513" t="n">
-        <v>0.3752065688588429</v>
+        <v>0.3566776749458535</v>
       </c>
       <c r="R513" t="n">
         <v>1</v>
       </c>
       <c r="S513" t="n">
-        <v>0.004582688682489511</v>
+        <v>0.2209076284652716</v>
       </c>
       <c r="T513" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U513" t="n">
-        <v>0.004582688682489511</v>
+        <v>0.2209076284652716</v>
       </c>
       <c r="V513" t="n">
-        <v>0.3752065688588429</v>
+        <v>0.3926451799139036</v>
       </c>
       <c r="W513" t="n">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="X513" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y513" t="inlineStr"/>
       <c r="Z513" t="n">
-        <v>1.747670253314161</v>
+        <v>3.926451799139036</v>
       </c>
       <c r="AA513" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB513" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="AC513" t="inlineStr"/>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="AC513" t="n">
+        <v>1</v>
+      </c>
       <c r="AD513" t="inlineStr"/>
       <c r="AE513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>xdpX3Q36</t>
         </is>
       </c>
       <c r="B514" s="2" t="n">
-        <v>45603.69791666666</v>
+        <v>45618.625</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E514" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F514" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G514" t="n">
-        <v>2.9</v>
+        <v>1.53</v>
       </c>
       <c r="H514" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="I514" t="n">
-        <v>2.4</v>
+        <v>5.75</v>
       </c>
       <c r="J514" t="n">
-        <v>0.3239263803680982</v>
+        <v>0.6174990513369328</v>
       </c>
       <c r="K514" t="n">
-        <v>0.2846625766871166</v>
+        <v>0.2181925054377615</v>
       </c>
       <c r="L514" t="n">
-        <v>0.3914110429447853</v>
+        <v>0.1643084432253056</v>
       </c>
       <c r="M514" t="n">
-        <v>0.0645245559038663</v>
+        <v>0.05845469693718108</v>
       </c>
       <c r="N514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O514" t="n">
-        <v>0.1616330260227123</v>
+        <v>0.519876569818237</v>
       </c>
       <c r="P514" t="n">
-        <v>0.4255251614233783</v>
+        <v>0.2800465345400713</v>
       </c>
       <c r="Q514" t="n">
-        <v>0.4128418125539094</v>
+        <v>0.2000768956416916</v>
       </c>
       <c r="R514" t="n">
         <v>1</v>
       </c>
       <c r="S514" t="n">
-        <v>0.1408625847362617</v>
+        <v>-0.09762248151869579</v>
       </c>
       <c r="T514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U514" t="n">
-        <v>0.1408625847362617</v>
+        <v>-0.09762248151869579</v>
       </c>
       <c r="V514" t="n">
-        <v>0.4255251614233783</v>
+        <v>0.519876569818237</v>
       </c>
       <c r="W514" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="X514" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y514" t="inlineStr"/>
       <c r="Z514" t="n">
-        <v>0.851050322846756</v>
+        <v>5.19876569818237</v>
       </c>
       <c r="AA514" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB514" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC514" t="n">
-        <v>1</v>
-      </c>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="AC514" t="inlineStr"/>
       <c r="AD514" t="inlineStr"/>
       <c r="AE514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>Im9H9ezS</t>
         </is>
       </c>
       <c r="B515" s="2" t="n">
-        <v>45604.69791666666</v>
+        <v>45618.70833333334</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="E515" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F515" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G515" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="H515" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="I515" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="J515" t="n">
-        <v>0.4212076583210604</v>
+        <v>0.7099057574385776</v>
       </c>
       <c r="K515" t="n">
-        <v>0.2916053019145803</v>
+        <v>0.1642042882423145</v>
       </c>
       <c r="L515" t="n">
-        <v>0.2871870397643594</v>
+        <v>0.1258899543191078</v>
       </c>
       <c r="M515" t="n">
-        <v>0.05516705516705511</v>
+        <v>0.05912607605971454</v>
       </c>
       <c r="N515" t="n">
         <v>1</v>
       </c>
       <c r="O515" t="n">
-        <v>0.3692435114836438</v>
+        <v>0.6503282940627227</v>
       </c>
       <c r="P515" t="n">
-        <v>0.2730166960722579</v>
+        <v>0.2948201431721411</v>
       </c>
       <c r="Q515" t="n">
-        <v>0.3577397924440981</v>
+        <v>0.05485156276513609</v>
       </c>
       <c r="R515" t="n">
         <v>1</v>
       </c>
       <c r="S515" t="n">
-        <v>-0.05196414683741662</v>
+        <v>-0.0595774633758549</v>
       </c>
       <c r="T515" t="n">
         <v>1</v>
       </c>
       <c r="U515" t="n">
-        <v>-0.05196414683741662</v>
+        <v>-0.0595774633758549</v>
       </c>
       <c r="V515" t="n">
-        <v>0.3692435114836438</v>
+        <v>0.6503282940627227</v>
       </c>
       <c r="W515" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="X515" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y515" t="inlineStr"/>
       <c r="Z515" t="n">
-        <v>0.3227738482679543</v>
+        <v>6.503282940627227</v>
       </c>
       <c r="AA515" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB515" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC515" t="inlineStr"/>
@@ -52113,96 +52113,96 @@
     <row r="516">
       <c r="A516" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>SMfm4Zck</t>
         </is>
       </c>
       <c r="B516" s="2" t="n">
-        <v>45605.45833333334</v>
+        <v>45619.54166666666</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E516" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F516" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G516" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="H516" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I516" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J516" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.4221789883268482</v>
       </c>
       <c r="K516" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2714007782101167</v>
       </c>
       <c r="L516" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.306420233463035</v>
       </c>
       <c r="M516" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.05273937532002049</v>
       </c>
       <c r="N516" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O516" t="n">
-        <v>0.3561877499891236</v>
+        <v>0.2796054787068856</v>
       </c>
       <c r="P516" t="n">
-        <v>0.3065246375688527</v>
+        <v>0.3367051480589169</v>
       </c>
       <c r="Q516" t="n">
-        <v>0.3372876124420239</v>
+        <v>0.3836893732341974</v>
       </c>
       <c r="R516" t="n">
         <v>1</v>
       </c>
       <c r="S516" t="n">
-        <v>-0.01494627062943316</v>
+        <v>0.0772691397711624</v>
       </c>
       <c r="T516" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U516" t="n">
-        <v>-0.01494627062943316</v>
+        <v>0.0772691397711624</v>
       </c>
       <c r="V516" t="n">
-        <v>0.3561877499891236</v>
+        <v>0.3836893732341974</v>
       </c>
       <c r="W516" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="X516" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y516" t="inlineStr"/>
       <c r="Z516" t="n">
-        <v>0.5928053349427814</v>
+        <v>3.836893732341974</v>
       </c>
       <c r="AA516" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB516" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC516" t="inlineStr"/>
@@ -52212,96 +52212,96 @@
     <row r="517">
       <c r="A517" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>GryrQGK8</t>
         </is>
       </c>
       <c r="B517" s="2" t="n">
-        <v>45605.58333333334</v>
+        <v>45619.625</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="E517" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F517" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G517" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="H517" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I517" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="J517" t="n">
-        <v>0.1893830703012913</v>
+        <v>0.3966088481777432</v>
       </c>
       <c r="K517" t="n">
-        <v>0.236728837876614</v>
+        <v>0.2572597934125901</v>
       </c>
       <c r="L517" t="n">
-        <v>0.5738880918220947</v>
+        <v>0.3461313584096668</v>
       </c>
       <c r="M517" t="n">
-        <v>0.05606060606060614</v>
+        <v>0.05057330057330045</v>
       </c>
       <c r="N517" t="n">
         <v>2</v>
       </c>
       <c r="O517" t="n">
-        <v>0.08274019555151668</v>
+        <v>0.2952010208929276</v>
       </c>
       <c r="P517" t="n">
-        <v>0.4044060291221481</v>
+        <v>0.3153863873607415</v>
       </c>
       <c r="Q517" t="n">
-        <v>0.5128537753263355</v>
+        <v>0.3894125917463309</v>
       </c>
       <c r="R517" t="n">
         <v>1</v>
       </c>
       <c r="S517" t="n">
-        <v>-0.06103431649575919</v>
+        <v>0.04328123333666412</v>
       </c>
       <c r="T517" t="n">
         <v>2</v>
       </c>
       <c r="U517" t="n">
-        <v>-0.06103431649575919</v>
+        <v>0.04328123333666412</v>
       </c>
       <c r="V517" t="n">
-        <v>0.5128537753263355</v>
+        <v>0.3894125917463309</v>
       </c>
       <c r="W517" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="X517" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y517" t="inlineStr"/>
       <c r="Z517" t="n">
-        <v>0.5374330186865971</v>
+        <v>3.894125917463309</v>
       </c>
       <c r="AA517" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB517" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC517" t="inlineStr"/>
@@ -52311,96 +52311,94 @@
     <row r="518">
       <c r="A518" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B518" s="2" t="n">
-        <v>45605.69791666666</v>
+        <v>45604.6875</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E518" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F518" t="n">
-        <v>771</v>
+        <v>591</v>
       </c>
       <c r="G518" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="H518" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="I518" t="n">
-        <v>6.25</v>
+        <v>3.1</v>
       </c>
       <c r="J518" t="n">
-        <v>0.6046811624762779</v>
+        <v>0.3999920597109735</v>
       </c>
       <c r="K518" t="n">
-        <v>0.2434229295096811</v>
+        <v>0.2929172621883437</v>
       </c>
       <c r="L518" t="n">
-        <v>0.151895908014041</v>
+        <v>0.3070906781006829</v>
       </c>
       <c r="M518" t="n">
-        <v>0.05335293156949206</v>
+        <v>0.05044102008048879</v>
       </c>
       <c r="N518" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O518" t="n">
-        <v>0.4491990320618583</v>
+        <v>0.2451816872879612</v>
       </c>
       <c r="P518" t="n">
-        <v>0.3324819716292451</v>
+        <v>0.2823895203883839</v>
       </c>
       <c r="Q518" t="n">
-        <v>0.2183189963088966</v>
-      </c>
-      <c r="R518" t="n">
-        <v>1</v>
-      </c>
+        <v>0.4724287923236548</v>
+      </c>
+      <c r="R518" t="inlineStr"/>
       <c r="S518" t="n">
-        <v>-0.1554821304144196</v>
+        <v>0.165338114222972</v>
       </c>
       <c r="T518" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U518" t="n">
-        <v>-0.1554821304144196</v>
+        <v>0.165338114222972</v>
       </c>
       <c r="V518" t="n">
-        <v>0.4491990320618583</v>
+        <v>0.4724287923236548</v>
       </c>
       <c r="W518" t="n">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="X518" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y518" t="inlineStr"/>
       <c r="Z518" t="n">
-        <v>0</v>
+        <v>7.086132807597141</v>
       </c>
       <c r="AA518" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB518" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC518" t="inlineStr"/>
@@ -52410,96 +52408,96 @@
     <row r="519">
       <c r="A519" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B519" s="2" t="n">
-        <v>45606.35416666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="E519" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F519" t="n">
-        <v>771</v>
+        <v>591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.38</v>
+        <v>9.5</v>
       </c>
       <c r="H519" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="I519" t="n">
-        <v>8</v>
+        <v>1.25</v>
       </c>
       <c r="J519" t="n">
-        <v>0.6835147045597626</v>
+        <v>0.09938837920489296</v>
       </c>
       <c r="K519" t="n">
-        <v>0.1985790089036784</v>
+        <v>0.1452599388379205</v>
       </c>
       <c r="L519" t="n">
-        <v>0.117906286536559</v>
+        <v>0.7553516819571866</v>
       </c>
       <c r="M519" t="n">
-        <v>0.06016399694889407</v>
+        <v>0.05910931174089074</v>
       </c>
       <c r="N519" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O519" t="n">
-        <v>0.2743034273969107</v>
+        <v>0.05423050087842236</v>
       </c>
       <c r="P519" t="n">
-        <v>0.4923804000276243</v>
+        <v>0.2116805041199112</v>
       </c>
       <c r="Q519" t="n">
-        <v>0.2333161725754651</v>
+        <v>0.7340889950016665</v>
       </c>
       <c r="R519" t="n">
         <v>1</v>
       </c>
       <c r="S519" t="n">
-        <v>0.293801391123946</v>
+        <v>-0.02126268695552014</v>
       </c>
       <c r="T519" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U519" t="n">
-        <v>0.293801391123946</v>
+        <v>-0.02126268695552014</v>
       </c>
       <c r="V519" t="n">
-        <v>0.4923804000276243</v>
+        <v>0.7340889950016665</v>
       </c>
       <c r="W519" t="n">
-        <v>4.75</v>
+        <v>1.25</v>
       </c>
       <c r="X519" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y519" t="inlineStr"/>
       <c r="Z519" t="n">
-        <v>0.984760800055248</v>
+        <v>4.056489044872412</v>
       </c>
       <c r="AA519" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB519" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC519" t="inlineStr"/>
@@ -52509,96 +52507,96 @@
     <row r="520">
       <c r="A520" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B520" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E520" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F520" t="n">
-        <v>771</v>
+        <v>591</v>
       </c>
       <c r="G520" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="H520" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I520" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J520" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="K520" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="L520" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="M520" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="N520" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O520" t="n">
-        <v>0.3691151532503577</v>
+        <v>0.1379586541384551</v>
       </c>
       <c r="P520" t="n">
-        <v>0.2669719738686972</v>
+        <v>0.2194789658739746</v>
       </c>
       <c r="Q520" t="n">
-        <v>0.3639128728809451</v>
+        <v>0.6425623799875704</v>
       </c>
       <c r="R520" t="n">
         <v>1</v>
       </c>
       <c r="S520" t="n">
-        <v>-0.09120827661049219</v>
+        <v>0.1724131262562271</v>
       </c>
       <c r="T520" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U520" t="n">
-        <v>-0.09120827661049219</v>
+        <v>0.1724131262562271</v>
       </c>
       <c r="V520" t="n">
-        <v>0.3691151532503577</v>
+        <v>0.6425623799875704</v>
       </c>
       <c r="W520" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="X520" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y520" t="inlineStr"/>
       <c r="Z520" t="n">
-        <v>0.008564093616777896</v>
+        <v>8.326343031327992</v>
       </c>
       <c r="AA520" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB520" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC520" t="inlineStr"/>
@@ -52608,96 +52606,96 @@
     <row r="521">
       <c r="A521" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B521" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="E521" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F521" t="n">
-        <v>771</v>
+        <v>591</v>
       </c>
       <c r="G521" t="n">
-        <v>1.44</v>
+        <v>9.5</v>
       </c>
       <c r="H521" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="I521" t="n">
-        <v>7</v>
+        <v>1.22</v>
       </c>
       <c r="J521" t="n">
-        <v>0.6554307116104868</v>
+        <v>0.09946733340580496</v>
       </c>
       <c r="K521" t="n">
-        <v>0.2097378277153558</v>
+        <v>0.125991955647353</v>
       </c>
       <c r="L521" t="n">
-        <v>0.1348314606741573</v>
+        <v>0.774540710946842</v>
       </c>
       <c r="M521" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.05826862237561126</v>
       </c>
       <c r="N521" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O521" t="n">
-        <v>0.2602123189645497</v>
+        <v>0.04048311270516788</v>
       </c>
       <c r="P521" t="n">
-        <v>0.4274435564298052</v>
+        <v>0.08763839322117328</v>
       </c>
       <c r="Q521" t="n">
-        <v>0.3123441246056451</v>
+        <v>0.8718784940736588</v>
       </c>
       <c r="R521" t="n">
         <v>1</v>
       </c>
       <c r="S521" t="n">
-        <v>0.2177057287144495</v>
+        <v>0.09733778312681685</v>
       </c>
       <c r="T521" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U521" t="n">
-        <v>0.2177057287144495</v>
+        <v>0.09733778312681685</v>
       </c>
       <c r="V521" t="n">
-        <v>0.4274435564298052</v>
+        <v>0.8718784940736588</v>
       </c>
       <c r="W521" t="n">
-        <v>4.5</v>
+        <v>1.22</v>
       </c>
       <c r="X521" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y521" t="inlineStr"/>
       <c r="Z521" t="n">
-        <v>0.8548871128596099</v>
+        <v>7.882685166130789</v>
       </c>
       <c r="AA521" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB521" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC521" t="inlineStr"/>
@@ -52707,96 +52705,96 @@
     <row r="522">
       <c r="A522" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B522" s="2" t="n">
-        <v>45606.58333333334</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="E522" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F522" t="n">
-        <v>771</v>
+        <v>591</v>
       </c>
       <c r="G522" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="H522" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I522" t="n">
-        <v>1.83</v>
+        <v>5</v>
       </c>
       <c r="J522" t="n">
-        <v>0.2315144654925592</v>
+        <v>0.5968169761273209</v>
       </c>
       <c r="K522" t="n">
-        <v>0.2497919232946033</v>
+        <v>0.2122015915119363</v>
       </c>
       <c r="L522" t="n">
-        <v>0.5186936112128375</v>
+        <v>0.1909814323607427</v>
       </c>
       <c r="M522" t="n">
-        <v>0.0535084211929262</v>
+        <v>0.04722222222222228</v>
       </c>
       <c r="N522" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O522" t="n">
-        <v>0.2807527424691044</v>
+        <v>0.5305649849773443</v>
       </c>
       <c r="P522" t="n">
-        <v>0.3628947951606609</v>
+        <v>0.2977688303422035</v>
       </c>
       <c r="Q522" t="n">
-        <v>0.3563524623702344</v>
+        <v>0.1716661846804522</v>
       </c>
       <c r="R522" t="n">
         <v>1</v>
       </c>
       <c r="S522" t="n">
-        <v>0.1131028718660576</v>
+        <v>-0.0662519911499766</v>
       </c>
       <c r="T522" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U522" t="n">
-        <v>0.1131028718660576</v>
+        <v>-0.0662519911499766</v>
       </c>
       <c r="V522" t="n">
-        <v>0.3628947951606609</v>
+        <v>0.5305649849773443</v>
       </c>
       <c r="W522" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="X522" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y522" t="inlineStr"/>
       <c r="Z522" t="n">
-        <v>0.7257895903213214</v>
+        <v>1.659731377358987</v>
       </c>
       <c r="AA522" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB522" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC522" t="inlineStr"/>
@@ -52806,96 +52804,96 @@
     <row r="523">
       <c r="A523" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B523" s="2" t="n">
-        <v>45606.69791666666</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E523" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F523" t="n">
-        <v>771</v>
+        <v>591</v>
       </c>
       <c r="G523" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="H523" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="I523" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J523" t="n">
-        <v>0.5180518051805181</v>
+        <v>0.5964499519258584</v>
       </c>
       <c r="K523" t="n">
-        <v>0.2562256225622562</v>
+        <v>0.2162647631694221</v>
       </c>
       <c r="L523" t="n">
-        <v>0.2257225722572257</v>
+        <v>0.1872852849047196</v>
       </c>
       <c r="M523" t="n">
-        <v>0.05481359579720224</v>
+        <v>0.06788955737632563</v>
       </c>
       <c r="N523" t="n">
         <v>1</v>
       </c>
       <c r="O523" t="n">
-        <v>0.4930172902943962</v>
+        <v>0.5443949375586612</v>
       </c>
       <c r="P523" t="n">
-        <v>0.259383353039037</v>
+        <v>0.3369520895012321</v>
       </c>
       <c r="Q523" t="n">
-        <v>0.2475993566665667</v>
+        <v>0.1186529729401067</v>
       </c>
       <c r="R523" t="n">
         <v>1</v>
       </c>
       <c r="S523" t="n">
-        <v>-0.02503451488612191</v>
+        <v>-0.05205501436719717</v>
       </c>
       <c r="T523" t="n">
         <v>1</v>
       </c>
       <c r="U523" t="n">
-        <v>-0.02503451488612191</v>
+        <v>-0.05205501436719717</v>
       </c>
       <c r="V523" t="n">
-        <v>0.4930172902943962</v>
+        <v>0.5443949375586612</v>
       </c>
       <c r="W523" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="X523" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y523" t="inlineStr"/>
       <c r="Z523" t="n">
-        <v>0.7857584614998165</v>
+        <v>2.101093000561703</v>
       </c>
       <c r="AA523" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB523" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC523" t="inlineStr"/>
@@ -52905,78 +52903,78 @@
     <row r="524">
       <c r="A524" s="1" t="inlineStr">
         <is>
-          <t>rPc4X7Gj</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B524" s="2" t="n">
-        <v>45604.70833333334</v>
+        <v>45606.47916666666</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="E524" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F524" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G524" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="H524" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I524" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="J524" t="n">
-        <v>0.5405405405405405</v>
+        <v>0.4592557701365991</v>
       </c>
       <c r="K524" t="n">
-        <v>0.2702702702702702</v>
+        <v>0.2510598210080075</v>
       </c>
       <c r="L524" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.2896844088553933</v>
       </c>
       <c r="M524" t="n">
-        <v>0.05714285714285716</v>
+        <v>0.06216385240775502</v>
       </c>
       <c r="N524" t="n">
         <v>1</v>
       </c>
       <c r="O524" t="n">
-        <v>0.6303389668464661</v>
+        <v>0.3713369211320147</v>
       </c>
       <c r="P524" t="n">
-        <v>0.245873898267746</v>
+        <v>0.3192392031647657</v>
       </c>
       <c r="Q524" t="n">
-        <v>0.1237871721386909</v>
+        <v>0.3094238757032194</v>
       </c>
       <c r="R524" t="n">
         <v>1</v>
       </c>
       <c r="S524" t="n">
-        <v>0.0897984263059256</v>
+        <v>-0.08791884900458441</v>
       </c>
       <c r="T524" t="n">
         <v>1</v>
       </c>
       <c r="U524" t="n">
-        <v>0.0897984263059256</v>
+        <v>-0.08791884900458441</v>
       </c>
       <c r="V524" t="n">
-        <v>0.6303389668464661</v>
+        <v>0.3713369211320147</v>
       </c>
       <c r="W524" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="X524" t="inlineStr">
         <is>
@@ -52985,97 +52983,99 @@
       </c>
       <c r="Y524" t="inlineStr"/>
       <c r="Z524" t="n">
-        <v>7.02978622343648</v>
+        <v>0.1228845319604818</v>
       </c>
       <c r="AA524" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB524" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC524" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="AC524" t="n">
+        <v>1</v>
+      </c>
       <c r="AD524" t="inlineStr"/>
       <c r="AE524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="1" t="inlineStr">
         <is>
-          <t>nucZxUhT</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B525" s="2" t="n">
-        <v>45605.41666666666</v>
+        <v>45606.5625</v>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="E525" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F525" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G525" t="n">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="H525" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="I525" t="n">
-        <v>15</v>
+        <v>3.7</v>
       </c>
       <c r="J525" t="n">
-        <v>0.7935216082037927</v>
+        <v>0.5028882093102276</v>
       </c>
       <c r="K525" t="n">
-        <v>0.1440546919508424</v>
+        <v>0.2388718994223581</v>
       </c>
       <c r="L525" t="n">
-        <v>0.06242369984536501</v>
+        <v>0.2582398912674141</v>
       </c>
       <c r="M525" t="n">
-        <v>0.06797044763146465</v>
+        <v>0.04658605974395447</v>
       </c>
       <c r="N525" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O525" t="n">
-        <v>0.7477745413780212</v>
+        <v>0.3899514257709533</v>
       </c>
       <c r="P525" t="n">
-        <v>0.1773705929517746</v>
+        <v>0.3914355888829029</v>
       </c>
       <c r="Q525" t="n">
-        <v>0.07485481351613998</v>
+        <v>0.2186129853461438</v>
       </c>
       <c r="R525" t="n">
         <v>1</v>
       </c>
       <c r="S525" t="n">
-        <v>-0.04574706682577145</v>
+        <v>0.1525636894605448</v>
       </c>
       <c r="T525" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U525" t="n">
-        <v>-0.04574706682577145</v>
+        <v>0.1525636894605448</v>
       </c>
       <c r="V525" t="n">
-        <v>0.7477745413780212</v>
+        <v>0.3914355888829029</v>
       </c>
       <c r="W525" t="n">
-        <v>1.18</v>
+        <v>4</v>
       </c>
       <c r="X525" t="inlineStr">
         <is>
@@ -53084,16 +53084,16 @@
       </c>
       <c r="Y525" t="inlineStr"/>
       <c r="Z525" t="n">
-        <v>7.829284446384814</v>
+        <v>6.260564667031762</v>
       </c>
       <c r="AA525" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB525" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC525" t="inlineStr"/>
@@ -53103,78 +53103,78 @@
     <row r="526">
       <c r="A526" s="1" t="inlineStr">
         <is>
-          <t>bXuieB8c</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B526" s="2" t="n">
-        <v>45605.51041666666</v>
+        <v>45606.64583333334</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="E526" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F526" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G526" t="n">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="H526" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="I526" t="n">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="J526" t="n">
-        <v>0.5835764902042518</v>
+        <v>0.3344262295081967</v>
       </c>
       <c r="K526" t="n">
-        <v>0.236348478532722</v>
+        <v>0.2754098360655738</v>
       </c>
       <c r="L526" t="n">
-        <v>0.1800750312630263</v>
+        <v>0.3901639344262295</v>
       </c>
       <c r="M526" t="n">
-        <v>0.05776014109347427</v>
+        <v>0.06792717086834732</v>
       </c>
       <c r="N526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O526" t="n">
-        <v>0.5775689482688904</v>
+        <v>0.2903942023150049</v>
       </c>
       <c r="P526" t="n">
-        <v>0.279651403427124</v>
+        <v>0.2457897659363611</v>
       </c>
       <c r="Q526" t="n">
-        <v>0.142779678106308</v>
+        <v>0.463816031748634</v>
       </c>
       <c r="R526" t="n">
         <v>1</v>
       </c>
       <c r="S526" t="n">
-        <v>-0.00600754193536146</v>
+        <v>0.07365209732240446</v>
       </c>
       <c r="T526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U526" t="n">
-        <v>-0.00600754193536146</v>
+        <v>0.07365209732240446</v>
       </c>
       <c r="V526" t="n">
-        <v>0.5775689482688904</v>
+        <v>0.463816031748634</v>
       </c>
       <c r="W526" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="X526" t="inlineStr">
         <is>
@@ -53183,16 +53183,16 @@
       </c>
       <c r="Y526" t="inlineStr"/>
       <c r="Z526" t="n">
-        <v>6.374275923623946</v>
+        <v>4.740152631489074</v>
       </c>
       <c r="AA526" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB526" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC526" t="inlineStr"/>
@@ -53202,78 +53202,78 @@
     <row r="527">
       <c r="A527" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>EuQnZBVQ</t>
         </is>
       </c>
       <c r="B527" s="2" t="n">
-        <v>45605.60416666666</v>
+        <v>45618.6875</v>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E527" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F527" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G527" t="n">
-        <v>2.63</v>
+        <v>1.1</v>
       </c>
       <c r="H527" t="n">
-        <v>2.9</v>
+        <v>10</v>
       </c>
       <c r="I527" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J527" t="n">
-        <v>0.3592517652888467</v>
+        <v>0.8450704225352113</v>
       </c>
       <c r="K527" t="n">
-        <v>0.3258041871412644</v>
+        <v>0.09295774647887325</v>
       </c>
       <c r="L527" t="n">
-        <v>0.3149440475698889</v>
+        <v>0.06197183098591549</v>
       </c>
       <c r="M527" t="n">
-        <v>0.05838905642235925</v>
+        <v>0.07575757575757569</v>
       </c>
       <c r="N527" t="n">
         <v>1</v>
       </c>
       <c r="O527" t="n">
-        <v>0.5252802968025208</v>
+        <v>0.4207096998051714</v>
       </c>
       <c r="P527" t="n">
-        <v>0.3036795258522034</v>
+        <v>0.3667474441088974</v>
       </c>
       <c r="Q527" t="n">
-        <v>0.1710400879383087</v>
+        <v>0.2125428560859311</v>
       </c>
       <c r="R527" t="n">
         <v>1</v>
       </c>
       <c r="S527" t="n">
-        <v>0.1660285315136741</v>
+        <v>-0.4243607227300398</v>
       </c>
       <c r="T527" t="n">
         <v>1</v>
       </c>
       <c r="U527" t="n">
-        <v>0.1660285315136741</v>
+        <v>-0.4243607227300398</v>
       </c>
       <c r="V527" t="n">
-        <v>0.5252802968025208</v>
+        <v>0.4207096998051714</v>
       </c>
       <c r="W527" t="n">
-        <v>2.63</v>
+        <v>1.1</v>
       </c>
       <c r="X527" t="inlineStr">
         <is>
@@ -53282,97 +53282,99 @@
       </c>
       <c r="Y527" t="inlineStr"/>
       <c r="Z527" t="n">
-        <v>5.858130923396344</v>
+        <v>0</v>
       </c>
       <c r="AA527" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB527" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC527" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="AC527" t="n">
+        <v>1</v>
+      </c>
       <c r="AD527" t="inlineStr"/>
       <c r="AE527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>2qNaDU87</t>
         </is>
       </c>
       <c r="B528" s="2" t="n">
-        <v>45605.70833333334</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E528" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F528" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G528" t="n">
-        <v>2.88</v>
+        <v>1.22</v>
       </c>
       <c r="H528" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I528" t="n">
-        <v>2.55</v>
+        <v>15</v>
       </c>
       <c r="J528" t="n">
-        <v>0.3300970873786407</v>
+        <v>0.7784120394395433</v>
       </c>
       <c r="K528" t="n">
-        <v>0.2970873786407767</v>
+        <v>0.1582771146860404</v>
       </c>
       <c r="L528" t="n">
-        <v>0.3728155339805825</v>
+        <v>0.06331084587441618</v>
       </c>
       <c r="M528" t="n">
-        <v>0.0518790849673203</v>
+        <v>0.0530054644808744</v>
       </c>
       <c r="N528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O528" t="n">
-        <v>0.279819667339325</v>
+        <v>0.6939419031995516</v>
       </c>
       <c r="P528" t="n">
-        <v>0.3650146722793579</v>
+        <v>0.2565956046804507</v>
       </c>
       <c r="Q528" t="n">
-        <v>0.3551656901836395</v>
+        <v>0.04946249211999764</v>
       </c>
       <c r="R528" t="n">
         <v>1</v>
       </c>
       <c r="S528" t="n">
-        <v>0.06792729363858124</v>
+        <v>-0.08447013623999167</v>
       </c>
       <c r="T528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U528" t="n">
-        <v>0.06792729363858124</v>
+        <v>-0.08447013623999167</v>
       </c>
       <c r="V528" t="n">
-        <v>0.3650146722793579</v>
+        <v>0.6939419031995516</v>
       </c>
       <c r="W528" t="n">
-        <v>3.2</v>
+        <v>1.22</v>
       </c>
       <c r="X528" t="inlineStr">
         <is>
@@ -53381,16 +53383,16 @@
       </c>
       <c r="Y528" t="inlineStr"/>
       <c r="Z528" t="n">
-        <v>4.070786115887732</v>
+        <v>2.225383488997406</v>
       </c>
       <c r="AA528" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB528" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC528" t="inlineStr"/>
@@ -53400,78 +53402,78 @@
     <row r="529">
       <c r="A529" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>pOGITkgl</t>
         </is>
       </c>
       <c r="B529" s="2" t="n">
-        <v>45606.41666666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E529" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F529" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G529" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="H529" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="I529" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="J529" t="n">
-        <v>0.4822695035460994</v>
+        <v>0.5746381507885073</v>
       </c>
       <c r="K529" t="n">
-        <v>0.2765957446808511</v>
+        <v>0.225750702095485</v>
       </c>
       <c r="L529" t="n">
-        <v>0.2411347517730497</v>
+        <v>0.1996111471160078</v>
       </c>
       <c r="M529" t="n">
-        <v>0.06334841628959276</v>
+        <v>0.05468215994531778</v>
       </c>
       <c r="N529" t="n">
         <v>1</v>
       </c>
       <c r="O529" t="n">
-        <v>0.4491502046585083</v>
+        <v>0.5353976182872061</v>
       </c>
       <c r="P529" t="n">
-        <v>0.3417275846004486</v>
+        <v>0.2974335586995293</v>
       </c>
       <c r="Q529" t="n">
-        <v>0.2091221958398819</v>
+        <v>0.1671688230132646</v>
       </c>
       <c r="R529" t="n">
         <v>1</v>
       </c>
       <c r="S529" t="n">
-        <v>-0.03311929888759108</v>
+        <v>-0.03924053250130122</v>
       </c>
       <c r="T529" t="n">
         <v>1</v>
       </c>
       <c r="U529" t="n">
-        <v>-0.03311929888759108</v>
+        <v>-0.03924053250130122</v>
       </c>
       <c r="V529" t="n">
-        <v>0.4491502046585083</v>
+        <v>0.5353976182872061</v>
       </c>
       <c r="W529" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="X529" t="inlineStr">
         <is>
@@ -53480,99 +53482,97 @@
       </c>
       <c r="Y529" t="inlineStr"/>
       <c r="Z529" t="n">
-        <v>4.639739066971805</v>
+        <v>2.365221801762508</v>
       </c>
       <c r="AA529" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB529" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC529" t="n">
-        <v>1</v>
-      </c>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="AC529" t="inlineStr"/>
       <c r="AD529" t="inlineStr"/>
       <c r="AE529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>E38ZP7hD</t>
         </is>
       </c>
       <c r="B530" s="2" t="n">
-        <v>45606.51041666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E530" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F530" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G530" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="H530" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="I530" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="J530" t="n">
-        <v>0.2882865057380293</v>
+        <v>0.2299619616899878</v>
       </c>
       <c r="K530" t="n">
-        <v>0.3068856351404828</v>
+        <v>0.2548227143051216</v>
       </c>
       <c r="L530" t="n">
-        <v>0.4048278591214879</v>
+        <v>0.5152153240048907</v>
       </c>
       <c r="M530" t="n">
-        <v>0.05114286308521043</v>
+        <v>0.06062079672635434</v>
       </c>
       <c r="N530" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O530" t="n">
-        <v>0.3025104105472565</v>
+        <v>0.1850353483586111</v>
       </c>
       <c r="P530" t="n">
-        <v>0.3739364445209503</v>
+        <v>0.3068453998404827</v>
       </c>
       <c r="Q530" t="n">
-        <v>0.3235531151294708</v>
+        <v>0.5081192518009061</v>
       </c>
       <c r="R530" t="n">
         <v>1</v>
       </c>
       <c r="S530" t="n">
-        <v>0.06705080938046754</v>
+        <v>-0.00709607220398456</v>
       </c>
       <c r="T530" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U530" t="n">
-        <v>0.06705080938046754</v>
+        <v>-0.00709607220398456</v>
       </c>
       <c r="V530" t="n">
-        <v>0.3739364445209503</v>
+        <v>0.5081192518009061</v>
       </c>
       <c r="W530" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="X530" t="inlineStr">
         <is>
@@ -53581,16 +53581,16 @@
       </c>
       <c r="Y530" t="inlineStr"/>
       <c r="Z530" t="n">
-        <v>4.170285202714552</v>
+        <v>2.998343518656049</v>
       </c>
       <c r="AA530" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB530" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC530" t="inlineStr"/>
@@ -53600,78 +53600,78 @@
     <row r="531">
       <c r="A531" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>fwAoyY0E</t>
         </is>
       </c>
       <c r="B531" s="2" t="n">
-        <v>45606.60416666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="E531" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F531" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G531" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="H531" t="n">
-        <v>3.1</v>
+        <v>6.25</v>
       </c>
       <c r="I531" t="n">
-        <v>3.1</v>
+        <v>12</v>
       </c>
       <c r="J531" t="n">
-        <v>0.3875</v>
+        <v>0.7710892921400297</v>
       </c>
       <c r="K531" t="n">
-        <v>0.30625</v>
+        <v>0.1505166298257338</v>
       </c>
       <c r="L531" t="n">
-        <v>0.30625</v>
+        <v>0.07839407803423636</v>
       </c>
       <c r="M531" t="n">
-        <v>0.05332455562870297</v>
+        <v>0.06300546448087441</v>
       </c>
       <c r="N531" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O531" t="n">
-        <v>0.3117114901542664</v>
+        <v>0.5040588622807577</v>
       </c>
       <c r="P531" t="n">
-        <v>0.3761576414108276</v>
+        <v>0.3973333315804643</v>
       </c>
       <c r="Q531" t="n">
-        <v>0.3121309876441956</v>
+        <v>0.09860780613877793</v>
       </c>
       <c r="R531" t="n">
         <v>1</v>
       </c>
       <c r="S531" t="n">
-        <v>0.06990764141082761</v>
+        <v>-0.2670304298592721</v>
       </c>
       <c r="T531" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U531" t="n">
-        <v>0.06990764141082761</v>
+        <v>-0.2670304298592721</v>
       </c>
       <c r="V531" t="n">
-        <v>0.3761576414108276</v>
+        <v>0.5040588622807577</v>
       </c>
       <c r="W531" t="n">
-        <v>3.1</v>
+        <v>1.22</v>
       </c>
       <c r="X531" t="inlineStr">
         <is>
@@ -53680,16 +53680,16 @@
       </c>
       <c r="Y531" t="inlineStr"/>
       <c r="Z531" t="n">
-        <v>4.195056857518185</v>
+        <v>0</v>
       </c>
       <c r="AA531" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB531" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC531" t="inlineStr"/>
@@ -53699,78 +53699,78 @@
     <row r="532">
       <c r="A532" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>SrjMmBpK</t>
         </is>
       </c>
       <c r="B532" s="2" t="n">
-        <v>45606.60416666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E532" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F532" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G532" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="H532" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I532" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J532" t="n">
-        <v>0.2001588562351072</v>
+        <v>0.4512877939529675</v>
       </c>
       <c r="K532" t="n">
-        <v>0.2716441620333598</v>
+        <v>0.2430011198208287</v>
       </c>
       <c r="L532" t="n">
-        <v>0.5281969817315331</v>
+        <v>0.3057110862262038</v>
       </c>
       <c r="M532" t="n">
-        <v>0.05179615705931484</v>
+        <v>0.05518137776202292</v>
       </c>
       <c r="N532" t="n">
         <v>2</v>
       </c>
       <c r="O532" t="n">
-        <v>0.2408535778522491</v>
+        <v>0.347094786384264</v>
       </c>
       <c r="P532" t="n">
-        <v>0.340700089931488</v>
+        <v>0.2445510541796648</v>
       </c>
       <c r="Q532" t="n">
-        <v>0.418446272611618</v>
+        <v>0.4083541594360711</v>
       </c>
       <c r="R532" t="n">
         <v>1</v>
       </c>
       <c r="S532" t="n">
-        <v>-0.109750709119915</v>
+        <v>0.1026430732098673</v>
       </c>
       <c r="T532" t="n">
         <v>2</v>
       </c>
       <c r="U532" t="n">
-        <v>-0.109750709119915</v>
+        <v>0.1026430732098673</v>
       </c>
       <c r="V532" t="n">
-        <v>0.418446272611618</v>
+        <v>0.4083541594360711</v>
       </c>
       <c r="W532" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="X532" t="inlineStr">
         <is>
@@ -53779,16 +53779,16 @@
       </c>
       <c r="Y532" t="inlineStr"/>
       <c r="Z532" t="n">
-        <v>3.442693429420341</v>
+        <v>5.118290326722128</v>
       </c>
       <c r="AA532" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB532" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC532" t="inlineStr"/>
@@ -53798,78 +53798,78 @@
     <row r="533">
       <c r="A533" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>6w5RRTN0</t>
         </is>
       </c>
       <c r="B533" s="2" t="n">
-        <v>45606.70833333334</v>
+        <v>45619.60416666666</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="E533" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F533" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G533" t="n">
-        <v>3.75</v>
+        <v>1.62</v>
       </c>
       <c r="H533" t="n">
         <v>4.33</v>
       </c>
       <c r="I533" t="n">
-        <v>1.8</v>
+        <v>4.75</v>
       </c>
       <c r="J533" t="n">
-        <v>0.2532040348910872</v>
+        <v>0.5830269494941478</v>
       </c>
       <c r="K533" t="n">
-        <v>0.2192875590858145</v>
+        <v>0.2181301750994271</v>
       </c>
       <c r="L533" t="n">
-        <v>0.5275084060230983</v>
+        <v>0.1988428754064251</v>
       </c>
       <c r="M533" t="n">
-        <v>0.05316910443931233</v>
+        <v>0.05875714862384762</v>
       </c>
       <c r="N533" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O533" t="n">
-        <v>0.1872458159923553</v>
+        <v>0.3959207641875817</v>
       </c>
       <c r="P533" t="n">
-        <v>0.3025525510311127</v>
+        <v>0.2899290307132603</v>
       </c>
       <c r="Q533" t="n">
-        <v>0.510201632976532</v>
+        <v>0.314150205099158</v>
       </c>
       <c r="R533" t="n">
         <v>1</v>
       </c>
       <c r="S533" t="n">
-        <v>-0.01730677304656636</v>
+        <v>-0.1871061853065661</v>
       </c>
       <c r="T533" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U533" t="n">
-        <v>-0.01730677304656636</v>
+        <v>-0.1871061853065661</v>
       </c>
       <c r="V533" t="n">
-        <v>0.510201632976532</v>
+        <v>0.3959207641875817</v>
       </c>
       <c r="W533" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="X533" t="inlineStr">
         <is>
@@ -53878,21 +53878,2496 @@
       </c>
       <c r="Y533" t="inlineStr"/>
       <c r="Z533" t="n">
-        <v>5.496955889103862</v>
+        <v>0</v>
       </c>
       <c r="AA533" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB533" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC533" t="inlineStr"/>
       <c r="AD533" t="inlineStr"/>
       <c r="AE533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="n">
+        <v>45604.69791666666</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>77</v>
+      </c>
+      <c r="F534" t="n">
+        <v>771</v>
+      </c>
+      <c r="G534" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H534" t="n">
+        <v>3</v>
+      </c>
+      <c r="I534" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J534" t="n">
+        <v>0.4041204437400951</v>
+      </c>
+      <c r="K534" t="n">
+        <v>0.3165610142630745</v>
+      </c>
+      <c r="L534" t="n">
+        <v>0.2793185419968304</v>
+      </c>
+      <c r="M534" t="n">
+        <v>0.05298289528577382</v>
+      </c>
+      <c r="N534" t="n">
+        <v>0</v>
+      </c>
+      <c r="O534" t="n">
+        <v>0.2939333909711497</v>
+      </c>
+      <c r="P534" t="n">
+        <v>0.4106573401420681</v>
+      </c>
+      <c r="Q534" t="n">
+        <v>0.2954092688867823</v>
+      </c>
+      <c r="R534" t="n">
+        <v>1</v>
+      </c>
+      <c r="S534" t="n">
+        <v>0.09409632587899358</v>
+      </c>
+      <c r="T534" t="n">
+        <v>0</v>
+      </c>
+      <c r="U534" t="n">
+        <v>0.09409632587899358</v>
+      </c>
+      <c r="V534" t="n">
+        <v>0.4106573401420681</v>
+      </c>
+      <c r="W534" t="n">
+        <v>3</v>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y534" t="inlineStr"/>
+      <c r="Z534" t="n">
+        <v>5.902819827435319</v>
+      </c>
+      <c r="AA534" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB534" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC534" t="inlineStr"/>
+      <c r="AD534" t="inlineStr"/>
+      <c r="AE534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>hO2h1JgB</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="n">
+        <v>45605.45833333334</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>77</v>
+      </c>
+      <c r="F535" t="n">
+        <v>771</v>
+      </c>
+      <c r="G535" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H535" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I535" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J535" t="n">
+        <v>0.3711340206185567</v>
+      </c>
+      <c r="K535" t="n">
+        <v>0.2783505154639175</v>
+      </c>
+      <c r="L535" t="n">
+        <v>0.3505154639175257</v>
+      </c>
+      <c r="M535" t="n">
+        <v>0.05664488017429203</v>
+      </c>
+      <c r="N535" t="n">
+        <v>2</v>
+      </c>
+      <c r="O535" t="n">
+        <v>0.2498867756386013</v>
+      </c>
+      <c r="P535" t="n">
+        <v>0.3748693937364196</v>
+      </c>
+      <c r="Q535" t="n">
+        <v>0.3752438306249791</v>
+      </c>
+      <c r="R535" t="n">
+        <v>1</v>
+      </c>
+      <c r="S535" t="n">
+        <v>0.02472836670745338</v>
+      </c>
+      <c r="T535" t="n">
+        <v>2</v>
+      </c>
+      <c r="U535" t="n">
+        <v>0.02472836670745338</v>
+      </c>
+      <c r="V535" t="n">
+        <v>0.3752438306249791</v>
+      </c>
+      <c r="W535" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y535" t="inlineStr"/>
+      <c r="Z535" t="n">
+        <v>3.556179730910945</v>
+      </c>
+      <c r="AA535" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB535" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC535" t="inlineStr"/>
+      <c r="AD535" t="inlineStr"/>
+      <c r="AE535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>E3zhYKPO</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="n">
+        <v>45605.58333333334</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>77</v>
+      </c>
+      <c r="F536" t="n">
+        <v>771</v>
+      </c>
+      <c r="G536" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H536" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I536" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J536" t="n">
+        <v>0.173041413874967</v>
+      </c>
+      <c r="K536" t="n">
+        <v>0.2321287259298338</v>
+      </c>
+      <c r="L536" t="n">
+        <v>0.5948298601951991</v>
+      </c>
+      <c r="M536" t="n">
+        <v>0.05072062084257212</v>
+      </c>
+      <c r="N536" t="n">
+        <v>2</v>
+      </c>
+      <c r="O536" t="n">
+        <v>0.06416446372416562</v>
+      </c>
+      <c r="P536" t="n">
+        <v>0.1884644760211565</v>
+      </c>
+      <c r="Q536" t="n">
+        <v>0.7473710602546778</v>
+      </c>
+      <c r="R536" t="n">
+        <v>1</v>
+      </c>
+      <c r="S536" t="n">
+        <v>0.1525412000594787</v>
+      </c>
+      <c r="T536" t="n">
+        <v>2</v>
+      </c>
+      <c r="U536" t="n">
+        <v>0.1525412000594787</v>
+      </c>
+      <c r="V536" t="n">
+        <v>0.7473710602546778</v>
+      </c>
+      <c r="W536" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X536" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y536" t="inlineStr"/>
+      <c r="Z536" t="n">
+        <v>10.18151895369444</v>
+      </c>
+      <c r="AA536" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB536" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC536" t="inlineStr"/>
+      <c r="AD536" t="inlineStr"/>
+      <c r="AE536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>S60RnKvI</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="n">
+        <v>45605.69791666666</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>77</v>
+      </c>
+      <c r="F537" t="n">
+        <v>771</v>
+      </c>
+      <c r="G537" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H537" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I537" t="n">
+        <v>7</v>
+      </c>
+      <c r="J537" t="n">
+        <v>0.6137517305029996</v>
+      </c>
+      <c r="K537" t="n">
+        <v>0.2503461005999077</v>
+      </c>
+      <c r="L537" t="n">
+        <v>0.1359021688970928</v>
+      </c>
+      <c r="M537" t="n">
+        <v>0.05117632791656557</v>
+      </c>
+      <c r="N537" t="n">
+        <v>1</v>
+      </c>
+      <c r="O537" t="n">
+        <v>0.5787070596671816</v>
+      </c>
+      <c r="P537" t="n">
+        <v>0.2676145090391487</v>
+      </c>
+      <c r="Q537" t="n">
+        <v>0.1536784312936697</v>
+      </c>
+      <c r="R537" t="n">
+        <v>1</v>
+      </c>
+      <c r="S537" t="n">
+        <v>-0.03504467083581797</v>
+      </c>
+      <c r="T537" t="n">
+        <v>1</v>
+      </c>
+      <c r="U537" t="n">
+        <v>-0.03504467083581797</v>
+      </c>
+      <c r="V537" t="n">
+        <v>0.5787070596671816</v>
+      </c>
+      <c r="W537" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X537" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y537" t="inlineStr"/>
+      <c r="Z537" t="n">
+        <v>3.288962822429323</v>
+      </c>
+      <c r="AA537" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB537" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC537" t="inlineStr"/>
+      <c r="AD537" t="inlineStr"/>
+      <c r="AE537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>tjxpzseC</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="n">
+        <v>45606.35416666666</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>77</v>
+      </c>
+      <c r="F538" t="n">
+        <v>771</v>
+      </c>
+      <c r="G538" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H538" t="n">
+        <v>5</v>
+      </c>
+      <c r="I538" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J538" t="n">
+        <v>0.6849315068493151</v>
+      </c>
+      <c r="K538" t="n">
+        <v>0.189041095890411</v>
+      </c>
+      <c r="L538" t="n">
+        <v>0.126027397260274</v>
+      </c>
+      <c r="M538" t="n">
+        <v>0.05797101449275366</v>
+      </c>
+      <c r="N538" t="n">
+        <v>1</v>
+      </c>
+      <c r="O538" t="n">
+        <v>0.6210748069468638</v>
+      </c>
+      <c r="P538" t="n">
+        <v>0.2700769638529026</v>
+      </c>
+      <c r="Q538" t="n">
+        <v>0.1088482292002337</v>
+      </c>
+      <c r="R538" t="n">
+        <v>1</v>
+      </c>
+      <c r="S538" t="n">
+        <v>-0.06385669990245135</v>
+      </c>
+      <c r="T538" t="n">
+        <v>1</v>
+      </c>
+      <c r="U538" t="n">
+        <v>-0.06385669990245135</v>
+      </c>
+      <c r="V538" t="n">
+        <v>0.6210748069468638</v>
+      </c>
+      <c r="W538" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y538" t="inlineStr"/>
+      <c r="Z538" t="n">
+        <v>2.742360055027938</v>
+      </c>
+      <c r="AA538" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB538" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC538" t="inlineStr"/>
+      <c r="AD538" t="inlineStr"/>
+      <c r="AE538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>pbap3uPb</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>77</v>
+      </c>
+      <c r="F539" t="n">
+        <v>771</v>
+      </c>
+      <c r="G539" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H539" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I539" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J539" t="n">
+        <v>0.4603234298608499</v>
+      </c>
+      <c r="K539" t="n">
+        <v>0.2775479503572771</v>
+      </c>
+      <c r="L539" t="n">
+        <v>0.2621286197818729</v>
+      </c>
+      <c r="M539" t="n">
+        <v>0.05970030288538197</v>
+      </c>
+      <c r="N539" t="n">
+        <v>2</v>
+      </c>
+      <c r="O539" t="n">
+        <v>0.2121643271392464</v>
+      </c>
+      <c r="P539" t="n">
+        <v>0.28252457474014</v>
+      </c>
+      <c r="Q539" t="n">
+        <v>0.5053110981206135</v>
+      </c>
+      <c r="R539" t="n">
+        <v>1</v>
+      </c>
+      <c r="S539" t="n">
+        <v>0.2431824783387406</v>
+      </c>
+      <c r="T539" t="n">
+        <v>2</v>
+      </c>
+      <c r="U539" t="n">
+        <v>0.2431824783387406</v>
+      </c>
+      <c r="V539" t="n">
+        <v>0.5053110981206135</v>
+      </c>
+      <c r="W539" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X539" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y539" t="inlineStr"/>
+      <c r="Z539" t="n">
+        <v>11.08530758606682</v>
+      </c>
+      <c r="AA539" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB539" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC539" t="inlineStr"/>
+      <c r="AD539" t="inlineStr"/>
+      <c r="AE539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>hU52hOAt</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>77</v>
+      </c>
+      <c r="F540" t="n">
+        <v>771</v>
+      </c>
+      <c r="G540" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H540" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I540" t="n">
+        <v>7</v>
+      </c>
+      <c r="J540" t="n">
+        <v>0.6554307116104868</v>
+      </c>
+      <c r="K540" t="n">
+        <v>0.2097378277153558</v>
+      </c>
+      <c r="L540" t="n">
+        <v>0.1348314606741573</v>
+      </c>
+      <c r="M540" t="n">
+        <v>0.05952380952380953</v>
+      </c>
+      <c r="N540" t="n">
+        <v>1</v>
+      </c>
+      <c r="O540" t="n">
+        <v>0.5616255264882302</v>
+      </c>
+      <c r="P540" t="n">
+        <v>0.3175377770356159</v>
+      </c>
+      <c r="Q540" t="n">
+        <v>0.120836696476154</v>
+      </c>
+      <c r="R540" t="n">
+        <v>1</v>
+      </c>
+      <c r="S540" t="n">
+        <v>-0.09380518512225666</v>
+      </c>
+      <c r="T540" t="n">
+        <v>1</v>
+      </c>
+      <c r="U540" t="n">
+        <v>-0.09380518512225666</v>
+      </c>
+      <c r="V540" t="n">
+        <v>0.5616255264882302</v>
+      </c>
+      <c r="W540" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y540" t="inlineStr"/>
+      <c r="Z540" t="n">
+        <v>1.398035894994026</v>
+      </c>
+      <c r="AA540" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB540" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC540" t="inlineStr"/>
+      <c r="AD540" t="inlineStr"/>
+      <c r="AE540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>voUq51fn</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="n">
+        <v>45606.58333333334</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>77</v>
+      </c>
+      <c r="F541" t="n">
+        <v>771</v>
+      </c>
+      <c r="G541" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H541" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I541" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J541" t="n">
+        <v>0.2315144654925592</v>
+      </c>
+      <c r="K541" t="n">
+        <v>0.2497919232946033</v>
+      </c>
+      <c r="L541" t="n">
+        <v>0.5186936112128375</v>
+      </c>
+      <c r="M541" t="n">
+        <v>0.0535084211929262</v>
+      </c>
+      <c r="N541" t="n">
+        <v>0</v>
+      </c>
+      <c r="O541" t="n">
+        <v>0.1944810728279434</v>
+      </c>
+      <c r="P541" t="n">
+        <v>0.4216163095235277</v>
+      </c>
+      <c r="Q541" t="n">
+        <v>0.3839026176485287</v>
+      </c>
+      <c r="R541" t="n">
+        <v>1</v>
+      </c>
+      <c r="S541" t="n">
+        <v>0.1718243862289244</v>
+      </c>
+      <c r="T541" t="n">
+        <v>0</v>
+      </c>
+      <c r="U541" t="n">
+        <v>0.1718243862289244</v>
+      </c>
+      <c r="V541" t="n">
+        <v>0.4216163095235277</v>
+      </c>
+      <c r="W541" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X541" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y541" t="inlineStr"/>
+      <c r="Z541" t="n">
+        <v>8.31685390829419</v>
+      </c>
+      <c r="AA541" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB541" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC541" t="inlineStr"/>
+      <c r="AD541" t="inlineStr"/>
+      <c r="AE541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>KtcJltA5</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="n">
+        <v>45606.69791666666</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>77</v>
+      </c>
+      <c r="F542" t="n">
+        <v>771</v>
+      </c>
+      <c r="G542" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H542" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I542" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J542" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="K542" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="L542" t="n">
+        <v>0.23125</v>
+      </c>
+      <c r="M542" t="n">
+        <v>0.05471324983520098</v>
+      </c>
+      <c r="N542" t="n">
+        <v>1</v>
+      </c>
+      <c r="O542" t="n">
+        <v>0.5199129358101434</v>
+      </c>
+      <c r="P542" t="n">
+        <v>0.2471773357794682</v>
+      </c>
+      <c r="Q542" t="n">
+        <v>0.2329097284103884</v>
+      </c>
+      <c r="R542" t="n">
+        <v>1</v>
+      </c>
+      <c r="S542" t="n">
+        <v>0.007412935810143462</v>
+      </c>
+      <c r="T542" t="n">
+        <v>1</v>
+      </c>
+      <c r="U542" t="n">
+        <v>0.007412935810143462</v>
+      </c>
+      <c r="V542" t="n">
+        <v>0.5199129358101434</v>
+      </c>
+      <c r="W542" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X542" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y542" t="inlineStr"/>
+      <c r="Z542" t="n">
+        <v>4.121735092880379</v>
+      </c>
+      <c r="AA542" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB542" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC542" t="inlineStr"/>
+      <c r="AD542" t="inlineStr"/>
+      <c r="AE542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>WENRFI84</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="n">
+        <v>45619.45833333334</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>77</v>
+      </c>
+      <c r="F543" t="n">
+        <v>771</v>
+      </c>
+      <c r="G543" t="n">
+        <v>7</v>
+      </c>
+      <c r="H543" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="I543" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J543" t="n">
+        <v>0.1350293542074364</v>
+      </c>
+      <c r="K543" t="n">
+        <v>0.1800391389432485</v>
+      </c>
+      <c r="L543" t="n">
+        <v>0.6849315068493151</v>
+      </c>
+      <c r="M543" t="n">
+        <v>0.05797101449275366</v>
+      </c>
+      <c r="N543" t="n">
+        <v>2</v>
+      </c>
+      <c r="O543" t="n">
+        <v>0.03250536456456055</v>
+      </c>
+      <c r="P543" t="n">
+        <v>0.2018595202117701</v>
+      </c>
+      <c r="Q543" t="n">
+        <v>0.7656351152236692</v>
+      </c>
+      <c r="R543" t="n">
+        <v>1</v>
+      </c>
+      <c r="S543" t="n">
+        <v>0.08070360837435409</v>
+      </c>
+      <c r="T543" t="n">
+        <v>2</v>
+      </c>
+      <c r="U543" t="n">
+        <v>0.08070360837435409</v>
+      </c>
+      <c r="V543" t="n">
+        <v>0.7656351152236692</v>
+      </c>
+      <c r="W543" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y543" t="inlineStr"/>
+      <c r="Z543" t="n">
+        <v>8.163371615408142</v>
+      </c>
+      <c r="AA543" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB543" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC543" t="inlineStr"/>
+      <c r="AD543" t="inlineStr"/>
+      <c r="AE543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>z7KrCz8T</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="n">
+        <v>45619.58333333334</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>77</v>
+      </c>
+      <c r="F544" t="n">
+        <v>771</v>
+      </c>
+      <c r="G544" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H544" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I544" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J544" t="n">
+        <v>0.4509283819628648</v>
+      </c>
+      <c r="K544" t="n">
+        <v>0.2785145888594165</v>
+      </c>
+      <c r="L544" t="n">
+        <v>0.2705570291777188</v>
+      </c>
+      <c r="M544" t="n">
+        <v>0.05602240896358524</v>
+      </c>
+      <c r="N544" t="n">
+        <v>0</v>
+      </c>
+      <c r="O544" t="n">
+        <v>0.3327198060038317</v>
+      </c>
+      <c r="P544" t="n">
+        <v>0.4494769501082279</v>
+      </c>
+      <c r="Q544" t="n">
+        <v>0.2178032438879404</v>
+      </c>
+      <c r="R544" t="n">
+        <v>1</v>
+      </c>
+      <c r="S544" t="n">
+        <v>0.1709623612488114</v>
+      </c>
+      <c r="T544" t="n">
+        <v>0</v>
+      </c>
+      <c r="U544" t="n">
+        <v>0.1709623612488114</v>
+      </c>
+      <c r="V544" t="n">
+        <v>0.4494769501082279</v>
+      </c>
+      <c r="W544" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X544" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y544" t="inlineStr"/>
+      <c r="Z544" t="n">
+        <v>8.499947963276052</v>
+      </c>
+      <c r="AA544" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="AB544" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC544" t="inlineStr"/>
+      <c r="AD544" t="inlineStr"/>
+      <c r="AE544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>rPc4X7Gj</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="n">
+        <v>45604.70833333334</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>148</v>
+      </c>
+      <c r="F545" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G545" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H545" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I545" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J545" t="n">
+        <v>0.5114491057997661</v>
+      </c>
+      <c r="K545" t="n">
+        <v>0.2782884840381081</v>
+      </c>
+      <c r="L545" t="n">
+        <v>0.2102624101621261</v>
+      </c>
+      <c r="M545" t="n">
+        <v>0.05688040982158604</v>
+      </c>
+      <c r="N545" t="n">
+        <v>1</v>
+      </c>
+      <c r="O545" t="n">
+        <v>0.4278689274643216</v>
+      </c>
+      <c r="P545" t="n">
+        <v>0.3629548310488862</v>
+      </c>
+      <c r="Q545" t="n">
+        <v>0.2091762414867922</v>
+      </c>
+      <c r="R545" t="n">
+        <v>1</v>
+      </c>
+      <c r="S545" t="n">
+        <v>-0.08358017833544445</v>
+      </c>
+      <c r="T545" t="n">
+        <v>1</v>
+      </c>
+      <c r="U545" t="n">
+        <v>-0.08358017833544445</v>
+      </c>
+      <c r="V545" t="n">
+        <v>0.4278689274643216</v>
+      </c>
+      <c r="W545" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y545" t="inlineStr"/>
+      <c r="Z545" t="n">
+        <v>4.278689274643217</v>
+      </c>
+      <c r="AA545" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB545" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC545" t="inlineStr"/>
+      <c r="AD545" t="inlineStr"/>
+      <c r="AE545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>nucZxUhT</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="n">
+        <v>45605.41666666666</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>148</v>
+      </c>
+      <c r="F546" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G546" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H546" t="n">
+        <v>7</v>
+      </c>
+      <c r="I546" t="n">
+        <v>13</v>
+      </c>
+      <c r="J546" t="n">
+        <v>0.7913043478260869</v>
+      </c>
+      <c r="K546" t="n">
+        <v>0.1356521739130435</v>
+      </c>
+      <c r="L546" t="n">
+        <v>0.07304347826086957</v>
+      </c>
+      <c r="M546" t="n">
+        <v>0.05311355311355315</v>
+      </c>
+      <c r="N546" t="n">
+        <v>1</v>
+      </c>
+      <c r="O546" t="n">
+        <v>0.6756412174164625</v>
+      </c>
+      <c r="P546" t="n">
+        <v>0.2876177085514129</v>
+      </c>
+      <c r="Q546" t="n">
+        <v>0.03674107403212467</v>
+      </c>
+      <c r="R546" t="n">
+        <v>1</v>
+      </c>
+      <c r="S546" t="n">
+        <v>-0.1156631304096244</v>
+      </c>
+      <c r="T546" t="n">
+        <v>1</v>
+      </c>
+      <c r="U546" t="n">
+        <v>-0.1156631304096244</v>
+      </c>
+      <c r="V546" t="n">
+        <v>0.6756412174164625</v>
+      </c>
+      <c r="W546" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X546" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y546" t="inlineStr"/>
+      <c r="Z546" t="n">
+        <v>6.756412174164625</v>
+      </c>
+      <c r="AA546" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB546" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC546" t="inlineStr"/>
+      <c r="AD546" t="inlineStr"/>
+      <c r="AE546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>bXuieB8c</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="n">
+        <v>45605.51041666666</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>148</v>
+      </c>
+      <c r="F547" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G547" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H547" t="n">
+        <v>4</v>
+      </c>
+      <c r="I547" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J547" t="n">
+        <v>0.5883926183471516</v>
+      </c>
+      <c r="K547" t="n">
+        <v>0.2382990104305964</v>
+      </c>
+      <c r="L547" t="n">
+        <v>0.173308371222252</v>
+      </c>
+      <c r="M547" t="n">
+        <v>0.04910213243546568</v>
+      </c>
+      <c r="N547" t="n">
+        <v>1</v>
+      </c>
+      <c r="O547" t="n">
+        <v>0.3760498972198434</v>
+      </c>
+      <c r="P547" t="n">
+        <v>0.3622639674720201</v>
+      </c>
+      <c r="Q547" t="n">
+        <v>0.2616861353081363</v>
+      </c>
+      <c r="R547" t="n">
+        <v>1</v>
+      </c>
+      <c r="S547" t="n">
+        <v>-0.2123427211273082</v>
+      </c>
+      <c r="T547" t="n">
+        <v>1</v>
+      </c>
+      <c r="U547" t="n">
+        <v>-0.2123427211273082</v>
+      </c>
+      <c r="V547" t="n">
+        <v>0.3760498972198434</v>
+      </c>
+      <c r="W547" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X547" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y547" t="inlineStr"/>
+      <c r="Z547" t="n">
+        <v>3.760498972198434</v>
+      </c>
+      <c r="AA547" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB547" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC547" t="inlineStr"/>
+      <c r="AD547" t="inlineStr"/>
+      <c r="AE547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>UwPNKUWp</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="n">
+        <v>45605.70833333334</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>148</v>
+      </c>
+      <c r="F548" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G548" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H548" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I548" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J548" t="n">
+        <v>0.3300970873786407</v>
+      </c>
+      <c r="K548" t="n">
+        <v>0.2970873786407767</v>
+      </c>
+      <c r="L548" t="n">
+        <v>0.3728155339805825</v>
+      </c>
+      <c r="M548" t="n">
+        <v>0.0518790849673203</v>
+      </c>
+      <c r="N548" t="n">
+        <v>0</v>
+      </c>
+      <c r="O548" t="n">
+        <v>0.2549275904880438</v>
+      </c>
+      <c r="P548" t="n">
+        <v>0.3827680317442166</v>
+      </c>
+      <c r="Q548" t="n">
+        <v>0.3623043777677396</v>
+      </c>
+      <c r="R548" t="n">
+        <v>1</v>
+      </c>
+      <c r="S548" t="n">
+        <v>0.08568065310343997</v>
+      </c>
+      <c r="T548" t="n">
+        <v>0</v>
+      </c>
+      <c r="U548" t="n">
+        <v>0.08568065310343997</v>
+      </c>
+      <c r="V548" t="n">
+        <v>0.3827680317442166</v>
+      </c>
+      <c r="W548" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X548" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y548" t="inlineStr"/>
+      <c r="Z548" t="n">
+        <v>3.827680317442166</v>
+      </c>
+      <c r="AA548" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB548" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC548" t="inlineStr"/>
+      <c r="AD548" t="inlineStr"/>
+      <c r="AE548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="n">
+        <v>45606.41666666666</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>148</v>
+      </c>
+      <c r="F549" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G549" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H549" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I549" t="n">
+        <v>4</v>
+      </c>
+      <c r="J549" t="n">
+        <v>0.4851944345344275</v>
+      </c>
+      <c r="K549" t="n">
+        <v>0.2782732786300393</v>
+      </c>
+      <c r="L549" t="n">
+        <v>0.2365322868355333</v>
+      </c>
+      <c r="M549" t="n">
+        <v>0.05693815987933637</v>
+      </c>
+      <c r="N549" t="n">
+        <v>1</v>
+      </c>
+      <c r="O549" t="n">
+        <v>0.5124871616120684</v>
+      </c>
+      <c r="P549" t="n">
+        <v>0.2662130224057716</v>
+      </c>
+      <c r="Q549" t="n">
+        <v>0.2212998159821599</v>
+      </c>
+      <c r="R549" t="n">
+        <v>1</v>
+      </c>
+      <c r="S549" t="n">
+        <v>0.02729272707764097</v>
+      </c>
+      <c r="T549" t="n">
+        <v>1</v>
+      </c>
+      <c r="U549" t="n">
+        <v>0.02729272707764097</v>
+      </c>
+      <c r="V549" t="n">
+        <v>0.5124871616120684</v>
+      </c>
+      <c r="W549" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X549" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y549" t="inlineStr"/>
+      <c r="Z549" t="n">
+        <v>5.124871616120684</v>
+      </c>
+      <c r="AA549" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB549" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC549" t="inlineStr"/>
+      <c r="AD549" t="inlineStr"/>
+      <c r="AE549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>Ia5ItCg4</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="n">
+        <v>45606.51041666666</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>148</v>
+      </c>
+      <c r="F550" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G550" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H550" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I550" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J550" t="n">
+        <v>0.2797175362887406</v>
+      </c>
+      <c r="K550" t="n">
+        <v>0.3067869752844252</v>
+      </c>
+      <c r="L550" t="n">
+        <v>0.413495488426834</v>
+      </c>
+      <c r="M550" t="n">
+        <v>0.05148090091576618</v>
+      </c>
+      <c r="N550" t="n">
+        <v>2</v>
+      </c>
+      <c r="O550" t="n">
+        <v>0.2084941196855593</v>
+      </c>
+      <c r="P550" t="n">
+        <v>0.2497989324274281</v>
+      </c>
+      <c r="Q550" t="n">
+        <v>0.5417069478870126</v>
+      </c>
+      <c r="R550" t="n">
+        <v>1</v>
+      </c>
+      <c r="S550" t="n">
+        <v>0.1282114594601785</v>
+      </c>
+      <c r="T550" t="n">
+        <v>2</v>
+      </c>
+      <c r="U550" t="n">
+        <v>0.1282114594601785</v>
+      </c>
+      <c r="V550" t="n">
+        <v>0.5417069478870126</v>
+      </c>
+      <c r="W550" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X550" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y550" t="inlineStr"/>
+      <c r="Z550" t="n">
+        <v>5.417069478870125</v>
+      </c>
+      <c r="AA550" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB550" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC550" t="inlineStr"/>
+      <c r="AD550" t="inlineStr"/>
+      <c r="AE550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>CMriQj9N</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="n">
+        <v>45606.60416666666</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>148</v>
+      </c>
+      <c r="F551" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G551" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H551" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I551" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J551" t="n">
+        <v>0.3981697037810067</v>
+      </c>
+      <c r="K551" t="n">
+        <v>0.2961387171871237</v>
+      </c>
+      <c r="L551" t="n">
+        <v>0.3056915790318696</v>
+      </c>
+      <c r="M551" t="n">
+        <v>0.05524871238818108</v>
+      </c>
+      <c r="N551" t="n">
+        <v>2</v>
+      </c>
+      <c r="O551" t="n">
+        <v>0.1902676964861811</v>
+      </c>
+      <c r="P551" t="n">
+        <v>0.3783058884736485</v>
+      </c>
+      <c r="Q551" t="n">
+        <v>0.4314264150401704</v>
+      </c>
+      <c r="R551" t="n">
+        <v>1</v>
+      </c>
+      <c r="S551" t="n">
+        <v>0.1257348360083008</v>
+      </c>
+      <c r="T551" t="n">
+        <v>2</v>
+      </c>
+      <c r="U551" t="n">
+        <v>0.1257348360083008</v>
+      </c>
+      <c r="V551" t="n">
+        <v>0.4314264150401704</v>
+      </c>
+      <c r="W551" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y551" t="inlineStr"/>
+      <c r="Z551" t="n">
+        <v>4.314264150401704</v>
+      </c>
+      <c r="AA551" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB551" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC551" t="inlineStr"/>
+      <c r="AD551" t="inlineStr"/>
+      <c r="AE551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="n">
+        <v>45606.60416666666</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>148</v>
+      </c>
+      <c r="F552" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G552" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H552" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I552" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J552" t="n">
+        <v>0.1985723556132381</v>
+      </c>
+      <c r="K552" t="n">
+        <v>0.2774172615184945</v>
+      </c>
+      <c r="L552" t="n">
+        <v>0.5240103828682673</v>
+      </c>
+      <c r="M552" t="n">
+        <v>0.06019951840385285</v>
+      </c>
+      <c r="N552" t="n">
+        <v>2</v>
+      </c>
+      <c r="O552" t="n">
+        <v>0.2148935711721427</v>
+      </c>
+      <c r="P552" t="n">
+        <v>0.3105838141353662</v>
+      </c>
+      <c r="Q552" t="n">
+        <v>0.4745226146924911</v>
+      </c>
+      <c r="R552" t="n">
+        <v>1</v>
+      </c>
+      <c r="S552" t="n">
+        <v>-0.04948776817577621</v>
+      </c>
+      <c r="T552" t="n">
+        <v>2</v>
+      </c>
+      <c r="U552" t="n">
+        <v>-0.04948776817577621</v>
+      </c>
+      <c r="V552" t="n">
+        <v>0.4745226146924911</v>
+      </c>
+      <c r="W552" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X552" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y552" t="inlineStr"/>
+      <c r="Z552" t="n">
+        <v>4.745226146924911</v>
+      </c>
+      <c r="AA552" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB552" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC552" t="inlineStr"/>
+      <c r="AD552" t="inlineStr"/>
+      <c r="AE552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="n">
+        <v>45606.70833333334</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>148</v>
+      </c>
+      <c r="F553" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G553" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H553" t="n">
+        <v>4</v>
+      </c>
+      <c r="I553" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J553" t="n">
+        <v>0.2095531587057011</v>
+      </c>
+      <c r="K553" t="n">
+        <v>0.2357473035439137</v>
+      </c>
+      <c r="L553" t="n">
+        <v>0.5546995377503853</v>
+      </c>
+      <c r="M553" t="n">
+        <v>0.06045751633986929</v>
+      </c>
+      <c r="N553" t="n">
+        <v>2</v>
+      </c>
+      <c r="O553" t="n">
+        <v>0.1428502156665979</v>
+      </c>
+      <c r="P553" t="n">
+        <v>0.3223447561188271</v>
+      </c>
+      <c r="Q553" t="n">
+        <v>0.534805028214575</v>
+      </c>
+      <c r="R553" t="n">
+        <v>1</v>
+      </c>
+      <c r="S553" t="n">
+        <v>-0.01989450953581029</v>
+      </c>
+      <c r="T553" t="n">
+        <v>2</v>
+      </c>
+      <c r="U553" t="n">
+        <v>-0.01989450953581029</v>
+      </c>
+      <c r="V553" t="n">
+        <v>0.534805028214575</v>
+      </c>
+      <c r="W553" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X553" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y553" t="inlineStr"/>
+      <c r="Z553" t="n">
+        <v>5.34805028214575</v>
+      </c>
+      <c r="AA553" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB553" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC553" t="inlineStr"/>
+      <c r="AD553" t="inlineStr"/>
+      <c r="AE553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>SCX7iT7M</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="n">
+        <v>45618.70833333334</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>148</v>
+      </c>
+      <c r="F554" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G554" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H554" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I554" t="n">
+        <v>6</v>
+      </c>
+      <c r="J554" t="n">
+        <v>0.5696460056964601</v>
+      </c>
+      <c r="K554" t="n">
+        <v>0.2718025227180252</v>
+      </c>
+      <c r="L554" t="n">
+        <v>0.1585514715855147</v>
+      </c>
+      <c r="M554" t="n">
+        <v>0.05118334759053322</v>
+      </c>
+      <c r="N554" t="n">
+        <v>0</v>
+      </c>
+      <c r="O554" t="n">
+        <v>0.3426184699525135</v>
+      </c>
+      <c r="P554" t="n">
+        <v>0.4034798208331402</v>
+      </c>
+      <c r="Q554" t="n">
+        <v>0.2539017092143463</v>
+      </c>
+      <c r="R554" t="n">
+        <v>1</v>
+      </c>
+      <c r="S554" t="n">
+        <v>0.131677298115115</v>
+      </c>
+      <c r="T554" t="n">
+        <v>0</v>
+      </c>
+      <c r="U554" t="n">
+        <v>0.131677298115115</v>
+      </c>
+      <c r="V554" t="n">
+        <v>0.4034798208331402</v>
+      </c>
+      <c r="W554" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y554" t="inlineStr"/>
+      <c r="Z554" t="n">
+        <v>4.034798208331401</v>
+      </c>
+      <c r="AA554" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB554" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC554" t="inlineStr"/>
+      <c r="AD554" t="inlineStr"/>
+      <c r="AE554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>C2KEmK6l</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="n">
+        <v>45619.41666666666</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>148</v>
+      </c>
+      <c r="F555" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G555" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H555" t="n">
+        <v>3</v>
+      </c>
+      <c r="I555" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J555" t="n">
+        <v>0.3303964757709251</v>
+      </c>
+      <c r="K555" t="n">
+        <v>0.3171806167400881</v>
+      </c>
+      <c r="L555" t="n">
+        <v>0.3524229074889867</v>
+      </c>
+      <c r="M555" t="n">
+        <v>0.05092592592592604</v>
+      </c>
+      <c r="N555" t="n">
+        <v>2</v>
+      </c>
+      <c r="O555" t="n">
+        <v>0.3375807081572289</v>
+      </c>
+      <c r="P555" t="n">
+        <v>0.3114246541767539</v>
+      </c>
+      <c r="Q555" t="n">
+        <v>0.3509946376660172</v>
+      </c>
+      <c r="R555" t="n">
+        <v>1</v>
+      </c>
+      <c r="S555" t="n">
+        <v>-0.001428269822969563</v>
+      </c>
+      <c r="T555" t="n">
+        <v>2</v>
+      </c>
+      <c r="U555" t="n">
+        <v>-0.001428269822969563</v>
+      </c>
+      <c r="V555" t="n">
+        <v>0.3509946376660172</v>
+      </c>
+      <c r="W555" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y555" t="inlineStr"/>
+      <c r="Z555" t="n">
+        <v>3.509946376660172</v>
+      </c>
+      <c r="AA555" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB555" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC555" t="inlineStr"/>
+      <c r="AD555" t="inlineStr"/>
+      <c r="AE555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>vVwOqx6D</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="n">
+        <v>45619.51041666666</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>148</v>
+      </c>
+      <c r="F556" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G556" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H556" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I556" t="n">
+        <v>9</v>
+      </c>
+      <c r="J556" t="n">
+        <v>0.6849315068493151</v>
+      </c>
+      <c r="K556" t="n">
+        <v>0.2100456621004566</v>
+      </c>
+      <c r="L556" t="n">
+        <v>0.1050228310502283</v>
+      </c>
+      <c r="M556" t="n">
+        <v>0.05797101449275366</v>
+      </c>
+      <c r="N556" t="n">
+        <v>1</v>
+      </c>
+      <c r="O556" t="n">
+        <v>0.5819079639761686</v>
+      </c>
+      <c r="P556" t="n">
+        <v>0.3113331289129357</v>
+      </c>
+      <c r="Q556" t="n">
+        <v>0.1067589071108957</v>
+      </c>
+      <c r="R556" t="n">
+        <v>1</v>
+      </c>
+      <c r="S556" t="n">
+        <v>-0.1030235428731465</v>
+      </c>
+      <c r="T556" t="n">
+        <v>1</v>
+      </c>
+      <c r="U556" t="n">
+        <v>-0.1030235428731465</v>
+      </c>
+      <c r="V556" t="n">
+        <v>0.5819079639761686</v>
+      </c>
+      <c r="W556" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y556" t="inlineStr"/>
+      <c r="Z556" t="n">
+        <v>5.819079639761686</v>
+      </c>
+      <c r="AA556" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB556" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC556" t="inlineStr"/>
+      <c r="AD556" t="inlineStr"/>
+      <c r="AE556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>buKPeYL5</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>148</v>
+      </c>
+      <c r="F557" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G557" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H557" t="n">
+        <v>4</v>
+      </c>
+      <c r="I557" t="n">
+        <v>5</v>
+      </c>
+      <c r="J557" t="n">
+        <v>0.5709391949757351</v>
+      </c>
+      <c r="K557" t="n">
+        <v>0.2383671139023694</v>
+      </c>
+      <c r="L557" t="n">
+        <v>0.1906936911218955</v>
+      </c>
+      <c r="M557" t="n">
+        <v>0.04880239520958085</v>
+      </c>
+      <c r="N557" t="n">
+        <v>1</v>
+      </c>
+      <c r="O557" t="n">
+        <v>0.5913279285595855</v>
+      </c>
+      <c r="P557" t="n">
+        <v>0.2967899811784423</v>
+      </c>
+      <c r="Q557" t="n">
+        <v>0.1118820902619721</v>
+      </c>
+      <c r="R557" t="n">
+        <v>1</v>
+      </c>
+      <c r="S557" t="n">
+        <v>0.0203887335838504</v>
+      </c>
+      <c r="T557" t="n">
+        <v>1</v>
+      </c>
+      <c r="U557" t="n">
+        <v>0.0203887335838504</v>
+      </c>
+      <c r="V557" t="n">
+        <v>0.5913279285595855</v>
+      </c>
+      <c r="W557" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y557" t="inlineStr"/>
+      <c r="Z557" t="n">
+        <v>5.913279285595855</v>
+      </c>
+      <c r="AA557" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB557" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC557" t="inlineStr"/>
+      <c r="AD557" t="inlineStr"/>
+      <c r="AE557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>IsCnpo0d</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>148</v>
+      </c>
+      <c r="F558" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G558" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H558" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I558" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J558" t="n">
+        <v>0.3351544442109687</v>
+      </c>
+      <c r="K558" t="n">
+        <v>0.3235973944105905</v>
+      </c>
+      <c r="L558" t="n">
+        <v>0.3412481613784409</v>
+      </c>
+      <c r="M558" t="n">
+        <v>0.06560680698611732</v>
+      </c>
+      <c r="N558" t="n">
+        <v>2</v>
+      </c>
+      <c r="O558" t="n">
+        <v>0.2444187323844127</v>
+      </c>
+      <c r="P558" t="n">
+        <v>0.325586583467244</v>
+      </c>
+      <c r="Q558" t="n">
+        <v>0.4299946841483434</v>
+      </c>
+      <c r="R558" t="n">
+        <v>1</v>
+      </c>
+      <c r="S558" t="n">
+        <v>0.08874652276990247</v>
+      </c>
+      <c r="T558" t="n">
+        <v>2</v>
+      </c>
+      <c r="U558" t="n">
+        <v>0.08874652276990247</v>
+      </c>
+      <c r="V558" t="n">
+        <v>0.4299946841483434</v>
+      </c>
+      <c r="W558" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="Y558" t="inlineStr"/>
+      <c r="Z558" t="n">
+        <v>4.299946841483433</v>
+      </c>
+      <c r="AA558" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="AB558" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC558" t="inlineStr"/>
+      <c r="AD558" t="inlineStr"/>
+      <c r="AE558" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -49933,20 +49933,20 @@
     <row r="494">
       <c r="A494" s="1" t="inlineStr">
         <is>
-          <t>KK9ggF3s</t>
+          <t>EubK3NNG</t>
         </is>
       </c>
       <c r="B494" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45619.39583333334</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="E494" t="n">
@@ -49956,55 +49956,55 @@
         <v>481</v>
       </c>
       <c r="G494" t="n">
-        <v>1.36</v>
+        <v>5</v>
       </c>
       <c r="H494" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="I494" t="n">
-        <v>7</v>
+        <v>1.65</v>
       </c>
       <c r="J494" t="n">
-        <v>0.6936936936936937</v>
+        <v>0.1893830703012913</v>
       </c>
       <c r="K494" t="n">
-        <v>0.1715315315315316</v>
+        <v>0.236728837876614</v>
       </c>
       <c r="L494" t="n">
-        <v>0.1347747747747748</v>
+        <v>0.5738880918220947</v>
       </c>
       <c r="M494" t="n">
-        <v>0.05996944232238333</v>
+        <v>0.05606060606060614</v>
       </c>
       <c r="N494" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O494" t="n">
-        <v>0.5736403463949913</v>
+        <v>0.1413065091688256</v>
       </c>
       <c r="P494" t="n">
-        <v>0.3644374378711059</v>
+        <v>0.4078634062770092</v>
       </c>
       <c r="Q494" t="n">
-        <v>0.06192221573390277</v>
+        <v>0.4508300845541651</v>
       </c>
       <c r="R494" t="n">
         <v>1</v>
       </c>
       <c r="S494" t="n">
-        <v>-0.1200533472987024</v>
+        <v>-0.1230580072679295</v>
       </c>
       <c r="T494" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U494" t="n">
-        <v>-0.1200533472987024</v>
+        <v>-0.1230580072679295</v>
       </c>
       <c r="V494" t="n">
-        <v>0.5736403463949913</v>
+        <v>0.4508300845541651</v>
       </c>
       <c r="W494" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="X494" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
       </c>
       <c r="Y494" t="inlineStr"/>
       <c r="Z494" t="n">
-        <v>0.4671347860009079</v>
+        <v>0</v>
       </c>
       <c r="AA494" t="inlineStr">
         <is>
@@ -50032,20 +50032,20 @@
     <row r="495">
       <c r="A495" s="1" t="inlineStr">
         <is>
-          <t>hY71igYg</t>
+          <t>Cl3y4WHa</t>
         </is>
       </c>
       <c r="B495" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45619.5</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
+          <t>arsenal</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
           <t>nottingham</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>newcastle</t>
         </is>
       </c>
       <c r="E495" t="n">
@@ -50055,55 +50055,55 @@
         <v>481</v>
       </c>
       <c r="G495" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="H495" t="n">
-        <v>3.3</v>
+        <v>5.75</v>
       </c>
       <c r="I495" t="n">
-        <v>2.63</v>
+        <v>8</v>
       </c>
       <c r="J495" t="n">
-        <v>0.3515188335358444</v>
+        <v>0.7155356795644564</v>
       </c>
       <c r="K495" t="n">
-        <v>0.287606318347509</v>
+        <v>0.1655065137079526</v>
       </c>
       <c r="L495" t="n">
-        <v>0.3608748481166464</v>
+        <v>0.1189578067275909</v>
       </c>
       <c r="M495" t="n">
-        <v>0.05362881028280286</v>
+        <v>0.05079274272638123</v>
       </c>
       <c r="N495" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O495" t="n">
-        <v>0.1919490033785586</v>
+        <v>0.7501533031177688</v>
       </c>
       <c r="P495" t="n">
-        <v>0.3633721987060077</v>
+        <v>0.1480937774734568</v>
       </c>
       <c r="Q495" t="n">
-        <v>0.4446787979154337</v>
+        <v>0.1017529194087745</v>
       </c>
       <c r="R495" t="n">
         <v>1</v>
       </c>
       <c r="S495" t="n">
-        <v>0.08380394979878736</v>
+        <v>0.03461762355331244</v>
       </c>
       <c r="T495" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U495" t="n">
-        <v>0.08380394979878736</v>
+        <v>0.03461762355331244</v>
       </c>
       <c r="V495" t="n">
-        <v>0.4446787979154337</v>
+        <v>0.7501533031177688</v>
       </c>
       <c r="W495" t="n">
-        <v>2.63</v>
+        <v>1.33</v>
       </c>
       <c r="X495" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
       </c>
       <c r="Y495" t="inlineStr"/>
       <c r="Z495" t="n">
-        <v>3.899472985552916</v>
+        <v>4.443118986655093</v>
       </c>
       <c r="AA495" t="inlineStr">
         <is>
@@ -50131,20 +50131,20 @@
     <row r="496">
       <c r="A496" s="1" t="inlineStr">
         <is>
-          <t>CzO2kX26</t>
+          <t>p21q2AnC</t>
         </is>
       </c>
       <c r="B496" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45619.5</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>ipswich</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="E496" t="n">
@@ -50154,55 +50154,55 @@
         <v>481</v>
       </c>
       <c r="G496" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="H496" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="I496" t="n">
-        <v>9</v>
+        <v>4.75</v>
       </c>
       <c r="J496" t="n">
-        <v>0.7561209793566971</v>
+        <v>0.5574781823653325</v>
       </c>
       <c r="K496" t="n">
-        <v>0.1371819491118579</v>
+        <v>0.2430033102618116</v>
       </c>
       <c r="L496" t="n">
-        <v>0.106697071531445</v>
+        <v>0.1995185073728558</v>
       </c>
       <c r="M496" t="n">
-        <v>0.04136982877140349</v>
+        <v>0.05517186631737725</v>
       </c>
       <c r="N496" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O496" t="n">
-        <v>0.6484027698424354</v>
+        <v>0.318295233421524</v>
       </c>
       <c r="P496" t="n">
-        <v>0.3011042777339618</v>
+        <v>0.467122865816885</v>
       </c>
       <c r="Q496" t="n">
-        <v>0.05049295242360272</v>
+        <v>0.2145819007615911</v>
       </c>
       <c r="R496" t="n">
         <v>1</v>
       </c>
       <c r="S496" t="n">
-        <v>-0.1077182095142617</v>
+        <v>0.2241195555550734</v>
       </c>
       <c r="T496" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U496" t="n">
-        <v>-0.1077182095142617</v>
+        <v>0.2241195555550734</v>
       </c>
       <c r="V496" t="n">
-        <v>0.6484027698424354</v>
+        <v>0.467122865816885</v>
       </c>
       <c r="W496" t="n">
-        <v>1.27</v>
+        <v>3.9</v>
       </c>
       <c r="X496" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
       </c>
       <c r="Y496" t="inlineStr"/>
       <c r="Z496" t="n">
-        <v>1.087649658926943</v>
+        <v>6.818005440185892</v>
       </c>
       <c r="AA496" t="inlineStr">
         <is>
@@ -50230,20 +50230,20 @@
     <row r="497">
       <c r="A497" s="1" t="inlineStr">
         <is>
-          <t>CEnSxfJ0</t>
+          <t>WveT5hmm</t>
         </is>
       </c>
       <c r="B497" s="2" t="n">
-        <v>45606.5625</v>
+        <v>45619.5</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="E497" t="n">
@@ -50253,55 +50253,55 @@
         <v>481</v>
       </c>
       <c r="G497" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="H497" t="n">
         <v>3.4</v>
       </c>
       <c r="I497" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="J497" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.4302959501557632</v>
       </c>
       <c r="K497" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2784267912772586</v>
       </c>
       <c r="L497" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.2912772585669782</v>
       </c>
       <c r="M497" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.05635540929658589</v>
       </c>
       <c r="N497" t="n">
         <v>1</v>
       </c>
       <c r="O497" t="n">
-        <v>0.5423281239799856</v>
+        <v>0.740850919529086</v>
       </c>
       <c r="P497" t="n">
-        <v>0.1883515769780034</v>
+        <v>0.1916123727298028</v>
       </c>
       <c r="Q497" t="n">
-        <v>0.2693202990420109</v>
+        <v>0.06753670774111104</v>
       </c>
       <c r="R497" t="n">
         <v>1</v>
       </c>
       <c r="S497" t="n">
-        <v>0.1918126600624599</v>
+        <v>0.3105549693733228</v>
       </c>
       <c r="T497" t="n">
         <v>1</v>
       </c>
       <c r="U497" t="n">
-        <v>0.1918126600624599</v>
+        <v>0.3105549693733228</v>
       </c>
       <c r="V497" t="n">
-        <v>0.5423281239799856</v>
+        <v>0.740850919529086</v>
       </c>
       <c r="W497" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="X497" t="inlineStr">
         <is>
@@ -50310,7 +50310,7 @@
       </c>
       <c r="Y497" t="inlineStr"/>
       <c r="Z497" t="n">
-        <v>6.547893821149127</v>
+        <v>9.915353985111887</v>
       </c>
       <c r="AA497" t="inlineStr">
         <is>
@@ -50329,20 +50329,20 @@
     <row r="498">
       <c r="A498" s="1" t="inlineStr">
         <is>
-          <t>EubK3NNG</t>
+          <t>v3JHq2Wp</t>
         </is>
       </c>
       <c r="B498" s="2" t="n">
-        <v>45619.39583333334</v>
+        <v>45619.5</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>leicester</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="E498" t="n">
@@ -50352,55 +50352,55 @@
         <v>481</v>
       </c>
       <c r="G498" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="H498" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I498" t="n">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="J498" t="n">
-        <v>0.1893830703012913</v>
+        <v>0.4081222356252514</v>
       </c>
       <c r="K498" t="n">
-        <v>0.236728837876614</v>
+        <v>0.268194611982308</v>
       </c>
       <c r="L498" t="n">
-        <v>0.5738880918220947</v>
+        <v>0.3236831523924407</v>
       </c>
       <c r="M498" t="n">
-        <v>0.05606060606060614</v>
+        <v>0.06532448061683449</v>
       </c>
       <c r="N498" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O498" t="n">
-        <v>0.1413065091688256</v>
+        <v>0.4102408758399712</v>
       </c>
       <c r="P498" t="n">
-        <v>0.4078634062770092</v>
+        <v>0.2792937644542169</v>
       </c>
       <c r="Q498" t="n">
-        <v>0.4508300845541651</v>
+        <v>0.3104653597058119</v>
       </c>
       <c r="R498" t="n">
         <v>1</v>
       </c>
       <c r="S498" t="n">
-        <v>-0.1230580072679295</v>
+        <v>0.002118640214719858</v>
       </c>
       <c r="T498" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U498" t="n">
-        <v>-0.1230580072679295</v>
+        <v>0.002118640214719858</v>
       </c>
       <c r="V498" t="n">
-        <v>0.4508300845541651</v>
+        <v>0.4102408758399712</v>
       </c>
       <c r="W498" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="X498" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
       </c>
       <c r="Y498" t="inlineStr"/>
       <c r="Z498" t="n">
-        <v>0</v>
+        <v>2.093577183494253</v>
       </c>
       <c r="AA498" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
     <row r="499">
       <c r="A499" s="1" t="inlineStr">
         <is>
-          <t>Cl3y4WHa</t>
+          <t>69B375Oi</t>
         </is>
       </c>
       <c r="B499" s="2" t="n">
@@ -50436,12 +50436,12 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="E499" t="n">
@@ -50451,55 +50451,55 @@
         <v>481</v>
       </c>
       <c r="G499" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="H499" t="n">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
       <c r="I499" t="n">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="J499" t="n">
-        <v>0.7155356795644564</v>
+        <v>0.5574781823653325</v>
       </c>
       <c r="K499" t="n">
-        <v>0.1655065137079526</v>
+        <v>0.2430033102618116</v>
       </c>
       <c r="L499" t="n">
-        <v>0.1189578067275909</v>
+        <v>0.1995185073728558</v>
       </c>
       <c r="M499" t="n">
-        <v>0.05079274272638123</v>
+        <v>0.05517186631737725</v>
       </c>
       <c r="N499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O499" t="n">
-        <v>0.7501533031177688</v>
+        <v>0.3357476902870436</v>
       </c>
       <c r="P499" t="n">
-        <v>0.1480937774734568</v>
+        <v>0.2702324548598613</v>
       </c>
       <c r="Q499" t="n">
-        <v>0.1017529194087745</v>
+        <v>0.3940198548530951</v>
       </c>
       <c r="R499" t="n">
         <v>1</v>
       </c>
       <c r="S499" t="n">
-        <v>0.03461762355331244</v>
+        <v>0.1945013474802393</v>
       </c>
       <c r="T499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U499" t="n">
-        <v>0.03461762355331244</v>
+        <v>0.1945013474802393</v>
       </c>
       <c r="V499" t="n">
-        <v>0.7501533031177688</v>
+        <v>0.3940198548530951</v>
       </c>
       <c r="W499" t="n">
-        <v>1.33</v>
+        <v>4.75</v>
       </c>
       <c r="X499" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
       </c>
       <c r="Y499" t="inlineStr"/>
       <c r="Z499" t="n">
-        <v>4.443118986655093</v>
+        <v>5.860126223870261</v>
       </c>
       <c r="AA499" t="inlineStr">
         <is>
@@ -50527,20 +50527,20 @@
     <row r="500">
       <c r="A500" s="1" t="inlineStr">
         <is>
-          <t>p21q2AnC</t>
+          <t>A7iT11hT</t>
         </is>
       </c>
       <c r="B500" s="2" t="n">
-        <v>45619.5</v>
+        <v>45619.60416666666</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="E500" t="n">
@@ -50550,55 +50550,55 @@
         <v>481</v>
       </c>
       <c r="G500" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="H500" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I500" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="J500" t="n">
-        <v>0.5574781823653325</v>
+        <v>0.6026768243366641</v>
       </c>
       <c r="K500" t="n">
-        <v>0.2430033102618116</v>
+        <v>0.2252863367163244</v>
       </c>
       <c r="L500" t="n">
-        <v>0.1995185073728558</v>
+        <v>0.1720368389470114</v>
       </c>
       <c r="M500" t="n">
-        <v>0.05517186631737725</v>
+        <v>0.05685609507265554</v>
       </c>
       <c r="N500" t="n">
         <v>0</v>
       </c>
       <c r="O500" t="n">
-        <v>0.318295233421524</v>
+        <v>0.2355670630895556</v>
       </c>
       <c r="P500" t="n">
-        <v>0.467122865816885</v>
+        <v>0.6893672198989927</v>
       </c>
       <c r="Q500" t="n">
-        <v>0.2145819007615911</v>
+        <v>0.07506571701145179</v>
       </c>
       <c r="R500" t="n">
         <v>1</v>
       </c>
       <c r="S500" t="n">
-        <v>0.2241195555550734</v>
+        <v>0.4640808831826683</v>
       </c>
       <c r="T500" t="n">
         <v>0</v>
       </c>
       <c r="U500" t="n">
-        <v>0.2241195555550734</v>
+        <v>0.4640808831826683</v>
       </c>
       <c r="V500" t="n">
-        <v>0.467122865816885</v>
+        <v>0.6893672198989927</v>
       </c>
       <c r="W500" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="X500" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
       </c>
       <c r="Y500" t="inlineStr"/>
       <c r="Z500" t="n">
-        <v>6.818005440185892</v>
+        <v>12.72845376314833</v>
       </c>
       <c r="AA500" t="inlineStr">
         <is>
@@ -50626,96 +50626,96 @@
     <row r="501">
       <c r="A501" s="1" t="inlineStr">
         <is>
-          <t>WveT5hmm</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B501" s="2" t="n">
-        <v>45619.5</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E501" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F501" t="n">
-        <v>481</v>
+        <v>551</v>
       </c>
       <c r="G501" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="H501" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="I501" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="J501" t="n">
-        <v>0.4302959501557632</v>
+        <v>0.6997667444185273</v>
       </c>
       <c r="K501" t="n">
-        <v>0.2784267912772586</v>
+        <v>0.1812729090303233</v>
       </c>
       <c r="L501" t="n">
-        <v>0.2912772585669782</v>
+        <v>0.1189603465511496</v>
       </c>
       <c r="M501" t="n">
-        <v>0.05635540929658589</v>
+        <v>0.05077030812324912</v>
       </c>
       <c r="N501" t="n">
         <v>1</v>
       </c>
       <c r="O501" t="n">
-        <v>0.740850919529086</v>
+        <v>0.5933453961434054</v>
       </c>
       <c r="P501" t="n">
-        <v>0.1916123727298028</v>
+        <v>0.2785554211040788</v>
       </c>
       <c r="Q501" t="n">
-        <v>0.06753670774111104</v>
+        <v>0.1280991827525158</v>
       </c>
       <c r="R501" t="n">
         <v>1</v>
       </c>
       <c r="S501" t="n">
-        <v>0.3105549693733228</v>
+        <v>-0.1064213482751218</v>
       </c>
       <c r="T501" t="n">
         <v>1</v>
       </c>
       <c r="U501" t="n">
-        <v>0.3105549693733228</v>
+        <v>-0.1064213482751218</v>
       </c>
       <c r="V501" t="n">
-        <v>0.740850919529086</v>
+        <v>0.5933453961434054</v>
       </c>
       <c r="W501" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="X501" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y501" t="inlineStr"/>
       <c r="Z501" t="n">
-        <v>9.915353985111887</v>
+        <v>5.933453961434054</v>
       </c>
       <c r="AA501" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB501" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC501" t="inlineStr"/>
@@ -50725,96 +50725,96 @@
     <row r="502">
       <c r="A502" s="1" t="inlineStr">
         <is>
-          <t>v3JHq2Wp</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B502" s="2" t="n">
-        <v>45619.5</v>
+        <v>45605.54166666666</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="E502" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F502" t="n">
-        <v>481</v>
+        <v>551</v>
       </c>
       <c r="G502" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="H502" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I502" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J502" t="n">
-        <v>0.4081222356252514</v>
+        <v>0.2763256161314414</v>
       </c>
       <c r="K502" t="n">
-        <v>0.268194611982308</v>
+        <v>0.2539208364451083</v>
       </c>
       <c r="L502" t="n">
-        <v>0.3236831523924407</v>
+        <v>0.4697535474234503</v>
       </c>
       <c r="M502" t="n">
-        <v>0.06532448061683449</v>
+        <v>0.06438791732909377</v>
       </c>
       <c r="N502" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O502" t="n">
-        <v>0.4102408758399712</v>
+        <v>0.213938813213297</v>
       </c>
       <c r="P502" t="n">
-        <v>0.2792937644542169</v>
+        <v>0.3080877883666737</v>
       </c>
       <c r="Q502" t="n">
-        <v>0.3104653597058119</v>
+        <v>0.4779733984200293</v>
       </c>
       <c r="R502" t="n">
         <v>1</v>
       </c>
       <c r="S502" t="n">
-        <v>0.002118640214719858</v>
+        <v>0.008219850996579015</v>
       </c>
       <c r="T502" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U502" t="n">
-        <v>0.002118640214719858</v>
+        <v>0.008219850996579015</v>
       </c>
       <c r="V502" t="n">
-        <v>0.4102408758399712</v>
+        <v>0.4779733984200293</v>
       </c>
       <c r="W502" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="X502" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y502" t="inlineStr"/>
       <c r="Z502" t="n">
-        <v>2.093577183494253</v>
+        <v>4.779733984200293</v>
       </c>
       <c r="AA502" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB502" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC502" t="inlineStr"/>
@@ -50824,96 +50824,96 @@
     <row r="503">
       <c r="A503" s="1" t="inlineStr">
         <is>
-          <t>69B375Oi</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B503" s="2" t="n">
-        <v>45619.5</v>
+        <v>45605.625</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E503" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F503" t="n">
-        <v>481</v>
+        <v>551</v>
       </c>
       <c r="G503" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="H503" t="n">
         <v>3.9</v>
       </c>
       <c r="I503" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="J503" t="n">
-        <v>0.5574781823653325</v>
+        <v>0.5922355737488446</v>
       </c>
       <c r="K503" t="n">
-        <v>0.2430033102618116</v>
+        <v>0.2429684405123466</v>
       </c>
       <c r="L503" t="n">
-        <v>0.1995185073728558</v>
+        <v>0.1647959857388089</v>
       </c>
       <c r="M503" t="n">
-        <v>0.05517186631737725</v>
+        <v>0.05532329988851714</v>
       </c>
       <c r="N503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O503" t="n">
-        <v>0.3357476902870436</v>
+        <v>0.4584897570020434</v>
       </c>
       <c r="P503" t="n">
-        <v>0.2702324548598613</v>
+        <v>0.3112641842728145</v>
       </c>
       <c r="Q503" t="n">
-        <v>0.3940198548530951</v>
+        <v>0.2302460587251422</v>
       </c>
       <c r="R503" t="n">
         <v>1</v>
       </c>
       <c r="S503" t="n">
-        <v>0.1945013474802393</v>
+        <v>-0.1337458167468012</v>
       </c>
       <c r="T503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U503" t="n">
-        <v>0.1945013474802393</v>
+        <v>-0.1337458167468012</v>
       </c>
       <c r="V503" t="n">
-        <v>0.3940198548530951</v>
+        <v>0.4584897570020434</v>
       </c>
       <c r="W503" t="n">
-        <v>4.75</v>
+        <v>1.6</v>
       </c>
       <c r="X503" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y503" t="inlineStr"/>
       <c r="Z503" t="n">
-        <v>5.860126223870261</v>
+        <v>4.584897570020433</v>
       </c>
       <c r="AA503" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB503" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC503" t="inlineStr"/>
@@ -50923,96 +50923,96 @@
     <row r="504">
       <c r="A504" s="1" t="inlineStr">
         <is>
-          <t>A7iT11hT</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B504" s="2" t="n">
-        <v>45619.60416666666</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>manchester city</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>tottenham</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E504" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F504" t="n">
-        <v>481</v>
+        <v>551</v>
       </c>
       <c r="G504" t="n">
-        <v>1.57</v>
+        <v>12</v>
       </c>
       <c r="H504" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="I504" t="n">
-        <v>5.5</v>
+        <v>1.22</v>
       </c>
       <c r="J504" t="n">
-        <v>0.6026768243366641</v>
+        <v>0.07839407803423636</v>
       </c>
       <c r="K504" t="n">
-        <v>0.2252863367163244</v>
+        <v>0.1505166298257338</v>
       </c>
       <c r="L504" t="n">
-        <v>0.1720368389470114</v>
+        <v>0.7710892921400297</v>
       </c>
       <c r="M504" t="n">
-        <v>0.05685609507265554</v>
+        <v>0.06300546448087441</v>
       </c>
       <c r="N504" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O504" t="n">
-        <v>0.2355670630895556</v>
+        <v>0.03045557869308633</v>
       </c>
       <c r="P504" t="n">
-        <v>0.6893672198989927</v>
+        <v>0.1237471865783788</v>
       </c>
       <c r="Q504" t="n">
-        <v>0.07506571701145179</v>
+        <v>0.8457972347285347</v>
       </c>
       <c r="R504" t="n">
         <v>1</v>
       </c>
       <c r="S504" t="n">
-        <v>0.4640808831826683</v>
+        <v>0.07470794258850499</v>
       </c>
       <c r="T504" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U504" t="n">
-        <v>0.4640808831826683</v>
+        <v>0.07470794258850499</v>
       </c>
       <c r="V504" t="n">
-        <v>0.6893672198989927</v>
+        <v>0.8457972347285347</v>
       </c>
       <c r="W504" t="n">
-        <v>4.2</v>
+        <v>1.22</v>
       </c>
       <c r="X504" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y504" t="inlineStr"/>
       <c r="Z504" t="n">
-        <v>12.72845376314833</v>
+        <v>8.457972347285347</v>
       </c>
       <c r="AA504" t="inlineStr">
         <is>
-          <t>england</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB504" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC504" t="inlineStr"/>
@@ -51022,20 +51022,20 @@
     <row r="505">
       <c r="A505" s="1" t="inlineStr">
         <is>
-          <t>Gp6AbAAT</t>
+          <t>xdpX3Q36</t>
         </is>
       </c>
       <c r="B505" s="2" t="n">
-        <v>45604.69791666666</v>
+        <v>45618.625</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E505" t="n">
@@ -51045,55 +51045,55 @@
         <v>551</v>
       </c>
       <c r="G505" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="H505" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="I505" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="J505" t="n">
-        <v>0.6997667444185273</v>
+        <v>0.6174990513369328</v>
       </c>
       <c r="K505" t="n">
-        <v>0.1812729090303233</v>
+        <v>0.2181925054377615</v>
       </c>
       <c r="L505" t="n">
-        <v>0.1189603465511496</v>
+        <v>0.1643084432253056</v>
       </c>
       <c r="M505" t="n">
-        <v>0.05077030812324912</v>
+        <v>0.05845469693718108</v>
       </c>
       <c r="N505" t="n">
         <v>1</v>
       </c>
       <c r="O505" t="n">
-        <v>0.5933453961434054</v>
+        <v>0.519876569818237</v>
       </c>
       <c r="P505" t="n">
-        <v>0.2785554211040788</v>
+        <v>0.2800465345400713</v>
       </c>
       <c r="Q505" t="n">
-        <v>0.1280991827525158</v>
+        <v>0.2000768956416916</v>
       </c>
       <c r="R505" t="n">
         <v>1</v>
       </c>
       <c r="S505" t="n">
-        <v>-0.1064213482751218</v>
+        <v>-0.09762248151869579</v>
       </c>
       <c r="T505" t="n">
         <v>1</v>
       </c>
       <c r="U505" t="n">
-        <v>-0.1064213482751218</v>
+        <v>-0.09762248151869579</v>
       </c>
       <c r="V505" t="n">
-        <v>0.5933453961434054</v>
+        <v>0.519876569818237</v>
       </c>
       <c r="W505" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="X505" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
       </c>
       <c r="Y505" t="inlineStr"/>
       <c r="Z505" t="n">
-        <v>5.933453961434054</v>
+        <v>5.19876569818237</v>
       </c>
       <c r="AA505" t="inlineStr">
         <is>
@@ -51121,20 +51121,20 @@
     <row r="506">
       <c r="A506" s="1" t="inlineStr">
         <is>
-          <t>figxD9PM</t>
+          <t>Im9H9ezS</t>
         </is>
       </c>
       <c r="B506" s="2" t="n">
-        <v>45605.54166666666</v>
+        <v>45618.70833333334</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="E506" t="n">
@@ -51144,55 +51144,55 @@
         <v>551</v>
       </c>
       <c r="G506" t="n">
-        <v>3.4</v>
+        <v>1.33</v>
       </c>
       <c r="H506" t="n">
-        <v>3.7</v>
+        <v>5.75</v>
       </c>
       <c r="I506" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="J506" t="n">
-        <v>0.2763256161314414</v>
+        <v>0.7099057574385776</v>
       </c>
       <c r="K506" t="n">
-        <v>0.2539208364451083</v>
+        <v>0.1642042882423145</v>
       </c>
       <c r="L506" t="n">
-        <v>0.4697535474234503</v>
+        <v>0.1258899543191078</v>
       </c>
       <c r="M506" t="n">
-        <v>0.06438791732909377</v>
+        <v>0.05912607605971454</v>
       </c>
       <c r="N506" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O506" t="n">
-        <v>0.213938813213297</v>
+        <v>0.6503282940627227</v>
       </c>
       <c r="P506" t="n">
-        <v>0.3080877883666737</v>
+        <v>0.2948201431721411</v>
       </c>
       <c r="Q506" t="n">
-        <v>0.4779733984200293</v>
+        <v>0.05485156276513609</v>
       </c>
       <c r="R506" t="n">
         <v>1</v>
       </c>
       <c r="S506" t="n">
-        <v>0.008219850996579015</v>
+        <v>-0.0595774633758549</v>
       </c>
       <c r="T506" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U506" t="n">
-        <v>0.008219850996579015</v>
+        <v>-0.0595774633758549</v>
       </c>
       <c r="V506" t="n">
-        <v>0.4779733984200293</v>
+        <v>0.6503282940627227</v>
       </c>
       <c r="W506" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="X506" t="inlineStr">
         <is>
@@ -51201,7 +51201,7 @@
       </c>
       <c r="Y506" t="inlineStr"/>
       <c r="Z506" t="n">
-        <v>4.779733984200293</v>
+        <v>6.503282940627227</v>
       </c>
       <c r="AA506" t="inlineStr">
         <is>
@@ -51220,11 +51220,11 @@
     <row r="507">
       <c r="A507" s="1" t="inlineStr">
         <is>
-          <t>bJl87mmp</t>
+          <t>SMfm4Zck</t>
         </is>
       </c>
       <c r="B507" s="2" t="n">
-        <v>45605.625</v>
+        <v>45619.54166666666</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E507" t="n">
@@ -51243,55 +51243,55 @@
         <v>551</v>
       </c>
       <c r="G507" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="H507" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I507" t="n">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="J507" t="n">
-        <v>0.5922355737488446</v>
+        <v>0.4221789883268482</v>
       </c>
       <c r="K507" t="n">
-        <v>0.2429684405123466</v>
+        <v>0.2714007782101167</v>
       </c>
       <c r="L507" t="n">
-        <v>0.1647959857388089</v>
+        <v>0.306420233463035</v>
       </c>
       <c r="M507" t="n">
-        <v>0.05532329988851714</v>
+        <v>0.05273937532002049</v>
       </c>
       <c r="N507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O507" t="n">
-        <v>0.4584897570020434</v>
+        <v>0.2796054787068856</v>
       </c>
       <c r="P507" t="n">
-        <v>0.3112641842728145</v>
+        <v>0.3367051480589169</v>
       </c>
       <c r="Q507" t="n">
-        <v>0.2302460587251422</v>
+        <v>0.3836893732341974</v>
       </c>
       <c r="R507" t="n">
         <v>1</v>
       </c>
       <c r="S507" t="n">
-        <v>-0.1337458167468012</v>
+        <v>0.0772691397711624</v>
       </c>
       <c r="T507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U507" t="n">
-        <v>-0.1337458167468012</v>
+        <v>0.0772691397711624</v>
       </c>
       <c r="V507" t="n">
-        <v>0.4584897570020434</v>
+        <v>0.3836893732341974</v>
       </c>
       <c r="W507" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="X507" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
       </c>
       <c r="Y507" t="inlineStr"/>
       <c r="Z507" t="n">
-        <v>4.584897570020433</v>
+        <v>3.836893732341974</v>
       </c>
       <c r="AA507" t="inlineStr">
         <is>
@@ -51319,20 +51319,20 @@
     <row r="508">
       <c r="A508" s="1" t="inlineStr">
         <is>
-          <t>dYK8BH5F</t>
+          <t>GryrQGK8</t>
         </is>
       </c>
       <c r="B508" s="2" t="n">
-        <v>45605.70833333334</v>
+        <v>45619.625</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="E508" t="n">
@@ -51342,55 +51342,55 @@
         <v>551</v>
       </c>
       <c r="G508" t="n">
-        <v>12</v>
+        <v>2.4</v>
       </c>
       <c r="H508" t="n">
-        <v>6.25</v>
+        <v>3.7</v>
       </c>
       <c r="I508" t="n">
-        <v>1.22</v>
+        <v>2.75</v>
       </c>
       <c r="J508" t="n">
-        <v>0.07839407803423636</v>
+        <v>0.3966088481777432</v>
       </c>
       <c r="K508" t="n">
-        <v>0.1505166298257338</v>
+        <v>0.2572597934125901</v>
       </c>
       <c r="L508" t="n">
-        <v>0.7710892921400297</v>
+        <v>0.3461313584096668</v>
       </c>
       <c r="M508" t="n">
-        <v>0.06300546448087441</v>
+        <v>0.05057330057330045</v>
       </c>
       <c r="N508" t="n">
         <v>2</v>
       </c>
       <c r="O508" t="n">
-        <v>0.03045557869308633</v>
+        <v>0.2952010208929276</v>
       </c>
       <c r="P508" t="n">
-        <v>0.1237471865783788</v>
+        <v>0.3153863873607415</v>
       </c>
       <c r="Q508" t="n">
-        <v>0.8457972347285347</v>
+        <v>0.3894125917463309</v>
       </c>
       <c r="R508" t="n">
         <v>1</v>
       </c>
       <c r="S508" t="n">
-        <v>0.07470794258850499</v>
+        <v>0.04328123333666412</v>
       </c>
       <c r="T508" t="n">
         <v>2</v>
       </c>
       <c r="U508" t="n">
-        <v>0.07470794258850499</v>
+        <v>0.04328123333666412</v>
       </c>
       <c r="V508" t="n">
-        <v>0.8457972347285347</v>
+        <v>0.3894125917463309</v>
       </c>
       <c r="W508" t="n">
-        <v>1.22</v>
+        <v>2.75</v>
       </c>
       <c r="X508" t="inlineStr">
         <is>
@@ -51399,7 +51399,7 @@
       </c>
       <c r="Y508" t="inlineStr"/>
       <c r="Z508" t="n">
-        <v>8.457972347285347</v>
+        <v>3.894125917463309</v>
       </c>
       <c r="AA508" t="inlineStr">
         <is>
@@ -51418,96 +51418,94 @@
     <row r="509">
       <c r="A509" s="1" t="inlineStr">
         <is>
-          <t>l8H0Dwy3</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B509" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45604.6875</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E509" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F509" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G509" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="H509" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I509" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J509" t="n">
-        <v>0.373666196899537</v>
+        <v>0.3999920597109735</v>
       </c>
       <c r="K509" t="n">
-        <v>0.2977652506543185</v>
+        <v>0.2929172621883437</v>
       </c>
       <c r="L509" t="n">
-        <v>0.3285685524461445</v>
+        <v>0.3070906781006829</v>
       </c>
       <c r="M509" t="n">
-        <v>0.04948444895199478</v>
+        <v>0.05044102008048879</v>
       </c>
       <c r="N509" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O509" t="n">
-        <v>0.2956078794391212</v>
+        <v>0.2451816872879612</v>
       </c>
       <c r="P509" t="n">
-        <v>0.3572410901173454</v>
+        <v>0.2823895203883839</v>
       </c>
       <c r="Q509" t="n">
-        <v>0.3471510304435335</v>
-      </c>
-      <c r="R509" t="n">
-        <v>1</v>
-      </c>
+        <v>0.4724287923236548</v>
+      </c>
+      <c r="R509" t="inlineStr"/>
       <c r="S509" t="n">
-        <v>0.05947583946302692</v>
+        <v>0.165338114222972</v>
       </c>
       <c r="T509" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U509" t="n">
-        <v>0.05947583946302692</v>
+        <v>0.165338114222972</v>
       </c>
       <c r="V509" t="n">
-        <v>0.3572410901173454</v>
+        <v>0.4724287923236548</v>
       </c>
       <c r="W509" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="X509" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y509" t="inlineStr"/>
       <c r="Z509" t="n">
-        <v>3.572410901173454</v>
+        <v>7.086132807597141</v>
       </c>
       <c r="AA509" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB509" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC509" t="inlineStr"/>
@@ -51517,96 +51515,96 @@
     <row r="510">
       <c r="A510" s="1" t="inlineStr">
         <is>
-          <t>nRkUEVfA</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B510" s="2" t="n">
-        <v>45606.54166666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F510" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G510" t="n">
-        <v>3.3</v>
+        <v>9.5</v>
       </c>
       <c r="H510" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="I510" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="J510" t="n">
-        <v>0.2885143081144649</v>
+        <v>0.09938837920489296</v>
       </c>
       <c r="K510" t="n">
-        <v>0.297530380243042</v>
+        <v>0.1452599388379205</v>
       </c>
       <c r="L510" t="n">
-        <v>0.4139553116424932</v>
+        <v>0.7553516819571866</v>
       </c>
       <c r="M510" t="n">
-        <v>0.05031291172595509</v>
+        <v>0.05910931174089074</v>
       </c>
       <c r="N510" t="n">
         <v>2</v>
       </c>
       <c r="O510" t="n">
-        <v>0.1593014358863176</v>
+        <v>0.05423050087842236</v>
       </c>
       <c r="P510" t="n">
-        <v>0.2837467808408203</v>
+        <v>0.2116805041199112</v>
       </c>
       <c r="Q510" t="n">
-        <v>0.5569517832728622</v>
+        <v>0.7340889950016665</v>
       </c>
       <c r="R510" t="n">
         <v>1</v>
       </c>
       <c r="S510" t="n">
-        <v>0.142996471630369</v>
+        <v>-0.02126268695552014</v>
       </c>
       <c r="T510" t="n">
         <v>2</v>
       </c>
       <c r="U510" t="n">
-        <v>0.142996471630369</v>
+        <v>-0.02126268695552014</v>
       </c>
       <c r="V510" t="n">
-        <v>0.5569517832728622</v>
+        <v>0.7340889950016665</v>
       </c>
       <c r="W510" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="X510" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y510" t="inlineStr"/>
       <c r="Z510" t="n">
-        <v>5.569517832728622</v>
+        <v>4.056489044872412</v>
       </c>
       <c r="AA510" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB510" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC510" t="inlineStr"/>
@@ -51616,96 +51614,96 @@
     <row r="511">
       <c r="A511" s="1" t="inlineStr">
         <is>
-          <t>QB1LGiQc</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B511" s="2" t="n">
-        <v>45606.54166666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F511" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G511" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="H511" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I511" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="J511" t="n">
-        <v>0.2875429881543752</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="K511" t="n">
-        <v>0.2711119602598395</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="L511" t="n">
-        <v>0.4413450515857852</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="M511" t="n">
-        <v>0.05386086781435617</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="N511" t="n">
         <v>2</v>
       </c>
       <c r="O511" t="n">
-        <v>0.3191279762580632</v>
+        <v>0.1379586541384551</v>
       </c>
       <c r="P511" t="n">
-        <v>0.3286445238624505</v>
+        <v>0.2194789658739746</v>
       </c>
       <c r="Q511" t="n">
-        <v>0.3522274998794863</v>
+        <v>0.6425623799875704</v>
       </c>
       <c r="R511" t="n">
         <v>1</v>
       </c>
       <c r="S511" t="n">
-        <v>-0.08911755170629893</v>
+        <v>0.1724131262562271</v>
       </c>
       <c r="T511" t="n">
         <v>2</v>
       </c>
       <c r="U511" t="n">
-        <v>-0.08911755170629893</v>
+        <v>0.1724131262562271</v>
       </c>
       <c r="V511" t="n">
-        <v>0.3522274998794863</v>
+        <v>0.6425623799875704</v>
       </c>
       <c r="W511" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="X511" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y511" t="inlineStr"/>
       <c r="Z511" t="n">
-        <v>3.522274998794863</v>
+        <v>8.326343031327992</v>
       </c>
       <c r="AA511" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB511" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC511" t="inlineStr"/>
@@ -51715,96 +51713,96 @@
     <row r="512">
       <c r="A512" s="1" t="inlineStr">
         <is>
-          <t>WWnG5RHd</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B512" s="2" t="n">
-        <v>45606.54166666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="E512" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F512" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G512" t="n">
-        <v>2.15</v>
+        <v>9.5</v>
       </c>
       <c r="H512" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="I512" t="n">
-        <v>3.4</v>
+        <v>1.22</v>
       </c>
       <c r="J512" t="n">
-        <v>0.4415584415584415</v>
+        <v>0.09946733340580496</v>
       </c>
       <c r="K512" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.125991955647353</v>
       </c>
       <c r="L512" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.774540710946842</v>
       </c>
       <c r="M512" t="n">
-        <v>0.05335157318741457</v>
+        <v>0.05826862237561126</v>
       </c>
       <c r="N512" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O512" t="n">
-        <v>0.4771835695487086</v>
+        <v>0.04048311270516788</v>
       </c>
       <c r="P512" t="n">
-        <v>0.332348546930707</v>
+        <v>0.08763839322117328</v>
       </c>
       <c r="Q512" t="n">
-        <v>0.1904678835205843</v>
+        <v>0.8718784940736588</v>
       </c>
       <c r="R512" t="n">
         <v>1</v>
       </c>
       <c r="S512" t="n">
-        <v>0.03562512799026707</v>
+        <v>0.09733778312681685</v>
       </c>
       <c r="T512" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U512" t="n">
-        <v>0.03562512799026707</v>
+        <v>0.09733778312681685</v>
       </c>
       <c r="V512" t="n">
-        <v>0.4771835695487086</v>
+        <v>0.8718784940736588</v>
       </c>
       <c r="W512" t="n">
-        <v>2.15</v>
+        <v>1.22</v>
       </c>
       <c r="X512" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y512" t="inlineStr"/>
       <c r="Z512" t="n">
-        <v>4.771835695487086</v>
+        <v>7.882685166130789</v>
       </c>
       <c r="AA512" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB512" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC512" t="inlineStr"/>
@@ -51814,197 +51812,195 @@
     <row r="513">
       <c r="A513" s="1" t="inlineStr">
         <is>
-          <t>b59ZhlYj</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B513" s="2" t="n">
-        <v>45606.69791666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="E513" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F513" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G513" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="H513" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="I513" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J513" t="n">
-        <v>0.7101928819304333</v>
+        <v>0.5968169761273209</v>
       </c>
       <c r="K513" t="n">
-        <v>0.1717375514486321</v>
+        <v>0.2122015915119363</v>
       </c>
       <c r="L513" t="n">
-        <v>0.1180695666209345</v>
+        <v>0.1909814323607427</v>
       </c>
       <c r="M513" t="n">
-        <v>0.05869788106630214</v>
+        <v>0.04722222222222228</v>
       </c>
       <c r="N513" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O513" t="n">
-        <v>0.2506771451402429</v>
+        <v>0.5305649849773443</v>
       </c>
       <c r="P513" t="n">
-        <v>0.3926451799139036</v>
+        <v>0.2977688303422035</v>
       </c>
       <c r="Q513" t="n">
-        <v>0.3566776749458535</v>
+        <v>0.1716661846804522</v>
       </c>
       <c r="R513" t="n">
         <v>1</v>
       </c>
       <c r="S513" t="n">
-        <v>0.2209076284652716</v>
+        <v>-0.0662519911499766</v>
       </c>
       <c r="T513" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U513" t="n">
-        <v>0.2209076284652716</v>
+        <v>-0.0662519911499766</v>
       </c>
       <c r="V513" t="n">
-        <v>0.3926451799139036</v>
+        <v>0.5305649849773443</v>
       </c>
       <c r="W513" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="X513" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y513" t="inlineStr"/>
       <c r="Z513" t="n">
-        <v>3.926451799139036</v>
+        <v>1.659731377358987</v>
       </c>
       <c r="AA513" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB513" t="inlineStr">
         <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="AC513" t="n">
-        <v>1</v>
-      </c>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="AC513" t="inlineStr"/>
       <c r="AD513" t="inlineStr"/>
       <c r="AE513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="1" t="inlineStr">
         <is>
-          <t>xdpX3Q36</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B514" s="2" t="n">
-        <v>45618.625</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E514" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F514" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G514" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="H514" t="n">
         <v>4.33</v>
       </c>
       <c r="I514" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="J514" t="n">
-        <v>0.6174990513369328</v>
+        <v>0.5964499519258584</v>
       </c>
       <c r="K514" t="n">
-        <v>0.2181925054377615</v>
+        <v>0.2162647631694221</v>
       </c>
       <c r="L514" t="n">
-        <v>0.1643084432253056</v>
+        <v>0.1872852849047196</v>
       </c>
       <c r="M514" t="n">
-        <v>0.05845469693718108</v>
+        <v>0.06788955737632563</v>
       </c>
       <c r="N514" t="n">
         <v>1</v>
       </c>
       <c r="O514" t="n">
-        <v>0.519876569818237</v>
+        <v>0.5443949375586612</v>
       </c>
       <c r="P514" t="n">
-        <v>0.2800465345400713</v>
+        <v>0.3369520895012321</v>
       </c>
       <c r="Q514" t="n">
-        <v>0.2000768956416916</v>
+        <v>0.1186529729401067</v>
       </c>
       <c r="R514" t="n">
         <v>1</v>
       </c>
       <c r="S514" t="n">
-        <v>-0.09762248151869579</v>
+        <v>-0.05205501436719717</v>
       </c>
       <c r="T514" t="n">
         <v>1</v>
       </c>
       <c r="U514" t="n">
-        <v>-0.09762248151869579</v>
+        <v>-0.05205501436719717</v>
       </c>
       <c r="V514" t="n">
-        <v>0.519876569818237</v>
+        <v>0.5443949375586612</v>
       </c>
       <c r="W514" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X514" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y514" t="inlineStr"/>
       <c r="Z514" t="n">
-        <v>5.19876569818237</v>
+        <v>2.101093000561703</v>
       </c>
       <c r="AA514" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB514" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC514" t="inlineStr"/>
@@ -52014,195 +52010,197 @@
     <row r="515">
       <c r="A515" s="1" t="inlineStr">
         <is>
-          <t>Im9H9ezS</t>
+          <t>EuQnZBVQ</t>
         </is>
       </c>
       <c r="B515" s="2" t="n">
-        <v>45618.70833333334</v>
+        <v>45618.6875</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E515" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F515" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G515" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="H515" t="n">
-        <v>5.75</v>
+        <v>10</v>
       </c>
       <c r="I515" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="J515" t="n">
-        <v>0.7099057574385776</v>
+        <v>0.8450704225352113</v>
       </c>
       <c r="K515" t="n">
-        <v>0.1642042882423145</v>
+        <v>0.09295774647887325</v>
       </c>
       <c r="L515" t="n">
-        <v>0.1258899543191078</v>
+        <v>0.06197183098591549</v>
       </c>
       <c r="M515" t="n">
-        <v>0.05912607605971454</v>
+        <v>0.07575757575757569</v>
       </c>
       <c r="N515" t="n">
         <v>1</v>
       </c>
       <c r="O515" t="n">
-        <v>0.6503282940627227</v>
+        <v>0.4207096998051714</v>
       </c>
       <c r="P515" t="n">
-        <v>0.2948201431721411</v>
+        <v>0.3667474441088974</v>
       </c>
       <c r="Q515" t="n">
-        <v>0.05485156276513609</v>
+        <v>0.2125428560859311</v>
       </c>
       <c r="R515" t="n">
         <v>1</v>
       </c>
       <c r="S515" t="n">
-        <v>-0.0595774633758549</v>
+        <v>-0.4243607227300398</v>
       </c>
       <c r="T515" t="n">
         <v>1</v>
       </c>
       <c r="U515" t="n">
-        <v>-0.0595774633758549</v>
+        <v>-0.4243607227300398</v>
       </c>
       <c r="V515" t="n">
-        <v>0.6503282940627227</v>
+        <v>0.4207096998051714</v>
       </c>
       <c r="W515" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="X515" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y515" t="inlineStr"/>
       <c r="Z515" t="n">
-        <v>6.503282940627227</v>
+        <v>0</v>
       </c>
       <c r="AA515" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB515" t="inlineStr">
         <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="AC515" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="AC515" t="n">
+        <v>1</v>
+      </c>
       <c r="AD515" t="inlineStr"/>
       <c r="AE515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="1" t="inlineStr">
         <is>
-          <t>SMfm4Zck</t>
+          <t>2qNaDU87</t>
         </is>
       </c>
       <c r="B516" s="2" t="n">
-        <v>45619.54166666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E516" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F516" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G516" t="n">
-        <v>2.25</v>
+        <v>1.22</v>
       </c>
       <c r="H516" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="I516" t="n">
-        <v>3.1</v>
+        <v>15</v>
       </c>
       <c r="J516" t="n">
-        <v>0.4221789883268482</v>
+        <v>0.7784120394395433</v>
       </c>
       <c r="K516" t="n">
-        <v>0.2714007782101167</v>
+        <v>0.1582771146860404</v>
       </c>
       <c r="L516" t="n">
-        <v>0.306420233463035</v>
+        <v>0.06331084587441618</v>
       </c>
       <c r="M516" t="n">
-        <v>0.05273937532002049</v>
+        <v>0.0530054644808744</v>
       </c>
       <c r="N516" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O516" t="n">
-        <v>0.2796054787068856</v>
+        <v>0.6939419031995516</v>
       </c>
       <c r="P516" t="n">
-        <v>0.3367051480589169</v>
+        <v>0.2565956046804507</v>
       </c>
       <c r="Q516" t="n">
-        <v>0.3836893732341974</v>
+        <v>0.04946249211999764</v>
       </c>
       <c r="R516" t="n">
         <v>1</v>
       </c>
       <c r="S516" t="n">
-        <v>0.0772691397711624</v>
+        <v>-0.08447013623999167</v>
       </c>
       <c r="T516" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U516" t="n">
-        <v>0.0772691397711624</v>
+        <v>-0.08447013623999167</v>
       </c>
       <c r="V516" t="n">
-        <v>0.3836893732341974</v>
+        <v>0.6939419031995516</v>
       </c>
       <c r="W516" t="n">
-        <v>3.1</v>
+        <v>1.22</v>
       </c>
       <c r="X516" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y516" t="inlineStr"/>
       <c r="Z516" t="n">
-        <v>3.836893732341974</v>
+        <v>2.225383488997406</v>
       </c>
       <c r="AA516" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB516" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC516" t="inlineStr"/>
@@ -52212,96 +52210,96 @@
     <row r="517">
       <c r="A517" s="1" t="inlineStr">
         <is>
-          <t>GryrQGK8</t>
+          <t>pOGITkgl</t>
         </is>
       </c>
       <c r="B517" s="2" t="n">
-        <v>45619.625</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E517" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F517" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G517" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="H517" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="I517" t="n">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="J517" t="n">
-        <v>0.3966088481777432</v>
+        <v>0.5746381507885073</v>
       </c>
       <c r="K517" t="n">
-        <v>0.2572597934125901</v>
+        <v>0.225750702095485</v>
       </c>
       <c r="L517" t="n">
-        <v>0.3461313584096668</v>
+        <v>0.1996111471160078</v>
       </c>
       <c r="M517" t="n">
-        <v>0.05057330057330045</v>
+        <v>0.05468215994531778</v>
       </c>
       <c r="N517" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O517" t="n">
-        <v>0.2952010208929276</v>
+        <v>0.5353976182872061</v>
       </c>
       <c r="P517" t="n">
-        <v>0.3153863873607415</v>
+        <v>0.2974335586995293</v>
       </c>
       <c r="Q517" t="n">
-        <v>0.3894125917463309</v>
+        <v>0.1671688230132646</v>
       </c>
       <c r="R517" t="n">
         <v>1</v>
       </c>
       <c r="S517" t="n">
-        <v>0.04328123333666412</v>
+        <v>-0.03924053250130122</v>
       </c>
       <c r="T517" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U517" t="n">
-        <v>0.04328123333666412</v>
+        <v>-0.03924053250130122</v>
       </c>
       <c r="V517" t="n">
-        <v>0.3894125917463309</v>
+        <v>0.5353976182872061</v>
       </c>
       <c r="W517" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="X517" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y517" t="inlineStr"/>
       <c r="Z517" t="n">
-        <v>3.894125917463309</v>
+        <v>2.365221801762508</v>
       </c>
       <c r="AA517" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB517" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC517" t="inlineStr"/>
@@ -52311,20 +52309,20 @@
     <row r="518">
       <c r="A518" s="1" t="inlineStr">
         <is>
-          <t>v3DAZKP9</t>
+          <t>E38ZP7hD</t>
         </is>
       </c>
       <c r="B518" s="2" t="n">
-        <v>45604.6875</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E518" t="n">
@@ -52334,53 +52332,55 @@
         <v>591</v>
       </c>
       <c r="G518" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="H518" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="I518" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="J518" t="n">
-        <v>0.3999920597109735</v>
+        <v>0.2299619616899878</v>
       </c>
       <c r="K518" t="n">
-        <v>0.2929172621883437</v>
+        <v>0.2548227143051216</v>
       </c>
       <c r="L518" t="n">
-        <v>0.3070906781006829</v>
+        <v>0.5152153240048907</v>
       </c>
       <c r="M518" t="n">
-        <v>0.05044102008048879</v>
+        <v>0.06062079672635434</v>
       </c>
       <c r="N518" t="n">
         <v>2</v>
       </c>
       <c r="O518" t="n">
-        <v>0.2451816872879612</v>
+        <v>0.1850353483586111</v>
       </c>
       <c r="P518" t="n">
-        <v>0.2823895203883839</v>
+        <v>0.3068453998404827</v>
       </c>
       <c r="Q518" t="n">
-        <v>0.4724287923236548</v>
-      </c>
-      <c r="R518" t="inlineStr"/>
+        <v>0.5081192518009061</v>
+      </c>
+      <c r="R518" t="n">
+        <v>1</v>
+      </c>
       <c r="S518" t="n">
-        <v>0.165338114222972</v>
+        <v>-0.00709607220398456</v>
       </c>
       <c r="T518" t="n">
         <v>2</v>
       </c>
       <c r="U518" t="n">
-        <v>0.165338114222972</v>
+        <v>-0.00709607220398456</v>
       </c>
       <c r="V518" t="n">
-        <v>0.4724287923236548</v>
+        <v>0.5081192518009061</v>
       </c>
       <c r="W518" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="X518" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
       </c>
       <c r="Y518" t="inlineStr"/>
       <c r="Z518" t="n">
-        <v>7.086132807597141</v>
+        <v>2.998343518656049</v>
       </c>
       <c r="AA518" t="inlineStr">
         <is>
@@ -52408,20 +52408,20 @@
     <row r="519">
       <c r="A519" s="1" t="inlineStr">
         <is>
-          <t>biQrHC9r</t>
+          <t>fwAoyY0E</t>
         </is>
       </c>
       <c r="B519" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C519" t="inlineStr">
         <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
           <t>bochum</t>
-        </is>
-      </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="E519" t="n">
@@ -52431,55 +52431,55 @@
         <v>591</v>
       </c>
       <c r="G519" t="n">
-        <v>9.5</v>
+        <v>1.22</v>
       </c>
       <c r="H519" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="I519" t="n">
-        <v>1.25</v>
+        <v>12</v>
       </c>
       <c r="J519" t="n">
-        <v>0.09938837920489296</v>
+        <v>0.7710892921400297</v>
       </c>
       <c r="K519" t="n">
-        <v>0.1452599388379205</v>
+        <v>0.1505166298257338</v>
       </c>
       <c r="L519" t="n">
-        <v>0.7553516819571866</v>
+        <v>0.07839407803423636</v>
       </c>
       <c r="M519" t="n">
-        <v>0.05910931174089074</v>
+        <v>0.06300546448087441</v>
       </c>
       <c r="N519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O519" t="n">
-        <v>0.05423050087842236</v>
+        <v>0.5040588622807577</v>
       </c>
       <c r="P519" t="n">
-        <v>0.2116805041199112</v>
+        <v>0.3973333315804643</v>
       </c>
       <c r="Q519" t="n">
-        <v>0.7340889950016665</v>
+        <v>0.09860780613877793</v>
       </c>
       <c r="R519" t="n">
         <v>1</v>
       </c>
       <c r="S519" t="n">
-        <v>-0.02126268695552014</v>
+        <v>-0.2670304298592721</v>
       </c>
       <c r="T519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U519" t="n">
-        <v>-0.02126268695552014</v>
+        <v>-0.2670304298592721</v>
       </c>
       <c r="V519" t="n">
-        <v>0.7340889950016665</v>
+        <v>0.5040588622807577</v>
       </c>
       <c r="W519" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X519" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
       </c>
       <c r="Y519" t="inlineStr"/>
       <c r="Z519" t="n">
-        <v>4.056489044872412</v>
+        <v>0</v>
       </c>
       <c r="AA519" t="inlineStr">
         <is>
@@ -52507,20 +52507,20 @@
     <row r="520">
       <c r="A520" s="1" t="inlineStr">
         <is>
-          <t>nee3ysec</t>
+          <t>SrjMmBpK</t>
         </is>
       </c>
       <c r="B520" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E520" t="n">
@@ -52530,55 +52530,55 @@
         <v>591</v>
       </c>
       <c r="G520" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="H520" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I520" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J520" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.4512877939529675</v>
       </c>
       <c r="K520" t="n">
-        <v>0.2611940298507463</v>
+        <v>0.2430011198208287</v>
       </c>
       <c r="L520" t="n">
-        <v>0.4701492537313433</v>
+        <v>0.3057110862262038</v>
       </c>
       <c r="M520" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.05518137776202292</v>
       </c>
       <c r="N520" t="n">
         <v>2</v>
       </c>
       <c r="O520" t="n">
-        <v>0.1379586541384551</v>
+        <v>0.347094786384264</v>
       </c>
       <c r="P520" t="n">
-        <v>0.2194789658739746</v>
+        <v>0.2445510541796648</v>
       </c>
       <c r="Q520" t="n">
-        <v>0.6425623799875704</v>
+        <v>0.4083541594360711</v>
       </c>
       <c r="R520" t="n">
         <v>1</v>
       </c>
       <c r="S520" t="n">
-        <v>0.1724131262562271</v>
+        <v>0.1026430732098673</v>
       </c>
       <c r="T520" t="n">
         <v>2</v>
       </c>
       <c r="U520" t="n">
-        <v>0.1724131262562271</v>
+        <v>0.1026430732098673</v>
       </c>
       <c r="V520" t="n">
-        <v>0.6425623799875704</v>
+        <v>0.4083541594360711</v>
       </c>
       <c r="W520" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="X520" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
       </c>
       <c r="Y520" t="inlineStr"/>
       <c r="Z520" t="n">
-        <v>8.326343031327992</v>
+        <v>5.118290326722128</v>
       </c>
       <c r="AA520" t="inlineStr">
         <is>
@@ -52606,20 +52606,20 @@
     <row r="521">
       <c r="A521" s="1" t="inlineStr">
         <is>
-          <t>6HTjFjve</t>
+          <t>6w5RRTN0</t>
         </is>
       </c>
       <c r="B521" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45619.60416666666</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="E521" t="n">
@@ -52629,55 +52629,55 @@
         <v>591</v>
       </c>
       <c r="G521" t="n">
-        <v>9.5</v>
+        <v>1.62</v>
       </c>
       <c r="H521" t="n">
-        <v>7.5</v>
+        <v>4.33</v>
       </c>
       <c r="I521" t="n">
-        <v>1.22</v>
+        <v>4.75</v>
       </c>
       <c r="J521" t="n">
-        <v>0.09946733340580496</v>
+        <v>0.5830269494941478</v>
       </c>
       <c r="K521" t="n">
-        <v>0.125991955647353</v>
+        <v>0.2181301750994271</v>
       </c>
       <c r="L521" t="n">
-        <v>0.774540710946842</v>
+        <v>0.1988428754064251</v>
       </c>
       <c r="M521" t="n">
-        <v>0.05826862237561126</v>
+        <v>0.05875714862384762</v>
       </c>
       <c r="N521" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O521" t="n">
-        <v>0.04048311270516788</v>
+        <v>0.3959207641875817</v>
       </c>
       <c r="P521" t="n">
-        <v>0.08763839322117328</v>
+        <v>0.2899290307132603</v>
       </c>
       <c r="Q521" t="n">
-        <v>0.8718784940736588</v>
+        <v>0.314150205099158</v>
       </c>
       <c r="R521" t="n">
         <v>1</v>
       </c>
       <c r="S521" t="n">
-        <v>0.09733778312681685</v>
+        <v>-0.1871061853065661</v>
       </c>
       <c r="T521" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U521" t="n">
-        <v>0.09733778312681685</v>
+        <v>-0.1871061853065661</v>
       </c>
       <c r="V521" t="n">
-        <v>0.8718784940736588</v>
+        <v>0.3959207641875817</v>
       </c>
       <c r="W521" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="X521" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
       </c>
       <c r="Y521" t="inlineStr"/>
       <c r="Z521" t="n">
-        <v>7.882685166130789</v>
+        <v>0</v>
       </c>
       <c r="AA521" t="inlineStr">
         <is>
@@ -52705,78 +52705,78 @@
     <row r="522">
       <c r="A522" s="1" t="inlineStr">
         <is>
-          <t>YmumZjET</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B522" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E522" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F522" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G522" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="H522" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="I522" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J522" t="n">
-        <v>0.5968169761273209</v>
+        <v>0.4041204437400951</v>
       </c>
       <c r="K522" t="n">
-        <v>0.2122015915119363</v>
+        <v>0.3165610142630745</v>
       </c>
       <c r="L522" t="n">
-        <v>0.1909814323607427</v>
+        <v>0.2793185419968304</v>
       </c>
       <c r="M522" t="n">
-        <v>0.04722222222222228</v>
+        <v>0.05298289528577382</v>
       </c>
       <c r="N522" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O522" t="n">
-        <v>0.5305649849773443</v>
+        <v>0.2939333909711497</v>
       </c>
       <c r="P522" t="n">
-        <v>0.2977688303422035</v>
+        <v>0.4106573401420681</v>
       </c>
       <c r="Q522" t="n">
-        <v>0.1716661846804522</v>
+        <v>0.2954092688867823</v>
       </c>
       <c r="R522" t="n">
         <v>1</v>
       </c>
       <c r="S522" t="n">
-        <v>-0.0662519911499766</v>
+        <v>0.09409632587899358</v>
       </c>
       <c r="T522" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U522" t="n">
-        <v>-0.0662519911499766</v>
+        <v>0.09409632587899358</v>
       </c>
       <c r="V522" t="n">
-        <v>0.5305649849773443</v>
+        <v>0.4106573401420681</v>
       </c>
       <c r="W522" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="X522" t="inlineStr">
         <is>
@@ -52785,16 +52785,16 @@
       </c>
       <c r="Y522" t="inlineStr"/>
       <c r="Z522" t="n">
-        <v>1.659731377358987</v>
+        <v>5.902819827435319</v>
       </c>
       <c r="AA522" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB522" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC522" t="inlineStr"/>
@@ -52804,78 +52804,78 @@
     <row r="523">
       <c r="A523" s="1" t="inlineStr">
         <is>
-          <t>j5mWxZE4</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B523" s="2" t="n">
-        <v>45605.60416666666</v>
+        <v>45605.45833333334</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E523" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F523" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G523" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="H523" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="I523" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J523" t="n">
-        <v>0.5964499519258584</v>
+        <v>0.3711340206185567</v>
       </c>
       <c r="K523" t="n">
-        <v>0.2162647631694221</v>
+        <v>0.2783505154639175</v>
       </c>
       <c r="L523" t="n">
-        <v>0.1872852849047196</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="M523" t="n">
-        <v>0.06788955737632563</v>
+        <v>0.05664488017429203</v>
       </c>
       <c r="N523" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O523" t="n">
-        <v>0.5443949375586612</v>
+        <v>0.2498867756386013</v>
       </c>
       <c r="P523" t="n">
-        <v>0.3369520895012321</v>
+        <v>0.3748693937364196</v>
       </c>
       <c r="Q523" t="n">
-        <v>0.1186529729401067</v>
+        <v>0.3752438306249791</v>
       </c>
       <c r="R523" t="n">
         <v>1</v>
       </c>
       <c r="S523" t="n">
-        <v>-0.05205501436719717</v>
+        <v>0.02472836670745338</v>
       </c>
       <c r="T523" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U523" t="n">
-        <v>-0.05205501436719717</v>
+        <v>0.02472836670745338</v>
       </c>
       <c r="V523" t="n">
-        <v>0.5443949375586612</v>
+        <v>0.3752438306249791</v>
       </c>
       <c r="W523" t="n">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="X523" t="inlineStr">
         <is>
@@ -52884,16 +52884,16 @@
       </c>
       <c r="Y523" t="inlineStr"/>
       <c r="Z523" t="n">
-        <v>2.101093000561703</v>
+        <v>3.556179730910945</v>
       </c>
       <c r="AA523" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB523" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC523" t="inlineStr"/>
@@ -52903,78 +52903,78 @@
     <row r="524">
       <c r="A524" s="1" t="inlineStr">
         <is>
-          <t>UJQITUyi</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B524" s="2" t="n">
-        <v>45606.47916666666</v>
+        <v>45605.58333333334</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E524" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F524" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G524" t="n">
-        <v>2.05</v>
+        <v>5.5</v>
       </c>
       <c r="H524" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I524" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="J524" t="n">
-        <v>0.4592557701365991</v>
+        <v>0.173041413874967</v>
       </c>
       <c r="K524" t="n">
-        <v>0.2510598210080075</v>
+        <v>0.2321287259298338</v>
       </c>
       <c r="L524" t="n">
-        <v>0.2896844088553933</v>
+        <v>0.5948298601951991</v>
       </c>
       <c r="M524" t="n">
-        <v>0.06216385240775502</v>
+        <v>0.05072062084257212</v>
       </c>
       <c r="N524" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O524" t="n">
-        <v>0.3713369211320147</v>
+        <v>0.06416446372416562</v>
       </c>
       <c r="P524" t="n">
-        <v>0.3192392031647657</v>
+        <v>0.1884644760211565</v>
       </c>
       <c r="Q524" t="n">
-        <v>0.3094238757032194</v>
+        <v>0.7473710602546778</v>
       </c>
       <c r="R524" t="n">
         <v>1</v>
       </c>
       <c r="S524" t="n">
-        <v>-0.08791884900458441</v>
+        <v>0.1525412000594787</v>
       </c>
       <c r="T524" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U524" t="n">
-        <v>-0.08791884900458441</v>
+        <v>0.1525412000594787</v>
       </c>
       <c r="V524" t="n">
-        <v>0.3713369211320147</v>
+        <v>0.7473710602546778</v>
       </c>
       <c r="W524" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="X524" t="inlineStr">
         <is>
@@ -52983,99 +52983,97 @@
       </c>
       <c r="Y524" t="inlineStr"/>
       <c r="Z524" t="n">
-        <v>0.1228845319604818</v>
+        <v>10.18151895369444</v>
       </c>
       <c r="AA524" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB524" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="AC524" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC524" t="inlineStr"/>
       <c r="AD524" t="inlineStr"/>
       <c r="AE524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="1" t="inlineStr">
         <is>
-          <t>UkaNveph</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B525" s="2" t="n">
-        <v>45606.5625</v>
+        <v>45605.69791666666</v>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E525" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F525" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G525" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="H525" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I525" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="J525" t="n">
-        <v>0.5028882093102276</v>
+        <v>0.6137517305029996</v>
       </c>
       <c r="K525" t="n">
-        <v>0.2388718994223581</v>
+        <v>0.2503461005999077</v>
       </c>
       <c r="L525" t="n">
-        <v>0.2582398912674141</v>
+        <v>0.1359021688970928</v>
       </c>
       <c r="M525" t="n">
-        <v>0.04658605974395447</v>
+        <v>0.05117632791656557</v>
       </c>
       <c r="N525" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O525" t="n">
-        <v>0.3899514257709533</v>
+        <v>0.5787070596671816</v>
       </c>
       <c r="P525" t="n">
-        <v>0.3914355888829029</v>
+        <v>0.2676145090391487</v>
       </c>
       <c r="Q525" t="n">
-        <v>0.2186129853461438</v>
+        <v>0.1536784312936697</v>
       </c>
       <c r="R525" t="n">
         <v>1</v>
       </c>
       <c r="S525" t="n">
-        <v>0.1525636894605448</v>
+        <v>-0.03504467083581797</v>
       </c>
       <c r="T525" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U525" t="n">
-        <v>0.1525636894605448</v>
+        <v>-0.03504467083581797</v>
       </c>
       <c r="V525" t="n">
-        <v>0.3914355888829029</v>
+        <v>0.5787070596671816</v>
       </c>
       <c r="W525" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="X525" t="inlineStr">
         <is>
@@ -53084,16 +53082,16 @@
       </c>
       <c r="Y525" t="inlineStr"/>
       <c r="Z525" t="n">
-        <v>6.260564667031762</v>
+        <v>3.288962822429323</v>
       </c>
       <c r="AA525" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB525" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC525" t="inlineStr"/>
@@ -53103,78 +53101,78 @@
     <row r="526">
       <c r="A526" s="1" t="inlineStr">
         <is>
-          <t>xMovyDqH</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B526" s="2" t="n">
-        <v>45606.64583333334</v>
+        <v>45619.45833333334</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="E526" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F526" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G526" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="H526" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="I526" t="n">
-        <v>2.4</v>
+        <v>1.38</v>
       </c>
       <c r="J526" t="n">
-        <v>0.3344262295081967</v>
+        <v>0.1350293542074364</v>
       </c>
       <c r="K526" t="n">
-        <v>0.2754098360655738</v>
+        <v>0.1800391389432485</v>
       </c>
       <c r="L526" t="n">
-        <v>0.3901639344262295</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="M526" t="n">
-        <v>0.06792717086834732</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="N526" t="n">
         <v>2</v>
       </c>
       <c r="O526" t="n">
-        <v>0.2903942023150049</v>
+        <v>0.03250536456456055</v>
       </c>
       <c r="P526" t="n">
-        <v>0.2457897659363611</v>
+        <v>0.2018595202117701</v>
       </c>
       <c r="Q526" t="n">
-        <v>0.463816031748634</v>
+        <v>0.7656351152236692</v>
       </c>
       <c r="R526" t="n">
         <v>1</v>
       </c>
       <c r="S526" t="n">
-        <v>0.07365209732240446</v>
+        <v>0.08070360837435409</v>
       </c>
       <c r="T526" t="n">
         <v>2</v>
       </c>
       <c r="U526" t="n">
-        <v>0.07365209732240446</v>
+        <v>0.08070360837435409</v>
       </c>
       <c r="V526" t="n">
-        <v>0.463816031748634</v>
+        <v>0.7656351152236692</v>
       </c>
       <c r="W526" t="n">
-        <v>2.4</v>
+        <v>1.38</v>
       </c>
       <c r="X526" t="inlineStr">
         <is>
@@ -53183,16 +53181,16 @@
       </c>
       <c r="Y526" t="inlineStr"/>
       <c r="Z526" t="n">
-        <v>4.740152631489074</v>
+        <v>8.163371615408142</v>
       </c>
       <c r="AA526" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB526" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC526" t="inlineStr"/>
@@ -53202,78 +53200,78 @@
     <row r="527">
       <c r="A527" s="1" t="inlineStr">
         <is>
-          <t>EuQnZBVQ</t>
+          <t>z7KrCz8T</t>
         </is>
       </c>
       <c r="B527" s="2" t="n">
-        <v>45618.6875</v>
+        <v>45619.58333333334</v>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="E527" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F527" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G527" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H527" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="I527" t="n">
-        <v>15</v>
+        <v>3.5</v>
       </c>
       <c r="J527" t="n">
-        <v>0.8450704225352113</v>
+        <v>0.4509283819628648</v>
       </c>
       <c r="K527" t="n">
-        <v>0.09295774647887325</v>
+        <v>0.2785145888594165</v>
       </c>
       <c r="L527" t="n">
-        <v>0.06197183098591549</v>
+        <v>0.2705570291777188</v>
       </c>
       <c r="M527" t="n">
-        <v>0.07575757575757569</v>
+        <v>0.05602240896358524</v>
       </c>
       <c r="N527" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O527" t="n">
-        <v>0.4207096998051714</v>
+        <v>0.3327198060038317</v>
       </c>
       <c r="P527" t="n">
-        <v>0.3667474441088974</v>
+        <v>0.4494769501082279</v>
       </c>
       <c r="Q527" t="n">
-        <v>0.2125428560859311</v>
+        <v>0.2178032438879404</v>
       </c>
       <c r="R527" t="n">
         <v>1</v>
       </c>
       <c r="S527" t="n">
-        <v>-0.4243607227300398</v>
+        <v>0.1709623612488114</v>
       </c>
       <c r="T527" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U527" t="n">
-        <v>-0.4243607227300398</v>
+        <v>0.1709623612488114</v>
       </c>
       <c r="V527" t="n">
-        <v>0.4207096998051714</v>
+        <v>0.4494769501082279</v>
       </c>
       <c r="W527" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="X527" t="inlineStr">
         <is>
@@ -53282,117 +53280,115 @@
       </c>
       <c r="Y527" t="inlineStr"/>
       <c r="Z527" t="n">
-        <v>0</v>
+        <v>8.499947963276052</v>
       </c>
       <c r="AA527" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB527" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="AC527" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC527" t="inlineStr"/>
       <c r="AD527" t="inlineStr"/>
       <c r="AE527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="1" t="inlineStr">
         <is>
-          <t>2qNaDU87</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B528" s="2" t="n">
-        <v>45619.47916666666</v>
+        <v>45604.70833333334</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E528" t="n">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="F528" t="n">
-        <v>591</v>
+        <v>1481</v>
       </c>
       <c r="G528" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="H528" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="I528" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="J528" t="n">
-        <v>0.7784120394395433</v>
+        <v>0.5114491057997661</v>
       </c>
       <c r="K528" t="n">
-        <v>0.1582771146860404</v>
+        <v>0.2782884840381081</v>
       </c>
       <c r="L528" t="n">
-        <v>0.06331084587441618</v>
+        <v>0.2102624101621261</v>
       </c>
       <c r="M528" t="n">
-        <v>0.0530054644808744</v>
+        <v>0.05688040982158604</v>
       </c>
       <c r="N528" t="n">
         <v>1</v>
       </c>
       <c r="O528" t="n">
-        <v>0.6939419031995516</v>
+        <v>0.4278689274643216</v>
       </c>
       <c r="P528" t="n">
-        <v>0.2565956046804507</v>
+        <v>0.3629548310488862</v>
       </c>
       <c r="Q528" t="n">
-        <v>0.04946249211999764</v>
+        <v>0.2091762414867922</v>
       </c>
       <c r="R528" t="n">
         <v>1</v>
       </c>
       <c r="S528" t="n">
-        <v>-0.08447013623999167</v>
+        <v>-0.08358017833544445</v>
       </c>
       <c r="T528" t="n">
         <v>1</v>
       </c>
       <c r="U528" t="n">
-        <v>-0.08447013623999167</v>
+        <v>-0.08358017833544445</v>
       </c>
       <c r="V528" t="n">
-        <v>0.6939419031995516</v>
+        <v>0.4278689274643216</v>
       </c>
       <c r="W528" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="X528" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y528" t="inlineStr"/>
       <c r="Z528" t="n">
-        <v>2.225383488997406</v>
+        <v>4.278689274643217</v>
       </c>
       <c r="AA528" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB528" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC528" t="inlineStr"/>
@@ -53402,96 +53398,96 @@
     <row r="529">
       <c r="A529" s="1" t="inlineStr">
         <is>
-          <t>pOGITkgl</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B529" s="2" t="n">
-        <v>45619.47916666666</v>
+        <v>45605.41666666666</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E529" t="n">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="F529" t="n">
-        <v>591</v>
+        <v>1481</v>
       </c>
       <c r="G529" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="H529" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="I529" t="n">
-        <v>4.75</v>
+        <v>13</v>
       </c>
       <c r="J529" t="n">
-        <v>0.5746381507885073</v>
+        <v>0.7913043478260869</v>
       </c>
       <c r="K529" t="n">
-        <v>0.225750702095485</v>
+        <v>0.1356521739130435</v>
       </c>
       <c r="L529" t="n">
-        <v>0.1996111471160078</v>
+        <v>0.07304347826086957</v>
       </c>
       <c r="M529" t="n">
-        <v>0.05468215994531778</v>
+        <v>0.05311355311355315</v>
       </c>
       <c r="N529" t="n">
         <v>1</v>
       </c>
       <c r="O529" t="n">
-        <v>0.5353976182872061</v>
+        <v>0.6756412174164625</v>
       </c>
       <c r="P529" t="n">
-        <v>0.2974335586995293</v>
+        <v>0.2876177085514129</v>
       </c>
       <c r="Q529" t="n">
-        <v>0.1671688230132646</v>
+        <v>0.03674107403212467</v>
       </c>
       <c r="R529" t="n">
         <v>1</v>
       </c>
       <c r="S529" t="n">
-        <v>-0.03924053250130122</v>
+        <v>-0.1156631304096244</v>
       </c>
       <c r="T529" t="n">
         <v>1</v>
       </c>
       <c r="U529" t="n">
-        <v>-0.03924053250130122</v>
+        <v>-0.1156631304096244</v>
       </c>
       <c r="V529" t="n">
-        <v>0.5353976182872061</v>
+        <v>0.6756412174164625</v>
       </c>
       <c r="W529" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="X529" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y529" t="inlineStr"/>
       <c r="Z529" t="n">
-        <v>2.365221801762508</v>
+        <v>6.756412174164625</v>
       </c>
       <c r="AA529" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB529" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC529" t="inlineStr"/>
@@ -53501,96 +53497,96 @@
     <row r="530">
       <c r="A530" s="1" t="inlineStr">
         <is>
-          <t>E38ZP7hD</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B530" s="2" t="n">
-        <v>45619.47916666666</v>
+        <v>45605.51041666666</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E530" t="n">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="F530" t="n">
-        <v>591</v>
+        <v>1481</v>
       </c>
       <c r="G530" t="n">
-        <v>4.1</v>
+        <v>1.62</v>
       </c>
       <c r="H530" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I530" t="n">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="J530" t="n">
-        <v>0.2299619616899878</v>
+        <v>0.5883926183471516</v>
       </c>
       <c r="K530" t="n">
-        <v>0.2548227143051216</v>
+        <v>0.2382990104305964</v>
       </c>
       <c r="L530" t="n">
-        <v>0.5152153240048907</v>
+        <v>0.173308371222252</v>
       </c>
       <c r="M530" t="n">
-        <v>0.06062079672635434</v>
+        <v>0.04910213243546568</v>
       </c>
       <c r="N530" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O530" t="n">
-        <v>0.1850353483586111</v>
+        <v>0.3760498972198434</v>
       </c>
       <c r="P530" t="n">
-        <v>0.3068453998404827</v>
+        <v>0.3622639674720201</v>
       </c>
       <c r="Q530" t="n">
-        <v>0.5081192518009061</v>
+        <v>0.2616861353081363</v>
       </c>
       <c r="R530" t="n">
         <v>1</v>
       </c>
       <c r="S530" t="n">
-        <v>-0.00709607220398456</v>
+        <v>-0.2123427211273082</v>
       </c>
       <c r="T530" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U530" t="n">
-        <v>-0.00709607220398456</v>
+        <v>-0.2123427211273082</v>
       </c>
       <c r="V530" t="n">
-        <v>0.5081192518009061</v>
+        <v>0.3760498972198434</v>
       </c>
       <c r="W530" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="X530" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y530" t="inlineStr"/>
       <c r="Z530" t="n">
-        <v>2.998343518656049</v>
+        <v>3.760498972198434</v>
       </c>
       <c r="AA530" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB530" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC530" t="inlineStr"/>
@@ -53600,96 +53596,96 @@
     <row r="531">
       <c r="A531" s="1" t="inlineStr">
         <is>
-          <t>fwAoyY0E</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B531" s="2" t="n">
-        <v>45619.47916666666</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E531" t="n">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="F531" t="n">
-        <v>591</v>
+        <v>1481</v>
       </c>
       <c r="G531" t="n">
-        <v>1.22</v>
+        <v>2.88</v>
       </c>
       <c r="H531" t="n">
-        <v>6.25</v>
+        <v>3.2</v>
       </c>
       <c r="I531" t="n">
-        <v>12</v>
+        <v>2.55</v>
       </c>
       <c r="J531" t="n">
-        <v>0.7710892921400297</v>
+        <v>0.3300970873786407</v>
       </c>
       <c r="K531" t="n">
-        <v>0.1505166298257338</v>
+        <v>0.2970873786407767</v>
       </c>
       <c r="L531" t="n">
-        <v>0.07839407803423636</v>
+        <v>0.3728155339805825</v>
       </c>
       <c r="M531" t="n">
-        <v>0.06300546448087441</v>
+        <v>0.0518790849673203</v>
       </c>
       <c r="N531" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O531" t="n">
-        <v>0.5040588622807577</v>
+        <v>0.2549275904880438</v>
       </c>
       <c r="P531" t="n">
-        <v>0.3973333315804643</v>
+        <v>0.3827680317442166</v>
       </c>
       <c r="Q531" t="n">
-        <v>0.09860780613877793</v>
+        <v>0.3623043777677396</v>
       </c>
       <c r="R531" t="n">
         <v>1</v>
       </c>
       <c r="S531" t="n">
-        <v>-0.2670304298592721</v>
+        <v>0.08568065310343997</v>
       </c>
       <c r="T531" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U531" t="n">
-        <v>-0.2670304298592721</v>
+        <v>0.08568065310343997</v>
       </c>
       <c r="V531" t="n">
-        <v>0.5040588622807577</v>
+        <v>0.3827680317442166</v>
       </c>
       <c r="W531" t="n">
-        <v>1.22</v>
+        <v>3.2</v>
       </c>
       <c r="X531" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y531" t="inlineStr"/>
       <c r="Z531" t="n">
-        <v>0</v>
+        <v>3.827680317442166</v>
       </c>
       <c r="AA531" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB531" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC531" t="inlineStr"/>
@@ -53699,96 +53695,96 @@
     <row r="532">
       <c r="A532" s="1" t="inlineStr">
         <is>
-          <t>SrjMmBpK</t>
+          <t>SCX7iT7M</t>
         </is>
       </c>
       <c r="B532" s="2" t="n">
-        <v>45619.47916666666</v>
+        <v>45618.70833333334</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E532" t="n">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="F532" t="n">
-        <v>591</v>
+        <v>1481</v>
       </c>
       <c r="G532" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="H532" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I532" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="J532" t="n">
-        <v>0.4512877939529675</v>
+        <v>0.5696460056964601</v>
       </c>
       <c r="K532" t="n">
-        <v>0.2430011198208287</v>
+        <v>0.2718025227180252</v>
       </c>
       <c r="L532" t="n">
-        <v>0.3057110862262038</v>
+        <v>0.1585514715855147</v>
       </c>
       <c r="M532" t="n">
-        <v>0.05518137776202292</v>
+        <v>0.05118334759053322</v>
       </c>
       <c r="N532" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O532" t="n">
-        <v>0.347094786384264</v>
+        <v>0.3426184699525135</v>
       </c>
       <c r="P532" t="n">
-        <v>0.2445510541796648</v>
+        <v>0.4034798208331402</v>
       </c>
       <c r="Q532" t="n">
-        <v>0.4083541594360711</v>
+        <v>0.2539017092143463</v>
       </c>
       <c r="R532" t="n">
         <v>1</v>
       </c>
       <c r="S532" t="n">
-        <v>0.1026430732098673</v>
+        <v>0.131677298115115</v>
       </c>
       <c r="T532" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U532" t="n">
-        <v>0.1026430732098673</v>
+        <v>0.131677298115115</v>
       </c>
       <c r="V532" t="n">
-        <v>0.4083541594360711</v>
+        <v>0.4034798208331402</v>
       </c>
       <c r="W532" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="X532" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y532" t="inlineStr"/>
       <c r="Z532" t="n">
-        <v>5.118290326722128</v>
+        <v>4.034798208331401</v>
       </c>
       <c r="AA532" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB532" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC532" t="inlineStr"/>
@@ -53798,96 +53794,96 @@
     <row r="533">
       <c r="A533" s="1" t="inlineStr">
         <is>
-          <t>6w5RRTN0</t>
+          <t>C2KEmK6l</t>
         </is>
       </c>
       <c r="B533" s="2" t="n">
-        <v>45619.60416666666</v>
+        <v>45619.41666666666</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E533" t="n">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="F533" t="n">
-        <v>591</v>
+        <v>1481</v>
       </c>
       <c r="G533" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="H533" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="I533" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="J533" t="n">
-        <v>0.5830269494941478</v>
+        <v>0.3303964757709251</v>
       </c>
       <c r="K533" t="n">
-        <v>0.2181301750994271</v>
+        <v>0.3171806167400881</v>
       </c>
       <c r="L533" t="n">
-        <v>0.1988428754064251</v>
+        <v>0.3524229074889867</v>
       </c>
       <c r="M533" t="n">
-        <v>0.05875714862384762</v>
+        <v>0.05092592592592604</v>
       </c>
       <c r="N533" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O533" t="n">
-        <v>0.3959207641875817</v>
+        <v>0.3375807081572289</v>
       </c>
       <c r="P533" t="n">
-        <v>0.2899290307132603</v>
+        <v>0.3114246541767539</v>
       </c>
       <c r="Q533" t="n">
-        <v>0.314150205099158</v>
+        <v>0.3509946376660172</v>
       </c>
       <c r="R533" t="n">
         <v>1</v>
       </c>
       <c r="S533" t="n">
-        <v>-0.1871061853065661</v>
+        <v>-0.001428269822969563</v>
       </c>
       <c r="T533" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U533" t="n">
-        <v>-0.1871061853065661</v>
+        <v>-0.001428269822969563</v>
       </c>
       <c r="V533" t="n">
-        <v>0.3959207641875817</v>
+        <v>0.3509946376660172</v>
       </c>
       <c r="W533" t="n">
-        <v>1.62</v>
+        <v>2.7</v>
       </c>
       <c r="X533" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y533" t="inlineStr"/>
       <c r="Z533" t="n">
-        <v>0</v>
+        <v>3.509946376660172</v>
       </c>
       <c r="AA533" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB533" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC533" t="inlineStr"/>
@@ -53897,96 +53893,96 @@
     <row r="534">
       <c r="A534" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>vVwOqx6D</t>
         </is>
       </c>
       <c r="B534" s="2" t="n">
-        <v>45604.69791666666</v>
+        <v>45619.51041666666</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E534" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F534" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G534" t="n">
-        <v>2.35</v>
+        <v>1.38</v>
       </c>
       <c r="H534" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="I534" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="J534" t="n">
-        <v>0.4041204437400951</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="K534" t="n">
-        <v>0.3165610142630745</v>
+        <v>0.2100456621004566</v>
       </c>
       <c r="L534" t="n">
-        <v>0.2793185419968304</v>
+        <v>0.1050228310502283</v>
       </c>
       <c r="M534" t="n">
-        <v>0.05298289528577382</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="N534" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O534" t="n">
-        <v>0.2939333909711497</v>
+        <v>0.5819079639761686</v>
       </c>
       <c r="P534" t="n">
-        <v>0.4106573401420681</v>
+        <v>0.3113331289129357</v>
       </c>
       <c r="Q534" t="n">
-        <v>0.2954092688867823</v>
+        <v>0.1067589071108957</v>
       </c>
       <c r="R534" t="n">
         <v>1</v>
       </c>
       <c r="S534" t="n">
-        <v>0.09409632587899358</v>
+        <v>-0.1030235428731465</v>
       </c>
       <c r="T534" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U534" t="n">
-        <v>0.09409632587899358</v>
+        <v>-0.1030235428731465</v>
       </c>
       <c r="V534" t="n">
-        <v>0.4106573401420681</v>
+        <v>0.5819079639761686</v>
       </c>
       <c r="W534" t="n">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="X534" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y534" t="inlineStr"/>
       <c r="Z534" t="n">
-        <v>5.902819827435319</v>
+        <v>5.819079639761686</v>
       </c>
       <c r="AA534" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB534" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC534" t="inlineStr"/>
@@ -53996,96 +53992,96 @@
     <row r="535">
       <c r="A535" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>buKPeYL5</t>
         </is>
       </c>
       <c r="B535" s="2" t="n">
-        <v>45605.45833333334</v>
+        <v>45619.60416666666</v>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E535" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F535" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G535" t="n">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="H535" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I535" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="J535" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.5709391949757351</v>
       </c>
       <c r="K535" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2383671139023694</v>
       </c>
       <c r="L535" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.1906936911218955</v>
       </c>
       <c r="M535" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.04880239520958085</v>
       </c>
       <c r="N535" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O535" t="n">
-        <v>0.2498867756386013</v>
+        <v>0.5913279285595855</v>
       </c>
       <c r="P535" t="n">
-        <v>0.3748693937364196</v>
+        <v>0.2967899811784423</v>
       </c>
       <c r="Q535" t="n">
-        <v>0.3752438306249791</v>
+        <v>0.1118820902619721</v>
       </c>
       <c r="R535" t="n">
         <v>1</v>
       </c>
       <c r="S535" t="n">
-        <v>0.02472836670745338</v>
+        <v>0.0203887335838504</v>
       </c>
       <c r="T535" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U535" t="n">
-        <v>0.02472836670745338</v>
+        <v>0.0203887335838504</v>
       </c>
       <c r="V535" t="n">
-        <v>0.3752438306249791</v>
+        <v>0.5913279285595855</v>
       </c>
       <c r="W535" t="n">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="X535" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y535" t="inlineStr"/>
       <c r="Z535" t="n">
-        <v>3.556179730910945</v>
+        <v>5.913279285595855</v>
       </c>
       <c r="AA535" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB535" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC535" t="inlineStr"/>
@@ -54095,96 +54091,96 @@
     <row r="536">
       <c r="A536" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>IsCnpo0d</t>
         </is>
       </c>
       <c r="B536" s="2" t="n">
-        <v>45605.58333333334</v>
+        <v>45619.60416666666</v>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E536" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F536" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G536" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="H536" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="I536" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="J536" t="n">
-        <v>0.173041413874967</v>
+        <v>0.3351544442109687</v>
       </c>
       <c r="K536" t="n">
-        <v>0.2321287259298338</v>
+        <v>0.3235973944105905</v>
       </c>
       <c r="L536" t="n">
-        <v>0.5948298601951991</v>
+        <v>0.3412481613784409</v>
       </c>
       <c r="M536" t="n">
-        <v>0.05072062084257212</v>
+        <v>0.06560680698611732</v>
       </c>
       <c r="N536" t="n">
         <v>2</v>
       </c>
       <c r="O536" t="n">
-        <v>0.06416446372416562</v>
+        <v>0.2444187323844127</v>
       </c>
       <c r="P536" t="n">
-        <v>0.1884644760211565</v>
+        <v>0.325586583467244</v>
       </c>
       <c r="Q536" t="n">
-        <v>0.7473710602546778</v>
+        <v>0.4299946841483434</v>
       </c>
       <c r="R536" t="n">
         <v>1</v>
       </c>
       <c r="S536" t="n">
-        <v>0.1525412000594787</v>
+        <v>0.08874652276990247</v>
       </c>
       <c r="T536" t="n">
         <v>2</v>
       </c>
       <c r="U536" t="n">
-        <v>0.1525412000594787</v>
+        <v>0.08874652276990247</v>
       </c>
       <c r="V536" t="n">
-        <v>0.7473710602546778</v>
+        <v>0.4299946841483434</v>
       </c>
       <c r="W536" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="X536" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y536" t="inlineStr"/>
       <c r="Z536" t="n">
-        <v>10.18151895369444</v>
+        <v>4.299946841483433</v>
       </c>
       <c r="AA536" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB536" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC536" t="inlineStr"/>
@@ -54194,96 +54190,96 @@
     <row r="537">
       <c r="A537" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B537" s="2" t="n">
-        <v>45605.69791666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="E537" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="F537" t="n">
-        <v>771</v>
+        <v>481</v>
       </c>
       <c r="G537" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="H537" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="I537" t="n">
         <v>7</v>
       </c>
       <c r="J537" t="n">
-        <v>0.6137517305029996</v>
+        <v>0.6936936936936937</v>
       </c>
       <c r="K537" t="n">
-        <v>0.2503461005999077</v>
+        <v>0.1715315315315316</v>
       </c>
       <c r="L537" t="n">
-        <v>0.1359021688970928</v>
+        <v>0.1347747747747748</v>
       </c>
       <c r="M537" t="n">
-        <v>0.05117632791656557</v>
+        <v>0.05996944232238333</v>
       </c>
       <c r="N537" t="n">
         <v>1</v>
       </c>
       <c r="O537" t="n">
-        <v>0.5787070596671816</v>
+        <v>0.5378592901613963</v>
       </c>
       <c r="P537" t="n">
-        <v>0.2676145090391487</v>
+        <v>0.3484836460601265</v>
       </c>
       <c r="Q537" t="n">
-        <v>0.1536784312936697</v>
+        <v>0.1136570637784773</v>
       </c>
       <c r="R537" t="n">
         <v>1</v>
       </c>
       <c r="S537" t="n">
-        <v>-0.03504467083581797</v>
+        <v>-0.1558344035322974</v>
       </c>
       <c r="T537" t="n">
         <v>1</v>
       </c>
       <c r="U537" t="n">
-        <v>-0.03504467083581797</v>
+        <v>-0.1558344035322974</v>
       </c>
       <c r="V537" t="n">
-        <v>0.5787070596671816</v>
+        <v>0.5378592901613963</v>
       </c>
       <c r="W537" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="X537" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y537" t="inlineStr"/>
       <c r="Z537" t="n">
-        <v>3.288962822429323</v>
+        <v>0</v>
       </c>
       <c r="AA537" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB537" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC537" t="inlineStr"/>
@@ -54293,96 +54289,96 @@
     <row r="538">
       <c r="A538" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B538" s="2" t="n">
-        <v>45606.35416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="E538" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="F538" t="n">
-        <v>771</v>
+        <v>481</v>
       </c>
       <c r="G538" t="n">
-        <v>1.38</v>
+        <v>2.63</v>
       </c>
       <c r="H538" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="I538" t="n">
-        <v>7.5</v>
+        <v>2.63</v>
       </c>
       <c r="J538" t="n">
-        <v>0.6849315068493151</v>
+        <v>0.3575297941495125</v>
       </c>
       <c r="K538" t="n">
-        <v>0.189041095890411</v>
+        <v>0.2849404117009751</v>
       </c>
       <c r="L538" t="n">
-        <v>0.126027397260274</v>
+        <v>0.3575297941495125</v>
       </c>
       <c r="M538" t="n">
-        <v>0.05797101449275366</v>
+        <v>0.0634865767945616</v>
       </c>
       <c r="N538" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O538" t="n">
-        <v>0.6210748069468638</v>
+        <v>0.1986032024594239</v>
       </c>
       <c r="P538" t="n">
-        <v>0.2700769638529026</v>
+        <v>0.3797264780887767</v>
       </c>
       <c r="Q538" t="n">
-        <v>0.1088482292002337</v>
+        <v>0.4216703194517993</v>
       </c>
       <c r="R538" t="n">
         <v>1</v>
       </c>
       <c r="S538" t="n">
-        <v>-0.06385669990245135</v>
+        <v>0.06414052530228687</v>
       </c>
       <c r="T538" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U538" t="n">
-        <v>-0.06385669990245135</v>
+        <v>0.06414052530228687</v>
       </c>
       <c r="V538" t="n">
-        <v>0.6210748069468638</v>
+        <v>0.4216703194517993</v>
       </c>
       <c r="W538" t="n">
-        <v>1.38</v>
+        <v>2.63</v>
       </c>
       <c r="X538" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y538" t="inlineStr"/>
       <c r="Z538" t="n">
-        <v>2.742360055027938</v>
+        <v>5.086743154957101</v>
       </c>
       <c r="AA538" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB538" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC538" t="inlineStr"/>
@@ -54392,7 +54388,7 @@
     <row r="539">
       <c r="A539" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B539" s="2" t="n">
@@ -54400,88 +54396,88 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="E539" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="F539" t="n">
-        <v>771</v>
+        <v>481</v>
       </c>
       <c r="G539" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="H539" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="I539" t="n">
-        <v>3.6</v>
+        <v>9.5</v>
       </c>
       <c r="J539" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.763271162123386</v>
       </c>
       <c r="K539" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.1362984218077475</v>
       </c>
       <c r="L539" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.1004304160688666</v>
       </c>
       <c r="M539" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.04812030075187979</v>
       </c>
       <c r="N539" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O539" t="n">
-        <v>0.2121643271392464</v>
+        <v>0.6780859114535537</v>
       </c>
       <c r="P539" t="n">
-        <v>0.28252457474014</v>
+        <v>0.2652415082892427</v>
       </c>
       <c r="Q539" t="n">
-        <v>0.5053110981206135</v>
+        <v>0.05667258025720368</v>
       </c>
       <c r="R539" t="n">
         <v>1</v>
       </c>
       <c r="S539" t="n">
-        <v>0.2431824783387406</v>
+        <v>-0.08518525066983229</v>
       </c>
       <c r="T539" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U539" t="n">
-        <v>0.2431824783387406</v>
+        <v>-0.08518525066983229</v>
       </c>
       <c r="V539" t="n">
-        <v>0.5053110981206135</v>
+        <v>0.6780859114535537</v>
       </c>
       <c r="W539" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="X539" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y539" t="inlineStr"/>
       <c r="Z539" t="n">
-        <v>11.08530758606682</v>
+        <v>2.530086815806684</v>
       </c>
       <c r="AA539" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB539" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC539" t="inlineStr"/>
@@ -54491,96 +54487,96 @@
     <row r="540">
       <c r="A540" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B540" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45606.5625</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="E540" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="F540" t="n">
-        <v>771</v>
+        <v>481</v>
       </c>
       <c r="G540" t="n">
-        <v>1.44</v>
+        <v>2.9</v>
       </c>
       <c r="H540" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I540" t="n">
-        <v>7</v>
+        <v>2.38</v>
       </c>
       <c r="J540" t="n">
-        <v>0.6554307116104868</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="K540" t="n">
-        <v>0.2097378277153558</v>
+        <v>0.2777017783857729</v>
       </c>
       <c r="L540" t="n">
-        <v>0.1348314606741573</v>
+        <v>0.3967168262653898</v>
       </c>
       <c r="M540" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.05911330049261099</v>
       </c>
       <c r="N540" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O540" t="n">
-        <v>0.5616255264882302</v>
+        <v>0.2788967213864181</v>
       </c>
       <c r="P540" t="n">
-        <v>0.3175377770356159</v>
+        <v>0.3575630948150566</v>
       </c>
       <c r="Q540" t="n">
-        <v>0.120836696476154</v>
+        <v>0.3635401837985254</v>
       </c>
       <c r="R540" t="n">
         <v>1</v>
       </c>
       <c r="S540" t="n">
-        <v>-0.09380518512225666</v>
+        <v>-0.03317664246686447</v>
       </c>
       <c r="T540" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U540" t="n">
-        <v>-0.09380518512225666</v>
+        <v>-0.03317664246686447</v>
       </c>
       <c r="V540" t="n">
-        <v>0.5616255264882302</v>
+        <v>0.3635401837985254</v>
       </c>
       <c r="W540" t="n">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="X540" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y540" t="inlineStr"/>
       <c r="Z540" t="n">
-        <v>1.398035894994026</v>
+        <v>1.731252104483006</v>
       </c>
       <c r="AA540" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>england</t>
         </is>
       </c>
       <c r="AB540" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="AC540" t="inlineStr"/>
@@ -54590,96 +54586,96 @@
     <row r="541">
       <c r="A541" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B541" s="2" t="n">
-        <v>45606.58333333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E541" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F541" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G541" t="n">
-        <v>4.1</v>
+        <v>2.45</v>
       </c>
       <c r="H541" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="I541" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="J541" t="n">
-        <v>0.2315144654925592</v>
+        <v>0.3872529245663574</v>
       </c>
       <c r="K541" t="n">
-        <v>0.2497919232946033</v>
+        <v>0.2964905203711174</v>
       </c>
       <c r="L541" t="n">
-        <v>0.5186936112128375</v>
+        <v>0.3162565550625252</v>
       </c>
       <c r="M541" t="n">
-        <v>0.0535084211929262</v>
+        <v>0.05399659863945572</v>
       </c>
       <c r="N541" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O541" t="n">
-        <v>0.1944810728279434</v>
+        <v>0.3231888607310542</v>
       </c>
       <c r="P541" t="n">
-        <v>0.4216163095235277</v>
+        <v>0.336113990438709</v>
       </c>
       <c r="Q541" t="n">
-        <v>0.3839026176485287</v>
+        <v>0.3406971488302368</v>
       </c>
       <c r="R541" t="n">
         <v>1</v>
       </c>
       <c r="S541" t="n">
-        <v>0.1718243862289244</v>
+        <v>0.02444059376771157</v>
       </c>
       <c r="T541" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U541" t="n">
-        <v>0.1718243862289244</v>
+        <v>0.02444059376771157</v>
       </c>
       <c r="V541" t="n">
-        <v>0.4216163095235277</v>
+        <v>0.3406971488302368</v>
       </c>
       <c r="W541" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="X541" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y541" t="inlineStr"/>
       <c r="Z541" t="n">
-        <v>8.31685390829419</v>
+        <v>3.895783363656599</v>
       </c>
       <c r="AA541" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB541" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC541" t="inlineStr"/>
@@ -54689,96 +54685,96 @@
     <row r="542">
       <c r="A542" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B542" s="2" t="n">
-        <v>45606.69791666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="E542" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F542" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G542" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="H542" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="I542" t="n">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="J542" t="n">
-        <v>0.5125</v>
+        <v>0.2942384818546415</v>
       </c>
       <c r="K542" t="n">
-        <v>0.25625</v>
+        <v>0.2988359581336203</v>
       </c>
       <c r="L542" t="n">
-        <v>0.23125</v>
+        <v>0.4069255600117382</v>
       </c>
       <c r="M542" t="n">
-        <v>0.05471324983520098</v>
+        <v>0.04572422258592468</v>
       </c>
       <c r="N542" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O542" t="n">
-        <v>0.5199129358101434</v>
+        <v>0.1278399194423144</v>
       </c>
       <c r="P542" t="n">
-        <v>0.2471773357794682</v>
+        <v>0.3064311079222078</v>
       </c>
       <c r="Q542" t="n">
-        <v>0.2329097284103884</v>
+        <v>0.5657289726354777</v>
       </c>
       <c r="R542" t="n">
         <v>1</v>
       </c>
       <c r="S542" t="n">
-        <v>0.007412935810143462</v>
+        <v>0.1588034126237395</v>
       </c>
       <c r="T542" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U542" t="n">
-        <v>0.007412935810143462</v>
+        <v>0.1588034126237395</v>
       </c>
       <c r="V542" t="n">
-        <v>0.5199129358101434</v>
+        <v>0.5657289726354777</v>
       </c>
       <c r="W542" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="X542" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y542" t="inlineStr"/>
       <c r="Z542" t="n">
-        <v>4.121735092880379</v>
+        <v>8.833357978829566</v>
       </c>
       <c r="AA542" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB542" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC542" t="inlineStr"/>
@@ -54788,96 +54784,96 @@
     <row r="543">
       <c r="A543" s="1" t="inlineStr">
         <is>
-          <t>WENRFI84</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B543" s="2" t="n">
-        <v>45619.45833333334</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E543" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F543" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G543" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="H543" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="I543" t="n">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="J543" t="n">
-        <v>0.1350293542074364</v>
+        <v>0.2875429881543752</v>
       </c>
       <c r="K543" t="n">
-        <v>0.1800391389432485</v>
+        <v>0.2711119602598395</v>
       </c>
       <c r="L543" t="n">
-        <v>0.6849315068493151</v>
+        <v>0.4413450515857852</v>
       </c>
       <c r="M543" t="n">
-        <v>0.05797101449275366</v>
+        <v>0.05386086781435617</v>
       </c>
       <c r="N543" t="n">
         <v>2</v>
       </c>
       <c r="O543" t="n">
-        <v>0.03250536456456055</v>
+        <v>0.3055025668389336</v>
       </c>
       <c r="P543" t="n">
-        <v>0.2018595202117701</v>
+        <v>0.3217084751146663</v>
       </c>
       <c r="Q543" t="n">
-        <v>0.7656351152236692</v>
+        <v>0.3727889580464001</v>
       </c>
       <c r="R543" t="n">
         <v>1</v>
       </c>
       <c r="S543" t="n">
-        <v>0.08070360837435409</v>
+        <v>-0.06855609353938513</v>
       </c>
       <c r="T543" t="n">
         <v>2</v>
       </c>
       <c r="U543" t="n">
-        <v>0.08070360837435409</v>
+        <v>-0.06855609353938513</v>
       </c>
       <c r="V543" t="n">
-        <v>0.7656351152236692</v>
+        <v>0.3727889580464001</v>
       </c>
       <c r="W543" t="n">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="X543" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y543" t="inlineStr"/>
       <c r="Z543" t="n">
-        <v>8.163371615408142</v>
+        <v>2.356767709676299</v>
       </c>
       <c r="AA543" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB543" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC543" t="inlineStr"/>
@@ -54887,96 +54883,96 @@
     <row r="544">
       <c r="A544" s="1" t="inlineStr">
         <is>
-          <t>z7KrCz8T</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B544" s="2" t="n">
-        <v>45619.58333333334</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="E544" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F544" t="n">
-        <v>771</v>
+        <v>551</v>
       </c>
       <c r="G544" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="H544" t="n">
         <v>3.4</v>
       </c>
       <c r="I544" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J544" t="n">
-        <v>0.4509283819628648</v>
+        <v>0.4415584415584415</v>
       </c>
       <c r="K544" t="n">
-        <v>0.2785145888594165</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="L544" t="n">
-        <v>0.2705570291777188</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="M544" t="n">
-        <v>0.05602240896358524</v>
+        <v>0.05335157318741457</v>
       </c>
       <c r="N544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O544" t="n">
-        <v>0.3327198060038317</v>
+        <v>0.5582621172651853</v>
       </c>
       <c r="P544" t="n">
-        <v>0.4494769501082279</v>
+        <v>0.2953693838037555</v>
       </c>
       <c r="Q544" t="n">
-        <v>0.2178032438879404</v>
+        <v>0.1463684989310591</v>
       </c>
       <c r="R544" t="n">
         <v>1</v>
       </c>
       <c r="S544" t="n">
-        <v>0.1709623612488114</v>
+        <v>0.1167036757067437</v>
       </c>
       <c r="T544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U544" t="n">
-        <v>0.1709623612488114</v>
+        <v>0.1167036757067437</v>
       </c>
       <c r="V544" t="n">
-        <v>0.4494769501082279</v>
+        <v>0.5582621172651853</v>
       </c>
       <c r="W544" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="X544" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y544" t="inlineStr"/>
       <c r="Z544" t="n">
-        <v>8.499947963276052</v>
+        <v>7.916694686786727</v>
       </c>
       <c r="AA544" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB544" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>ligue 1</t>
         </is>
       </c>
       <c r="AC544" t="inlineStr"/>
@@ -54986,294 +54982,298 @@
     <row r="545">
       <c r="A545" s="1" t="inlineStr">
         <is>
-          <t>rPc4X7Gj</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B545" s="2" t="n">
-        <v>45604.70833333334</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E545" t="n">
-        <v>148</v>
+        <v>55</v>
       </c>
       <c r="F545" t="n">
-        <v>1481</v>
+        <v>551</v>
       </c>
       <c r="G545" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="H545" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="I545" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="J545" t="n">
-        <v>0.5114491057997661</v>
+        <v>0.7101928819304333</v>
       </c>
       <c r="K545" t="n">
-        <v>0.2782884840381081</v>
+        <v>0.1717375514486321</v>
       </c>
       <c r="L545" t="n">
-        <v>0.2102624101621261</v>
+        <v>0.1180695666209345</v>
       </c>
       <c r="M545" t="n">
-        <v>0.05688040982158604</v>
+        <v>0.05869788106630214</v>
       </c>
       <c r="N545" t="n">
         <v>1</v>
       </c>
       <c r="O545" t="n">
-        <v>0.4278689274643216</v>
+        <v>0.4285473990809589</v>
       </c>
       <c r="P545" t="n">
-        <v>0.3629548310488862</v>
+        <v>0.3196829283047876</v>
       </c>
       <c r="Q545" t="n">
-        <v>0.2091762414867922</v>
+        <v>0.2517696726142534</v>
       </c>
       <c r="R545" t="n">
         <v>1</v>
       </c>
       <c r="S545" t="n">
-        <v>-0.08358017833544445</v>
+        <v>-0.2816454828494744</v>
       </c>
       <c r="T545" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U545" t="n">
-        <v>-0.08358017833544445</v>
+        <v>0.2816454828494744</v>
       </c>
       <c r="V545" t="n">
-        <v>0.4278689274643216</v>
+        <v>0.571452600919041</v>
       </c>
       <c r="W545" t="n">
-        <v>1.85</v>
+        <v>3.259259259259259</v>
       </c>
       <c r="X545" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y545" t="inlineStr"/>
       <c r="Z545" t="n">
-        <v>4.278689274643217</v>
+        <v>11.3474356661799</v>
       </c>
       <c r="AA545" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>france</t>
         </is>
       </c>
       <c r="AB545" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC545" t="inlineStr"/>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="AC545" t="n">
+        <v>1</v>
+      </c>
       <c r="AD545" t="inlineStr"/>
       <c r="AE545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="1" t="inlineStr">
         <is>
-          <t>nucZxUhT</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B546" s="2" t="n">
-        <v>45605.41666666666</v>
+        <v>45606.47916666666</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="E546" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F546" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G546" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="H546" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="I546" t="n">
-        <v>13</v>
+        <v>3.25</v>
       </c>
       <c r="J546" t="n">
-        <v>0.7913043478260869</v>
+        <v>0.4485336400230017</v>
       </c>
       <c r="K546" t="n">
-        <v>0.1356521739130435</v>
+        <v>0.261644623346751</v>
       </c>
       <c r="L546" t="n">
-        <v>0.07304347826086957</v>
+        <v>0.2898217366302473</v>
       </c>
       <c r="M546" t="n">
-        <v>0.05311355311355315</v>
+        <v>0.06166056166056166</v>
       </c>
       <c r="N546" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O546" t="n">
-        <v>0.6756412174164625</v>
+        <v>0.3597390994038149</v>
       </c>
       <c r="P546" t="n">
-        <v>0.2876177085514129</v>
+        <v>0.4347694480007554</v>
       </c>
       <c r="Q546" t="n">
-        <v>0.03674107403212467</v>
+        <v>0.2054914525954297</v>
       </c>
       <c r="R546" t="n">
         <v>1</v>
       </c>
       <c r="S546" t="n">
-        <v>-0.1156631304096244</v>
+        <v>0.1731248246540044</v>
       </c>
       <c r="T546" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U546" t="n">
-        <v>-0.1156631304096244</v>
+        <v>0.1731248246540044</v>
       </c>
       <c r="V546" t="n">
-        <v>0.6756412174164625</v>
+        <v>0.4347694480007554</v>
       </c>
       <c r="W546" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="X546" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y546" t="inlineStr"/>
       <c r="Z546" t="n">
-        <v>6.756412174164625</v>
+        <v>5.434618100009443</v>
       </c>
       <c r="AA546" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB546" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC546" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="AC546" t="n">
+        <v>1</v>
+      </c>
       <c r="AD546" t="inlineStr"/>
       <c r="AE546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="1" t="inlineStr">
         <is>
-          <t>bXuieB8c</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B547" s="2" t="n">
-        <v>45605.51041666666</v>
+        <v>45606.5625</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="E547" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F547" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G547" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="H547" t="n">
         <v>4</v>
       </c>
       <c r="I547" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="J547" t="n">
-        <v>0.5883926183471516</v>
+        <v>0.4979941900677826</v>
       </c>
       <c r="K547" t="n">
-        <v>0.2382990104305964</v>
+        <v>0.2377922257573662</v>
       </c>
       <c r="L547" t="n">
-        <v>0.173308371222252</v>
+        <v>0.2642135841748513</v>
       </c>
       <c r="M547" t="n">
-        <v>0.04910213243546568</v>
+        <v>0.05133798720186156</v>
       </c>
       <c r="N547" t="n">
         <v>1</v>
       </c>
       <c r="O547" t="n">
-        <v>0.3760498972198434</v>
+        <v>0.4640757913280562</v>
       </c>
       <c r="P547" t="n">
-        <v>0.3622639674720201</v>
+        <v>0.3996185027236255</v>
       </c>
       <c r="Q547" t="n">
-        <v>0.2616861353081363</v>
+        <v>0.1363057059483183</v>
       </c>
       <c r="R547" t="n">
         <v>1</v>
       </c>
       <c r="S547" t="n">
-        <v>-0.2123427211273082</v>
+        <v>-0.03391839873972635</v>
       </c>
       <c r="T547" t="n">
         <v>1</v>
       </c>
       <c r="U547" t="n">
-        <v>-0.2123427211273082</v>
+        <v>-0.03391839873972635</v>
       </c>
       <c r="V547" t="n">
-        <v>0.3760498972198434</v>
+        <v>0.4640757913280562</v>
       </c>
       <c r="W547" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="X547" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y547" t="inlineStr"/>
       <c r="Z547" t="n">
-        <v>3.760498972198434</v>
+        <v>4.105027454614385</v>
       </c>
       <c r="AA547" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB547" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC547" t="inlineStr"/>
@@ -55283,96 +55283,96 @@
     <row r="548">
       <c r="A548" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B548" s="2" t="n">
-        <v>45605.70833333334</v>
+        <v>45606.64583333334</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="E548" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F548" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G548" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="H548" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I548" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="J548" t="n">
-        <v>0.3300970873786407</v>
+        <v>0.3344262295081967</v>
       </c>
       <c r="K548" t="n">
-        <v>0.2970873786407767</v>
+        <v>0.2754098360655738</v>
       </c>
       <c r="L548" t="n">
-        <v>0.3728155339805825</v>
+        <v>0.3901639344262295</v>
       </c>
       <c r="M548" t="n">
-        <v>0.0518790849673203</v>
+        <v>0.06792717086834732</v>
       </c>
       <c r="N548" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O548" t="n">
-        <v>0.2549275904880438</v>
+        <v>0.2366214817997867</v>
       </c>
       <c r="P548" t="n">
-        <v>0.3827680317442166</v>
+        <v>0.3563001439412624</v>
       </c>
       <c r="Q548" t="n">
-        <v>0.3623043777677396</v>
+        <v>0.4070783742589508</v>
       </c>
       <c r="R548" t="n">
         <v>1</v>
       </c>
       <c r="S548" t="n">
-        <v>0.08568065310343997</v>
+        <v>0.01691443983272128</v>
       </c>
       <c r="T548" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U548" t="n">
-        <v>0.08568065310343997</v>
+        <v>0.01691443983272128</v>
       </c>
       <c r="V548" t="n">
-        <v>0.3827680317442166</v>
+        <v>0.4070783742589508</v>
       </c>
       <c r="W548" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="X548" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y548" t="inlineStr"/>
       <c r="Z548" t="n">
-        <v>3.827680317442166</v>
+        <v>5.088479678236886</v>
       </c>
       <c r="AA548" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB548" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC548" t="inlineStr"/>
@@ -55382,96 +55382,96 @@
     <row r="549">
       <c r="A549" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B549" s="2" t="n">
-        <v>45606.41666666666</v>
+        <v>45606.35416666666</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="E549" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F549" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G549" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="H549" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="I549" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="J549" t="n">
-        <v>0.4851944345344275</v>
+        <v>0.6942607775720708</v>
       </c>
       <c r="K549" t="n">
-        <v>0.2782732786300393</v>
+        <v>0.1798466014281936</v>
       </c>
       <c r="L549" t="n">
-        <v>0.2365322868355333</v>
+        <v>0.1258926209997355</v>
       </c>
       <c r="M549" t="n">
-        <v>0.05693815987933637</v>
+        <v>0.05910364145658265</v>
       </c>
       <c r="N549" t="n">
         <v>1</v>
       </c>
       <c r="O549" t="n">
-        <v>0.5124871616120684</v>
+        <v>0.5947624819621442</v>
       </c>
       <c r="P549" t="n">
-        <v>0.2662130224057716</v>
+        <v>0.2947669673315003</v>
       </c>
       <c r="Q549" t="n">
-        <v>0.2212998159821599</v>
+        <v>0.1104705507063555</v>
       </c>
       <c r="R549" t="n">
         <v>1</v>
       </c>
       <c r="S549" t="n">
-        <v>0.02729272707764097</v>
+        <v>-0.09949829560992662</v>
       </c>
       <c r="T549" t="n">
         <v>1</v>
       </c>
       <c r="U549" t="n">
-        <v>0.02729272707764097</v>
+        <v>-0.09949829560992662</v>
       </c>
       <c r="V549" t="n">
-        <v>0.5124871616120684</v>
+        <v>0.5947624819621442</v>
       </c>
       <c r="W549" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="X549" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y549" t="inlineStr"/>
       <c r="Z549" t="n">
-        <v>5.124871616120684</v>
+        <v>1.475769746418283</v>
       </c>
       <c r="AA549" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB549" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC549" t="inlineStr"/>
@@ -55481,96 +55481,96 @@
     <row r="550">
       <c r="A550" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B550" s="2" t="n">
-        <v>45606.51041666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F550" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G550" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="H550" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I550" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J550" t="n">
-        <v>0.2797175362887406</v>
+        <v>0.4505119453924914</v>
       </c>
       <c r="K550" t="n">
-        <v>0.3067869752844252</v>
+        <v>0.2866894197952218</v>
       </c>
       <c r="L550" t="n">
-        <v>0.413495488426834</v>
+        <v>0.2627986348122867</v>
       </c>
       <c r="M550" t="n">
-        <v>0.05148090091576618</v>
+        <v>0.05699855699855716</v>
       </c>
       <c r="N550" t="n">
         <v>2</v>
       </c>
       <c r="O550" t="n">
-        <v>0.2084941196855593</v>
+        <v>0.2257188642876106</v>
       </c>
       <c r="P550" t="n">
-        <v>0.2497989324274281</v>
+        <v>0.2807878519730899</v>
       </c>
       <c r="Q550" t="n">
-        <v>0.5417069478870126</v>
+        <v>0.4934932837392993</v>
       </c>
       <c r="R550" t="n">
         <v>1</v>
       </c>
       <c r="S550" t="n">
-        <v>0.1282114594601785</v>
+        <v>0.2306946489270126</v>
       </c>
       <c r="T550" t="n">
         <v>2</v>
       </c>
       <c r="U550" t="n">
-        <v>0.1282114594601785</v>
+        <v>0.2306946489270126</v>
       </c>
       <c r="V550" t="n">
-        <v>0.5417069478870126</v>
+        <v>0.4934932837392993</v>
       </c>
       <c r="W550" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="X550" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y550" t="inlineStr"/>
       <c r="Z550" t="n">
-        <v>5.417069478870125</v>
+        <v>10.62203909585512</v>
       </c>
       <c r="AA550" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB550" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC550" t="inlineStr"/>
@@ -55580,96 +55580,96 @@
     <row r="551">
       <c r="A551" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B551" s="2" t="n">
-        <v>45606.60416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F551" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G551" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="H551" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="I551" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="J551" t="n">
-        <v>0.3981697037810067</v>
+        <v>0.6538661131292164</v>
       </c>
       <c r="K551" t="n">
-        <v>0.2961387171871237</v>
+        <v>0.210690192008303</v>
       </c>
       <c r="L551" t="n">
-        <v>0.3056915790318696</v>
+        <v>0.1354436948624805</v>
       </c>
       <c r="M551" t="n">
-        <v>0.05524871238818108</v>
+        <v>0.05473453749315826</v>
       </c>
       <c r="N551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O551" t="n">
-        <v>0.1902676964861811</v>
+        <v>0.5597977247595817</v>
       </c>
       <c r="P551" t="n">
-        <v>0.3783058884736485</v>
+        <v>0.3177754976243357</v>
       </c>
       <c r="Q551" t="n">
-        <v>0.4314264150401704</v>
+        <v>0.1224267776160825</v>
       </c>
       <c r="R551" t="n">
         <v>1</v>
       </c>
       <c r="S551" t="n">
-        <v>0.1257348360083008</v>
+        <v>-0.09406838836963471</v>
       </c>
       <c r="T551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U551" t="n">
-        <v>0.1257348360083008</v>
+        <v>-0.09406838836963471</v>
       </c>
       <c r="V551" t="n">
-        <v>0.4314264150401704</v>
+        <v>0.5597977247595817</v>
       </c>
       <c r="W551" t="n">
-        <v>3.1</v>
+        <v>1.45</v>
       </c>
       <c r="X551" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y551" t="inlineStr"/>
       <c r="Z551" t="n">
-        <v>4.314264150401704</v>
+        <v>1.376431284607821</v>
       </c>
       <c r="AA551" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB551" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC551" t="inlineStr"/>
@@ -55679,27 +55679,27 @@
     <row r="552">
       <c r="A552" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B552" s="2" t="n">
-        <v>45606.60416666666</v>
+        <v>45606.58333333334</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E552" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F552" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G552" t="n">
         <v>4.75</v>
@@ -55708,67 +55708,67 @@
         <v>3.4</v>
       </c>
       <c r="I552" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="J552" t="n">
-        <v>0.1985723556132381</v>
+        <v>0.2002929388852227</v>
       </c>
       <c r="K552" t="n">
-        <v>0.2774172615184945</v>
+        <v>0.2798210175602376</v>
       </c>
       <c r="L552" t="n">
-        <v>0.5240103828682673</v>
+        <v>0.5198860435545397</v>
       </c>
       <c r="M552" t="n">
-        <v>0.06019951840385285</v>
+        <v>0.0510920502799912</v>
       </c>
       <c r="N552" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O552" t="n">
-        <v>0.2148935711721427</v>
+        <v>0.1944810728279434</v>
       </c>
       <c r="P552" t="n">
-        <v>0.3105838141353662</v>
+        <v>0.4216163095235277</v>
       </c>
       <c r="Q552" t="n">
-        <v>0.4745226146924911</v>
+        <v>0.3839026176485287</v>
       </c>
       <c r="R552" t="n">
         <v>1</v>
       </c>
       <c r="S552" t="n">
-        <v>-0.04948776817577621</v>
+        <v>0.1417952919632902</v>
       </c>
       <c r="T552" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U552" t="n">
-        <v>-0.04948776817577621</v>
+        <v>0.1417952919632902</v>
       </c>
       <c r="V552" t="n">
-        <v>0.4745226146924911</v>
+        <v>0.4216163095235277</v>
       </c>
       <c r="W552" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="X552" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y552" t="inlineStr"/>
       <c r="Z552" t="n">
-        <v>4.745226146924911</v>
+        <v>7.415981080325162</v>
       </c>
       <c r="AA552" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB552" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC552" t="inlineStr"/>
@@ -55778,96 +55778,96 @@
     <row r="553">
       <c r="A553" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B553" s="2" t="n">
-        <v>45606.70833333334</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="E553" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F553" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G553" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="H553" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="I553" t="n">
-        <v>1.7</v>
+        <v>4.33</v>
       </c>
       <c r="J553" t="n">
-        <v>0.2095531587057011</v>
+        <v>0.5275084060230983</v>
       </c>
       <c r="K553" t="n">
-        <v>0.2357473035439137</v>
+        <v>0.2532040348910872</v>
       </c>
       <c r="L553" t="n">
-        <v>0.5546995377503853</v>
+        <v>0.2192875590858145</v>
       </c>
       <c r="M553" t="n">
-        <v>0.06045751633986929</v>
+        <v>0.05316910443931233</v>
       </c>
       <c r="N553" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O553" t="n">
-        <v>0.1428502156665979</v>
+        <v>0.5199129358101434</v>
       </c>
       <c r="P553" t="n">
-        <v>0.3223447561188271</v>
+        <v>0.2471773357794682</v>
       </c>
       <c r="Q553" t="n">
-        <v>0.534805028214575</v>
+        <v>0.2329097284103884</v>
       </c>
       <c r="R553" t="n">
         <v>1</v>
       </c>
       <c r="S553" t="n">
-        <v>-0.01989450953581029</v>
+        <v>-0.007595470212954925</v>
       </c>
       <c r="T553" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U553" t="n">
-        <v>-0.01989450953581029</v>
+        <v>-0.007595470212954925</v>
       </c>
       <c r="V553" t="n">
-        <v>0.534805028214575</v>
+        <v>0.5199129358101434</v>
       </c>
       <c r="W553" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="X553" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y553" t="inlineStr"/>
       <c r="Z553" t="n">
-        <v>5.34805028214575</v>
+        <v>3.671482912187428</v>
       </c>
       <c r="AA553" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB553" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC553" t="inlineStr"/>
@@ -55877,20 +55877,20 @@
     <row r="554">
       <c r="A554" s="1" t="inlineStr">
         <is>
-          <t>SCX7iT7M</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B554" s="2" t="n">
-        <v>45618.70833333334</v>
+        <v>45606.41666666666</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E554" t="n">
@@ -55900,64 +55900,64 @@
         <v>1481</v>
       </c>
       <c r="G554" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="H554" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I554" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="J554" t="n">
-        <v>0.5696460056964601</v>
+        <v>0.4792284866468843</v>
       </c>
       <c r="K554" t="n">
-        <v>0.2718025227180252</v>
+        <v>0.2748516320474778</v>
       </c>
       <c r="L554" t="n">
-        <v>0.1585514715855147</v>
+        <v>0.245919881305638</v>
       </c>
       <c r="M554" t="n">
-        <v>0.05118334759053322</v>
+        <v>0.0700960546161784</v>
       </c>
       <c r="N554" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O554" t="n">
-        <v>0.3426184699525135</v>
+        <v>0.3771387037169621</v>
       </c>
       <c r="P554" t="n">
-        <v>0.4034798208331402</v>
+        <v>0.3515714603523336</v>
       </c>
       <c r="Q554" t="n">
-        <v>0.2539017092143463</v>
+        <v>0.2712898359307043</v>
       </c>
       <c r="R554" t="n">
         <v>1</v>
       </c>
       <c r="S554" t="n">
-        <v>0.131677298115115</v>
+        <v>-0.1020897829299222</v>
       </c>
       <c r="T554" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U554" t="n">
-        <v>0.131677298115115</v>
+        <v>-0.1020897829299222</v>
       </c>
       <c r="V554" t="n">
-        <v>0.4034798208331402</v>
+        <v>0.3771387037169621</v>
       </c>
       <c r="W554" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="X554" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y554" t="inlineStr"/>
       <c r="Z554" t="n">
-        <v>4.034798208331401</v>
+        <v>4.714233796462026</v>
       </c>
       <c r="AA554" t="inlineStr">
         <is>
@@ -55976,20 +55976,20 @@
     <row r="555">
       <c r="A555" s="1" t="inlineStr">
         <is>
-          <t>C2KEmK6l</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B555" s="2" t="n">
-        <v>45619.41666666666</v>
+        <v>45606.51041666666</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E555" t="n">
@@ -55999,64 +55999,64 @@
         <v>1481</v>
       </c>
       <c r="G555" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="H555" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I555" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J555" t="n">
-        <v>0.3303964757709251</v>
+        <v>0.2857715430861724</v>
       </c>
       <c r="K555" t="n">
-        <v>0.3171806167400881</v>
+        <v>0.3042084168336673</v>
       </c>
       <c r="L555" t="n">
-        <v>0.3524229074889867</v>
+        <v>0.4100200400801604</v>
       </c>
       <c r="M555" t="n">
-        <v>0.05092592592592604</v>
+        <v>0.06039355688724557</v>
       </c>
       <c r="N555" t="n">
         <v>2</v>
       </c>
       <c r="O555" t="n">
-        <v>0.3375807081572289</v>
+        <v>0.2229940666134111</v>
       </c>
       <c r="P555" t="n">
-        <v>0.3114246541767539</v>
+        <v>0.2956775239646158</v>
       </c>
       <c r="Q555" t="n">
-        <v>0.3509946376660172</v>
+        <v>0.4813284094219731</v>
       </c>
       <c r="R555" t="n">
         <v>1</v>
       </c>
       <c r="S555" t="n">
-        <v>-0.001428269822969563</v>
+        <v>0.07130836934181273</v>
       </c>
       <c r="T555" t="n">
         <v>2</v>
       </c>
       <c r="U555" t="n">
-        <v>-0.001428269822969563</v>
+        <v>0.07130836934181273</v>
       </c>
       <c r="V555" t="n">
-        <v>0.3509946376660172</v>
+        <v>0.4813284094219731</v>
       </c>
       <c r="W555" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="X555" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y555" t="inlineStr"/>
       <c r="Z555" t="n">
-        <v>3.509946376660172</v>
+        <v>6.016605117774663</v>
       </c>
       <c r="AA555" t="inlineStr">
         <is>
@@ -56075,20 +56075,20 @@
     <row r="556">
       <c r="A556" s="1" t="inlineStr">
         <is>
-          <t>vVwOqx6D</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B556" s="2" t="n">
-        <v>45619.51041666666</v>
+        <v>45606.60416666666</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E556" t="n">
@@ -56098,64 +56098,64 @@
         <v>1481</v>
       </c>
       <c r="G556" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="H556" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="I556" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="J556" t="n">
-        <v>0.6849315068493151</v>
+        <v>0.449677174325864</v>
       </c>
       <c r="K556" t="n">
-        <v>0.2100456621004566</v>
+        <v>0.2951006456513482</v>
       </c>
       <c r="L556" t="n">
-        <v>0.1050228310502283</v>
+        <v>0.2552221800227877</v>
       </c>
       <c r="M556" t="n">
-        <v>0.05797101449275366</v>
+        <v>0.05896074646074645</v>
       </c>
       <c r="N556" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O556" t="n">
-        <v>0.5819079639761686</v>
+        <v>0.2271588222031189</v>
       </c>
       <c r="P556" t="n">
-        <v>0.3113331289129357</v>
+        <v>0.3932950285981397</v>
       </c>
       <c r="Q556" t="n">
-        <v>0.1067589071108957</v>
+        <v>0.3795461491987414</v>
       </c>
       <c r="R556" t="n">
         <v>1</v>
       </c>
       <c r="S556" t="n">
-        <v>-0.1030235428731465</v>
+        <v>0.09819438294679145</v>
       </c>
       <c r="T556" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U556" t="n">
-        <v>-0.1030235428731465</v>
+        <v>0.09819438294679145</v>
       </c>
       <c r="V556" t="n">
-        <v>0.5819079639761686</v>
+        <v>0.3932950285981397</v>
       </c>
       <c r="W556" t="n">
-        <v>1.38</v>
+        <v>3.2</v>
       </c>
       <c r="X556" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y556" t="inlineStr"/>
       <c r="Z556" t="n">
-        <v>5.819079639761686</v>
+        <v>4.916187857476746</v>
       </c>
       <c r="AA556" t="inlineStr">
         <is>
@@ -56174,20 +56174,20 @@
     <row r="557">
       <c r="A557" s="1" t="inlineStr">
         <is>
-          <t>buKPeYL5</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B557" s="2" t="n">
-        <v>45619.60416666666</v>
+        <v>45606.60416666666</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="E557" t="n">
@@ -56197,64 +56197,64 @@
         <v>1481</v>
       </c>
       <c r="G557" t="n">
-        <v>1.67</v>
+        <v>4.33</v>
       </c>
       <c r="H557" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="I557" t="n">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="J557" t="n">
-        <v>0.5709391949757351</v>
+        <v>0.2183817644470468</v>
       </c>
       <c r="K557" t="n">
-        <v>0.2383671139023694</v>
+        <v>0.2865433454714282</v>
       </c>
       <c r="L557" t="n">
-        <v>0.1906936911218955</v>
+        <v>0.4950748900815251</v>
       </c>
       <c r="M557" t="n">
-        <v>0.04880239520958085</v>
+        <v>0.05753739467147678</v>
       </c>
       <c r="N557" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O557" t="n">
-        <v>0.5913279285595855</v>
+        <v>0.1793070603139877</v>
       </c>
       <c r="P557" t="n">
-        <v>0.2967899811784423</v>
+        <v>0.2586315208420592</v>
       </c>
       <c r="Q557" t="n">
-        <v>0.1118820902619721</v>
+        <v>0.562061418843953</v>
       </c>
       <c r="R557" t="n">
         <v>1</v>
       </c>
       <c r="S557" t="n">
-        <v>0.0203887335838504</v>
+        <v>0.06698652876242794</v>
       </c>
       <c r="T557" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U557" t="n">
-        <v>0.0203887335838504</v>
+        <v>0.06698652876242794</v>
       </c>
       <c r="V557" t="n">
-        <v>0.5913279285595855</v>
+        <v>0.562061418843953</v>
       </c>
       <c r="W557" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="X557" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y557" t="inlineStr"/>
       <c r="Z557" t="n">
-        <v>5.913279285595855</v>
+        <v>7.025767735549413</v>
       </c>
       <c r="AA557" t="inlineStr">
         <is>
@@ -56273,20 +56273,20 @@
     <row r="558">
       <c r="A558" s="1" t="inlineStr">
         <is>
-          <t>IsCnpo0d</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B558" s="2" t="n">
-        <v>45619.60416666666</v>
+        <v>45606.70833333334</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E558" t="n">
@@ -56296,64 +56296,64 @@
         <v>1481</v>
       </c>
       <c r="G558" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H558" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="I558" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="J558" t="n">
-        <v>0.3351544442109687</v>
+        <v>0.2354124748490946</v>
       </c>
       <c r="K558" t="n">
-        <v>0.3235973944105905</v>
+        <v>0.2414486921529175</v>
       </c>
       <c r="L558" t="n">
-        <v>0.3412481613784409</v>
+        <v>0.5231388329979879</v>
       </c>
       <c r="M558" t="n">
-        <v>0.06560680698611732</v>
+        <v>0.06196581196581197</v>
       </c>
       <c r="N558" t="n">
         <v>2</v>
       </c>
       <c r="O558" t="n">
-        <v>0.2444187323844127</v>
+        <v>0.1123262670565472</v>
       </c>
       <c r="P558" t="n">
-        <v>0.325586583467244</v>
+        <v>0.2792080595552685</v>
       </c>
       <c r="Q558" t="n">
-        <v>0.4299946841483434</v>
+        <v>0.6084656733881844</v>
       </c>
       <c r="R558" t="n">
         <v>1</v>
       </c>
       <c r="S558" t="n">
-        <v>0.08874652276990247</v>
+        <v>0.08532684039019645</v>
       </c>
       <c r="T558" t="n">
         <v>2</v>
       </c>
       <c r="U558" t="n">
-        <v>0.08874652276990247</v>
+        <v>0.08532684039019645</v>
       </c>
       <c r="V558" t="n">
-        <v>0.4299946841483434</v>
+        <v>0.6084656733881844</v>
       </c>
       <c r="W558" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="X558" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y558" t="inlineStr"/>
       <c r="Z558" t="n">
-        <v>4.299946841483433</v>
+        <v>7.605820917352305</v>
       </c>
       <c r="AA558" t="inlineStr">
         <is>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -62253,43 +62253,43 @@
         <v>0.05958670893507123</v>
       </c>
       <c r="N620" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O620" t="n">
-        <v>0.7184902928921869</v>
+        <v>0.4380788505077362</v>
       </c>
       <c r="P620" t="n">
-        <v>0.2034047392590317</v>
+        <v>0.487432450056076</v>
       </c>
       <c r="Q620" t="n">
-        <v>0.07810496784878133</v>
+        <v>0.07448867708444595</v>
       </c>
       <c r="R620" t="n">
         <v>1</v>
       </c>
       <c r="S620" t="n">
-        <v>0.1533620309386161</v>
+        <v>0.2098547449200575</v>
       </c>
       <c r="T620" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U620" t="n">
-        <v>0.1533620309386161</v>
+        <v>0.2098547449200575</v>
       </c>
       <c r="V620" t="n">
-        <v>0.7184902928921869</v>
+        <v>0.487432450056076</v>
       </c>
       <c r="W620" t="n">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="X620" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y620" t="inlineStr"/>
       <c r="Z620" t="n">
-        <v>12.57358012561327</v>
+        <v>8.530067875981331</v>
       </c>
       <c r="AA620" t="inlineStr">
         <is>
@@ -62355,40 +62355,40 @@
         <v>0</v>
       </c>
       <c r="O621" t="n">
-        <v>0.06510227056649795</v>
+        <v>0.3059642314910889</v>
       </c>
       <c r="P621" t="n">
-        <v>0.5041676322345764</v>
+        <v>0.4625942409038544</v>
       </c>
       <c r="Q621" t="n">
-        <v>0.4307300971989256</v>
+        <v>0.2314416021108627</v>
       </c>
       <c r="R621" t="n">
         <v>1</v>
       </c>
       <c r="S621" t="n">
-        <v>0.1884853511755133</v>
+        <v>0.1469119598447913</v>
       </c>
       <c r="T621" t="n">
         <v>0</v>
       </c>
       <c r="U621" t="n">
-        <v>0.1884853511755133</v>
+        <v>0.1469119598447913</v>
       </c>
       <c r="V621" t="n">
-        <v>0.5041676322345764</v>
+        <v>0.4625942409038544</v>
       </c>
       <c r="W621" t="n">
         <v>3</v>
       </c>
       <c r="X621" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y621" t="inlineStr"/>
       <c r="Z621" t="n">
-        <v>8.822933564105087</v>
+        <v>8.095399215817451</v>
       </c>
       <c r="AA621" t="inlineStr">
         <is>
@@ -62456,40 +62456,40 @@
         <v>1</v>
       </c>
       <c r="O622" t="n">
-        <v>0.7619521193300006</v>
+        <v>0.8815600275993347</v>
       </c>
       <c r="P622" t="n">
-        <v>0.1918999227194019</v>
+        <v>0.09728441387414932</v>
       </c>
       <c r="Q622" t="n">
-        <v>0.04614795795059752</v>
+        <v>0.02115556225180626</v>
       </c>
       <c r="R622" t="n">
         <v>1</v>
       </c>
       <c r="S622" t="n">
-        <v>0.08122601148162889</v>
+        <v>0.200833919750963</v>
       </c>
       <c r="T622" t="n">
         <v>1</v>
       </c>
       <c r="U622" t="n">
-        <v>0.08122601148162889</v>
+        <v>0.200833919750963</v>
       </c>
       <c r="V622" t="n">
-        <v>0.7619521193300006</v>
+        <v>0.8815600275993347</v>
       </c>
       <c r="W622" t="n">
         <v>1.38</v>
       </c>
       <c r="X622" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y622" t="inlineStr"/>
       <c r="Z622" t="n">
-        <v>13.33416208827501</v>
+        <v>15.42730048298836</v>
       </c>
       <c r="AA622" t="inlineStr">
         <is>
@@ -62555,40 +62555,40 @@
         <v>1</v>
       </c>
       <c r="O623" t="n">
-        <v>0.4651637178206616</v>
+        <v>0.4232662916183472</v>
       </c>
       <c r="P623" t="n">
-        <v>0.3021492415741182</v>
+        <v>0.1972329318523407</v>
       </c>
       <c r="Q623" t="n">
-        <v>0.2326870406052202</v>
+        <v>0.3795007765293121</v>
       </c>
       <c r="R623" t="n">
         <v>1</v>
       </c>
       <c r="S623" t="n">
-        <v>-0.1104213549181113</v>
+        <v>-0.1523187811204257</v>
       </c>
       <c r="T623" t="n">
         <v>1</v>
       </c>
       <c r="U623" t="n">
-        <v>-0.1104213549181113</v>
+        <v>-0.1523187811204257</v>
       </c>
       <c r="V623" t="n">
-        <v>0.4651637178206616</v>
+        <v>0.4232662916183472</v>
       </c>
       <c r="W623" t="n">
         <v>1.65</v>
       </c>
       <c r="X623" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y623" t="inlineStr"/>
       <c r="Z623" t="n">
-        <v>0.4108702175937888</v>
+        <v>2.076002764106175</v>
       </c>
       <c r="AA623" t="inlineStr">
         <is>
@@ -62653,43 +62653,43 @@
         <v>0.06277630415561442</v>
       </c>
       <c r="N624" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O624" t="n">
-        <v>0.1317361903191667</v>
+        <v>0.2766321897506714</v>
       </c>
       <c r="P624" t="n">
-        <v>0.3171854353409633</v>
+        <v>0.4907961785793304</v>
       </c>
       <c r="Q624" t="n">
-        <v>0.5510783743398699</v>
+        <v>0.2325715571641922</v>
       </c>
       <c r="R624" t="n">
         <v>1</v>
       </c>
       <c r="S624" t="n">
-        <v>0.1891815357375405</v>
+        <v>0.1663369439703454</v>
       </c>
       <c r="T624" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U624" t="n">
-        <v>0.1891815357375405</v>
+        <v>0.1663369439703454</v>
       </c>
       <c r="V624" t="n">
-        <v>0.5510783743398699</v>
+        <v>0.4907961785793304</v>
       </c>
       <c r="W624" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="X624" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y624" t="inlineStr"/>
       <c r="Z624" t="n">
-        <v>9.643871550947724</v>
+        <v>8.588933125138283</v>
       </c>
       <c r="AA624" t="inlineStr">
         <is>
@@ -62755,40 +62755,40 @@
         <v>2</v>
       </c>
       <c r="O625" t="n">
-        <v>0.03682417779639348</v>
+        <v>0.04302779212594032</v>
       </c>
       <c r="P625" t="n">
-        <v>0.07686330039214101</v>
+        <v>0.08403868973255157</v>
       </c>
       <c r="Q625" t="n">
-        <v>0.8863125218114655</v>
+        <v>0.8729335069656372</v>
       </c>
       <c r="R625" t="n">
         <v>1</v>
       </c>
       <c r="S625" t="n">
-        <v>0.3380096497488022</v>
+        <v>0.3246306349029739</v>
       </c>
       <c r="T625" t="n">
         <v>2</v>
       </c>
       <c r="U625" t="n">
-        <v>0.3380096497488022</v>
+        <v>0.3246306349029739</v>
       </c>
       <c r="V625" t="n">
-        <v>0.8863125218114655</v>
+        <v>0.8729335069656372</v>
       </c>
       <c r="W625" t="n">
         <v>1.73</v>
       </c>
       <c r="X625" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y625" t="inlineStr"/>
       <c r="Z625" t="n">
-        <v>15.51046913170065</v>
+        <v>15.27633637189865</v>
       </c>
       <c r="AA625" t="inlineStr">
         <is>
@@ -62854,40 +62854,40 @@
         <v>2</v>
       </c>
       <c r="O626" t="n">
-        <v>0.08865098957765606</v>
+        <v>0.2263692766427994</v>
       </c>
       <c r="P626" t="n">
-        <v>0.3173732192583593</v>
+        <v>0.2608787417411804</v>
       </c>
       <c r="Q626" t="n">
-        <v>0.5939757911639847</v>
+        <v>0.5127519965171814</v>
       </c>
       <c r="R626" t="n">
         <v>1</v>
       </c>
       <c r="S626" t="n">
-        <v>0.2110537065934923</v>
+        <v>0.129829911946689</v>
       </c>
       <c r="T626" t="n">
         <v>2</v>
       </c>
       <c r="U626" t="n">
-        <v>0.2110537065934923</v>
+        <v>0.129829911946689</v>
       </c>
       <c r="V626" t="n">
-        <v>0.5939757911639847</v>
+        <v>0.5127519965171814</v>
       </c>
       <c r="W626" t="n">
         <v>2.45</v>
       </c>
       <c r="X626" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y626" t="inlineStr"/>
       <c r="Z626" t="n">
-        <v>10.39457634536973</v>
+        <v>8.973159939050674</v>
       </c>
       <c r="AA626" t="inlineStr">
         <is>
@@ -62953,40 +62953,40 @@
         <v>0</v>
       </c>
       <c r="O627" t="n">
-        <v>0.3090568887998504</v>
+        <v>0.2207784503698349</v>
       </c>
       <c r="P627" t="n">
-        <v>0.4106878150893326</v>
+        <v>0.5502509474754333</v>
       </c>
       <c r="Q627" t="n">
-        <v>0.280255296110817</v>
+        <v>0.2289706021547318</v>
       </c>
       <c r="R627" t="n">
         <v>1</v>
       </c>
       <c r="S627" t="n">
-        <v>0.09688364173459746</v>
+        <v>0.2364467741206983</v>
       </c>
       <c r="T627" t="n">
         <v>0</v>
       </c>
       <c r="U627" t="n">
-        <v>0.09688364173459746</v>
+        <v>0.2364467741206983</v>
       </c>
       <c r="V627" t="n">
-        <v>0.4106878150893326</v>
+        <v>0.5502509474754333</v>
       </c>
       <c r="W627" t="n">
         <v>3</v>
       </c>
       <c r="X627" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y627" t="inlineStr"/>
       <c r="Z627" t="n">
-        <v>7.187036764063319</v>
+        <v>9.629391580820084</v>
       </c>
       <c r="AA627" t="inlineStr">
         <is>
@@ -63054,40 +63054,40 @@
         <v>2</v>
       </c>
       <c r="O628" t="n">
-        <v>0.004314461375559076</v>
+        <v>0.07501446455717087</v>
       </c>
       <c r="P628" t="n">
-        <v>0.01836210622104234</v>
+        <v>0.0668170303106308</v>
       </c>
       <c r="Q628" t="n">
-        <v>0.9773234324033986</v>
+        <v>0.8581684827804565</v>
       </c>
       <c r="R628" t="n">
         <v>1</v>
       </c>
       <c r="S628" t="n">
-        <v>0.3234573192741822</v>
+        <v>0.2043023696512402</v>
       </c>
       <c r="T628" t="n">
         <v>2</v>
       </c>
       <c r="U628" t="n">
-        <v>0.3234573192741822</v>
+        <v>0.2043023696512402</v>
       </c>
       <c r="V628" t="n">
-        <v>0.9773234324033986</v>
+        <v>0.8581684827804565</v>
       </c>
       <c r="W628" t="n">
         <v>1.45</v>
       </c>
       <c r="X628" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y628" t="inlineStr"/>
       <c r="Z628" t="n">
-        <v>17.10316006705948</v>
+        <v>15.01794844865799</v>
       </c>
       <c r="AA628" t="inlineStr">
         <is>
@@ -63150,43 +63150,43 @@
         <v>0.06565656565656575</v>
       </c>
       <c r="N629" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O629" t="n">
-        <v>0.4424752725230887</v>
+        <v>0.3437532186508179</v>
       </c>
       <c r="P629" t="n">
-        <v>0.2448774174274614</v>
+        <v>0.1945755779743195</v>
       </c>
       <c r="Q629" t="n">
-        <v>0.31264731004945</v>
+        <v>0.4616712033748627</v>
       </c>
       <c r="R629" t="n">
         <v>1</v>
       </c>
       <c r="S629" t="n">
-        <v>0.01593498816289918</v>
+        <v>0.201007696265858</v>
       </c>
       <c r="T629" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U629" t="n">
-        <v>0.01593498816289918</v>
+        <v>0.201007696265858</v>
       </c>
       <c r="V629" t="n">
-        <v>0.4424752725230887</v>
+        <v>0.4616712033748627</v>
       </c>
       <c r="W629" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="X629" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y629" t="inlineStr"/>
       <c r="Z629" t="n">
-        <v>7.743317269154052</v>
+        <v>8.079246059060097</v>
       </c>
       <c r="AA629" t="inlineStr">
         <is>
@@ -63252,40 +63252,40 @@
         <v>1</v>
       </c>
       <c r="O630" t="n">
-        <v>0.5694948776563049</v>
+        <v>0.5841125249862671</v>
       </c>
       <c r="P630" t="n">
-        <v>0.2014548824272862</v>
+        <v>0.2444181740283966</v>
       </c>
       <c r="Q630" t="n">
-        <v>0.2290502399164089</v>
+        <v>0.1714693456888199</v>
       </c>
       <c r="R630" t="n">
         <v>1</v>
       </c>
       <c r="S630" t="n">
-        <v>0.07528075624943209</v>
+        <v>0.08989840357939427</v>
       </c>
       <c r="T630" t="n">
         <v>1</v>
       </c>
       <c r="U630" t="n">
-        <v>0.07528075624943209</v>
+        <v>0.08989840357939427</v>
       </c>
       <c r="V630" t="n">
-        <v>0.5694948776563049</v>
+        <v>0.5841125249862671</v>
       </c>
       <c r="W630" t="n">
         <v>1.9</v>
       </c>
       <c r="X630" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y630" t="inlineStr"/>
       <c r="Z630" t="n">
-        <v>9.966160358985336</v>
+        <v>10.22196918725967</v>
       </c>
       <c r="AA630" t="inlineStr">
         <is>
@@ -63351,40 +63351,40 @@
         <v>1</v>
       </c>
       <c r="O631" t="n">
-        <v>0.951221279460578</v>
+        <v>0.6555708050727844</v>
       </c>
       <c r="P631" t="n">
-        <v>0.04302405013321797</v>
+        <v>0.2326910942792892</v>
       </c>
       <c r="Q631" t="n">
-        <v>0.005754670406204023</v>
+        <v>0.1117381155490875</v>
       </c>
       <c r="R631" t="n">
         <v>1</v>
       </c>
       <c r="S631" t="n">
-        <v>0.2029959165393015</v>
+        <v>-0.09265455784849208</v>
       </c>
       <c r="T631" t="n">
         <v>1</v>
       </c>
       <c r="U631" t="n">
-        <v>0.2029959165393015</v>
+        <v>-0.09265455784849208</v>
       </c>
       <c r="V631" t="n">
-        <v>0.951221279460578</v>
+        <v>0.6555708050727844</v>
       </c>
       <c r="W631" t="n">
         <v>1.27</v>
       </c>
       <c r="X631" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y631" t="inlineStr"/>
       <c r="Z631" t="n">
-        <v>16.64637239056011</v>
+        <v>8.229579564076504</v>
       </c>
       <c r="AA631" t="inlineStr">
         <is>
@@ -63450,40 +63450,40 @@
         <v>1</v>
       </c>
       <c r="O632" t="n">
-        <v>0.4721386647460002</v>
+        <v>0.5136918425559998</v>
       </c>
       <c r="P632" t="n">
-        <v>0.2222211274056271</v>
+        <v>0.2290997058153152</v>
       </c>
       <c r="Q632" t="n">
-        <v>0.3056402078483726</v>
+        <v>0.2572084963321686</v>
       </c>
       <c r="R632" t="n">
         <v>1</v>
       </c>
       <c r="S632" t="n">
-        <v>-0.03843755698995899</v>
+        <v>0.003115620820040577</v>
       </c>
       <c r="T632" t="n">
         <v>1</v>
       </c>
       <c r="U632" t="n">
-        <v>-0.03843755698995899</v>
+        <v>0.003115620820040577</v>
       </c>
       <c r="V632" t="n">
-        <v>0.4721386647460002</v>
+        <v>0.5136918425559998</v>
       </c>
       <c r="W632" t="n">
         <v>1.83</v>
       </c>
       <c r="X632" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y632" t="inlineStr"/>
       <c r="Z632" t="n">
-        <v>5.571797643757874</v>
+        <v>8.989607244729996</v>
       </c>
       <c r="AA632" t="inlineStr">
         <is>
@@ -63549,40 +63549,40 @@
         <v>0</v>
       </c>
       <c r="O633" t="n">
-        <v>0.278567760480365</v>
+        <v>0.2504731118679047</v>
       </c>
       <c r="P633" t="n">
-        <v>0.4390872220153065</v>
+        <v>0.4024161696434021</v>
       </c>
       <c r="Q633" t="n">
-        <v>0.2823450175043283</v>
+        <v>0.3471106588840485</v>
       </c>
       <c r="R633" t="n">
         <v>1</v>
       </c>
       <c r="S633" t="n">
-        <v>0.1537198874676441</v>
+        <v>0.1170488350957397</v>
       </c>
       <c r="T633" t="n">
         <v>0</v>
       </c>
       <c r="U633" t="n">
-        <v>0.1537198874676441</v>
+        <v>0.1170488350957397</v>
       </c>
       <c r="V633" t="n">
-        <v>0.4390872220153065</v>
+        <v>0.4024161696434021</v>
       </c>
       <c r="W633" t="n">
         <v>3.3</v>
       </c>
       <c r="X633" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y633" t="inlineStr"/>
       <c r="Z633" t="n">
-        <v>7.684026385267864</v>
+        <v>7.042282968759537</v>
       </c>
       <c r="AA633" t="inlineStr">
         <is>
@@ -63650,40 +63650,40 @@
         <v>2</v>
       </c>
       <c r="O634" t="n">
-        <v>0.01731246134187259</v>
+        <v>0.2667881846427917</v>
       </c>
       <c r="P634" t="n">
-        <v>0.2238994226737401</v>
+        <v>0.06890491396188736</v>
       </c>
       <c r="Q634" t="n">
-        <v>0.7587881159843872</v>
+        <v>0.6643068790435791</v>
       </c>
       <c r="R634" t="n">
         <v>1</v>
       </c>
       <c r="S634" t="n">
-        <v>0.2225105134607279</v>
+        <v>0.1280292765199198</v>
       </c>
       <c r="T634" t="n">
         <v>2</v>
       </c>
       <c r="U634" t="n">
-        <v>0.2225105134607279</v>
+        <v>0.1280292765199198</v>
       </c>
       <c r="V634" t="n">
-        <v>0.7587881159843872</v>
+        <v>0.6643068790435791</v>
       </c>
       <c r="W634" t="n">
         <v>1.75</v>
       </c>
       <c r="X634" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y634" t="inlineStr"/>
       <c r="Z634" t="n">
-        <v>13.27879202972678</v>
+        <v>11.62537038326263</v>
       </c>
       <c r="AA634" t="inlineStr">
         <is>
@@ -63746,43 +63746,43 @@
         <v>0.06633877564817636</v>
       </c>
       <c r="N635" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O635" t="n">
-        <v>0.4026825348140227</v>
+        <v>0.1618411689996719</v>
       </c>
       <c r="P635" t="n">
-        <v>0.4010809930803445</v>
+        <v>0.6041640639305115</v>
       </c>
       <c r="Q635" t="n">
-        <v>0.1962364721056327</v>
+        <v>0.233994796872139</v>
       </c>
       <c r="R635" t="n">
         <v>1</v>
       </c>
       <c r="S635" t="n">
-        <v>-0.1393916120532008</v>
+        <v>0.343667321130429</v>
       </c>
       <c r="T635" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U635" t="n">
-        <v>-0.1393916120532008</v>
+        <v>0.343667321130429</v>
       </c>
       <c r="V635" t="n">
-        <v>0.4026825348140227</v>
+        <v>0.6041640639305115</v>
       </c>
       <c r="W635" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="X635" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y635" t="inlineStr"/>
       <c r="Z635" t="n">
-        <v>0</v>
+        <v>10.57287111878395</v>
       </c>
       <c r="AA635" t="inlineStr">
         <is>
@@ -63848,40 +63848,40 @@
         <v>1</v>
       </c>
       <c r="O636" t="n">
-        <v>0.7745913844514704</v>
+        <v>0.6979084014892578</v>
       </c>
       <c r="P636" t="n">
-        <v>0.2172895827385753</v>
+        <v>0.2521724700927734</v>
       </c>
       <c r="Q636" t="n">
-        <v>0.008119032809954187</v>
+        <v>0.04991911724209785</v>
       </c>
       <c r="R636" t="n">
         <v>1</v>
       </c>
       <c r="S636" t="n">
-        <v>0.1037505973316135</v>
+        <v>0.02706761436940097</v>
       </c>
       <c r="T636" t="n">
         <v>1</v>
       </c>
       <c r="U636" t="n">
-        <v>0.1037505973316135</v>
+        <v>0.02706761436940097</v>
       </c>
       <c r="V636" t="n">
-        <v>0.7745913844514704</v>
+        <v>0.6979084014892578</v>
       </c>
       <c r="W636" t="n">
         <v>1.4</v>
       </c>
       <c r="X636" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y636" t="inlineStr"/>
       <c r="Z636" t="n">
-        <v>13.55534922790073</v>
+        <v>12.21339702606201</v>
       </c>
       <c r="AA636" t="inlineStr">
         <is>
@@ -63947,40 +63947,40 @@
         <v>2</v>
       </c>
       <c r="O637" t="n">
-        <v>0.26709617836359</v>
+        <v>0.2134273052215576</v>
       </c>
       <c r="P637" t="n">
-        <v>0.2749479399344654</v>
+        <v>0.1886194497346878</v>
       </c>
       <c r="Q637" t="n">
-        <v>0.4579558817019445</v>
+        <v>0.597953200340271</v>
       </c>
       <c r="R637" t="n">
         <v>1</v>
       </c>
       <c r="S637" t="n">
-        <v>0.1151458281378737</v>
+        <v>0.2551431467762001</v>
       </c>
       <c r="T637" t="n">
         <v>2</v>
       </c>
       <c r="U637" t="n">
-        <v>0.1151458281378737</v>
+        <v>0.2551431467762001</v>
       </c>
       <c r="V637" t="n">
-        <v>0.4579558817019445</v>
+        <v>0.597953200340271</v>
       </c>
       <c r="W637" t="n">
         <v>2.75</v>
       </c>
       <c r="X637" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y637" t="inlineStr"/>
       <c r="Z637" t="n">
-        <v>8.014227929784029</v>
+        <v>10.46418100595474</v>
       </c>
       <c r="AA637" t="inlineStr">
         <is>
@@ -64046,40 +64046,40 @@
         <v>0</v>
       </c>
       <c r="O638" t="n">
-        <v>0.3015195750249093</v>
+        <v>0.3529403209686279</v>
       </c>
       <c r="P638" t="n">
-        <v>0.4061404499255671</v>
+        <v>0.4221764802932739</v>
       </c>
       <c r="Q638" t="n">
-        <v>0.2923399750495236</v>
+        <v>0.2248831689357758</v>
       </c>
       <c r="R638" t="n">
         <v>1</v>
       </c>
       <c r="S638" t="n">
-        <v>0.1388192198403503</v>
+        <v>0.1548552502080572</v>
       </c>
       <c r="T638" t="n">
         <v>0</v>
       </c>
       <c r="U638" t="n">
-        <v>0.1388192198403503</v>
+        <v>0.1548552502080572</v>
       </c>
       <c r="V638" t="n">
-        <v>0.4061404499255671</v>
+        <v>0.4221764802932739</v>
       </c>
       <c r="W638" t="n">
         <v>3.5</v>
       </c>
       <c r="X638" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y638" t="inlineStr"/>
       <c r="Z638" t="n">
-        <v>7.107457873697424</v>
+        <v>7.388088405132294</v>
       </c>
       <c r="AA638" t="inlineStr">
         <is>
@@ -64147,40 +64147,40 @@
         <v>1</v>
       </c>
       <c r="O639" t="n">
-        <v>0.5894690908832416</v>
+        <v>0.4925592541694641</v>
       </c>
       <c r="P639" t="n">
-        <v>0.2590308906176526</v>
+        <v>0.3403346836566925</v>
       </c>
       <c r="Q639" t="n">
-        <v>0.1515000184991058</v>
+        <v>0.1671060621738434</v>
       </c>
       <c r="R639" t="n">
         <v>1</v>
       </c>
       <c r="S639" t="n">
-        <v>0.2038330592338198</v>
+        <v>0.1069232225200423</v>
       </c>
       <c r="T639" t="n">
         <v>1</v>
       </c>
       <c r="U639" t="n">
-        <v>0.2038330592338198</v>
+        <v>0.1069232225200423</v>
       </c>
       <c r="V639" t="n">
-        <v>0.5894690908832416</v>
+        <v>0.4925592541694641</v>
       </c>
       <c r="W639" t="n">
         <v>2.45</v>
       </c>
       <c r="X639" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y639" t="inlineStr"/>
       <c r="Z639" t="n">
-        <v>10.31570909045673</v>
+        <v>8.619786947965622</v>
       </c>
       <c r="AA639" t="inlineStr">
         <is>
@@ -64234,13 +64234,13 @@
         <v>2</v>
       </c>
       <c r="O640" t="n">
-        <v>0.04759327094221052</v>
+        <v>0.2457361966371536</v>
       </c>
       <c r="P640" t="n">
-        <v>0.1400388062730517</v>
+        <v>0.2980333566665649</v>
       </c>
       <c r="Q640" t="n">
-        <v>0.8123679227847378</v>
+        <v>0.4562304019927979</v>
       </c>
       <c r="R640" t="n">
         <v>1</v>
@@ -64251,12 +64251,12 @@
       </c>
       <c r="U640" t="inlineStr"/>
       <c r="V640" t="n">
-        <v>0.1876320772152622</v>
+        <v>0.5437695980072021</v>
       </c>
       <c r="W640" t="inlineStr"/>
       <c r="X640" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y640" t="inlineStr"/>
@@ -64311,13 +64311,13 @@
         <v>2</v>
       </c>
       <c r="O641" t="n">
-        <v>0.03427928789846806</v>
+        <v>0.04795290529727936</v>
       </c>
       <c r="P641" t="n">
-        <v>0.07558148975112403</v>
+        <v>0.05862414836883545</v>
       </c>
       <c r="Q641" t="n">
-        <v>0.890139222350408</v>
+        <v>0.8934229612350464</v>
       </c>
       <c r="R641" t="n">
         <v>1</v>
@@ -64328,12 +64328,12 @@
       </c>
       <c r="U641" t="inlineStr"/>
       <c r="V641" t="n">
-        <v>0.109860777649592</v>
+        <v>0.1065770387649536</v>
       </c>
       <c r="W641" t="inlineStr"/>
       <c r="X641" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y641" t="inlineStr"/>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -61474,197 +61474,195 @@
     <row r="613">
       <c r="A613" s="1" t="inlineStr">
         <is>
-          <t>EuQnZBVQ</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B613" s="2" t="n">
-        <v>45618.6875</v>
+        <v>45619.45833333334</v>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="E613" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F613" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G613" t="n">
-        <v>1.13</v>
+        <v>7</v>
       </c>
       <c r="H613" t="n">
-        <v>10</v>
+        <v>5.25</v>
       </c>
       <c r="I613" t="n">
-        <v>15</v>
+        <v>1.38</v>
       </c>
       <c r="J613" t="n">
-        <v>0.8415147265077139</v>
+        <v>0.1350293542074364</v>
       </c>
       <c r="K613" t="n">
-        <v>0.09509116409537166</v>
+        <v>0.1800391389432485</v>
       </c>
       <c r="L613" t="n">
-        <v>0.06339410939691444</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="M613" t="n">
-        <v>0.05162241887905616</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="N613" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O613" t="n">
-        <v>0.6659861207008362</v>
+        <v>0.07605352458246978</v>
       </c>
       <c r="P613" t="n">
-        <v>0.1339152902364731</v>
+        <v>0.2423606517662135</v>
       </c>
       <c r="Q613" t="n">
-        <v>0.2000985443592072</v>
+        <v>0.6815858236513167</v>
       </c>
       <c r="R613" t="n">
         <v>1</v>
       </c>
       <c r="S613" t="n">
-        <v>-0.1755286058068777</v>
+        <v>-0.003345683197998439</v>
       </c>
       <c r="T613" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U613" t="n">
-        <v>-0.1755286058068777</v>
+        <v>-0.003345683197998439</v>
       </c>
       <c r="V613" t="n">
-        <v>0.6659861207008362</v>
+        <v>0.6815858236513167</v>
       </c>
       <c r="W613" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="X613" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y613" t="inlineStr"/>
       <c r="Z613" t="n">
-        <v>0</v>
+        <v>11.69355409003815</v>
       </c>
       <c r="AA613" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB613" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="AC613" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC613" t="inlineStr"/>
       <c r="AD613" t="inlineStr"/>
       <c r="AE613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="1" t="inlineStr">
         <is>
-          <t>2qNaDU87</t>
+          <t>z7KrCz8T</t>
         </is>
       </c>
       <c r="B614" s="2" t="n">
-        <v>45619.47916666666</v>
+        <v>45619.58333333334</v>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F614" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G614" t="n">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="H614" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="I614" t="n">
-        <v>15</v>
+        <v>3.5</v>
       </c>
       <c r="J614" t="n">
-        <v>0.7907542579075426</v>
+        <v>0.4413450515857852</v>
       </c>
       <c r="K614" t="n">
-        <v>0.145985401459854</v>
+        <v>0.2875429881543752</v>
       </c>
       <c r="L614" t="n">
-        <v>0.0632603406326034</v>
+        <v>0.2711119602598395</v>
       </c>
       <c r="M614" t="n">
-        <v>0.05384615384615388</v>
+        <v>0.05386086781435617</v>
       </c>
       <c r="N614" t="n">
         <v>1</v>
       </c>
       <c r="O614" t="n">
-        <v>0.8486636281013489</v>
+        <v>0.35669835414836</v>
       </c>
       <c r="P614" t="n">
-        <v>0.1071945801377296</v>
+        <v>0.3483631099687277</v>
       </c>
       <c r="Q614" t="n">
-        <v>0.04414178058505058</v>
+        <v>0.2949385358829122</v>
       </c>
       <c r="R614" t="n">
         <v>1</v>
       </c>
       <c r="S614" t="n">
-        <v>0.05790937019380626</v>
+        <v>-0.0846466974374252</v>
       </c>
       <c r="T614" t="n">
         <v>1</v>
       </c>
       <c r="U614" t="n">
-        <v>0.05790937019380626</v>
+        <v>-0.0846466974374252</v>
       </c>
       <c r="V614" t="n">
-        <v>0.8486636281013489</v>
+        <v>0.35669835414836</v>
       </c>
       <c r="W614" t="n">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="X614" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y614" t="inlineStr"/>
       <c r="Z614" t="n">
-        <v>5.940645396709442</v>
+        <v>0.3169523769765367</v>
       </c>
       <c r="AA614" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB614" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC614" t="inlineStr"/>
@@ -61674,96 +61672,96 @@
     <row r="615">
       <c r="A615" s="1" t="inlineStr">
         <is>
-          <t>pOGITkgl</t>
+          <t>Qyq1UHNc</t>
         </is>
       </c>
       <c r="B615" s="2" t="n">
-        <v>45619.47916666666</v>
+        <v>45619.69791666666</v>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E615" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F615" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G615" t="n">
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="H615" t="n">
         <v>4.2</v>
       </c>
       <c r="I615" t="n">
-        <v>4.75</v>
+        <v>1.62</v>
       </c>
       <c r="J615" t="n">
-        <v>0.5716905706876048</v>
+        <v>0.1895053475935829</v>
       </c>
       <c r="K615" t="n">
-        <v>0.2273150602495952</v>
+        <v>0.2256016042780749</v>
       </c>
       <c r="L615" t="n">
-        <v>0.2009943690628</v>
+        <v>0.5848930481283423</v>
       </c>
       <c r="M615" t="n">
-        <v>0.04742394909429271</v>
+        <v>0.0553791887125219</v>
       </c>
       <c r="N615" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O615" t="n">
-        <v>0.7468887567520142</v>
+        <v>0.1777861207576573</v>
       </c>
       <c r="P615" t="n">
-        <v>0.1249512881040573</v>
+        <v>0.2673919524648737</v>
       </c>
       <c r="Q615" t="n">
-        <v>0.1281599253416061</v>
+        <v>0.554821926777469</v>
       </c>
       <c r="R615" t="n">
         <v>1</v>
       </c>
       <c r="S615" t="n">
-        <v>0.1751981860644094</v>
+        <v>-0.03007112135087331</v>
       </c>
       <c r="T615" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U615" t="n">
-        <v>0.1751981860644094</v>
+        <v>-0.03007112135087331</v>
       </c>
       <c r="V615" t="n">
-        <v>0.7468887567520142</v>
+        <v>0.554821926777469</v>
       </c>
       <c r="W615" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="X615" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y615" t="inlineStr"/>
       <c r="Z615" t="n">
-        <v>5.228221297264099</v>
+        <v>7.604405224044576</v>
       </c>
       <c r="AA615" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB615" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC615" t="inlineStr"/>
@@ -61773,96 +61771,96 @@
     <row r="616">
       <c r="A616" s="1" t="inlineStr">
         <is>
-          <t>E38ZP7hD</t>
+          <t>b1PJHvvh</t>
         </is>
       </c>
       <c r="B616" s="2" t="n">
-        <v>45619.47916666666</v>
+        <v>45620.35416666666</v>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E616" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F616" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G616" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="H616" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="I616" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J616" t="n">
-        <v>0.2806236080178174</v>
+        <v>0.3655957706384709</v>
       </c>
       <c r="K616" t="n">
-        <v>0.2650334075723831</v>
+        <v>0.3066287108580724</v>
       </c>
       <c r="L616" t="n">
-        <v>0.4543429844097996</v>
+        <v>0.3277755185034567</v>
       </c>
       <c r="M616" t="n">
-        <v>0.04808590102707733</v>
+        <v>0.05202361598357141</v>
       </c>
       <c r="N616" t="n">
         <v>0</v>
       </c>
       <c r="O616" t="n">
-        <v>0.1142816692590714</v>
+        <v>0.2535054733691977</v>
       </c>
       <c r="P616" t="n">
-        <v>0.4521372020244598</v>
+        <v>0.3798675715489841</v>
       </c>
       <c r="Q616" t="n">
-        <v>0.4335811138153076</v>
+        <v>0.3666269550818181</v>
       </c>
       <c r="R616" t="n">
         <v>1</v>
       </c>
       <c r="S616" t="n">
-        <v>0.1871037944520767</v>
+        <v>0.07323886069091168</v>
       </c>
       <c r="T616" t="n">
         <v>0</v>
       </c>
       <c r="U616" t="n">
-        <v>0.1871037944520767</v>
+        <v>0.07323886069091168</v>
       </c>
       <c r="V616" t="n">
-        <v>0.4521372020244598</v>
+        <v>0.3798675715489841</v>
       </c>
       <c r="W616" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="X616" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y616" t="inlineStr"/>
       <c r="Z616" t="n">
-        <v>3.164960414171219</v>
+        <v>6.647682502107221</v>
       </c>
       <c r="AA616" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB616" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC616" t="inlineStr"/>
@@ -61872,195 +61870,197 @@
     <row r="617">
       <c r="A617" s="1" t="inlineStr">
         <is>
-          <t>fwAoyY0E</t>
+          <t>Ewi1acON</t>
         </is>
       </c>
       <c r="B617" s="2" t="n">
-        <v>45619.47916666666</v>
+        <v>45620.45833333334</v>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>como</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="E617" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F617" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G617" t="n">
-        <v>1.29</v>
+        <v>3.2</v>
       </c>
       <c r="H617" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="I617" t="n">
-        <v>9.5</v>
+        <v>2.38</v>
       </c>
       <c r="J617" t="n">
-        <v>0.7403078121955972</v>
+        <v>0.2961387171871237</v>
       </c>
       <c r="K617" t="n">
-        <v>0.1591661796220534</v>
+        <v>0.3056915790318696</v>
       </c>
       <c r="L617" t="n">
-        <v>0.1005260081823495</v>
+        <v>0.3981697037810067</v>
       </c>
       <c r="M617" t="n">
-        <v>0.04712362301101569</v>
+        <v>0.05524871238818108</v>
       </c>
       <c r="N617" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O617" t="n">
-        <v>0.3674966990947723</v>
+        <v>0.04644974435671278</v>
       </c>
       <c r="P617" t="n">
-        <v>0.3553413152694702</v>
+        <v>0.1673757544185006</v>
       </c>
       <c r="Q617" t="n">
-        <v>0.2771620154380798</v>
+        <v>0.7861745012247867</v>
       </c>
       <c r="R617" t="n">
         <v>1</v>
       </c>
       <c r="S617" t="n">
-        <v>-0.3728111131008248</v>
+        <v>0.38800479744378</v>
       </c>
       <c r="T617" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U617" t="n">
-        <v>0.3728111131008248</v>
+        <v>0.38800479744378</v>
       </c>
       <c r="V617" t="n">
-        <v>0.6325033009052277</v>
+        <v>0.7861745012247867</v>
       </c>
       <c r="W617" t="n">
-        <v>3.67741935483871</v>
+        <v>2.38</v>
       </c>
       <c r="X617" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y617" t="inlineStr"/>
       <c r="Z617" t="n">
-        <v>4.427523106336594</v>
+        <v>13.75805377143377</v>
       </c>
       <c r="AA617" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB617" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="AC617" t="inlineStr"/>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC617" t="n">
+        <v>1</v>
+      </c>
       <c r="AD617" t="inlineStr"/>
       <c r="AE617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="1" t="inlineStr">
         <is>
-          <t>SrjMmBpK</t>
+          <t>M3xASehA</t>
         </is>
       </c>
       <c r="B618" s="2" t="n">
-        <v>45619.47916666666</v>
+        <v>45620.45833333334</v>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E618" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F618" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G618" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="H618" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I618" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J618" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.4671532846715329</v>
       </c>
       <c r="K618" t="n">
-        <v>0.2884615384615385</v>
+        <v>0.2992700729927008</v>
       </c>
       <c r="L618" t="n">
-        <v>0.2884615384615385</v>
+        <v>0.2335766423357664</v>
       </c>
       <c r="M618" t="n">
-        <v>0.05050505050505039</v>
+        <v>0.04420731707317072</v>
       </c>
       <c r="N618" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O618" t="n">
-        <v>0.2910822629928589</v>
+        <v>0.2445397211952143</v>
       </c>
       <c r="P618" t="n">
-        <v>0.188929095864296</v>
+        <v>0.4735163323756597</v>
       </c>
       <c r="Q618" t="n">
-        <v>0.5199886560440063</v>
+        <v>0.2819439464291261</v>
       </c>
       <c r="R618" t="n">
         <v>1</v>
       </c>
       <c r="S618" t="n">
-        <v>0.2315271175824679</v>
+        <v>0.174246259382959</v>
       </c>
       <c r="T618" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U618" t="n">
-        <v>0.2315271175824679</v>
+        <v>0.174246259382959</v>
       </c>
       <c r="V618" t="n">
-        <v>0.5199886560440063</v>
+        <v>0.4735163323756597</v>
       </c>
       <c r="W618" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="X618" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y618" t="inlineStr"/>
       <c r="Z618" t="n">
-        <v>3.639920592308044</v>
+        <v>8.286535816574045</v>
       </c>
       <c r="AA618" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB618" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC618" t="inlineStr"/>
@@ -62070,96 +62070,96 @@
     <row r="619">
       <c r="A619" s="1" t="inlineStr">
         <is>
-          <t>6w5RRTN0</t>
+          <t>KvdF6EVj</t>
         </is>
       </c>
       <c r="B619" s="2" t="n">
-        <v>45619.60416666666</v>
+        <v>45620.58333333334</v>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="E619" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F619" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G619" t="n">
         <v>1.73</v>
       </c>
       <c r="H619" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="I619" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="J619" t="n">
-        <v>0.5490012957333573</v>
+        <v>0.5474785570898474</v>
       </c>
       <c r="K619" t="n">
-        <v>0.2316517662484654</v>
+        <v>0.2630938621570655</v>
       </c>
       <c r="L619" t="n">
-        <v>0.2193469380181774</v>
+        <v>0.1894275807530872</v>
       </c>
       <c r="M619" t="n">
-        <v>0.05288400332240517</v>
+        <v>0.05581245985870265</v>
       </c>
       <c r="N619" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O619" t="n">
-        <v>0.231614962220192</v>
+        <v>0.423275112177328</v>
       </c>
       <c r="P619" t="n">
-        <v>0.5006377100944519</v>
+        <v>0.3892870005141383</v>
       </c>
       <c r="Q619" t="n">
-        <v>0.2677473425865173</v>
+        <v>0.1874378873085338</v>
       </c>
       <c r="R619" t="n">
         <v>1</v>
       </c>
       <c r="S619" t="n">
-        <v>0.2689859438459865</v>
+        <v>-0.1242034449125194</v>
       </c>
       <c r="T619" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U619" t="n">
-        <v>0.2689859438459865</v>
+        <v>-0.1242034449125194</v>
       </c>
       <c r="V619" t="n">
-        <v>0.5006377100944519</v>
+        <v>0.423275112177328</v>
       </c>
       <c r="W619" t="n">
-        <v>4.1</v>
+        <v>1.73</v>
       </c>
       <c r="X619" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y619" t="inlineStr"/>
       <c r="Z619" t="n">
-        <v>3.504463970661163</v>
+        <v>0</v>
       </c>
       <c r="AA619" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB619" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC619" t="inlineStr"/>
@@ -62169,96 +62169,96 @@
     <row r="620">
       <c r="A620" s="1" t="inlineStr">
         <is>
-          <t>KtV0tTxf</t>
+          <t>StHzEdwH</t>
         </is>
       </c>
       <c r="B620" s="2" t="n">
-        <v>45620.47916666666</v>
+        <v>45620.69791666666</v>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E620" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F620" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G620" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="H620" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I620" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J620" t="n">
-        <v>0.3067869752844252</v>
+        <v>0.5011933174224343</v>
       </c>
       <c r="K620" t="n">
-        <v>0.2797175362887406</v>
+        <v>0.2720763723150358</v>
       </c>
       <c r="L620" t="n">
-        <v>0.413495488426834</v>
+        <v>0.2267303102625298</v>
       </c>
       <c r="M620" t="n">
-        <v>0.05148090091576618</v>
+        <v>0.05012531328320802</v>
       </c>
       <c r="N620" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O620" t="n">
-        <v>0.0898820087313652</v>
+        <v>0.3619515607914891</v>
       </c>
       <c r="P620" t="n">
-        <v>0.2830811440944672</v>
+        <v>0.3888795289225333</v>
       </c>
       <c r="Q620" t="n">
-        <v>0.6270368695259094</v>
+        <v>0.2491689102859776</v>
       </c>
       <c r="R620" t="n">
         <v>1</v>
       </c>
       <c r="S620" t="n">
-        <v>0.2135413810990754</v>
+        <v>0.1168031566074975</v>
       </c>
       <c r="T620" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U620" t="n">
-        <v>0.2135413810990754</v>
+        <v>0.1168031566074975</v>
       </c>
       <c r="V620" t="n">
-        <v>0.6270368695259094</v>
+        <v>0.3888795289225333</v>
       </c>
       <c r="W620" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="X620" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y620" t="inlineStr"/>
       <c r="Z620" t="n">
-        <v>4.389258086681366</v>
+        <v>6.805391756144333</v>
       </c>
       <c r="AA620" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB620" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC620" t="inlineStr"/>
@@ -62268,96 +62268,96 @@
     <row r="621">
       <c r="A621" s="1" t="inlineStr">
         <is>
-          <t>OEyhrk8s</t>
+          <t>pMsXgyno</t>
         </is>
       </c>
       <c r="B621" s="2" t="n">
-        <v>45620.5625</v>
+        <v>45621.60416666666</v>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="E621" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F621" t="n">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="G621" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="H621" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="I621" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J621" t="n">
-        <v>0.5256916996047432</v>
+        <v>0.3372093023255813</v>
       </c>
       <c r="K621" t="n">
-        <v>0.2490118577075099</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="L621" t="n">
-        <v>0.225296442687747</v>
+        <v>0.3372093023255813</v>
       </c>
       <c r="M621" t="n">
-        <v>0.05680868838763575</v>
+        <v>0.05911330049261099</v>
       </c>
       <c r="N621" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O621" t="n">
-        <v>0.3624015152454376</v>
+        <v>0.4336302148290543</v>
       </c>
       <c r="P621" t="n">
-        <v>0.4057324230670929</v>
+        <v>0.3649604099178962</v>
       </c>
       <c r="Q621" t="n">
-        <v>0.2318660914897919</v>
+        <v>0.2014093752530495</v>
       </c>
       <c r="R621" t="n">
         <v>1</v>
       </c>
       <c r="S621" t="n">
-        <v>0.156720565359583</v>
+        <v>0.09642091250347301</v>
       </c>
       <c r="T621" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U621" t="n">
-        <v>0.156720565359583</v>
+        <v>0.09642091250347301</v>
       </c>
       <c r="V621" t="n">
-        <v>0.4057324230670929</v>
+        <v>0.4336302148290543</v>
       </c>
       <c r="W621" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="X621" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y621" t="inlineStr"/>
       <c r="Z621" t="n">
-        <v>2.84012696146965</v>
+        <v>7.588528759508451</v>
       </c>
       <c r="AA621" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB621" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC621" t="inlineStr"/>
@@ -62367,20 +62367,20 @@
     <row r="622">
       <c r="A622" s="1" t="inlineStr">
         <is>
-          <t>WENRFI84</t>
+          <t>hjasAmxq</t>
         </is>
       </c>
       <c r="B622" s="2" t="n">
-        <v>45619.45833333334</v>
+        <v>45621.69791666666</v>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E622" t="n">
@@ -62390,55 +62390,55 @@
         <v>771</v>
       </c>
       <c r="G622" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="H622" t="n">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="I622" t="n">
-        <v>1.38</v>
+        <v>3.2</v>
       </c>
       <c r="J622" t="n">
-        <v>0.1350293542074364</v>
+        <v>0.4121260154547257</v>
       </c>
       <c r="K622" t="n">
-        <v>0.1800391389432485</v>
+        <v>0.2916584109371904</v>
       </c>
       <c r="L622" t="n">
-        <v>0.6849315068493151</v>
+        <v>0.296215573608084</v>
       </c>
       <c r="M622" t="n">
-        <v>0.05797101449275366</v>
+        <v>0.05497491638795982</v>
       </c>
       <c r="N622" t="n">
         <v>2</v>
       </c>
       <c r="O622" t="n">
-        <v>0.07605352458246978</v>
+        <v>0.1856164616886396</v>
       </c>
       <c r="P622" t="n">
-        <v>0.2423606517662135</v>
+        <v>0.3424946146248241</v>
       </c>
       <c r="Q622" t="n">
-        <v>0.6815858236513167</v>
+        <v>0.4718889236865362</v>
       </c>
       <c r="R622" t="n">
         <v>1</v>
       </c>
       <c r="S622" t="n">
-        <v>-0.003345683197998439</v>
+        <v>0.1756733500784522</v>
       </c>
       <c r="T622" t="n">
         <v>2</v>
       </c>
       <c r="U622" t="n">
-        <v>-0.003345683197998439</v>
+        <v>0.1756733500784522</v>
       </c>
       <c r="V622" t="n">
-        <v>0.6815858236513167</v>
+        <v>0.4718889236865362</v>
       </c>
       <c r="W622" t="n">
-        <v>1.38</v>
+        <v>3.2</v>
       </c>
       <c r="X622" t="inlineStr">
         <is>
@@ -62447,7 +62447,7 @@
       </c>
       <c r="Y622" t="inlineStr"/>
       <c r="Z622" t="n">
-        <v>11.69355409003815</v>
+        <v>8.258056164514384</v>
       </c>
       <c r="AA622" t="inlineStr">
         <is>
@@ -62466,96 +62466,96 @@
     <row r="623">
       <c r="A623" s="1" t="inlineStr">
         <is>
-          <t>z7KrCz8T</t>
+          <t>SCX7iT7M</t>
         </is>
       </c>
       <c r="B623" s="2" t="n">
-        <v>45619.58333333334</v>
+        <v>45618.70833333334</v>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E623" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F623" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G623" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="H623" t="n">
         <v>3.3</v>
       </c>
       <c r="I623" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="J623" t="n">
-        <v>0.4413450515857852</v>
+        <v>0.5479115833850685</v>
       </c>
       <c r="K623" t="n">
-        <v>0.2875429881543752</v>
+        <v>0.2872384967442935</v>
       </c>
       <c r="L623" t="n">
-        <v>0.2711119602598395</v>
+        <v>0.164849919870638</v>
       </c>
       <c r="M623" t="n">
-        <v>0.05386086781435617</v>
+        <v>0.05497802858948875</v>
       </c>
       <c r="N623" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O623" t="n">
-        <v>0.35669835414836</v>
+        <v>0.2291478365659714</v>
       </c>
       <c r="P623" t="n">
-        <v>0.3483631099687277</v>
+        <v>0.6676607728004456</v>
       </c>
       <c r="Q623" t="n">
-        <v>0.2949385358829122</v>
+        <v>0.1031913980841637</v>
       </c>
       <c r="R623" t="n">
         <v>1</v>
       </c>
       <c r="S623" t="n">
-        <v>-0.0846466974374252</v>
+        <v>0.380422276056152</v>
       </c>
       <c r="T623" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U623" t="n">
-        <v>-0.0846466974374252</v>
+        <v>0.380422276056152</v>
       </c>
       <c r="V623" t="n">
-        <v>0.35669835414836</v>
+        <v>0.6676607728004456</v>
       </c>
       <c r="W623" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="X623" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y623" t="inlineStr"/>
       <c r="Z623" t="n">
-        <v>0.3169523769765367</v>
+        <v>11.6840635240078</v>
       </c>
       <c r="AA623" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB623" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC623" t="inlineStr"/>
@@ -62565,195 +62565,197 @@
     <row r="624">
       <c r="A624" s="1" t="inlineStr">
         <is>
-          <t>Qyq1UHNc</t>
+          <t>C2KEmK6l</t>
         </is>
       </c>
       <c r="B624" s="2" t="n">
-        <v>45619.69791666666</v>
+        <v>45619.41666666666</v>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E624" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F624" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G624" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H624" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="I624" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="J624" t="n">
-        <v>0.1895053475935829</v>
+        <v>0.3170731707317074</v>
       </c>
       <c r="K624" t="n">
-        <v>0.2256016042780749</v>
+        <v>0.3170731707317074</v>
       </c>
       <c r="L624" t="n">
-        <v>0.5848930481283423</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="M624" t="n">
-        <v>0.0553791887125219</v>
+        <v>0.0512820512820511</v>
       </c>
       <c r="N624" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O624" t="n">
-        <v>0.1777861207576573</v>
+        <v>0.3059642314910889</v>
       </c>
       <c r="P624" t="n">
-        <v>0.2673919524648737</v>
+        <v>0.4625942409038544</v>
       </c>
       <c r="Q624" t="n">
-        <v>0.554821926777469</v>
+        <v>0.2314416021108627</v>
       </c>
       <c r="R624" t="n">
         <v>1</v>
       </c>
       <c r="S624" t="n">
-        <v>-0.03007112135087331</v>
+        <v>0.145521070172147</v>
       </c>
       <c r="T624" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U624" t="n">
-        <v>-0.03007112135087331</v>
+        <v>0.145521070172147</v>
       </c>
       <c r="V624" t="n">
-        <v>0.554821926777469</v>
+        <v>0.4625942409038544</v>
       </c>
       <c r="W624" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="X624" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y624" t="inlineStr"/>
       <c r="Z624" t="n">
-        <v>7.604405224044576</v>
+        <v>8.095399215817451</v>
       </c>
       <c r="AA624" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB624" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC624" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC624" t="n">
+        <v>1</v>
+      </c>
       <c r="AD624" t="inlineStr"/>
       <c r="AE624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" s="1" t="inlineStr">
         <is>
-          <t>b1PJHvvh</t>
+          <t>vVwOqx6D</t>
         </is>
       </c>
       <c r="B625" s="2" t="n">
-        <v>45620.35416666666</v>
+        <v>45619.51041666666</v>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E625" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F625" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G625" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="H625" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="I625" t="n">
-        <v>2.9</v>
+        <v>9</v>
       </c>
       <c r="J625" t="n">
-        <v>0.3655957706384709</v>
+        <v>0.6956875508543532</v>
       </c>
       <c r="K625" t="n">
-        <v>0.3066287108580724</v>
+        <v>0.199186330349878</v>
       </c>
       <c r="L625" t="n">
-        <v>0.3277755185034567</v>
+        <v>0.1051261187957689</v>
       </c>
       <c r="M625" t="n">
-        <v>0.05202361598357141</v>
+        <v>0.05693154454764349</v>
       </c>
       <c r="N625" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O625" t="n">
-        <v>0.2535054733691977</v>
+        <v>0.8715217709541321</v>
       </c>
       <c r="P625" t="n">
-        <v>0.3798675715489841</v>
+        <v>0.09871138632297516</v>
       </c>
       <c r="Q625" t="n">
-        <v>0.3666269550818181</v>
+        <v>0.02976679056882858</v>
       </c>
       <c r="R625" t="n">
         <v>1</v>
       </c>
       <c r="S625" t="n">
-        <v>0.07323886069091168</v>
+        <v>0.1758342200997789</v>
       </c>
       <c r="T625" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U625" t="n">
-        <v>0.07323886069091168</v>
+        <v>0.1758342200997789</v>
       </c>
       <c r="V625" t="n">
-        <v>0.3798675715489841</v>
+        <v>0.8715217709541321</v>
       </c>
       <c r="W625" t="n">
-        <v>3.1</v>
+        <v>1.36</v>
       </c>
       <c r="X625" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y625" t="inlineStr"/>
       <c r="Z625" t="n">
-        <v>6.647682502107221</v>
+        <v>15.25163099169731</v>
       </c>
       <c r="AA625" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB625" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC625" t="inlineStr"/>
@@ -62763,96 +62765,96 @@
     <row r="626">
       <c r="A626" s="1" t="inlineStr">
         <is>
-          <t>Ewi1acON</t>
+          <t>buKPeYL5</t>
         </is>
       </c>
       <c r="B626" s="2" t="n">
-        <v>45620.45833333334</v>
+        <v>45619.60416666666</v>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E626" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F626" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G626" t="n">
-        <v>3.2</v>
+        <v>1.67</v>
       </c>
       <c r="H626" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="I626" t="n">
-        <v>2.38</v>
+        <v>5.25</v>
       </c>
       <c r="J626" t="n">
-        <v>0.2961387171871237</v>
+        <v>0.5689677299756157</v>
       </c>
       <c r="K626" t="n">
-        <v>0.3056915790318696</v>
+        <v>0.2500463444892837</v>
       </c>
       <c r="L626" t="n">
-        <v>0.3981697037810067</v>
+        <v>0.1809859255351006</v>
       </c>
       <c r="M626" t="n">
-        <v>0.05524871238818108</v>
+        <v>0.0524364804226134</v>
       </c>
       <c r="N626" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O626" t="n">
-        <v>0.04644974435671278</v>
+        <v>0.6232661008834839</v>
       </c>
       <c r="P626" t="n">
-        <v>0.1673757544185006</v>
+        <v>0.1015298962593079</v>
       </c>
       <c r="Q626" t="n">
-        <v>0.7861745012247867</v>
+        <v>0.2752040326595306</v>
       </c>
       <c r="R626" t="n">
         <v>1</v>
       </c>
       <c r="S626" t="n">
-        <v>0.38800479744378</v>
+        <v>0.05429837090786815</v>
       </c>
       <c r="T626" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U626" t="n">
-        <v>0.38800479744378</v>
+        <v>0.05429837090786815</v>
       </c>
       <c r="V626" t="n">
-        <v>0.7861745012247867</v>
+        <v>0.6232661008834839</v>
       </c>
       <c r="W626" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="X626" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y626" t="inlineStr"/>
       <c r="Z626" t="n">
-        <v>13.75805377143377</v>
+        <v>10.90715676546097</v>
       </c>
       <c r="AA626" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB626" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC626" t="n">
@@ -62864,96 +62866,96 @@
     <row r="627">
       <c r="A627" s="1" t="inlineStr">
         <is>
-          <t>M3xASehA</t>
+          <t>IsCnpo0d</t>
         </is>
       </c>
       <c r="B627" s="2" t="n">
-        <v>45620.45833333334</v>
+        <v>45619.60416666666</v>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E627" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F627" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G627" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="H627" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I627" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="J627" t="n">
-        <v>0.4671532846715329</v>
+        <v>0.3148148148148148</v>
       </c>
       <c r="K627" t="n">
-        <v>0.2992700729927008</v>
+        <v>0.3148148148148148</v>
       </c>
       <c r="L627" t="n">
-        <v>0.2335766423357664</v>
+        <v>0.3703703703703704</v>
       </c>
       <c r="M627" t="n">
-        <v>0.04420731707317072</v>
+        <v>0.05882352941176472</v>
       </c>
       <c r="N627" t="n">
         <v>0</v>
       </c>
       <c r="O627" t="n">
-        <v>0.2445397211952143</v>
+        <v>0.2897258102893829</v>
       </c>
       <c r="P627" t="n">
-        <v>0.4735163323756597</v>
+        <v>0.4301001131534576</v>
       </c>
       <c r="Q627" t="n">
-        <v>0.2819439464291261</v>
+        <v>0.2801741063594818</v>
       </c>
       <c r="R627" t="n">
         <v>1</v>
       </c>
       <c r="S627" t="n">
-        <v>0.174246259382959</v>
+        <v>0.1152852983386429</v>
       </c>
       <c r="T627" t="n">
         <v>0</v>
       </c>
       <c r="U627" t="n">
-        <v>0.174246259382959</v>
+        <v>0.1152852983386429</v>
       </c>
       <c r="V627" t="n">
-        <v>0.4735163323756597</v>
+        <v>0.4301001131534576</v>
       </c>
       <c r="W627" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="X627" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y627" t="inlineStr"/>
       <c r="Z627" t="n">
-        <v>8.286535816574045</v>
+        <v>7.526751980185509</v>
       </c>
       <c r="AA627" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB627" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC627" t="inlineStr"/>
@@ -62963,96 +62965,96 @@
     <row r="628">
       <c r="A628" s="1" t="inlineStr">
         <is>
-          <t>KvdF6EVj</t>
+          <t>tGcs6SMF</t>
         </is>
       </c>
       <c r="B628" s="2" t="n">
-        <v>45620.58333333334</v>
+        <v>45619.70833333334</v>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E628" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F628" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G628" t="n">
-        <v>1.73</v>
+        <v>4.5</v>
       </c>
       <c r="H628" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="I628" t="n">
-        <v>5</v>
+        <v>1.67</v>
       </c>
       <c r="J628" t="n">
-        <v>0.5474785570898474</v>
+        <v>0.2112435767474606</v>
       </c>
       <c r="K628" t="n">
-        <v>0.2630938621570655</v>
+        <v>0.2195372044719568</v>
       </c>
       <c r="L628" t="n">
-        <v>0.1894275807530872</v>
+        <v>0.5692192187805826</v>
       </c>
       <c r="M628" t="n">
-        <v>0.05581245985870265</v>
+        <v>0.05197149964889314</v>
       </c>
       <c r="N628" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O628" t="n">
-        <v>0.423275112177328</v>
+        <v>0.04584328830242157</v>
       </c>
       <c r="P628" t="n">
-        <v>0.3892870005141383</v>
+        <v>0.1309177875518799</v>
       </c>
       <c r="Q628" t="n">
-        <v>0.1874378873085338</v>
+        <v>0.8232389092445374</v>
       </c>
       <c r="R628" t="n">
         <v>1</v>
       </c>
       <c r="S628" t="n">
-        <v>-0.1242034449125194</v>
+        <v>0.2540196904639548</v>
       </c>
       <c r="T628" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U628" t="n">
-        <v>-0.1242034449125194</v>
+        <v>0.2540196904639548</v>
       </c>
       <c r="V628" t="n">
-        <v>0.423275112177328</v>
+        <v>0.8232389092445374</v>
       </c>
       <c r="W628" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="X628" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y628" t="inlineStr"/>
       <c r="Z628" t="n">
-        <v>0</v>
+        <v>14.4066809117794</v>
       </c>
       <c r="AA628" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB628" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC628" t="inlineStr"/>
@@ -63062,96 +63064,96 @@
     <row r="629">
       <c r="A629" s="1" t="inlineStr">
         <is>
-          <t>StHzEdwH</t>
+          <t>dSNwn7Vq</t>
         </is>
       </c>
       <c r="B629" s="2" t="n">
-        <v>45620.69791666666</v>
+        <v>45620.41666666666</v>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E629" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F629" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G629" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="H629" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I629" t="n">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="J629" t="n">
-        <v>0.5011933174224343</v>
+        <v>0.3515188335358444</v>
       </c>
       <c r="K629" t="n">
-        <v>0.2720763723150358</v>
+        <v>0.287606318347509</v>
       </c>
       <c r="L629" t="n">
-        <v>0.2267303102625298</v>
+        <v>0.3608748481166464</v>
       </c>
       <c r="M629" t="n">
-        <v>0.05012531328320802</v>
+        <v>0.05362881028280286</v>
       </c>
       <c r="N629" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O629" t="n">
-        <v>0.3619515607914891</v>
+        <v>0.2457459270954132</v>
       </c>
       <c r="P629" t="n">
-        <v>0.3888795289225333</v>
+        <v>0.3619625866413116</v>
       </c>
       <c r="Q629" t="n">
-        <v>0.2491689102859776</v>
+        <v>0.3922915160655975</v>
       </c>
       <c r="R629" t="n">
         <v>1</v>
       </c>
       <c r="S629" t="n">
-        <v>0.1168031566074975</v>
+        <v>0.03141666794895115</v>
       </c>
       <c r="T629" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U629" t="n">
-        <v>0.1168031566074975</v>
+        <v>0.03141666794895115</v>
       </c>
       <c r="V629" t="n">
-        <v>0.3888795289225333</v>
+        <v>0.3922915160655975</v>
       </c>
       <c r="W629" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="X629" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y629" t="inlineStr"/>
       <c r="Z629" t="n">
-        <v>6.805391756144333</v>
+        <v>6.865101531147957</v>
       </c>
       <c r="AA629" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB629" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC629" t="inlineStr"/>
@@ -63161,195 +63163,197 @@
     <row r="630">
       <c r="A630" s="1" t="inlineStr">
         <is>
-          <t>pMsXgyno</t>
+          <t>W4zGoby1</t>
         </is>
       </c>
       <c r="B630" s="2" t="n">
-        <v>45621.60416666666</v>
+        <v>45620.51041666666</v>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E630" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F630" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G630" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="H630" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="I630" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J630" t="n">
-        <v>0.3372093023255813</v>
+        <v>0.4139553116424932</v>
       </c>
       <c r="K630" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.2975303802430419</v>
       </c>
       <c r="L630" t="n">
-        <v>0.3372093023255813</v>
+        <v>0.2885143081144649</v>
       </c>
       <c r="M630" t="n">
-        <v>0.05911330049261099</v>
+        <v>0.05031291172595531</v>
       </c>
       <c r="N630" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O630" t="n">
-        <v>0.4336302148290543</v>
+        <v>0.2018209844827652</v>
       </c>
       <c r="P630" t="n">
-        <v>0.3649604099178962</v>
+        <v>0.5636378526687622</v>
       </c>
       <c r="Q630" t="n">
-        <v>0.2014093752530495</v>
+        <v>0.2345411628484726</v>
       </c>
       <c r="R630" t="n">
         <v>1</v>
       </c>
       <c r="S630" t="n">
-        <v>0.09642091250347301</v>
+        <v>0.2661074724257203</v>
       </c>
       <c r="T630" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U630" t="n">
-        <v>0.09642091250347301</v>
+        <v>0.2661074724257203</v>
       </c>
       <c r="V630" t="n">
-        <v>0.4336302148290543</v>
+        <v>0.5636378526687622</v>
       </c>
       <c r="W630" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="X630" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y630" t="inlineStr"/>
       <c r="Z630" t="n">
-        <v>7.588528759508451</v>
+        <v>9.863662421703339</v>
       </c>
       <c r="AA630" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB630" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC630" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC630" t="n">
+        <v>1</v>
+      </c>
       <c r="AD630" t="inlineStr"/>
       <c r="AE630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" s="1" t="inlineStr">
         <is>
-          <t>hjasAmxq</t>
+          <t>pl4Y7lh3</t>
         </is>
       </c>
       <c r="B631" s="2" t="n">
-        <v>45621.69791666666</v>
+        <v>45620.60416666666</v>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F631" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G631" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="H631" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="I631" t="n">
-        <v>3.2</v>
+        <v>1.45</v>
       </c>
       <c r="J631" t="n">
-        <v>0.4121260154547257</v>
+        <v>0.1354436948624805</v>
       </c>
       <c r="K631" t="n">
-        <v>0.2916584109371904</v>
+        <v>0.210690192008303</v>
       </c>
       <c r="L631" t="n">
-        <v>0.296215573608084</v>
+        <v>0.6538661131292164</v>
       </c>
       <c r="M631" t="n">
-        <v>0.05497491638795982</v>
+        <v>0.05473453749315826</v>
       </c>
       <c r="N631" t="n">
         <v>2</v>
       </c>
       <c r="O631" t="n">
-        <v>0.1856164616886396</v>
+        <v>0.0941070169210434</v>
       </c>
       <c r="P631" t="n">
-        <v>0.3424946146248241</v>
+        <v>0.09887459129095078</v>
       </c>
       <c r="Q631" t="n">
-        <v>0.4718889236865362</v>
+        <v>0.8070184588432312</v>
       </c>
       <c r="R631" t="n">
         <v>1</v>
       </c>
       <c r="S631" t="n">
-        <v>0.1756733500784522</v>
+        <v>0.1531523457140148</v>
       </c>
       <c r="T631" t="n">
         <v>2</v>
       </c>
       <c r="U631" t="n">
-        <v>0.1756733500784522</v>
+        <v>0.1531523457140148</v>
       </c>
       <c r="V631" t="n">
-        <v>0.4718889236865362</v>
+        <v>0.8070184588432312</v>
       </c>
       <c r="W631" t="n">
-        <v>3.2</v>
+        <v>1.45</v>
       </c>
       <c r="X631" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y631" t="inlineStr"/>
       <c r="Z631" t="n">
-        <v>8.258056164514384</v>
+        <v>14.12282302975655</v>
       </c>
       <c r="AA631" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB631" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC631" t="inlineStr"/>
@@ -63359,20 +63363,20 @@
     <row r="632">
       <c r="A632" s="1" t="inlineStr">
         <is>
-          <t>SCX7iT7M</t>
+          <t>WpvagkwA</t>
         </is>
       </c>
       <c r="B632" s="2" t="n">
-        <v>45618.70833333334</v>
+        <v>45620.70833333334</v>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E632" t="n">
@@ -63382,55 +63386,55 @@
         <v>1481</v>
       </c>
       <c r="G632" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="H632" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="I632" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="J632" t="n">
-        <v>0.5479115833850685</v>
+        <v>0.4310344827586207</v>
       </c>
       <c r="K632" t="n">
-        <v>0.2872384967442935</v>
+        <v>0.3160919540229885</v>
       </c>
       <c r="L632" t="n">
-        <v>0.164849919870638</v>
+        <v>0.2528735632183908</v>
       </c>
       <c r="M632" t="n">
-        <v>0.05497802858948875</v>
+        <v>0.05454545454545445</v>
       </c>
       <c r="N632" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O632" t="n">
-        <v>0.2291478365659714</v>
+        <v>0.3089075982570648</v>
       </c>
       <c r="P632" t="n">
-        <v>0.6676607728004456</v>
+        <v>0.2107562869787216</v>
       </c>
       <c r="Q632" t="n">
-        <v>0.1031913980841637</v>
+        <v>0.4803360998630524</v>
       </c>
       <c r="R632" t="n">
         <v>1</v>
       </c>
       <c r="S632" t="n">
-        <v>0.380422276056152</v>
+        <v>0.2274625366446615</v>
       </c>
       <c r="T632" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U632" t="n">
-        <v>0.380422276056152</v>
+        <v>0.2274625366446615</v>
       </c>
       <c r="V632" t="n">
-        <v>0.6676607728004456</v>
+        <v>0.4803360998630524</v>
       </c>
       <c r="W632" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="X632" t="inlineStr">
         <is>
@@ -63439,7 +63443,7 @@
       </c>
       <c r="Y632" t="inlineStr"/>
       <c r="Z632" t="n">
-        <v>11.6840635240078</v>
+        <v>8.405881747603416</v>
       </c>
       <c r="AA632" t="inlineStr">
         <is>
@@ -63458,96 +63462,96 @@
     <row r="633">
       <c r="A633" s="1" t="inlineStr">
         <is>
-          <t>C2KEmK6l</t>
+          <t>EuQnZBVQ</t>
         </is>
       </c>
       <c r="B633" s="2" t="n">
-        <v>45619.41666666666</v>
+        <v>45618.6875</v>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E633" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F633" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G633" t="n">
-        <v>3</v>
+        <v>1.13</v>
       </c>
       <c r="H633" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I633" t="n">
-        <v>2.6</v>
+        <v>15</v>
       </c>
       <c r="J633" t="n">
-        <v>0.3170731707317074</v>
+        <v>0.8415147265077139</v>
       </c>
       <c r="K633" t="n">
-        <v>0.3170731707317074</v>
+        <v>0.09509116409537166</v>
       </c>
       <c r="L633" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.06339410939691444</v>
       </c>
       <c r="M633" t="n">
-        <v>0.0512820512820511</v>
+        <v>0.05162241887905616</v>
       </c>
       <c r="N633" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O633" t="n">
-        <v>0.3059642314910889</v>
+        <v>0.816745400428772</v>
       </c>
       <c r="P633" t="n">
-        <v>0.4625942409038544</v>
+        <v>0.1343889534473419</v>
       </c>
       <c r="Q633" t="n">
-        <v>0.2314416021108627</v>
+        <v>0.04886569455265999</v>
       </c>
       <c r="R633" t="n">
         <v>1</v>
       </c>
       <c r="S633" t="n">
-        <v>0.145521070172147</v>
+        <v>-0.02476932607894189</v>
       </c>
       <c r="T633" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U633" t="n">
-        <v>0.145521070172147</v>
+        <v>-0.02476932607894189</v>
       </c>
       <c r="V633" t="n">
-        <v>0.4625942409038544</v>
+        <v>0.816745400428772</v>
       </c>
       <c r="W633" t="n">
-        <v>3</v>
+        <v>1.13</v>
       </c>
       <c r="X633" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="Y633" t="inlineStr"/>
       <c r="Z633" t="n">
-        <v>8.095399215817451</v>
+        <v>3.588340480565022</v>
       </c>
       <c r="AA633" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB633" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC633" t="n">
@@ -63559,96 +63563,96 @@
     <row r="634">
       <c r="A634" s="1" t="inlineStr">
         <is>
-          <t>vVwOqx6D</t>
+          <t>2qNaDU87</t>
         </is>
       </c>
       <c r="B634" s="2" t="n">
-        <v>45619.51041666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E634" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F634" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G634" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="H634" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="I634" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J634" t="n">
-        <v>0.6956875508543532</v>
+        <v>0.7907542579075426</v>
       </c>
       <c r="K634" t="n">
-        <v>0.199186330349878</v>
+        <v>0.145985401459854</v>
       </c>
       <c r="L634" t="n">
-        <v>0.1051261187957689</v>
+        <v>0.0632603406326034</v>
       </c>
       <c r="M634" t="n">
-        <v>0.05693154454764349</v>
+        <v>0.05384615384615388</v>
       </c>
       <c r="N634" t="n">
         <v>1</v>
       </c>
       <c r="O634" t="n">
-        <v>0.8715217709541321</v>
+        <v>0.58930504322052</v>
       </c>
       <c r="P634" t="n">
-        <v>0.09871138632297516</v>
+        <v>0.3469331860542297</v>
       </c>
       <c r="Q634" t="n">
-        <v>0.02976679056882858</v>
+        <v>0.06376180797815323</v>
       </c>
       <c r="R634" t="n">
         <v>1</v>
       </c>
       <c r="S634" t="n">
-        <v>0.1758342200997789</v>
+        <v>-0.2014492146870226</v>
       </c>
       <c r="T634" t="n">
         <v>1</v>
       </c>
       <c r="U634" t="n">
-        <v>0.1758342200997789</v>
+        <v>-0.2014492146870226</v>
       </c>
       <c r="V634" t="n">
-        <v>0.8715217709541321</v>
+        <v>0.58930504322052</v>
       </c>
       <c r="W634" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="X634" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="Y634" t="inlineStr"/>
       <c r="Z634" t="n">
-        <v>15.25163099169731</v>
+        <v>0</v>
       </c>
       <c r="AA634" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB634" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC634" t="inlineStr"/>
@@ -63658,197 +63662,195 @@
     <row r="635">
       <c r="A635" s="1" t="inlineStr">
         <is>
-          <t>buKPeYL5</t>
+          <t>pOGITkgl</t>
         </is>
       </c>
       <c r="B635" s="2" t="n">
-        <v>45619.60416666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E635" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F635" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G635" t="n">
         <v>1.67</v>
       </c>
       <c r="H635" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I635" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="J635" t="n">
-        <v>0.5689677299756157</v>
+        <v>0.5716905706876048</v>
       </c>
       <c r="K635" t="n">
-        <v>0.2500463444892837</v>
+        <v>0.2273150602495952</v>
       </c>
       <c r="L635" t="n">
-        <v>0.1809859255351006</v>
+        <v>0.2009943690628</v>
       </c>
       <c r="M635" t="n">
-        <v>0.0524364804226134</v>
+        <v>0.04742394909429271</v>
       </c>
       <c r="N635" t="n">
         <v>1</v>
       </c>
       <c r="O635" t="n">
-        <v>0.6232661008834839</v>
+        <v>0.5137215852737427</v>
       </c>
       <c r="P635" t="n">
-        <v>0.1015298962593079</v>
+        <v>0.2179991900920868</v>
       </c>
       <c r="Q635" t="n">
-        <v>0.2752040326595306</v>
+        <v>0.2682792246341705</v>
       </c>
       <c r="R635" t="n">
         <v>1</v>
       </c>
       <c r="S635" t="n">
-        <v>0.05429837090786815</v>
+        <v>-0.05796898541386208</v>
       </c>
       <c r="T635" t="n">
         <v>1</v>
       </c>
       <c r="U635" t="n">
-        <v>0.05429837090786815</v>
+        <v>-0.05796898541386208</v>
       </c>
       <c r="V635" t="n">
-        <v>0.6232661008834839</v>
+        <v>0.5137215852737427</v>
       </c>
       <c r="W635" t="n">
         <v>1.67</v>
       </c>
       <c r="X635" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="Y635" t="inlineStr"/>
       <c r="Z635" t="n">
-        <v>10.90715676546097</v>
+        <v>1.409228218091472</v>
       </c>
       <c r="AA635" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB635" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC635" t="n">
-        <v>1</v>
-      </c>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="AC635" t="inlineStr"/>
       <c r="AD635" t="inlineStr"/>
       <c r="AE635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" s="1" t="inlineStr">
         <is>
-          <t>IsCnpo0d</t>
+          <t>E38ZP7hD</t>
         </is>
       </c>
       <c r="B636" s="2" t="n">
-        <v>45619.60416666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E636" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F636" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G636" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="H636" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I636" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="J636" t="n">
-        <v>0.3148148148148148</v>
+        <v>0.2806236080178174</v>
       </c>
       <c r="K636" t="n">
-        <v>0.3148148148148148</v>
+        <v>0.2650334075723831</v>
       </c>
       <c r="L636" t="n">
-        <v>0.3703703703703704</v>
+        <v>0.4543429844097996</v>
       </c>
       <c r="M636" t="n">
-        <v>0.05882352941176472</v>
+        <v>0.04808590102707733</v>
       </c>
       <c r="N636" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O636" t="n">
-        <v>0.2897258102893829</v>
+        <v>0.4148953557014465</v>
       </c>
       <c r="P636" t="n">
-        <v>0.4301001131534576</v>
+        <v>0.288111537694931</v>
       </c>
       <c r="Q636" t="n">
-        <v>0.2801741063594818</v>
+        <v>0.2969931662082672</v>
       </c>
       <c r="R636" t="n">
         <v>1</v>
       </c>
       <c r="S636" t="n">
-        <v>0.1152852983386429</v>
+        <v>0.1342717476836291</v>
       </c>
       <c r="T636" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U636" t="n">
-        <v>0.1152852983386429</v>
+        <v>0.1342717476836291</v>
       </c>
       <c r="V636" t="n">
-        <v>0.4301001131534576</v>
+        <v>0.4148953557014465</v>
       </c>
       <c r="W636" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="X636" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="Y636" t="inlineStr"/>
       <c r="Z636" t="n">
-        <v>7.526751980185509</v>
+        <v>4.759911732179814</v>
       </c>
       <c r="AA636" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB636" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC636" t="inlineStr"/>
@@ -63858,96 +63860,96 @@
     <row r="637">
       <c r="A637" s="1" t="inlineStr">
         <is>
-          <t>tGcs6SMF</t>
+          <t>fwAoyY0E</t>
         </is>
       </c>
       <c r="B637" s="2" t="n">
-        <v>45619.70833333334</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="E637" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F637" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G637" t="n">
-        <v>4.5</v>
+        <v>1.29</v>
       </c>
       <c r="H637" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="I637" t="n">
-        <v>1.67</v>
+        <v>9.5</v>
       </c>
       <c r="J637" t="n">
-        <v>0.2112435767474606</v>
+        <v>0.7403078121955972</v>
       </c>
       <c r="K637" t="n">
-        <v>0.2195372044719568</v>
+        <v>0.1591661796220534</v>
       </c>
       <c r="L637" t="n">
-        <v>0.5692192187805826</v>
+        <v>0.1005260081823495</v>
       </c>
       <c r="M637" t="n">
-        <v>0.05197149964889314</v>
+        <v>0.04712362301101569</v>
       </c>
       <c r="N637" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O637" t="n">
-        <v>0.04584328830242157</v>
+        <v>0.4565851092338562</v>
       </c>
       <c r="P637" t="n">
-        <v>0.1309177875518799</v>
+        <v>0.3439750373363495</v>
       </c>
       <c r="Q637" t="n">
-        <v>0.8232389092445374</v>
+        <v>0.1994399130344391</v>
       </c>
       <c r="R637" t="n">
         <v>1</v>
       </c>
       <c r="S637" t="n">
-        <v>0.2540196904639548</v>
+        <v>-0.283722702961741</v>
       </c>
       <c r="T637" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U637" t="n">
-        <v>0.2540196904639548</v>
+        <v>-0.283722702961741</v>
       </c>
       <c r="V637" t="n">
-        <v>0.8232389092445374</v>
+        <v>0.4565851092338562</v>
       </c>
       <c r="W637" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="X637" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="Y637" t="inlineStr"/>
       <c r="Z637" t="n">
-        <v>14.4066809117794</v>
+        <v>0</v>
       </c>
       <c r="AA637" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB637" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC637" t="inlineStr"/>
@@ -63957,96 +63959,96 @@
     <row r="638">
       <c r="A638" s="1" t="inlineStr">
         <is>
-          <t>dSNwn7Vq</t>
+          <t>SrjMmBpK</t>
         </is>
       </c>
       <c r="B638" s="2" t="n">
-        <v>45620.41666666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E638" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F638" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G638" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="H638" t="n">
         <v>3.3</v>
       </c>
       <c r="I638" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="J638" t="n">
-        <v>0.3515188335358444</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="K638" t="n">
-        <v>0.287606318347509</v>
+        <v>0.2884615384615385</v>
       </c>
       <c r="L638" t="n">
-        <v>0.3608748481166464</v>
+        <v>0.2884615384615385</v>
       </c>
       <c r="M638" t="n">
-        <v>0.05362881028280286</v>
+        <v>0.05050505050505039</v>
       </c>
       <c r="N638" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O638" t="n">
-        <v>0.2457459270954132</v>
+        <v>0.1679377406835556</v>
       </c>
       <c r="P638" t="n">
-        <v>0.3619625866413116</v>
+        <v>0.5087574124336243</v>
       </c>
       <c r="Q638" t="n">
-        <v>0.3922915160655975</v>
+        <v>0.3233048617839813</v>
       </c>
       <c r="R638" t="n">
         <v>1</v>
       </c>
       <c r="S638" t="n">
-        <v>0.03141666794895115</v>
+        <v>0.2202958739720858</v>
       </c>
       <c r="T638" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U638" t="n">
-        <v>0.03141666794895115</v>
+        <v>0.2202958739720858</v>
       </c>
       <c r="V638" t="n">
-        <v>0.3922915160655975</v>
+        <v>0.5087574124336243</v>
       </c>
       <c r="W638" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="X638" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="Y638" t="inlineStr"/>
       <c r="Z638" t="n">
-        <v>6.865101531147957</v>
+        <v>6.949704541609837</v>
       </c>
       <c r="AA638" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB638" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC638" t="inlineStr"/>
@@ -64056,197 +64058,195 @@
     <row r="639">
       <c r="A639" s="1" t="inlineStr">
         <is>
-          <t>W4zGoby1</t>
+          <t>6w5RRTN0</t>
         </is>
       </c>
       <c r="B639" s="2" t="n">
-        <v>45620.51041666666</v>
+        <v>45619.60416666666</v>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="E639" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F639" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G639" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="H639" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="I639" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="J639" t="n">
-        <v>0.4139553116424932</v>
+        <v>0.5490012957333573</v>
       </c>
       <c r="K639" t="n">
-        <v>0.2975303802430419</v>
+        <v>0.2316517662484654</v>
       </c>
       <c r="L639" t="n">
-        <v>0.2885143081144649</v>
+        <v>0.2193469380181774</v>
       </c>
       <c r="M639" t="n">
-        <v>0.05031291172595531</v>
+        <v>0.05288400332240517</v>
       </c>
       <c r="N639" t="n">
         <v>0</v>
       </c>
       <c r="O639" t="n">
-        <v>0.2018209844827652</v>
+        <v>0.2694219946861267</v>
       </c>
       <c r="P639" t="n">
-        <v>0.5636378526687622</v>
+        <v>0.3896504938602448</v>
       </c>
       <c r="Q639" t="n">
-        <v>0.2345411628484726</v>
+        <v>0.3409274816513062</v>
       </c>
       <c r="R639" t="n">
         <v>1</v>
       </c>
       <c r="S639" t="n">
-        <v>0.2661074724257203</v>
+        <v>0.1579987276117794</v>
       </c>
       <c r="T639" t="n">
         <v>0</v>
       </c>
       <c r="U639" t="n">
-        <v>0.2661074724257203</v>
+        <v>0.1579987276117794</v>
       </c>
       <c r="V639" t="n">
-        <v>0.5636378526687622</v>
+        <v>0.3896504938602448</v>
       </c>
       <c r="W639" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="X639" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="Y639" t="inlineStr"/>
       <c r="Z639" t="n">
-        <v>9.863662421703339</v>
+        <v>5.108227021536811</v>
       </c>
       <c r="AA639" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB639" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC639" t="n">
-        <v>1</v>
-      </c>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="AC639" t="inlineStr"/>
       <c r="AD639" t="inlineStr"/>
       <c r="AE639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" s="1" t="inlineStr">
         <is>
-          <t>pl4Y7lh3</t>
+          <t>KtV0tTxf</t>
         </is>
       </c>
       <c r="B640" s="2" t="n">
-        <v>45620.60416666666</v>
+        <v>45620.47916666666</v>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="E640" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F640" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G640" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="H640" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I640" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="J640" t="n">
-        <v>0.1354436948624805</v>
+        <v>0.3067869752844252</v>
       </c>
       <c r="K640" t="n">
-        <v>0.210690192008303</v>
+        <v>0.2797175362887406</v>
       </c>
       <c r="L640" t="n">
-        <v>0.6538661131292164</v>
+        <v>0.413495488426834</v>
       </c>
       <c r="M640" t="n">
-        <v>0.05473453749315826</v>
+        <v>0.05148090091576618</v>
       </c>
       <c r="N640" t="n">
         <v>2</v>
       </c>
       <c r="O640" t="n">
-        <v>0.0941070169210434</v>
+        <v>0.2973787784576416</v>
       </c>
       <c r="P640" t="n">
-        <v>0.09887459129095078</v>
+        <v>0.2567306756973267</v>
       </c>
       <c r="Q640" t="n">
-        <v>0.8070184588432312</v>
+        <v>0.4458905756473541</v>
       </c>
       <c r="R640" t="n">
         <v>1</v>
       </c>
       <c r="S640" t="n">
-        <v>0.1531523457140148</v>
+        <v>0.03239508722052009</v>
       </c>
       <c r="T640" t="n">
         <v>2</v>
       </c>
       <c r="U640" t="n">
-        <v>0.1531523457140148</v>
+        <v>0.03239508722052009</v>
       </c>
       <c r="V640" t="n">
-        <v>0.8070184588432312</v>
+        <v>0.4458905756473541</v>
       </c>
       <c r="W640" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="X640" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="Y640" t="inlineStr"/>
       <c r="Z640" t="n">
-        <v>14.12282302975655</v>
+        <v>2.877354622647172</v>
       </c>
       <c r="AA640" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB640" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC640" t="inlineStr"/>
@@ -64256,96 +64256,96 @@
     <row r="641">
       <c r="A641" s="1" t="inlineStr">
         <is>
-          <t>WpvagkwA</t>
+          <t>OEyhrk8s</t>
         </is>
       </c>
       <c r="B641" s="2" t="n">
-        <v>45620.70833333334</v>
+        <v>45620.5625</v>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="E641" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F641" t="n">
-        <v>1481</v>
+        <v>591</v>
       </c>
       <c r="G641" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="H641" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="I641" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="J641" t="n">
-        <v>0.4310344827586207</v>
+        <v>0.5256916996047432</v>
       </c>
       <c r="K641" t="n">
-        <v>0.3160919540229885</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="L641" t="n">
-        <v>0.2528735632183908</v>
+        <v>0.225296442687747</v>
       </c>
       <c r="M641" t="n">
-        <v>0.05454545454545445</v>
+        <v>0.05680868838763575</v>
       </c>
       <c r="N641" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O641" t="n">
-        <v>0.3089075982570648</v>
+        <v>0.4326812624931335</v>
       </c>
       <c r="P641" t="n">
-        <v>0.2107562869787216</v>
+        <v>0.3608728647232056</v>
       </c>
       <c r="Q641" t="n">
-        <v>0.4803360998630524</v>
+        <v>0.2064459025859833</v>
       </c>
       <c r="R641" t="n">
         <v>1</v>
       </c>
       <c r="S641" t="n">
-        <v>0.2274625366446615</v>
+        <v>-0.09301043711160961</v>
       </c>
       <c r="T641" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U641" t="n">
-        <v>0.2274625366446615</v>
+        <v>-0.09301043711160961</v>
       </c>
       <c r="V641" t="n">
-        <v>0.4803360998630524</v>
+        <v>0.4326812624931335</v>
       </c>
       <c r="W641" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="X641" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="Y641" t="inlineStr"/>
       <c r="Z641" t="n">
-        <v>8.405881747603416</v>
+        <v>0.3031975702334755</v>
       </c>
       <c r="AA641" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB641" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC641" t="inlineStr"/>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -65005,78 +65005,78 @@
     <row r="648">
       <c r="A648" s="1" t="inlineStr">
         <is>
-          <t>tQAc65y8</t>
+          <t>j97t2JLs</t>
         </is>
       </c>
       <c r="B648" s="2" t="n">
-        <v>45625.69791666666</v>
+        <v>45625.70833333334</v>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E648" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F648" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G648" t="n">
         <v>2</v>
       </c>
       <c r="H648" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I648" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J648" t="n">
-        <v>0.4727272727272727</v>
+        <v>0.4713975380159305</v>
       </c>
       <c r="K648" t="n">
-        <v>0.2909090909090909</v>
+        <v>0.3041274438812455</v>
       </c>
       <c r="L648" t="n">
-        <v>0.2363636363636364</v>
+        <v>0.224475018102824</v>
       </c>
       <c r="M648" t="n">
-        <v>0.05769230769230771</v>
+        <v>0.0606758832565284</v>
       </c>
       <c r="N648" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O648" t="n">
-        <v>0.3343786122345805</v>
+        <v>0.6795424648395748</v>
       </c>
       <c r="P648" t="n">
-        <v>0.3989291891686038</v>
+        <v>0.05966986528324565</v>
       </c>
       <c r="Q648" t="n">
-        <v>0.2666921985968158</v>
+        <v>0.2607876698771796</v>
       </c>
       <c r="R648" t="n">
         <v>1</v>
       </c>
       <c r="S648" t="n">
-        <v>0.1080200982595129</v>
+        <v>0.2081449268236443</v>
       </c>
       <c r="T648" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U648" t="n">
-        <v>0.1080200982595129</v>
+        <v>0.2081449268236443</v>
       </c>
       <c r="V648" t="n">
-        <v>0.3989291891686038</v>
+        <v>0.6795424648395748</v>
       </c>
       <c r="W648" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="X648" t="inlineStr">
         <is>
@@ -65085,16 +65085,16 @@
       </c>
       <c r="Y648" t="inlineStr"/>
       <c r="Z648" t="n">
-        <v>8.377512972540679</v>
+        <v>4.756797253877023</v>
       </c>
       <c r="AA648" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB648" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC648" t="inlineStr"/>
@@ -65104,78 +65104,78 @@
     <row r="649">
       <c r="A649" s="1" t="inlineStr">
         <is>
-          <t>OlzrEHfE</t>
+          <t>KQGA7ubK</t>
         </is>
       </c>
       <c r="B649" s="2" t="n">
-        <v>45626.45833333334</v>
+        <v>45626.41666666666</v>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E649" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F649" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="H649" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="I649" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J649" t="n">
-        <v>0.4851944345344275</v>
+        <v>0.8145663632007667</v>
       </c>
       <c r="K649" t="n">
-        <v>0.2782732786300393</v>
+        <v>0.1121226641111643</v>
       </c>
       <c r="L649" t="n">
-        <v>0.2365322868355333</v>
+        <v>0.07331097268806899</v>
       </c>
       <c r="M649" t="n">
-        <v>0.05693815987933637</v>
+        <v>0.04927099044746108</v>
       </c>
       <c r="N649" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O649" t="n">
-        <v>0.1538137651670233</v>
+        <v>0.8029938257928729</v>
       </c>
       <c r="P649" t="n">
-        <v>0.3326924613960893</v>
+        <v>0.1347825064321962</v>
       </c>
       <c r="Q649" t="n">
-        <v>0.5134937734368874</v>
+        <v>0.06222366777493086</v>
       </c>
       <c r="R649" t="n">
         <v>1</v>
       </c>
       <c r="S649" t="n">
-        <v>0.2769614866013541</v>
+        <v>-0.01157253740789377</v>
       </c>
       <c r="T649" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U649" t="n">
-        <v>0.2769614866013541</v>
+        <v>-0.01157253740789377</v>
       </c>
       <c r="V649" t="n">
-        <v>0.5134937734368874</v>
+        <v>0.8029938257928729</v>
       </c>
       <c r="W649" t="n">
-        <v>4</v>
+        <v>1.17</v>
       </c>
       <c r="X649" t="inlineStr">
         <is>
@@ -65184,99 +65184,97 @@
       </c>
       <c r="Y649" t="inlineStr"/>
       <c r="Z649" t="n">
-        <v>8.087526931630977</v>
+        <v>5.296925733129084</v>
       </c>
       <c r="AA649" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB649" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC649" t="n">
-        <v>1</v>
-      </c>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC649" t="inlineStr"/>
       <c r="AD649" t="inlineStr"/>
       <c r="AE649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" s="1" t="inlineStr">
         <is>
-          <t>OCIU4DH0</t>
+          <t>WIFl0cjf</t>
         </is>
       </c>
       <c r="B650" s="2" t="n">
-        <v>45626.58333333334</v>
+        <v>45626.51041666666</v>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F650" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G650" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="H650" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I650" t="n">
-        <v>9.5</v>
+        <v>4.75</v>
       </c>
       <c r="J650" t="n">
-        <v>0.6918595241948534</v>
+        <v>0.5240103828682673</v>
       </c>
       <c r="K650" t="n">
-        <v>0.2090953228677779</v>
+        <v>0.2774172615184945</v>
       </c>
       <c r="L650" t="n">
-        <v>0.0990451529373685</v>
+        <v>0.1985723556132381</v>
       </c>
       <c r="M650" t="n">
-        <v>0.06277949776401792</v>
+        <v>0.06019951840385285</v>
       </c>
       <c r="N650" t="n">
         <v>1</v>
       </c>
       <c r="O650" t="n">
-        <v>0.7275980360544261</v>
+        <v>0.639611381544596</v>
       </c>
       <c r="P650" t="n">
-        <v>0.2249092994105007</v>
+        <v>0.1446644112402621</v>
       </c>
       <c r="Q650" t="n">
-        <v>0.0474926645350732</v>
+        <v>0.215724207215142</v>
       </c>
       <c r="R650" t="n">
         <v>1</v>
       </c>
       <c r="S650" t="n">
-        <v>0.03573851185957266</v>
+        <v>0.1156009986763287</v>
       </c>
       <c r="T650" t="n">
         <v>1</v>
       </c>
       <c r="U650" t="n">
-        <v>0.03573851185957266</v>
+        <v>0.1156009986763287</v>
       </c>
       <c r="V650" t="n">
-        <v>0.7275980360544261</v>
+        <v>0.639611381544596</v>
       </c>
       <c r="W650" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="X650" t="inlineStr">
         <is>
@@ -65285,16 +65283,16 @@
       </c>
       <c r="Y650" t="inlineStr"/>
       <c r="Z650" t="n">
-        <v>15.27955875714295</v>
+        <v>4.477279670812171</v>
       </c>
       <c r="AA650" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB650" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC650" t="inlineStr"/>
@@ -65304,78 +65302,78 @@
     <row r="651">
       <c r="A651" s="1" t="inlineStr">
         <is>
-          <t>lIhj8R6e</t>
+          <t>hvDYgCjI</t>
         </is>
       </c>
       <c r="B651" s="2" t="n">
-        <v>45626.69791666666</v>
+        <v>45626.60416666666</v>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F651" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G651" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="H651" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="I651" t="n">
-        <v>5.25</v>
+        <v>2.2</v>
       </c>
       <c r="J651" t="n">
-        <v>0.5755850727387729</v>
+        <v>0.2944881889763779</v>
       </c>
       <c r="K651" t="n">
-        <v>0.243516761543327</v>
+        <v>0.2771653543307087</v>
       </c>
       <c r="L651" t="n">
-        <v>0.1808981657179</v>
+        <v>0.4283464566929133</v>
       </c>
       <c r="M651" t="n">
-        <v>0.05294705294705304</v>
+        <v>0.06116310160427818</v>
       </c>
       <c r="N651" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O651" t="n">
-        <v>0.4360202517077544</v>
+        <v>0.3173727876506836</v>
       </c>
       <c r="P651" t="n">
-        <v>0.3575268233919255</v>
+        <v>0.4097685363727157</v>
       </c>
       <c r="Q651" t="n">
-        <v>0.2064529249003201</v>
+        <v>0.2728586759766006</v>
       </c>
       <c r="R651" t="n">
         <v>1</v>
       </c>
       <c r="S651" t="n">
-        <v>-0.1395648210310185</v>
+        <v>0.1326031820420071</v>
       </c>
       <c r="T651" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U651" t="n">
-        <v>-0.1395648210310185</v>
+        <v>0.1326031820420071</v>
       </c>
       <c r="V651" t="n">
-        <v>0.4360202517077544</v>
+        <v>0.4097685363727157</v>
       </c>
       <c r="W651" t="n">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
       <c r="X651" t="inlineStr">
         <is>
@@ -65384,97 +65382,99 @@
       </c>
       <c r="Y651" t="inlineStr"/>
       <c r="Z651" t="n">
-        <v>0</v>
+        <v>2.151284815956757</v>
       </c>
       <c r="AA651" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB651" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC651" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC651" t="n">
+        <v>1</v>
+      </c>
       <c r="AD651" t="inlineStr"/>
       <c r="AE651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" s="1" t="inlineStr">
         <is>
-          <t>2J5dJCWg</t>
+          <t>0b75dFkJ</t>
         </is>
       </c>
       <c r="B652" s="2" t="n">
-        <v>45627.35416666666</v>
+        <v>45626.70833333334</v>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F652" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G652" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H652" t="n">
+        <v>4</v>
+      </c>
+      <c r="I652" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J652" t="n">
+        <v>0.1437125748502994</v>
+      </c>
+      <c r="K652" t="n">
+        <v>0.2335329341317365</v>
+      </c>
+      <c r="L652" t="n">
+        <v>0.6227544910179641</v>
+      </c>
+      <c r="M652" t="n">
+        <v>0.07051282051282048</v>
+      </c>
+      <c r="N652" t="n">
         <v>2</v>
       </c>
-      <c r="H652" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I652" t="n">
-        <v>4</v>
-      </c>
-      <c r="J652" t="n">
-        <v>0.4748201438848921</v>
-      </c>
-      <c r="K652" t="n">
-        <v>0.2877697841726619</v>
-      </c>
-      <c r="L652" t="n">
-        <v>0.2374100719424461</v>
-      </c>
-      <c r="M652" t="n">
-        <v>0.05303030303030298</v>
-      </c>
-      <c r="N652" t="n">
-        <v>1</v>
-      </c>
       <c r="O652" t="n">
-        <v>0.3952751672617327</v>
+        <v>0.1040452703598607</v>
       </c>
       <c r="P652" t="n">
-        <v>0.3068441819132643</v>
+        <v>0.2209607119396674</v>
       </c>
       <c r="Q652" t="n">
-        <v>0.297880650825003</v>
+        <v>0.6749940177004718</v>
       </c>
       <c r="R652" t="n">
         <v>1</v>
       </c>
       <c r="S652" t="n">
-        <v>-0.0795449766231594</v>
+        <v>0.05223952668250775</v>
       </c>
       <c r="T652" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U652" t="n">
-        <v>-0.0795449766231594</v>
+        <v>0.05223952668250775</v>
       </c>
       <c r="V652" t="n">
-        <v>0.3952751672617327</v>
+        <v>0.6749940177004718</v>
       </c>
       <c r="W652" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="X652" t="inlineStr">
         <is>
@@ -65483,16 +65483,16 @@
       </c>
       <c r="Y652" t="inlineStr"/>
       <c r="Z652" t="n">
-        <v>1.619000476150998</v>
+        <v>4.724958123903303</v>
       </c>
       <c r="AA652" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB652" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC652" t="inlineStr"/>
@@ -65502,75 +65502,75 @@
     <row r="653">
       <c r="A653" s="1" t="inlineStr">
         <is>
-          <t>rFYV2inD</t>
+          <t>bgZVCzz0</t>
         </is>
       </c>
       <c r="B653" s="2" t="n">
-        <v>45627.45833333334</v>
+        <v>45627.41666666666</v>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E653" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F653" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G653" t="n">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="H653" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I653" t="n">
-        <v>1.85</v>
+        <v>4.1</v>
       </c>
       <c r="J653" t="n">
-        <v>0.2356687898089173</v>
+        <v>0.5088777796931563</v>
       </c>
       <c r="K653" t="n">
-        <v>0.2547770700636943</v>
+        <v>0.2615066367867609</v>
       </c>
       <c r="L653" t="n">
-        <v>0.5095541401273886</v>
+        <v>0.2296155835200828</v>
       </c>
       <c r="M653" t="n">
-        <v>0.06081081081081052</v>
+        <v>0.06222075734270849</v>
       </c>
       <c r="N653" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O653" t="n">
-        <v>0.1866290639078643</v>
+        <v>0.4961890919825087</v>
       </c>
       <c r="P653" t="n">
-        <v>0.2934921049291458</v>
+        <v>0.2818342886703442</v>
       </c>
       <c r="Q653" t="n">
-        <v>0.5198788311629898</v>
+        <v>0.2219766193471472</v>
       </c>
       <c r="R653" t="n">
         <v>1</v>
       </c>
       <c r="S653" t="n">
-        <v>0.01032469103560119</v>
+        <v>-0.01268868771064763</v>
       </c>
       <c r="T653" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U653" t="n">
-        <v>0.01032469103560119</v>
+        <v>-0.01268868771064763</v>
       </c>
       <c r="V653" t="n">
-        <v>0.5198788311629898</v>
+        <v>0.4961890919825087</v>
       </c>
       <c r="W653" t="n">
         <v>1.85</v>
@@ -65582,16 +65582,16 @@
       </c>
       <c r="Y653" t="inlineStr"/>
       <c r="Z653" t="n">
-        <v>10.91745545442279</v>
+        <v>3.118040387979427</v>
       </c>
       <c r="AA653" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB653" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC653" t="inlineStr"/>
@@ -65601,78 +65601,78 @@
     <row r="654">
       <c r="A654" s="1" t="inlineStr">
         <is>
-          <t>fg2lLY1s</t>
+          <t>CxyOEd5m</t>
         </is>
       </c>
       <c r="B654" s="2" t="n">
-        <v>45627.45833333334</v>
+        <v>45627.51041666666</v>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E654" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F654" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G654" t="n">
-        <v>4.75</v>
+        <v>1.33</v>
       </c>
       <c r="H654" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="I654" t="n">
-        <v>1.83</v>
+        <v>7.5</v>
       </c>
       <c r="J654" t="n">
-        <v>0.2002929388852227</v>
+        <v>0.7046463956269218</v>
       </c>
       <c r="K654" t="n">
-        <v>0.2798210175602376</v>
+        <v>0.1703963102152375</v>
       </c>
       <c r="L654" t="n">
-        <v>0.5198860435545397</v>
+        <v>0.1249572941578408</v>
       </c>
       <c r="M654" t="n">
-        <v>0.0510920502799912</v>
+        <v>0.06703121439963544</v>
       </c>
       <c r="N654" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O654" t="n">
-        <v>0.0965133207350658</v>
+        <v>0.8416286955283455</v>
       </c>
       <c r="P654" t="n">
-        <v>0.279520901609035</v>
+        <v>0.07555601743385819</v>
       </c>
       <c r="Q654" t="n">
-        <v>0.6239657776558992</v>
+        <v>0.08281528703779631</v>
       </c>
       <c r="R654" t="n">
         <v>1</v>
       </c>
       <c r="S654" t="n">
-        <v>0.1040797341013595</v>
+        <v>0.1369822999014237</v>
       </c>
       <c r="T654" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U654" t="n">
-        <v>0.1040797341013595</v>
+        <v>0.1369822999014237</v>
       </c>
       <c r="V654" t="n">
-        <v>0.6239657776558992</v>
+        <v>0.8416286955283455</v>
       </c>
       <c r="W654" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="X654" t="inlineStr">
         <is>
@@ -65681,16 +65681,16 @@
       </c>
       <c r="Y654" t="inlineStr"/>
       <c r="Z654" t="n">
-        <v>13.10328133077388</v>
+        <v>5.891400868698418</v>
       </c>
       <c r="AA654" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB654" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC654" t="inlineStr"/>
@@ -65700,78 +65700,78 @@
     <row r="655">
       <c r="A655" s="1" t="inlineStr">
         <is>
-          <t>WEwjCePQ</t>
+          <t>4WDdbyL6</t>
         </is>
       </c>
       <c r="B655" s="2" t="n">
-        <v>45627.58333333334</v>
+        <v>45627.60416666666</v>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="E655" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F655" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G655" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="H655" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="I655" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J655" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.3355537052456287</v>
       </c>
       <c r="K655" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.3030807660283097</v>
       </c>
       <c r="L655" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.3613655287260616</v>
       </c>
       <c r="M655" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.06433888691953205</v>
       </c>
       <c r="N655" t="n">
         <v>2</v>
       </c>
       <c r="O655" t="n">
-        <v>0.1446087215957911</v>
+        <v>0.3097596603204356</v>
       </c>
       <c r="P655" t="n">
-        <v>0.3339116150701119</v>
+        <v>0.1600008455595573</v>
       </c>
       <c r="Q655" t="n">
-        <v>0.5214796633340969</v>
+        <v>0.5302394941200071</v>
       </c>
       <c r="R655" t="n">
         <v>1</v>
       </c>
       <c r="S655" t="n">
-        <v>0.04779545280778114</v>
+        <v>0.1688739653939456</v>
       </c>
       <c r="T655" t="n">
         <v>2</v>
       </c>
       <c r="U655" t="n">
-        <v>0.04779545280778114</v>
+        <v>0.1688739653939456</v>
       </c>
       <c r="V655" t="n">
-        <v>0.5214796633340969</v>
+        <v>0.5302394941200071</v>
       </c>
       <c r="W655" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="X655" t="inlineStr">
         <is>
@@ -65780,16 +65780,16 @@
       </c>
       <c r="Y655" t="inlineStr"/>
       <c r="Z655" t="n">
-        <v>10.95107293001604</v>
+        <v>3.71167645884005</v>
       </c>
       <c r="AA655" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB655" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC655" t="inlineStr"/>
@@ -65799,78 +65799,78 @@
     <row r="656">
       <c r="A656" s="1" t="inlineStr">
         <is>
-          <t>jaKM6Znl</t>
+          <t>S4aiKIsQ</t>
         </is>
       </c>
       <c r="B656" s="2" t="n">
-        <v>45627.69791666666</v>
+        <v>45627.70833333334</v>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E656" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F656" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G656" t="n">
-        <v>5.25</v>
+        <v>1.8</v>
       </c>
       <c r="H656" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I656" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J656" t="n">
-        <v>0.1802916482545294</v>
+        <v>0.5293737895416398</v>
       </c>
       <c r="K656" t="n">
-        <v>0.2629253203711887</v>
+        <v>0.2382182052937379</v>
       </c>
       <c r="L656" t="n">
-        <v>0.556783031374282</v>
+        <v>0.2324080051646223</v>
       </c>
       <c r="M656" t="n">
-        <v>0.05648926237161533</v>
+        <v>0.04945799457994582</v>
       </c>
       <c r="N656" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O656" t="n">
-        <v>0.09590784308916961</v>
+        <v>0.3721768940064084</v>
       </c>
       <c r="P656" t="n">
-        <v>0.3267320171868486</v>
+        <v>0.3208198570125288</v>
       </c>
       <c r="Q656" t="n">
-        <v>0.5773601397239818</v>
+        <v>0.3070032489810627</v>
       </c>
       <c r="R656" t="n">
         <v>1</v>
       </c>
       <c r="S656" t="n">
-        <v>0.02057710834969984</v>
+        <v>-0.1571968955352314</v>
       </c>
       <c r="T656" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U656" t="n">
-        <v>0.02057710834969984</v>
+        <v>-0.1571968955352314</v>
       </c>
       <c r="V656" t="n">
-        <v>0.5773601397239818</v>
+        <v>0.3721768940064084</v>
       </c>
       <c r="W656" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="X656" t="inlineStr">
         <is>
@@ -65879,97 +65879,99 @@
       </c>
       <c r="Y656" t="inlineStr"/>
       <c r="Z656" t="n">
-        <v>12.12456293420362</v>
+        <v>0</v>
       </c>
       <c r="AA656" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB656" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC656" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC656" t="n">
+        <v>1</v>
+      </c>
       <c r="AD656" t="inlineStr"/>
       <c r="AE656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" s="1" t="inlineStr">
         <is>
-          <t>ALQHQfvK</t>
+          <t>fLSvBE4C</t>
         </is>
       </c>
       <c r="B657" s="2" t="n">
-        <v>45628.69791666666</v>
+        <v>45628.70833333334</v>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E657" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F657" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G657" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="H657" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I657" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J657" t="n">
-        <v>0.3236831523924407</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="K657" t="n">
-        <v>0.268194611982308</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="L657" t="n">
-        <v>0.4081222356252514</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="M657" t="n">
-        <v>0.06532448061683449</v>
+        <v>0.06442577030812324</v>
       </c>
       <c r="N657" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O657" t="n">
-        <v>0.2672128383073122</v>
+        <v>0.5696353676644</v>
       </c>
       <c r="P657" t="n">
-        <v>0.2924487814297281</v>
+        <v>0.1454423329213267</v>
       </c>
       <c r="Q657" t="n">
-        <v>0.4403383802629597</v>
+        <v>0.2849222994142732</v>
       </c>
       <c r="R657" t="n">
         <v>1</v>
       </c>
       <c r="S657" t="n">
-        <v>0.03221614463770833</v>
+        <v>0.1222669466117685</v>
       </c>
       <c r="T657" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U657" t="n">
-        <v>0.03221614463770833</v>
+        <v>0.1222669466117685</v>
       </c>
       <c r="V657" t="n">
-        <v>0.4403383802629597</v>
+        <v>0.5696353676644</v>
       </c>
       <c r="W657" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="X657" t="inlineStr">
         <is>
@@ -65978,97 +65980,99 @@
       </c>
       <c r="Y657" t="inlineStr"/>
       <c r="Z657" t="n">
-        <v>9.247105985522154</v>
+        <v>2.9905856802381</v>
       </c>
       <c r="AA657" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB657" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC657" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC657" t="n">
+        <v>1</v>
+      </c>
       <c r="AD657" t="inlineStr"/>
       <c r="AE657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" s="1" t="inlineStr">
         <is>
-          <t>xxKvWkGa</t>
+          <t>48cSecHb</t>
         </is>
       </c>
       <c r="B658" s="2" t="n">
-        <v>45632.60416666666</v>
+        <v>45629.625</v>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F658" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G658" t="n">
-        <v>1.18</v>
+        <v>5</v>
       </c>
       <c r="H658" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="I658" t="n">
-        <v>13</v>
+        <v>1.73</v>
       </c>
       <c r="J658" t="n">
-        <v>0.8012162051113485</v>
+        <v>0.1880142834963515</v>
       </c>
       <c r="K658" t="n">
-        <v>0.1260580162708521</v>
+        <v>0.2685918335662164</v>
       </c>
       <c r="L658" t="n">
-        <v>0.07272577861779932</v>
+        <v>0.5433938829374321</v>
       </c>
       <c r="M658" t="n">
-        <v>0.05771403737505443</v>
+        <v>0.06374896779521055</v>
       </c>
       <c r="N658" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O658" t="n">
-        <v>0.6365045278836701</v>
+        <v>0.2071690537412557</v>
       </c>
       <c r="P658" t="n">
-        <v>0.2501552136244563</v>
+        <v>0.1284957469970615</v>
       </c>
       <c r="Q658" t="n">
-        <v>0.1133402584918736</v>
+        <v>0.6643351992616827</v>
       </c>
       <c r="R658" t="n">
         <v>1</v>
       </c>
       <c r="S658" t="n">
-        <v>-0.1647116772276784</v>
+        <v>0.1209413163242506</v>
       </c>
       <c r="T658" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U658" t="n">
-        <v>-0.1647116772276784</v>
+        <v>0.1209413163242506</v>
       </c>
       <c r="V658" t="n">
-        <v>0.6365045278836701</v>
+        <v>0.6643351992616827</v>
       </c>
       <c r="W658" t="n">
-        <v>1.18</v>
+        <v>1.73</v>
       </c>
       <c r="X658" t="inlineStr">
         <is>
@@ -66077,16 +66081,16 @@
       </c>
       <c r="Y658" t="inlineStr"/>
       <c r="Z658" t="n">
-        <v>0</v>
+        <v>4.650346394831779</v>
       </c>
       <c r="AA658" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB658" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC658" t="inlineStr"/>
@@ -66096,78 +66100,78 @@
     <row r="659">
       <c r="A659" s="1" t="inlineStr">
         <is>
-          <t>dIb5Hj16</t>
+          <t>8Ohqd6Bs</t>
         </is>
       </c>
       <c r="B659" s="2" t="n">
-        <v>45632.69791666666</v>
+        <v>45630.70833333334</v>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F659" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G659" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="H659" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I659" t="n">
-        <v>3.8</v>
+        <v>1.95</v>
       </c>
       <c r="J659" t="n">
-        <v>0.472913616398243</v>
+        <v>0.2478663519157435</v>
       </c>
       <c r="K659" t="n">
-        <v>0.2781844802342606</v>
+        <v>0.2691120392228073</v>
       </c>
       <c r="L659" t="n">
-        <v>0.2489019033674963</v>
+        <v>0.483021608861449</v>
       </c>
       <c r="M659" t="n">
-        <v>0.05727554179566563</v>
+        <v>0.06169269327164084</v>
       </c>
       <c r="N659" t="n">
         <v>2</v>
       </c>
       <c r="O659" t="n">
-        <v>0.2227412088117584</v>
+        <v>0.09791287116682856</v>
       </c>
       <c r="P659" t="n">
-        <v>0.2953545539303223</v>
+        <v>0.4264171676190112</v>
       </c>
       <c r="Q659" t="n">
-        <v>0.4819042372579194</v>
+        <v>0.4756699612141602</v>
       </c>
       <c r="R659" t="n">
         <v>1</v>
       </c>
       <c r="S659" t="n">
-        <v>0.233002333890423</v>
+        <v>-0.00735164764728885</v>
       </c>
       <c r="T659" t="n">
         <v>2</v>
       </c>
       <c r="U659" t="n">
-        <v>0.233002333890423</v>
+        <v>-0.00735164764728885</v>
       </c>
       <c r="V659" t="n">
-        <v>0.4819042372579194</v>
+        <v>0.4756699612141602</v>
       </c>
       <c r="W659" t="n">
-        <v>3.8</v>
+        <v>1.95</v>
       </c>
       <c r="X659" t="inlineStr">
         <is>
@@ -66176,16 +66180,16 @@
       </c>
       <c r="Y659" t="inlineStr"/>
       <c r="Z659" t="n">
-        <v>10.11998898241631</v>
+        <v>3.123843594375033</v>
       </c>
       <c r="AA659" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB659" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC659" t="inlineStr"/>
@@ -66195,78 +66199,78 @@
     <row r="660">
       <c r="A660" s="1" t="inlineStr">
         <is>
-          <t>pvu0wYNP</t>
+          <t>Cda5RZlg</t>
         </is>
       </c>
       <c r="B660" s="2" t="n">
-        <v>45633.45833333334</v>
+        <v>45632.70833333334</v>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F660" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G660" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="H660" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I660" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="J660" t="n">
-        <v>0.3463687150837989</v>
+        <v>0.4982964224872232</v>
       </c>
       <c r="K660" t="n">
-        <v>0.3072625698324022</v>
+        <v>0.2913117546848382</v>
       </c>
       <c r="L660" t="n">
-        <v>0.3463687150837989</v>
+        <v>0.2103918228279387</v>
       </c>
       <c r="M660" t="n">
-        <v>0.04985337243401755</v>
+        <v>0.0562303193882141</v>
       </c>
       <c r="N660" t="n">
         <v>2</v>
       </c>
       <c r="O660" t="n">
-        <v>0.2145881076473719</v>
+        <v>0.214039901620808</v>
       </c>
       <c r="P660" t="n">
-        <v>0.3785773100882495</v>
+        <v>0.3328445469426146</v>
       </c>
       <c r="Q660" t="n">
-        <v>0.4068345822643785</v>
+        <v>0.4531155514365773</v>
       </c>
       <c r="R660" t="n">
         <v>1</v>
       </c>
       <c r="S660" t="n">
-        <v>0.06046586718057961</v>
+        <v>0.2427237286086386</v>
       </c>
       <c r="T660" t="n">
         <v>2</v>
       </c>
       <c r="U660" t="n">
-        <v>0.06046586718057961</v>
+        <v>0.2427237286086386</v>
       </c>
       <c r="V660" t="n">
-        <v>0.4068345822643785</v>
+        <v>0.4531155514365773</v>
       </c>
       <c r="W660" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="X660" t="inlineStr">
         <is>
@@ -66275,16 +66279,16 @@
       </c>
       <c r="Y660" t="inlineStr"/>
       <c r="Z660" t="n">
-        <v>8.543526227551949</v>
+        <v>3.171808860056041</v>
       </c>
       <c r="AA660" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB660" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC660" t="inlineStr"/>
@@ -66294,78 +66298,78 @@
     <row r="661">
       <c r="A661" s="1" t="inlineStr">
         <is>
-          <t>A3XoUTpC</t>
+          <t>txiMNilI</t>
         </is>
       </c>
       <c r="B661" s="2" t="n">
-        <v>45633.58333333334</v>
+        <v>45633.41666666666</v>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F661" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G661" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H661" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I661" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="J661" t="n">
-        <v>0.5539358600583091</v>
+        <v>0.5220012055455093</v>
       </c>
       <c r="K661" t="n">
-        <v>0.2478134110787172</v>
+        <v>0.2610006027727547</v>
       </c>
       <c r="L661" t="n">
-        <v>0.1982507288629737</v>
+        <v>0.216998191681736</v>
       </c>
       <c r="M661" t="n">
-        <v>0.0619195046439629</v>
+        <v>0.0642802155504234</v>
       </c>
       <c r="N661" t="n">
         <v>1</v>
       </c>
       <c r="O661" t="n">
-        <v>0.4212909115101407</v>
+        <v>0.4417636402217124</v>
       </c>
       <c r="P661" t="n">
-        <v>0.3903068946087573</v>
+        <v>0.3295331068623175</v>
       </c>
       <c r="Q661" t="n">
-        <v>0.1884021938811019</v>
+        <v>0.22870325291597</v>
       </c>
       <c r="R661" t="n">
         <v>1</v>
       </c>
       <c r="S661" t="n">
-        <v>-0.1326449485481684</v>
+        <v>-0.08023756532379694</v>
       </c>
       <c r="T661" t="n">
         <v>1</v>
       </c>
       <c r="U661" t="n">
-        <v>-0.1326449485481684</v>
+        <v>-0.08023756532379694</v>
       </c>
       <c r="V661" t="n">
-        <v>0.4212909115101407</v>
+        <v>0.4417636402217124</v>
       </c>
       <c r="W661" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="X661" t="inlineStr">
         <is>
@@ -66374,16 +66378,16 @@
       </c>
       <c r="Y661" t="inlineStr"/>
       <c r="Z661" t="n">
-        <v>0</v>
+        <v>0.8456936524856722</v>
       </c>
       <c r="AA661" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB661" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC661" t="inlineStr"/>
@@ -66393,78 +66397,78 @@
     <row r="662">
       <c r="A662" s="1" t="inlineStr">
         <is>
-          <t>I9fDpkVh</t>
+          <t>hGKvtZ3n</t>
         </is>
       </c>
       <c r="B662" s="2" t="n">
-        <v>45633.69791666666</v>
+        <v>45633.51041666666</v>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F662" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G662" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="H662" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="I662" t="n">
-        <v>4.75</v>
+        <v>1.8</v>
       </c>
       <c r="J662" t="n">
-        <v>0.5908776779543885</v>
+        <v>0.2287747839349263</v>
       </c>
       <c r="K662" t="n">
-        <v>0.2100898410504492</v>
+        <v>0.2501270971021861</v>
       </c>
       <c r="L662" t="n">
-        <v>0.1990324809951624</v>
+        <v>0.5210981189628877</v>
       </c>
       <c r="M662" t="n">
-        <v>0.05774853801169577</v>
+        <v>0.06612466124661243</v>
       </c>
       <c r="N662" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O662" t="n">
-        <v>0.4291503770899929</v>
+        <v>0.2277310654352266</v>
       </c>
       <c r="P662" t="n">
-        <v>0.3509085014441618</v>
+        <v>0.1541295286232683</v>
       </c>
       <c r="Q662" t="n">
-        <v>0.2199411214658453</v>
+        <v>0.6181394059415051</v>
       </c>
       <c r="R662" t="n">
         <v>1</v>
       </c>
       <c r="S662" t="n">
-        <v>-0.1617273008643956</v>
+        <v>0.09704128697861736</v>
       </c>
       <c r="T662" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U662" t="n">
-        <v>-0.1617273008643956</v>
+        <v>0.09704128697861736</v>
       </c>
       <c r="V662" t="n">
-        <v>0.4291503770899929</v>
+        <v>0.6181394059415051</v>
       </c>
       <c r="W662" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="X662" t="inlineStr">
         <is>
@@ -66473,97 +66477,99 @@
       </c>
       <c r="Y662" t="inlineStr"/>
       <c r="Z662" t="n">
-        <v>0</v>
+        <v>3.245231881192901</v>
       </c>
       <c r="AA662" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB662" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC662" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC662" t="n">
+        <v>1</v>
+      </c>
       <c r="AD662" t="inlineStr"/>
       <c r="AE662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" s="1" t="inlineStr">
         <is>
-          <t>UVdDFUVI</t>
+          <t>bTkuvDYb</t>
         </is>
       </c>
       <c r="B663" s="2" t="n">
-        <v>45634.35416666666</v>
+        <v>45633.60416666666</v>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E663" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F663" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G663" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="H663" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="I663" t="n">
-        <v>6.25</v>
+        <v>3.4</v>
       </c>
       <c r="J663" t="n">
-        <v>0.6386964914272737</v>
+        <v>0.4093097913322633</v>
       </c>
       <c r="K663" t="n">
-        <v>0.2100601794027478</v>
+        <v>0.3138041733547351</v>
       </c>
       <c r="L663" t="n">
-        <v>0.1512433291699784</v>
+        <v>0.2768860353130016</v>
       </c>
       <c r="M663" t="n">
-        <v>0.0578978978978979</v>
+        <v>0.06223358908780918</v>
       </c>
       <c r="N663" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O663" t="n">
-        <v>0.526693189107853</v>
+        <v>0.1381945149934806</v>
       </c>
       <c r="P663" t="n">
-        <v>0.3645717820130432</v>
+        <v>0.6723033673950275</v>
       </c>
       <c r="Q663" t="n">
-        <v>0.1087350288791037</v>
+        <v>0.1895021176114919</v>
       </c>
       <c r="R663" t="n">
         <v>1</v>
       </c>
       <c r="S663" t="n">
-        <v>-0.1120033023194207</v>
+        <v>0.3584991940402924</v>
       </c>
       <c r="T663" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U663" t="n">
-        <v>-0.1120033023194207</v>
+        <v>0.3584991940402924</v>
       </c>
       <c r="V663" t="n">
-        <v>0.526693189107853</v>
+        <v>0.6723033673950275</v>
       </c>
       <c r="W663" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="X663" t="inlineStr">
         <is>
@@ -66572,16 +66578,16 @@
       </c>
       <c r="Y663" t="inlineStr"/>
       <c r="Z663" t="n">
-        <v>1.652279576433576</v>
+        <v>4.706123571765191</v>
       </c>
       <c r="AA663" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB663" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC663" t="inlineStr"/>
@@ -66591,78 +66597,78 @@
     <row r="664">
       <c r="A664" s="1" t="inlineStr">
         <is>
-          <t>GMVVXBom</t>
+          <t>YBmEPDJ5</t>
         </is>
       </c>
       <c r="B664" s="2" t="n">
-        <v>45634.45833333334</v>
+        <v>45633.70833333334</v>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F664" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G664" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="H664" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="I664" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="J664" t="n">
-        <v>0.3961661341853036</v>
+        <v>0.2089704059251724</v>
       </c>
       <c r="K664" t="n">
-        <v>0.3067092651757188</v>
+        <v>0.2474649543850726</v>
       </c>
       <c r="L664" t="n">
-        <v>0.2971246006389776</v>
+        <v>0.543564639689755</v>
       </c>
       <c r="M664" t="n">
-        <v>0.051747311827957</v>
+        <v>0.06341479903998914</v>
       </c>
       <c r="N664" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O664" t="n">
-        <v>0.4243488981564436</v>
+        <v>0.1046341649382865</v>
       </c>
       <c r="P664" t="n">
-        <v>0.3399222056302907</v>
+        <v>0.2781440526825718</v>
       </c>
       <c r="Q664" t="n">
-        <v>0.2357288962132656</v>
+        <v>0.6172217823791418</v>
       </c>
       <c r="R664" t="n">
         <v>1</v>
       </c>
       <c r="S664" t="n">
-        <v>0.02818276397114</v>
+        <v>0.07365714268938683</v>
       </c>
       <c r="T664" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U664" t="n">
-        <v>0.02818276397114</v>
+        <v>0.07365714268938683</v>
       </c>
       <c r="V664" t="n">
-        <v>0.4243488981564436</v>
+        <v>0.6172217823791418</v>
       </c>
       <c r="W664" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="X664" t="inlineStr">
         <is>
@@ -66671,16 +66677,16 @@
       </c>
       <c r="Y664" t="inlineStr"/>
       <c r="Z664" t="n">
-        <v>8.911326861285314</v>
+        <v>4.320552476653992</v>
       </c>
       <c r="AA664" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB664" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC664" t="inlineStr"/>
@@ -66690,78 +66696,78 @@
     <row r="665">
       <c r="A665" s="1" t="inlineStr">
         <is>
-          <t>O6cLrTa5</t>
+          <t>x4pVLVIU</t>
         </is>
       </c>
       <c r="B665" s="2" t="n">
-        <v>45634.58333333334</v>
+        <v>45634.41666666666</v>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E665" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F665" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G665" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="H665" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I665" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="J665" t="n">
-        <v>0.3401778496362166</v>
+        <v>0.2503639010189229</v>
       </c>
       <c r="K665" t="n">
-        <v>0.2976556184316895</v>
+        <v>0.3129548762736535</v>
       </c>
       <c r="L665" t="n">
-        <v>0.3621665319320937</v>
+        <v>0.4366812227074235</v>
       </c>
       <c r="M665" t="n">
-        <v>0.04987099402498663</v>
+        <v>0.06511627906976747</v>
       </c>
       <c r="N665" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O665" t="n">
-        <v>0.3645846543700696</v>
+        <v>0.1339553127540217</v>
       </c>
       <c r="P665" t="n">
-        <v>0.3674452723489626</v>
+        <v>0.2863560337764773</v>
       </c>
       <c r="Q665" t="n">
-        <v>0.2679700732809676</v>
+        <v>0.579688653469501</v>
       </c>
       <c r="R665" t="n">
         <v>1</v>
       </c>
       <c r="S665" t="n">
-        <v>0.0697896539172731</v>
+        <v>0.1430074307620775</v>
       </c>
       <c r="T665" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U665" t="n">
-        <v>0.0697896539172731</v>
+        <v>0.1430074307620775</v>
       </c>
       <c r="V665" t="n">
-        <v>0.3674452723489626</v>
+        <v>0.579688653469501</v>
       </c>
       <c r="W665" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="X665" t="inlineStr">
         <is>
@@ -66770,96 +66776,94 @@
       </c>
       <c r="Y665" t="inlineStr"/>
       <c r="Z665" t="n">
-        <v>5.787263039496161</v>
+        <v>4.057820574286507</v>
       </c>
       <c r="AA665" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB665" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC665" t="n">
-        <v>1</v>
-      </c>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC665" t="inlineStr"/>
       <c r="AD665" t="inlineStr"/>
       <c r="AE665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" s="1" t="inlineStr">
         <is>
-          <t>Ms14nB0t</t>
+          <t>SYQn9hZO</t>
         </is>
       </c>
       <c r="B666" s="2" t="n">
-        <v>45634.69791666666</v>
+        <v>45634.51041666666</v>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F666" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G666" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="H666" t="n">
         <v>3.5</v>
       </c>
       <c r="I666" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J666" t="n">
-        <v>0.5011933174224343</v>
+        <v>0.4569015166058744</v>
       </c>
       <c r="K666" t="n">
-        <v>0.2720763723150358</v>
+        <v>0.2676137454405835</v>
       </c>
       <c r="L666" t="n">
-        <v>0.2267303102625298</v>
+        <v>0.2754847379535419</v>
       </c>
       <c r="M666" t="n">
-        <v>0.05012531328320802</v>
+        <v>0.06763681082188988</v>
       </c>
       <c r="N666" t="n">
         <v>0</v>
       </c>
       <c r="O666" t="n">
-        <v>0.3502423014959015</v>
+        <v>0.2642732261147921</v>
       </c>
       <c r="P666" t="n">
-        <v>0.3721186356344405</v>
+        <v>0.5411720307700715</v>
       </c>
       <c r="Q666" t="n">
-        <v>0.277639062869658</v>
+        <v>0.1945547431151363</v>
       </c>
       <c r="R666" t="n">
         <v>1</v>
       </c>
       <c r="S666" t="n">
-        <v>0.1000422633194047</v>
+        <v>0.2735582853294879</v>
       </c>
       <c r="T666" t="n">
         <v>0</v>
       </c>
       <c r="U666" t="n">
-        <v>0.1000422633194047</v>
+        <v>0.2735582853294879</v>
       </c>
       <c r="V666" t="n">
-        <v>0.3721186356344405</v>
+        <v>0.5411720307700715</v>
       </c>
       <c r="W666" t="n">
         <v>3.5</v>
@@ -66871,16 +66875,16 @@
       </c>
       <c r="Y666" t="inlineStr"/>
       <c r="Z666" t="n">
-        <v>7.81449134832325</v>
+        <v>3.7882042153905</v>
       </c>
       <c r="AA666" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB666" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC666" t="inlineStr"/>
@@ -66890,78 +66894,78 @@
     <row r="667">
       <c r="A667" s="1" t="inlineStr">
         <is>
-          <t>6VQfS7FO</t>
+          <t>6ggmxi3B</t>
         </is>
       </c>
       <c r="B667" s="2" t="n">
-        <v>45635.69791666666</v>
+        <v>45634.60416666666</v>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F667" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G667" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="H667" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="I667" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="J667" t="n">
-        <v>0.3491271820448877</v>
+        <v>0.4564841498559078</v>
       </c>
       <c r="K667" t="n">
-        <v>0.314214463840399</v>
+        <v>0.2835734870317003</v>
       </c>
       <c r="L667" t="n">
-        <v>0.3366583541147132</v>
+        <v>0.2599423631123919</v>
       </c>
       <c r="M667" t="n">
-        <v>0.06084656084656093</v>
+        <v>0.06861295885686136</v>
       </c>
       <c r="N667" t="n">
         <v>1</v>
       </c>
       <c r="O667" t="n">
-        <v>0.5360361378096365</v>
+        <v>0.379156971689786</v>
       </c>
       <c r="P667" t="n">
-        <v>0.3230779713317339</v>
+        <v>0.2754970793912254</v>
       </c>
       <c r="Q667" t="n">
-        <v>0.1408858908586295</v>
+        <v>0.3453459489189886</v>
       </c>
       <c r="R667" t="n">
         <v>1</v>
       </c>
       <c r="S667" t="n">
-        <v>0.1869089557647488</v>
+        <v>-0.07732717816612178</v>
       </c>
       <c r="T667" t="n">
         <v>1</v>
       </c>
       <c r="U667" t="n">
-        <v>0.1869089557647488</v>
+        <v>-0.07732717816612178</v>
       </c>
       <c r="V667" t="n">
-        <v>0.5360361378096365</v>
+        <v>0.379156971689786</v>
       </c>
       <c r="W667" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="X667" t="inlineStr">
         <is>
@@ -66970,16 +66974,16 @@
       </c>
       <c r="Y667" t="inlineStr"/>
       <c r="Z667" t="n">
-        <v>11.25675889400237</v>
+        <v>0.4889378131770922</v>
       </c>
       <c r="AA667" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB667" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC667" t="inlineStr"/>
@@ -66989,20 +66993,20 @@
     <row r="668">
       <c r="A668" s="1" t="inlineStr">
         <is>
-          <t>j97t2JLs</t>
+          <t>6adcTeKt</t>
         </is>
       </c>
       <c r="B668" s="2" t="n">
-        <v>45625.70833333334</v>
+        <v>45634.70833333334</v>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E668" t="n">
@@ -67012,55 +67016,55 @@
         <v>1481</v>
       </c>
       <c r="G668" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="H668" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="I668" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="J668" t="n">
-        <v>0.4713975380159305</v>
+        <v>0.6386964914272737</v>
       </c>
       <c r="K668" t="n">
-        <v>0.3041274438812455</v>
+        <v>0.2100601794027478</v>
       </c>
       <c r="L668" t="n">
-        <v>0.224475018102824</v>
+        <v>0.1512433291699784</v>
       </c>
       <c r="M668" t="n">
-        <v>0.0606758832565284</v>
+        <v>0.0578978978978979</v>
       </c>
       <c r="N668" t="n">
         <v>1</v>
       </c>
       <c r="O668" t="n">
-        <v>0.6795424648395748</v>
+        <v>0.6876294806540308</v>
       </c>
       <c r="P668" t="n">
-        <v>0.05966986528324565</v>
+        <v>0.2239759775707063</v>
       </c>
       <c r="Q668" t="n">
-        <v>0.2607876698771796</v>
+        <v>0.08839454177526286</v>
       </c>
       <c r="R668" t="n">
         <v>1</v>
       </c>
       <c r="S668" t="n">
-        <v>0.2081449268236443</v>
+        <v>0.04893298922675715</v>
       </c>
       <c r="T668" t="n">
         <v>1</v>
       </c>
       <c r="U668" t="n">
-        <v>0.2081449268236443</v>
+        <v>0.04893298922675715</v>
       </c>
       <c r="V668" t="n">
-        <v>0.6795424648395748</v>
+        <v>0.6876294806540308</v>
       </c>
       <c r="W668" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="X668" t="inlineStr">
         <is>
@@ -67069,7 +67073,7 @@
       </c>
       <c r="Y668" t="inlineStr"/>
       <c r="Z668" t="n">
-        <v>4.756797253877023</v>
+        <v>3.610054773433661</v>
       </c>
       <c r="AA668" t="inlineStr">
         <is>
@@ -67081,27 +67085,29 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC668" t="inlineStr"/>
+      <c r="AC668" t="n">
+        <v>1</v>
+      </c>
       <c r="AD668" t="inlineStr"/>
       <c r="AE668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" s="1" t="inlineStr">
         <is>
-          <t>KQGA7ubK</t>
+          <t>QiBthjLU</t>
         </is>
       </c>
       <c r="B669" s="2" t="n">
-        <v>45626.41666666666</v>
+        <v>45635.70833333334</v>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E669" t="n">
@@ -67111,55 +67117,55 @@
         <v>1481</v>
       </c>
       <c r="G669" t="n">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="H669" t="n">
-        <v>8.5</v>
+        <v>3.25</v>
       </c>
       <c r="I669" t="n">
-        <v>13</v>
+        <v>5.75</v>
       </c>
       <c r="J669" t="n">
-        <v>0.8145663632007667</v>
+        <v>0.5455009851857258</v>
       </c>
       <c r="K669" t="n">
-        <v>0.1121226641111643</v>
+        <v>0.2903743705757863</v>
       </c>
       <c r="L669" t="n">
-        <v>0.07331097268806899</v>
+        <v>0.1641246442384879</v>
       </c>
       <c r="M669" t="n">
-        <v>0.04927099044746108</v>
+        <v>0.05964003325149347</v>
       </c>
       <c r="N669" t="n">
         <v>1</v>
       </c>
       <c r="O669" t="n">
-        <v>0.8029938257928729</v>
+        <v>0.5470552261742939</v>
       </c>
       <c r="P669" t="n">
-        <v>0.1347825064321962</v>
+        <v>0.2208072968412841</v>
       </c>
       <c r="Q669" t="n">
-        <v>0.06222366777493086</v>
+        <v>0.232137476984422</v>
       </c>
       <c r="R669" t="n">
         <v>1</v>
       </c>
       <c r="S669" t="n">
-        <v>-0.01157253740789377</v>
+        <v>0.001554240988568156</v>
       </c>
       <c r="T669" t="n">
         <v>1</v>
       </c>
       <c r="U669" t="n">
-        <v>-0.01157253740789377</v>
+        <v>0.001554240988568156</v>
       </c>
       <c r="V669" t="n">
-        <v>0.8029938257928729</v>
+        <v>0.5470552261742939</v>
       </c>
       <c r="W669" t="n">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="X669" t="inlineStr">
         <is>
@@ -67168,7 +67174,7 @@
       </c>
       <c r="Y669" t="inlineStr"/>
       <c r="Z669" t="n">
-        <v>5.296925733129084</v>
+        <v>2.872039937415043</v>
       </c>
       <c r="AA669" t="inlineStr">
         <is>
@@ -67180,85 +67186,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC669" t="inlineStr"/>
+      <c r="AC669" t="n">
+        <v>1</v>
+      </c>
       <c r="AD669" t="inlineStr"/>
       <c r="AE669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" s="1" t="inlineStr">
         <is>
-          <t>WIFl0cjf</t>
+          <t>tQAc65y8</t>
         </is>
       </c>
       <c r="B670" s="2" t="n">
-        <v>45626.51041666666</v>
+        <v>45625.69791666666</v>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E670" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F670" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G670" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H670" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I670" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="J670" t="n">
-        <v>0.5240103828682673</v>
+        <v>0.4727272727272727</v>
       </c>
       <c r="K670" t="n">
-        <v>0.2774172615184945</v>
+        <v>0.2909090909090909</v>
       </c>
       <c r="L670" t="n">
-        <v>0.1985723556132381</v>
+        <v>0.2363636363636364</v>
       </c>
       <c r="M670" t="n">
-        <v>0.06019951840385285</v>
+        <v>0.05769230769230771</v>
       </c>
       <c r="N670" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O670" t="n">
-        <v>0.639611381544596</v>
+        <v>0.3464786187338829</v>
       </c>
       <c r="P670" t="n">
-        <v>0.1446644112402621</v>
+        <v>0.4322170723968437</v>
       </c>
       <c r="Q670" t="n">
-        <v>0.215724207215142</v>
+        <v>0.2213043088692734</v>
       </c>
       <c r="R670" t="n">
         <v>1</v>
       </c>
       <c r="S670" t="n">
-        <v>0.1156009986763287</v>
+        <v>0.1413079814877528</v>
       </c>
       <c r="T670" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U670" t="n">
-        <v>0.1156009986763287</v>
+        <v>0.1413079814877528</v>
       </c>
       <c r="V670" t="n">
-        <v>0.639611381544596</v>
+        <v>0.4322170723968437</v>
       </c>
       <c r="W670" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="X670" t="inlineStr">
         <is>
@@ -67267,16 +67275,16 @@
       </c>
       <c r="Y670" t="inlineStr"/>
       <c r="Z670" t="n">
-        <v>4.477279670812171</v>
+        <v>5.98469399008713</v>
       </c>
       <c r="AA670" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB670" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC670" t="inlineStr"/>
@@ -67286,78 +67294,78 @@
     <row r="671">
       <c r="A671" s="1" t="inlineStr">
         <is>
-          <t>hvDYgCjI</t>
+          <t>OlzrEHfE</t>
         </is>
       </c>
       <c r="B671" s="2" t="n">
-        <v>45626.60416666666</v>
+        <v>45626.45833333334</v>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>como</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E671" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F671" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G671" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="H671" t="n">
         <v>3.4</v>
       </c>
       <c r="I671" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J671" t="n">
-        <v>0.2944881889763779</v>
+        <v>0.4851944345344275</v>
       </c>
       <c r="K671" t="n">
-        <v>0.2771653543307087</v>
+        <v>0.2782732786300393</v>
       </c>
       <c r="L671" t="n">
-        <v>0.4283464566929133</v>
+        <v>0.2365322868355333</v>
       </c>
       <c r="M671" t="n">
-        <v>0.06116310160427818</v>
+        <v>0.05693815987933637</v>
       </c>
       <c r="N671" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O671" t="n">
-        <v>0.3173727876506836</v>
+        <v>0.3562965023670175</v>
       </c>
       <c r="P671" t="n">
-        <v>0.4097685363727157</v>
+        <v>0.2765670089449155</v>
       </c>
       <c r="Q671" t="n">
-        <v>0.2728586759766006</v>
+        <v>0.367136488688067</v>
       </c>
       <c r="R671" t="n">
         <v>1</v>
       </c>
       <c r="S671" t="n">
-        <v>0.1326031820420071</v>
+        <v>0.1306042018525336</v>
       </c>
       <c r="T671" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U671" t="n">
-        <v>0.1326031820420071</v>
+        <v>0.1306042018525336</v>
       </c>
       <c r="V671" t="n">
-        <v>0.4097685363727157</v>
+        <v>0.367136488688067</v>
       </c>
       <c r="W671" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="X671" t="inlineStr">
         <is>
@@ -67366,16 +67374,16 @@
       </c>
       <c r="Y671" t="inlineStr"/>
       <c r="Z671" t="n">
-        <v>2.151284815956757</v>
+        <v>4.002989832441907</v>
       </c>
       <c r="AA671" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB671" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC671" t="n">
@@ -67387,78 +67395,78 @@
     <row r="672">
       <c r="A672" s="1" t="inlineStr">
         <is>
-          <t>0b75dFkJ</t>
+          <t>OCIU4DH0</t>
         </is>
       </c>
       <c r="B672" s="2" t="n">
-        <v>45626.70833333334</v>
+        <v>45626.58333333334</v>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E672" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F672" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G672" t="n">
-        <v>6.5</v>
+        <v>1.36</v>
       </c>
       <c r="H672" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I672" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="J672" t="n">
-        <v>0.1437125748502994</v>
+        <v>0.6918595241948534</v>
       </c>
       <c r="K672" t="n">
-        <v>0.2335329341317365</v>
+        <v>0.2090953228677779</v>
       </c>
       <c r="L672" t="n">
-        <v>0.6227544910179641</v>
+        <v>0.0990451529373685</v>
       </c>
       <c r="M672" t="n">
-        <v>0.07051282051282048</v>
+        <v>0.06277949776401792</v>
       </c>
       <c r="N672" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O672" t="n">
-        <v>0.1040452703598607</v>
+        <v>0.8758564861116346</v>
       </c>
       <c r="P672" t="n">
-        <v>0.2209607119396674</v>
+        <v>0.1095808510520968</v>
       </c>
       <c r="Q672" t="n">
-        <v>0.6749940177004718</v>
+        <v>0.0145626628362686</v>
       </c>
       <c r="R672" t="n">
         <v>1</v>
       </c>
       <c r="S672" t="n">
-        <v>0.05223952668250775</v>
+        <v>0.1839969619167812</v>
       </c>
       <c r="T672" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U672" t="n">
-        <v>0.05223952668250775</v>
+        <v>0.1839969619167812</v>
       </c>
       <c r="V672" t="n">
-        <v>0.6749940177004718</v>
+        <v>0.8758564861116346</v>
       </c>
       <c r="W672" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="X672" t="inlineStr">
         <is>
@@ -67467,16 +67475,16 @@
       </c>
       <c r="Y672" t="inlineStr"/>
       <c r="Z672" t="n">
-        <v>4.724958123903303</v>
+        <v>9.671066002672557</v>
       </c>
       <c r="AA672" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB672" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC672" t="inlineStr"/>
@@ -67486,78 +67494,78 @@
     <row r="673">
       <c r="A673" s="1" t="inlineStr">
         <is>
-          <t>bgZVCzz0</t>
+          <t>lIhj8R6e</t>
         </is>
       </c>
       <c r="B673" s="2" t="n">
-        <v>45627.41666666666</v>
+        <v>45626.69791666666</v>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F673" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G673" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="H673" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I673" t="n">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="J673" t="n">
-        <v>0.5088777796931563</v>
+        <v>0.5755850727387729</v>
       </c>
       <c r="K673" t="n">
-        <v>0.2615066367867609</v>
+        <v>0.243516761543327</v>
       </c>
       <c r="L673" t="n">
-        <v>0.2296155835200828</v>
+        <v>0.1808981657179</v>
       </c>
       <c r="M673" t="n">
-        <v>0.06222075734270849</v>
+        <v>0.05294705294705304</v>
       </c>
       <c r="N673" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O673" t="n">
-        <v>0.4961890919825087</v>
+        <v>0.3838907969951727</v>
       </c>
       <c r="P673" t="n">
-        <v>0.2818342886703442</v>
+        <v>0.4797446191064985</v>
       </c>
       <c r="Q673" t="n">
-        <v>0.2219766193471472</v>
+        <v>0.1363645838983289</v>
       </c>
       <c r="R673" t="n">
         <v>1</v>
       </c>
       <c r="S673" t="n">
-        <v>-0.01268868771064763</v>
+        <v>0.2362278575631715</v>
       </c>
       <c r="T673" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U673" t="n">
-        <v>-0.01268868771064763</v>
+        <v>0.2362278575631715</v>
       </c>
       <c r="V673" t="n">
-        <v>0.4961890919825087</v>
+        <v>0.4797446191064985</v>
       </c>
       <c r="W673" t="n">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="X673" t="inlineStr">
         <is>
@@ -67566,16 +67574,16 @@
       </c>
       <c r="Y673" t="inlineStr"/>
       <c r="Z673" t="n">
-        <v>3.118040387979427</v>
+        <v>8.547936296155108</v>
       </c>
       <c r="AA673" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB673" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC673" t="inlineStr"/>
@@ -67585,78 +67593,78 @@
     <row r="674">
       <c r="A674" s="1" t="inlineStr">
         <is>
-          <t>CxyOEd5m</t>
+          <t>2J5dJCWg</t>
         </is>
       </c>
       <c r="B674" s="2" t="n">
-        <v>45627.51041666666</v>
+        <v>45627.35416666666</v>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="E674" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F674" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G674" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="H674" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="I674" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="J674" t="n">
-        <v>0.7046463956269218</v>
+        <v>0.4748201438848921</v>
       </c>
       <c r="K674" t="n">
-        <v>0.1703963102152375</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="L674" t="n">
-        <v>0.1249572941578408</v>
+        <v>0.2374100719424461</v>
       </c>
       <c r="M674" t="n">
-        <v>0.06703121439963544</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="N674" t="n">
         <v>1</v>
       </c>
       <c r="O674" t="n">
-        <v>0.8416286955283455</v>
+        <v>0.5502918099006705</v>
       </c>
       <c r="P674" t="n">
-        <v>0.07555601743385819</v>
+        <v>0.2377715696004742</v>
       </c>
       <c r="Q674" t="n">
-        <v>0.08281528703779631</v>
+        <v>0.2119366204988552</v>
       </c>
       <c r="R674" t="n">
         <v>1</v>
       </c>
       <c r="S674" t="n">
-        <v>0.1369822999014237</v>
+        <v>0.07547166601577837</v>
       </c>
       <c r="T674" t="n">
         <v>1</v>
       </c>
       <c r="U674" t="n">
-        <v>0.1369822999014237</v>
+        <v>0.07547166601577837</v>
       </c>
       <c r="V674" t="n">
-        <v>0.8416286955283455</v>
+        <v>0.5502918099006705</v>
       </c>
       <c r="W674" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="X674" t="inlineStr">
         <is>
@@ -67665,16 +67673,16 @@
       </c>
       <c r="Y674" t="inlineStr"/>
       <c r="Z674" t="n">
-        <v>5.891400868698418</v>
+        <v>5.113070843782704</v>
       </c>
       <c r="AA674" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB674" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC674" t="inlineStr"/>
@@ -67684,78 +67692,78 @@
     <row r="675">
       <c r="A675" s="1" t="inlineStr">
         <is>
-          <t>4WDdbyL6</t>
+          <t>rFYV2inD</t>
         </is>
       </c>
       <c r="B675" s="2" t="n">
-        <v>45627.60416666666</v>
+        <v>45627.45833333334</v>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F675" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G675" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H675" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="I675" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="J675" t="n">
-        <v>0.3355537052456287</v>
+        <v>0.2356687898089173</v>
       </c>
       <c r="K675" t="n">
-        <v>0.3030807660283097</v>
+        <v>0.2547770700636943</v>
       </c>
       <c r="L675" t="n">
-        <v>0.3613655287260616</v>
+        <v>0.5095541401273886</v>
       </c>
       <c r="M675" t="n">
-        <v>0.06433888691953205</v>
+        <v>0.06081081081081052</v>
       </c>
       <c r="N675" t="n">
         <v>2</v>
       </c>
       <c r="O675" t="n">
-        <v>0.3097596603204356</v>
+        <v>0.1829826560839328</v>
       </c>
       <c r="P675" t="n">
-        <v>0.1600008455595573</v>
+        <v>0.194532258249935</v>
       </c>
       <c r="Q675" t="n">
-        <v>0.5302394941200071</v>
+        <v>0.6224850856661321</v>
       </c>
       <c r="R675" t="n">
         <v>1</v>
       </c>
       <c r="S675" t="n">
-        <v>0.1688739653939456</v>
+        <v>0.1129309455387435</v>
       </c>
       <c r="T675" t="n">
         <v>2</v>
       </c>
       <c r="U675" t="n">
-        <v>0.1688739653939456</v>
+        <v>0.1129309455387435</v>
       </c>
       <c r="V675" t="n">
-        <v>0.5302394941200071</v>
+        <v>0.6224850856661321</v>
       </c>
       <c r="W675" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="X675" t="inlineStr">
         <is>
@@ -67764,16 +67772,16 @@
       </c>
       <c r="Y675" t="inlineStr"/>
       <c r="Z675" t="n">
-        <v>3.71167645884005</v>
+        <v>6.445253206926637</v>
       </c>
       <c r="AA675" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB675" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC675" t="inlineStr"/>
@@ -67783,78 +67791,78 @@
     <row r="676">
       <c r="A676" s="1" t="inlineStr">
         <is>
-          <t>S4aiKIsQ</t>
+          <t>fg2lLY1s</t>
         </is>
       </c>
       <c r="B676" s="2" t="n">
-        <v>45627.70833333334</v>
+        <v>45627.45833333334</v>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F676" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G676" t="n">
-        <v>1.8</v>
+        <v>4.75</v>
       </c>
       <c r="H676" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="I676" t="n">
-        <v>4.1</v>
+        <v>1.83</v>
       </c>
       <c r="J676" t="n">
-        <v>0.5293737895416398</v>
+        <v>0.2002929388852227</v>
       </c>
       <c r="K676" t="n">
-        <v>0.2382182052937379</v>
+        <v>0.2798210175602376</v>
       </c>
       <c r="L676" t="n">
-        <v>0.2324080051646223</v>
+        <v>0.5198860435545397</v>
       </c>
       <c r="M676" t="n">
-        <v>0.04945799457994582</v>
+        <v>0.0510920502799912</v>
       </c>
       <c r="N676" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O676" t="n">
-        <v>0.3721768940064084</v>
+        <v>0.1098262048296866</v>
       </c>
       <c r="P676" t="n">
-        <v>0.3208198570125288</v>
+        <v>0.4382004937361949</v>
       </c>
       <c r="Q676" t="n">
-        <v>0.3070032489810627</v>
+        <v>0.4519733014341185</v>
       </c>
       <c r="R676" t="n">
         <v>1</v>
       </c>
       <c r="S676" t="n">
-        <v>-0.1571968955352314</v>
+        <v>-0.0679127421204212</v>
       </c>
       <c r="T676" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U676" t="n">
-        <v>-0.1571968955352314</v>
+        <v>-0.0679127421204212</v>
       </c>
       <c r="V676" t="n">
-        <v>0.3721768940064084</v>
+        <v>0.4519733014341185</v>
       </c>
       <c r="W676" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X676" t="inlineStr">
         <is>
@@ -67863,99 +67871,97 @@
       </c>
       <c r="Y676" t="inlineStr"/>
       <c r="Z676" t="n">
-        <v>0</v>
+        <v>1.081933997714602</v>
       </c>
       <c r="AA676" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB676" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC676" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC676" t="inlineStr"/>
       <c r="AD676" t="inlineStr"/>
       <c r="AE676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" s="1" t="inlineStr">
         <is>
-          <t>fLSvBE4C</t>
+          <t>WEwjCePQ</t>
         </is>
       </c>
       <c r="B677" s="2" t="n">
-        <v>45628.70833333334</v>
+        <v>45627.58333333334</v>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F677" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G677" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="H677" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I677" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J677" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="K677" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="L677" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="M677" t="n">
-        <v>0.06442577030812324</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N677" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O677" t="n">
-        <v>0.5696353676644</v>
+        <v>0.07101939991427249</v>
       </c>
       <c r="P677" t="n">
-        <v>0.1454423329213267</v>
+        <v>0.3840033678393322</v>
       </c>
       <c r="Q677" t="n">
-        <v>0.2849222994142732</v>
+        <v>0.5449772322463953</v>
       </c>
       <c r="R677" t="n">
         <v>1</v>
       </c>
       <c r="S677" t="n">
-        <v>0.1222669466117685</v>
+        <v>0.07129302172007951</v>
       </c>
       <c r="T677" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U677" t="n">
-        <v>0.1222669466117685</v>
+        <v>0.07129302172007951</v>
       </c>
       <c r="V677" t="n">
-        <v>0.5696353676644</v>
+        <v>0.5449772322463953</v>
       </c>
       <c r="W677" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="X677" t="inlineStr">
         <is>
@@ -67964,99 +67970,97 @@
       </c>
       <c r="Y677" t="inlineStr"/>
       <c r="Z677" t="n">
-        <v>2.9905856802381</v>
+        <v>4.98089591476028</v>
       </c>
       <c r="AA677" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB677" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC677" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC677" t="inlineStr"/>
       <c r="AD677" t="inlineStr"/>
       <c r="AE677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" s="1" t="inlineStr">
         <is>
-          <t>48cSecHb</t>
+          <t>jaKM6Znl</t>
         </is>
       </c>
       <c r="B678" s="2" t="n">
-        <v>45629.625</v>
+        <v>45627.69791666666</v>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F678" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G678" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="H678" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I678" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="J678" t="n">
-        <v>0.1880142834963515</v>
+        <v>0.1802916482545294</v>
       </c>
       <c r="K678" t="n">
-        <v>0.2685918335662164</v>
+        <v>0.2629253203711887</v>
       </c>
       <c r="L678" t="n">
-        <v>0.5433938829374321</v>
+        <v>0.556783031374282</v>
       </c>
       <c r="M678" t="n">
-        <v>0.06374896779521055</v>
+        <v>0.05648926237161533</v>
       </c>
       <c r="N678" t="n">
         <v>2</v>
       </c>
       <c r="O678" t="n">
-        <v>0.2071690537412557</v>
+        <v>0.02501249038420713</v>
       </c>
       <c r="P678" t="n">
-        <v>0.1284957469970615</v>
+        <v>0.4201530308432082</v>
       </c>
       <c r="Q678" t="n">
-        <v>0.6643351992616827</v>
+        <v>0.5548344787725847</v>
       </c>
       <c r="R678" t="n">
         <v>1</v>
       </c>
       <c r="S678" t="n">
-        <v>0.1209413163242506</v>
+        <v>-0.00194855260169724</v>
       </c>
       <c r="T678" t="n">
         <v>2</v>
       </c>
       <c r="U678" t="n">
-        <v>0.1209413163242506</v>
+        <v>-0.00194855260169724</v>
       </c>
       <c r="V678" t="n">
-        <v>0.6643351992616827</v>
+        <v>0.5548344787725847</v>
       </c>
       <c r="W678" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X678" t="inlineStr">
         <is>
@@ -68065,16 +68069,16 @@
       </c>
       <c r="Y678" t="inlineStr"/>
       <c r="Z678" t="n">
-        <v>4.650346394831779</v>
+        <v>3.282241610194775</v>
       </c>
       <c r="AA678" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB678" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC678" t="inlineStr"/>
@@ -68084,78 +68088,78 @@
     <row r="679">
       <c r="A679" s="1" t="inlineStr">
         <is>
-          <t>8Ohqd6Bs</t>
+          <t>ALQHQfvK</t>
         </is>
       </c>
       <c r="B679" s="2" t="n">
-        <v>45630.70833333334</v>
+        <v>45628.69791666666</v>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F679" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G679" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="H679" t="n">
         <v>3.5</v>
       </c>
       <c r="I679" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="J679" t="n">
-        <v>0.2478663519157435</v>
+        <v>0.3236831523924407</v>
       </c>
       <c r="K679" t="n">
-        <v>0.2691120392228073</v>
+        <v>0.268194611982308</v>
       </c>
       <c r="L679" t="n">
-        <v>0.483021608861449</v>
+        <v>0.4081222356252514</v>
       </c>
       <c r="M679" t="n">
-        <v>0.06169269327164084</v>
+        <v>0.06532448061683449</v>
       </c>
       <c r="N679" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O679" t="n">
-        <v>0.09791287116682856</v>
+        <v>0.4008100119953498</v>
       </c>
       <c r="P679" t="n">
-        <v>0.4264171676190112</v>
+        <v>0.4440127221017852</v>
       </c>
       <c r="Q679" t="n">
-        <v>0.4756699612141602</v>
+        <v>0.1551772659028649</v>
       </c>
       <c r="R679" t="n">
         <v>1</v>
       </c>
       <c r="S679" t="n">
-        <v>-0.00735164764728885</v>
+        <v>0.1758181101194772</v>
       </c>
       <c r="T679" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U679" t="n">
-        <v>-0.00735164764728885</v>
+        <v>0.1758181101194772</v>
       </c>
       <c r="V679" t="n">
-        <v>0.4756699612141602</v>
+        <v>0.4440127221017852</v>
       </c>
       <c r="W679" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="X679" t="inlineStr">
         <is>
@@ -68164,16 +68168,16 @@
       </c>
       <c r="Y679" t="inlineStr"/>
       <c r="Z679" t="n">
-        <v>3.123843594375033</v>
+        <v>6.883710975478166</v>
       </c>
       <c r="AA679" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB679" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC679" t="inlineStr"/>
@@ -68183,78 +68187,78 @@
     <row r="680">
       <c r="A680" s="1" t="inlineStr">
         <is>
-          <t>Cda5RZlg</t>
+          <t>xxKvWkGa</t>
         </is>
       </c>
       <c r="B680" s="2" t="n">
-        <v>45632.70833333334</v>
+        <v>45632.60416666666</v>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F680" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G680" t="n">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="H680" t="n">
-        <v>3.25</v>
+        <v>7.5</v>
       </c>
       <c r="I680" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="J680" t="n">
-        <v>0.4982964224872232</v>
+        <v>0.8012162051113485</v>
       </c>
       <c r="K680" t="n">
-        <v>0.2913117546848382</v>
+        <v>0.1260580162708521</v>
       </c>
       <c r="L680" t="n">
-        <v>0.2103918228279387</v>
+        <v>0.07272577861779932</v>
       </c>
       <c r="M680" t="n">
-        <v>0.0562303193882141</v>
+        <v>0.05771403737505443</v>
       </c>
       <c r="N680" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O680" t="n">
-        <v>0.214039901620808</v>
+        <v>0.6819522550436041</v>
       </c>
       <c r="P680" t="n">
-        <v>0.3328445469426146</v>
+        <v>0.2742901711558433</v>
       </c>
       <c r="Q680" t="n">
-        <v>0.4531155514365773</v>
+        <v>0.04375757380055258</v>
       </c>
       <c r="R680" t="n">
         <v>1</v>
       </c>
       <c r="S680" t="n">
-        <v>0.2427237286086386</v>
+        <v>-0.1192639500677444</v>
       </c>
       <c r="T680" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U680" t="n">
-        <v>0.2427237286086386</v>
+        <v>-0.1192639500677444</v>
       </c>
       <c r="V680" t="n">
-        <v>0.4531155514365773</v>
+        <v>0.6819522550436041</v>
       </c>
       <c r="W680" t="n">
-        <v>4.5</v>
+        <v>1.18</v>
       </c>
       <c r="X680" t="inlineStr">
         <is>
@@ -68263,16 +68267,16 @@
       </c>
       <c r="Y680" t="inlineStr"/>
       <c r="Z680" t="n">
-        <v>3.171808860056041</v>
+        <v>1.22937872863576</v>
       </c>
       <c r="AA680" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB680" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC680" t="inlineStr"/>
@@ -68282,78 +68286,78 @@
     <row r="681">
       <c r="A681" s="1" t="inlineStr">
         <is>
-          <t>txiMNilI</t>
+          <t>dIb5Hj16</t>
         </is>
       </c>
       <c r="B681" s="2" t="n">
-        <v>45633.41666666666</v>
+        <v>45632.69791666666</v>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F681" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G681" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H681" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I681" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="J681" t="n">
-        <v>0.5220012055455093</v>
+        <v>0.472913616398243</v>
       </c>
       <c r="K681" t="n">
-        <v>0.2610006027727547</v>
+        <v>0.2781844802342606</v>
       </c>
       <c r="L681" t="n">
-        <v>0.216998191681736</v>
+        <v>0.2489019033674963</v>
       </c>
       <c r="M681" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.05727554179566563</v>
       </c>
       <c r="N681" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O681" t="n">
-        <v>0.4417636402217124</v>
+        <v>0.1524676050625625</v>
       </c>
       <c r="P681" t="n">
-        <v>0.3295331068623175</v>
+        <v>0.402080435051089</v>
       </c>
       <c r="Q681" t="n">
-        <v>0.22870325291597</v>
+        <v>0.4454519598863484</v>
       </c>
       <c r="R681" t="n">
         <v>1</v>
       </c>
       <c r="S681" t="n">
-        <v>-0.08023756532379694</v>
+        <v>0.1965500565188521</v>
       </c>
       <c r="T681" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U681" t="n">
-        <v>-0.08023756532379694</v>
+        <v>0.1965500565188521</v>
       </c>
       <c r="V681" t="n">
-        <v>0.4417636402217124</v>
+        <v>0.4454519598863484</v>
       </c>
       <c r="W681" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="X681" t="inlineStr">
         <is>
@@ -68362,16 +68366,16 @@
       </c>
       <c r="Y681" t="inlineStr"/>
       <c r="Z681" t="n">
-        <v>0.8456936524856722</v>
+        <v>7.389913115770542</v>
       </c>
       <c r="AA681" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB681" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC681" t="inlineStr"/>
@@ -68381,78 +68385,78 @@
     <row r="682">
       <c r="A682" s="1" t="inlineStr">
         <is>
-          <t>hGKvtZ3n</t>
+          <t>pvu0wYNP</t>
         </is>
       </c>
       <c r="B682" s="2" t="n">
-        <v>45633.51041666666</v>
+        <v>45633.45833333334</v>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F682" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G682" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="H682" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="I682" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="J682" t="n">
-        <v>0.2287747839349263</v>
+        <v>0.3463687150837989</v>
       </c>
       <c r="K682" t="n">
-        <v>0.2501270971021861</v>
+        <v>0.3072625698324022</v>
       </c>
       <c r="L682" t="n">
-        <v>0.5210981189628877</v>
+        <v>0.3463687150837989</v>
       </c>
       <c r="M682" t="n">
-        <v>0.06612466124661243</v>
+        <v>0.04985337243401755</v>
       </c>
       <c r="N682" t="n">
         <v>2</v>
       </c>
       <c r="O682" t="n">
-        <v>0.2277310654352266</v>
+        <v>0.2115151381454063</v>
       </c>
       <c r="P682" t="n">
-        <v>0.1541295286232683</v>
+        <v>0.3482433293572979</v>
       </c>
       <c r="Q682" t="n">
-        <v>0.6181394059415051</v>
+        <v>0.4402415324972958</v>
       </c>
       <c r="R682" t="n">
         <v>1</v>
       </c>
       <c r="S682" t="n">
-        <v>0.09704128697861736</v>
+        <v>0.09387281741349685</v>
       </c>
       <c r="T682" t="n">
         <v>2</v>
       </c>
       <c r="U682" t="n">
-        <v>0.09704128697861736</v>
+        <v>0.09387281741349685</v>
       </c>
       <c r="V682" t="n">
-        <v>0.6181394059415051</v>
+        <v>0.4402415324972958</v>
       </c>
       <c r="W682" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="X682" t="inlineStr">
         <is>
@@ -68461,99 +68465,97 @@
       </c>
       <c r="Y682" t="inlineStr"/>
       <c r="Z682" t="n">
-        <v>3.245231881192901</v>
+        <v>4.894396812907699</v>
       </c>
       <c r="AA682" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB682" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC682" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC682" t="inlineStr"/>
       <c r="AD682" t="inlineStr"/>
       <c r="AE682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" s="1" t="inlineStr">
         <is>
-          <t>bTkuvDYb</t>
+          <t>A3XoUTpC</t>
         </is>
       </c>
       <c r="B683" s="2" t="n">
-        <v>45633.60416666666</v>
+        <v>45633.58333333334</v>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E683" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F683" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G683" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="H683" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="I683" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="J683" t="n">
-        <v>0.4093097913322633</v>
+        <v>0.5539358600583091</v>
       </c>
       <c r="K683" t="n">
-        <v>0.3138041733547351</v>
+        <v>0.2478134110787172</v>
       </c>
       <c r="L683" t="n">
-        <v>0.2768860353130016</v>
+        <v>0.1982507288629737</v>
       </c>
       <c r="M683" t="n">
-        <v>0.06223358908780918</v>
+        <v>0.0619195046439629</v>
       </c>
       <c r="N683" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O683" t="n">
-        <v>0.1381945149934806</v>
+        <v>0.4485956599638385</v>
       </c>
       <c r="P683" t="n">
-        <v>0.6723033673950275</v>
+        <v>0.3367607009925253</v>
       </c>
       <c r="Q683" t="n">
-        <v>0.1895021176114919</v>
+        <v>0.2146436390436363</v>
       </c>
       <c r="R683" t="n">
         <v>1</v>
       </c>
       <c r="S683" t="n">
-        <v>0.3584991940402924</v>
+        <v>-0.1053402000944705</v>
       </c>
       <c r="T683" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U683" t="n">
-        <v>0.3584991940402924</v>
+        <v>-0.1053402000944705</v>
       </c>
       <c r="V683" t="n">
-        <v>0.6723033673950275</v>
+        <v>0.4485956599638385</v>
       </c>
       <c r="W683" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="X683" t="inlineStr">
         <is>
@@ -68562,16 +68564,16 @@
       </c>
       <c r="Y683" t="inlineStr"/>
       <c r="Z683" t="n">
-        <v>4.706123571765191</v>
+        <v>0.1634091575157384</v>
       </c>
       <c r="AA683" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB683" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC683" t="inlineStr"/>
@@ -68581,78 +68583,78 @@
     <row r="684">
       <c r="A684" s="1" t="inlineStr">
         <is>
-          <t>YBmEPDJ5</t>
+          <t>I9fDpkVh</t>
         </is>
       </c>
       <c r="B684" s="2" t="n">
-        <v>45633.70833333334</v>
+        <v>45633.69791666666</v>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E684" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F684" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G684" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H684" t="n">
         <v>4.5</v>
       </c>
-      <c r="H684" t="n">
-        <v>3.8</v>
-      </c>
       <c r="I684" t="n">
-        <v>1.73</v>
+        <v>4.75</v>
       </c>
       <c r="J684" t="n">
-        <v>0.2089704059251724</v>
+        <v>0.5908776779543885</v>
       </c>
       <c r="K684" t="n">
-        <v>0.2474649543850726</v>
+        <v>0.2100898410504492</v>
       </c>
       <c r="L684" t="n">
-        <v>0.543564639689755</v>
+        <v>0.1990324809951624</v>
       </c>
       <c r="M684" t="n">
-        <v>0.06341479903998914</v>
+        <v>0.05774853801169577</v>
       </c>
       <c r="N684" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O684" t="n">
-        <v>0.1046341649382865</v>
+        <v>0.6709779833537367</v>
       </c>
       <c r="P684" t="n">
-        <v>0.2781440526825718</v>
+        <v>0.2498808355915251</v>
       </c>
       <c r="Q684" t="n">
-        <v>0.6172217823791418</v>
+        <v>0.07914118105473826</v>
       </c>
       <c r="R684" t="n">
         <v>1</v>
       </c>
       <c r="S684" t="n">
-        <v>0.07365714268938683</v>
+        <v>0.0801003053993482</v>
       </c>
       <c r="T684" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U684" t="n">
-        <v>0.07365714268938683</v>
+        <v>0.0801003053993482</v>
       </c>
       <c r="V684" t="n">
-        <v>0.6172217823791418</v>
+        <v>0.6709779833537367</v>
       </c>
       <c r="W684" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="X684" t="inlineStr">
         <is>
@@ -68661,16 +68663,16 @@
       </c>
       <c r="Y684" t="inlineStr"/>
       <c r="Z684" t="n">
-        <v>4.320552476653992</v>
+        <v>5.948275229706777</v>
       </c>
       <c r="AA684" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB684" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC684" t="inlineStr"/>
@@ -68680,78 +68682,78 @@
     <row r="685">
       <c r="A685" s="1" t="inlineStr">
         <is>
-          <t>x4pVLVIU</t>
+          <t>UVdDFUVI</t>
         </is>
       </c>
       <c r="B685" s="2" t="n">
-        <v>45634.41666666666</v>
+        <v>45634.35416666666</v>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E685" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F685" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G685" t="n">
-        <v>3.75</v>
+        <v>1.48</v>
       </c>
       <c r="H685" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="I685" t="n">
-        <v>2.15</v>
+        <v>6.25</v>
       </c>
       <c r="J685" t="n">
-        <v>0.2503639010189229</v>
+        <v>0.6386964914272737</v>
       </c>
       <c r="K685" t="n">
-        <v>0.3129548762736535</v>
+        <v>0.2100601794027478</v>
       </c>
       <c r="L685" t="n">
-        <v>0.4366812227074235</v>
+        <v>0.1512433291699784</v>
       </c>
       <c r="M685" t="n">
-        <v>0.06511627906976747</v>
+        <v>0.0578978978978979</v>
       </c>
       <c r="N685" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O685" t="n">
-        <v>0.1339553127540217</v>
+        <v>0.4956919986152321</v>
       </c>
       <c r="P685" t="n">
-        <v>0.2863560337764773</v>
+        <v>0.3861540012743248</v>
       </c>
       <c r="Q685" t="n">
-        <v>0.579688653469501</v>
+        <v>0.1181540001104432</v>
       </c>
       <c r="R685" t="n">
         <v>1</v>
       </c>
       <c r="S685" t="n">
-        <v>0.1430074307620775</v>
+        <v>-0.1430044928120416</v>
       </c>
       <c r="T685" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U685" t="n">
-        <v>0.1430074307620775</v>
+        <v>-0.1430044928120416</v>
       </c>
       <c r="V685" t="n">
-        <v>0.579688653469501</v>
+        <v>0.4956919986152321</v>
       </c>
       <c r="W685" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="X685" t="inlineStr">
         <is>
@@ -68760,16 +68762,16 @@
       </c>
       <c r="Y685" t="inlineStr"/>
       <c r="Z685" t="n">
-        <v>4.057820574286507</v>
+        <v>0</v>
       </c>
       <c r="AA685" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB685" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC685" t="inlineStr"/>
@@ -68779,78 +68781,78 @@
     <row r="686">
       <c r="A686" s="1" t="inlineStr">
         <is>
-          <t>SYQn9hZO</t>
+          <t>GMVVXBom</t>
         </is>
       </c>
       <c r="B686" s="2" t="n">
-        <v>45634.51041666666</v>
+        <v>45634.45833333334</v>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F686" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G686" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="H686" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I686" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J686" t="n">
-        <v>0.4569015166058744</v>
+        <v>0.3961661341853036</v>
       </c>
       <c r="K686" t="n">
-        <v>0.2676137454405835</v>
+        <v>0.3067092651757188</v>
       </c>
       <c r="L686" t="n">
-        <v>0.2754847379535419</v>
+        <v>0.2971246006389776</v>
       </c>
       <c r="M686" t="n">
-        <v>0.06763681082188988</v>
+        <v>0.051747311827957</v>
       </c>
       <c r="N686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O686" t="n">
-        <v>0.2642732261147921</v>
+        <v>0.4429670897822505</v>
       </c>
       <c r="P686" t="n">
-        <v>0.5411720307700715</v>
+        <v>0.4301544548924254</v>
       </c>
       <c r="Q686" t="n">
-        <v>0.1945547431151363</v>
+        <v>0.1268784553253241</v>
       </c>
       <c r="R686" t="n">
         <v>1</v>
       </c>
       <c r="S686" t="n">
-        <v>0.2735582853294879</v>
+        <v>0.04680095559694691</v>
       </c>
       <c r="T686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U686" t="n">
-        <v>0.2735582853294879</v>
+        <v>0.04680095559694691</v>
       </c>
       <c r="V686" t="n">
-        <v>0.5411720307700715</v>
+        <v>0.4429670897822505</v>
       </c>
       <c r="W686" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="X686" t="inlineStr">
         <is>
@@ -68859,16 +68861,16 @@
       </c>
       <c r="Y686" t="inlineStr"/>
       <c r="Z686" t="n">
-        <v>3.7882042153905</v>
+        <v>3.781025473020228</v>
       </c>
       <c r="AA686" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB686" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC686" t="inlineStr"/>
@@ -68878,78 +68880,78 @@
     <row r="687">
       <c r="A687" s="1" t="inlineStr">
         <is>
-          <t>6ggmxi3B</t>
+          <t>O6cLrTa5</t>
         </is>
       </c>
       <c r="B687" s="2" t="n">
-        <v>45634.60416666666</v>
+        <v>45634.58333333334</v>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E687" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F687" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G687" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="H687" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I687" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="J687" t="n">
-        <v>0.4564841498559078</v>
+        <v>0.3401778496362166</v>
       </c>
       <c r="K687" t="n">
-        <v>0.2835734870317003</v>
+        <v>0.2976556184316895</v>
       </c>
       <c r="L687" t="n">
-        <v>0.2599423631123919</v>
+        <v>0.3621665319320937</v>
       </c>
       <c r="M687" t="n">
-        <v>0.06861295885686136</v>
+        <v>0.04987099402498663</v>
       </c>
       <c r="N687" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O687" t="n">
-        <v>0.379156971689786</v>
+        <v>0.3205599158752609</v>
       </c>
       <c r="P687" t="n">
-        <v>0.2754970793912254</v>
+        <v>0.3801074283004797</v>
       </c>
       <c r="Q687" t="n">
-        <v>0.3453459489189886</v>
+        <v>0.2993326558242593</v>
       </c>
       <c r="R687" t="n">
         <v>1</v>
       </c>
       <c r="S687" t="n">
-        <v>-0.07732717816612178</v>
+        <v>0.08245180986879014</v>
       </c>
       <c r="T687" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U687" t="n">
-        <v>-0.07732717816612178</v>
+        <v>0.08245180986879014</v>
       </c>
       <c r="V687" t="n">
-        <v>0.379156971689786</v>
+        <v>0.3801074283004797</v>
       </c>
       <c r="W687" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="X687" t="inlineStr">
         <is>
@@ -68958,97 +68960,99 @@
       </c>
       <c r="Y687" t="inlineStr"/>
       <c r="Z687" t="n">
-        <v>0.4889378131770922</v>
+        <v>3.194616004990381</v>
       </c>
       <c r="AA687" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB687" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC687" t="inlineStr"/>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC687" t="n">
+        <v>1</v>
+      </c>
       <c r="AD687" t="inlineStr"/>
       <c r="AE687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" s="1" t="inlineStr">
         <is>
-          <t>6adcTeKt</t>
+          <t>Ms14nB0t</t>
         </is>
       </c>
       <c r="B688" s="2" t="n">
-        <v>45634.70833333334</v>
+        <v>45634.69791666666</v>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E688" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F688" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G688" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="H688" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I688" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="J688" t="n">
-        <v>0.6386964914272737</v>
+        <v>0.5011933174224343</v>
       </c>
       <c r="K688" t="n">
-        <v>0.2100601794027478</v>
+        <v>0.2720763723150358</v>
       </c>
       <c r="L688" t="n">
-        <v>0.1512433291699784</v>
+        <v>0.2267303102625298</v>
       </c>
       <c r="M688" t="n">
-        <v>0.0578978978978979</v>
+        <v>0.05012531328320802</v>
       </c>
       <c r="N688" t="n">
         <v>1</v>
       </c>
       <c r="O688" t="n">
-        <v>0.6876294806540308</v>
+        <v>0.4210781796623052</v>
       </c>
       <c r="P688" t="n">
-        <v>0.2239759775707063</v>
+        <v>0.2406412996342734</v>
       </c>
       <c r="Q688" t="n">
-        <v>0.08839454177526286</v>
+        <v>0.3382805207034215</v>
       </c>
       <c r="R688" t="n">
         <v>1</v>
       </c>
       <c r="S688" t="n">
-        <v>0.04893298922675715</v>
+        <v>-0.08011513776012913</v>
       </c>
       <c r="T688" t="n">
         <v>1</v>
       </c>
       <c r="U688" t="n">
-        <v>0.04893298922675715</v>
+        <v>-0.08011513776012913</v>
       </c>
       <c r="V688" t="n">
-        <v>0.6876294806540308</v>
+        <v>0.4210781796623052</v>
       </c>
       <c r="W688" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="X688" t="inlineStr">
         <is>
@@ -69057,99 +69061,97 @@
       </c>
       <c r="Y688" t="inlineStr"/>
       <c r="Z688" t="n">
-        <v>3.610054773433661</v>
+        <v>0.6037057717307321</v>
       </c>
       <c r="AA688" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB688" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC688" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC688" t="inlineStr"/>
       <c r="AD688" t="inlineStr"/>
       <c r="AE688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" s="1" t="inlineStr">
         <is>
-          <t>QiBthjLU</t>
+          <t>6VQfS7FO</t>
         </is>
       </c>
       <c r="B689" s="2" t="n">
-        <v>45635.70833333334</v>
+        <v>45635.69791666666</v>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F689" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G689" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="H689" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I689" t="n">
-        <v>5.75</v>
+        <v>2.8</v>
       </c>
       <c r="J689" t="n">
-        <v>0.5455009851857258</v>
+        <v>0.3491271820448877</v>
       </c>
       <c r="K689" t="n">
-        <v>0.2903743705757863</v>
+        <v>0.314214463840399</v>
       </c>
       <c r="L689" t="n">
-        <v>0.1641246442384879</v>
+        <v>0.3366583541147132</v>
       </c>
       <c r="M689" t="n">
-        <v>0.05964003325149347</v>
+        <v>0.06084656084656093</v>
       </c>
       <c r="N689" t="n">
         <v>1</v>
       </c>
       <c r="O689" t="n">
-        <v>0.5470552261742939</v>
+        <v>0.4058053964949509</v>
       </c>
       <c r="P689" t="n">
-        <v>0.2208072968412841</v>
+        <v>0.3780843172166185</v>
       </c>
       <c r="Q689" t="n">
-        <v>0.232137476984422</v>
+        <v>0.2161102862884306</v>
       </c>
       <c r="R689" t="n">
         <v>1</v>
       </c>
       <c r="S689" t="n">
-        <v>0.001554240988568156</v>
+        <v>0.05667821445006316</v>
       </c>
       <c r="T689" t="n">
         <v>1</v>
       </c>
       <c r="U689" t="n">
-        <v>0.001554240988568156</v>
+        <v>0.05667821445006316</v>
       </c>
       <c r="V689" t="n">
-        <v>0.5470552261742939</v>
+        <v>0.4058053964949509</v>
       </c>
       <c r="W689" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="X689" t="inlineStr">
         <is>
@@ -69158,21 +69160,19 @@
       </c>
       <c r="Y689" t="inlineStr"/>
       <c r="Z689" t="n">
-        <v>2.872039937415043</v>
+        <v>3.795109525771221</v>
       </c>
       <c r="AA689" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB689" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC689" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC689" t="inlineStr"/>
       <c r="AD689" t="inlineStr"/>
       <c r="AE689" t="inlineStr"/>
     </row>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -68206,55 +68206,55 @@
         <v>1481</v>
       </c>
       <c r="G680" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H680" t="n">
         <v>3</v>
       </c>
       <c r="I680" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J680" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4736842105263159</v>
       </c>
       <c r="K680" t="n">
-        <v>0.3181818181818181</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="L680" t="n">
-        <v>0.2272727272727272</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="M680" t="n">
-        <v>0.04761904761904767</v>
+        <v>0.05555555555555536</v>
       </c>
       <c r="N680" t="n">
         <v>1</v>
       </c>
       <c r="O680" t="n">
-        <v>0.6691015928987419</v>
+        <v>0.3431180417537689</v>
       </c>
       <c r="P680" t="n">
-        <v>0.06142903498792147</v>
+        <v>0.3292394876480103</v>
       </c>
       <c r="Q680" t="n">
-        <v>0.2694693721133367</v>
+        <v>0.3276424705982208</v>
       </c>
       <c r="R680" t="n">
         <v>1</v>
       </c>
       <c r="S680" t="n">
-        <v>0.2145561383532875</v>
+        <v>-0.130566168772547</v>
       </c>
       <c r="T680" t="n">
         <v>1</v>
       </c>
       <c r="U680" t="n">
-        <v>0.2145561383532875</v>
+        <v>-0.130566168772547</v>
       </c>
       <c r="V680" t="n">
-        <v>0.6691015928987419</v>
+        <v>0.3431180417537689</v>
       </c>
       <c r="W680" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="X680" t="inlineStr">
         <is>
@@ -68263,7 +68263,7 @@
       </c>
       <c r="Y680" t="inlineStr"/>
       <c r="Z680" t="n">
-        <v>7.02556672543679</v>
+        <v>3.602739438414574</v>
       </c>
       <c r="AA680" t="inlineStr">
         <is>
@@ -68329,28 +68329,28 @@
         <v>1</v>
       </c>
       <c r="O681" t="n">
-        <v>0.8036545960024415</v>
+        <v>0.3493945300579071</v>
       </c>
       <c r="P681" t="n">
-        <v>0.1338717363532121</v>
+        <v>0.3345171511173248</v>
       </c>
       <c r="Q681" t="n">
-        <v>0.06247366764434627</v>
+        <v>0.3160882890224457</v>
       </c>
       <c r="R681" t="n">
         <v>1</v>
       </c>
       <c r="S681" t="n">
-        <v>-0.01091176719832521</v>
+        <v>-0.4651718331428596</v>
       </c>
       <c r="T681" t="n">
         <v>1</v>
       </c>
       <c r="U681" t="n">
-        <v>-0.01091176719832521</v>
+        <v>-0.4651718331428596</v>
       </c>
       <c r="V681" t="n">
-        <v>0.8036545960024415</v>
+        <v>0.3493945300579071</v>
       </c>
       <c r="W681" t="n">
         <v>1.17</v>
@@ -68362,7 +68362,7 @@
       </c>
       <c r="Y681" t="inlineStr"/>
       <c r="Z681" t="n">
-        <v>7.980079035695977</v>
+        <v>3.668642565608025</v>
       </c>
       <c r="AA681" t="inlineStr">
         <is>
@@ -68425,34 +68425,34 @@
         <v>0.04967320261437913</v>
       </c>
       <c r="N682" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O682" t="n">
-        <v>0.6382183917849941</v>
+        <v>0.3312021791934967</v>
       </c>
       <c r="P682" t="n">
-        <v>0.1427516307438271</v>
+        <v>0.3346035182476044</v>
       </c>
       <c r="Q682" t="n">
-        <v>0.2190299774711789</v>
+        <v>0.3341943621635437</v>
       </c>
       <c r="R682" t="n">
         <v>1</v>
       </c>
       <c r="S682" t="n">
-        <v>0.1089531364923415</v>
+        <v>0.05440426544561183</v>
       </c>
       <c r="T682" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U682" t="n">
-        <v>0.1089531364923415</v>
+        <v>0.05440426544561183</v>
       </c>
       <c r="V682" t="n">
-        <v>0.6382183917849941</v>
+        <v>0.3346035182476044</v>
       </c>
       <c r="W682" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="X682" t="inlineStr">
         <is>
@@ -68461,7 +68461,7 @@
       </c>
       <c r="Y682" t="inlineStr"/>
       <c r="Z682" t="n">
-        <v>6.701293113742437</v>
+        <v>3.513336941599846</v>
       </c>
       <c r="AA682" t="inlineStr">
         <is>
@@ -68527,28 +68527,28 @@
         <v>0</v>
       </c>
       <c r="O683" t="n">
-        <v>0.324682485536592</v>
+        <v>0.3099367618560791</v>
       </c>
       <c r="P683" t="n">
-        <v>0.4042483378758187</v>
+        <v>0.3478402495384216</v>
       </c>
       <c r="Q683" t="n">
-        <v>0.2710691765875894</v>
+        <v>0.3422229588031769</v>
       </c>
       <c r="R683" t="n">
         <v>1</v>
       </c>
       <c r="S683" t="n">
-        <v>0.1245873209266661</v>
+        <v>0.06817923258926911</v>
       </c>
       <c r="T683" t="n">
         <v>0</v>
       </c>
       <c r="U683" t="n">
-        <v>0.1245873209266661</v>
+        <v>0.06817923258926911</v>
       </c>
       <c r="V683" t="n">
-        <v>0.4042483378758187</v>
+        <v>0.3478402495384216</v>
       </c>
       <c r="W683" t="n">
         <v>3.4</v>
@@ -68560,7 +68560,7 @@
       </c>
       <c r="Y683" t="inlineStr"/>
       <c r="Z683" t="n">
-        <v>3.183455660772072</v>
+        <v>2.73924196511507</v>
       </c>
       <c r="AA683" t="inlineStr">
         <is>
@@ -68604,55 +68604,55 @@
         <v>1481</v>
       </c>
       <c r="G684" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="H684" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I684" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="J684" t="n">
-        <v>0.1648842838663405</v>
+        <v>0.1574768416409351</v>
       </c>
       <c r="K684" t="n">
-        <v>0.2312401542027946</v>
+        <v>0.2249669166299073</v>
       </c>
       <c r="L684" t="n">
-        <v>0.6038755619308649</v>
+        <v>0.6175562417291575</v>
       </c>
       <c r="M684" t="n">
-        <v>0.05475815766188674</v>
+        <v>0.05835667600373484</v>
       </c>
       <c r="N684" t="n">
         <v>2</v>
       </c>
       <c r="O684" t="n">
-        <v>0.1009777218165367</v>
+        <v>0.3339175879955292</v>
       </c>
       <c r="P684" t="n">
-        <v>0.2313452870418226</v>
+        <v>0.3184289336204529</v>
       </c>
       <c r="Q684" t="n">
-        <v>0.6676769911416407</v>
+        <v>0.3476535081863403</v>
       </c>
       <c r="R684" t="n">
         <v>1</v>
       </c>
       <c r="S684" t="n">
-        <v>0.06380142921077581</v>
+        <v>-0.2699027335428171</v>
       </c>
       <c r="T684" t="n">
         <v>2</v>
       </c>
       <c r="U684" t="n">
-        <v>0.06380142921077581</v>
+        <v>-0.2699027335428171</v>
       </c>
       <c r="V684" t="n">
-        <v>0.6676769911416407</v>
+        <v>0.3476535081863403</v>
       </c>
       <c r="W684" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="X684" t="inlineStr">
         <is>
@@ -68661,7 +68661,7 @@
       </c>
       <c r="Y684" t="inlineStr"/>
       <c r="Z684" t="n">
-        <v>7.010608406987227</v>
+        <v>3.650361835956573</v>
       </c>
       <c r="AA684" t="inlineStr">
         <is>
@@ -68727,28 +68727,28 @@
         <v>1</v>
       </c>
       <c r="O685" t="n">
-        <v>0.507582859485448</v>
+        <v>0.3452942371368408</v>
       </c>
       <c r="P685" t="n">
-        <v>0.2727172214745165</v>
+        <v>0.342877984046936</v>
       </c>
       <c r="Q685" t="n">
-        <v>0.2196999190400354</v>
+        <v>0.3118277788162231</v>
       </c>
       <c r="R685" t="n">
         <v>1</v>
       </c>
       <c r="S685" t="n">
-        <v>-0.01046894569507006</v>
+        <v>-0.1727575680436773</v>
       </c>
       <c r="T685" t="n">
         <v>1</v>
       </c>
       <c r="U685" t="n">
-        <v>-0.01046894569507006</v>
+        <v>-0.1727575680436773</v>
       </c>
       <c r="V685" t="n">
-        <v>0.507582859485448</v>
+        <v>0.3452942371368408</v>
       </c>
       <c r="W685" t="n">
         <v>1.83</v>
@@ -68760,7 +68760,7 @@
       </c>
       <c r="Y685" t="inlineStr"/>
       <c r="Z685" t="n">
-        <v>4.889924305404262</v>
+        <v>3.625589489936829</v>
       </c>
       <c r="AA685" t="inlineStr">
         <is>
@@ -68805,49 +68805,49 @@
         <v>1.36</v>
       </c>
       <c r="H686" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I686" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J686" t="n">
-        <v>0.6934812760055478</v>
+        <v>0.6953028430160691</v>
       </c>
       <c r="K686" t="n">
-        <v>0.188626907073509</v>
+        <v>0.2101359703337453</v>
       </c>
       <c r="L686" t="n">
-        <v>0.1178918169209431</v>
+        <v>0.09456118665018541</v>
       </c>
       <c r="M686" t="n">
-        <v>0.06029411764705883</v>
+        <v>0.05751633986928106</v>
       </c>
       <c r="N686" t="n">
         <v>1</v>
       </c>
       <c r="O686" t="n">
-        <v>0.8451646071692897</v>
+        <v>0.3507839739322662</v>
       </c>
       <c r="P686" t="n">
-        <v>0.07771171929663059</v>
+        <v>0.3240694105625153</v>
       </c>
       <c r="Q686" t="n">
-        <v>0.07712367353407977</v>
+        <v>0.3251466155052185</v>
       </c>
       <c r="R686" t="n">
         <v>1</v>
       </c>
       <c r="S686" t="n">
-        <v>0.1516833311637419</v>
+        <v>-0.3445188690838029</v>
       </c>
       <c r="T686" t="n">
         <v>1</v>
       </c>
       <c r="U686" t="n">
-        <v>0.1516833311637419</v>
+        <v>-0.3445188690838029</v>
       </c>
       <c r="V686" t="n">
-        <v>0.8451646071692897</v>
+        <v>0.3507839739322662</v>
       </c>
       <c r="W686" t="n">
         <v>1.36</v>
@@ -68859,7 +68859,7 @@
       </c>
       <c r="Y686" t="inlineStr"/>
       <c r="Z686" t="n">
-        <v>8.874228375277541</v>
+        <v>3.683231726288795</v>
       </c>
       <c r="AA686" t="inlineStr">
         <is>
@@ -68922,34 +68922,34 @@
         <v>0.05009387267451793</v>
       </c>
       <c r="N687" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O687" t="n">
-        <v>0.305886745942742</v>
+        <v>0.3466003835201263</v>
       </c>
       <c r="P687" t="n">
-        <v>0.1593788878408367</v>
+        <v>0.3370699882507324</v>
       </c>
       <c r="Q687" t="n">
-        <v>0.5347343662164213</v>
+        <v>0.3163296282291412</v>
       </c>
       <c r="R687" t="n">
         <v>1</v>
       </c>
       <c r="S687" t="n">
-        <v>0.1820322126203223</v>
+        <v>0.006494735409602215</v>
       </c>
       <c r="T687" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U687" t="n">
-        <v>0.1820322126203223</v>
+        <v>0.006494735409602215</v>
       </c>
       <c r="V687" t="n">
-        <v>0.5347343662164213</v>
+        <v>0.3466003835201263</v>
       </c>
       <c r="W687" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="X687" t="inlineStr">
         <is>
@@ -68958,7 +68958,7 @@
       </c>
       <c r="Y687" t="inlineStr"/>
       <c r="Z687" t="n">
-        <v>5.614710845272424</v>
+        <v>3.639304026961327</v>
       </c>
       <c r="AA687" t="inlineStr">
         <is>
@@ -69000,55 +69000,55 @@
         <v>1481</v>
       </c>
       <c r="G688" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="H688" t="n">
         <v>3.6</v>
       </c>
       <c r="I688" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="J688" t="n">
-        <v>0.5392195506503745</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="K688" t="n">
-        <v>0.2621206148994876</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="L688" t="n">
-        <v>0.198659834450138</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="M688" t="n">
-        <v>0.05973266499582275</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N688" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O688" t="n">
-        <v>0.3471487420816711</v>
+        <v>0.3296301364898682</v>
       </c>
       <c r="P688" t="n">
-        <v>0.3416191168279354</v>
+        <v>0.326541393995285</v>
       </c>
       <c r="Q688" t="n">
-        <v>0.3112321410903934</v>
+        <v>0.3438284695148468</v>
       </c>
       <c r="R688" t="n">
         <v>1</v>
       </c>
       <c r="S688" t="n">
-        <v>-0.1920708085687034</v>
+        <v>0.1333021537253731</v>
       </c>
       <c r="T688" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U688" t="n">
-        <v>-0.1920708085687034</v>
+        <v>0.1333021537253731</v>
       </c>
       <c r="V688" t="n">
-        <v>0.3471487420816711</v>
+        <v>0.3438284695148468</v>
       </c>
       <c r="W688" t="n">
-        <v>1.75</v>
+        <v>4.5</v>
       </c>
       <c r="X688" t="inlineStr">
         <is>
@@ -69057,7 +69057,7 @@
       </c>
       <c r="Y688" t="inlineStr"/>
       <c r="Z688" t="n">
-        <v>0</v>
+        <v>2.707649197429419</v>
       </c>
       <c r="AA688" t="inlineStr">
         <is>
@@ -69125,28 +69125,28 @@
         <v>1</v>
       </c>
       <c r="O689" t="n">
-        <v>0.5748051679220132</v>
+        <v>0.3555161952972412</v>
       </c>
       <c r="P689" t="n">
-        <v>0.142279117365902</v>
+        <v>0.3192315399646759</v>
       </c>
       <c r="Q689" t="n">
-        <v>0.2829157147120847</v>
+        <v>0.3252522349357605</v>
       </c>
       <c r="R689" t="n">
         <v>1</v>
       </c>
       <c r="S689" t="n">
-        <v>0.1238767859591484</v>
+        <v>-0.09541218666562357</v>
       </c>
       <c r="T689" t="n">
         <v>1</v>
       </c>
       <c r="U689" t="n">
-        <v>0.1238767859591484</v>
+        <v>-0.09541218666562357</v>
       </c>
       <c r="V689" t="n">
-        <v>0.5748051679220132</v>
+        <v>0.3555161952972412</v>
       </c>
       <c r="W689" t="n">
         <v>2.1</v>
@@ -69158,7 +69158,7 @@
       </c>
       <c r="Y689" t="inlineStr"/>
       <c r="Z689" t="n">
-        <v>4.526590697385855</v>
+        <v>2.799690037965775</v>
       </c>
       <c r="AA689" t="inlineStr">
         <is>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -68230,40 +68230,40 @@
         <v>1</v>
       </c>
       <c r="O680" t="n">
-        <v>0.3431180417537689</v>
+        <v>0.6148039698600769</v>
       </c>
       <c r="P680" t="n">
-        <v>0.3292394876480103</v>
+        <v>0.2291441261768341</v>
       </c>
       <c r="Q680" t="n">
-        <v>0.3276424705982208</v>
+        <v>0.1560518741607666</v>
       </c>
       <c r="R680" t="n">
         <v>1</v>
       </c>
       <c r="S680" t="n">
-        <v>-0.130566168772547</v>
+        <v>0.141119759333761</v>
       </c>
       <c r="T680" t="n">
         <v>1</v>
       </c>
       <c r="U680" t="n">
-        <v>-0.130566168772547</v>
+        <v>0.141119759333761</v>
       </c>
       <c r="V680" t="n">
-        <v>0.3431180417537689</v>
+        <v>0.6148039698600769</v>
       </c>
       <c r="W680" t="n">
         <v>2</v>
       </c>
       <c r="X680" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y680" t="inlineStr"/>
       <c r="Z680" t="n">
-        <v>3.602739438414574</v>
+        <v>6.455441683530807</v>
       </c>
       <c r="AA680" t="inlineStr">
         <is>
@@ -68329,40 +68329,40 @@
         <v>1</v>
       </c>
       <c r="O681" t="n">
-        <v>0.3493945300579071</v>
+        <v>0.6315798163414001</v>
       </c>
       <c r="P681" t="n">
-        <v>0.3345171511173248</v>
+        <v>0.2134162187576294</v>
       </c>
       <c r="Q681" t="n">
-        <v>0.3160882890224457</v>
+        <v>0.1550039499998093</v>
       </c>
       <c r="R681" t="n">
         <v>1</v>
       </c>
       <c r="S681" t="n">
-        <v>-0.4651718331428596</v>
+        <v>-0.1829865468593666</v>
       </c>
       <c r="T681" t="n">
         <v>1</v>
       </c>
       <c r="U681" t="n">
-        <v>-0.4651718331428596</v>
+        <v>-0.1829865468593666</v>
       </c>
       <c r="V681" t="n">
-        <v>0.3493945300579071</v>
+        <v>0.6315798163414001</v>
       </c>
       <c r="W681" t="n">
         <v>1.17</v>
       </c>
       <c r="X681" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y681" t="inlineStr"/>
       <c r="Z681" t="n">
-        <v>3.668642565608025</v>
+        <v>6.631588071584702</v>
       </c>
       <c r="AA681" t="inlineStr">
         <is>
@@ -68428,40 +68428,40 @@
         <v>0</v>
       </c>
       <c r="O682" t="n">
-        <v>0.3312021791934967</v>
+        <v>0.2924555242061615</v>
       </c>
       <c r="P682" t="n">
-        <v>0.3346035182476044</v>
+        <v>0.3657283782958984</v>
       </c>
       <c r="Q682" t="n">
-        <v>0.3341943621635437</v>
+        <v>0.3418160378932953</v>
       </c>
       <c r="R682" t="n">
         <v>1</v>
       </c>
       <c r="S682" t="n">
-        <v>0.05440426544561183</v>
+        <v>0.0855291254939059</v>
       </c>
       <c r="T682" t="n">
         <v>0</v>
       </c>
       <c r="U682" t="n">
-        <v>0.05440426544561183</v>
+        <v>0.0855291254939059</v>
       </c>
       <c r="V682" t="n">
-        <v>0.3346035182476044</v>
+        <v>0.3657283782958984</v>
       </c>
       <c r="W682" t="n">
         <v>3.4</v>
       </c>
       <c r="X682" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y682" t="inlineStr"/>
       <c r="Z682" t="n">
-        <v>3.513336941599846</v>
+        <v>3.840147972106934</v>
       </c>
       <c r="AA682" t="inlineStr">
         <is>
@@ -68524,43 +68524,43 @@
         <v>0.05169340463458116</v>
       </c>
       <c r="N683" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O683" t="n">
-        <v>0.3099367618560791</v>
+        <v>0.110199049115181</v>
       </c>
       <c r="P683" t="n">
-        <v>0.3478402495384216</v>
+        <v>0.2768021821975708</v>
       </c>
       <c r="Q683" t="n">
-        <v>0.3422229588031769</v>
+        <v>0.6129987239837646</v>
       </c>
       <c r="R683" t="n">
         <v>1</v>
       </c>
       <c r="S683" t="n">
-        <v>0.06817923258926911</v>
+        <v>0.1807953341532562</v>
       </c>
       <c r="T683" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U683" t="n">
-        <v>0.06817923258926911</v>
+        <v>0.1807953341532562</v>
       </c>
       <c r="V683" t="n">
-        <v>0.3478402495384216</v>
+        <v>0.6129987239837646</v>
       </c>
       <c r="W683" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="X683" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y683" t="inlineStr"/>
       <c r="Z683" t="n">
-        <v>2.73924196511507</v>
+        <v>4.827364951372147</v>
       </c>
       <c r="AA683" t="inlineStr">
         <is>
@@ -68628,40 +68628,40 @@
         <v>2</v>
       </c>
       <c r="O684" t="n">
-        <v>0.3339175879955292</v>
+        <v>0.09451180696487427</v>
       </c>
       <c r="P684" t="n">
-        <v>0.3184289336204529</v>
+        <v>0.2090925276279449</v>
       </c>
       <c r="Q684" t="n">
-        <v>0.3476535081863403</v>
+        <v>0.6963956356048584</v>
       </c>
       <c r="R684" t="n">
         <v>1</v>
       </c>
       <c r="S684" t="n">
-        <v>-0.2699027335428171</v>
+        <v>0.07883939387570094</v>
       </c>
       <c r="T684" t="n">
         <v>2</v>
       </c>
       <c r="U684" t="n">
-        <v>-0.2699027335428171</v>
+        <v>0.07883939387570094</v>
       </c>
       <c r="V684" t="n">
-        <v>0.3476535081863403</v>
+        <v>0.6963956356048584</v>
       </c>
       <c r="W684" t="n">
         <v>1.53</v>
       </c>
       <c r="X684" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y684" t="inlineStr"/>
       <c r="Z684" t="n">
-        <v>3.650361835956573</v>
+        <v>7.312154173851013</v>
       </c>
       <c r="AA684" t="inlineStr">
         <is>
@@ -68724,43 +68724,43 @@
         <v>0.05481359579720224</v>
       </c>
       <c r="N685" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O685" t="n">
-        <v>0.3452942371368408</v>
+        <v>0.1948871463537216</v>
       </c>
       <c r="P685" t="n">
-        <v>0.342877984046936</v>
+        <v>0.1989489793777466</v>
       </c>
       <c r="Q685" t="n">
-        <v>0.3118277788162231</v>
+        <v>0.6061638593673706</v>
       </c>
       <c r="R685" t="n">
         <v>1</v>
       </c>
       <c r="S685" t="n">
-        <v>-0.1727575680436773</v>
+        <v>0.3804412871101449</v>
       </c>
       <c r="T685" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U685" t="n">
-        <v>-0.1727575680436773</v>
+        <v>0.3804412871101449</v>
       </c>
       <c r="V685" t="n">
-        <v>0.3452942371368408</v>
+        <v>0.6061638593673706</v>
       </c>
       <c r="W685" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="X685" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y685" t="inlineStr"/>
       <c r="Z685" t="n">
-        <v>3.625589489936829</v>
+        <v>6.364720523357391</v>
       </c>
       <c r="AA685" t="inlineStr">
         <is>
@@ -68826,40 +68826,40 @@
         <v>1</v>
       </c>
       <c r="O686" t="n">
-        <v>0.3507839739322662</v>
+        <v>0.5046667456626892</v>
       </c>
       <c r="P686" t="n">
-        <v>0.3240694105625153</v>
+        <v>0.3227453529834747</v>
       </c>
       <c r="Q686" t="n">
-        <v>0.3251466155052185</v>
+        <v>0.1725879162549973</v>
       </c>
       <c r="R686" t="n">
         <v>1</v>
       </c>
       <c r="S686" t="n">
-        <v>-0.3445188690838029</v>
+        <v>-0.1906360973533799</v>
       </c>
       <c r="T686" t="n">
         <v>1</v>
       </c>
       <c r="U686" t="n">
-        <v>-0.3445188690838029</v>
+        <v>-0.1906360973533799</v>
       </c>
       <c r="V686" t="n">
-        <v>0.3507839739322662</v>
+        <v>0.5046667456626892</v>
       </c>
       <c r="W686" t="n">
         <v>1.36</v>
       </c>
       <c r="X686" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y686" t="inlineStr"/>
       <c r="Z686" t="n">
-        <v>3.683231726288795</v>
+        <v>5.299000829458237</v>
       </c>
       <c r="AA686" t="inlineStr">
         <is>
@@ -68922,43 +68922,43 @@
         <v>0.05009387267451793</v>
       </c>
       <c r="N687" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O687" t="n">
-        <v>0.3466003835201263</v>
+        <v>0.1954513341188431</v>
       </c>
       <c r="P687" t="n">
-        <v>0.3370699882507324</v>
+        <v>0.4579564332962036</v>
       </c>
       <c r="Q687" t="n">
-        <v>0.3163296282291412</v>
+        <v>0.3465921580791473</v>
       </c>
       <c r="R687" t="n">
         <v>1</v>
       </c>
       <c r="S687" t="n">
-        <v>0.006494735409602215</v>
+        <v>0.150764235002827</v>
       </c>
       <c r="T687" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U687" t="n">
-        <v>0.006494735409602215</v>
+        <v>0.150764235002827</v>
       </c>
       <c r="V687" t="n">
-        <v>0.3466003835201263</v>
+        <v>0.4579564332962036</v>
       </c>
       <c r="W687" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="X687" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y687" t="inlineStr"/>
       <c r="Z687" t="n">
-        <v>3.639304026961327</v>
+        <v>4.808542549610138</v>
       </c>
       <c r="AA687" t="inlineStr">
         <is>
@@ -69021,43 +69021,43 @@
         <v>0.05555555555555558</v>
       </c>
       <c r="N688" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O688" t="n">
-        <v>0.3296301364898682</v>
+        <v>0.2176385521888733</v>
       </c>
       <c r="P688" t="n">
-        <v>0.326541393995285</v>
+        <v>0.4210319221019745</v>
       </c>
       <c r="Q688" t="n">
-        <v>0.3438284695148468</v>
+        <v>0.3613295257091522</v>
       </c>
       <c r="R688" t="n">
         <v>1</v>
       </c>
       <c r="S688" t="n">
-        <v>0.1333021537253731</v>
+        <v>0.1578740273651324</v>
       </c>
       <c r="T688" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U688" t="n">
-        <v>0.1333021537253731</v>
+        <v>0.1578740273651324</v>
       </c>
       <c r="V688" t="n">
-        <v>0.3438284695148468</v>
+        <v>0.4210319221019745</v>
       </c>
       <c r="W688" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="X688" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y688" t="inlineStr"/>
       <c r="Z688" t="n">
-        <v>2.707649197429419</v>
+        <v>3.315626386553049</v>
       </c>
       <c r="AA688" t="inlineStr">
         <is>
@@ -69125,40 +69125,40 @@
         <v>1</v>
       </c>
       <c r="O689" t="n">
-        <v>0.3555161952972412</v>
+        <v>0.4133053123950958</v>
       </c>
       <c r="P689" t="n">
-        <v>0.3192315399646759</v>
+        <v>0.2662601470947266</v>
       </c>
       <c r="Q689" t="n">
-        <v>0.3252522349357605</v>
+        <v>0.3204345703125</v>
       </c>
       <c r="R689" t="n">
         <v>1</v>
       </c>
       <c r="S689" t="n">
-        <v>-0.09541218666562357</v>
+        <v>-0.03762306956776895</v>
       </c>
       <c r="T689" t="n">
         <v>1</v>
       </c>
       <c r="U689" t="n">
-        <v>-0.09541218666562357</v>
+        <v>-0.03762306956776895</v>
       </c>
       <c r="V689" t="n">
-        <v>0.3555161952972412</v>
+        <v>0.4133053123950958</v>
       </c>
       <c r="W689" t="n">
         <v>2.1</v>
       </c>
       <c r="X689" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y689" t="inlineStr"/>
       <c r="Z689" t="n">
-        <v>2.799690037965775</v>
+        <v>3.25477933511138</v>
       </c>
       <c r="AA689" t="inlineStr">
         <is>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -65163,96 +65163,96 @@
     <row r="650">
       <c r="A650" s="1" t="inlineStr">
         <is>
-          <t>tQAc65y8</t>
+          <t>j97t2JLs</t>
         </is>
       </c>
       <c r="B650" s="2" t="n">
-        <v>45625.69791666666</v>
+        <v>45625.70833333334</v>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F650" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G650" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="H650" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="I650" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J650" t="n">
-        <v>0.4931894569255263</v>
+        <v>0.4736842105263159</v>
       </c>
       <c r="K650" t="n">
-        <v>0.2770564302140457</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="L650" t="n">
-        <v>0.2297541128604281</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="M650" t="n">
-        <v>0.06158029550729749</v>
+        <v>0.05555555555555536</v>
       </c>
       <c r="N650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O650" t="n">
-        <v>0.3464786187338829</v>
+        <v>0.6148039698600769</v>
       </c>
       <c r="P650" t="n">
-        <v>0.4322170723968437</v>
+        <v>0.2291441261768341</v>
       </c>
       <c r="Q650" t="n">
-        <v>0.2213043088692734</v>
+        <v>0.1560518741607666</v>
       </c>
       <c r="R650" t="n">
         <v>1</v>
       </c>
       <c r="S650" t="n">
-        <v>0.155160642182798</v>
+        <v>0.141119759333761</v>
       </c>
       <c r="T650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U650" t="n">
-        <v>0.155160642182798</v>
+        <v>0.141119759333761</v>
       </c>
       <c r="V650" t="n">
-        <v>0.4322170723968437</v>
+        <v>0.6148039698600769</v>
       </c>
       <c r="W650" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="X650" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y650" t="inlineStr"/>
       <c r="Z650" t="n">
-        <v>6.317157846768215</v>
+        <v>6.455441683530807</v>
       </c>
       <c r="AA650" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB650" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC650" t="inlineStr"/>
@@ -65262,197 +65262,195 @@
     <row r="651">
       <c r="A651" s="1" t="inlineStr">
         <is>
-          <t>OlzrEHfE</t>
+          <t>KQGA7ubK</t>
         </is>
       </c>
       <c r="B651" s="2" t="n">
-        <v>45626.45833333334</v>
+        <v>45626.41666666666</v>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F651" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G651" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="H651" t="n">
-        <v>3.25</v>
+        <v>8.5</v>
       </c>
       <c r="I651" t="n">
-        <v>3.9</v>
+        <v>13</v>
       </c>
       <c r="J651" t="n">
-        <v>0.4698795180722892</v>
+        <v>0.8145663632007667</v>
       </c>
       <c r="K651" t="n">
-        <v>0.2891566265060241</v>
+        <v>0.1121226641111643</v>
       </c>
       <c r="L651" t="n">
-        <v>0.2409638554216868</v>
+        <v>0.07331097268806899</v>
       </c>
       <c r="M651" t="n">
-        <v>0.0641025641025641</v>
+        <v>0.04927099044746108</v>
       </c>
       <c r="N651" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O651" t="n">
-        <v>0.3562965023670175</v>
+        <v>0.6315798163414001</v>
       </c>
       <c r="P651" t="n">
-        <v>0.2765670089449155</v>
+        <v>0.2134162187576294</v>
       </c>
       <c r="Q651" t="n">
-        <v>0.367136488688067</v>
+        <v>0.1550039499998093</v>
       </c>
       <c r="R651" t="n">
         <v>1</v>
       </c>
       <c r="S651" t="n">
-        <v>0.1261726332663802</v>
+        <v>-0.1829865468593666</v>
       </c>
       <c r="T651" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U651" t="n">
-        <v>0.1261726332663802</v>
+        <v>-0.1829865468593666</v>
       </c>
       <c r="V651" t="n">
-        <v>0.367136488688067</v>
+        <v>0.6315798163414001</v>
       </c>
       <c r="W651" t="n">
-        <v>3.9</v>
+        <v>1.17</v>
       </c>
       <c r="X651" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y651" t="inlineStr"/>
       <c r="Z651" t="n">
-        <v>3.923221597891144</v>
+        <v>6.631588071584702</v>
       </c>
       <c r="AA651" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB651" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC651" t="n">
-        <v>1</v>
-      </c>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC651" t="inlineStr"/>
       <c r="AD651" t="inlineStr"/>
       <c r="AE651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" s="1" t="inlineStr">
         <is>
-          <t>OCIU4DH0</t>
+          <t>WIFl0cjf</t>
         </is>
       </c>
       <c r="B652" s="2" t="n">
-        <v>45626.58333333334</v>
+        <v>45626.51041666666</v>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F652" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G652" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="H652" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="I652" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J652" t="n">
-        <v>0.6956875508543532</v>
+        <v>0.5292652552926526</v>
       </c>
       <c r="K652" t="n">
-        <v>0.199186330349878</v>
+        <v>0.2801992528019925</v>
       </c>
       <c r="L652" t="n">
-        <v>0.1051261187957689</v>
+        <v>0.1905354919053549</v>
       </c>
       <c r="M652" t="n">
-        <v>0.05693154454764349</v>
+        <v>0.04967320261437913</v>
       </c>
       <c r="N652" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O652" t="n">
-        <v>0.8758564861116346</v>
+        <v>0.2924555242061615</v>
       </c>
       <c r="P652" t="n">
-        <v>0.1095808510520968</v>
+        <v>0.3657283782958984</v>
       </c>
       <c r="Q652" t="n">
-        <v>0.0145626628362686</v>
+        <v>0.3418160378932953</v>
       </c>
       <c r="R652" t="n">
         <v>1</v>
       </c>
       <c r="S652" t="n">
-        <v>0.1801689352572814</v>
+        <v>0.0855291254939059</v>
       </c>
       <c r="T652" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U652" t="n">
-        <v>0.1801689352572814</v>
+        <v>0.0855291254939059</v>
       </c>
       <c r="V652" t="n">
-        <v>0.8758564861116346</v>
+        <v>0.3657283782958984</v>
       </c>
       <c r="W652" t="n">
-        <v>1.36</v>
+        <v>3.4</v>
       </c>
       <c r="X652" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y652" t="inlineStr"/>
       <c r="Z652" t="n">
-        <v>9.579193362844562</v>
+        <v>3.840147972106934</v>
       </c>
       <c r="AA652" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB652" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC652" t="inlineStr"/>
@@ -65462,195 +65460,197 @@
     <row r="653">
       <c r="A653" s="1" t="inlineStr">
         <is>
-          <t>lIhj8R6e</t>
+          <t>hvDYgCjI</t>
         </is>
       </c>
       <c r="B653" s="2" t="n">
-        <v>45626.69791666666</v>
+        <v>45626.60416666666</v>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E653" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F653" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G653" t="n">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="H653" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="I653" t="n">
-        <v>5.25</v>
+        <v>2.2</v>
       </c>
       <c r="J653" t="n">
-        <v>0.5755850727387729</v>
+        <v>0.288135593220339</v>
       </c>
       <c r="K653" t="n">
-        <v>0.243516761543327</v>
+        <v>0.2796610169491525</v>
       </c>
       <c r="L653" t="n">
-        <v>0.1808981657179</v>
+        <v>0.4322033898305084</v>
       </c>
       <c r="M653" t="n">
-        <v>0.05294705294705304</v>
+        <v>0.05169340463458116</v>
       </c>
       <c r="N653" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O653" t="n">
-        <v>0.3838907969951727</v>
+        <v>0.110199049115181</v>
       </c>
       <c r="P653" t="n">
-        <v>0.4797446191064985</v>
+        <v>0.2768021821975708</v>
       </c>
       <c r="Q653" t="n">
-        <v>0.1363645838983289</v>
+        <v>0.6129987239837646</v>
       </c>
       <c r="R653" t="n">
         <v>1</v>
       </c>
       <c r="S653" t="n">
-        <v>0.2362278575631715</v>
+        <v>0.1807953341532562</v>
       </c>
       <c r="T653" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U653" t="n">
-        <v>0.2362278575631715</v>
+        <v>0.1807953341532562</v>
       </c>
       <c r="V653" t="n">
-        <v>0.4797446191064985</v>
+        <v>0.6129987239837646</v>
       </c>
       <c r="W653" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="X653" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y653" t="inlineStr"/>
       <c r="Z653" t="n">
-        <v>8.547936296155108</v>
+        <v>4.827364951372147</v>
       </c>
       <c r="AA653" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB653" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC653" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC653" t="n">
+        <v>1</v>
+      </c>
       <c r="AD653" t="inlineStr"/>
       <c r="AE653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" s="1" t="inlineStr">
         <is>
-          <t>2J5dJCWg</t>
+          <t>0b75dFkJ</t>
         </is>
       </c>
       <c r="B654" s="2" t="n">
-        <v>45627.35416666666</v>
+        <v>45626.70833333334</v>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E654" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F654" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G654" t="n">
+        <v>6</v>
+      </c>
+      <c r="H654" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I654" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J654" t="n">
+        <v>0.1574768416409351</v>
+      </c>
+      <c r="K654" t="n">
+        <v>0.2249669166299073</v>
+      </c>
+      <c r="L654" t="n">
+        <v>0.6175562417291575</v>
+      </c>
+      <c r="M654" t="n">
+        <v>0.05835667600373484</v>
+      </c>
+      <c r="N654" t="n">
         <v>2</v>
       </c>
-      <c r="H654" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I654" t="n">
-        <v>4</v>
-      </c>
-      <c r="J654" t="n">
-        <v>0.4748201438848921</v>
-      </c>
-      <c r="K654" t="n">
-        <v>0.2877697841726619</v>
-      </c>
-      <c r="L654" t="n">
-        <v>0.2374100719424461</v>
-      </c>
-      <c r="M654" t="n">
-        <v>0.05303030303030298</v>
-      </c>
-      <c r="N654" t="n">
-        <v>1</v>
-      </c>
       <c r="O654" t="n">
-        <v>0.5517785790518059</v>
+        <v>0.09451180696487427</v>
       </c>
       <c r="P654" t="n">
-        <v>0.2341420137544359</v>
+        <v>0.2090925276279449</v>
       </c>
       <c r="Q654" t="n">
-        <v>0.2140794071937581</v>
+        <v>0.6963956356048584</v>
       </c>
       <c r="R654" t="n">
         <v>1</v>
       </c>
       <c r="S654" t="n">
-        <v>0.07695843516691381</v>
+        <v>0.07883939387570094</v>
       </c>
       <c r="T654" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U654" t="n">
-        <v>0.07695843516691381</v>
+        <v>0.07883939387570094</v>
       </c>
       <c r="V654" t="n">
-        <v>0.5517785790518059</v>
+        <v>0.6963956356048584</v>
       </c>
       <c r="W654" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="X654" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y654" t="inlineStr"/>
       <c r="Z654" t="n">
-        <v>5.157673918316767</v>
+        <v>7.312154173851013</v>
       </c>
       <c r="AA654" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB654" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC654" t="inlineStr"/>
@@ -65660,96 +65660,96 @@
     <row r="655">
       <c r="A655" s="1" t="inlineStr">
         <is>
-          <t>rFYV2inD</t>
+          <t>bgZVCzz0</t>
         </is>
       </c>
       <c r="B655" s="2" t="n">
-        <v>45627.45833333334</v>
+        <v>45627.41666666666</v>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E655" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F655" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G655" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H655" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I655" t="n">
         <v>4.2</v>
       </c>
-      <c r="H655" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I655" t="n">
-        <v>1.8</v>
-      </c>
       <c r="J655" t="n">
-        <v>0.225296442687747</v>
+        <v>0.5180518051805181</v>
       </c>
       <c r="K655" t="n">
-        <v>0.2490118577075099</v>
+        <v>0.2562256225622562</v>
       </c>
       <c r="L655" t="n">
-        <v>0.5256916996047432</v>
+        <v>0.2257225722572257</v>
       </c>
       <c r="M655" t="n">
-        <v>0.05680868838763575</v>
+        <v>0.05481359579720224</v>
       </c>
       <c r="N655" t="n">
         <v>2</v>
       </c>
       <c r="O655" t="n">
-        <v>0.2072081673409037</v>
+        <v>0.1948871463537216</v>
       </c>
       <c r="P655" t="n">
-        <v>0.1798614105842249</v>
+        <v>0.1989489793777466</v>
       </c>
       <c r="Q655" t="n">
-        <v>0.6129304220748714</v>
+        <v>0.6061638593673706</v>
       </c>
       <c r="R655" t="n">
         <v>1</v>
       </c>
       <c r="S655" t="n">
-        <v>0.0872387224701282</v>
+        <v>0.3804412871101449</v>
       </c>
       <c r="T655" t="n">
         <v>2</v>
       </c>
       <c r="U655" t="n">
-        <v>0.0872387224701282</v>
+        <v>0.3804412871101449</v>
       </c>
       <c r="V655" t="n">
-        <v>0.6129304220748714</v>
+        <v>0.6061638593673706</v>
       </c>
       <c r="W655" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="X655" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y655" t="inlineStr"/>
       <c r="Z655" t="n">
-        <v>5.771311871732305</v>
+        <v>6.364720523357391</v>
       </c>
       <c r="AA655" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB655" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC655" t="inlineStr"/>
@@ -65759,96 +65759,96 @@
     <row r="656">
       <c r="A656" s="1" t="inlineStr">
         <is>
-          <t>fg2lLY1s</t>
+          <t>CxyOEd5m</t>
         </is>
       </c>
       <c r="B656" s="2" t="n">
-        <v>45627.45833333334</v>
+        <v>45627.51041666666</v>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E656" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F656" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G656" t="n">
-        <v>5</v>
+        <v>1.36</v>
       </c>
       <c r="H656" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I656" t="n">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="J656" t="n">
-        <v>0.1905354919053549</v>
+        <v>0.6953028430160691</v>
       </c>
       <c r="K656" t="n">
-        <v>0.2801992528019925</v>
+        <v>0.2101359703337453</v>
       </c>
       <c r="L656" t="n">
-        <v>0.5292652552926526</v>
+        <v>0.09456118665018541</v>
       </c>
       <c r="M656" t="n">
-        <v>0.04967320261437913</v>
+        <v>0.05751633986928106</v>
       </c>
       <c r="N656" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O656" t="n">
-        <v>0.1104714687874638</v>
+        <v>0.5046667456626892</v>
       </c>
       <c r="P656" t="n">
-        <v>0.3219981241348892</v>
+        <v>0.3227453529834747</v>
       </c>
       <c r="Q656" t="n">
-        <v>0.567530407077647</v>
+        <v>0.1725879162549973</v>
       </c>
       <c r="R656" t="n">
         <v>1</v>
       </c>
       <c r="S656" t="n">
-        <v>0.03826515178499446</v>
+        <v>-0.1906360973533799</v>
       </c>
       <c r="T656" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U656" t="n">
-        <v>0.03826515178499446</v>
+        <v>-0.1906360973533799</v>
       </c>
       <c r="V656" t="n">
-        <v>0.567530407077647</v>
+        <v>0.5046667456626892</v>
       </c>
       <c r="W656" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="X656" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y656" t="inlineStr"/>
       <c r="Z656" t="n">
-        <v>4.323546085305749</v>
+        <v>5.299000829458237</v>
       </c>
       <c r="AA656" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB656" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC656" t="inlineStr"/>
@@ -65858,96 +65858,96 @@
     <row r="657">
       <c r="A657" s="1" t="inlineStr">
         <is>
-          <t>WEwjCePQ</t>
+          <t>4WDdbyL6</t>
         </is>
       </c>
       <c r="B657" s="2" t="n">
-        <v>45627.58333333334</v>
+        <v>45627.60416666666</v>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="E657" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F657" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G657" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="H657" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I657" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="J657" t="n">
-        <v>0.2642238998342847</v>
+        <v>0.3401056481105241</v>
       </c>
       <c r="K657" t="n">
-        <v>0.2717731541152642</v>
+        <v>0.3071921982933766</v>
       </c>
       <c r="L657" t="n">
-        <v>0.4640029460504512</v>
+        <v>0.3527021535960991</v>
       </c>
       <c r="M657" t="n">
-        <v>0.05129694154084397</v>
+        <v>0.05009387267451793</v>
       </c>
       <c r="N657" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O657" t="n">
-        <v>0.07801747287276779</v>
+        <v>0.1954513341188431</v>
       </c>
       <c r="P657" t="n">
-        <v>0.3821410104917382</v>
+        <v>0.4579564332962036</v>
       </c>
       <c r="Q657" t="n">
-        <v>0.539841516635494</v>
+        <v>0.3465921580791473</v>
       </c>
       <c r="R657" t="n">
         <v>1</v>
       </c>
       <c r="S657" t="n">
-        <v>0.07583857058504279</v>
+        <v>0.150764235002827</v>
       </c>
       <c r="T657" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U657" t="n">
-        <v>0.07583857058504279</v>
+        <v>0.150764235002827</v>
       </c>
       <c r="V657" t="n">
-        <v>0.539841516635494</v>
+        <v>0.4579564332962036</v>
       </c>
       <c r="W657" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="X657" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y657" t="inlineStr"/>
       <c r="Z657" t="n">
-        <v>5.059174793853991</v>
+        <v>4.808542549610138</v>
       </c>
       <c r="AA657" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB657" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC657" t="inlineStr"/>
@@ -65957,294 +65957,298 @@
     <row r="658">
       <c r="A658" s="1" t="inlineStr">
         <is>
-          <t>jaKM6Znl</t>
+          <t>S4aiKIsQ</t>
         </is>
       </c>
       <c r="B658" s="2" t="n">
-        <v>45627.69791666666</v>
+        <v>45627.70833333334</v>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F658" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G658" t="n">
-        <v>5.25</v>
+        <v>1.8</v>
       </c>
       <c r="H658" t="n">
         <v>3.6</v>
       </c>
       <c r="I658" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J658" t="n">
-        <v>0.1802916482545294</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="K658" t="n">
-        <v>0.2629253203711887</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="L658" t="n">
-        <v>0.556783031374282</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="M658" t="n">
-        <v>0.05648926237161533</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N658" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O658" t="n">
-        <v>0.03666590796829697</v>
+        <v>0.2176385521888733</v>
       </c>
       <c r="P658" t="n">
-        <v>0.3769814948774627</v>
+        <v>0.4210319221019745</v>
       </c>
       <c r="Q658" t="n">
-        <v>0.5863525971542403</v>
+        <v>0.3613295257091522</v>
       </c>
       <c r="R658" t="n">
         <v>1</v>
       </c>
       <c r="S658" t="n">
-        <v>0.02956956577995828</v>
+        <v>0.1578740273651324</v>
       </c>
       <c r="T658" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U658" t="n">
-        <v>0.02956956577995828</v>
+        <v>0.1578740273651324</v>
       </c>
       <c r="V658" t="n">
-        <v>0.5863525971542403</v>
+        <v>0.4210319221019745</v>
       </c>
       <c r="W658" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="X658" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y658" t="inlineStr"/>
       <c r="Z658" t="n">
-        <v>4.227785161644441</v>
+        <v>3.315626386553049</v>
       </c>
       <c r="AA658" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB658" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC658" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC658" t="n">
+        <v>1</v>
+      </c>
       <c r="AD658" t="inlineStr"/>
       <c r="AE658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" s="1" t="inlineStr">
         <is>
-          <t>ALQHQfvK</t>
+          <t>fLSvBE4C</t>
         </is>
       </c>
       <c r="B659" s="2" t="n">
-        <v>45628.69791666666</v>
+        <v>45628.70833333334</v>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F659" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G659" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="H659" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I659" t="n">
         <v>3.5</v>
       </c>
-      <c r="I659" t="n">
-        <v>2.2</v>
-      </c>
       <c r="J659" t="n">
-        <v>0.2968388589051658</v>
+        <v>0.4509283819628648</v>
       </c>
       <c r="K659" t="n">
-        <v>0.2713955281418658</v>
+        <v>0.2785145888594165</v>
       </c>
       <c r="L659" t="n">
-        <v>0.4317656129529684</v>
+        <v>0.2705570291777188</v>
       </c>
       <c r="M659" t="n">
-        <v>0.05275974025974017</v>
+        <v>0.05602240896358524</v>
       </c>
       <c r="N659" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O659" t="n">
-        <v>0.4008100119953498</v>
+        <v>0.4133053123950958</v>
       </c>
       <c r="P659" t="n">
-        <v>0.4440127221017852</v>
+        <v>0.2662601470947266</v>
       </c>
       <c r="Q659" t="n">
-        <v>0.1551772659028649</v>
+        <v>0.3204345703125</v>
       </c>
       <c r="R659" t="n">
         <v>1</v>
       </c>
       <c r="S659" t="n">
-        <v>0.1726171939599194</v>
+        <v>-0.03762306956776895</v>
       </c>
       <c r="T659" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U659" t="n">
-        <v>0.1726171939599194</v>
+        <v>-0.03762306956776895</v>
       </c>
       <c r="V659" t="n">
-        <v>0.4440127221017852</v>
+        <v>0.4133053123950958</v>
       </c>
       <c r="W659" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="X659" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y659" t="inlineStr"/>
       <c r="Z659" t="n">
-        <v>6.806888987648777</v>
+        <v>3.25477933511138</v>
       </c>
       <c r="AA659" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB659" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC659" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC659" t="n">
+        <v>1</v>
+      </c>
       <c r="AD659" t="inlineStr"/>
       <c r="AE659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" s="1" t="inlineStr">
         <is>
-          <t>xxKvWkGa</t>
+          <t>48cSecHb</t>
         </is>
       </c>
       <c r="B660" s="2" t="n">
-        <v>45632.60416666666</v>
+        <v>45629.625</v>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F660" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G660" t="n">
-        <v>1.18</v>
+        <v>5</v>
       </c>
       <c r="H660" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="I660" t="n">
-        <v>13</v>
+        <v>1.73</v>
       </c>
       <c r="J660" t="n">
-        <v>0.8012162051113485</v>
+        <v>0.1880142834963515</v>
       </c>
       <c r="K660" t="n">
-        <v>0.1260580162708521</v>
+        <v>0.2685918335662164</v>
       </c>
       <c r="L660" t="n">
-        <v>0.07272577861779932</v>
+        <v>0.5433938829374321</v>
       </c>
       <c r="M660" t="n">
-        <v>0.05771403737505443</v>
+        <v>0.06374896779521055</v>
       </c>
       <c r="N660" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O660" t="n">
-        <v>0.6819522550436041</v>
+        <v>0.1319563686847687</v>
       </c>
       <c r="P660" t="n">
-        <v>0.2742901711558433</v>
+        <v>0.3100301325321198</v>
       </c>
       <c r="Q660" t="n">
-        <v>0.04375757380055258</v>
+        <v>0.5580134987831116</v>
       </c>
       <c r="R660" t="n">
         <v>1</v>
       </c>
       <c r="S660" t="n">
-        <v>-0.1192639500677444</v>
+        <v>0.0146196158456795</v>
       </c>
       <c r="T660" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U660" t="n">
-        <v>-0.1192639500677444</v>
+        <v>0.0146196158456795</v>
       </c>
       <c r="V660" t="n">
-        <v>0.6819522550436041</v>
+        <v>0.5580134987831116</v>
       </c>
       <c r="W660" t="n">
-        <v>1.18</v>
+        <v>1.73</v>
       </c>
       <c r="X660" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y660" t="inlineStr"/>
       <c r="Z660" t="n">
-        <v>1.22937872863576</v>
+        <v>5.859141737222672</v>
       </c>
       <c r="AA660" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB660" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC660" t="inlineStr"/>
@@ -66254,96 +66258,96 @@
     <row r="661">
       <c r="A661" s="1" t="inlineStr">
         <is>
-          <t>dIb5Hj16</t>
+          <t>8Ohqd6Bs</t>
         </is>
       </c>
       <c r="B661" s="2" t="n">
-        <v>45632.69791666666</v>
+        <v>45630.70833333334</v>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F661" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G661" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="H661" t="n">
         <v>3.4</v>
       </c>
       <c r="I661" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="J661" t="n">
-        <v>0.472913616398243</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="K661" t="n">
-        <v>0.2781844802342606</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="L661" t="n">
-        <v>0.2489019033674963</v>
+        <v>0.4415584415584415</v>
       </c>
       <c r="M661" t="n">
-        <v>0.05727554179566563</v>
+        <v>0.05335157318741457</v>
       </c>
       <c r="N661" t="n">
         <v>2</v>
       </c>
       <c r="O661" t="n">
-        <v>0.1524676050625625</v>
+        <v>0.1275329440832138</v>
       </c>
       <c r="P661" t="n">
-        <v>0.402080435051089</v>
+        <v>0.3165941536426544</v>
       </c>
       <c r="Q661" t="n">
-        <v>0.4454519598863484</v>
+        <v>0.555872917175293</v>
       </c>
       <c r="R661" t="n">
         <v>1</v>
       </c>
       <c r="S661" t="n">
-        <v>0.1965500565188521</v>
+        <v>0.1143144756168514</v>
       </c>
       <c r="T661" t="n">
         <v>2</v>
       </c>
       <c r="U661" t="n">
-        <v>0.1965500565188521</v>
+        <v>0.1143144756168514</v>
       </c>
       <c r="V661" t="n">
-        <v>0.4454519598863484</v>
+        <v>0.555872917175293</v>
       </c>
       <c r="W661" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="X661" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y661" t="inlineStr"/>
       <c r="Z661" t="n">
-        <v>7.389913115770542</v>
+        <v>5.836665630340576</v>
       </c>
       <c r="AA661" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB661" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC661" t="inlineStr"/>
@@ -66353,96 +66357,96 @@
     <row r="662">
       <c r="A662" s="1" t="inlineStr">
         <is>
-          <t>pvu0wYNP</t>
+          <t>Cda5RZlg</t>
         </is>
       </c>
       <c r="B662" s="2" t="n">
-        <v>45633.45833333334</v>
+        <v>45632.70833333334</v>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F662" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G662" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="H662" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I662" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="J662" t="n">
-        <v>0.3463687150837989</v>
+        <v>0.4982964224872232</v>
       </c>
       <c r="K662" t="n">
-        <v>0.3072625698324022</v>
+        <v>0.2913117546848382</v>
       </c>
       <c r="L662" t="n">
-        <v>0.3463687150837989</v>
+        <v>0.2103918228279387</v>
       </c>
       <c r="M662" t="n">
-        <v>0.04985337243401755</v>
+        <v>0.0562303193882141</v>
       </c>
       <c r="N662" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O662" t="n">
-        <v>0.2115151381454063</v>
+        <v>0.3950425386428833</v>
       </c>
       <c r="P662" t="n">
-        <v>0.3482433293572979</v>
+        <v>0.4416070282459259</v>
       </c>
       <c r="Q662" t="n">
-        <v>0.4402415324972958</v>
+        <v>0.1633504033088684</v>
       </c>
       <c r="R662" t="n">
         <v>1</v>
       </c>
       <c r="S662" t="n">
-        <v>0.09387281741349685</v>
+        <v>0.1502952735610877</v>
       </c>
       <c r="T662" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U662" t="n">
-        <v>0.09387281741349685</v>
+        <v>0.1502952735610877</v>
       </c>
       <c r="V662" t="n">
-        <v>0.4402415324972958</v>
+        <v>0.4416070282459259</v>
       </c>
       <c r="W662" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="X662" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y662" t="inlineStr"/>
       <c r="Z662" t="n">
-        <v>4.894396812907699</v>
+        <v>4.636873796582222</v>
       </c>
       <c r="AA662" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB662" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC662" t="inlineStr"/>
@@ -66452,96 +66456,96 @@
     <row r="663">
       <c r="A663" s="1" t="inlineStr">
         <is>
-          <t>A3XoUTpC</t>
+          <t>txiMNilI</t>
         </is>
       </c>
       <c r="B663" s="2" t="n">
-        <v>45633.58333333334</v>
+        <v>45633.41666666666</v>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E663" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F663" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G663" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H663" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I663" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="J663" t="n">
-        <v>0.5539358600583091</v>
+        <v>0.5220012055455093</v>
       </c>
       <c r="K663" t="n">
-        <v>0.2478134110787172</v>
+        <v>0.2610006027727547</v>
       </c>
       <c r="L663" t="n">
-        <v>0.1982507288629737</v>
+        <v>0.216998191681736</v>
       </c>
       <c r="M663" t="n">
-        <v>0.0619195046439629</v>
+        <v>0.0642802155504234</v>
       </c>
       <c r="N663" t="n">
         <v>1</v>
       </c>
       <c r="O663" t="n">
-        <v>0.4485956599638385</v>
+        <v>0.4089520275592804</v>
       </c>
       <c r="P663" t="n">
-        <v>0.3367607009925253</v>
+        <v>0.3634155988693237</v>
       </c>
       <c r="Q663" t="n">
-        <v>0.2146436390436363</v>
+        <v>0.2276323586702347</v>
       </c>
       <c r="R663" t="n">
         <v>1</v>
       </c>
       <c r="S663" t="n">
-        <v>-0.1053402000944705</v>
+        <v>-0.1130491779862289</v>
       </c>
       <c r="T663" t="n">
         <v>1</v>
       </c>
       <c r="U663" t="n">
-        <v>-0.1053402000944705</v>
+        <v>-0.1130491779862289</v>
       </c>
       <c r="V663" t="n">
-        <v>0.4485956599638385</v>
+        <v>0.4089520275592804</v>
       </c>
       <c r="W663" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="X663" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y663" t="inlineStr"/>
       <c r="Z663" t="n">
-        <v>0.1634091575157384</v>
+        <v>4.293996289372444</v>
       </c>
       <c r="AA663" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB663" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC663" t="inlineStr"/>
@@ -66551,195 +66555,197 @@
     <row r="664">
       <c r="A664" s="1" t="inlineStr">
         <is>
-          <t>I9fDpkVh</t>
+          <t>hGKvtZ3n</t>
         </is>
       </c>
       <c r="B664" s="2" t="n">
-        <v>45633.69791666666</v>
+        <v>45633.51041666666</v>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F664" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G664" t="n">
-        <v>1.55</v>
+        <v>4.1</v>
       </c>
       <c r="H664" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="I664" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J664" t="n">
-        <v>0.6111289803795432</v>
+        <v>0.2287747839349263</v>
       </c>
       <c r="K664" t="n">
-        <v>0.1994210357027983</v>
+        <v>0.2501270971021861</v>
       </c>
       <c r="L664" t="n">
-        <v>0.1894499839176584</v>
+        <v>0.5210981189628877</v>
       </c>
       <c r="M664" t="n">
-        <v>0.05568760611205437</v>
+        <v>0.06612466124661243</v>
       </c>
       <c r="N664" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O664" t="n">
-        <v>0.6709779833537367</v>
+        <v>0.1309074908494949</v>
       </c>
       <c r="P664" t="n">
-        <v>0.2498808355915251</v>
+        <v>0.3584269881248474</v>
       </c>
       <c r="Q664" t="n">
-        <v>0.07914118105473826</v>
+        <v>0.5106655359268188</v>
       </c>
       <c r="R664" t="n">
         <v>1</v>
       </c>
       <c r="S664" t="n">
-        <v>0.05984900297419349</v>
+        <v>-0.01043258303606887</v>
       </c>
       <c r="T664" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U664" t="n">
-        <v>0.05984900297419349</v>
+        <v>-0.01043258303606887</v>
       </c>
       <c r="V664" t="n">
-        <v>0.6709779833537367</v>
+        <v>0.5106655359268188</v>
       </c>
       <c r="W664" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="X664" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y664" t="inlineStr"/>
       <c r="Z664" t="n">
-        <v>5.462243971503064</v>
+        <v>4.021491095423698</v>
       </c>
       <c r="AA664" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB664" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC664" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC664" t="n">
+        <v>1</v>
+      </c>
       <c r="AD664" t="inlineStr"/>
       <c r="AE664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" s="1" t="inlineStr">
         <is>
-          <t>UVdDFUVI</t>
+          <t>bTkuvDYb</t>
         </is>
       </c>
       <c r="B665" s="2" t="n">
-        <v>45634.35416666666</v>
+        <v>45633.60416666666</v>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E665" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F665" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G665" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="H665" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="I665" t="n">
-        <v>6.25</v>
+        <v>3.4</v>
       </c>
       <c r="J665" t="n">
-        <v>0.6386964914272737</v>
+        <v>0.4093097913322633</v>
       </c>
       <c r="K665" t="n">
-        <v>0.2100601794027478</v>
+        <v>0.3138041733547351</v>
       </c>
       <c r="L665" t="n">
-        <v>0.1512433291699784</v>
+        <v>0.2768860353130016</v>
       </c>
       <c r="M665" t="n">
-        <v>0.0578978978978979</v>
+        <v>0.06223358908780918</v>
       </c>
       <c r="N665" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O665" t="n">
-        <v>0.4956919986152321</v>
+        <v>0.3098367154598236</v>
       </c>
       <c r="P665" t="n">
-        <v>0.3861540012743248</v>
+        <v>0.5194622278213501</v>
       </c>
       <c r="Q665" t="n">
-        <v>0.1181540001104432</v>
+        <v>0.1707010269165039</v>
       </c>
       <c r="R665" t="n">
         <v>1</v>
       </c>
       <c r="S665" t="n">
-        <v>-0.1430044928120416</v>
+        <v>0.205658054466615</v>
       </c>
       <c r="T665" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U665" t="n">
-        <v>-0.1430044928120416</v>
+        <v>0.205658054466615</v>
       </c>
       <c r="V665" t="n">
-        <v>0.4956919986152321</v>
+        <v>0.5194622278213501</v>
       </c>
       <c r="W665" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="X665" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y665" t="inlineStr"/>
       <c r="Z665" t="n">
-        <v>0</v>
+        <v>5.454353392124176</v>
       </c>
       <c r="AA665" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB665" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC665" t="inlineStr"/>
@@ -66749,96 +66755,96 @@
     <row r="666">
       <c r="A666" s="1" t="inlineStr">
         <is>
-          <t>GMVVXBom</t>
+          <t>YBmEPDJ5</t>
         </is>
       </c>
       <c r="B666" s="2" t="n">
-        <v>45634.45833333334</v>
+        <v>45633.70833333334</v>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F666" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G666" t="n">
-        <v>2.45</v>
+        <v>4.75</v>
       </c>
       <c r="H666" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="I666" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J666" t="n">
-        <v>0.3872529245663574</v>
+        <v>0.1969317470256731</v>
       </c>
       <c r="K666" t="n">
-        <v>0.3162565550625252</v>
+        <v>0.2528177833437695</v>
       </c>
       <c r="L666" t="n">
-        <v>0.2964905203711174</v>
+        <v>0.5502504696305573</v>
       </c>
       <c r="M666" t="n">
-        <v>0.05399659863945572</v>
+        <v>0.06903188017739104</v>
       </c>
       <c r="N666" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O666" t="n">
-        <v>0.4429670897822505</v>
+        <v>0.1717308014631271</v>
       </c>
       <c r="P666" t="n">
-        <v>0.4301544548924254</v>
+        <v>0.2694768905639648</v>
       </c>
       <c r="Q666" t="n">
-        <v>0.1268784553253241</v>
+        <v>0.5587922930717468</v>
       </c>
       <c r="R666" t="n">
         <v>1</v>
       </c>
       <c r="S666" t="n">
-        <v>0.05571416521589306</v>
+        <v>0.008541823441189478</v>
       </c>
       <c r="T666" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U666" t="n">
-        <v>0.05571416521589306</v>
+        <v>0.008541823441189478</v>
       </c>
       <c r="V666" t="n">
-        <v>0.4429670897822505</v>
+        <v>0.5587922930717468</v>
       </c>
       <c r="W666" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="X666" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y666" t="inlineStr"/>
       <c r="Z666" t="n">
-        <v>3.994942503874936</v>
+        <v>5.867319077253342</v>
       </c>
       <c r="AA666" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB666" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC666" t="inlineStr"/>
@@ -66848,197 +66854,195 @@
     <row r="667">
       <c r="A667" s="1" t="inlineStr">
         <is>
-          <t>O6cLrTa5</t>
+          <t>x4pVLVIU</t>
         </is>
       </c>
       <c r="B667" s="2" t="n">
-        <v>45634.58333333334</v>
+        <v>45634.41666666666</v>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F667" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G667" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="H667" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I667" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="J667" t="n">
-        <v>0.3401778496362166</v>
+        <v>0.2503639010189229</v>
       </c>
       <c r="K667" t="n">
-        <v>0.2976556184316895</v>
+        <v>0.3129548762736535</v>
       </c>
       <c r="L667" t="n">
-        <v>0.3621665319320937</v>
+        <v>0.4366812227074235</v>
       </c>
       <c r="M667" t="n">
-        <v>0.04987099402498663</v>
+        <v>0.06511627906976747</v>
       </c>
       <c r="N667" t="n">
         <v>0</v>
       </c>
       <c r="O667" t="n">
-        <v>0.3205599158752609</v>
+        <v>0.3164181709289551</v>
       </c>
       <c r="P667" t="n">
-        <v>0.3801074283004797</v>
+        <v>0.3465518057346344</v>
       </c>
       <c r="Q667" t="n">
-        <v>0.2993326558242593</v>
+        <v>0.3370300531387329</v>
       </c>
       <c r="R667" t="n">
         <v>1</v>
       </c>
       <c r="S667" t="n">
-        <v>0.08245180986879014</v>
+        <v>0.03359692946098086</v>
       </c>
       <c r="T667" t="n">
         <v>0</v>
       </c>
       <c r="U667" t="n">
-        <v>0.08245180986879014</v>
+        <v>0.03359692946098086</v>
       </c>
       <c r="V667" t="n">
-        <v>0.3801074283004797</v>
+        <v>0.3465518057346344</v>
       </c>
       <c r="W667" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="X667" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y667" t="inlineStr"/>
       <c r="Z667" t="n">
-        <v>3.194616004990381</v>
+        <v>3.638793960213661</v>
       </c>
       <c r="AA667" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB667" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC667" t="n">
-        <v>1</v>
-      </c>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC667" t="inlineStr"/>
       <c r="AD667" t="inlineStr"/>
       <c r="AE667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" s="1" t="inlineStr">
         <is>
-          <t>Ms14nB0t</t>
+          <t>SYQn9hZO</t>
         </is>
       </c>
       <c r="B668" s="2" t="n">
-        <v>45634.69791666666</v>
+        <v>45634.51041666666</v>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E668" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F668" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G668" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="H668" t="n">
         <v>3.5</v>
       </c>
       <c r="I668" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J668" t="n">
-        <v>0.5011933174224343</v>
+        <v>0.4569015166058744</v>
       </c>
       <c r="K668" t="n">
-        <v>0.2720763723150358</v>
+        <v>0.2676137454405835</v>
       </c>
       <c r="L668" t="n">
-        <v>0.2267303102625298</v>
+        <v>0.2754847379535419</v>
       </c>
       <c r="M668" t="n">
-        <v>0.05012531328320802</v>
+        <v>0.06763681082188988</v>
       </c>
       <c r="N668" t="n">
         <v>1</v>
       </c>
       <c r="O668" t="n">
-        <v>0.4210781796623052</v>
+        <v>0.4779868423938751</v>
       </c>
       <c r="P668" t="n">
-        <v>0.2406412996342734</v>
+        <v>0.1914146095514297</v>
       </c>
       <c r="Q668" t="n">
-        <v>0.3382805207034215</v>
+        <v>0.3305985629558563</v>
       </c>
       <c r="R668" t="n">
         <v>1</v>
       </c>
       <c r="S668" t="n">
-        <v>-0.08011513776012913</v>
+        <v>0.02108532578800071</v>
       </c>
       <c r="T668" t="n">
         <v>1</v>
       </c>
       <c r="U668" t="n">
-        <v>-0.08011513776012913</v>
+        <v>0.02108532578800071</v>
       </c>
       <c r="V668" t="n">
-        <v>0.4210781796623052</v>
+        <v>0.4779868423938751</v>
       </c>
       <c r="W668" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="X668" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y668" t="inlineStr"/>
       <c r="Z668" t="n">
-        <v>0.6037057717307321</v>
+        <v>5.018861845135689</v>
       </c>
       <c r="AA668" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB668" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC668" t="inlineStr"/>
@@ -67048,96 +67052,96 @@
     <row r="669">
       <c r="A669" s="1" t="inlineStr">
         <is>
-          <t>6VQfS7FO</t>
+          <t>6ggmxi3B</t>
         </is>
       </c>
       <c r="B669" s="2" t="n">
-        <v>45635.69791666666</v>
+        <v>45634.60416666666</v>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E669" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F669" t="n">
-        <v>771</v>
+        <v>1481</v>
       </c>
       <c r="G669" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="H669" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="I669" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="J669" t="n">
-        <v>0.3491271820448877</v>
+        <v>0.4564841498559078</v>
       </c>
       <c r="K669" t="n">
-        <v>0.314214463840399</v>
+        <v>0.2835734870317003</v>
       </c>
       <c r="L669" t="n">
-        <v>0.3366583541147132</v>
+        <v>0.2599423631123919</v>
       </c>
       <c r="M669" t="n">
-        <v>0.06084656084656093</v>
+        <v>0.06861295885686136</v>
       </c>
       <c r="N669" t="n">
         <v>1</v>
       </c>
       <c r="O669" t="n">
-        <v>0.4058053964949509</v>
+        <v>0.3984593152999878</v>
       </c>
       <c r="P669" t="n">
-        <v>0.3780843172166185</v>
+        <v>0.2241911292076111</v>
       </c>
       <c r="Q669" t="n">
-        <v>0.2161102862884306</v>
+        <v>0.3773495554924011</v>
       </c>
       <c r="R669" t="n">
         <v>1</v>
       </c>
       <c r="S669" t="n">
-        <v>0.05667821445006316</v>
+        <v>-0.05802483455592</v>
       </c>
       <c r="T669" t="n">
         <v>1</v>
       </c>
       <c r="U669" t="n">
-        <v>0.05667821445006316</v>
+        <v>-0.05802483455592</v>
       </c>
       <c r="V669" t="n">
-        <v>0.4058053964949509</v>
+        <v>0.3984593152999878</v>
       </c>
       <c r="W669" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="X669" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y669" t="inlineStr"/>
       <c r="Z669" t="n">
-        <v>3.795109525771221</v>
+        <v>4.183822810649872</v>
       </c>
       <c r="AA669" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB669" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="AC669" t="inlineStr"/>
@@ -67147,97 +67151,121 @@
     <row r="670">
       <c r="A670" s="1" t="inlineStr">
         <is>
-          <t>vsfdptyA</t>
+          <t>6adcTeKt</t>
         </is>
       </c>
       <c r="B670" s="2" t="n">
-        <v>45639.69791666666</v>
+        <v>45634.70833333334</v>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E670" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="F670" t="n">
-        <v>771</v>
-      </c>
-      <c r="G670" t="inlineStr"/>
-      <c r="H670" t="inlineStr"/>
-      <c r="I670" t="inlineStr"/>
-      <c r="J670" t="inlineStr"/>
-      <c r="K670" t="inlineStr"/>
-      <c r="L670" t="inlineStr"/>
-      <c r="M670" t="inlineStr"/>
+        <v>1481</v>
+      </c>
+      <c r="G670" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H670" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I670" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J670" t="n">
+        <v>0.6386964914272737</v>
+      </c>
+      <c r="K670" t="n">
+        <v>0.2100601794027478</v>
+      </c>
+      <c r="L670" t="n">
+        <v>0.1512433291699784</v>
+      </c>
+      <c r="M670" t="n">
+        <v>0.0578978978978979</v>
+      </c>
       <c r="N670" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O670" t="n">
-        <v>0.1019052334408661</v>
+        <v>0.488122969865799</v>
       </c>
       <c r="P670" t="n">
-        <v>0.3290946163935401</v>
+        <v>0.3047187328338623</v>
       </c>
       <c r="Q670" t="n">
-        <v>0.5690001501655938</v>
+        <v>0.2071582823991776</v>
       </c>
       <c r="R670" t="n">
         <v>1</v>
       </c>
-      <c r="S670" t="inlineStr"/>
+      <c r="S670" t="n">
+        <v>-0.1505735215614747</v>
+      </c>
       <c r="T670" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U670" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U670" t="n">
+        <v>-0.1505735215614747</v>
+      </c>
       <c r="V670" t="n">
-        <v>0.4309998498344062</v>
-      </c>
-      <c r="W670" t="inlineStr"/>
+        <v>0.488122969865799</v>
+      </c>
+      <c r="W670" t="n">
+        <v>1.48</v>
+      </c>
       <c r="X670" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y670" t="inlineStr"/>
-      <c r="Z670" t="inlineStr"/>
+      <c r="Z670" t="n">
+        <v>3.843968387693167</v>
+      </c>
       <c r="AA670" t="inlineStr">
         <is>
-          <t>italy</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="AB670" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="AC670" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="AC670" t="n">
+        <v>1</v>
+      </c>
       <c r="AD670" t="inlineStr"/>
       <c r="AE670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" s="1" t="inlineStr">
         <is>
-          <t>j97t2JLs</t>
+          <t>QiBthjLU</t>
         </is>
       </c>
       <c r="B671" s="2" t="n">
-        <v>45625.70833333334</v>
+        <v>45635.70833333334</v>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E671" t="n">
@@ -67247,55 +67275,55 @@
         <v>1481</v>
       </c>
       <c r="G671" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="H671" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="I671" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="J671" t="n">
-        <v>0.4736842105263159</v>
+        <v>0.5455009851857258</v>
       </c>
       <c r="K671" t="n">
-        <v>0.3157894736842106</v>
+        <v>0.2903743705757863</v>
       </c>
       <c r="L671" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1641246442384879</v>
       </c>
       <c r="M671" t="n">
-        <v>0.05555555555555536</v>
+        <v>0.05964003325149347</v>
       </c>
       <c r="N671" t="n">
         <v>1</v>
       </c>
       <c r="O671" t="n">
-        <v>0.6148039698600769</v>
+        <v>0.5763322114944458</v>
       </c>
       <c r="P671" t="n">
-        <v>0.2291441261768341</v>
+        <v>0.1866425275802612</v>
       </c>
       <c r="Q671" t="n">
-        <v>0.1560518741607666</v>
+        <v>0.237025260925293</v>
       </c>
       <c r="R671" t="n">
         <v>1</v>
       </c>
       <c r="S671" t="n">
-        <v>0.141119759333761</v>
+        <v>0.03083122630872004</v>
       </c>
       <c r="T671" t="n">
         <v>1</v>
       </c>
       <c r="U671" t="n">
-        <v>0.141119759333761</v>
+        <v>0.03083122630872004</v>
       </c>
       <c r="V671" t="n">
-        <v>0.6148039698600769</v>
+        <v>0.5763322114944458</v>
       </c>
       <c r="W671" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="X671" t="inlineStr">
         <is>
@@ -67304,7 +67332,7 @@
       </c>
       <c r="Y671" t="inlineStr"/>
       <c r="Z671" t="n">
-        <v>6.455441683530807</v>
+        <v>4.538616165518761</v>
       </c>
       <c r="AA671" t="inlineStr">
         <is>
@@ -67316,27 +67344,29 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC671" t="inlineStr"/>
+      <c r="AC671" t="n">
+        <v>1</v>
+      </c>
       <c r="AD671" t="inlineStr"/>
       <c r="AE671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" s="1" t="inlineStr">
         <is>
-          <t>KQGA7ubK</t>
+          <t>GjcexCK8</t>
         </is>
       </c>
       <c r="B672" s="2" t="n">
-        <v>45626.41666666666</v>
+        <v>45639.70833333334</v>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E672" t="n">
@@ -67345,66 +67375,44 @@
       <c r="F672" t="n">
         <v>1481</v>
       </c>
-      <c r="G672" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H672" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I672" t="n">
-        <v>13</v>
-      </c>
-      <c r="J672" t="n">
-        <v>0.8145663632007667</v>
-      </c>
-      <c r="K672" t="n">
-        <v>0.1121226641111643</v>
-      </c>
-      <c r="L672" t="n">
-        <v>0.07331097268806899</v>
-      </c>
-      <c r="M672" t="n">
-        <v>0.04927099044746108</v>
-      </c>
+      <c r="G672" t="inlineStr"/>
+      <c r="H672" t="inlineStr"/>
+      <c r="I672" t="inlineStr"/>
+      <c r="J672" t="inlineStr"/>
+      <c r="K672" t="inlineStr"/>
+      <c r="L672" t="inlineStr"/>
+      <c r="M672" t="inlineStr"/>
       <c r="N672" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O672" t="n">
-        <v>0.6315798163414001</v>
+        <v>0.1504876017570496</v>
       </c>
       <c r="P672" t="n">
-        <v>0.2134162187576294</v>
+        <v>0.3762744665145874</v>
       </c>
       <c r="Q672" t="n">
-        <v>0.1550039499998093</v>
+        <v>0.4732378721237183</v>
       </c>
       <c r="R672" t="n">
         <v>1</v>
       </c>
-      <c r="S672" t="n">
-        <v>-0.1829865468593666</v>
-      </c>
+      <c r="S672" t="inlineStr"/>
       <c r="T672" t="n">
-        <v>1</v>
-      </c>
-      <c r="U672" t="n">
-        <v>-0.1829865468593666</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U672" t="inlineStr"/>
       <c r="V672" t="n">
-        <v>0.6315798163414001</v>
-      </c>
-      <c r="W672" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0.5267621278762817</v>
+      </c>
+      <c r="W672" t="inlineStr"/>
       <c r="X672" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="Y672" t="inlineStr"/>
-      <c r="Z672" t="n">
-        <v>6.631588071584702</v>
-      </c>
+      <c r="Z672" t="inlineStr"/>
       <c r="AA672" t="inlineStr">
         <is>
           <t>spain</t>
@@ -67422,96 +67430,96 @@
     <row r="673">
       <c r="A673" s="1" t="inlineStr">
         <is>
-          <t>WIFl0cjf</t>
+          <t>tQAc65y8</t>
         </is>
       </c>
       <c r="B673" s="2" t="n">
-        <v>45626.51041666666</v>
+        <v>45625.69791666666</v>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F673" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G673" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="H673" t="n">
         <v>3.4</v>
       </c>
       <c r="I673" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="J673" t="n">
-        <v>0.5292652552926526</v>
+        <v>0.4931894569255263</v>
       </c>
       <c r="K673" t="n">
-        <v>0.2801992528019925</v>
+        <v>0.2770564302140457</v>
       </c>
       <c r="L673" t="n">
-        <v>0.1905354919053549</v>
+        <v>0.2297541128604281</v>
       </c>
       <c r="M673" t="n">
-        <v>0.04967320261437913</v>
+        <v>0.06158029550729749</v>
       </c>
       <c r="N673" t="n">
         <v>0</v>
       </c>
       <c r="O673" t="n">
-        <v>0.2924555242061615</v>
+        <v>0.2835758085818864</v>
       </c>
       <c r="P673" t="n">
-        <v>0.3657283782958984</v>
+        <v>0.4145972522413352</v>
       </c>
       <c r="Q673" t="n">
-        <v>0.3418160378932953</v>
+        <v>0.3018269391767783</v>
       </c>
       <c r="R673" t="n">
         <v>1</v>
       </c>
       <c r="S673" t="n">
-        <v>0.0855291254939059</v>
+        <v>0.1375408220272895</v>
       </c>
       <c r="T673" t="n">
         <v>0</v>
       </c>
       <c r="U673" t="n">
-        <v>0.0855291254939059</v>
+        <v>0.1375408220272895</v>
       </c>
       <c r="V673" t="n">
-        <v>0.3657283782958984</v>
+        <v>0.4145972522413352</v>
       </c>
       <c r="W673" t="n">
         <v>3.4</v>
       </c>
       <c r="X673" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y673" t="inlineStr"/>
       <c r="Z673" t="n">
-        <v>3.840147972106934</v>
+        <v>5.79744977982056</v>
       </c>
       <c r="AA673" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB673" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC673" t="inlineStr"/>
@@ -67521,96 +67529,96 @@
     <row r="674">
       <c r="A674" s="1" t="inlineStr">
         <is>
-          <t>hvDYgCjI</t>
+          <t>OlzrEHfE</t>
         </is>
       </c>
       <c r="B674" s="2" t="n">
-        <v>45626.60416666666</v>
+        <v>45626.45833333334</v>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>como</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E674" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F674" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G674" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H674" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I674" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J674" t="n">
-        <v>0.288135593220339</v>
+        <v>0.4698795180722892</v>
       </c>
       <c r="K674" t="n">
-        <v>0.2796610169491525</v>
+        <v>0.2891566265060241</v>
       </c>
       <c r="L674" t="n">
-        <v>0.4322033898305084</v>
+        <v>0.2409638554216868</v>
       </c>
       <c r="M674" t="n">
-        <v>0.05169340463458116</v>
+        <v>0.0641025641025641</v>
       </c>
       <c r="N674" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O674" t="n">
-        <v>0.110199049115181</v>
+        <v>0.2396538928833228</v>
       </c>
       <c r="P674" t="n">
-        <v>0.2768021821975708</v>
+        <v>0.4572605132748576</v>
       </c>
       <c r="Q674" t="n">
-        <v>0.6129987239837646</v>
+        <v>0.3030855938418196</v>
       </c>
       <c r="R674" t="n">
         <v>1</v>
       </c>
       <c r="S674" t="n">
-        <v>0.1807953341532562</v>
+        <v>0.1681038867688335</v>
       </c>
       <c r="T674" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U674" t="n">
-        <v>0.1807953341532562</v>
+        <v>0.1681038867688335</v>
       </c>
       <c r="V674" t="n">
-        <v>0.6129987239837646</v>
+        <v>0.4572605132748576</v>
       </c>
       <c r="W674" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="X674" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y674" t="inlineStr"/>
       <c r="Z674" t="n">
-        <v>4.827364951372147</v>
+        <v>4.924744650344067</v>
       </c>
       <c r="AA674" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB674" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC674" t="n">
@@ -67622,96 +67630,96 @@
     <row r="675">
       <c r="A675" s="1" t="inlineStr">
         <is>
-          <t>0b75dFkJ</t>
+          <t>OCIU4DH0</t>
         </is>
       </c>
       <c r="B675" s="2" t="n">
-        <v>45626.70833333334</v>
+        <v>45626.58333333334</v>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F675" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G675" t="n">
-        <v>6</v>
+        <v>1.36</v>
       </c>
       <c r="H675" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="I675" t="n">
-        <v>1.53</v>
+        <v>9</v>
       </c>
       <c r="J675" t="n">
-        <v>0.1574768416409351</v>
+        <v>0.6956875508543532</v>
       </c>
       <c r="K675" t="n">
-        <v>0.2249669166299073</v>
+        <v>0.199186330349878</v>
       </c>
       <c r="L675" t="n">
-        <v>0.6175562417291575</v>
+        <v>0.1051261187957689</v>
       </c>
       <c r="M675" t="n">
-        <v>0.05835667600373484</v>
+        <v>0.05693154454764349</v>
       </c>
       <c r="N675" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O675" t="n">
-        <v>0.09451180696487427</v>
+        <v>0.7836830058460498</v>
       </c>
       <c r="P675" t="n">
-        <v>0.2090925276279449</v>
+        <v>0.1814076152230594</v>
       </c>
       <c r="Q675" t="n">
-        <v>0.6963956356048584</v>
+        <v>0.03490937893089069</v>
       </c>
       <c r="R675" t="n">
         <v>1</v>
       </c>
       <c r="S675" t="n">
-        <v>0.07883939387570094</v>
+        <v>0.08799545499169659</v>
       </c>
       <c r="T675" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U675" t="n">
-        <v>0.07883939387570094</v>
+        <v>0.08799545499169659</v>
       </c>
       <c r="V675" t="n">
-        <v>0.6963956356048584</v>
+        <v>0.7836830058460498</v>
       </c>
       <c r="W675" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="X675" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y675" t="inlineStr"/>
       <c r="Z675" t="n">
-        <v>7.312154173851013</v>
+        <v>9.152623838796337</v>
       </c>
       <c r="AA675" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB675" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC675" t="inlineStr"/>
@@ -67721,96 +67729,96 @@
     <row r="676">
       <c r="A676" s="1" t="inlineStr">
         <is>
-          <t>bgZVCzz0</t>
+          <t>lIhj8R6e</t>
         </is>
       </c>
       <c r="B676" s="2" t="n">
-        <v>45627.41666666666</v>
+        <v>45626.69791666666</v>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F676" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G676" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="H676" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I676" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="J676" t="n">
-        <v>0.5180518051805181</v>
+        <v>0.5755850727387729</v>
       </c>
       <c r="K676" t="n">
-        <v>0.2562256225622562</v>
+        <v>0.243516761543327</v>
       </c>
       <c r="L676" t="n">
-        <v>0.2257225722572257</v>
+        <v>0.1808981657179</v>
       </c>
       <c r="M676" t="n">
-        <v>0.05481359579720224</v>
+        <v>0.05294705294705304</v>
       </c>
       <c r="N676" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O676" t="n">
-        <v>0.1948871463537216</v>
+        <v>0.4702693431392767</v>
       </c>
       <c r="P676" t="n">
-        <v>0.1989489793777466</v>
+        <v>0.3998042762184685</v>
       </c>
       <c r="Q676" t="n">
-        <v>0.6061638593673706</v>
+        <v>0.1299263806422548</v>
       </c>
       <c r="R676" t="n">
         <v>1</v>
       </c>
       <c r="S676" t="n">
-        <v>0.3804412871101449</v>
+        <v>-0.1053157295994963</v>
       </c>
       <c r="T676" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U676" t="n">
-        <v>0.3804412871101449</v>
+        <v>-0.1053157295994963</v>
       </c>
       <c r="V676" t="n">
-        <v>0.6061638593673706</v>
+        <v>0.4702693431392767</v>
       </c>
       <c r="W676" t="n">
-        <v>4.2</v>
+        <v>1.65</v>
       </c>
       <c r="X676" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y676" t="inlineStr"/>
       <c r="Z676" t="n">
-        <v>6.364720523357391</v>
+        <v>3.832012942167694</v>
       </c>
       <c r="AA676" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB676" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC676" t="inlineStr"/>
@@ -67820,96 +67828,96 @@
     <row r="677">
       <c r="A677" s="1" t="inlineStr">
         <is>
-          <t>CxyOEd5m</t>
+          <t>2J5dJCWg</t>
         </is>
       </c>
       <c r="B677" s="2" t="n">
-        <v>45627.51041666666</v>
+        <v>45627.35416666666</v>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F677" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G677" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="H677" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="I677" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J677" t="n">
-        <v>0.6953028430160691</v>
+        <v>0.4748201438848921</v>
       </c>
       <c r="K677" t="n">
-        <v>0.2101359703337453</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="L677" t="n">
-        <v>0.09456118665018541</v>
+        <v>0.2374100719424461</v>
       </c>
       <c r="M677" t="n">
-        <v>0.05751633986928106</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="N677" t="n">
         <v>1</v>
       </c>
       <c r="O677" t="n">
-        <v>0.5046667456626892</v>
+        <v>0.5204416974359901</v>
       </c>
       <c r="P677" t="n">
-        <v>0.3227453529834747</v>
+        <v>0.2817129282240267</v>
       </c>
       <c r="Q677" t="n">
-        <v>0.1725879162549973</v>
+        <v>0.1978453743399832</v>
       </c>
       <c r="R677" t="n">
         <v>1</v>
       </c>
       <c r="S677" t="n">
-        <v>-0.1906360973533799</v>
+        <v>0.04562155355109798</v>
       </c>
       <c r="T677" t="n">
         <v>1</v>
       </c>
       <c r="U677" t="n">
-        <v>-0.1906360973533799</v>
+        <v>0.04562155355109798</v>
       </c>
       <c r="V677" t="n">
-        <v>0.5046667456626892</v>
+        <v>0.5204416974359901</v>
       </c>
       <c r="W677" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="X677" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y677" t="inlineStr"/>
       <c r="Z677" t="n">
-        <v>5.299000829458237</v>
+        <v>5.943664135364425</v>
       </c>
       <c r="AA677" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB677" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC677" t="inlineStr"/>
@@ -67919,96 +67927,96 @@
     <row r="678">
       <c r="A678" s="1" t="inlineStr">
         <is>
-          <t>4WDdbyL6</t>
+          <t>rFYV2inD</t>
         </is>
       </c>
       <c r="B678" s="2" t="n">
-        <v>45627.60416666666</v>
+        <v>45627.45833333334</v>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F678" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G678" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="H678" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="I678" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J678" t="n">
-        <v>0.3401056481105241</v>
+        <v>0.225296442687747</v>
       </c>
       <c r="K678" t="n">
-        <v>0.3071921982933766</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="L678" t="n">
-        <v>0.3527021535960991</v>
+        <v>0.5256916996047432</v>
       </c>
       <c r="M678" t="n">
-        <v>0.05009387267451793</v>
+        <v>0.05680868838763575</v>
       </c>
       <c r="N678" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O678" t="n">
-        <v>0.1954513341188431</v>
+        <v>0.1610918220096157</v>
       </c>
       <c r="P678" t="n">
-        <v>0.4579564332962036</v>
+        <v>0.2816285034329082</v>
       </c>
       <c r="Q678" t="n">
-        <v>0.3465921580791473</v>
+        <v>0.5572796745574761</v>
       </c>
       <c r="R678" t="n">
         <v>1</v>
       </c>
       <c r="S678" t="n">
-        <v>0.150764235002827</v>
+        <v>0.03158797495273291</v>
       </c>
       <c r="T678" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U678" t="n">
-        <v>0.150764235002827</v>
+        <v>0.03158797495273291</v>
       </c>
       <c r="V678" t="n">
-        <v>0.4579564332962036</v>
+        <v>0.5572796745574761</v>
       </c>
       <c r="W678" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="X678" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y678" t="inlineStr"/>
       <c r="Z678" t="n">
-        <v>4.808542549610138</v>
+        <v>6.183110319857194</v>
       </c>
       <c r="AA678" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB678" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC678" t="inlineStr"/>
@@ -68018,298 +68026,294 @@
     <row r="679">
       <c r="A679" s="1" t="inlineStr">
         <is>
-          <t>S4aiKIsQ</t>
+          <t>fg2lLY1s</t>
         </is>
       </c>
       <c r="B679" s="2" t="n">
-        <v>45627.70833333334</v>
+        <v>45627.45833333334</v>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F679" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G679" t="n">
+        <v>5</v>
+      </c>
+      <c r="H679" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I679" t="n">
         <v>1.8</v>
       </c>
-      <c r="H679" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I679" t="n">
-        <v>4.5</v>
-      </c>
       <c r="J679" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.1905354919053549</v>
       </c>
       <c r="K679" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2801992528019925</v>
       </c>
       <c r="L679" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.5292652552926526</v>
       </c>
       <c r="M679" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.04967320261437913</v>
       </c>
       <c r="N679" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O679" t="n">
-        <v>0.2176385521888733</v>
+        <v>0.06960531734056917</v>
       </c>
       <c r="P679" t="n">
-        <v>0.4210319221019745</v>
+        <v>0.2214251685607912</v>
       </c>
       <c r="Q679" t="n">
-        <v>0.3613295257091522</v>
+        <v>0.7089695140986397</v>
       </c>
       <c r="R679" t="n">
         <v>1</v>
       </c>
       <c r="S679" t="n">
-        <v>0.1578740273651324</v>
+        <v>0.1797042588059872</v>
       </c>
       <c r="T679" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U679" t="n">
-        <v>0.1578740273651324</v>
+        <v>0.1797042588059872</v>
       </c>
       <c r="V679" t="n">
-        <v>0.4210319221019745</v>
+        <v>0.7089695140986397</v>
       </c>
       <c r="W679" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="X679" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y679" t="inlineStr"/>
       <c r="Z679" t="n">
-        <v>3.315626386553049</v>
+        <v>9.331074615498583</v>
       </c>
       <c r="AA679" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB679" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC679" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC679" t="inlineStr"/>
       <c r="AD679" t="inlineStr"/>
       <c r="AE679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" s="1" t="inlineStr">
         <is>
-          <t>fLSvBE4C</t>
+          <t>WEwjCePQ</t>
         </is>
       </c>
       <c r="B680" s="2" t="n">
-        <v>45628.70833333334</v>
+        <v>45627.58333333334</v>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F680" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G680" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="H680" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I680" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="J680" t="n">
-        <v>0.4509283819628648</v>
+        <v>0.2642238998342847</v>
       </c>
       <c r="K680" t="n">
-        <v>0.2785145888594165</v>
+        <v>0.2717731541152642</v>
       </c>
       <c r="L680" t="n">
-        <v>0.2705570291777188</v>
+        <v>0.4640029460504512</v>
       </c>
       <c r="M680" t="n">
-        <v>0.05602240896358524</v>
+        <v>0.05129694154084397</v>
       </c>
       <c r="N680" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O680" t="n">
-        <v>0.4133053123950958</v>
+        <v>0.09640361205414306</v>
       </c>
       <c r="P680" t="n">
-        <v>0.2662601470947266</v>
+        <v>0.276131019959361</v>
       </c>
       <c r="Q680" t="n">
-        <v>0.3204345703125</v>
+        <v>0.6274653679864959</v>
       </c>
       <c r="R680" t="n">
         <v>1</v>
       </c>
       <c r="S680" t="n">
-        <v>-0.03762306956776895</v>
+        <v>0.1634624219360447</v>
       </c>
       <c r="T680" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U680" t="n">
-        <v>-0.03762306956776895</v>
+        <v>0.1634624219360447</v>
       </c>
       <c r="V680" t="n">
-        <v>0.4133053123950958</v>
+        <v>0.6274653679864959</v>
       </c>
       <c r="W680" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="X680" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y680" t="inlineStr"/>
       <c r="Z680" t="n">
-        <v>3.25477933511138</v>
+        <v>8.304741794186677</v>
       </c>
       <c r="AA680" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB680" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC680" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC680" t="inlineStr"/>
       <c r="AD680" t="inlineStr"/>
       <c r="AE680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" s="1" t="inlineStr">
         <is>
-          <t>48cSecHb</t>
+          <t>jaKM6Znl</t>
         </is>
       </c>
       <c r="B681" s="2" t="n">
-        <v>45629.625</v>
+        <v>45627.69791666666</v>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F681" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G681" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="H681" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I681" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="J681" t="n">
-        <v>0.1880142834963515</v>
+        <v>0.1802916482545294</v>
       </c>
       <c r="K681" t="n">
-        <v>0.2685918335662164</v>
+        <v>0.2629253203711887</v>
       </c>
       <c r="L681" t="n">
-        <v>0.5433938829374321</v>
+        <v>0.556783031374282</v>
       </c>
       <c r="M681" t="n">
-        <v>0.06374896779521055</v>
+        <v>0.05648926237161533</v>
       </c>
       <c r="N681" t="n">
         <v>2</v>
       </c>
       <c r="O681" t="n">
-        <v>0.1319563686847687</v>
+        <v>0.1559592206890427</v>
       </c>
       <c r="P681" t="n">
-        <v>0.3100301325321198</v>
+        <v>0.2926569637129593</v>
       </c>
       <c r="Q681" t="n">
-        <v>0.5580134987831116</v>
+        <v>0.5513838155979981</v>
       </c>
       <c r="R681" t="n">
         <v>1</v>
       </c>
       <c r="S681" t="n">
-        <v>0.0146196158456795</v>
+        <v>-0.005399215776283883</v>
       </c>
       <c r="T681" t="n">
         <v>2</v>
       </c>
       <c r="U681" t="n">
-        <v>0.0146196158456795</v>
+        <v>-0.005399215776283883</v>
       </c>
       <c r="V681" t="n">
-        <v>0.5580134987831116</v>
+        <v>0.5513838155979981</v>
       </c>
       <c r="W681" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X681" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y681" t="inlineStr"/>
       <c r="Z681" t="n">
-        <v>5.859141737222672</v>
+        <v>5.732838298127999</v>
       </c>
       <c r="AA681" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB681" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC681" t="inlineStr"/>
@@ -68319,96 +68323,96 @@
     <row r="682">
       <c r="A682" s="1" t="inlineStr">
         <is>
-          <t>8Ohqd6Bs</t>
+          <t>ALQHQfvK</t>
         </is>
       </c>
       <c r="B682" s="2" t="n">
-        <v>45630.70833333334</v>
+        <v>45628.69791666666</v>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F682" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G682" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H682" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I682" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="J682" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.2968388589051658</v>
       </c>
       <c r="K682" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.2713955281418658</v>
       </c>
       <c r="L682" t="n">
-        <v>0.4415584415584415</v>
+        <v>0.4317656129529684</v>
       </c>
       <c r="M682" t="n">
-        <v>0.05335157318741457</v>
+        <v>0.05275974025974017</v>
       </c>
       <c r="N682" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O682" t="n">
-        <v>0.1275329440832138</v>
+        <v>0.2641571867920867</v>
       </c>
       <c r="P682" t="n">
-        <v>0.3165941536426544</v>
+        <v>0.3937535347815069</v>
       </c>
       <c r="Q682" t="n">
-        <v>0.555872917175293</v>
+        <v>0.3420892784264065</v>
       </c>
       <c r="R682" t="n">
         <v>1</v>
       </c>
       <c r="S682" t="n">
-        <v>0.1143144756168514</v>
+        <v>0.122358006639641</v>
       </c>
       <c r="T682" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U682" t="n">
-        <v>0.1143144756168514</v>
+        <v>0.122358006639641</v>
       </c>
       <c r="V682" t="n">
-        <v>0.555872917175293</v>
+        <v>0.3937535347815069</v>
       </c>
       <c r="W682" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="X682" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y682" t="inlineStr"/>
       <c r="Z682" t="n">
-        <v>5.836665630340576</v>
+        <v>5.419171184922053</v>
       </c>
       <c r="AA682" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB682" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC682" t="inlineStr"/>
@@ -68418,96 +68422,96 @@
     <row r="683">
       <c r="A683" s="1" t="inlineStr">
         <is>
-          <t>Cda5RZlg</t>
+          <t>xxKvWkGa</t>
         </is>
       </c>
       <c r="B683" s="2" t="n">
-        <v>45632.70833333334</v>
+        <v>45632.60416666666</v>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E683" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F683" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G683" t="n">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="H683" t="n">
-        <v>3.25</v>
+        <v>7.5</v>
       </c>
       <c r="I683" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="J683" t="n">
-        <v>0.4982964224872232</v>
+        <v>0.8012162051113485</v>
       </c>
       <c r="K683" t="n">
-        <v>0.2913117546848382</v>
+        <v>0.1260580162708521</v>
       </c>
       <c r="L683" t="n">
-        <v>0.2103918228279387</v>
+        <v>0.07272577861779932</v>
       </c>
       <c r="M683" t="n">
-        <v>0.0562303193882141</v>
+        <v>0.05771403737505443</v>
       </c>
       <c r="N683" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O683" t="n">
-        <v>0.3950425386428833</v>
+        <v>0.7773281113965803</v>
       </c>
       <c r="P683" t="n">
-        <v>0.4416070282459259</v>
+        <v>0.1811886559517202</v>
       </c>
       <c r="Q683" t="n">
-        <v>0.1633504033088684</v>
+        <v>0.04148323265169956</v>
       </c>
       <c r="R683" t="n">
         <v>1</v>
       </c>
       <c r="S683" t="n">
-        <v>0.1502952735610877</v>
+        <v>-0.02388809371476819</v>
       </c>
       <c r="T683" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U683" t="n">
-        <v>0.1502952735610877</v>
+        <v>-0.02388809371476819</v>
       </c>
       <c r="V683" t="n">
-        <v>0.4416070282459259</v>
+        <v>0.7773281113965803</v>
       </c>
       <c r="W683" t="n">
-        <v>3.25</v>
+        <v>1.18</v>
       </c>
       <c r="X683" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y683" t="inlineStr"/>
       <c r="Z683" t="n">
-        <v>4.636873796582222</v>
+        <v>7.911120185659027</v>
       </c>
       <c r="AA683" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB683" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC683" t="inlineStr"/>
@@ -68517,96 +68521,96 @@
     <row r="684">
       <c r="A684" s="1" t="inlineStr">
         <is>
-          <t>txiMNilI</t>
+          <t>dIb5Hj16</t>
         </is>
       </c>
       <c r="B684" s="2" t="n">
-        <v>45633.41666666666</v>
+        <v>45632.69791666666</v>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E684" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F684" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G684" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H684" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I684" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="J684" t="n">
-        <v>0.5220012055455093</v>
+        <v>0.472913616398243</v>
       </c>
       <c r="K684" t="n">
-        <v>0.2610006027727547</v>
+        <v>0.2781844802342606</v>
       </c>
       <c r="L684" t="n">
-        <v>0.216998191681736</v>
+        <v>0.2489019033674963</v>
       </c>
       <c r="M684" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.05727554179566563</v>
       </c>
       <c r="N684" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O684" t="n">
-        <v>0.4089520275592804</v>
+        <v>0.1415595642482154</v>
       </c>
       <c r="P684" t="n">
-        <v>0.3634155988693237</v>
+        <v>0.3599841726241931</v>
       </c>
       <c r="Q684" t="n">
-        <v>0.2276323586702347</v>
+        <v>0.4984562631275914</v>
       </c>
       <c r="R684" t="n">
         <v>1</v>
       </c>
       <c r="S684" t="n">
-        <v>-0.1130491779862289</v>
+        <v>0.2495543597600951</v>
       </c>
       <c r="T684" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U684" t="n">
-        <v>-0.1130491779862289</v>
+        <v>0.2495543597600951</v>
       </c>
       <c r="V684" t="n">
-        <v>0.4089520275592804</v>
+        <v>0.4984562631275914</v>
       </c>
       <c r="W684" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="X684" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y684" t="inlineStr"/>
       <c r="Z684" t="n">
-        <v>4.293996289372444</v>
+        <v>7.85411154032071</v>
       </c>
       <c r="AA684" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB684" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC684" t="inlineStr"/>
@@ -68616,197 +68620,195 @@
     <row r="685">
       <c r="A685" s="1" t="inlineStr">
         <is>
-          <t>hGKvtZ3n</t>
+          <t>pvu0wYNP</t>
         </is>
       </c>
       <c r="B685" s="2" t="n">
-        <v>45633.51041666666</v>
+        <v>45633.45833333334</v>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E685" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F685" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G685" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="H685" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="I685" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="J685" t="n">
-        <v>0.2287747839349263</v>
+        <v>0.3463687150837989</v>
       </c>
       <c r="K685" t="n">
-        <v>0.2501270971021861</v>
+        <v>0.3072625698324022</v>
       </c>
       <c r="L685" t="n">
-        <v>0.5210981189628877</v>
+        <v>0.3463687150837989</v>
       </c>
       <c r="M685" t="n">
-        <v>0.06612466124661243</v>
+        <v>0.04985337243401755</v>
       </c>
       <c r="N685" t="n">
         <v>2</v>
       </c>
       <c r="O685" t="n">
-        <v>0.1309074908494949</v>
+        <v>0.2940388343344094</v>
       </c>
       <c r="P685" t="n">
-        <v>0.3584269881248474</v>
+        <v>0.3307302941416034</v>
       </c>
       <c r="Q685" t="n">
-        <v>0.5106655359268188</v>
+        <v>0.3752308715239872</v>
       </c>
       <c r="R685" t="n">
         <v>1</v>
       </c>
       <c r="S685" t="n">
-        <v>-0.01043258303606887</v>
+        <v>0.02886215644018825</v>
       </c>
       <c r="T685" t="n">
         <v>2</v>
       </c>
       <c r="U685" t="n">
-        <v>-0.01043258303606887</v>
+        <v>0.02886215644018825</v>
       </c>
       <c r="V685" t="n">
-        <v>0.5106655359268188</v>
+        <v>0.3752308715239872</v>
       </c>
       <c r="W685" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="X685" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y685" t="inlineStr"/>
       <c r="Z685" t="n">
-        <v>4.021491095423698</v>
+        <v>4.242976793623842</v>
       </c>
       <c r="AA685" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB685" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC685" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC685" t="inlineStr"/>
       <c r="AD685" t="inlineStr"/>
       <c r="AE685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" s="1" t="inlineStr">
         <is>
-          <t>bTkuvDYb</t>
+          <t>A3XoUTpC</t>
         </is>
       </c>
       <c r="B686" s="2" t="n">
-        <v>45633.60416666666</v>
+        <v>45633.58333333334</v>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F686" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G686" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="H686" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="I686" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="J686" t="n">
-        <v>0.4093097913322633</v>
+        <v>0.5539358600583091</v>
       </c>
       <c r="K686" t="n">
-        <v>0.3138041733547351</v>
+        <v>0.2478134110787172</v>
       </c>
       <c r="L686" t="n">
-        <v>0.2768860353130016</v>
+        <v>0.1982507288629737</v>
       </c>
       <c r="M686" t="n">
-        <v>0.06223358908780918</v>
+        <v>0.0619195046439629</v>
       </c>
       <c r="N686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O686" t="n">
-        <v>0.3098367154598236</v>
+        <v>0.5022740367148163</v>
       </c>
       <c r="P686" t="n">
-        <v>0.5194622278213501</v>
+        <v>0.3154211642314957</v>
       </c>
       <c r="Q686" t="n">
-        <v>0.1707010269165039</v>
+        <v>0.1823047990536879</v>
       </c>
       <c r="R686" t="n">
         <v>1</v>
       </c>
       <c r="S686" t="n">
-        <v>0.205658054466615</v>
+        <v>-0.05166182334349279</v>
       </c>
       <c r="T686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U686" t="n">
-        <v>0.205658054466615</v>
+        <v>-0.05166182334349279</v>
       </c>
       <c r="V686" t="n">
-        <v>0.5194622278213501</v>
+        <v>0.5022740367148163</v>
       </c>
       <c r="W686" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="X686" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y686" t="inlineStr"/>
       <c r="Z686" t="n">
-        <v>5.454353392124176</v>
+        <v>4.731428240398897</v>
       </c>
       <c r="AA686" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB686" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC686" t="inlineStr"/>
@@ -68816,96 +68818,96 @@
     <row r="687">
       <c r="A687" s="1" t="inlineStr">
         <is>
-          <t>YBmEPDJ5</t>
+          <t>I9fDpkVh</t>
         </is>
       </c>
       <c r="B687" s="2" t="n">
-        <v>45633.70833333334</v>
+        <v>45633.69791666666</v>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E687" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F687" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G687" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H687" t="n">
         <v>4.75</v>
       </c>
-      <c r="H687" t="n">
-        <v>3.7</v>
-      </c>
       <c r="I687" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J687" t="n">
-        <v>0.1969317470256731</v>
+        <v>0.6111289803795432</v>
       </c>
       <c r="K687" t="n">
-        <v>0.2528177833437695</v>
+        <v>0.1994210357027983</v>
       </c>
       <c r="L687" t="n">
-        <v>0.5502504696305573</v>
+        <v>0.1894499839176584</v>
       </c>
       <c r="M687" t="n">
-        <v>0.06903188017739104</v>
+        <v>0.05568760611205437</v>
       </c>
       <c r="N687" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O687" t="n">
-        <v>0.1717308014631271</v>
+        <v>0.570323965889506</v>
       </c>
       <c r="P687" t="n">
-        <v>0.2694768905639648</v>
+        <v>0.2904887822129973</v>
       </c>
       <c r="Q687" t="n">
-        <v>0.5587922930717468</v>
+        <v>0.1391872518974968</v>
       </c>
       <c r="R687" t="n">
         <v>1</v>
       </c>
       <c r="S687" t="n">
-        <v>0.008541823441189478</v>
+        <v>-0.04080501449003726</v>
       </c>
       <c r="T687" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U687" t="n">
-        <v>0.008541823441189478</v>
+        <v>-0.04080501449003726</v>
       </c>
       <c r="V687" t="n">
-        <v>0.5587922930717468</v>
+        <v>0.570323965889506</v>
       </c>
       <c r="W687" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="X687" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y687" t="inlineStr"/>
       <c r="Z687" t="n">
-        <v>5.867319077253342</v>
+        <v>5.559948989694421</v>
       </c>
       <c r="AA687" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB687" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC687" t="inlineStr"/>
@@ -68915,96 +68917,96 @@
     <row r="688">
       <c r="A688" s="1" t="inlineStr">
         <is>
-          <t>x4pVLVIU</t>
+          <t>UVdDFUVI</t>
         </is>
       </c>
       <c r="B688" s="2" t="n">
-        <v>45634.41666666666</v>
+        <v>45634.35416666666</v>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E688" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F688" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G688" t="n">
-        <v>3.75</v>
+        <v>1.48</v>
       </c>
       <c r="H688" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="I688" t="n">
-        <v>2.15</v>
+        <v>6.25</v>
       </c>
       <c r="J688" t="n">
-        <v>0.2503639010189229</v>
+        <v>0.6386964914272737</v>
       </c>
       <c r="K688" t="n">
-        <v>0.3129548762736535</v>
+        <v>0.2100601794027478</v>
       </c>
       <c r="L688" t="n">
-        <v>0.4366812227074235</v>
+        <v>0.1512433291699784</v>
       </c>
       <c r="M688" t="n">
-        <v>0.06511627906976747</v>
+        <v>0.0578978978978979</v>
       </c>
       <c r="N688" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O688" t="n">
-        <v>0.3164181709289551</v>
+        <v>0.5588401243340348</v>
       </c>
       <c r="P688" t="n">
-        <v>0.3465518057346344</v>
+        <v>0.3353989762821539</v>
       </c>
       <c r="Q688" t="n">
-        <v>0.3370300531387329</v>
+        <v>0.1057608993838113</v>
       </c>
       <c r="R688" t="n">
         <v>1</v>
       </c>
       <c r="S688" t="n">
-        <v>0.03359692946098086</v>
+        <v>-0.07985636709323884</v>
       </c>
       <c r="T688" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U688" t="n">
-        <v>0.03359692946098086</v>
+        <v>-0.07985636709323884</v>
       </c>
       <c r="V688" t="n">
-        <v>0.3465518057346344</v>
+        <v>0.5588401243340348</v>
       </c>
       <c r="W688" t="n">
-        <v>3</v>
+        <v>1.48</v>
       </c>
       <c r="X688" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y688" t="inlineStr"/>
       <c r="Z688" t="n">
-        <v>3.638793960213661</v>
+        <v>5.029329451028358</v>
       </c>
       <c r="AA688" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB688" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC688" t="inlineStr"/>
@@ -69014,96 +69016,96 @@
     <row r="689">
       <c r="A689" s="1" t="inlineStr">
         <is>
-          <t>SYQn9hZO</t>
+          <t>GMVVXBom</t>
         </is>
       </c>
       <c r="B689" s="2" t="n">
-        <v>45634.51041666666</v>
+        <v>45634.45833333334</v>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F689" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G689" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="H689" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I689" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J689" t="n">
-        <v>0.4569015166058744</v>
+        <v>0.3872529245663574</v>
       </c>
       <c r="K689" t="n">
-        <v>0.2676137454405835</v>
+        <v>0.3162565550625252</v>
       </c>
       <c r="L689" t="n">
-        <v>0.2754847379535419</v>
+        <v>0.2964905203711174</v>
       </c>
       <c r="M689" t="n">
-        <v>0.06763681082188988</v>
+        <v>0.05399659863945572</v>
       </c>
       <c r="N689" t="n">
         <v>1</v>
       </c>
       <c r="O689" t="n">
-        <v>0.4779868423938751</v>
+        <v>0.3930217319224656</v>
       </c>
       <c r="P689" t="n">
-        <v>0.1914146095514297</v>
+        <v>0.3556106575321916</v>
       </c>
       <c r="Q689" t="n">
-        <v>0.3305985629558563</v>
+        <v>0.2513676105453429</v>
       </c>
       <c r="R689" t="n">
         <v>1</v>
       </c>
       <c r="S689" t="n">
-        <v>0.02108532578800071</v>
+        <v>0.005768807356108185</v>
       </c>
       <c r="T689" t="n">
         <v>1</v>
       </c>
       <c r="U689" t="n">
-        <v>0.02108532578800071</v>
+        <v>0.005768807356108185</v>
       </c>
       <c r="V689" t="n">
-        <v>0.4779868423938751</v>
+        <v>0.3930217319224656</v>
       </c>
       <c r="W689" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="X689" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y689" t="inlineStr"/>
       <c r="Z689" t="n">
-        <v>5.018861845135689</v>
+        <v>4.187300662425025</v>
       </c>
       <c r="AA689" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB689" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC689" t="inlineStr"/>
@@ -69113,328 +69115,326 @@
     <row r="690">
       <c r="A690" s="1" t="inlineStr">
         <is>
-          <t>6ggmxi3B</t>
+          <t>O6cLrTa5</t>
         </is>
       </c>
       <c r="B690" s="2" t="n">
-        <v>45634.60416666666</v>
+        <v>45634.58333333334</v>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F690" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G690" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="H690" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I690" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="J690" t="n">
-        <v>0.4564841498559078</v>
+        <v>0.3401778496362166</v>
       </c>
       <c r="K690" t="n">
-        <v>0.2835734870317003</v>
+        <v>0.2976556184316895</v>
       </c>
       <c r="L690" t="n">
-        <v>0.2599423631123919</v>
+        <v>0.3621665319320937</v>
       </c>
       <c r="M690" t="n">
-        <v>0.06861295885686136</v>
+        <v>0.04987099402498663</v>
       </c>
       <c r="N690" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O690" t="n">
-        <v>0.3984593152999878</v>
+        <v>0.314272745240414</v>
       </c>
       <c r="P690" t="n">
-        <v>0.2241911292076111</v>
+        <v>0.3375805581600361</v>
       </c>
       <c r="Q690" t="n">
-        <v>0.3773495554924011</v>
+        <v>0.3481466965995498</v>
       </c>
       <c r="R690" t="n">
         <v>1</v>
       </c>
       <c r="S690" t="n">
-        <v>-0.05802483455592</v>
+        <v>-0.01401983533254397</v>
       </c>
       <c r="T690" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U690" t="n">
-        <v>-0.05802483455592</v>
+        <v>-0.01401983533254397</v>
       </c>
       <c r="V690" t="n">
-        <v>0.3984593152999878</v>
+        <v>0.3481466965995498</v>
       </c>
       <c r="W690" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="X690" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y690" t="inlineStr"/>
       <c r="Z690" t="n">
-        <v>4.183822810649872</v>
+        <v>2.631249032477671</v>
       </c>
       <c r="AA690" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB690" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC690" t="inlineStr"/>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC690" t="n">
+        <v>1</v>
+      </c>
       <c r="AD690" t="inlineStr"/>
       <c r="AE690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" s="1" t="inlineStr">
         <is>
-          <t>6adcTeKt</t>
+          <t>Ms14nB0t</t>
         </is>
       </c>
       <c r="B691" s="2" t="n">
-        <v>45634.70833333334</v>
+        <v>45634.69791666666</v>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F691" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G691" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="H691" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I691" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="J691" t="n">
-        <v>0.6386964914272737</v>
+        <v>0.5011933174224343</v>
       </c>
       <c r="K691" t="n">
-        <v>0.2100601794027478</v>
+        <v>0.2720763723150358</v>
       </c>
       <c r="L691" t="n">
-        <v>0.1512433291699784</v>
+        <v>0.2267303102625298</v>
       </c>
       <c r="M691" t="n">
-        <v>0.0578978978978979</v>
+        <v>0.05012531328320802</v>
       </c>
       <c r="N691" t="n">
         <v>1</v>
       </c>
       <c r="O691" t="n">
-        <v>0.488122969865799</v>
+        <v>0.4669355469200022</v>
       </c>
       <c r="P691" t="n">
-        <v>0.3047187328338623</v>
+        <v>0.3148553905821113</v>
       </c>
       <c r="Q691" t="n">
-        <v>0.2071582823991776</v>
+        <v>0.2182090624978865</v>
       </c>
       <c r="R691" t="n">
         <v>1</v>
       </c>
       <c r="S691" t="n">
-        <v>-0.1505735215614747</v>
+        <v>-0.03425777050243212</v>
       </c>
       <c r="T691" t="n">
         <v>1</v>
       </c>
       <c r="U691" t="n">
-        <v>-0.1505735215614747</v>
+        <v>-0.03425777050243212</v>
       </c>
       <c r="V691" t="n">
-        <v>0.488122969865799</v>
+        <v>0.4669355469200022</v>
       </c>
       <c r="W691" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="X691" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y691" t="inlineStr"/>
       <c r="Z691" t="n">
-        <v>3.843968387693167</v>
+        <v>4.543116652384486</v>
       </c>
       <c r="AA691" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB691" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC691" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC691" t="inlineStr"/>
       <c r="AD691" t="inlineStr"/>
       <c r="AE691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" s="1" t="inlineStr">
         <is>
-          <t>QiBthjLU</t>
+          <t>6VQfS7FO</t>
         </is>
       </c>
       <c r="B692" s="2" t="n">
-        <v>45635.70833333334</v>
+        <v>45635.69791666666</v>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="E692" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F692" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G692" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="H692" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I692" t="n">
-        <v>5.75</v>
+        <v>2.8</v>
       </c>
       <c r="J692" t="n">
-        <v>0.5455009851857258</v>
+        <v>0.3491271820448877</v>
       </c>
       <c r="K692" t="n">
-        <v>0.2903743705757863</v>
+        <v>0.314214463840399</v>
       </c>
       <c r="L692" t="n">
-        <v>0.1641246442384879</v>
+        <v>0.3366583541147132</v>
       </c>
       <c r="M692" t="n">
-        <v>0.05964003325149347</v>
+        <v>0.06084656084656093</v>
       </c>
       <c r="N692" t="n">
         <v>1</v>
       </c>
       <c r="O692" t="n">
-        <v>0.5763322114944458</v>
+        <v>0.5121303379494033</v>
       </c>
       <c r="P692" t="n">
-        <v>0.1866425275802612</v>
+        <v>0.321007451004068</v>
       </c>
       <c r="Q692" t="n">
-        <v>0.237025260925293</v>
+        <v>0.1668622110465286</v>
       </c>
       <c r="R692" t="n">
         <v>1</v>
       </c>
       <c r="S692" t="n">
-        <v>0.03083122630872004</v>
+        <v>0.1630031559045156</v>
       </c>
       <c r="T692" t="n">
         <v>1</v>
       </c>
       <c r="U692" t="n">
-        <v>0.03083122630872004</v>
+        <v>0.1630031559045156</v>
       </c>
       <c r="V692" t="n">
-        <v>0.5763322114944458</v>
+        <v>0.5121303379494033</v>
       </c>
       <c r="W692" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="X692" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y692" t="inlineStr"/>
       <c r="Z692" t="n">
-        <v>4.538616165518761</v>
+        <v>7.088901685466148</v>
       </c>
       <c r="AA692" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB692" t="inlineStr">
         <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="AC692" t="n">
-        <v>1</v>
-      </c>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="AC692" t="inlineStr"/>
       <c r="AD692" t="inlineStr"/>
       <c r="AE692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" s="1" t="inlineStr">
         <is>
-          <t>GjcexCK8</t>
+          <t>vsfdptyA</t>
         </is>
       </c>
       <c r="B693" s="2" t="n">
-        <v>45639.70833333334</v>
+        <v>45639.69791666666</v>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="F693" t="n">
-        <v>1481</v>
+        <v>771</v>
       </c>
       <c r="G693" t="inlineStr"/>
       <c r="H693" t="inlineStr"/>
@@ -69447,13 +69447,13 @@
         <v>2</v>
       </c>
       <c r="O693" t="n">
-        <v>0.1504876017570496</v>
+        <v>0.2046493558145721</v>
       </c>
       <c r="P693" t="n">
-        <v>0.3762744665145874</v>
+        <v>0.3518096768018866</v>
       </c>
       <c r="Q693" t="n">
-        <v>0.4732378721237183</v>
+        <v>0.4435409673835415</v>
       </c>
       <c r="R693" t="n">
         <v>1</v>
@@ -69464,24 +69464,24 @@
       </c>
       <c r="U693" t="inlineStr"/>
       <c r="V693" t="n">
-        <v>0.5267621278762817</v>
+        <v>0.5564590326164585</v>
       </c>
       <c r="W693" t="inlineStr"/>
       <c r="X693" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="Y693" t="inlineStr"/>
       <c r="Z693" t="inlineStr"/>
       <c r="AA693" t="inlineStr">
         <is>
-          <t>spain</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="AB693" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="AC693" t="inlineStr"/>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -71840,20 +71840,20 @@
     <row r="717">
       <c r="A717" s="1" t="inlineStr">
         <is>
-          <t>8Ohqd6Bs</t>
+          <t>GjcexCK8</t>
         </is>
       </c>
       <c r="B717" s="2" t="n">
-        <v>45630.70833333334</v>
+        <v>45639.70833333334</v>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E717" t="n">
@@ -71863,55 +71863,55 @@
         <v>1481</v>
       </c>
       <c r="G717" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="H717" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="I717" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="J717" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.323051271363068</v>
       </c>
       <c r="K717" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.3022092538557732</v>
       </c>
       <c r="L717" t="n">
-        <v>0.4415584415584415</v>
+        <v>0.3747394747811589</v>
       </c>
       <c r="M717" t="n">
-        <v>0.05335157318741457</v>
+        <v>0.06740823136818674</v>
       </c>
       <c r="N717" t="n">
         <v>2</v>
       </c>
       <c r="O717" t="n">
-        <v>0.09697163744755813</v>
+        <v>0.3041696802322068</v>
       </c>
       <c r="P717" t="n">
-        <v>0.3834946833720042</v>
+        <v>0.106062395503738</v>
       </c>
       <c r="Q717" t="n">
-        <v>0.5195336791804377</v>
+        <v>0.5897679242640552</v>
       </c>
       <c r="R717" t="n">
         <v>1</v>
       </c>
       <c r="S717" t="n">
-        <v>0.07797523762199615</v>
+        <v>0.2150284494828963</v>
       </c>
       <c r="T717" t="n">
         <v>2</v>
       </c>
       <c r="U717" t="n">
-        <v>0.07797523762199615</v>
+        <v>0.2150284494828963</v>
       </c>
       <c r="V717" t="n">
-        <v>0.5195336791804377</v>
+        <v>0.5897679242640552</v>
       </c>
       <c r="W717" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="X717" t="inlineStr">
         <is>
@@ -71920,7 +71920,7 @@
       </c>
       <c r="Y717" t="inlineStr"/>
       <c r="Z717" t="n">
-        <v>4.545919692828829</v>
+        <v>5.160469337310484</v>
       </c>
       <c r="AA717" t="inlineStr">
         <is>
@@ -71939,20 +71939,20 @@
     <row r="718">
       <c r="A718" s="1" t="inlineStr">
         <is>
-          <t>Cda5RZlg</t>
+          <t>6oTld2Xo</t>
         </is>
       </c>
       <c r="B718" s="2" t="n">
-        <v>45632.70833333334</v>
+        <v>45640.41666666666</v>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E718" t="n">
@@ -71962,55 +71962,55 @@
         <v>1481</v>
       </c>
       <c r="G718" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="H718" t="n">
         <v>3.25</v>
       </c>
       <c r="I718" t="n">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="J718" t="n">
-        <v>0.5105415460934271</v>
+        <v>0.3485254691689008</v>
       </c>
       <c r="K718" t="n">
-        <v>0.2906159570070277</v>
+        <v>0.2895442359249329</v>
       </c>
       <c r="L718" t="n">
-        <v>0.1988424968995453</v>
+        <v>0.3619302949061662</v>
       </c>
       <c r="M718" t="n">
-        <v>0.05875916402232173</v>
+        <v>0.06267806267806275</v>
       </c>
       <c r="N718" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O718" t="n">
-        <v>0.2396790731484521</v>
+        <v>0.4598616416606767</v>
       </c>
       <c r="P718" t="n">
-        <v>0.2541723490556476</v>
+        <v>0.1655833690832157</v>
       </c>
       <c r="Q718" t="n">
-        <v>0.5061485777959002</v>
+        <v>0.3745549892561075</v>
       </c>
       <c r="R718" t="n">
         <v>1</v>
       </c>
       <c r="S718" t="n">
-        <v>0.3073060808963549</v>
+        <v>0.1113361724917759</v>
       </c>
       <c r="T718" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U718" t="n">
-        <v>0.3073060808963549</v>
+        <v>0.1113361724917759</v>
       </c>
       <c r="V718" t="n">
-        <v>0.5061485777959002</v>
+        <v>0.4598616416606767</v>
       </c>
       <c r="W718" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="X718" t="inlineStr">
         <is>
@@ -72019,7 +72019,7 @@
       </c>
       <c r="Y718" t="inlineStr"/>
       <c r="Z718" t="n">
-        <v>4.428800055714126</v>
+        <v>3.017842023398191</v>
       </c>
       <c r="AA718" t="inlineStr">
         <is>
@@ -72031,27 +72031,29 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC718" t="inlineStr"/>
+      <c r="AC718" t="n">
+        <v>1</v>
+      </c>
       <c r="AD718" t="inlineStr"/>
       <c r="AE718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" s="1" t="inlineStr">
         <is>
-          <t>txiMNilI</t>
+          <t>AgA9E8S1</t>
         </is>
       </c>
       <c r="B719" s="2" t="n">
-        <v>45633.41666666666</v>
+        <v>45640.51041666666</v>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E719" t="n">
@@ -72061,55 +72063,55 @@
         <v>1481</v>
       </c>
       <c r="G719" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="H719" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="I719" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="J719" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.4063908234330192</v>
       </c>
       <c r="K719" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.3015157722244981</v>
       </c>
       <c r="L719" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2920934043424825</v>
       </c>
       <c r="M719" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.06986325385694259</v>
       </c>
       <c r="N719" t="n">
         <v>0</v>
       </c>
       <c r="O719" t="n">
-        <v>0.3905487361951514</v>
+        <v>0.3330528714185551</v>
       </c>
       <c r="P719" t="n">
-        <v>0.4159023904963547</v>
+        <v>0.3503192469913491</v>
       </c>
       <c r="Q719" t="n">
-        <v>0.1935488733084939</v>
+        <v>0.3166278815900957</v>
       </c>
       <c r="R719" t="n">
         <v>1</v>
       </c>
       <c r="S719" t="n">
-        <v>0.1527444957595127</v>
+        <v>0.04880347476685104</v>
       </c>
       <c r="T719" t="n">
         <v>0</v>
       </c>
       <c r="U719" t="n">
-        <v>0.1527444957595127</v>
+        <v>0.04880347476685104</v>
       </c>
       <c r="V719" t="n">
-        <v>0.4159023904963547</v>
+        <v>0.3503192469913491</v>
       </c>
       <c r="W719" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="X719" t="inlineStr">
         <is>
@@ -72118,7 +72120,7 @@
       </c>
       <c r="Y719" t="inlineStr"/>
       <c r="Z719" t="n">
-        <v>3.639145916843104</v>
+        <v>3.065293411174305</v>
       </c>
       <c r="AA719" t="inlineStr">
         <is>
@@ -72137,20 +72139,20 @@
     <row r="720">
       <c r="A720" s="1" t="inlineStr">
         <is>
-          <t>hGKvtZ3n</t>
+          <t>lvM0GUck</t>
         </is>
       </c>
       <c r="B720" s="2" t="n">
-        <v>45633.51041666666</v>
+        <v>45640.60416666666</v>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E720" t="n">
@@ -72160,55 +72162,55 @@
         <v>1481</v>
       </c>
       <c r="G720" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="H720" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="I720" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J720" t="n">
-        <v>0.2172422391223039</v>
+        <v>0.4266958424507659</v>
       </c>
       <c r="K720" t="n">
-        <v>0.2294289988779454</v>
+        <v>0.2888402625820569</v>
       </c>
       <c r="L720" t="n">
-        <v>0.5533287619997507</v>
+        <v>0.2844638949671772</v>
       </c>
       <c r="M720" t="n">
-        <v>0.06308461535912735</v>
+        <v>0.06526806526806528</v>
       </c>
       <c r="N720" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O720" t="n">
-        <v>0.1726836283006191</v>
+        <v>0.4464053938417443</v>
       </c>
       <c r="P720" t="n">
-        <v>0.1303151594159098</v>
+        <v>0.2293411239659109</v>
       </c>
       <c r="Q720" t="n">
-        <v>0.6970012122834711</v>
+        <v>0.324253482192345</v>
       </c>
       <c r="R720" t="n">
         <v>1</v>
       </c>
       <c r="S720" t="n">
-        <v>0.1436724502837204</v>
+        <v>0.01970955139097841</v>
       </c>
       <c r="T720" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U720" t="n">
-        <v>0.1436724502837204</v>
+        <v>0.01970955139097841</v>
       </c>
       <c r="V720" t="n">
-        <v>0.6970012122834711</v>
+        <v>0.4464053938417443</v>
       </c>
       <c r="W720" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="X720" t="inlineStr">
         <is>
@@ -72217,7 +72219,7 @@
       </c>
       <c r="Y720" t="inlineStr"/>
       <c r="Z720" t="n">
-        <v>4.574070455610279</v>
+        <v>2.929535397086447</v>
       </c>
       <c r="AA720" t="inlineStr">
         <is>
@@ -72238,20 +72240,20 @@
     <row r="721">
       <c r="A721" s="1" t="inlineStr">
         <is>
-          <t>bTkuvDYb</t>
+          <t>lGwEPYz3</t>
         </is>
       </c>
       <c r="B721" s="2" t="n">
-        <v>45633.60416666666</v>
+        <v>45640.70833333334</v>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E721" t="n">
@@ -72261,55 +72263,55 @@
         <v>1481</v>
       </c>
       <c r="G721" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="H721" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I721" t="n">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="J721" t="n">
-        <v>0.4179104477611941</v>
+        <v>0.1557251908396947</v>
       </c>
       <c r="K721" t="n">
-        <v>0.3134328358208956</v>
+        <v>0.233587786259542</v>
       </c>
       <c r="L721" t="n">
-        <v>0.2686567164179105</v>
+        <v>0.6106870229007634</v>
       </c>
       <c r="M721" t="n">
-        <v>0.06349206349206327</v>
+        <v>0.0702614379084967</v>
       </c>
       <c r="N721" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O721" t="n">
-        <v>0.1248189062273611</v>
+        <v>0.09734271630283801</v>
       </c>
       <c r="P721" t="n">
-        <v>0.7047458262908883</v>
+        <v>0.3103618040799995</v>
       </c>
       <c r="Q721" t="n">
-        <v>0.1704352674817506</v>
+        <v>0.5922954796171626</v>
       </c>
       <c r="R721" t="n">
         <v>1</v>
       </c>
       <c r="S721" t="n">
-        <v>0.3913129904699927</v>
+        <v>-0.01839154328360082</v>
       </c>
       <c r="T721" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U721" t="n">
-        <v>0.3913129904699927</v>
+        <v>-0.01839154328360082</v>
       </c>
       <c r="V721" t="n">
-        <v>0.7047458262908883</v>
+        <v>0.5922954796171626</v>
       </c>
       <c r="W721" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="X721" t="inlineStr">
         <is>
@@ -72318,7 +72320,7 @@
       </c>
       <c r="Y721" t="inlineStr"/>
       <c r="Z721" t="n">
-        <v>6.166525980045273</v>
+        <v>4.538881431724143</v>
       </c>
       <c r="AA721" t="inlineStr">
         <is>
@@ -72337,20 +72339,20 @@
     <row r="722">
       <c r="A722" s="1" t="inlineStr">
         <is>
-          <t>YBmEPDJ5</t>
+          <t>Qs6LJrmp</t>
         </is>
       </c>
       <c r="B722" s="2" t="n">
-        <v>45633.70833333334</v>
+        <v>45641.41666666666</v>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E722" t="n">
@@ -72360,55 +72362,55 @@
         <v>1481</v>
       </c>
       <c r="G722" t="n">
-        <v>4.75</v>
+        <v>1.44</v>
       </c>
       <c r="H722" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I722" t="n">
-        <v>1.67</v>
+        <v>7.5</v>
       </c>
       <c r="J722" t="n">
-        <v>0.197540225352967</v>
+        <v>0.6479959539764825</v>
       </c>
       <c r="K722" t="n">
-        <v>0.2405938642119471</v>
+        <v>0.2275888228600329</v>
       </c>
       <c r="L722" t="n">
-        <v>0.5618659104350859</v>
+        <v>0.1244152231634846</v>
       </c>
       <c r="M722" t="n">
-        <v>0.06573896740931096</v>
+        <v>0.07168021680216796</v>
       </c>
       <c r="N722" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O722" t="n">
-        <v>0.09966839248819739</v>
+        <v>0.8065540589965901</v>
       </c>
       <c r="P722" t="n">
-        <v>0.3388776020652297</v>
+        <v>0.1075162629697439</v>
       </c>
       <c r="Q722" t="n">
-        <v>0.561454005446573</v>
+        <v>0.08592967803366615</v>
       </c>
       <c r="R722" t="n">
         <v>1</v>
       </c>
       <c r="S722" t="n">
-        <v>-0.0004119049885129566</v>
+        <v>0.1585581050201076</v>
       </c>
       <c r="T722" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U722" t="n">
-        <v>-0.0004119049885129566</v>
+        <v>0.1585581050201076</v>
       </c>
       <c r="V722" t="n">
-        <v>0.561454005446573</v>
+        <v>0.8065540589965901</v>
       </c>
       <c r="W722" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="X722" t="inlineStr">
         <is>
@@ -72417,7 +72419,7 @@
       </c>
       <c r="Y722" t="inlineStr"/>
       <c r="Z722" t="n">
-        <v>4.89830587305956</v>
+        <v>7.057348016220163</v>
       </c>
       <c r="AA722" t="inlineStr">
         <is>
@@ -72436,20 +72438,20 @@
     <row r="723">
       <c r="A723" s="1" t="inlineStr">
         <is>
-          <t>x4pVLVIU</t>
+          <t>MTyMNC5F</t>
         </is>
       </c>
       <c r="B723" s="2" t="n">
-        <v>45634.41666666666</v>
+        <v>45641.51041666666</v>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="E723" t="n">
@@ -72459,55 +72461,55 @@
         <v>1481</v>
       </c>
       <c r="G723" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="H723" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I723" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J723" t="n">
-        <v>0.2405498281786942</v>
+        <v>0.2688214426487978</v>
       </c>
       <c r="K723" t="n">
-        <v>0.3127147766323024</v>
+        <v>0.303508080409933</v>
       </c>
       <c r="L723" t="n">
-        <v>0.4467353951890034</v>
+        <v>0.4276704769412692</v>
       </c>
       <c r="M723" t="n">
-        <v>0.06593406593406592</v>
+        <v>0.06284038542103065</v>
       </c>
       <c r="N723" t="n">
         <v>2</v>
       </c>
       <c r="O723" t="n">
-        <v>0.142797894199751</v>
+        <v>0.1651261126596817</v>
       </c>
       <c r="P723" t="n">
-        <v>0.2282314368640934</v>
+        <v>0.2397973370757538</v>
       </c>
       <c r="Q723" t="n">
-        <v>0.6289706689361556</v>
+        <v>0.5950765502645645</v>
       </c>
       <c r="R723" t="n">
         <v>1</v>
       </c>
       <c r="S723" t="n">
-        <v>0.1822352737471522</v>
+        <v>0.1674060733232953</v>
       </c>
       <c r="T723" t="n">
         <v>2</v>
       </c>
       <c r="U723" t="n">
-        <v>0.1822352737471522</v>
+        <v>0.1674060733232953</v>
       </c>
       <c r="V723" t="n">
-        <v>0.6289706689361556</v>
+        <v>0.5950765502645645</v>
       </c>
       <c r="W723" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="X723" t="inlineStr">
         <is>
@@ -72516,7 +72518,7 @@
       </c>
       <c r="Y723" t="inlineStr"/>
       <c r="Z723" t="n">
-        <v>5.503493353191361</v>
+        <v>5.206919814814939</v>
       </c>
       <c r="AA723" t="inlineStr">
         <is>
@@ -72535,20 +72537,20 @@
     <row r="724">
       <c r="A724" s="1" t="inlineStr">
         <is>
-          <t>SYQn9hZO</t>
+          <t>CIj4zjkL</t>
         </is>
       </c>
       <c r="B724" s="2" t="n">
-        <v>45634.51041666666</v>
+        <v>45641.60416666666</v>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E724" t="n">
@@ -72558,55 +72560,55 @@
         <v>1481</v>
       </c>
       <c r="G724" t="n">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="H724" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I724" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="J724" t="n">
-        <v>0.4569015166058744</v>
+        <v>0.6380263717566993</v>
       </c>
       <c r="K724" t="n">
-        <v>0.2676137454405835</v>
+        <v>0.2360697575499787</v>
       </c>
       <c r="L724" t="n">
-        <v>0.2754847379535419</v>
+        <v>0.125903870693322</v>
       </c>
       <c r="M724" t="n">
-        <v>0.06763681082188988</v>
+        <v>0.05900900900900896</v>
       </c>
       <c r="N724" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O724" t="n">
-        <v>0.3342708214040265</v>
+        <v>0.7493405423687598</v>
       </c>
       <c r="P724" t="n">
-        <v>0.4557738136480177</v>
+        <v>0.1120255919790001</v>
       </c>
       <c r="Q724" t="n">
-        <v>0.2099553649479559</v>
+        <v>0.1386338656522401</v>
       </c>
       <c r="R724" t="n">
         <v>1</v>
       </c>
       <c r="S724" t="n">
-        <v>0.1881600682074341</v>
+        <v>0.1113141706120605</v>
       </c>
       <c r="T724" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U724" t="n">
-        <v>0.1881600682074341</v>
+        <v>0.1113141706120605</v>
       </c>
       <c r="V724" t="n">
-        <v>0.4557738136480177</v>
+        <v>0.7493405423687598</v>
       </c>
       <c r="W724" t="n">
-        <v>3.5</v>
+        <v>1.48</v>
       </c>
       <c r="X724" t="inlineStr">
         <is>
@@ -72615,7 +72617,7 @@
       </c>
       <c r="Y724" t="inlineStr"/>
       <c r="Z724" t="n">
-        <v>3.988020869420155</v>
+        <v>6.556729745726648</v>
       </c>
       <c r="AA724" t="inlineStr">
         <is>
@@ -72634,20 +72636,20 @@
     <row r="725">
       <c r="A725" s="1" t="inlineStr">
         <is>
-          <t>6ggmxi3B</t>
+          <t>IeVULjzS</t>
         </is>
       </c>
       <c r="B725" s="2" t="n">
-        <v>45634.60416666666</v>
+        <v>45641.60416666666</v>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E725" t="n">
@@ -72657,55 +72659,55 @@
         <v>1481</v>
       </c>
       <c r="G725" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="H725" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="I725" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="J725" t="n">
-        <v>0.4564841498559078</v>
+        <v>0.5220012055455093</v>
       </c>
       <c r="K725" t="n">
-        <v>0.2835734870317003</v>
+        <v>0.2610006027727547</v>
       </c>
       <c r="L725" t="n">
-        <v>0.2599423631123919</v>
+        <v>0.216998191681736</v>
       </c>
       <c r="M725" t="n">
-        <v>0.06861295885686136</v>
+        <v>0.0642802155504234</v>
       </c>
       <c r="N725" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O725" t="n">
-        <v>0.2719496470443259</v>
+        <v>0.4690630449137062</v>
       </c>
       <c r="P725" t="n">
-        <v>0.4013738821906585</v>
+        <v>0.2922910835040749</v>
       </c>
       <c r="Q725" t="n">
-        <v>0.3266764707650154</v>
+        <v>0.238645871582219</v>
       </c>
       <c r="R725" t="n">
         <v>1</v>
       </c>
       <c r="S725" t="n">
-        <v>0.1178003951589582</v>
+        <v>-0.05293816063180318</v>
       </c>
       <c r="T725" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U725" t="n">
-        <v>0.1178003951589582</v>
+        <v>-0.05293816063180318</v>
       </c>
       <c r="V725" t="n">
-        <v>0.4013738821906585</v>
+        <v>0.4690630449137062</v>
       </c>
       <c r="W725" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="X725" t="inlineStr">
         <is>
@@ -72714,7 +72716,7 @@
       </c>
       <c r="Y725" t="inlineStr"/>
       <c r="Z725" t="n">
-        <v>3.512021469168262</v>
+        <v>1.688599515661363</v>
       </c>
       <c r="AA725" t="inlineStr">
         <is>
@@ -72726,27 +72728,29 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC725" t="inlineStr"/>
+      <c r="AC725" t="n">
+        <v>1</v>
+      </c>
       <c r="AD725" t="inlineStr"/>
       <c r="AE725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" s="1" t="inlineStr">
         <is>
-          <t>6adcTeKt</t>
+          <t>Y79THMHd</t>
         </is>
       </c>
       <c r="B726" s="2" t="n">
-        <v>45634.70833333334</v>
+        <v>45641.70833333334</v>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E726" t="n">
@@ -72756,55 +72760,55 @@
         <v>1481</v>
       </c>
       <c r="G726" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="H726" t="n">
-        <v>4.75</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I726" t="n">
-        <v>6.5</v>
+        <v>15.5</v>
       </c>
       <c r="J726" t="n">
-        <v>0.6590181430096052</v>
+        <v>0.814083597300198</v>
       </c>
       <c r="K726" t="n">
-        <v>0.1970117395944503</v>
+        <v>0.12236536058798</v>
       </c>
       <c r="L726" t="n">
-        <v>0.1439701173959445</v>
+        <v>0.0635510421118219</v>
       </c>
       <c r="M726" t="n">
-        <v>0.06859782174830364</v>
+        <v>0.01518601250846574</v>
       </c>
       <c r="N726" t="n">
         <v>1</v>
       </c>
       <c r="O726" t="n">
-        <v>0.724276542125901</v>
+        <v>0.7450177560496657</v>
       </c>
       <c r="P726" t="n">
-        <v>0.1909871395307336</v>
+        <v>0.20429245166319</v>
       </c>
       <c r="Q726" t="n">
-        <v>0.08473631834336544</v>
+        <v>0.05068979228714423</v>
       </c>
       <c r="R726" t="n">
         <v>1</v>
       </c>
       <c r="S726" t="n">
-        <v>0.06525839911629583</v>
+        <v>-0.06906584125053228</v>
       </c>
       <c r="T726" t="n">
         <v>1</v>
       </c>
       <c r="U726" t="n">
-        <v>0.06525839911629583</v>
+        <v>-0.06906584125053228</v>
       </c>
       <c r="V726" t="n">
-        <v>0.724276542125901</v>
+        <v>0.7450177560496657</v>
       </c>
       <c r="W726" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="X726" t="inlineStr">
         <is>
@@ -72813,7 +72817,7 @@
       </c>
       <c r="Y726" t="inlineStr"/>
       <c r="Z726" t="n">
-        <v>4.753064807701225</v>
+        <v>4.101600921665945</v>
       </c>
       <c r="AA726" t="inlineStr">
         <is>
@@ -72825,29 +72829,27 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC726" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC726" t="inlineStr"/>
       <c r="AD726" t="inlineStr"/>
       <c r="AE726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" s="1" t="inlineStr">
         <is>
-          <t>QiBthjLU</t>
+          <t>8Ohqd6Bs</t>
         </is>
       </c>
       <c r="B727" s="2" t="n">
-        <v>45635.70833333334</v>
+        <v>45630.70833333334</v>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E727" t="n">
@@ -72857,55 +72859,55 @@
         <v>1481</v>
       </c>
       <c r="G727" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="H727" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I727" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="J727" t="n">
-        <v>0.5492570945708048</v>
+        <v>0.3042084168336673</v>
       </c>
       <c r="K727" t="n">
-        <v>0.292373776494613</v>
+        <v>0.2857715430861724</v>
       </c>
       <c r="L727" t="n">
-        <v>0.158369128934582</v>
+        <v>0.4100200400801604</v>
       </c>
       <c r="M727" t="n">
-        <v>0.05239365643989924</v>
+        <v>0.06039355688724557</v>
       </c>
       <c r="N727" t="n">
         <v>0</v>
       </c>
       <c r="O727" t="n">
-        <v>0.3598997462383696</v>
+        <v>0.110783219908732</v>
       </c>
       <c r="P727" t="n">
-        <v>0.4188406453191296</v>
+        <v>0.5282088013633487</v>
       </c>
       <c r="Q727" t="n">
-        <v>0.2212596084425009</v>
+        <v>0.3610079787279193</v>
       </c>
       <c r="R727" t="n">
         <v>1</v>
       </c>
       <c r="S727" t="n">
-        <v>0.1264668688245165</v>
+        <v>0.2424372582771763</v>
       </c>
       <c r="T727" t="n">
         <v>0</v>
       </c>
       <c r="U727" t="n">
-        <v>0.1264668688245165</v>
+        <v>0.2424372582771763</v>
       </c>
       <c r="V727" t="n">
-        <v>0.4188406453191296</v>
+        <v>0.5282088013633487</v>
       </c>
       <c r="W727" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X727" t="inlineStr">
         <is>
@@ -72914,7 +72916,7 @@
       </c>
       <c r="Y727" t="inlineStr"/>
       <c r="Z727" t="n">
-        <v>2.748641734906788</v>
+        <v>4.621827011929301</v>
       </c>
       <c r="AA727" t="inlineStr">
         <is>
@@ -72926,29 +72928,27 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC727" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC727" t="inlineStr"/>
       <c r="AD727" t="inlineStr"/>
       <c r="AE727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" s="1" t="inlineStr">
         <is>
-          <t>GjcexCK8</t>
+          <t>Cda5RZlg</t>
         </is>
       </c>
       <c r="B728" s="2" t="n">
-        <v>45639.70833333334</v>
+        <v>45632.70833333334</v>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E728" t="n">
@@ -72958,55 +72958,55 @@
         <v>1481</v>
       </c>
       <c r="G728" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="H728" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I728" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="J728" t="n">
-        <v>0.323051271363068</v>
+        <v>0.5105415460934271</v>
       </c>
       <c r="K728" t="n">
-        <v>0.3022092538557732</v>
+        <v>0.2906159570070277</v>
       </c>
       <c r="L728" t="n">
-        <v>0.3747394747811589</v>
+        <v>0.1988424968995453</v>
       </c>
       <c r="M728" t="n">
-        <v>0.06740823136818674</v>
+        <v>0.05875916402232173</v>
       </c>
       <c r="N728" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O728" t="n">
-        <v>0.3041696802322068</v>
+        <v>0.470816289965619</v>
       </c>
       <c r="P728" t="n">
-        <v>0.106062395503738</v>
+        <v>0.4081380208780662</v>
       </c>
       <c r="Q728" t="n">
-        <v>0.5897679242640552</v>
+        <v>0.121045689156315</v>
       </c>
       <c r="R728" t="n">
         <v>1</v>
       </c>
       <c r="S728" t="n">
-        <v>0.2150284494828963</v>
+        <v>-0.03972525612780808</v>
       </c>
       <c r="T728" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U728" t="n">
-        <v>0.2150284494828963</v>
+        <v>-0.03972525612780808</v>
       </c>
       <c r="V728" t="n">
-        <v>0.5897679242640552</v>
+        <v>0.470816289965619</v>
       </c>
       <c r="W728" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="X728" t="inlineStr">
         <is>
@@ -73015,7 +73015,7 @@
       </c>
       <c r="Y728" t="inlineStr"/>
       <c r="Z728" t="n">
-        <v>5.160469337310484</v>
+        <v>4.119642537199166</v>
       </c>
       <c r="AA728" t="inlineStr">
         <is>
@@ -73034,20 +73034,20 @@
     <row r="729">
       <c r="A729" s="1" t="inlineStr">
         <is>
-          <t>6oTld2Xo</t>
+          <t>txiMNilI</t>
         </is>
       </c>
       <c r="B729" s="2" t="n">
-        <v>45640.41666666666</v>
+        <v>45633.41666666666</v>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E729" t="n">
@@ -73057,55 +73057,55 @@
         <v>1481</v>
       </c>
       <c r="G729" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="H729" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="I729" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J729" t="n">
-        <v>0.3485254691689008</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="K729" t="n">
-        <v>0.2895442359249329</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="L729" t="n">
-        <v>0.3619302949061662</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="M729" t="n">
-        <v>0.06267806267806275</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N729" t="n">
         <v>1</v>
       </c>
       <c r="O729" t="n">
-        <v>0.4598616416606767</v>
+        <v>0.4604580809196993</v>
       </c>
       <c r="P729" t="n">
-        <v>0.1655833690832157</v>
+        <v>0.3958700510049712</v>
       </c>
       <c r="Q729" t="n">
-        <v>0.3745549892561075</v>
+        <v>0.1436718680753295</v>
       </c>
       <c r="R729" t="n">
         <v>1</v>
       </c>
       <c r="S729" t="n">
-        <v>0.1113361724917759</v>
+        <v>-0.06585770855398487</v>
       </c>
       <c r="T729" t="n">
         <v>1</v>
       </c>
       <c r="U729" t="n">
-        <v>0.1113361724917759</v>
+        <v>-0.06585770855398487</v>
       </c>
       <c r="V729" t="n">
-        <v>0.4598616416606767</v>
+        <v>0.4604580809196993</v>
       </c>
       <c r="W729" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="X729" t="inlineStr">
         <is>
@@ -73114,7 +73114,7 @@
       </c>
       <c r="Y729" t="inlineStr"/>
       <c r="Z729" t="n">
-        <v>3.017842023398191</v>
+        <v>4.029008208047369</v>
       </c>
       <c r="AA729" t="inlineStr">
         <is>
@@ -73126,29 +73126,27 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC729" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC729" t="inlineStr"/>
       <c r="AD729" t="inlineStr"/>
       <c r="AE729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" s="1" t="inlineStr">
         <is>
-          <t>AgA9E8S1</t>
+          <t>hGKvtZ3n</t>
         </is>
       </c>
       <c r="B730" s="2" t="n">
-        <v>45640.51041666666</v>
+        <v>45633.51041666666</v>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E730" t="n">
@@ -73158,55 +73156,55 @@
         <v>1481</v>
       </c>
       <c r="G730" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="H730" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="I730" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J730" t="n">
-        <v>0.4063908234330192</v>
+        <v>0.2172422391223039</v>
       </c>
       <c r="K730" t="n">
-        <v>0.3015157722244981</v>
+        <v>0.2294289988779454</v>
       </c>
       <c r="L730" t="n">
-        <v>0.2920934043424825</v>
+        <v>0.5533287619997507</v>
       </c>
       <c r="M730" t="n">
-        <v>0.06986325385694259</v>
+        <v>0.06308461535912735</v>
       </c>
       <c r="N730" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O730" t="n">
-        <v>0.3330528714185551</v>
+        <v>0.1031163620529184</v>
       </c>
       <c r="P730" t="n">
-        <v>0.3503192469913491</v>
+        <v>0.05365222444513004</v>
       </c>
       <c r="Q730" t="n">
-        <v>0.3166278815900957</v>
+        <v>0.8432314135019515</v>
       </c>
       <c r="R730" t="n">
         <v>1</v>
       </c>
       <c r="S730" t="n">
-        <v>0.04880347476685104</v>
+        <v>0.2899026515022008</v>
       </c>
       <c r="T730" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U730" t="n">
-        <v>0.04880347476685104</v>
+        <v>0.2899026515022008</v>
       </c>
       <c r="V730" t="n">
-        <v>0.3503192469913491</v>
+        <v>0.8432314135019515</v>
       </c>
       <c r="W730" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="X730" t="inlineStr">
         <is>
@@ -73215,7 +73213,7 @@
       </c>
       <c r="Y730" t="inlineStr"/>
       <c r="Z730" t="n">
-        <v>3.065293411174305</v>
+        <v>7.378274868142076</v>
       </c>
       <c r="AA730" t="inlineStr">
         <is>
@@ -73234,20 +73232,20 @@
     <row r="731">
       <c r="A731" s="1" t="inlineStr">
         <is>
-          <t>lvM0GUck</t>
+          <t>bTkuvDYb</t>
         </is>
       </c>
       <c r="B731" s="2" t="n">
-        <v>45640.60416666666</v>
+        <v>45633.60416666666</v>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E731" t="n">
@@ -73257,55 +73255,55 @@
         <v>1481</v>
       </c>
       <c r="G731" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="H731" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I731" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J731" t="n">
-        <v>0.4266958424507659</v>
+        <v>0.4179104477611941</v>
       </c>
       <c r="K731" t="n">
-        <v>0.2888402625820569</v>
+        <v>0.3134328358208956</v>
       </c>
       <c r="L731" t="n">
-        <v>0.2844638949671772</v>
+        <v>0.2686567164179105</v>
       </c>
       <c r="M731" t="n">
-        <v>0.06526806526806528</v>
+        <v>0.06349206349206327</v>
       </c>
       <c r="N731" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O731" t="n">
-        <v>0.4464053938417443</v>
+        <v>0.3289740228075826</v>
       </c>
       <c r="P731" t="n">
-        <v>0.2293411239659109</v>
+        <v>0.4829840511017798</v>
       </c>
       <c r="Q731" t="n">
-        <v>0.324253482192345</v>
+        <v>0.1880419260906376</v>
       </c>
       <c r="R731" t="n">
         <v>1</v>
       </c>
       <c r="S731" t="n">
-        <v>0.01970955139097841</v>
+        <v>0.1695512152808842</v>
       </c>
       <c r="T731" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U731" t="n">
-        <v>0.01970955139097841</v>
+        <v>0.1695512152808842</v>
       </c>
       <c r="V731" t="n">
-        <v>0.4464053938417443</v>
+        <v>0.4829840511017798</v>
       </c>
       <c r="W731" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="X731" t="inlineStr">
         <is>
@@ -73314,7 +73312,7 @@
       </c>
       <c r="Y731" t="inlineStr"/>
       <c r="Z731" t="n">
-        <v>2.929535397086447</v>
+        <v>4.226110447140574</v>
       </c>
       <c r="AA731" t="inlineStr">
         <is>
@@ -73326,24 +73324,22 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC731" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC731" t="inlineStr"/>
       <c r="AD731" t="inlineStr"/>
       <c r="AE731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" s="1" t="inlineStr">
         <is>
-          <t>lGwEPYz3</t>
+          <t>YBmEPDJ5</t>
         </is>
       </c>
       <c r="B732" s="2" t="n">
-        <v>45640.70833333334</v>
+        <v>45633.70833333334</v>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -73358,55 +73354,55 @@
         <v>1481</v>
       </c>
       <c r="G732" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="H732" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I732" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="J732" t="n">
-        <v>0.1557251908396947</v>
+        <v>0.2069849407241269</v>
       </c>
       <c r="K732" t="n">
-        <v>0.233587786259542</v>
+        <v>0.2451137455943608</v>
       </c>
       <c r="L732" t="n">
-        <v>0.6106870229007634</v>
+        <v>0.5479013136815124</v>
       </c>
       <c r="M732" t="n">
-        <v>0.0702614379084967</v>
+        <v>0.07361541107671132</v>
       </c>
       <c r="N732" t="n">
         <v>2</v>
       </c>
       <c r="O732" t="n">
-        <v>0.09734271630283801</v>
+        <v>0.08935367738988731</v>
       </c>
       <c r="P732" t="n">
-        <v>0.3103618040799995</v>
+        <v>0.3402662702026921</v>
       </c>
       <c r="Q732" t="n">
-        <v>0.5922954796171626</v>
+        <v>0.5703800524074205</v>
       </c>
       <c r="R732" t="n">
         <v>1</v>
       </c>
       <c r="S732" t="n">
-        <v>-0.01839154328360082</v>
+        <v>0.02247873872590811</v>
       </c>
       <c r="T732" t="n">
         <v>2</v>
       </c>
       <c r="U732" t="n">
-        <v>-0.01839154328360082</v>
+        <v>0.02247873872590811</v>
       </c>
       <c r="V732" t="n">
-        <v>0.5922954796171626</v>
+        <v>0.5703800524074205</v>
       </c>
       <c r="W732" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="X732" t="inlineStr">
         <is>
@@ -73415,7 +73411,7 @@
       </c>
       <c r="Y732" t="inlineStr"/>
       <c r="Z732" t="n">
-        <v>4.538881431724143</v>
+        <v>3.743119093923697</v>
       </c>
       <c r="AA732" t="inlineStr">
         <is>
@@ -73427,27 +73423,29 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="AC732" t="inlineStr"/>
+      <c r="AC732" t="n">
+        <v>1</v>
+      </c>
       <c r="AD732" t="inlineStr"/>
       <c r="AE732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" s="1" t="inlineStr">
         <is>
-          <t>Qs6LJrmp</t>
+          <t>x4pVLVIU</t>
         </is>
       </c>
       <c r="B733" s="2" t="n">
-        <v>45641.41666666666</v>
+        <v>45634.41666666666</v>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E733" t="n">
@@ -73457,55 +73455,55 @@
         <v>1481</v>
       </c>
       <c r="G733" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="H733" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="I733" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="J733" t="n">
-        <v>0.6479959539764825</v>
+        <v>0.2357633092190688</v>
       </c>
       <c r="K733" t="n">
-        <v>0.2275888228600329</v>
+        <v>0.3042107215729921</v>
       </c>
       <c r="L733" t="n">
-        <v>0.1244152231634846</v>
+        <v>0.4600259692079393</v>
       </c>
       <c r="M733" t="n">
-        <v>0.07168021680216796</v>
+        <v>0.06038552321007074</v>
       </c>
       <c r="N733" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O733" t="n">
-        <v>0.8065540589965901</v>
+        <v>0.3019674066521585</v>
       </c>
       <c r="P733" t="n">
-        <v>0.1075162629697439</v>
+        <v>0.1851173235850529</v>
       </c>
       <c r="Q733" t="n">
-        <v>0.08592967803366615</v>
+        <v>0.5129152697627886</v>
       </c>
       <c r="R733" t="n">
         <v>1</v>
       </c>
       <c r="S733" t="n">
-        <v>0.1585581050201076</v>
+        <v>0.05288930055484931</v>
       </c>
       <c r="T733" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U733" t="n">
-        <v>0.1585581050201076</v>
+        <v>0.05288930055484931</v>
       </c>
       <c r="V733" t="n">
-        <v>0.8065540589965901</v>
+        <v>0.5129152697627886</v>
       </c>
       <c r="W733" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="X733" t="inlineStr">
         <is>
@@ -73514,7 +73512,7 @@
       </c>
       <c r="Y733" t="inlineStr"/>
       <c r="Z733" t="n">
-        <v>7.057348016220163</v>
+        <v>4.4880086104244</v>
       </c>
       <c r="AA733" t="inlineStr">
         <is>
@@ -73533,20 +73531,20 @@
     <row r="734">
       <c r="A734" s="1" t="inlineStr">
         <is>
-          <t>MTyMNC5F</t>
+          <t>SYQn9hZO</t>
         </is>
       </c>
       <c r="B734" s="2" t="n">
-        <v>45641.51041666666</v>
+        <v>45634.51041666666</v>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E734" t="n">
@@ -73556,55 +73554,55 @@
         <v>1481</v>
       </c>
       <c r="G734" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H734" t="n">
         <v>3.5</v>
       </c>
-      <c r="H734" t="n">
-        <v>3.1</v>
-      </c>
       <c r="I734" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J734" t="n">
-        <v>0.2688214426487978</v>
+        <v>0.4569015166058744</v>
       </c>
       <c r="K734" t="n">
-        <v>0.303508080409933</v>
+        <v>0.2676137454405835</v>
       </c>
       <c r="L734" t="n">
-        <v>0.4276704769412692</v>
+        <v>0.2754847379535419</v>
       </c>
       <c r="M734" t="n">
-        <v>0.06284038542103065</v>
+        <v>0.06763681082188988</v>
       </c>
       <c r="N734" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O734" t="n">
-        <v>0.1651261126596817</v>
+        <v>0.3173149807235573</v>
       </c>
       <c r="P734" t="n">
-        <v>0.2397973370757538</v>
+        <v>0.531035715198538</v>
       </c>
       <c r="Q734" t="n">
-        <v>0.5950765502645645</v>
+        <v>0.1516493040779048</v>
       </c>
       <c r="R734" t="n">
         <v>1</v>
       </c>
       <c r="S734" t="n">
-        <v>0.1674060733232953</v>
+        <v>0.2634219697579545</v>
       </c>
       <c r="T734" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U734" t="n">
-        <v>0.1674060733232953</v>
+        <v>0.2634219697579545</v>
       </c>
       <c r="V734" t="n">
-        <v>0.5950765502645645</v>
+        <v>0.531035715198538</v>
       </c>
       <c r="W734" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="X734" t="inlineStr">
         <is>
@@ -73613,7 +73611,7 @@
       </c>
       <c r="Y734" t="inlineStr"/>
       <c r="Z734" t="n">
-        <v>5.206919814814939</v>
+        <v>4.646562507987207</v>
       </c>
       <c r="AA734" t="inlineStr">
         <is>
@@ -73632,20 +73630,20 @@
     <row r="735">
       <c r="A735" s="1" t="inlineStr">
         <is>
-          <t>CIj4zjkL</t>
+          <t>6ggmxi3B</t>
         </is>
       </c>
       <c r="B735" s="2" t="n">
-        <v>45641.60416666666</v>
+        <v>45634.60416666666</v>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E735" t="n">
@@ -73655,55 +73653,55 @@
         <v>1481</v>
       </c>
       <c r="G735" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="H735" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="I735" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="J735" t="n">
-        <v>0.6380263717566993</v>
+        <v>0.4564841498559078</v>
       </c>
       <c r="K735" t="n">
-        <v>0.2360697575499787</v>
+        <v>0.2835734870317003</v>
       </c>
       <c r="L735" t="n">
-        <v>0.125903870693322</v>
+        <v>0.2599423631123919</v>
       </c>
       <c r="M735" t="n">
-        <v>0.05900900900900896</v>
+        <v>0.06861295885686136</v>
       </c>
       <c r="N735" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O735" t="n">
-        <v>0.7493405423687598</v>
+        <v>0.2480680460289752</v>
       </c>
       <c r="P735" t="n">
-        <v>0.1120255919790001</v>
+        <v>0.4397676664598044</v>
       </c>
       <c r="Q735" t="n">
-        <v>0.1386338656522401</v>
+        <v>0.3121642875112202</v>
       </c>
       <c r="R735" t="n">
         <v>1</v>
       </c>
       <c r="S735" t="n">
-        <v>0.1113141706120605</v>
+        <v>0.1561941794281042</v>
       </c>
       <c r="T735" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U735" t="n">
-        <v>0.1113141706120605</v>
+        <v>0.1561941794281042</v>
       </c>
       <c r="V735" t="n">
-        <v>0.7493405423687598</v>
+        <v>0.4397676664598044</v>
       </c>
       <c r="W735" t="n">
-        <v>1.48</v>
+        <v>3.3</v>
       </c>
       <c r="X735" t="inlineStr">
         <is>
@@ -73712,7 +73710,7 @@
       </c>
       <c r="Y735" t="inlineStr"/>
       <c r="Z735" t="n">
-        <v>6.556729745726648</v>
+        <v>3.847967081523289</v>
       </c>
       <c r="AA735" t="inlineStr">
         <is>
@@ -73731,20 +73729,20 @@
     <row r="736">
       <c r="A736" s="1" t="inlineStr">
         <is>
-          <t>IeVULjzS</t>
+          <t>6adcTeKt</t>
         </is>
       </c>
       <c r="B736" s="2" t="n">
-        <v>45641.60416666666</v>
+        <v>45634.70833333334</v>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E736" t="n">
@@ -73754,55 +73752,55 @@
         <v>1481</v>
       </c>
       <c r="G736" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="H736" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="I736" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="J736" t="n">
-        <v>0.5220012055455093</v>
+        <v>0.6590181430096052</v>
       </c>
       <c r="K736" t="n">
-        <v>0.2610006027727547</v>
+        <v>0.1970117395944503</v>
       </c>
       <c r="L736" t="n">
-        <v>0.216998191681736</v>
+        <v>0.1439701173959445</v>
       </c>
       <c r="M736" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.06859782174830364</v>
       </c>
       <c r="N736" t="n">
         <v>1</v>
       </c>
       <c r="O736" t="n">
-        <v>0.4690630449137062</v>
+        <v>0.7383883992279784</v>
       </c>
       <c r="P736" t="n">
-        <v>0.2922910835040749</v>
+        <v>0.1901199132018631</v>
       </c>
       <c r="Q736" t="n">
-        <v>0.238645871582219</v>
+        <v>0.07149168757015868</v>
       </c>
       <c r="R736" t="n">
         <v>1</v>
       </c>
       <c r="S736" t="n">
-        <v>-0.05293816063180318</v>
+        <v>0.07937025621837324</v>
       </c>
       <c r="T736" t="n">
         <v>1</v>
       </c>
       <c r="U736" t="n">
-        <v>-0.05293816063180318</v>
+        <v>0.07937025621837324</v>
       </c>
       <c r="V736" t="n">
-        <v>0.4690630449137062</v>
+        <v>0.7383883992279784</v>
       </c>
       <c r="W736" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="X736" t="inlineStr">
         <is>
@@ -73811,7 +73809,7 @@
       </c>
       <c r="Y736" t="inlineStr"/>
       <c r="Z736" t="n">
-        <v>1.688599515661363</v>
+        <v>4.845673869933607</v>
       </c>
       <c r="AA736" t="inlineStr">
         <is>
@@ -73832,20 +73830,20 @@
     <row r="737">
       <c r="A737" s="1" t="inlineStr">
         <is>
-          <t>Y79THMHd</t>
+          <t>QiBthjLU</t>
         </is>
       </c>
       <c r="B737" s="2" t="n">
-        <v>45641.70833333334</v>
+        <v>45635.70833333334</v>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E737" t="n">
@@ -73855,55 +73853,55 @@
         <v>1481</v>
       </c>
       <c r="G737" t="n">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="H737" t="n">
-        <v>8.050000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="I737" t="n">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="J737" t="n">
-        <v>0.814083597300198</v>
+        <v>0.5492570945708048</v>
       </c>
       <c r="K737" t="n">
-        <v>0.12236536058798</v>
+        <v>0.292373776494613</v>
       </c>
       <c r="L737" t="n">
-        <v>0.0635510421118219</v>
+        <v>0.158369128934582</v>
       </c>
       <c r="M737" t="n">
-        <v>0.01518601250846574</v>
+        <v>0.05239365643989924</v>
       </c>
       <c r="N737" t="n">
         <v>1</v>
       </c>
       <c r="O737" t="n">
-        <v>0.7450177560496657</v>
+        <v>0.599763510126182</v>
       </c>
       <c r="P737" t="n">
-        <v>0.20429245166319</v>
+        <v>0.1666878812202979</v>
       </c>
       <c r="Q737" t="n">
-        <v>0.05068979228714423</v>
+        <v>0.2335486086535201</v>
       </c>
       <c r="R737" t="n">
         <v>1</v>
       </c>
       <c r="S737" t="n">
-        <v>-0.06906584125053228</v>
+        <v>0.05050641555537716</v>
       </c>
       <c r="T737" t="n">
         <v>1</v>
       </c>
       <c r="U737" t="n">
-        <v>-0.06906584125053228</v>
+        <v>0.05050641555537716</v>
       </c>
       <c r="V737" t="n">
-        <v>0.7450177560496657</v>
+        <v>0.599763510126182</v>
       </c>
       <c r="W737" t="n">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="X737" t="inlineStr">
         <is>
@@ -73912,7 +73910,7 @@
       </c>
       <c r="Y737" t="inlineStr"/>
       <c r="Z737" t="n">
-        <v>4.101600921665945</v>
+        <v>5.247930713604092</v>
       </c>
       <c r="AA737" t="inlineStr">
         <is>

--- a/data/historial_predicciones.xlsx
+++ b/data/historial_predicciones.xlsx
@@ -66209,96 +66209,96 @@
     <row r="658">
       <c r="A658" s="1" t="inlineStr">
         <is>
-          <t>WG42zbvo</t>
+          <t>GALX3NzI</t>
         </is>
       </c>
       <c r="B658" s="2" t="n">
-        <v>45632.625</v>
+        <v>45632.6875</v>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F658" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G658" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="H658" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I658" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="J658" t="n">
-        <v>0.5815383774327575</v>
+        <v>0.5474785570898474</v>
       </c>
       <c r="K658" t="n">
-        <v>0.254619505794883</v>
+        <v>0.2630938621570655</v>
       </c>
       <c r="L658" t="n">
-        <v>0.1638421167723595</v>
+        <v>0.1894275807530872</v>
       </c>
       <c r="M658" t="n">
-        <v>0.06146726436581496</v>
+        <v>0.05581245985870265</v>
       </c>
       <c r="N658" t="n">
         <v>1</v>
       </c>
       <c r="O658" t="n">
-        <v>0.4804724632828781</v>
+        <v>0.4770320642447111</v>
       </c>
       <c r="P658" t="n">
-        <v>0.3335201795538003</v>
+        <v>0.3819069293617366</v>
       </c>
       <c r="Q658" t="n">
-        <v>0.1860073571633216</v>
+        <v>0.1410610063935523</v>
       </c>
       <c r="R658" t="n">
         <v>1</v>
       </c>
       <c r="S658" t="n">
-        <v>-0.1010659141498794</v>
+        <v>-0.07044649284513627</v>
       </c>
       <c r="T658" t="n">
         <v>1</v>
       </c>
       <c r="U658" t="n">
-        <v>-0.1010659141498794</v>
+        <v>-0.07044649284513627</v>
       </c>
       <c r="V658" t="n">
-        <v>0.4804724632828781</v>
+        <v>0.4770320642447111</v>
       </c>
       <c r="W658" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="X658" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y658" t="inlineStr"/>
       <c r="Z658" t="n">
-        <v>0.8001924701752869</v>
+        <v>7.155480963670667</v>
       </c>
       <c r="AA658" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB658" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC658" t="inlineStr"/>
@@ -66308,96 +66308,96 @@
     <row r="659">
       <c r="A659" s="1" t="inlineStr">
         <is>
-          <t>riWEq2Hb</t>
+          <t>rcNP5q65</t>
         </is>
       </c>
       <c r="B659" s="2" t="n">
-        <v>45632.70833333334</v>
+        <v>45633.47916666666</v>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F659" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G659" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H659" t="n">
         <v>7</v>
       </c>
-      <c r="H659" t="n">
-        <v>5.5</v>
-      </c>
       <c r="I659" t="n">
-        <v>1.38</v>
+        <v>11</v>
       </c>
       <c r="J659" t="n">
-        <v>0.1361434977578475</v>
+        <v>0.7780921584478578</v>
       </c>
       <c r="K659" t="n">
-        <v>0.1732735426008968</v>
+        <v>0.1356103476151981</v>
       </c>
       <c r="L659" t="n">
-        <v>0.6905829596412556</v>
+        <v>0.08629749393694423</v>
       </c>
       <c r="M659" t="n">
-        <v>0.04931300583474507</v>
+        <v>0.05343836491377463</v>
       </c>
       <c r="N659" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O659" t="n">
-        <v>0.04294644528026133</v>
+        <v>0.5962981054319098</v>
       </c>
       <c r="P659" t="n">
-        <v>0.1930784782716471</v>
+        <v>0.3835696441520474</v>
       </c>
       <c r="Q659" t="n">
-        <v>0.7639750764480915</v>
+        <v>0.02013225041604288</v>
       </c>
       <c r="R659" t="n">
         <v>1</v>
       </c>
       <c r="S659" t="n">
-        <v>0.07339211680683588</v>
+        <v>-0.1817940530159481</v>
       </c>
       <c r="T659" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U659" t="n">
-        <v>0.07339211680683588</v>
+        <v>-0.1817940530159481</v>
       </c>
       <c r="V659" t="n">
-        <v>0.7639750764480915</v>
+        <v>0.5962981054319098</v>
       </c>
       <c r="W659" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="X659" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y659" t="inlineStr"/>
       <c r="Z659" t="n">
-        <v>8.021738302704961</v>
+        <v>8.944471581478647</v>
       </c>
       <c r="AA659" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB659" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC659" t="inlineStr"/>
@@ -66407,195 +66407,197 @@
     <row r="660">
       <c r="A660" s="1" t="inlineStr">
         <is>
-          <t>6oLxxBFk</t>
+          <t>Yo0boFKj</t>
         </is>
       </c>
       <c r="B660" s="2" t="n">
-        <v>45633.54166666666</v>
+        <v>45633.47916666666</v>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F660" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G660" t="n">
-        <v>1.73</v>
+        <v>1.1</v>
       </c>
       <c r="H660" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="I660" t="n">
-        <v>4.75</v>
+        <v>19</v>
       </c>
       <c r="J660" t="n">
-        <v>0.5477819635580841</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="K660" t="n">
-        <v>0.2527100791881294</v>
+        <v>0.08636363636363636</v>
       </c>
       <c r="L660" t="n">
-        <v>0.1995079572537864</v>
+        <v>0.05</v>
       </c>
       <c r="M660" t="n">
-        <v>0.05522766453706529</v>
+        <v>0.05263157894736836</v>
       </c>
       <c r="N660" t="n">
         <v>1</v>
       </c>
       <c r="O660" t="n">
-        <v>0.4825205181865818</v>
+        <v>0.665719857726229</v>
       </c>
       <c r="P660" t="n">
-        <v>0.3278760509161175</v>
+        <v>0.3180530561731942</v>
       </c>
       <c r="Q660" t="n">
-        <v>0.1896034308973007</v>
+        <v>0.01622708610057682</v>
       </c>
       <c r="R660" t="n">
         <v>1</v>
       </c>
       <c r="S660" t="n">
-        <v>-0.06526144537150225</v>
+        <v>-0.1979165059101347</v>
       </c>
       <c r="T660" t="n">
         <v>1</v>
       </c>
       <c r="U660" t="n">
-        <v>-0.06526144537150225</v>
+        <v>-0.1979165059101347</v>
       </c>
       <c r="V660" t="n">
-        <v>0.4825205181865818</v>
+        <v>0.665719857726229</v>
       </c>
       <c r="W660" t="n">
-        <v>1.73</v>
+        <v>1.1</v>
       </c>
       <c r="X660" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y660" t="inlineStr"/>
       <c r="Z660" t="n">
-        <v>2.325484735356015</v>
+        <v>7.489348399420076</v>
       </c>
       <c r="AA660" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB660" t="inlineStr">
         <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="AC660" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="AC660" t="n">
+        <v>1</v>
+      </c>
       <c r="AD660" t="inlineStr"/>
       <c r="AE660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" s="1" t="inlineStr">
         <is>
-          <t>dzY6oOnn</t>
+          <t>6Dwubh4d</t>
         </is>
       </c>
       <c r="B661" s="2" t="n">
-        <v>45633.625</v>
+        <v>45633.47916666666</v>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F661" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G661" t="n">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="H661" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I661" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="J661" t="n">
-        <v>0.6143667296786388</v>
+        <v>0.2968388589051658</v>
       </c>
       <c r="K661" t="n">
-        <v>0.2410207939508506</v>
+        <v>0.2713955281418658</v>
       </c>
       <c r="L661" t="n">
-        <v>0.1446124763705104</v>
+        <v>0.4317656129529684</v>
       </c>
       <c r="M661" t="n">
-        <v>0.06385118149824054</v>
+        <v>0.05275974025974017</v>
       </c>
       <c r="N661" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O661" t="n">
-        <v>0.563587110025252</v>
+        <v>0.1651058897515597</v>
       </c>
       <c r="P661" t="n">
-        <v>0.292788936882222</v>
+        <v>0.3192707382463268</v>
       </c>
       <c r="Q661" t="n">
-        <v>0.143623953092526</v>
+        <v>0.5156233720021135</v>
       </c>
       <c r="R661" t="n">
         <v>1</v>
       </c>
       <c r="S661" t="n">
-        <v>-0.05077961965338684</v>
+        <v>0.08385775904914511</v>
       </c>
       <c r="T661" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U661" t="n">
-        <v>-0.05077961965338684</v>
+        <v>0.08385775904914511</v>
       </c>
       <c r="V661" t="n">
-        <v>0.563587110025252</v>
+        <v>0.5156233720021135</v>
       </c>
       <c r="W661" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="X661" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y661" t="inlineStr"/>
       <c r="Z661" t="n">
-        <v>3.784920629822898</v>
+        <v>7.734350580031703</v>
       </c>
       <c r="AA661" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB661" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC661" t="inlineStr"/>
@@ -66605,195 +66607,197 @@
     <row r="662">
       <c r="A662" s="1" t="inlineStr">
         <is>
-          <t>CWNVuKGN</t>
+          <t>0hhp9ICc</t>
         </is>
       </c>
       <c r="B662" s="2" t="n">
-        <v>45633.70833333334</v>
+        <v>45633.47916666666</v>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F662" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G662" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="H662" t="n">
         <v>4</v>
       </c>
       <c r="I662" t="n">
-        <v>1.67</v>
+        <v>6</v>
       </c>
       <c r="J662" t="n">
-        <v>0.1906936911218955</v>
+        <v>0.6075949367088608</v>
       </c>
       <c r="K662" t="n">
-        <v>0.2383671139023694</v>
+        <v>0.2354430379746835</v>
       </c>
       <c r="L662" t="n">
-        <v>0.5709391949757351</v>
+        <v>0.1569620253164557</v>
       </c>
       <c r="M662" t="n">
-        <v>0.04880239520958085</v>
+        <v>0.06182795698924726</v>
       </c>
       <c r="N662" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O662" t="n">
-        <v>0.09818405001227695</v>
+        <v>0.4331605211726641</v>
       </c>
       <c r="P662" t="n">
-        <v>0.2665387478861541</v>
+        <v>0.367152397129698</v>
       </c>
       <c r="Q662" t="n">
-        <v>0.6352772021015688</v>
+        <v>0.1996870816976379</v>
       </c>
       <c r="R662" t="n">
         <v>1</v>
       </c>
       <c r="S662" t="n">
-        <v>0.06433800712583371</v>
+        <v>-0.1744344155361967</v>
       </c>
       <c r="T662" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U662" t="n">
-        <v>0.06433800712583371</v>
+        <v>-0.1744344155361967</v>
       </c>
       <c r="V662" t="n">
-        <v>0.6352772021015688</v>
+        <v>0.4331605211726641</v>
       </c>
       <c r="W662" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="X662" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y662" t="inlineStr"/>
       <c r="Z662" t="n">
-        <v>6.670410622066473</v>
+        <v>4.873055863192471</v>
       </c>
       <c r="AA662" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB662" t="inlineStr">
         <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="AC662" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="AC662" t="n">
+        <v>1</v>
+      </c>
       <c r="AD662" t="inlineStr"/>
       <c r="AE662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" s="1" t="inlineStr">
         <is>
-          <t>r5Bmb1Wi</t>
+          <t>MLLRLed3</t>
         </is>
       </c>
       <c r="B663" s="2" t="n">
-        <v>45634.45833333334</v>
+        <v>45633.47916666666</v>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E663" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F663" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G663" t="n">
-        <v>1.36</v>
+        <v>5.5</v>
       </c>
       <c r="H663" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="I663" t="n">
-        <v>7.5</v>
+        <v>1.62</v>
       </c>
       <c r="J663" t="n">
-        <v>0.6942607775720708</v>
+        <v>0.173308371222252</v>
       </c>
       <c r="K663" t="n">
-        <v>0.1798466014281936</v>
+        <v>0.2382990104305964</v>
       </c>
       <c r="L663" t="n">
-        <v>0.1258926209997355</v>
+        <v>0.5883926183471516</v>
       </c>
       <c r="M663" t="n">
-        <v>0.05910364145658265</v>
+        <v>0.04910213243546568</v>
       </c>
       <c r="N663" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O663" t="n">
-        <v>0.5202932245725481</v>
+        <v>0.07109415026980385</v>
       </c>
       <c r="P663" t="n">
-        <v>0.3268492403763394</v>
+        <v>0.2899550493463746</v>
       </c>
       <c r="Q663" t="n">
-        <v>0.1528575350511125</v>
+        <v>0.6389508003838217</v>
       </c>
       <c r="R663" t="n">
         <v>1</v>
       </c>
       <c r="S663" t="n">
-        <v>-0.1739675529995227</v>
+        <v>0.05055818203667006</v>
       </c>
       <c r="T663" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U663" t="n">
-        <v>-0.1739675529995227</v>
+        <v>0.05055818203667006</v>
       </c>
       <c r="V663" t="n">
-        <v>0.5202932245725481</v>
+        <v>0.6389508003838217</v>
       </c>
       <c r="W663" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="X663" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y663" t="inlineStr"/>
       <c r="Z663" t="n">
-        <v>0</v>
+        <v>9.584262005757326</v>
       </c>
       <c r="AA663" t="inlineStr">
         <is>
-          <t>france</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="AB663" t="inlineStr">
         <is>
-          <t>ligue 1</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="AC663" t="inlineStr"/>
@@ -66803,96 +66807,96 @@
     <row r="664">
       <c r="A664" s="1" t="inlineStr">
         <is>
-          <t>Cp34fJVG</t>
+          <t>YauXaEZq</t>
         </is>
       </c>
       <c r="B664" s="2" t="n">
-        <v>45634.54166666666</v>
+        <v>45633.60416666666</v>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F664" t="n">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="G664" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="H664" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="I664" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="J664" t="n">
-        <v>0.3177057356608479</v>
+        <v>0.2806236080178174</v>
       </c>
       <c r="K664" t="n">
-        <v>0.2932668329177058</v>
+        <v>0.2650334075723831</v>
       </c>
       <c r="L664" t="n">
-        <v>0.3890274314214464</v>
+        <v>0.4543429844097996</v>
       </c>
       <c r="M664" t="n">
-        <v>0.04918890633176343</v>
+        <v>0.04808590102707733</v>
       </c>
       <c r="N664" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O664" t="n">
-        <v>0.2642645865806705</v>
+        <v>0.2045749497706243</v>
       </c>
       <c r="P664" t="n">
-        <v>0.3099809157277156</v>
+        <v>0.4156545937292642</v>
       </c>
       <c r="Q664" t="n">
-        <v>0.4257544976916139</v>
+        <v>0.3797704565001115</v>
       </c>
       <c r="R664" t="n">
         <v>1</v>
       </c>
       <c r="S664" t="n">
-        <v>0.03672706627016759</v>
+        <v>0.150621186156881</v>
       </c>
       <c r="T664" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U664" t="n">
-        <v>0.03672706627016759</v>
+        <v>0.150621186156881</v>
       </c>
       <c r="V664" t="n">
-        <v>0.4257544976916139</v>
+        <v>0.4156545937292642</v>
       </c>
       <c r="W664" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="X664" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="Y664" t="inlineStr"/>
       <c r="Z664" t="n">
-        <v